--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3342" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{62E8FBD5-055D-4212-A059-2346ADF0A5D4}"/>
+  <xr:revisionPtr revIDLastSave="3395" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05980098-7E1F-4D2D-A38C-DD42E7D5A507}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="710" windowWidth="26500" windowHeight="18980" tabRatio="905" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10770" yWindow="1640" windowWidth="18160" windowHeight="17990" tabRatio="905" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="4" r:id="rId1"/>
     <sheet name="Online codes" sheetId="17" r:id="rId2"/>
     <sheet name="Lath" sheetId="7" r:id="rId3"/>
-    <sheet name="Wind class" sheetId="20" r:id="rId4"/>
-    <sheet name="Endlock" sheetId="16" r:id="rId5"/>
-    <sheet name="Bottom lath" sheetId="9" r:id="rId6"/>
+    <sheet name="Bottom lath" sheetId="9" r:id="rId4"/>
+    <sheet name="Wind class" sheetId="20" r:id="rId5"/>
+    <sheet name="Endlock" sheetId="16" r:id="rId6"/>
     <sheet name="Guides" sheetId="12" r:id="rId7"/>
     <sheet name="Axles" sheetId="6" r:id="rId8"/>
     <sheet name="Disc size" sheetId="21" r:id="rId9"/>
@@ -55,6 +55,132 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>robert hyrons</author>
+  </authors>
+  <commentList>
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{85067B68-D384-4989-8BC1-39E5AFD6EDD0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>robert hyrons:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+This will group in to common configerations such as seceurodoor motor opp, seceurodor spring opp or shield. There the physical make up is common.  </t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>robert hyrons</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{42B2D1D3-45D6-4B4F-92A5-C86E44261C2E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>robert hyrons:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+use this data column to match the max lift torque required to spec SB, advised from GFA UK 27/1/2026</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>robert hyrons</author>
+  </authors>
+  <commentList>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{680B1BE3-3686-4262-8DBA-BDEB6ADD9486}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>robert hyrons:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+current load info not verified, needs checking</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{C212F676-8F98-4020-9899-8B9BD0CC5028}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>robert hyrons:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+This is the distance from guide or angle attachment to the endplat outter</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>robert hyrons</author>
@@ -160,65 +286,7 @@
 </comments>
 </file>
 
-<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>robert hyrons</author>
-  </authors>
-  <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{680B1BE3-3686-4262-8DBA-BDEB6ADD9486}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>robert hyrons:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-current load info not verified, needs checking</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{C212F676-8F98-4020-9899-8B9BD0CC5028}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>robert hyrons:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-This is the distance from guide or angle attachment to the endplat outter</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>robert hyrons</author>
@@ -300,13 +368,13 @@
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Rob Hyrons</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{E228288C-211F-475A-BEA2-831A05E3FED9}">
+    <comment ref="E1" authorId="0" shapeId="0" xr:uid="{E228288C-211F-475A-BEA2-831A05E3FED9}">
       <text>
         <r>
           <rPr>
@@ -334,7 +402,7 @@
 </comments>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>robert hyrons</author>
@@ -393,7 +461,7 @@
 </comments>
 </file>
 
-<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>robert hyrons</author>
@@ -427,7 +495,7 @@
 </comments>
 </file>
 
-<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>robert hyrons</author>
@@ -610,7 +678,7 @@
 </comments>
 </file>
 
-<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>robert hyrons</author>
@@ -669,7 +737,7 @@
 </comments>
 </file>
 
-<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>robert hyrons</author>
@@ -696,40 +764,6 @@
           </rPr>
           <t xml:space="preserve">
 needs confirming with supplier</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>robert hyrons</author>
-  </authors>
-  <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{42B2D1D3-45D6-4B4F-92A5-C86E44261C2E}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>robert hyrons:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-use this data column to match the max lift torque required to spec SB, advised from GFA UK 27/1/2026</t>
         </r>
       </text>
     </comment>
@@ -770,7 +804,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2242" uniqueCount="599">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2282" uniqueCount="612">
   <si>
     <t>This over view explaines the working of this file and how it feeds information to the online calculator.</t>
   </si>
@@ -1819,9 +1853,6 @@
     <t>GA55/15GD</t>
   </si>
   <si>
-    <t>MT238M1</t>
-  </si>
-  <si>
     <t>GA65/15GD</t>
   </si>
   <si>
@@ -2567,6 +2598,48 @@
   </si>
   <si>
     <t>GA10/15GD</t>
+  </si>
+  <si>
+    <t>MT281M4</t>
+  </si>
+  <si>
+    <t>Sloping type</t>
+  </si>
+  <si>
+    <t>C section</t>
+  </si>
+  <si>
+    <t>L section</t>
+  </si>
+  <si>
+    <t>2 plates</t>
+  </si>
+  <si>
+    <t>Product class</t>
+  </si>
+  <si>
+    <t>GAEC</t>
+  </si>
+  <si>
+    <t>G=Guide</t>
+  </si>
+  <si>
+    <t xml:space="preserve">B=boxsection </t>
+  </si>
+  <si>
+    <t>EF = flat endplate</t>
+  </si>
+  <si>
+    <t>EC = cranked endplate</t>
+  </si>
+  <si>
+    <t>A = Angle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RA = reveal angle </t>
+  </si>
+  <si>
+    <t>Wind type</t>
   </si>
 </sst>
 </file>
@@ -2578,7 +2651,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2717,6 +2790,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
   </fonts>
   <fills count="16">
     <fill>
@@ -2851,7 +2937,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="146">
+  <cellXfs count="147">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3251,11 +3337,14 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -4701,8 +4790,8 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>69850</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>88928</xdr:rowOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>69878</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="10274017" cy="3179041"/>
     <xdr:pic>
@@ -4726,7 +4815,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="69850" y="4140228"/>
+          <a:off x="69850" y="4673628"/>
           <a:ext cx="10274017" cy="3179041"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6240,15 +6329,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>100</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:colOff>42334</xdr:colOff>
+      <xdr:row>99</xdr:row>
+      <xdr:rowOff>497416</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>711237</xdr:colOff>
+      <xdr:colOff>753571</xdr:colOff>
       <xdr:row>100</xdr:row>
-      <xdr:rowOff>444523</xdr:rowOff>
+      <xdr:rowOff>433939</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6271,7 +6360,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="21825857" y="44196000"/>
+          <a:off x="22489584" y="50789416"/>
           <a:ext cx="711237" cy="444523"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -10738,7 +10827,7 @@
         <v>270</v>
       </c>
       <c r="T1" s="11" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="U1" s="143" t="s">
         <v>272</v>
@@ -11149,10 +11238,10 @@
         <v>284</v>
       </c>
       <c r="H10" s="107" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="N10" s="107" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="Q10" s="59"/>
     </row>
@@ -11269,7 +11358,7 @@
       <c r="F13" s="118"/>
       <c r="G13" s="118"/>
       <c r="H13" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I13" s="118"/>
       <c r="J13" s="118"/>
@@ -11277,7 +11366,7 @@
       <c r="L13" s="118"/>
       <c r="M13" s="118"/>
       <c r="N13" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O13" s="121"/>
       <c r="P13" s="118"/>
@@ -11401,7 +11490,7 @@
     </row>
     <row r="16" spans="1:22" s="64" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>289</v>
@@ -12056,7 +12145,7 @@
       <c r="F28" s="118"/>
       <c r="G28" s="118"/>
       <c r="H28" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I28" s="118"/>
       <c r="J28" s="118"/>
@@ -12064,7 +12153,7 @@
       <c r="L28" s="118"/>
       <c r="M28" s="118"/>
       <c r="N28" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O28" s="121"/>
       <c r="P28" s="118"/>
@@ -12112,7 +12201,7 @@
         <v>59</v>
       </c>
       <c r="N29" s="107" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O29" s="54"/>
       <c r="P29" s="59"/>
@@ -12138,7 +12227,7 @@
       <c r="F30" s="118"/>
       <c r="G30" s="118"/>
       <c r="H30" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I30" s="118"/>
       <c r="J30" s="118"/>
@@ -12146,7 +12235,7 @@
       <c r="L30" s="118"/>
       <c r="M30" s="118"/>
       <c r="N30" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O30" s="121"/>
       <c r="P30" s="118"/>
@@ -12501,7 +12590,7 @@
       <c r="F38" s="118"/>
       <c r="G38" s="118"/>
       <c r="H38" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I38" s="118"/>
       <c r="J38" s="118"/>
@@ -12509,7 +12598,7 @@
       <c r="L38" s="118"/>
       <c r="M38" s="118"/>
       <c r="N38" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O38" s="121"/>
       <c r="P38" s="118"/>
@@ -12520,7 +12609,7 @@
     </row>
     <row r="39" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>319</v>
@@ -12568,7 +12657,7 @@
     </row>
     <row r="40" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>319</v>
@@ -12617,7 +12706,7 @@
     </row>
     <row r="41" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>319</v>
@@ -12666,7 +12755,7 @@
     </row>
     <row r="42" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>319</v>
@@ -12945,7 +13034,7 @@
       <c r="F48" s="118"/>
       <c r="G48" s="118"/>
       <c r="H48" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I48" s="118"/>
       <c r="J48" s="118"/>
@@ -12953,7 +13042,7 @@
       <c r="L48" s="118"/>
       <c r="M48" s="118"/>
       <c r="N48" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O48" s="121"/>
       <c r="P48" s="118"/>
@@ -13148,7 +13237,7 @@
       <c r="F53" s="118"/>
       <c r="G53" s="118"/>
       <c r="H53" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I53" s="118"/>
       <c r="J53" s="118"/>
@@ -13156,7 +13245,7 @@
       <c r="L53" s="118"/>
       <c r="M53" s="118"/>
       <c r="N53" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O53" s="121"/>
       <c r="P53" s="118"/>
@@ -13327,7 +13416,7 @@
       <c r="F57" s="118"/>
       <c r="G57" s="118"/>
       <c r="H57" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I57" s="118"/>
       <c r="J57" s="118"/>
@@ -13335,7 +13424,7 @@
       <c r="L57" s="118"/>
       <c r="M57" s="118"/>
       <c r="N57" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O57" s="121"/>
       <c r="P57" s="118"/>
@@ -13700,7 +13789,7 @@
       <c r="F65" s="118"/>
       <c r="G65" s="118"/>
       <c r="H65" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I65" s="118"/>
       <c r="J65" s="118"/>
@@ -13708,7 +13797,7 @@
       <c r="L65" s="118"/>
       <c r="M65" s="118"/>
       <c r="N65" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O65" s="121"/>
       <c r="P65" s="118"/>
@@ -14077,7 +14166,7 @@
       <c r="F72" s="123"/>
       <c r="G72" s="118"/>
       <c r="H72" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I72" s="118"/>
       <c r="J72" s="118"/>
@@ -14085,7 +14174,7 @@
       <c r="L72" s="118"/>
       <c r="M72" s="118"/>
       <c r="N72" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O72" s="121"/>
       <c r="P72" s="118"/>
@@ -14110,7 +14199,7 @@
         <v>342</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F73" s="29">
         <f>Chaindrive!L20</f>
@@ -14165,7 +14254,7 @@
         <v>342</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F74" s="29">
         <f>Chaindrive!L21</f>
@@ -14220,7 +14309,7 @@
         <v>475</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F75" s="29">
         <f>Chaindrive!L22</f>
@@ -14275,7 +14364,7 @@
         <v>475</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F76" s="29">
         <f>Chaindrive!L23</f>
@@ -14330,7 +14419,7 @@
         <v>712.5</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F77" s="29">
         <f>Chaindrive!L24</f>
@@ -14385,7 +14474,7 @@
         <v>712.5</v>
       </c>
       <c r="E78" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F78" s="29">
         <f>Chaindrive!L25</f>
@@ -14742,7 +14831,7 @@
       <c r="F85" s="123"/>
       <c r="G85" s="118"/>
       <c r="H85" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I85" s="118"/>
       <c r="J85" s="118"/>
@@ -14750,7 +14839,7 @@
       <c r="L85" s="118"/>
       <c r="M85" s="118"/>
       <c r="N85" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O85" s="121"/>
       <c r="P85" s="118"/>
@@ -14775,7 +14864,7 @@
         <v>1140</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F86" s="2">
         <f>Chaindrive!L35</f>
@@ -14836,7 +14925,7 @@
         <v>1900</v>
       </c>
       <c r="E87" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F87" s="2">
         <f>Chaindrive!L37</f>
@@ -14897,7 +14986,7 @@
         <v>3040</v>
       </c>
       <c r="E88" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F88" s="2">
         <f>Chaindrive!L38</f>
@@ -14977,10 +15066,10 @@
         <v>284</v>
       </c>
       <c r="H90" s="107" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="N90" s="107" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O90" s="1"/>
       <c r="R90" s="1"/>
@@ -14991,7 +15080,7 @@
     </row>
     <row r="91" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="B91" s="3" t="s">
         <v>335</v>
@@ -15045,7 +15134,7 @@
         <v>339</v>
       </c>
       <c r="T91" s="64"/>
-      <c r="U91" s="145">
+      <c r="U91" s="144">
         <v>266</v>
       </c>
       <c r="V91" s="64"/>
@@ -15107,7 +15196,7 @@
         <v>341</v>
       </c>
       <c r="T92" s="64"/>
-      <c r="U92" s="145">
+      <c r="U92" s="144">
         <v>280</v>
       </c>
       <c r="V92" s="64"/>
@@ -15169,7 +15258,7 @@
         <v>343</v>
       </c>
       <c r="T93" s="64"/>
-      <c r="U93" s="145">
+      <c r="U93" s="144">
         <v>307</v>
       </c>
       <c r="V93" s="64"/>
@@ -15228,7 +15317,7 @@
         <v>345</v>
       </c>
       <c r="T94" s="64"/>
-      <c r="U94" s="145">
+      <c r="U94" s="144">
         <v>383</v>
       </c>
       <c r="V94" s="64"/>
@@ -15287,7 +15376,7 @@
         <v>347</v>
       </c>
       <c r="T95" s="64"/>
-      <c r="U95" s="145"/>
+      <c r="U95" s="144"/>
       <c r="V95" s="64"/>
     </row>
     <row r="96" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -15341,15 +15430,15 @@
         <v>1100</v>
       </c>
       <c r="S96" s="1" t="s">
-        <v>349</v>
+        <v>371</v>
       </c>
       <c r="T96" s="64"/>
-      <c r="U96" s="145"/>
+      <c r="U96" s="144"/>
       <c r="V96" s="64"/>
     </row>
     <row r="97" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="64" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B97" s="64" t="s">
         <v>335</v>
@@ -15398,15 +15487,15 @@
         <v>1100</v>
       </c>
       <c r="S97" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="T97" s="64"/>
-      <c r="U97" s="145"/>
+      <c r="U97" s="144"/>
       <c r="V97" s="64"/>
     </row>
     <row r="98" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="64" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="B98" s="64" t="s">
         <v>335</v>
@@ -15455,15 +15544,15 @@
         <v>2800</v>
       </c>
       <c r="S98" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="T98" s="64"/>
-      <c r="U98" s="145"/>
+      <c r="U98" s="144"/>
       <c r="V98" s="64"/>
     </row>
     <row r="99" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="64" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B99" s="64" t="s">
         <v>335</v>
@@ -15512,7 +15601,7 @@
         <v>1100</v>
       </c>
       <c r="S99" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="T99" s="64"/>
       <c r="U99" s="124"/>
@@ -15520,7 +15609,7 @@
     </row>
     <row r="100" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="64" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="B100" s="64" t="s">
         <v>335</v>
@@ -15569,7 +15658,7 @@
         <v>2800</v>
       </c>
       <c r="S100" s="1" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="T100" s="64"/>
       <c r="U100" s="124"/>
@@ -15577,7 +15666,7 @@
     </row>
     <row r="101" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="64" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="B101" s="64" t="s">
         <v>335</v>
@@ -15626,7 +15715,7 @@
         <v>2800</v>
       </c>
       <c r="S101" s="1" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="T101" s="64"/>
       <c r="U101" s="124"/>
@@ -15634,7 +15723,7 @@
     </row>
     <row r="102" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="64" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="B102" s="64" t="s">
         <v>335</v>
@@ -15682,16 +15771,18 @@
       <c r="R102" s="1">
         <v>3125</v>
       </c>
-      <c r="S102" s="1"/>
+      <c r="S102" s="1" t="s">
+        <v>598</v>
+      </c>
       <c r="T102" s="64" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="U102" s="145"/>
+      <c r="U102" s="144"/>
       <c r="V102" s="64"/>
     </row>
     <row r="103" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="141" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B103" s="141" t="s">
         <v>335</v>
@@ -15743,12 +15834,12 @@
       </c>
       <c r="S103" s="59"/>
       <c r="T103" s="64"/>
-      <c r="U103" s="145"/>
+      <c r="U103" s="144"/>
       <c r="V103" s="64"/>
     </row>
     <row r="104" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="141" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B104" s="141" t="s">
         <v>335</v>
@@ -15800,12 +15891,12 @@
       </c>
       <c r="S104" s="59"/>
       <c r="T104" s="64"/>
-      <c r="U104" s="145"/>
+      <c r="U104" s="144"/>
       <c r="V104" s="64"/>
     </row>
     <row r="105" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="141" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B105" s="141" t="s">
         <v>335</v>
@@ -15857,12 +15948,12 @@
       </c>
       <c r="S105" s="59"/>
       <c r="T105" s="64"/>
-      <c r="U105" s="145"/>
+      <c r="U105" s="144"/>
       <c r="V105" s="64"/>
     </row>
     <row r="106" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="141" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="B106" s="141" t="s">
         <v>335</v>
@@ -15914,12 +16005,12 @@
       </c>
       <c r="S106" s="59"/>
       <c r="T106" s="64"/>
-      <c r="U106" s="145"/>
+      <c r="U106" s="144"/>
       <c r="V106" s="64"/>
     </row>
     <row r="107" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="141" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="B107" s="141" t="s">
         <v>335</v>
@@ -15971,7 +16062,7 @@
       </c>
       <c r="S107" s="59"/>
       <c r="T107" s="64"/>
-      <c r="U107" s="145"/>
+      <c r="U107" s="144"/>
       <c r="V107" s="64"/>
     </row>
     <row r="108" spans="1:22" s="120" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -15991,7 +16082,7 @@
       <c r="F108" s="118"/>
       <c r="G108" s="118"/>
       <c r="H108" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I108" s="118"/>
       <c r="J108" s="118"/>
@@ -15999,7 +16090,7 @@
       <c r="L108" s="118"/>
       <c r="M108" s="118"/>
       <c r="N108" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O108" s="121"/>
       <c r="P108" s="118"/>
@@ -16010,7 +16101,7 @@
     </row>
     <row r="109" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="B109" s="3" t="s">
         <v>335</v>
@@ -16058,7 +16149,7 @@
         <v>400</v>
       </c>
       <c r="S109" s="6" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="U109" s="87">
         <v>418</v>
@@ -16066,7 +16157,7 @@
     </row>
     <row r="110" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B110" s="3" t="s">
         <v>335</v>
@@ -16115,7 +16206,7 @@
         <v>400</v>
       </c>
       <c r="S110" s="6" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="U110" s="87">
         <v>474</v>
@@ -16123,7 +16214,7 @@
     </row>
     <row r="111" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="B111" s="3" t="s">
         <v>335</v>
@@ -16172,7 +16263,7 @@
         <v>550</v>
       </c>
       <c r="S111" s="6" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="T111" t="e" vm="2">
         <v>#VALUE!</v>
@@ -16180,7 +16271,7 @@
     </row>
     <row r="112" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>335</v>
@@ -16229,7 +16320,7 @@
         <v>750</v>
       </c>
       <c r="S112" s="6" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="U112" s="99"/>
     </row>
@@ -16250,7 +16341,7 @@
       <c r="F113" s="118"/>
       <c r="G113" s="118"/>
       <c r="H113" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I113" s="118"/>
       <c r="J113" s="118"/>
@@ -16258,7 +16349,7 @@
       <c r="L113" s="118"/>
       <c r="M113" s="118"/>
       <c r="N113" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O113" s="121"/>
       <c r="P113" s="118"/>
@@ -16269,7 +16360,7 @@
     </row>
     <row r="114" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B114" t="s">
         <v>335</v>
@@ -16281,7 +16372,7 @@
         <v>250</v>
       </c>
       <c r="E114" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F114" s="6">
         <v>80</v>
@@ -16299,7 +16390,7 @@
         <v>276</v>
       </c>
       <c r="L114" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M114" s="1" t="s">
         <v>59</v>
@@ -16319,7 +16410,7 @@
     </row>
     <row r="115" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B115" t="s">
         <v>335</v>
@@ -16332,7 +16423,7 @@
         <v>400</v>
       </c>
       <c r="E115" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F115" s="6">
         <v>40</v>
@@ -16368,7 +16459,7 @@
         <v>750</v>
       </c>
       <c r="S115" s="6" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="U115" s="87">
         <v>1481.78</v>
@@ -16376,7 +16467,7 @@
     </row>
     <row r="116" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B116" t="s">
         <v>335</v>
@@ -16389,7 +16480,7 @@
         <v>550</v>
       </c>
       <c r="E116" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F116" s="6">
         <v>20</v>
@@ -16427,7 +16518,7 @@
     </row>
     <row r="117" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B117" t="s">
         <v>335</v>
@@ -16440,7 +16531,7 @@
         <v>750</v>
       </c>
       <c r="E117" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F117" s="6">
         <v>20</v>
@@ -16493,7 +16584,7 @@
       <c r="F118" s="118"/>
       <c r="G118" s="118"/>
       <c r="H118" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I118" s="118"/>
       <c r="J118" s="118"/>
@@ -16501,7 +16592,7 @@
       <c r="L118" s="118"/>
       <c r="M118" s="118"/>
       <c r="N118" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O118" s="121"/>
       <c r="P118" s="118"/>
@@ -16512,7 +16603,7 @@
     </row>
     <row r="119" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B119" t="s">
         <v>335</v>
@@ -16524,7 +16615,7 @@
         <v>250</v>
       </c>
       <c r="E119" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F119" s="6">
         <v>80</v>
@@ -16542,7 +16633,7 @@
         <v>276</v>
       </c>
       <c r="L119" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="M119" s="1" t="s">
         <v>59</v>
@@ -16562,7 +16653,7 @@
     </row>
     <row r="120" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B120" t="s">
         <v>335</v>
@@ -16574,7 +16665,7 @@
         <v>250</v>
       </c>
       <c r="E120" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F120" s="6">
         <v>80</v>
@@ -16592,7 +16683,7 @@
         <v>276</v>
       </c>
       <c r="L120" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="M120" s="1" t="s">
         <v>59</v>
@@ -16612,7 +16703,7 @@
     </row>
     <row r="121" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B121" t="s">
         <v>335</v>
@@ -16625,7 +16716,7 @@
         <v>400</v>
       </c>
       <c r="E121" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F121" s="6">
         <v>40</v>
@@ -16663,7 +16754,7 @@
     </row>
     <row r="122" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="B122" t="s">
         <v>335</v>
@@ -16676,7 +16767,7 @@
         <v>450</v>
       </c>
       <c r="E122" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F122" s="6">
         <v>60</v>
@@ -16714,7 +16805,7 @@
     </row>
     <row r="123" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="B123" t="s">
         <v>335</v>
@@ -16727,7 +16818,7 @@
         <v>500</v>
       </c>
       <c r="E123" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F123" s="6">
         <v>80</v>
@@ -16765,7 +16856,7 @@
     </row>
     <row r="124" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="B124" t="s">
         <v>335</v>
@@ -16778,7 +16869,7 @@
         <v>550</v>
       </c>
       <c r="E124" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F124" s="6">
         <v>20</v>
@@ -16816,7 +16907,7 @@
     </row>
     <row r="125" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B125" t="s">
         <v>335</v>
@@ -16829,7 +16920,7 @@
         <v>550</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F125" s="6">
         <v>40</v>
@@ -16867,7 +16958,7 @@
     </row>
     <row r="126" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="B126" t="s">
         <v>335</v>
@@ -16880,7 +16971,7 @@
         <v>750</v>
       </c>
       <c r="E126" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F126" s="6">
         <v>20</v>
@@ -16918,7 +17009,7 @@
     </row>
     <row r="127" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B127" t="s">
         <v>335</v>
@@ -16931,7 +17022,7 @@
         <v>750</v>
       </c>
       <c r="E127" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F127" s="6">
         <v>45</v>
@@ -16969,7 +17060,7 @@
     </row>
     <row r="128" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B128" t="s">
         <v>335</v>
@@ -16982,7 +17073,7 @@
         <v>1000</v>
       </c>
       <c r="E128" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F128" s="6">
         <v>30</v>
@@ -17020,7 +17111,7 @@
     </row>
     <row r="129" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="B129" t="s">
         <v>335</v>
@@ -17033,7 +17124,7 @@
         <v>1400</v>
       </c>
       <c r="E129" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F129" s="6">
         <v>20</v>
@@ -17071,7 +17162,7 @@
     </row>
     <row r="130" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="B130" t="s">
         <v>335</v>
@@ -17084,7 +17175,7 @@
         <v>1800</v>
       </c>
       <c r="E130" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F130" s="1">
         <v>12</v>
@@ -17122,7 +17213,7 @@
     </row>
     <row r="131" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B131" t="s">
         <v>335</v>
@@ -17135,7 +17226,7 @@
         <v>2600</v>
       </c>
       <c r="E131" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F131" s="1">
         <v>12</v>
@@ -17173,7 +17264,7 @@
     </row>
     <row r="132" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="3" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B132" t="s">
         <v>335</v>
@@ -17186,7 +17277,7 @@
         <v>3600</v>
       </c>
       <c r="E132" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="F132" s="1">
         <v>12</v>
@@ -17239,7 +17330,7 @@
       <c r="F133" s="118"/>
       <c r="G133" s="118"/>
       <c r="H133" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I133" s="118"/>
       <c r="J133" s="118"/>
@@ -17247,7 +17338,7 @@
       <c r="L133" s="118"/>
       <c r="M133" s="118"/>
       <c r="N133" s="119" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="O133" s="121"/>
       <c r="P133" s="118"/>
@@ -17258,7 +17349,7 @@
     </row>
     <row r="134" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="B134" t="s">
         <v>335</v>
@@ -17270,7 +17361,7 @@
         <v>250</v>
       </c>
       <c r="E134" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F134" s="6">
         <v>15</v>
@@ -17306,7 +17397,7 @@
         <v>510</v>
       </c>
       <c r="S134" s="6" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="U134" s="87">
         <v>624.37</v>
@@ -17314,7 +17405,7 @@
     </row>
     <row r="135" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="3" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="B135" t="s">
         <v>335</v>
@@ -17327,7 +17418,7 @@
         <v>250</v>
       </c>
       <c r="E135" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F135" s="6">
         <v>24</v>
@@ -17365,7 +17456,7 @@
     </row>
     <row r="136" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B136" t="s">
         <v>335</v>
@@ -17378,7 +17469,7 @@
         <v>400</v>
       </c>
       <c r="E136" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F136" s="6">
         <v>15</v>
@@ -17416,7 +17507,7 @@
     </row>
     <row r="137" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="B137" t="s">
         <v>335</v>
@@ -17429,7 +17520,7 @@
         <v>400</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F137" s="6">
         <v>24</v>
@@ -17467,7 +17558,7 @@
     </row>
     <row r="138" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="B138" t="s">
         <v>335</v>
@@ -17480,7 +17571,7 @@
         <v>550</v>
       </c>
       <c r="E138" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F138" s="6">
         <v>15</v>
@@ -17518,7 +17609,7 @@
     </row>
     <row r="139" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="B139" t="s">
         <v>335</v>
@@ -17531,7 +17622,7 @@
         <v>550</v>
       </c>
       <c r="E139" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F139" s="6">
         <v>24</v>
@@ -17569,7 +17660,7 @@
     </row>
     <row r="140" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="B140" t="s">
         <v>335</v>
@@ -17582,7 +17673,7 @@
         <v>750</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F140" s="6">
         <v>24</v>
@@ -17620,7 +17711,7 @@
     </row>
     <row r="141" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B141" t="s">
         <v>335</v>
@@ -17633,7 +17724,7 @@
         <v>1000</v>
       </c>
       <c r="E141" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F141" s="6">
         <v>24</v>
@@ -17671,7 +17762,7 @@
     </row>
     <row r="142" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="3" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B142" t="s">
         <v>335</v>
@@ -17684,7 +17775,7 @@
         <v>1200</v>
       </c>
       <c r="E142" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="F142" s="6">
         <v>12</v>
@@ -17781,61 +17872,61 @@
   <sheetData>
     <row r="1" spans="1:21" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B1" s="9" t="s">
         <v>137</v>
       </c>
       <c r="C1" s="55" t="s">
+        <v>394</v>
+      </c>
+      <c r="D1" s="55" t="s">
         <v>395</v>
       </c>
-      <c r="D1" s="55" t="s">
+      <c r="E1" s="55" t="s">
         <v>396</v>
       </c>
-      <c r="E1" s="55" t="s">
+      <c r="F1" s="55" t="s">
         <v>397</v>
       </c>
-      <c r="F1" s="55" t="s">
+      <c r="G1" s="55" t="s">
         <v>398</v>
       </c>
-      <c r="G1" s="55" t="s">
+      <c r="H1" s="55" t="s">
         <v>399</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="I1" s="55" t="s">
         <v>400</v>
       </c>
-      <c r="I1" s="55" t="s">
+      <c r="J1" s="55" t="s">
         <v>401</v>
-      </c>
-      <c r="J1" s="55" t="s">
-        <v>402</v>
       </c>
       <c r="K1" s="55" t="s">
         <v>258</v>
       </c>
       <c r="L1" s="55" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="M1" s="55" t="s">
         <v>259</v>
       </c>
       <c r="N1" s="11" t="s">
+        <v>403</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>510</v>
+      </c>
+      <c r="P1" s="55" t="s">
         <v>404</v>
       </c>
-      <c r="O1" s="11" t="s">
-        <v>511</v>
-      </c>
-      <c r="P1" s="55" t="s">
+      <c r="Q1" s="55" t="s">
         <v>405</v>
-      </c>
-      <c r="Q1" s="55" t="s">
-        <v>406</v>
       </c>
       <c r="R1" s="10" t="s">
         <v>264</v>
       </c>
       <c r="S1" s="114" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="U1" s="11" t="s">
         <v>273</v>
@@ -17849,7 +17940,7 @@
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" s="63" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="B4" s="63" t="s">
         <v>335</v>
@@ -17871,7 +17962,7 @@
         <v>3</v>
       </c>
       <c r="H4" s="78" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I4" s="78">
         <v>70</v>
@@ -17912,7 +18003,7 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" s="63" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="B5" s="63" t="s">
         <v>335</v>
@@ -17934,7 +18025,7 @@
         <v>3.8</v>
       </c>
       <c r="H5" s="78" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I5" s="78">
         <v>70</v>
@@ -17996,7 +18087,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" s="63" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="B7" s="63" t="s">
         <v>335</v>
@@ -18018,7 +18109,7 @@
         <v>3</v>
       </c>
       <c r="H7" s="78" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I7" s="78">
         <v>90</v>
@@ -18059,7 +18150,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" s="63" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="B8" s="63" t="s">
         <v>335</v>
@@ -18081,7 +18172,7 @@
         <v>3.8</v>
       </c>
       <c r="H8" s="78" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I8" s="78">
         <v>90</v>
@@ -18145,7 +18236,7 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" s="63" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="B10" s="63" t="s">
         <v>335</v>
@@ -18167,7 +18258,7 @@
         <v>3</v>
       </c>
       <c r="H10" s="78" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I10" s="78">
         <v>90</v>
@@ -18208,7 +18299,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" s="63" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="B11" s="63" t="s">
         <v>335</v>
@@ -18230,7 +18321,7 @@
         <v>3.8</v>
       </c>
       <c r="H11" s="78" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I11" s="78">
         <v>90</v>
@@ -18294,7 +18385,7 @@
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" s="63" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B13" s="63" t="s">
         <v>335</v>
@@ -18316,7 +18407,7 @@
         <v>3.1666666666666665</v>
       </c>
       <c r="H13" s="78" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I13" s="78">
         <v>149</v>
@@ -18357,7 +18448,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" s="63" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B14" s="63" t="s">
         <v>335</v>
@@ -18379,7 +18470,7 @@
         <v>3.8</v>
       </c>
       <c r="H14" s="78" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I14" s="78">
         <v>150</v>
@@ -18420,7 +18511,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" s="128" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="B15" s="128" t="s">
         <v>335</v>
@@ -18442,7 +18533,7 @@
         <v>4.75</v>
       </c>
       <c r="H15" s="129" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I15" s="129">
         <v>150</v>
@@ -18506,7 +18597,7 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" s="63" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B17" s="63" t="s">
         <v>335</v>
@@ -18528,7 +18619,7 @@
         <v>3.8</v>
       </c>
       <c r="H17" s="78" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I17" s="78">
         <v>220</v>
@@ -18600,7 +18691,7 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="63" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B20" s="63" t="s">
         <v>335</v>
@@ -18622,7 +18713,7 @@
         <v>3.8</v>
       </c>
       <c r="H20" s="78" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I20" s="78">
         <v>90</v>
@@ -18663,7 +18754,7 @@
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" s="63" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B21" s="63" t="s">
         <v>335</v>
@@ -18685,7 +18776,7 @@
         <v>3.8</v>
       </c>
       <c r="H21" s="78" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I21" s="78">
         <v>90</v>
@@ -18726,7 +18817,7 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" s="63" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B22" s="63" t="s">
         <v>335</v>
@@ -18748,7 +18839,7 @@
         <v>3.1666666666666665</v>
       </c>
       <c r="H22" s="78" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I22" s="78">
         <v>150</v>
@@ -18789,7 +18880,7 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="63" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B23" s="63" t="s">
         <v>335</v>
@@ -18811,7 +18902,7 @@
         <v>3.1666666666666665</v>
       </c>
       <c r="H23" s="78" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I23" s="78">
         <v>150</v>
@@ -18852,7 +18943,7 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" s="63" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B24" s="63" t="s">
         <v>335</v>
@@ -18874,7 +18965,7 @@
         <v>4.75</v>
       </c>
       <c r="H24" s="78" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I24" s="78">
         <v>150</v>
@@ -18915,7 +19006,7 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" s="63" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B25" s="63" t="s">
         <v>335</v>
@@ -18937,7 +19028,7 @@
         <v>4.75</v>
       </c>
       <c r="H25" s="78" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I25" s="78">
         <v>150</v>
@@ -18995,7 +19086,7 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" s="93" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B28" t="s">
         <v>335</v>
@@ -19017,7 +19108,7 @@
         <v>3.8</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I28" s="6">
         <v>400</v>
@@ -19059,7 +19150,7 @@
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29" s="93" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B29" t="s">
         <v>335</v>
@@ -19081,7 +19172,7 @@
         <v>3.8</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I29" s="6">
         <v>400</v>
@@ -19123,7 +19214,7 @@
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B30" t="s">
         <v>335</v>
@@ -19145,7 +19236,7 @@
         <v>3.8</v>
       </c>
       <c r="H30" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I30" s="6">
         <v>600</v>
@@ -19187,7 +19278,7 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B31" t="s">
         <v>335</v>
@@ -19209,7 +19300,7 @@
         <v>3.8</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I31" s="6">
         <v>800</v>
@@ -19251,7 +19342,7 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B32" t="s">
         <v>335</v>
@@ -19273,7 +19364,7 @@
         <v>3.8</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I32" s="6">
         <v>800</v>
@@ -19315,7 +19406,7 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B35" t="s">
         <v>335</v>
@@ -19337,7 +19428,7 @@
         <v>3.8</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I35" s="6">
         <v>300</v>
@@ -19354,7 +19445,7 @@
         <v>10.526315789473685</v>
       </c>
       <c r="M35" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="N35" s="78">
         <v>40</v>
@@ -19378,7 +19469,7 @@
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B36" t="s">
         <v>335</v>
@@ -19400,7 +19491,7 @@
         <v>3.8</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I36" s="6">
         <v>300</v>
@@ -19417,7 +19508,7 @@
         <v>10.526315789473685</v>
       </c>
       <c r="M36" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="N36" s="78">
         <v>40</v>
@@ -19441,7 +19532,7 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B37" t="s">
         <v>335</v>
@@ -19463,7 +19554,7 @@
         <v>3.8</v>
       </c>
       <c r="H37" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I37" s="6">
         <v>500</v>
@@ -19480,7 +19571,7 @@
         <v>21.05263157894737</v>
       </c>
       <c r="M37" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="N37" s="78">
         <v>60</v>
@@ -19504,7 +19595,7 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B38" t="s">
         <v>335</v>
@@ -19526,7 +19617,7 @@
         <v>3.8</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I38" s="6">
         <v>800</v>
@@ -19543,7 +19634,7 @@
         <v>10.526315789473685</v>
       </c>
       <c r="M38" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="N38" s="78">
         <v>60</v>
@@ -19567,7 +19658,7 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B39" t="s">
         <v>335</v>
@@ -19589,7 +19680,7 @@
         <v>3.8</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="I39" s="6">
         <v>800</v>
@@ -19606,7 +19697,7 @@
         <v>10.526315789473685</v>
       </c>
       <c r="M39" s="6" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="N39" s="78">
         <v>60</v>
@@ -19630,7 +19721,7 @@
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>254</v>
@@ -19649,7 +19740,7 @@
         <v>5.5454545454545459</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I41" s="1">
         <v>20</v>
@@ -19693,7 +19784,7 @@
         <v>5.5555555555555554</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I42" s="1">
         <v>62</v>
@@ -19734,7 +19825,7 @@
         <v>6.4</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I43" s="1">
         <v>95</v>
@@ -19759,7 +19850,7 @@
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>254</v>
@@ -19775,7 +19866,7 @@
         <v>6.333333333333333</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I44" s="6">
         <v>128</v>
@@ -19800,7 +19891,7 @@
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>254</v>
@@ -19816,7 +19907,7 @@
         <v>4.3636363636363633</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I45" s="6">
         <v>369</v>
@@ -19838,7 +19929,7 @@
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C46" s="6">
         <v>14</v>
@@ -19851,7 +19942,7 @@
         <v>5.1428571428571432</v>
       </c>
       <c r="H46" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I46" s="6">
         <v>428</v>
@@ -19879,7 +19970,7 @@
     </row>
     <row r="48" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>254</v>
@@ -19898,7 +19989,7 @@
         <v>3</v>
       </c>
       <c r="H48" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I48" s="1">
         <v>15</v>
@@ -19945,7 +20036,7 @@
         <v>3</v>
       </c>
       <c r="H49" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I49" s="1">
         <v>62</v>
@@ -19992,7 +20083,7 @@
         <v>3</v>
       </c>
       <c r="H50" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I50" s="1">
         <v>95</v>
@@ -20024,7 +20115,7 @@
     </row>
     <row r="52" spans="1:24" s="63" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A52" s="63" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B52" s="132" t="s">
         <v>254</v>
@@ -20044,7 +20135,7 @@
         <v>3</v>
       </c>
       <c r="H52" s="78" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I52" s="125">
         <v>100</v>
@@ -20074,7 +20165,7 @@
     </row>
     <row r="53" spans="1:24" s="63" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="63" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B53" s="132" t="s">
         <v>254</v>
@@ -20094,7 +20185,7 @@
         <v>3.8</v>
       </c>
       <c r="H53" s="78" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I53" s="125">
         <v>160</v>
@@ -20128,7 +20219,7 @@
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>254</v>
@@ -20147,7 +20238,7 @@
         <v>3</v>
       </c>
       <c r="H55" s="6" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I55" s="1">
         <v>70</v>
@@ -20180,19 +20271,19 @@
       <c r="X55" s="87"/>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="H60" s="144" t="s">
-        <v>556</v>
-      </c>
-      <c r="I60" s="144"/>
-      <c r="J60" s="144"/>
-      <c r="K60" s="144"/>
-      <c r="L60" s="144"/>
-      <c r="M60" s="144"/>
-      <c r="N60" s="144"/>
-      <c r="O60" s="144"/>
-      <c r="P60" s="144"/>
-      <c r="Q60" s="144"/>
-      <c r="R60" s="144"/>
+      <c r="H60" s="145" t="s">
+        <v>555</v>
+      </c>
+      <c r="I60" s="145"/>
+      <c r="J60" s="145"/>
+      <c r="K60" s="145"/>
+      <c r="L60" s="145"/>
+      <c r="M60" s="145"/>
+      <c r="N60" s="145"/>
+      <c r="O60" s="145"/>
+      <c r="P60" s="145"/>
+      <c r="Q60" s="145"/>
+      <c r="R60" s="145"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -20223,39 +20314,39 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="B1" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="B1" s="8" t="s">
+      <c r="C1" s="8" t="s">
         <v>428</v>
       </c>
-      <c r="C1" s="8" t="s">
+      <c r="D1" s="8" t="s">
         <v>429</v>
       </c>
-      <c r="D1" s="8" t="s">
+      <c r="E1" s="8" t="s">
         <v>430</v>
       </c>
-      <c r="E1" s="8" t="s">
+      <c r="F1" s="8" t="s">
         <v>431</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="G1" s="8" t="s">
         <v>432</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>433</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="I1" s="8" t="s">
         <v>434</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>435</v>
-      </c>
       <c r="J1" s="8" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="94" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B2" s="94">
         <v>12</v>
@@ -20289,7 +20380,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="94" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B3" s="94">
         <v>15</v>
@@ -20323,7 +20414,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="94" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="B4" s="94">
         <v>19</v>
@@ -20357,7 +20448,7 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="96" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B5" s="97">
         <v>12</v>
@@ -20369,7 +20460,7 @@
         <v>57</v>
       </c>
       <c r="E5" s="97" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F5" s="97">
         <v>22400</v>
@@ -20391,7 +20482,7 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="96" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="B6" s="97">
         <v>18</v>
@@ -20403,7 +20494,7 @@
         <v>57</v>
       </c>
       <c r="E6" s="97" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="F6" s="97">
         <v>22400</v>
@@ -20425,7 +20516,7 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="133" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B7" s="133">
         <v>12</v>
@@ -20437,7 +20528,7 @@
         <v>57</v>
       </c>
       <c r="E7" s="133" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F7" s="133">
         <v>29000</v>
@@ -20459,7 +20550,7 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="133" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B8" s="133">
         <v>12</v>
@@ -20471,7 +20562,7 @@
         <v>57</v>
       </c>
       <c r="E8" s="133" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F8" s="133">
         <v>29000</v>
@@ -20493,7 +20584,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="133" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="B9" s="133">
         <v>15</v>
@@ -20505,7 +20596,7 @@
         <v>57</v>
       </c>
       <c r="E9" s="133" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F9" s="133">
         <v>29000</v>
@@ -20527,7 +20618,7 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="135" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="B10" s="135">
         <v>15</v>
@@ -20539,7 +20630,7 @@
         <v>57</v>
       </c>
       <c r="E10" s="135" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F10" s="135">
         <v>60000</v>
@@ -20560,7 +20651,7 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="137" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="B11" s="137">
         <v>15</v>
@@ -20572,7 +20663,7 @@
         <v>57</v>
       </c>
       <c r="E11" s="137" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F11" s="137">
         <v>95000</v>
@@ -20616,30 +20707,30 @@
   <sheetData>
     <row r="1" spans="1:7" s="11" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="50" t="s">
+        <v>439</v>
+      </c>
+      <c r="B1" s="50" t="s">
+        <v>547</v>
+      </c>
+      <c r="C1" s="50" t="s">
         <v>440</v>
       </c>
-      <c r="B1" s="50" t="s">
+      <c r="D1" s="50" t="s">
+        <v>441</v>
+      </c>
+      <c r="E1" s="50" t="s">
+        <v>442</v>
+      </c>
+      <c r="F1" s="50" t="s">
         <v>548</v>
       </c>
-      <c r="C1" s="50" t="s">
-        <v>441</v>
-      </c>
-      <c r="D1" s="50" t="s">
-        <v>442</v>
-      </c>
-      <c r="E1" s="50" t="s">
-        <v>443</v>
-      </c>
-      <c r="F1" s="50" t="s">
-        <v>549</v>
-      </c>
       <c r="G1" s="50" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B2" s="1">
         <v>30</v>
@@ -20658,7 +20749,7 @@
     </row>
     <row r="3" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B3" s="1">
         <v>40</v>
@@ -20677,7 +20768,7 @@
     </row>
     <row r="4" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B4" s="1">
         <v>30</v>
@@ -20693,12 +20784,12 @@
         <v>335</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="B5" s="1">
         <v>40</v>
@@ -20714,12 +20805,12 @@
         <v>335</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="B6" s="1">
         <v>55</v>
@@ -20735,12 +20826,12 @@
         <v>335</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B7" s="1">
         <v>60</v>
@@ -20756,7 +20847,7 @@
         <v>335</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -20766,7 +20857,7 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F8" s="1"/>
     </row>
@@ -20803,31 +20894,31 @@
         <v>3</v>
       </c>
       <c r="B1" s="43" t="s">
+        <v>446</v>
+      </c>
+      <c r="C1" s="43" t="s">
         <v>447</v>
       </c>
-      <c r="C1" s="43" t="s">
+      <c r="D1" s="43" t="s">
         <v>448</v>
       </c>
-      <c r="D1" s="43" t="s">
+      <c r="E1" s="43" t="s">
+        <v>442</v>
+      </c>
+      <c r="F1" s="44" t="s">
         <v>449</v>
-      </c>
-      <c r="E1" s="43" t="s">
-        <v>443</v>
-      </c>
-      <c r="F1" s="44" t="s">
-        <v>450</v>
       </c>
       <c r="G1" s="45" t="s">
         <v>264</v>
       </c>
       <c r="H1" s="46" t="s">
+        <v>450</v>
+      </c>
+      <c r="I1" s="47" t="s">
         <v>451</v>
       </c>
-      <c r="I1" s="47" t="s">
-        <v>452</v>
-      </c>
       <c r="J1" s="45" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="K1" s="139" t="s">
         <v>196</v>
@@ -20835,7 +20926,7 @@
     </row>
     <row r="2" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B2" s="91">
         <v>95</v>
@@ -20847,10 +20938,10 @@
         <v>22</v>
       </c>
       <c r="E2" s="91" t="s">
+        <v>453</v>
+      </c>
+      <c r="G2" s="91" t="s">
         <v>454</v>
-      </c>
-      <c r="G2" s="91" t="s">
-        <v>455</v>
       </c>
       <c r="H2">
         <v>10</v>
@@ -20858,7 +20949,7 @@
     </row>
     <row r="3" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B3" s="91">
         <v>147</v>
@@ -20870,10 +20961,10 @@
         <v>22</v>
       </c>
       <c r="E3" s="91" t="s">
+        <v>453</v>
+      </c>
+      <c r="G3" s="91" t="s">
         <v>454</v>
-      </c>
-      <c r="G3" s="91" t="s">
-        <v>455</v>
       </c>
       <c r="H3">
         <v>10</v>
@@ -20881,7 +20972,7 @@
     </row>
     <row r="4" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B4" s="91">
         <v>332</v>
@@ -20893,7 +20984,7 @@
         <v>22</v>
       </c>
       <c r="E4" s="91" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="F4" s="91">
         <v>480</v>
@@ -20905,12 +20996,12 @@
         <v>10</v>
       </c>
       <c r="K4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="5" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B5" s="91">
         <v>552</v>
@@ -20922,7 +21013,7 @@
         <v>22</v>
       </c>
       <c r="E5" s="91" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="G5" s="91">
         <v>40</v>
@@ -20931,12 +21022,12 @@
         <v>10</v>
       </c>
       <c r="K5" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="B6" s="106">
         <v>800</v>
@@ -20960,7 +21051,7 @@
     </row>
     <row r="7" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="105" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B7" s="106">
         <v>1200</v>
@@ -20984,7 +21075,7 @@
     </row>
     <row r="8" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="105" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="B8" s="106">
         <v>2200</v>
@@ -21006,12 +21097,12 @@
         <v>10</v>
       </c>
       <c r="K8" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="115" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B9" s="140">
         <v>3600</v>
@@ -21034,12 +21125,12 @@
       </c>
       <c r="I9" s="141"/>
       <c r="K9" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="92" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B10" s="91">
         <v>130</v>
@@ -21054,7 +21145,7 @@
         <v>254</v>
       </c>
       <c r="G10" s="91" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H10">
         <v>10</v>
@@ -21062,7 +21153,7 @@
     </row>
     <row r="11" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="92" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B11" s="91">
         <v>145</v>
@@ -21080,7 +21171,7 @@
         <v>200</v>
       </c>
       <c r="G11" s="91" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H11">
         <v>10</v>
@@ -21088,7 +21179,7 @@
     </row>
     <row r="12" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="92" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B12" s="91">
         <v>332</v>
@@ -21114,7 +21205,7 @@
     </row>
     <row r="13" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="92" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B13" s="91">
         <v>542</v>
@@ -21138,7 +21229,7 @@
     </row>
     <row r="14" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="92" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="B14" s="91">
         <v>1000</v>
@@ -21168,7 +21259,7 @@
     </row>
     <row r="16" spans="1:11" ht="49" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B16" s="91">
         <v>145</v>
@@ -21186,7 +21277,7 @@
         <v>200</v>
       </c>
       <c r="G16" s="91" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H16">
         <v>10</v>
@@ -21260,22 +21351,22 @@
         <v>3</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>468</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>469</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>470</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>16</v>
       </c>
       <c r="E1" s="6" t="s">
+        <v>470</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>471</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>472</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>473</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -21288,7 +21379,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="32" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B3" s="6">
         <v>300</v>
@@ -21312,7 +21403,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="32" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B4" s="6">
         <v>350</v>
@@ -21336,7 +21427,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="32" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B5" s="6">
         <v>400</v>
@@ -21360,7 +21451,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="32" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B6" s="6">
         <v>450</v>
@@ -21384,7 +21475,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="32" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B7" s="6">
         <v>300</v>
@@ -21408,7 +21499,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="32" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B8" s="6">
         <v>350</v>
@@ -21432,7 +21523,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="32" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B9" s="6">
         <v>400</v>
@@ -21456,7 +21547,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="32" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B10" s="6">
         <v>450</v>
@@ -21488,7 +21579,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="32" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B13" s="6">
         <v>300</v>
@@ -21512,7 +21603,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="32" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B14" s="6">
         <v>350</v>
@@ -21536,7 +21627,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="32" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B15" s="6">
         <v>400</v>
@@ -21560,7 +21651,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="32" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B16" s="6">
         <v>450</v>
@@ -21584,7 +21675,7 @@
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A17" s="32" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B17" s="6">
         <v>500</v>
@@ -21608,7 +21699,7 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="32" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B18" s="6">
         <v>550</v>
@@ -21632,7 +21723,7 @@
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A19" s="53" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B19" s="54">
         <v>600</v>
@@ -21659,7 +21750,7 @@
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A21" s="32" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B21" s="6">
         <v>135</v>
@@ -21677,10 +21768,13 @@
         <f t="shared" ref="F21:F26" si="3">B21-50</f>
         <v>85</v>
       </c>
+      <c r="G21" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A22" s="32" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B22" s="6">
         <v>180</v>
@@ -21698,10 +21792,13 @@
         <f t="shared" si="3"/>
         <v>130</v>
       </c>
+      <c r="G22" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A23" s="32" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B23" s="6">
         <v>205</v>
@@ -21719,10 +21816,13 @@
         <f t="shared" si="3"/>
         <v>155</v>
       </c>
+      <c r="G23" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A24" s="32" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B24" s="6">
         <v>250</v>
@@ -21740,10 +21840,13 @@
         <f t="shared" si="3"/>
         <v>200</v>
       </c>
+      <c r="G24" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A25" s="32" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B25" s="6">
         <v>300</v>
@@ -21761,10 +21864,13 @@
         <f t="shared" si="3"/>
         <v>250</v>
       </c>
+      <c r="G25" s="6">
+        <v>0</v>
+      </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A26" s="32" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B26" s="6">
         <v>350</v>
@@ -21781,6 +21887,9 @@
       <c r="F26" s="6">
         <f t="shared" si="3"/>
         <v>300</v>
+      </c>
+      <c r="G26" s="6">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -21804,7 +21913,7 @@
         <v>3</v>
       </c>
       <c r="B1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C1" t="s">
         <v>139</v>
@@ -21823,7 +21932,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B3">
         <v>1875</v>
@@ -21854,33 +21963,33 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="144" t="s">
-        <v>547</v>
-      </c>
-      <c r="B2" s="144"/>
-      <c r="C2" s="144"/>
-      <c r="D2" s="144"/>
-      <c r="E2" s="144"/>
-      <c r="F2" s="144"/>
+      <c r="A2" s="145" t="s">
+        <v>546</v>
+      </c>
+      <c r="B2" s="145"/>
+      <c r="C2" s="145"/>
+      <c r="D2" s="145"/>
+      <c r="E2" s="145"/>
+      <c r="F2" s="145"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>541</v>
+      </c>
+      <c r="B4" t="s">
         <v>542</v>
       </c>
-      <c r="B4" t="s">
-        <v>543</v>
-      </c>
       <c r="C4" s="6" t="s">
+        <v>537</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>538</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>539</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>540</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>541</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
@@ -21892,7 +22001,7 @@
         <v>142</v>
       </c>
       <c r="B5" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C5" s="6">
         <v>1000</v>
@@ -21916,7 +22025,7 @@
         <v>147</v>
       </c>
       <c r="B6" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C6" s="6">
         <v>1000</v>
@@ -21936,7 +22045,7 @@
         <v>148</v>
       </c>
       <c r="B7" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C7" s="6">
         <v>1000</v>
@@ -21960,7 +22069,7 @@
         <v>166</v>
       </c>
       <c r="B8" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C8" s="6">
         <v>1000</v>
@@ -21984,7 +22093,7 @@
         <v>150</v>
       </c>
       <c r="B9" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C9" s="6">
         <v>1000</v>
@@ -22008,7 +22117,7 @@
         <v>142</v>
       </c>
       <c r="B11" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C11" s="6">
         <v>1000</v>
@@ -22028,7 +22137,7 @@
         <v>147</v>
       </c>
       <c r="B12" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C12" s="6">
         <v>1000</v>
@@ -22048,7 +22157,7 @@
         <v>148</v>
       </c>
       <c r="B13" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C13" s="6">
         <v>1000</v>
@@ -22068,7 +22177,7 @@
         <v>166</v>
       </c>
       <c r="B14" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C14" s="6">
         <v>1000</v>
@@ -22088,7 +22197,7 @@
         <v>150</v>
       </c>
       <c r="B15" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="C15" s="6">
         <v>1000</v>
@@ -22108,7 +22217,7 @@
         <v>142</v>
       </c>
       <c r="B17" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C17" s="6">
         <v>1000</v>
@@ -22128,7 +22237,7 @@
         <v>147</v>
       </c>
       <c r="B18" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C18" s="6">
         <v>1000</v>
@@ -22148,7 +22257,7 @@
         <v>148</v>
       </c>
       <c r="B19" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C19" s="6">
         <v>1000</v>
@@ -22168,7 +22277,7 @@
         <v>166</v>
       </c>
       <c r="B20" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C20" s="6">
         <v>1000</v>
@@ -22188,7 +22297,7 @@
         <v>150</v>
       </c>
       <c r="B21" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="C21" s="6">
         <v>1000</v>
@@ -22212,8 +22321,8 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3B9ED08-8454-4272-8896-17578EF9EBC9}">
-  <dimension ref="A1:G36"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3B9ED08-8454-4272-8896-17578EF9EBC9}">
+  <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.26953125" customWidth="1"/>
@@ -22222,9 +22331,10 @@
     <col min="5" max="5" width="10.81640625" customWidth="1"/>
     <col min="6" max="6" width="11.453125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.453125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="77" t="s">
         <v>63</v>
       </c>
@@ -22244,8 +22354,11 @@
       <c r="G1" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H1" t="s">
+        <v>603</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="75" t="s">
         <v>69</v>
       </c>
@@ -22255,8 +22368,14 @@
       <c r="C2" s="75">
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H2" t="s">
+        <v>604</v>
+      </c>
+      <c r="K2" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="75" t="s">
         <v>71</v>
       </c>
@@ -22266,8 +22385,14 @@
       <c r="C3" s="75">
         <v>2</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H3" t="s">
+        <v>604</v>
+      </c>
+      <c r="K3" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="75" t="s">
         <v>73</v>
       </c>
@@ -22277,8 +22402,14 @@
       <c r="C4" s="75">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H4" t="s">
+        <v>604</v>
+      </c>
+      <c r="K4" t="s">
+        <v>607</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="75" t="s">
         <v>75</v>
       </c>
@@ -22288,8 +22419,14 @@
       <c r="C5" s="75">
         <v>5</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H5" t="s">
+        <v>604</v>
+      </c>
+      <c r="K5" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="75" t="s">
         <v>69</v>
       </c>
@@ -22299,8 +22436,11 @@
       <c r="C6" s="75">
         <v>6</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="K6" t="s">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="75" t="s">
         <v>71</v>
       </c>
@@ -22310,8 +22450,11 @@
       <c r="C7" s="75">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+      <c r="K7" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="16" x14ac:dyDescent="0.35">
       <c r="A8" s="75" t="s">
         <v>73</v>
       </c>
@@ -22322,7 +22465,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="75" t="s">
         <v>80</v>
       </c>
@@ -22333,7 +22476,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" ht="16" x14ac:dyDescent="0.35">
       <c r="A10" s="75" t="s">
         <v>82</v>
       </c>
@@ -22344,7 +22487,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="75" t="s">
         <v>84</v>
       </c>
@@ -22355,7 +22498,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:11" ht="16" x14ac:dyDescent="0.35">
       <c r="A12" s="75" t="s">
         <v>86</v>
       </c>
@@ -22366,7 +22509,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:11" ht="16" x14ac:dyDescent="0.35">
       <c r="A13" s="75" t="s">
         <v>88</v>
       </c>
@@ -22377,7 +22520,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="75" t="s">
         <v>90</v>
       </c>
@@ -22388,7 +22531,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:11" ht="16" x14ac:dyDescent="0.35">
       <c r="A15" s="75" t="s">
         <v>92</v>
       </c>
@@ -22399,7 +22542,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="75" t="s">
         <v>94</v>
       </c>
@@ -22632,6 +22775,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -22810,7 +22954,7 @@
         <v>10</v>
       </c>
       <c r="H4" s="5">
-        <v>4000</v>
+        <v>4600</v>
       </c>
       <c r="I4" s="48">
         <v>100</v>
@@ -22896,7 +23040,7 @@
         <v>10</v>
       </c>
       <c r="H6" s="5">
-        <v>4000</v>
+        <v>4600</v>
       </c>
       <c r="I6" s="48">
         <v>100</v>
@@ -24348,12 +24492,758 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB485315-044F-4FB0-A3DD-44B741CAB625}">
+  <dimension ref="A1:O24"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="33.453125" customWidth="1"/>
+    <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.81640625" customWidth="1"/>
+    <col min="5" max="8" width="8.7265625" style="6"/>
+    <col min="10" max="13" width="8.7265625" style="6"/>
+    <col min="15" max="15" width="11.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:15" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="26" t="s">
+        <v>170</v>
+      </c>
+      <c r="B1" s="26" t="s">
+        <v>171</v>
+      </c>
+      <c r="C1" s="27" t="s">
+        <v>172</v>
+      </c>
+      <c r="D1" s="26" t="s">
+        <v>173</v>
+      </c>
+      <c r="E1" s="142" t="s">
+        <v>574</v>
+      </c>
+      <c r="F1" s="26" t="s">
+        <v>575</v>
+      </c>
+      <c r="G1" s="26" t="s">
+        <v>576</v>
+      </c>
+      <c r="H1" s="26" t="s">
+        <v>577</v>
+      </c>
+      <c r="I1" s="26" t="s">
+        <v>583</v>
+      </c>
+      <c r="J1" s="26" t="s">
+        <v>579</v>
+      </c>
+      <c r="K1" s="26" t="s">
+        <v>578</v>
+      </c>
+      <c r="L1" s="26" t="s">
+        <v>580</v>
+      </c>
+      <c r="M1" s="26" t="s">
+        <v>581</v>
+      </c>
+      <c r="N1" s="26" t="s">
+        <v>582</v>
+      </c>
+      <c r="O1" s="146" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="103" t="s">
+        <v>174</v>
+      </c>
+      <c r="B3" s="23">
+        <v>3.2</v>
+      </c>
+      <c r="C3">
+        <v>65</v>
+      </c>
+      <c r="D3">
+        <v>50</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="N3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O3" s="6" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="103" t="s">
+        <v>175</v>
+      </c>
+      <c r="B4" s="23">
+        <f>B3+1.64+0.5</f>
+        <v>5.34</v>
+      </c>
+      <c r="C4">
+        <v>90</v>
+      </c>
+      <c r="D4">
+        <v>70</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="N4" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O4" s="6" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="103" t="s">
+        <v>176</v>
+      </c>
+      <c r="B5" s="23">
+        <f>B3+0.72+0.5</f>
+        <v>4.42</v>
+      </c>
+      <c r="C5">
+        <v>110</v>
+      </c>
+      <c r="D5">
+        <v>85</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="N5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O5" s="6" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="103" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" s="23">
+        <v>2.1</v>
+      </c>
+      <c r="C6">
+        <v>65</v>
+      </c>
+      <c r="D6">
+        <v>50</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="N6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O6" s="6" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="103" t="s">
+        <v>178</v>
+      </c>
+      <c r="B7" s="23">
+        <f>B6+0.72+0.5</f>
+        <v>3.3200000000000003</v>
+      </c>
+      <c r="C7">
+        <v>110</v>
+      </c>
+      <c r="D7">
+        <v>85</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G7" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H7" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I7" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J7" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K7" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L7" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M7" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="N7" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O7" s="6" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="103" t="s">
+        <v>179</v>
+      </c>
+      <c r="B8" s="23">
+        <v>2</v>
+      </c>
+      <c r="C8">
+        <v>112</v>
+      </c>
+      <c r="D8">
+        <v>80</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G8" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I8" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L8" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M8" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="N8" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O8" s="6" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="104" t="s">
+        <v>180</v>
+      </c>
+      <c r="B9" s="24">
+        <v>1.2</v>
+      </c>
+      <c r="C9">
+        <v>80</v>
+      </c>
+      <c r="D9">
+        <v>100</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K9" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L9" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M9" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="N9" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O9" s="6" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="104" t="s">
+        <v>181</v>
+      </c>
+      <c r="B10" s="25">
+        <f>0.82+0.72</f>
+        <v>1.54</v>
+      </c>
+      <c r="C10">
+        <v>120</v>
+      </c>
+      <c r="D10">
+        <v>100</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F10" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G10" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H10" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I10" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L10" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M10" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="N10" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O10" s="6" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="102" t="s">
+        <v>499</v>
+      </c>
+      <c r="B11" s="23">
+        <v>0.95</v>
+      </c>
+      <c r="C11">
+        <v>20</v>
+      </c>
+      <c r="D11">
+        <v>100</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F11" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G11" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="H11" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I11" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J11" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K11" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L11" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M11" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="N11" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O11" s="6" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="102" t="s">
+        <v>182</v>
+      </c>
+      <c r="B12" s="54">
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <v>58</v>
+      </c>
+      <c r="D12">
+        <v>50</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F12" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G12" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H12" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I12" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K12" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L12" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M12" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="N12" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O12" s="6" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="102" t="s">
+        <v>183</v>
+      </c>
+      <c r="B13" s="54">
+        <v>1.5</v>
+      </c>
+      <c r="C13">
+        <v>65</v>
+      </c>
+      <c r="D13">
+        <v>50</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="K13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="L13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="N13" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O13" s="6" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="102" t="s">
+        <v>184</v>
+      </c>
+      <c r="B14" s="54">
+        <v>2.5</v>
+      </c>
+      <c r="C14">
+        <v>96</v>
+      </c>
+      <c r="D14">
+        <v>50</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G14" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H14" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="J14" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K14" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="M14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="N14" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="O14" s="6" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="102" t="s">
+        <v>185</v>
+      </c>
+      <c r="B15" s="54">
+        <v>2</v>
+      </c>
+      <c r="C15">
+        <v>114</v>
+      </c>
+      <c r="D15">
+        <v>80</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="F15" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="G15" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="H15" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="I15" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="J15" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="K15" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="M15" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="N15" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="O15" s="6" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="19" spans="2:6" ht="16" x14ac:dyDescent="0.35">
+      <c r="B19" s="65" t="s">
+        <v>186</v>
+      </c>
+      <c r="C19">
+        <v>0.5</v>
+      </c>
+      <c r="D19">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="E19" s="6">
+        <f>C19/D19</f>
+        <v>0.4587155963302752</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" ht="16" x14ac:dyDescent="0.35">
+      <c r="B20" s="65" t="s">
+        <v>187</v>
+      </c>
+      <c r="C20">
+        <v>5.38</v>
+      </c>
+      <c r="D20">
+        <v>4.16</v>
+      </c>
+      <c r="E20" s="6">
+        <f t="shared" ref="E20:E21" si="0">C20/D20</f>
+        <v>1.2932692307692306</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" ht="16" x14ac:dyDescent="0.35">
+      <c r="B21" s="65" t="s">
+        <v>188</v>
+      </c>
+      <c r="C21">
+        <v>3.38</v>
+      </c>
+      <c r="D21">
+        <v>4.0910000000000002</v>
+      </c>
+      <c r="E21" s="6">
+        <f t="shared" si="0"/>
+        <v>0.82620386213639685</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B22" s="64" t="s">
+        <v>189</v>
+      </c>
+      <c r="F22" s="6">
+        <f>1.64*6</f>
+        <v>9.84</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B23" s="64" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
+      <c r="B24" s="64" t="s">
+        <v>191</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ADABCF3-96BE-45E9-B437-F36F44B301C9}">
   <dimension ref="A3:F21"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="12.54296875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="11.7265625" style="6" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.453125" style="6" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.36328125" style="6" customWidth="1"/>
     <col min="3" max="6" width="8.7265625" style="6"/>
   </cols>
   <sheetData>
@@ -24623,7 +25513,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A45B228-839B-4CA5-9448-9CA1774CB22C}">
   <dimension ref="B1:H11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -24654,7 +25544,7 @@
         <v>156</v>
       </c>
       <c r="G1" s="6" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H1" t="s">
         <v>67</v>
@@ -24824,724 +25714,23 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB485315-044F-4FB0-A3DD-44B741CAB625}">
-  <dimension ref="A1:N24"/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B0CC1CC-64D0-4115-AE5E-AF959282EFAA}">
+  <dimension ref="A1:J16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="33.453125" customWidth="1"/>
-    <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.81640625" customWidth="1"/>
-    <col min="5" max="8" width="8.7265625" style="6"/>
-    <col min="10" max="13" width="8.7265625" style="6"/>
+    <col min="2" max="2" width="15.54296875" customWidth="1"/>
+    <col min="3" max="3" width="14.81640625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="9.453125" style="6" customWidth="1"/>
+    <col min="5" max="5" width="13.81640625" style="6" customWidth="1"/>
+    <col min="6" max="6" width="12.1796875" style="6" customWidth="1"/>
+    <col min="7" max="7" width="13.7265625" style="6" customWidth="1"/>
+    <col min="8" max="8" width="12.81640625" style="6" customWidth="1"/>
+    <col min="9" max="9" width="13.26953125" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="29.7265625" style="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="26" t="s">
-        <v>170</v>
-      </c>
-      <c r="B1" s="26" t="s">
-        <v>171</v>
-      </c>
-      <c r="C1" s="27" t="s">
-        <v>172</v>
-      </c>
-      <c r="D1" s="26" t="s">
-        <v>173</v>
-      </c>
-      <c r="E1" s="142" t="s">
-        <v>575</v>
-      </c>
-      <c r="F1" s="26" t="s">
-        <v>576</v>
-      </c>
-      <c r="G1" s="26" t="s">
-        <v>577</v>
-      </c>
-      <c r="H1" s="26" t="s">
-        <v>578</v>
-      </c>
-      <c r="I1" s="26" t="s">
-        <v>584</v>
-      </c>
-      <c r="J1" s="26" t="s">
-        <v>580</v>
-      </c>
-      <c r="K1" s="26" t="s">
-        <v>579</v>
-      </c>
-      <c r="L1" s="26" t="s">
-        <v>581</v>
-      </c>
-      <c r="M1" s="26" t="s">
-        <v>582</v>
-      </c>
-      <c r="N1" s="26" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" s="103" t="s">
-        <v>174</v>
-      </c>
-      <c r="B3" s="23">
-        <v>3.2</v>
-      </c>
-      <c r="C3">
-        <v>65</v>
-      </c>
-      <c r="D3">
-        <v>50</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="J3" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="K3" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L3" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="M3" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="N3" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="103" t="s">
-        <v>175</v>
-      </c>
-      <c r="B4" s="23">
-        <f>B3+1.64+0.5</f>
-        <v>5.34</v>
-      </c>
-      <c r="C4">
-        <v>90</v>
-      </c>
-      <c r="D4">
-        <v>70</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G4" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H4" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I4" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="J4" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="K4" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L4" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="M4" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="N4" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A5" s="103" t="s">
-        <v>176</v>
-      </c>
-      <c r="B5" s="23">
-        <f>B3+0.72+0.5</f>
-        <v>4.42</v>
-      </c>
-      <c r="C5">
-        <v>110</v>
-      </c>
-      <c r="D5">
-        <v>85</v>
-      </c>
-      <c r="E5" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F5" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G5" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H5" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I5" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="J5" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="K5" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L5" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="M5" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="N5" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A6" s="103" t="s">
-        <v>177</v>
-      </c>
-      <c r="B6" s="23">
-        <v>2.1</v>
-      </c>
-      <c r="C6">
-        <v>65</v>
-      </c>
-      <c r="D6">
-        <v>50</v>
-      </c>
-      <c r="E6" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="K6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="M6" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="N6" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="103" t="s">
-        <v>178</v>
-      </c>
-      <c r="B7" s="23">
-        <f>B6+0.72+0.5</f>
-        <v>3.3200000000000003</v>
-      </c>
-      <c r="C7">
-        <v>110</v>
-      </c>
-      <c r="D7">
-        <v>85</v>
-      </c>
-      <c r="E7" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G7" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I7" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="K7" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L7" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="M7" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="N7" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="103" t="s">
-        <v>179</v>
-      </c>
-      <c r="B8" s="23">
-        <v>2</v>
-      </c>
-      <c r="C8">
-        <v>112</v>
-      </c>
-      <c r="D8">
-        <v>80</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F8" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G8" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I8" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K8" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L8" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="M8" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="N8" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="104" t="s">
-        <v>180</v>
-      </c>
-      <c r="B9" s="24">
-        <v>1.2</v>
-      </c>
-      <c r="C9">
-        <v>80</v>
-      </c>
-      <c r="D9">
-        <v>100</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="J9" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="K9" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L9" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="M9" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="N9" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="104" t="s">
-        <v>181</v>
-      </c>
-      <c r="B10" s="25">
-        <f>0.82+0.72</f>
-        <v>1.54</v>
-      </c>
-      <c r="C10">
-        <v>120</v>
-      </c>
-      <c r="D10">
-        <v>100</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F10" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H10" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I10" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="J10" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="K10" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L10" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="M10" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="N10" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A11" s="102" t="s">
-        <v>500</v>
-      </c>
-      <c r="B11" s="23">
-        <v>0.95</v>
-      </c>
-      <c r="C11">
-        <v>20</v>
-      </c>
-      <c r="D11">
-        <v>100</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F11" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G11" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="H11" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I11" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="J11" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="K11" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L11" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="M11" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="N11" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A12" s="102" t="s">
-        <v>182</v>
-      </c>
-      <c r="B12" s="54">
-        <v>1</v>
-      </c>
-      <c r="C12">
-        <v>58</v>
-      </c>
-      <c r="D12">
-        <v>50</v>
-      </c>
-      <c r="E12" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F12" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G12" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H12" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I12" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="J12" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K12" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L12" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="M12" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="N12" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A13" s="102" t="s">
-        <v>183</v>
-      </c>
-      <c r="B13" s="54">
-        <v>1.5</v>
-      </c>
-      <c r="C13">
-        <v>65</v>
-      </c>
-      <c r="D13">
-        <v>50</v>
-      </c>
-      <c r="E13" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G13" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H13" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I13" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="J13" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="K13" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="L13" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="M13" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="N13" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A14" s="102" t="s">
-        <v>184</v>
-      </c>
-      <c r="B14" s="54">
-        <v>2.5</v>
-      </c>
-      <c r="C14">
-        <v>96</v>
-      </c>
-      <c r="D14">
-        <v>50</v>
-      </c>
-      <c r="E14" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F14" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H14" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="I14" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="J14" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="K14" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L14" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="M14" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="N14" s="6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A15" s="102" t="s">
-        <v>185</v>
-      </c>
-      <c r="B15" s="54">
-        <v>2</v>
-      </c>
-      <c r="C15">
-        <v>114</v>
-      </c>
-      <c r="D15">
-        <v>80</v>
-      </c>
-      <c r="E15" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="F15" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="G15" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="H15" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="J15" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="K15" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="L15" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="M15" s="6" t="s">
-        <v>59</v>
-      </c>
-      <c r="N15" s="6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" ht="16" x14ac:dyDescent="0.35">
-      <c r="B19" s="65" t="s">
-        <v>186</v>
-      </c>
-      <c r="C19">
-        <v>0.5</v>
-      </c>
-      <c r="D19">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="E19" s="6">
-        <f>C19/D19</f>
-        <v>0.4587155963302752</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" ht="16" x14ac:dyDescent="0.35">
-      <c r="B20" s="65" t="s">
-        <v>187</v>
-      </c>
-      <c r="C20">
-        <v>5.38</v>
-      </c>
-      <c r="D20">
-        <v>4.16</v>
-      </c>
-      <c r="E20" s="6">
-        <f t="shared" ref="E20:E21" si="0">C20/D20</f>
-        <v>1.2932692307692306</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" ht="16" x14ac:dyDescent="0.35">
-      <c r="B21" s="65" t="s">
-        <v>188</v>
-      </c>
-      <c r="C21">
-        <v>3.38</v>
-      </c>
-      <c r="D21">
-        <v>4.0910000000000002</v>
-      </c>
-      <c r="E21" s="6">
-        <f t="shared" si="0"/>
-        <v>0.82620386213639685</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B22" s="64" t="s">
-        <v>189</v>
-      </c>
-      <c r="F22" s="6">
-        <f>1.64*6</f>
-        <v>9.84</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B23" s="64" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.35">
-      <c r="B24" s="64" t="s">
-        <v>191</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B0CC1CC-64D0-4115-AE5E-AF959282EFAA}">
-  <dimension ref="A1:I16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.453125" style="6" customWidth="1"/>
-    <col min="4" max="4" width="13.81640625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="12.1796875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="13.7265625" style="6" customWidth="1"/>
-    <col min="7" max="7" width="12.81640625" style="6" customWidth="1"/>
-    <col min="8" max="8" width="13.26953125" style="6" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.7265625" style="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>192</v>
       </c>
@@ -25549,318 +25738,360 @@
         <v>3</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>611</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="E1" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="F1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="H1" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="I1" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="J1" s="6" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>197</v>
       </c>
       <c r="B3" t="s">
         <v>198</v>
       </c>
-      <c r="C3" s="6">
+      <c r="C3" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D3" s="6">
         <v>65</v>
       </c>
-      <c r="D3" s="6">
-        <f t="shared" ref="D3:D6" si="0">C3-5</f>
+      <c r="E3" s="6">
+        <f t="shared" ref="E3:E6" si="0">D3-5</f>
         <v>60</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="F3" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="F3" s="6">
-        <v>0</v>
       </c>
       <c r="G3" s="6">
         <v>0</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="H3" s="6">
+        <v>0</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>199</v>
       </c>
       <c r="B4" t="s">
         <v>144</v>
       </c>
-      <c r="C4" s="6">
+      <c r="C4" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D4" s="6">
         <v>65</v>
       </c>
-      <c r="D4" s="6">
+      <c r="E4" s="6">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="F4" s="6">
-        <v>0</v>
       </c>
       <c r="G4" s="6">
         <v>0</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="6">
+        <v>0</v>
+      </c>
+      <c r="I4" s="6" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>200</v>
       </c>
       <c r="B5" t="s">
         <v>201</v>
       </c>
-      <c r="C5" s="6">
+      <c r="C5" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="6">
         <v>100</v>
       </c>
-      <c r="D5" s="6">
+      <c r="E5" s="6">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="F5" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="F5" s="6">
-        <v>0</v>
       </c>
       <c r="G5" s="6">
         <v>0</v>
       </c>
-      <c r="H5" s="6" t="s">
+      <c r="H5" s="6">
+        <v>0</v>
+      </c>
+      <c r="I5" s="6" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>202</v>
       </c>
       <c r="B6" t="s">
         <v>149</v>
       </c>
-      <c r="C6" s="6">
+      <c r="C6" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="6">
         <v>100</v>
       </c>
-      <c r="D6" s="6">
+      <c r="E6" s="6">
         <f t="shared" si="0"/>
         <v>95</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="F6" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="F6" s="6">
-        <v>0</v>
       </c>
       <c r="G6" s="6">
         <v>0</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="6">
+        <v>0</v>
+      </c>
+      <c r="I6" s="6" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>203</v>
       </c>
       <c r="B7" s="32" t="s">
-        <v>554</v>
-      </c>
-      <c r="C7" s="6">
+        <v>553</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="6">
         <v>82</v>
       </c>
-      <c r="D7" s="6">
-        <f>C7-5</f>
+      <c r="E7" s="6">
+        <f>D7-5</f>
         <v>77</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="F7" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="F7" s="6">
-        <v>4</v>
       </c>
       <c r="G7" s="6">
         <v>4</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="6">
+        <v>4</v>
+      </c>
+      <c r="I7" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="I7" s="6" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J7" s="6" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B8" t="s">
-        <v>555</v>
-      </c>
-      <c r="C8" s="6">
+        <v>554</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="6">
         <v>78</v>
       </c>
-      <c r="D8" s="6">
-        <f>C8-5</f>
+      <c r="E8" s="6">
+        <f>D8-5</f>
         <v>73</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>21</v>
-      </c>
-      <c r="F8" s="6">
-        <v>4</v>
       </c>
       <c r="G8" s="6">
         <v>4</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="6">
+        <v>4</v>
+      </c>
+      <c r="I8" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="I8" s="6" t="s">
-        <v>502</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J8" s="6" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>204</v>
       </c>
       <c r="B10" t="s">
         <v>204</v>
       </c>
-      <c r="C10" s="6">
+      <c r="C10" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D10" s="6">
         <v>45</v>
       </c>
-      <c r="D10" s="6">
+      <c r="E10" s="6">
         <f>17-5</f>
         <v>12</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="F10" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>205</v>
       </c>
       <c r="B11" t="s">
         <v>205</v>
       </c>
-      <c r="C11" s="6">
+      <c r="C11" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="6">
         <v>53</v>
       </c>
-      <c r="D11" s="6">
+      <c r="E11" s="6">
         <f>25-5</f>
         <v>20</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="F11" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>206</v>
       </c>
       <c r="B12" t="s">
         <v>206</v>
       </c>
-      <c r="C12" s="6">
+      <c r="C12" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="6">
         <v>60</v>
       </c>
-      <c r="D12" s="6">
+      <c r="E12" s="6">
         <f>31-7</f>
         <v>24</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="F12" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>207</v>
       </c>
       <c r="B13" t="s">
-        <v>510</v>
-      </c>
-      <c r="C13" s="6">
+        <v>509</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="6">
         <v>70</v>
       </c>
-      <c r="D13" s="6">
+      <c r="E13" s="6">
         <f>42-5</f>
         <v>37</v>
       </c>
-      <c r="E13" s="6" t="s">
+      <c r="F13" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>208</v>
       </c>
       <c r="B14" t="s">
         <v>208</v>
       </c>
-      <c r="C14" s="6">
+      <c r="C14" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D14" s="6">
         <v>60</v>
       </c>
-      <c r="D14" s="6">
+      <c r="E14" s="6">
         <f>32-5</f>
         <v>27</v>
       </c>
-      <c r="E14" s="6" t="s">
+      <c r="F14" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>209</v>
       </c>
       <c r="B15" t="s">
         <v>209</v>
       </c>
-      <c r="C15" s="6">
+      <c r="C15" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="6">
         <v>75</v>
       </c>
-      <c r="D15" s="6">
+      <c r="E15" s="6">
         <f>37-5</f>
         <v>32</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="F15" s="6" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>210</v>
       </c>
       <c r="B16" t="s">
         <v>210</v>
       </c>
-      <c r="C16" s="6">
+      <c r="C16" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="D16" s="6">
         <v>90</v>
       </c>
-      <c r="D16" s="6">
+      <c r="E16" s="6">
         <f>52-5</f>
         <v>47</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="F16" s="6" t="s">
         <v>48</v>
       </c>
     </row>
@@ -25924,7 +26155,7 @@
         <v>220</v>
       </c>
       <c r="M1" s="51" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
@@ -26350,13 +26581,13 @@
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A13" s="108" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B13" s="108" t="s">
         <v>228</v>
       </c>
       <c r="C13" s="108" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="D13" s="109">
         <v>273.05</v>
@@ -26392,7 +26623,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E438F573-1137-4940-BD62-685CBD871B42}">
-  <dimension ref="A1:L77"/>
+  <dimension ref="A1:N77"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.81640625" customWidth="1"/>
@@ -26408,18 +26639,18 @@
     <col min="11" max="11" width="11.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="D1" t="s">
         <v>507</v>
-      </c>
-      <c r="D1" t="s">
-        <v>508</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>246</v>
@@ -26440,15 +26671,15 @@
         <v>251</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>589</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>227</v>
@@ -26479,10 +26710,14 @@
         <f>PI() * G3</f>
         <v>79.796453401180742</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N3">
+        <f>L3/25.4</f>
+        <v>3.1415926535897931</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>227</v>
@@ -26506,7 +26741,7 @@
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="6" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="J4" s="6" t="s">
         <v>335</v>
@@ -26515,10 +26750,14 @@
         <f t="shared" ref="L4:L53" si="1">PI() * G4</f>
         <v>94.247779607693786</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N4">
+        <f t="shared" ref="N4:N53" si="2">L4/25.4</f>
+        <v>3.7105425042399132</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>227</v>
@@ -26549,10 +26788,14 @@
         <f t="shared" si="1"/>
         <v>109.95574287564276</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N5">
+        <f t="shared" si="2"/>
+        <v>4.3289662549465655</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B6" s="113" t="s">
         <v>230</v>
@@ -26583,10 +26826,14 @@
         <f t="shared" si="1"/>
         <v>79.796453401180742</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N6">
+        <f t="shared" si="2"/>
+        <v>3.1415926535897931</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B7" s="113" t="s">
         <v>230</v>
@@ -26610,7 +26857,7 @@
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>335</v>
@@ -26619,10 +26866,14 @@
         <f t="shared" si="1"/>
         <v>94.247779607693786</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N7">
+        <f t="shared" si="2"/>
+        <v>3.7105425042399132</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B8" s="113" t="s">
         <v>230</v>
@@ -26653,10 +26904,14 @@
         <f t="shared" si="1"/>
         <v>109.95574287564276</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N8">
+        <f t="shared" si="2"/>
+        <v>4.3289662549465655</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B9" s="113" t="s">
         <v>230</v>
@@ -26680,7 +26935,7 @@
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>335</v>
@@ -26689,10 +26944,14 @@
         <f t="shared" si="1"/>
         <v>125.66370614359172</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N9">
+        <f t="shared" si="2"/>
+        <v>4.9473900056532178</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B10" s="113" t="s">
         <v>230</v>
@@ -26723,8 +26982,12 @@
         <f t="shared" si="1"/>
         <v>141.37166941154069</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N10">
+        <f t="shared" si="2"/>
+        <v>5.5658137563598702</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>233</v>
       </c>
@@ -26757,8 +27020,12 @@
         <f t="shared" si="1"/>
         <v>79.796453401180742</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N11">
+        <f t="shared" si="2"/>
+        <v>3.1415926535897931</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>233</v>
       </c>
@@ -26784,7 +27051,7 @@
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>335</v>
@@ -26793,8 +27060,12 @@
         <f t="shared" si="1"/>
         <v>94.247779607693786</v>
       </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N12">
+        <f t="shared" si="2"/>
+        <v>3.7105425042399132</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>233</v>
       </c>
@@ -26827,8 +27098,12 @@
         <f t="shared" si="1"/>
         <v>109.95574287564276</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N13">
+        <f t="shared" si="2"/>
+        <v>4.3289662549465655</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>233</v>
       </c>
@@ -26854,7 +27129,7 @@
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="6" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>335</v>
@@ -26863,8 +27138,12 @@
         <f t="shared" si="1"/>
         <v>125.66370614359172</v>
       </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N14">
+        <f t="shared" si="2"/>
+        <v>4.9473900056532178</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>233</v>
       </c>
@@ -26897,8 +27176,12 @@
         <f t="shared" si="1"/>
         <v>141.37166941154069</v>
       </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N15">
+        <f t="shared" si="2"/>
+        <v>5.5658137563598702</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>235</v>
       </c>
@@ -26924,7 +27207,7 @@
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="6" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>335</v>
@@ -26933,8 +27216,12 @@
         <f t="shared" si="1"/>
         <v>94.247779607693786</v>
       </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N16">
+        <f t="shared" si="2"/>
+        <v>3.7105425042399132</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>235</v>
       </c>
@@ -26967,8 +27254,12 @@
         <f t="shared" si="1"/>
         <v>109.95574287564276</v>
       </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N17">
+        <f t="shared" si="2"/>
+        <v>4.3289662549465655</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>235</v>
       </c>
@@ -26994,7 +27285,7 @@
       </c>
       <c r="H18" s="6"/>
       <c r="I18" s="6" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>335</v>
@@ -27003,8 +27294,12 @@
         <f t="shared" si="1"/>
         <v>125.66370614359172</v>
       </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N18">
+        <f t="shared" si="2"/>
+        <v>4.9473900056532178</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>235</v>
       </c>
@@ -27037,8 +27332,12 @@
         <f t="shared" si="1"/>
         <v>141.37166941154069</v>
       </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N19">
+        <f t="shared" si="2"/>
+        <v>5.5658137563598702</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>235</v>
       </c>
@@ -27064,7 +27363,7 @@
       </c>
       <c r="H20" s="6"/>
       <c r="I20" s="6" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>335</v>
@@ -27073,8 +27372,12 @@
         <f t="shared" si="1"/>
         <v>172.78759594743863</v>
       </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N20">
+        <f t="shared" si="2"/>
+        <v>6.8026612577731749</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>237</v>
       </c>
@@ -27086,7 +27389,7 @@
         <v>158.4</v>
       </c>
       <c r="D21" s="113">
-        <f t="shared" ref="D21:D33" si="2">(E21-C21)/2</f>
+        <f t="shared" ref="D21:D33" si="3">(E21-C21)/2</f>
         <v>-1.7000000000000028</v>
       </c>
       <c r="E21" s="6">
@@ -27107,8 +27410,12 @@
         <f t="shared" si="1"/>
         <v>125.66370614359172</v>
       </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N21">
+        <f t="shared" si="2"/>
+        <v>4.9473900056532178</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>237</v>
       </c>
@@ -27120,7 +27427,7 @@
         <v>158.4</v>
       </c>
       <c r="D22" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-1.7000000000000028</v>
       </c>
       <c r="E22" s="6">
@@ -27141,8 +27448,12 @@
         <f t="shared" si="1"/>
         <v>141.37166941154069</v>
       </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N22">
+        <f t="shared" si="2"/>
+        <v>5.5658137563598702</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>237</v>
       </c>
@@ -27154,7 +27465,7 @@
         <v>158.4</v>
       </c>
       <c r="D23" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-1.7000000000000028</v>
       </c>
       <c r="E23" s="6">
@@ -27175,8 +27486,12 @@
         <f t="shared" si="1"/>
         <v>172.78759594743863</v>
       </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N23">
+        <f t="shared" si="2"/>
+        <v>6.8026612577731749</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>237</v>
       </c>
@@ -27188,7 +27503,7 @@
         <v>158.4</v>
       </c>
       <c r="D24" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E24" s="6">
@@ -27209,8 +27524,12 @@
         <f t="shared" si="1"/>
         <v>94.247779607693786</v>
       </c>
-    </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N24">
+        <f t="shared" si="2"/>
+        <v>3.7105425042399132</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
         <v>237</v>
       </c>
@@ -27222,7 +27541,7 @@
         <v>158.4</v>
       </c>
       <c r="D25" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E25" s="6">
@@ -27243,8 +27562,12 @@
         <f t="shared" si="1"/>
         <v>109.95574287564276</v>
       </c>
-    </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N25">
+        <f t="shared" si="2"/>
+        <v>4.3289662549465655</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>237</v>
       </c>
@@ -27256,7 +27579,7 @@
         <v>158.4</v>
       </c>
       <c r="D26" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E26" s="6">
@@ -27277,8 +27600,12 @@
         <f t="shared" si="1"/>
         <v>125.66370614359172</v>
       </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N26">
+        <f t="shared" si="2"/>
+        <v>4.9473900056532178</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>237</v>
       </c>
@@ -27290,7 +27617,7 @@
         <v>158.4</v>
       </c>
       <c r="D27" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E27" s="6">
@@ -27311,8 +27638,12 @@
         <f t="shared" si="1"/>
         <v>141.37166941154069</v>
       </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N27">
+        <f t="shared" si="2"/>
+        <v>5.5658137563598702</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
         <v>237</v>
       </c>
@@ -27324,7 +27655,7 @@
         <v>158.4</v>
       </c>
       <c r="D28" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E28" s="6">
@@ -27345,8 +27676,12 @@
         <f t="shared" si="1"/>
         <v>172.78759594743863</v>
       </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N28">
+        <f t="shared" si="2"/>
+        <v>6.8026612577731749</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
         <v>237</v>
       </c>
@@ -27358,7 +27693,7 @@
         <v>158.4</v>
       </c>
       <c r="D29" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.2999999999999972</v>
       </c>
       <c r="E29" s="6">
@@ -27379,8 +27714,12 @@
         <f t="shared" si="1"/>
         <v>94.247779607693786</v>
       </c>
-    </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N29">
+        <f t="shared" si="2"/>
+        <v>3.7105425042399132</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
         <v>237</v>
       </c>
@@ -27392,7 +27731,7 @@
         <v>158.4</v>
       </c>
       <c r="D30" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.2999999999999972</v>
       </c>
       <c r="E30" s="6">
@@ -27413,8 +27752,12 @@
         <f t="shared" si="1"/>
         <v>109.95574287564276</v>
       </c>
-    </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N30">
+        <f t="shared" si="2"/>
+        <v>4.3289662549465655</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
         <v>237</v>
       </c>
@@ -27426,7 +27769,7 @@
         <v>158.4</v>
       </c>
       <c r="D31" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.2999999999999972</v>
       </c>
       <c r="E31" s="6">
@@ -27447,8 +27790,12 @@
         <f t="shared" si="1"/>
         <v>125.66370614359172</v>
       </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N31">
+        <f t="shared" si="2"/>
+        <v>4.9473900056532178</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
         <v>237</v>
       </c>
@@ -27460,7 +27807,7 @@
         <v>158.4</v>
       </c>
       <c r="D32" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.2999999999999972</v>
       </c>
       <c r="E32" s="6">
@@ -27481,8 +27828,12 @@
         <f t="shared" si="1"/>
         <v>141.37166941154069</v>
       </c>
-    </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N32">
+        <f t="shared" si="2"/>
+        <v>5.5658137563598702</v>
+      </c>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
         <v>237</v>
       </c>
@@ -27494,7 +27845,7 @@
         <v>158.4</v>
       </c>
       <c r="D33" s="113">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>1.2999999999999972</v>
       </c>
       <c r="E33" s="6">
@@ -27515,8 +27866,12 @@
         <f t="shared" si="1"/>
         <v>172.78759594743863</v>
       </c>
-    </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N33">
+        <f t="shared" si="2"/>
+        <v>6.8026612577731749</v>
+      </c>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="113" t="s">
         <v>239</v>
       </c>
@@ -27549,8 +27904,12 @@
         <f t="shared" si="1"/>
         <v>125.66370614359172</v>
       </c>
-    </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N34">
+        <f t="shared" si="2"/>
+        <v>4.9473900056532178</v>
+      </c>
+    </row>
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="113" t="s">
         <v>239</v>
       </c>
@@ -27562,7 +27921,7 @@
         <v>180.4</v>
       </c>
       <c r="D35" s="113">
-        <f t="shared" ref="D35:D51" si="3">(E35-C35)/2</f>
+        <f t="shared" ref="D35:D51" si="4">(E35-C35)/2</f>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E35" s="6">
@@ -27583,8 +27942,12 @@
         <f t="shared" si="1"/>
         <v>141.37166941154069</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N35">
+        <f t="shared" si="2"/>
+        <v>5.5658137563598702</v>
+      </c>
+    </row>
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="113" t="s">
         <v>239</v>
       </c>
@@ -27596,7 +27959,7 @@
         <v>180.4</v>
       </c>
       <c r="D36" s="113">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E36" s="6">
@@ -27617,8 +27980,12 @@
         <f t="shared" si="1"/>
         <v>157.07963267948966</v>
       </c>
-    </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N36">
+        <f t="shared" si="2"/>
+        <v>6.1842375070665225</v>
+      </c>
+    </row>
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="113" t="s">
         <v>239</v>
       </c>
@@ -27630,7 +27997,7 @@
         <v>180.4</v>
       </c>
       <c r="D37" s="113">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E37" s="6">
@@ -27651,8 +28018,12 @@
         <f t="shared" si="1"/>
         <v>172.78759594743863</v>
       </c>
-    </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N37">
+        <f t="shared" si="2"/>
+        <v>6.8026612577731749</v>
+      </c>
+    </row>
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="113" t="s">
         <v>239</v>
       </c>
@@ -27664,7 +28035,7 @@
         <v>180.4</v>
       </c>
       <c r="D38" s="113">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E38" s="6">
@@ -27685,8 +28056,12 @@
         <f t="shared" si="1"/>
         <v>188.49555921538757</v>
       </c>
-    </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N38">
+        <f t="shared" si="2"/>
+        <v>7.4210850084798263</v>
+      </c>
+    </row>
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="113" t="s">
         <v>242</v>
       </c>
@@ -27698,7 +28073,7 @@
         <v>206.4</v>
       </c>
       <c r="D39" s="113">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-3.7000000000000028</v>
       </c>
       <c r="E39" s="6">
@@ -27719,8 +28094,12 @@
         <f t="shared" si="1"/>
         <v>157.07963267948966</v>
       </c>
-    </row>
-    <row r="40" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N39">
+        <f t="shared" si="2"/>
+        <v>6.1842375070665225</v>
+      </c>
+    </row>
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="113" t="s">
         <v>242</v>
       </c>
@@ -27732,7 +28111,7 @@
         <v>206.4</v>
       </c>
       <c r="D40" s="113">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-3.7000000000000028</v>
       </c>
       <c r="E40" s="6">
@@ -27753,8 +28132,12 @@
         <f t="shared" si="1"/>
         <v>172.78759594743863</v>
       </c>
-    </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N40">
+        <f t="shared" si="2"/>
+        <v>6.8026612577731749</v>
+      </c>
+    </row>
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="113" t="s">
         <v>242</v>
       </c>
@@ -27766,7 +28149,7 @@
         <v>206.4</v>
       </c>
       <c r="D41" s="113">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-3.7000000000000028</v>
       </c>
       <c r="E41" s="6">
@@ -27787,8 +28170,12 @@
         <f t="shared" si="1"/>
         <v>188.49555921538757</v>
       </c>
-    </row>
-    <row r="42" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N41">
+        <f t="shared" si="2"/>
+        <v>7.4210850084798263</v>
+      </c>
+    </row>
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="113" t="s">
         <v>242</v>
       </c>
@@ -27800,7 +28187,7 @@
         <v>206.4</v>
       </c>
       <c r="D42" s="113">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-1.7000000000000028</v>
       </c>
       <c r="E42" s="6">
@@ -27821,8 +28208,12 @@
         <f t="shared" si="1"/>
         <v>172.78759594743863</v>
       </c>
-    </row>
-    <row r="43" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N42">
+        <f t="shared" si="2"/>
+        <v>6.8026612577731749</v>
+      </c>
+    </row>
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" s="113" t="s">
         <v>242</v>
       </c>
@@ -27834,7 +28225,7 @@
         <v>206.4</v>
       </c>
       <c r="D43" s="113">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-1.7000000000000028</v>
       </c>
       <c r="E43" s="6">
@@ -27855,8 +28246,12 @@
         <f t="shared" si="1"/>
         <v>188.49555921538757</v>
       </c>
-    </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N43">
+        <f t="shared" si="2"/>
+        <v>7.4210850084798263</v>
+      </c>
+    </row>
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="113" t="s">
         <v>242</v>
       </c>
@@ -27868,7 +28263,7 @@
         <v>206.4</v>
       </c>
       <c r="D44" s="113">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E44" s="6">
@@ -27889,8 +28284,12 @@
         <f t="shared" si="1"/>
         <v>94.247779607693786</v>
       </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N44">
+        <f t="shared" si="2"/>
+        <v>3.7105425042399132</v>
+      </c>
+    </row>
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="113" t="s">
         <v>242</v>
       </c>
@@ -27902,7 +28301,7 @@
         <v>206.4</v>
       </c>
       <c r="D45" s="113">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E45" s="6">
@@ -27923,8 +28322,12 @@
         <f t="shared" si="1"/>
         <v>125.66370614359172</v>
       </c>
-    </row>
-    <row r="46" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N45">
+        <f t="shared" si="2"/>
+        <v>4.9473900056532178</v>
+      </c>
+    </row>
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="113" t="s">
         <v>242</v>
       </c>
@@ -27936,7 +28339,7 @@
         <v>206.4</v>
       </c>
       <c r="D46" s="113">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E46" s="6">
@@ -27957,8 +28360,12 @@
         <f t="shared" si="1"/>
         <v>157.07963267948966</v>
       </c>
-    </row>
-    <row r="47" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N46">
+        <f t="shared" si="2"/>
+        <v>6.1842375070665225</v>
+      </c>
+    </row>
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="113" t="s">
         <v>242</v>
       </c>
@@ -27970,7 +28377,7 @@
         <v>206.4</v>
       </c>
       <c r="D47" s="113">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E47" s="6">
@@ -27991,8 +28398,12 @@
         <f t="shared" si="1"/>
         <v>172.78759594743863</v>
       </c>
-    </row>
-    <row r="48" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N47">
+        <f t="shared" si="2"/>
+        <v>6.8026612577731749</v>
+      </c>
+    </row>
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="113" t="s">
         <v>242</v>
       </c>
@@ -28004,7 +28415,7 @@
         <v>206.4</v>
       </c>
       <c r="D48" s="113">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E48" s="6">
@@ -28025,8 +28436,12 @@
         <f t="shared" si="1"/>
         <v>188.49555921538757</v>
       </c>
-    </row>
-    <row r="49" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N48">
+        <f t="shared" si="2"/>
+        <v>7.4210850084798263</v>
+      </c>
+    </row>
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>245</v>
       </c>
@@ -28038,7 +28453,7 @@
         <v>261.27000000000004</v>
       </c>
       <c r="D49" s="113">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-2.1350000000000193</v>
       </c>
       <c r="E49" s="6">
@@ -28059,8 +28474,12 @@
         <f t="shared" si="1"/>
         <v>172.78759594743863</v>
       </c>
-    </row>
-    <row r="50" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N49">
+        <f t="shared" si="2"/>
+        <v>6.8026612577731749</v>
+      </c>
+    </row>
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>245</v>
       </c>
@@ -28072,7 +28491,7 @@
         <v>261.27000000000004</v>
       </c>
       <c r="D50" s="113">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-1.1350000000000193</v>
       </c>
       <c r="E50" s="6">
@@ -28093,8 +28512,12 @@
         <f t="shared" si="1"/>
         <v>157.07963267948966</v>
       </c>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N50">
+        <f t="shared" si="2"/>
+        <v>6.1842375070665225</v>
+      </c>
+    </row>
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>245</v>
       </c>
@@ -28106,7 +28529,7 @@
         <v>261.27000000000004</v>
       </c>
       <c r="D51" s="113">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-1.1350000000000193</v>
       </c>
       <c r="E51" s="6">
@@ -28127,20 +28550,24 @@
         <f t="shared" si="1"/>
         <v>188.49555921538757</v>
       </c>
-    </row>
-    <row r="52" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N51">
+        <f t="shared" si="2"/>
+        <v>7.4210850084798263</v>
+      </c>
+    </row>
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C52" s="6">
         <f>Axles!F13</f>
         <v>257.05</v>
       </c>
       <c r="D52" s="113">
-        <f t="shared" ref="D52" si="4">(E52-C52)/2</f>
+        <f t="shared" ref="D52" si="5">(E52-C52)/2</f>
         <v>1.4749999999999943</v>
       </c>
       <c r="E52" s="6">
@@ -28159,20 +28586,24 @@
         <f t="shared" si="1"/>
         <v>188.49555921538757</v>
       </c>
-    </row>
-    <row r="53" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N52">
+        <f t="shared" si="2"/>
+        <v>7.4210850084798263</v>
+      </c>
+    </row>
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C53" s="6">
         <f>Axles!F13</f>
         <v>257.05</v>
       </c>
       <c r="D53" s="113">
-        <f t="shared" ref="D53" si="5">(E53-C53)/2</f>
+        <f t="shared" ref="D53" si="6">(E53-C53)/2</f>
         <v>1.4749999999999943</v>
       </c>
       <c r="E53" s="6">
@@ -28191,8 +28622,12 @@
         <f t="shared" si="1"/>
         <v>251.32741228718345</v>
       </c>
-    </row>
-    <row r="58" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="N53">
+        <f t="shared" si="2"/>
+        <v>9.8947800113064357</v>
+      </c>
+    </row>
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" s="68"/>
       <c r="B58" s="68"/>
       <c r="C58" s="68"/>
@@ -28204,9 +28639,9 @@
       <c r="I58" s="68"/>
       <c r="J58" s="68"/>
     </row>
-    <row r="59" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B59" s="6"/>
       <c r="D59" s="6"/>
@@ -28225,9 +28660,9 @@
         <v>254</v>
       </c>
     </row>
-    <row r="60" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B60" s="6"/>
       <c r="D60" s="6"/>
@@ -28246,7 +28681,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="61" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="D61" s="6"/>
@@ -28265,7 +28700,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="62" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="D62" s="6"/>
@@ -28284,7 +28719,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="63" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="D63" s="6"/>
@@ -28303,7 +28738,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="64" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="D64" s="6"/>
@@ -28324,7 +28759,7 @@
     </row>
     <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B65" s="6"/>
       <c r="D65" s="6"/>
@@ -28345,7 +28780,7 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" s="6" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B66" s="6"/>
       <c r="D66" s="6"/>

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3478" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1A5D4E83-4F7C-4C11-8FCA-4DDE1F8B2BBE}"/>
+  <xr:revisionPtr revIDLastSave="3541" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2374123-818A-4C31-96B0-B20E2C7AA7A7}"/>
   <bookViews>
-    <workbookView xWindow="11200" yWindow="1490" windowWidth="23480" windowHeight="17860" tabRatio="905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1150" yWindow="2470" windowWidth="34980" windowHeight="18240" tabRatio="905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="4" r:id="rId1"/>
-    <sheet name="Online codes" sheetId="17" r:id="rId2"/>
+    <sheet name="Product group" sheetId="22" r:id="rId2"/>
     <sheet name="Lath" sheetId="7" r:id="rId3"/>
     <sheet name="Bottom lath" sheetId="9" r:id="rId4"/>
     <sheet name="Wind class" sheetId="20" r:id="rId5"/>
@@ -30,6 +30,7 @@
     <sheet name="Endplate" sheetId="13" r:id="rId15"/>
     <sheet name="Wicket doors" sheetId="14" r:id="rId16"/>
     <sheet name="Size range" sheetId="19" r:id="rId17"/>
+    <sheet name="Online codes" sheetId="17" r:id="rId18"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9">Motors!$A$1:$S$143</definedName>
@@ -55,132 +56,6 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>robert hyrons</author>
-  </authors>
-  <commentList>
-    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{85067B68-D384-4989-8BC1-39E5AFD6EDD0}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t>robert hyrons:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <charset val="1"/>
-          </rPr>
-          <t xml:space="preserve">
-This will group in to common configerations such as seceurodoor motor opp, seceurodor spring opp or shield. There the physical make up is common.  </t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>robert hyrons</author>
-  </authors>
-  <commentList>
-    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{42B2D1D3-45D6-4B4F-92A5-C86E44261C2E}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>robert hyrons:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-use this data column to match the max lift torque required to spec SB, advised from GFA UK 27/1/2026</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>robert hyrons</author>
-  </authors>
-  <commentList>
-    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{680B1BE3-3686-4262-8DBA-BDEB6ADD9486}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>robert hyrons:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-current load info not verified, needs checking</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{C212F676-8F98-4020-9899-8B9BD0CC5028}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>robert hyrons:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-This is the distance from guide or angle attachment to the endplat outter</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>robert hyrons</author>
@@ -282,11 +157,127 @@
         </r>
       </text>
     </comment>
+    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{4290DBF6-4C76-4889-AFBE-FA3A6B2BDE7F}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>robert hyrons:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+This is for lath that can be rever coiled, the calulation will add 10mm to the first wrap of the shutter, this will increase troque and possibly endplate size.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
-<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments10.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>robert hyrons</author>
+  </authors>
+  <commentList>
+    <comment ref="C1" authorId="0" shapeId="0" xr:uid="{680B1BE3-3686-4262-8DBA-BDEB6ADD9486}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>robert hyrons:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+current load info not verified, needs checking</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{C212F676-8F98-4020-9899-8B9BD0CC5028}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>robert hyrons:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+This is the distance from guide or angle attachment to the endplat outter</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments11.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>robert hyrons</author>
+  </authors>
+  <commentList>
+    <comment ref="H1" authorId="0" shapeId="0" xr:uid="{85067B68-D384-4989-8BC1-39E5AFD6EDD0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>robert hyrons:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+This will group in to common configerations such as seceurodoor motor opp, seceurodor spring opp or shield. There the physical make up is common.  </t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>robert hyrons</author>
@@ -368,7 +359,7 @@
 </comments>
 </file>
 
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Rob Hyrons</author>
@@ -402,7 +393,7 @@
 </comments>
 </file>
 
-<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>robert hyrons</author>
@@ -461,7 +452,7 @@
 </comments>
 </file>
 
-<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments5.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>robert hyrons</author>
@@ -495,7 +486,7 @@
 </comments>
 </file>
 
-<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments6.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>robert hyrons</author>
@@ -678,7 +669,7 @@
 </comments>
 </file>
 
-<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments7.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>robert hyrons</author>
@@ -737,7 +728,7 @@
 </comments>
 </file>
 
-<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>robert hyrons</author>
@@ -764,6 +755,40 @@
           </rPr>
           <t xml:space="preserve">
 needs confirming with supplier</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments9.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>robert hyrons</author>
+  </authors>
+  <commentList>
+    <comment ref="B1" authorId="0" shapeId="0" xr:uid="{42B2D1D3-45D6-4B4F-92A5-C86E44261C2E}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>robert hyrons:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+use this data column to match the max lift torque required to spec SB, advised from GFA UK 27/1/2026</t>
         </r>
       </text>
     </comment>
@@ -804,7 +829,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2393" uniqueCount="632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2478" uniqueCount="641">
   <si>
     <t>This over view explaines the working of this file and how it feeds information to the online calculator.</t>
   </si>
@@ -2687,9 +2712,6 @@
     <t>90 fixing</t>
   </si>
   <si>
-    <t xml:space="preserve">39 plastic wind </t>
-  </si>
-  <si>
     <t>T-Rail  with 11mm wireless-rubber 4.2kg/m</t>
   </si>
   <si>
@@ -2700,6 +2722,36 @@
   </si>
   <si>
     <t>100mm  Rail with 11mm wireless-rubber 0.95kg/m</t>
+  </si>
+  <si>
+    <t>Group name</t>
+  </si>
+  <si>
+    <t>Industrial with motor</t>
+  </si>
+  <si>
+    <t>Traditional with motor</t>
+  </si>
+  <si>
+    <t>Shield</t>
+  </si>
+  <si>
+    <t>Glide</t>
+  </si>
+  <si>
+    <t>Shield,Glide</t>
+  </si>
+  <si>
+    <t>Industrial with motor, Traditional with motor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">38 plastic wind </t>
+  </si>
+  <si>
+    <t>Endlock wind type</t>
+  </si>
+  <si>
+    <t>reversible</t>
   </si>
 </sst>
 </file>
@@ -2997,7 +3049,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="149">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3403,10 +3455,13 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="20% - Accent1 2" xfId="1" xr:uid="{4B6C72F7-C4CA-450E-9C13-94CEF72F8B8D}"/>
@@ -20288,19 +20343,19 @@
       <c r="X55" s="87"/>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="H60" s="146" t="s">
+      <c r="H60" s="147" t="s">
         <v>549</v>
       </c>
-      <c r="I60" s="146"/>
-      <c r="J60" s="146"/>
-      <c r="K60" s="146"/>
-      <c r="L60" s="146"/>
-      <c r="M60" s="146"/>
-      <c r="N60" s="146"/>
-      <c r="O60" s="146"/>
-      <c r="P60" s="146"/>
-      <c r="Q60" s="146"/>
-      <c r="R60" s="146"/>
+      <c r="I60" s="147"/>
+      <c r="J60" s="147"/>
+      <c r="K60" s="147"/>
+      <c r="L60" s="147"/>
+      <c r="M60" s="147"/>
+      <c r="N60" s="147"/>
+      <c r="O60" s="147"/>
+      <c r="P60" s="147"/>
+      <c r="Q60" s="147"/>
+      <c r="R60" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -21352,7 +21407,7 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63386739-1836-4135-BDCC-F0CD02A919B6}">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.90625" style="32" bestFit="1" customWidth="1"/>
@@ -21361,9 +21416,10 @@
     <col min="5" max="5" width="12.54296875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.54296875" customWidth="1"/>
     <col min="7" max="7" width="10.453125" customWidth="1"/>
+    <col min="8" max="8" width="26.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="32" t="s">
         <v>3</v>
       </c>
@@ -21385,8 +21441,11 @@
       <c r="G1" s="6" t="s">
         <v>468</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H1" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -21394,7 +21453,7 @@
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="32" t="s">
         <v>488</v>
       </c>
@@ -21417,8 +21476,11 @@
       <c r="G3" s="6">
         <v>40</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H3" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="32" t="s">
         <v>489</v>
       </c>
@@ -21441,8 +21503,11 @@
       <c r="G4" s="6">
         <v>40</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H4" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="32" t="s">
         <v>490</v>
       </c>
@@ -21465,8 +21530,11 @@
       <c r="G5" s="6">
         <v>40</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H5" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="32" t="s">
         <v>491</v>
       </c>
@@ -21489,8 +21557,11 @@
       <c r="G6" s="6">
         <v>40</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H6" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="32" t="s">
         <v>487</v>
       </c>
@@ -21513,8 +21584,11 @@
       <c r="G7" s="6">
         <v>60</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H7" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="32" t="s">
         <v>492</v>
       </c>
@@ -21537,8 +21611,11 @@
       <c r="G8" s="6">
         <v>60</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H8" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="32" t="s">
         <v>493</v>
       </c>
@@ -21561,8 +21638,11 @@
       <c r="G9" s="6">
         <v>60</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H9" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="32" t="s">
         <v>494</v>
       </c>
@@ -21585,8 +21665,11 @@
       <c r="G10" s="6">
         <v>60</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H10" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -21594,7 +21677,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="32" t="s">
         <v>469</v>
       </c>
@@ -21617,8 +21700,11 @@
       <c r="G13" s="6">
         <v>92</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H13" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="32" t="s">
         <v>470</v>
       </c>
@@ -21641,8 +21727,11 @@
       <c r="G14" s="6">
         <v>92</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H14" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="32" t="s">
         <v>471</v>
       </c>
@@ -21665,8 +21754,11 @@
       <c r="G15" s="6">
         <v>92</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H15" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="32" t="s">
         <v>472</v>
       </c>
@@ -21689,8 +21781,11 @@
       <c r="G16" s="6">
         <v>92</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H16" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="32" t="s">
         <v>473</v>
       </c>
@@ -21713,8 +21808,11 @@
       <c r="G17" s="6">
         <v>92</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H17" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="32" t="s">
         <v>474</v>
       </c>
@@ -21737,8 +21835,11 @@
       <c r="G18" s="6">
         <v>92</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H18" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="53" t="s">
         <v>475</v>
       </c>
@@ -21761,11 +21862,14 @@
       <c r="G19" s="6">
         <v>92</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H19" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="32" t="s">
         <v>609</v>
       </c>
@@ -21788,8 +21892,11 @@
       <c r="G21" s="6">
         <v>6</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H21" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="32" t="s">
         <v>610</v>
       </c>
@@ -21812,8 +21919,11 @@
       <c r="G22" s="6">
         <v>6</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H22" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="32" t="s">
         <v>611</v>
       </c>
@@ -21836,8 +21946,11 @@
       <c r="G23" s="6">
         <v>8</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H23" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="32" t="s">
         <v>612</v>
       </c>
@@ -21860,8 +21973,11 @@
       <c r="G24" s="6">
         <v>8</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H24" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="32" t="s">
         <v>613</v>
       </c>
@@ -21884,8 +22000,11 @@
       <c r="G25" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H25" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="32" t="s">
         <v>614</v>
       </c>
@@ -21908,8 +22027,11 @@
       <c r="G26" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H26" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="53" t="s">
         <v>615</v>
       </c>
@@ -21932,8 +22054,11 @@
       <c r="G27" s="6">
         <v>10</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H27" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="32" t="s">
         <v>476</v>
       </c>
@@ -21954,10 +22079,13 @@
         <v>85</v>
       </c>
       <c r="G30" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1E-3</v>
+      </c>
+      <c r="H30" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="32" t="s">
         <v>477</v>
       </c>
@@ -21978,10 +22106,13 @@
         <v>130</v>
       </c>
       <c r="G31" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1E-3</v>
+      </c>
+      <c r="H31" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="32" t="s">
         <v>478</v>
       </c>
@@ -22002,10 +22133,13 @@
         <v>155</v>
       </c>
       <c r="G32" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1E-3</v>
+      </c>
+      <c r="H32" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="32" t="s">
         <v>479</v>
       </c>
@@ -22026,10 +22160,13 @@
         <v>200</v>
       </c>
       <c r="G33" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1E-3</v>
+      </c>
+      <c r="H33" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="32" t="s">
         <v>480</v>
       </c>
@@ -22050,10 +22187,13 @@
         <v>250</v>
       </c>
       <c r="G34" s="6">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1E-3</v>
+      </c>
+      <c r="H34" t="s">
+        <v>635</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="32" t="s">
         <v>481</v>
       </c>
@@ -22074,7 +22214,10 @@
         <v>300</v>
       </c>
       <c r="G35" s="6">
-        <v>0</v>
+        <v>1E-3</v>
+      </c>
+      <c r="H35" t="s">
+        <v>635</v>
       </c>
     </row>
   </sheetData>
@@ -22148,14 +22291,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="146" t="s">
+      <c r="A2" s="147" t="s">
         <v>540</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="146"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -22545,7 +22688,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3B9ED08-8454-4272-8896-17578EF9EBC9}">
   <dimension ref="A1:K36"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -23004,9 +23147,47 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{54D6711C-947E-4308-A14E-8BE542A5BA69}">
+  <dimension ref="B1:B6"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="26.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B1" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="3" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B3" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="4" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B4" t="s">
+        <v>633</v>
+      </c>
+    </row>
+    <row r="5" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B5" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="6" spans="2:2" x14ac:dyDescent="0.35">
+      <c r="B6" t="s">
+        <v>635</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47E91FF3-79AA-48A9-9F88-C48DFFEF60AE}">
-  <dimension ref="A1:R210"/>
+  <dimension ref="A1:S210"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="35.453125" bestFit="1" customWidth="1"/>
@@ -23021,7 +23202,7 @@
     <col min="16" max="16" width="10.7265625" style="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="48.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:19" s="1" customFormat="1" ht="48.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="35" t="s">
         <v>3</v>
       </c>
@@ -23076,8 +23257,11 @@
       <c r="R1" s="1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="2" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S1" s="1" t="s">
+        <v>640</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="33" t="s">
         <v>19</v>
       </c>
@@ -23125,8 +23309,11 @@
       <c r="R2" s="142" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="3" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S2" s="148" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="39" t="s">
         <v>24</v>
       </c>
@@ -23174,8 +23361,11 @@
       <c r="R3" s="142" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="4" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S3" s="148" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="33" t="s">
         <v>26</v>
       </c>
@@ -23223,8 +23413,11 @@
       <c r="R4" s="142" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="5" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S4" s="148" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="39" t="s">
         <v>27</v>
       </c>
@@ -23272,8 +23465,11 @@
       <c r="R5" s="142" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="6" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S5" s="148" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="33" t="s">
         <v>28</v>
       </c>
@@ -23321,8 +23517,11 @@
       <c r="R6" s="142" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="7" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S6" s="148" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="39" t="s">
         <v>29</v>
       </c>
@@ -23370,8 +23569,11 @@
       <c r="R7" s="142" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="8" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S7" s="148" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="33" t="s">
         <v>30</v>
       </c>
@@ -23419,8 +23621,11 @@
       <c r="R8" s="142" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="9" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S8" s="148" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="39" t="s">
         <v>31</v>
       </c>
@@ -23468,8 +23673,11 @@
       <c r="R9" s="142" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="10" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S9" s="148" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="33" t="s">
         <v>32</v>
       </c>
@@ -23517,8 +23725,11 @@
       <c r="R10" s="142" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="11" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S10" s="148" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="39" t="s">
         <v>33</v>
       </c>
@@ -23566,8 +23777,11 @@
       <c r="R11" s="142" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="12" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S11" s="148" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="33" t="s">
         <v>34</v>
       </c>
@@ -23615,8 +23829,11 @@
       <c r="R12" s="142" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="13" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S12" s="148" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="39" t="s">
         <v>35</v>
       </c>
@@ -23664,8 +23881,11 @@
       <c r="R13" s="142" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="14" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S13" s="148" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="33" t="s">
         <v>36</v>
       </c>
@@ -23713,8 +23933,11 @@
       <c r="R14" s="142" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="15" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S14" s="148" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="39" t="s">
         <v>37</v>
       </c>
@@ -23762,8 +23985,11 @@
       <c r="R15" s="142" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="16" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S15" s="148" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="33" t="s">
         <v>38</v>
       </c>
@@ -23811,8 +24037,11 @@
       <c r="R16" s="142" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="17" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S16" s="148" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="39" t="s">
         <v>39</v>
       </c>
@@ -23860,8 +24089,11 @@
       <c r="R17" s="142" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="18" spans="1:18" s="69" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S17" s="148" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:19" s="69" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="101" t="s">
         <v>40</v>
       </c>
@@ -23880,7 +24112,7 @@
       <c r="O18" s="68"/>
       <c r="P18" s="70"/>
     </row>
-    <row r="19" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="33" t="s">
         <v>41</v>
       </c>
@@ -23927,8 +24159,11 @@
       <c r="R19" s="26" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="20" spans="1:18" s="69" customFormat="1" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S19" s="148" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="20" spans="1:19" s="69" customFormat="1" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="101" t="s">
         <v>40</v>
       </c>
@@ -23947,7 +24182,7 @@
       <c r="O20" s="68"/>
       <c r="P20" s="70"/>
     </row>
-    <row r="21" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="33" t="s">
         <v>43</v>
       </c>
@@ -23995,8 +24230,11 @@
       <c r="R21" s="26" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="22" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S21" s="148" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="33" t="s">
         <v>44</v>
       </c>
@@ -24042,8 +24280,11 @@
       <c r="R22" s="26" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="23" spans="1:18" s="69" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S22" s="148" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="23" spans="1:19" s="69" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="101" t="s">
         <v>40</v>
       </c>
@@ -24062,7 +24303,7 @@
       <c r="O23" s="68"/>
       <c r="P23" s="70"/>
     </row>
-    <row r="24" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="33" t="s">
         <v>45</v>
       </c>
@@ -24112,8 +24353,11 @@
       <c r="R24" s="26" t="s">
         <v>570</v>
       </c>
-    </row>
-    <row r="25" spans="1:18" s="69" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S24" s="148" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="25" spans="1:19" s="69" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="101" t="s">
         <v>40</v>
       </c>
@@ -24132,7 +24376,7 @@
       <c r="O25" s="68"/>
       <c r="P25" s="70"/>
     </row>
-    <row r="26" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="33" t="s">
         <v>46</v>
       </c>
@@ -24176,8 +24420,11 @@
       <c r="R26" s="26" t="s">
         <v>573</v>
       </c>
-    </row>
-    <row r="27" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S26" s="148" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="33" t="s">
         <v>49</v>
       </c>
@@ -24221,8 +24468,11 @@
       <c r="R27" s="26" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="28" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S27" s="148" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="33" t="s">
         <v>50</v>
       </c>
@@ -24266,8 +24516,11 @@
       <c r="R28" s="26" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="29" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S28" s="148" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="29" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="33" t="s">
         <v>51</v>
       </c>
@@ -24311,8 +24564,11 @@
       <c r="R29" s="26" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="30" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S29" s="148" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="30" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="33" t="s">
         <v>52</v>
       </c>
@@ -24356,8 +24612,11 @@
       <c r="R30" s="26" t="s">
         <v>572</v>
       </c>
-    </row>
-    <row r="31" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S30" s="148" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="33" t="s">
         <v>53</v>
       </c>
@@ -24401,8 +24660,11 @@
       <c r="R31" s="26" t="s">
         <v>574</v>
       </c>
-    </row>
-    <row r="32" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S31" s="148" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="33" t="s">
         <v>54</v>
       </c>
@@ -24446,8 +24708,11 @@
       <c r="R32" s="26" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="33" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S32" s="148" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="33" t="s">
         <v>55</v>
       </c>
@@ -24491,8 +24756,11 @@
       <c r="R33" s="26" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="34" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S33" s="148" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="33" t="s">
         <v>56</v>
       </c>
@@ -24536,8 +24804,11 @@
       <c r="R34" s="26" t="s">
         <v>575</v>
       </c>
-    </row>
-    <row r="35" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S34" s="148" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="33" t="s">
         <v>57</v>
       </c>
@@ -24581,8 +24852,11 @@
       <c r="R35" s="26" t="s">
         <v>576</v>
       </c>
-    </row>
-    <row r="36" spans="1:18" s="69" customFormat="1" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S35" s="148" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="36" spans="1:19" s="69" customFormat="1" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="101" t="s">
         <v>40</v>
       </c>
@@ -24601,7 +24875,7 @@
       <c r="O36" s="68"/>
       <c r="P36" s="70"/>
     </row>
-    <row r="37" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="33" t="s">
         <v>59</v>
       </c>
@@ -24645,8 +24919,11 @@
       <c r="R37" s="26" t="s">
         <v>571</v>
       </c>
-    </row>
-    <row r="38" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="S37" s="148" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="33" t="s">
         <v>61</v>
       </c>
@@ -24689,17 +24966,20 @@
       <c r="R38" s="26" t="s">
         <v>577</v>
       </c>
-    </row>
-    <row r="39" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="40" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="41" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="42" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="43" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="44" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="45" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="46" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="47" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="48" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+      <c r="S38" s="148" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="40" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="41" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="42" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="43" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="44" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="45" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="46" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="47" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="48" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="49" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="50" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="51" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -25027,7 +25307,7 @@
     </row>
     <row r="5" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="103" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B5" s="23">
         <f>B3+0.72+0.5</f>
@@ -25122,7 +25402,7 @@
     </row>
     <row r="7" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="103" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B7" s="23">
         <f>B6+0.72+0.5</f>
@@ -25200,7 +25480,7 @@
         <v>25</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>25</v>
+        <v>58</v>
       </c>
       <c r="L8" s="6" t="s">
         <v>58</v>
@@ -25264,7 +25544,7 @@
     </row>
     <row r="10" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="104" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B10" s="25">
         <f>0.82+0.72</f>
@@ -25312,7 +25592,7 @@
     </row>
     <row r="11" spans="1:15" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="102" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B11" s="23">
         <v>0.95</v>
@@ -25926,7 +26206,7 @@
         <v>552</v>
       </c>
       <c r="H1" t="s">
-        <v>66</v>
+        <v>639</v>
       </c>
     </row>
     <row r="2" spans="2:8" x14ac:dyDescent="0.35">
@@ -26068,10 +26348,10 @@
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B8" s="147" t="s">
+      <c r="B8" s="146" t="s">
         <v>625</v>
       </c>
-      <c r="C8" s="147" t="s">
+      <c r="C8" s="146" t="s">
         <v>625</v>
       </c>
     </row>
@@ -26105,7 +26385,7 @@
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>627</v>
+        <v>638</v>
       </c>
       <c r="H11" t="s">
         <v>15</v>
@@ -26180,7 +26460,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B0CC1CC-64D0-4115-AE5E-AF959282EFAA}">
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="15.54296875" customWidth="1"/>
@@ -26190,11 +26470,12 @@
     <col min="6" max="6" width="12.1796875" style="6" customWidth="1"/>
     <col min="7" max="7" width="13.7265625" style="6" customWidth="1"/>
     <col min="8" max="8" width="12.81640625" style="6" customWidth="1"/>
-    <col min="9" max="9" width="13.26953125" style="6" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="29.7265625" style="6" customWidth="1"/>
+    <col min="9" max="9" width="28.36328125" style="6" customWidth="1"/>
+    <col min="10" max="10" width="42.81640625" style="6" customWidth="1"/>
+    <col min="11" max="11" width="26.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>188</v>
       </c>
@@ -26222,11 +26503,17 @@
       <c r="I1" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" t="s">
+        <v>631</v>
+      </c>
+      <c r="K1" s="6" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="K2" s="6"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>193</v>
       </c>
@@ -26253,10 +26540,14 @@
         <v>0</v>
       </c>
       <c r="I3" s="6" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+        <v>568</v>
+      </c>
+      <c r="J3" t="s">
+        <v>637</v>
+      </c>
+      <c r="K3" s="6"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>195</v>
       </c>
@@ -26283,10 +26574,14 @@
         <v>0</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+        <v>568</v>
+      </c>
+      <c r="J4" t="s">
+        <v>637</v>
+      </c>
+      <c r="K4" s="6"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>196</v>
       </c>
@@ -26313,10 +26608,14 @@
         <v>0</v>
       </c>
       <c r="I5" s="6" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+        <v>568</v>
+      </c>
+      <c r="J5" t="s">
+        <v>637</v>
+      </c>
+      <c r="K5" s="6"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>198</v>
       </c>
@@ -26343,10 +26642,14 @@
         <v>0</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+        <v>568</v>
+      </c>
+      <c r="J6" t="s">
+        <v>637</v>
+      </c>
+      <c r="K6" s="6"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>199</v>
       </c>
@@ -26373,13 +26676,16 @@
         <v>4</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>165</v>
-      </c>
-      <c r="J7" s="6" t="s">
+        <v>569</v>
+      </c>
+      <c r="J7" t="s">
+        <v>637</v>
+      </c>
+      <c r="K7" s="6" t="s">
         <v>495</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>497</v>
       </c>
@@ -26406,13 +26712,16 @@
         <v>4</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>149</v>
-      </c>
-      <c r="J8" s="6" t="s">
+        <v>570</v>
+      </c>
+      <c r="J8" t="s">
+        <v>632</v>
+      </c>
+      <c r="K8" s="6" t="s">
         <v>496</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>200</v>
       </c>
@@ -26432,8 +26741,14 @@
       <c r="F10" s="6" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I10" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="J10" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>201</v>
       </c>
@@ -26453,8 +26768,14 @@
       <c r="F11" s="6" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I11" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="J11" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>202</v>
       </c>
@@ -26474,8 +26795,14 @@
       <c r="F12" s="6" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I12" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="J12" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>203</v>
       </c>
@@ -26495,8 +26822,14 @@
       <c r="F13" s="6" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="I13" s="6" t="s">
+        <v>572</v>
+      </c>
+      <c r="J13" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>204</v>
       </c>
@@ -26516,8 +26849,11 @@
       <c r="F14" s="6" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J14" t="s">
+        <v>636</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>205</v>
       </c>
@@ -26537,8 +26873,11 @@
       <c r="F15" s="6" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="J15" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>206</v>
       </c>
@@ -26557,6 +26896,9 @@
       </c>
       <c r="F16" s="6" t="s">
         <v>47</v>
+      </c>
+      <c r="J16" t="s">
+        <v>636</v>
       </c>
     </row>
   </sheetData>

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="3541" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F2374123-818A-4C31-96B0-B20E2C7AA7A7}"/>
   <bookViews>
-    <workbookView xWindow="1150" yWindow="2470" windowWidth="34980" windowHeight="18240" tabRatio="905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13840" yWindow="2390" windowWidth="22580" windowHeight="18240" tabRatio="905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="4" r:id="rId1"/>
@@ -3049,7 +3049,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="148">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3457,9 +3457,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -23309,7 +23306,7 @@
       <c r="R2" s="142" t="s">
         <v>568</v>
       </c>
-      <c r="S2" s="148" t="s">
+      <c r="S2" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -23361,7 +23358,7 @@
       <c r="R3" s="142" t="s">
         <v>568</v>
       </c>
-      <c r="S3" s="148" t="s">
+      <c r="S3" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -23413,7 +23410,7 @@
       <c r="R4" s="142" t="s">
         <v>568</v>
       </c>
-      <c r="S4" s="148" t="s">
+      <c r="S4" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -23465,7 +23462,7 @@
       <c r="R5" s="142" t="s">
         <v>568</v>
       </c>
-      <c r="S5" s="148" t="s">
+      <c r="S5" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -23517,7 +23514,7 @@
       <c r="R6" s="142" t="s">
         <v>568</v>
       </c>
-      <c r="S6" s="148" t="s">
+      <c r="S6" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -23569,7 +23566,7 @@
       <c r="R7" s="142" t="s">
         <v>568</v>
       </c>
-      <c r="S7" s="148" t="s">
+      <c r="S7" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -23621,7 +23618,7 @@
       <c r="R8" s="142" t="s">
         <v>568</v>
       </c>
-      <c r="S8" s="148" t="s">
+      <c r="S8" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -23673,7 +23670,7 @@
       <c r="R9" s="142" t="s">
         <v>568</v>
       </c>
-      <c r="S9" s="148" t="s">
+      <c r="S9" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -23725,7 +23722,7 @@
       <c r="R10" s="142" t="s">
         <v>568</v>
       </c>
-      <c r="S10" s="148" t="s">
+      <c r="S10" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -23777,7 +23774,7 @@
       <c r="R11" s="142" t="s">
         <v>568</v>
       </c>
-      <c r="S11" s="148" t="s">
+      <c r="S11" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -23829,7 +23826,7 @@
       <c r="R12" s="142" t="s">
         <v>568</v>
       </c>
-      <c r="S12" s="148" t="s">
+      <c r="S12" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -23881,7 +23878,7 @@
       <c r="R13" s="142" t="s">
         <v>568</v>
       </c>
-      <c r="S13" s="148" t="s">
+      <c r="S13" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -23933,7 +23930,7 @@
       <c r="R14" s="142" t="s">
         <v>568</v>
       </c>
-      <c r="S14" s="148" t="s">
+      <c r="S14" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -23985,7 +23982,7 @@
       <c r="R15" s="142" t="s">
         <v>568</v>
       </c>
-      <c r="S15" s="148" t="s">
+      <c r="S15" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -24037,7 +24034,7 @@
       <c r="R16" s="142" t="s">
         <v>568</v>
       </c>
-      <c r="S16" s="148" t="s">
+      <c r="S16" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -24089,7 +24086,7 @@
       <c r="R17" s="142" t="s">
         <v>568</v>
       </c>
-      <c r="S17" s="148" t="s">
+      <c r="S17" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -24159,7 +24156,7 @@
       <c r="R19" s="26" t="s">
         <v>571</v>
       </c>
-      <c r="S19" s="148" t="s">
+      <c r="S19" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -24230,7 +24227,7 @@
       <c r="R21" s="26" t="s">
         <v>569</v>
       </c>
-      <c r="S21" s="148" t="s">
+      <c r="S21" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -24280,7 +24277,7 @@
       <c r="R22" s="26" t="s">
         <v>569</v>
       </c>
-      <c r="S22" s="148" t="s">
+      <c r="S22" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -24353,7 +24350,7 @@
       <c r="R24" s="26" t="s">
         <v>570</v>
       </c>
-      <c r="S24" s="148" t="s">
+      <c r="S24" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -24420,7 +24417,7 @@
       <c r="R26" s="26" t="s">
         <v>573</v>
       </c>
-      <c r="S26" s="148" t="s">
+      <c r="S26" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -24468,7 +24465,7 @@
       <c r="R27" s="26" t="s">
         <v>572</v>
       </c>
-      <c r="S27" s="148" t="s">
+      <c r="S27" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -24516,7 +24513,7 @@
       <c r="R28" s="26" t="s">
         <v>572</v>
       </c>
-      <c r="S28" s="148" t="s">
+      <c r="S28" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -24564,7 +24561,7 @@
       <c r="R29" s="26" t="s">
         <v>572</v>
       </c>
-      <c r="S29" s="148" t="s">
+      <c r="S29" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -24612,7 +24609,7 @@
       <c r="R30" s="26" t="s">
         <v>572</v>
       </c>
-      <c r="S30" s="148" t="s">
+      <c r="S30" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -24660,7 +24657,7 @@
       <c r="R31" s="26" t="s">
         <v>574</v>
       </c>
-      <c r="S31" s="148" t="s">
+      <c r="S31" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -24708,7 +24705,7 @@
       <c r="R32" s="26" t="s">
         <v>575</v>
       </c>
-      <c r="S32" s="148" t="s">
+      <c r="S32" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -24756,7 +24753,7 @@
       <c r="R33" s="26" t="s">
         <v>575</v>
       </c>
-      <c r="S33" s="148" t="s">
+      <c r="S33" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -24804,7 +24801,7 @@
       <c r="R34" s="26" t="s">
         <v>575</v>
       </c>
-      <c r="S34" s="148" t="s">
+      <c r="S34" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -24852,7 +24849,7 @@
       <c r="R35" s="26" t="s">
         <v>576</v>
       </c>
-      <c r="S35" s="148" t="s">
+      <c r="S35" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -24919,7 +24916,7 @@
       <c r="R37" s="26" t="s">
         <v>571</v>
       </c>
-      <c r="S37" s="148" t="s">
+      <c r="S37" s="6" t="s">
         <v>20</v>
       </c>
     </row>
@@ -24966,7 +24963,7 @@
       <c r="R38" s="26" t="s">
         <v>577</v>
       </c>
-      <c r="S38" s="148" t="s">
+      <c r="S38" s="6" t="s">
         <v>20</v>
       </c>
     </row>

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3606" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5192AD95-B561-4AD1-8D4C-AD785C41E906}"/>
+  <xr:revisionPtr revIDLastSave="3613" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{811BE8AA-9709-4733-B00F-8CF9FECE79D2}"/>
   <bookViews>
     <workbookView xWindow="3210" yWindow="1320" windowWidth="33520" windowHeight="18240" tabRatio="905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3492,11 +3492,11 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -20400,19 +20400,19 @@
       <c r="X55" s="87"/>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="H60" s="146" t="s">
+      <c r="H60" s="147" t="s">
         <v>547</v>
       </c>
-      <c r="I60" s="146"/>
-      <c r="J60" s="146"/>
-      <c r="K60" s="146"/>
-      <c r="L60" s="146"/>
-      <c r="M60" s="146"/>
-      <c r="N60" s="146"/>
-      <c r="O60" s="146"/>
-      <c r="P60" s="146"/>
-      <c r="Q60" s="146"/>
-      <c r="R60" s="146"/>
+      <c r="I60" s="147"/>
+      <c r="J60" s="147"/>
+      <c r="K60" s="147"/>
+      <c r="L60" s="147"/>
+      <c r="M60" s="147"/>
+      <c r="N60" s="147"/>
+      <c r="O60" s="147"/>
+      <c r="P60" s="147"/>
+      <c r="Q60" s="147"/>
+      <c r="R60" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -22348,14 +22348,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="146" t="s">
+      <c r="A2" s="147" t="s">
         <v>538</v>
       </c>
-      <c r="B2" s="146"/>
-      <c r="C2" s="146"/>
-      <c r="D2" s="146"/>
-      <c r="E2" s="146"/>
-      <c r="F2" s="146"/>
+      <c r="B2" s="147"/>
+      <c r="C2" s="147"/>
+      <c r="D2" s="147"/>
+      <c r="E2" s="147"/>
+      <c r="F2" s="147"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -23483,7 +23483,7 @@
       </c>
       <c r="C5" s="21"/>
       <c r="D5" s="21">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E5" s="21">
         <v>80</v>
@@ -23535,7 +23535,7 @@
       </c>
       <c r="C6" s="4"/>
       <c r="D6" s="5">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E6" s="5">
         <v>80</v>
@@ -23587,7 +23587,7 @@
       </c>
       <c r="C7" s="22"/>
       <c r="D7" s="21">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E7" s="21">
         <v>80</v>
@@ -23639,7 +23639,7 @@
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E8" s="5">
         <v>80</v>
@@ -23691,7 +23691,7 @@
       </c>
       <c r="C9" s="21"/>
       <c r="D9" s="21">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E9" s="21">
         <v>80</v>
@@ -23743,7 +23743,7 @@
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E10" s="5">
         <v>80</v>
@@ -23795,7 +23795,7 @@
       </c>
       <c r="C11" s="21"/>
       <c r="D11" s="21">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E11" s="21">
         <v>80</v>
@@ -23847,7 +23847,7 @@
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E12" s="5">
         <v>80</v>
@@ -23899,7 +23899,7 @@
       </c>
       <c r="C13" s="21"/>
       <c r="D13" s="21">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E13" s="21">
         <v>80</v>
@@ -23951,7 +23951,7 @@
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E14" s="5">
         <v>80</v>
@@ -24003,7 +24003,7 @@
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E15" s="21">
         <v>80</v>
@@ -24055,7 +24055,7 @@
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E16" s="5">
         <v>80</v>
@@ -24107,7 +24107,7 @@
       </c>
       <c r="C17" s="21"/>
       <c r="D17" s="21">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E17" s="21">
         <v>80</v>
@@ -24248,10 +24248,10 @@
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E21" s="5">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F21" s="5">
         <v>25</v>
@@ -24300,10 +24300,10 @@
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="E22" s="5">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F22" s="5">
         <v>25</v>
@@ -26224,16 +26224,16 @@
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B45" s="146"/>
-      <c r="C45" s="146"/>
-      <c r="D45" s="146"/>
-      <c r="E45" s="146"/>
-      <c r="F45" s="146"/>
-      <c r="G45" s="146"/>
-      <c r="H45" s="146"/>
-      <c r="I45" s="146"/>
-      <c r="J45" s="146"/>
-      <c r="K45" s="146"/>
+      <c r="B45" s="147"/>
+      <c r="C45" s="147"/>
+      <c r="D45" s="147"/>
+      <c r="E45" s="147"/>
+      <c r="F45" s="147"/>
+      <c r="G45" s="147"/>
+      <c r="H45" s="147"/>
+      <c r="I45" s="147"/>
+      <c r="J45" s="147"/>
+      <c r="K45" s="147"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -27420,7 +27420,7 @@
       <c r="B11" s="108" t="s">
         <v>224</v>
       </c>
-      <c r="C11" s="147" t="s">
+      <c r="C11" s="146" t="s">
         <v>237</v>
       </c>
       <c r="D11" s="109">

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3613" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{811BE8AA-9709-4733-B00F-8CF9FECE79D2}"/>
+  <xr:revisionPtr revIDLastSave="3622" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F63276B8-B3E9-4C04-98C6-4B81F66D1DD0}"/>
   <bookViews>
     <workbookView xWindow="3210" yWindow="1320" windowWidth="33520" windowHeight="18240" tabRatio="905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23639,7 +23639,7 @@
       </c>
       <c r="C8" s="5"/>
       <c r="D8" s="5">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E8" s="5">
         <v>80</v>
@@ -23691,7 +23691,7 @@
       </c>
       <c r="C9" s="21"/>
       <c r="D9" s="21">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E9" s="21">
         <v>80</v>
@@ -23743,7 +23743,7 @@
       </c>
       <c r="C10" s="5"/>
       <c r="D10" s="5">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E10" s="5">
         <v>80</v>
@@ -23795,7 +23795,7 @@
       </c>
       <c r="C11" s="21"/>
       <c r="D11" s="21">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E11" s="21">
         <v>80</v>
@@ -23847,7 +23847,7 @@
       </c>
       <c r="C12" s="5"/>
       <c r="D12" s="5">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E12" s="5">
         <v>80</v>
@@ -23899,7 +23899,7 @@
       </c>
       <c r="C13" s="21"/>
       <c r="D13" s="21">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E13" s="21">
         <v>80</v>
@@ -23951,7 +23951,7 @@
       </c>
       <c r="C14" s="5"/>
       <c r="D14" s="5">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E14" s="5">
         <v>80</v>
@@ -24003,7 +24003,7 @@
       </c>
       <c r="C15" s="21"/>
       <c r="D15" s="21">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E15" s="21">
         <v>80</v>
@@ -24055,7 +24055,7 @@
       </c>
       <c r="C16" s="5"/>
       <c r="D16" s="5">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E16" s="5">
         <v>80</v>
@@ -24107,7 +24107,7 @@
       </c>
       <c r="C17" s="21"/>
       <c r="D17" s="21">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="E17" s="21">
         <v>80</v>
@@ -24248,7 +24248,7 @@
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E21" s="5">
         <v>95</v>
@@ -24300,7 +24300,7 @@
       </c>
       <c r="C22" s="5"/>
       <c r="D22" s="5">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E22" s="5">
         <v>95</v>

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3622" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F63276B8-B3E9-4C04-98C6-4B81F66D1DD0}"/>
+  <xr:revisionPtr revIDLastSave="3645" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E547D04-74D7-43DD-8C26-B45A0FCBD33B}"/>
   <bookViews>
     <workbookView xWindow="3210" yWindow="1320" windowWidth="33520" windowHeight="18240" tabRatio="905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -133,7 +133,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F1" authorId="0" shapeId="0" xr:uid="{CD83C146-519E-4D93-A49C-77C95D0C2637}">
+    <comment ref="G1" authorId="0" shapeId="0" xr:uid="{CD83C146-519E-4D93-A49C-77C95D0C2637}">
       <text>
         <r>
           <rPr>
@@ -157,7 +157,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="S1" authorId="0" shapeId="0" xr:uid="{4290DBF6-4C76-4889-AFBE-FA3A6B2BDE7F}">
+    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{4290DBF6-4C76-4889-AFBE-FA3A6B2BDE7F}">
       <text>
         <r>
           <rPr>
@@ -829,7 +829,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2495" uniqueCount="654">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2496" uniqueCount="655">
   <si>
     <t>This over view explaines the working of this file and how it feeds information to the online calculator.</t>
   </si>
@@ -2791,6 +2791,9 @@
   </si>
   <si>
     <t>102 x 3</t>
+  </si>
+  <si>
+    <t>Attchement strap</t>
   </si>
 </sst>
 </file>
@@ -3088,7 +3091,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="148">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3498,6 +3501,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="20% - Accent1 2" xfId="1" xr:uid="{4B6C72F7-C4CA-450E-9C13-94CEF72F8B8D}"/>
@@ -3527,13 +3536,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>69953</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>542361</xdr:colOff>
       <xdr:row>1</xdr:row>
       <xdr:rowOff>469900</xdr:rowOff>
@@ -3571,13 +3580,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>44450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>567658</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>6350</xdr:rowOff>
@@ -3615,13 +3624,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>82550</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>31750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>554958</xdr:colOff>
       <xdr:row>5</xdr:row>
       <xdr:rowOff>501650</xdr:rowOff>
@@ -3659,13 +3668,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>88900</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>574641</xdr:colOff>
       <xdr:row>21</xdr:row>
       <xdr:rowOff>482600</xdr:rowOff>
@@ -3703,13 +3712,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>146050</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>6351</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>521901</xdr:colOff>
       <xdr:row>20</xdr:row>
       <xdr:rowOff>482601</xdr:rowOff>
@@ -3747,13 +3756,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>141765</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>12701</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>490964</xdr:colOff>
       <xdr:row>23</xdr:row>
       <xdr:rowOff>495301</xdr:rowOff>
@@ -3791,13 +3800,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>55307</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>66571</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>572637</xdr:colOff>
       <xdr:row>13</xdr:row>
       <xdr:rowOff>430161</xdr:rowOff>
@@ -3835,13 +3844,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>45884</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>51004</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>563214</xdr:colOff>
       <xdr:row>14</xdr:row>
       <xdr:rowOff>414594</xdr:rowOff>
@@ -3879,13 +3888,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>44655</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>62066</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>561985</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>425656</xdr:rowOff>
@@ -3923,13 +3932,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>45474</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>54692</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>562804</xdr:colOff>
       <xdr:row>16</xdr:row>
       <xdr:rowOff>418282</xdr:rowOff>
@@ -3967,13 +3976,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>71892</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>29723</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>559339</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>472436</xdr:rowOff>
@@ -4011,13 +4020,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>74054</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>31885</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>561501</xdr:colOff>
       <xdr:row>9</xdr:row>
       <xdr:rowOff>474598</xdr:rowOff>
@@ -4055,13 +4064,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>78918</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>34047</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>566365</xdr:colOff>
       <xdr:row>11</xdr:row>
       <xdr:rowOff>476760</xdr:rowOff>
@@ -4099,13 +4108,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>84720</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>43233</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>512293</xdr:colOff>
       <xdr:row>18</xdr:row>
       <xdr:rowOff>474738</xdr:rowOff>
@@ -4143,13 +4152,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>82551</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>25401</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>533401</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>476251</xdr:rowOff>
@@ -4187,13 +4196,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>120650</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>571500</xdr:colOff>
       <xdr:row>4</xdr:row>
       <xdr:rowOff>488950</xdr:rowOff>
@@ -4231,13 +4240,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>25400</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>546100</xdr:colOff>
       <xdr:row>6</xdr:row>
       <xdr:rowOff>476250</xdr:rowOff>
@@ -4275,13 +4284,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>86448</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>38100</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>558799</xdr:colOff>
       <xdr:row>8</xdr:row>
       <xdr:rowOff>462888</xdr:rowOff>
@@ -4319,13 +4328,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>92798</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>44450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>565149</xdr:colOff>
       <xdr:row>10</xdr:row>
       <xdr:rowOff>469238</xdr:rowOff>
@@ -4363,13 +4372,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>99148</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>571499</xdr:colOff>
       <xdr:row>12</xdr:row>
       <xdr:rowOff>475588</xdr:rowOff>
@@ -4407,13 +4416,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>83039</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>24424</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>510612</xdr:colOff>
       <xdr:row>36</xdr:row>
       <xdr:rowOff>455929</xdr:rowOff>
@@ -4451,13 +4460,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>185987</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>585669</xdr:colOff>
       <xdr:row>34</xdr:row>
       <xdr:rowOff>482600</xdr:rowOff>
@@ -4495,13 +4504,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>107950</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>25924</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>543578</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>463550</xdr:rowOff>
@@ -4539,13 +4548,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>32274</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>530878</xdr:colOff>
       <xdr:row>32</xdr:row>
       <xdr:rowOff>469900</xdr:rowOff>
@@ -4583,13 +4592,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>95250</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>38624</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>530878</xdr:colOff>
       <xdr:row>33</xdr:row>
       <xdr:rowOff>476250</xdr:rowOff>
@@ -4627,13 +4636,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>104865</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>476486</xdr:colOff>
       <xdr:row>30</xdr:row>
       <xdr:rowOff>489229</xdr:rowOff>
@@ -4671,13 +4680,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>30719</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>44450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>542733</xdr:colOff>
       <xdr:row>29</xdr:row>
       <xdr:rowOff>444705</xdr:rowOff>
@@ -4715,13 +4724,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>38100</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>50800</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>550114</xdr:colOff>
       <xdr:row>28</xdr:row>
       <xdr:rowOff>451055</xdr:rowOff>
@@ -4759,13 +4768,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>60714</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>88900</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>546099</xdr:colOff>
       <xdr:row>27</xdr:row>
       <xdr:rowOff>440464</xdr:rowOff>
@@ -4803,13 +4812,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>51802</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>508223</xdr:colOff>
       <xdr:row>26</xdr:row>
       <xdr:rowOff>470102</xdr:rowOff>
@@ -4847,13 +4856,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>133351</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>508001</xdr:colOff>
       <xdr:row>25</xdr:row>
       <xdr:rowOff>476702</xdr:rowOff>
@@ -23244,22 +23253,23 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47E91FF3-79AA-48A9-9F88-C48DFFEF60AE}">
-  <dimension ref="A1:S210"/>
+  <dimension ref="A1:T210"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="35.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.7265625" style="6"/>
     <col min="3" max="3" width="14.1796875" customWidth="1"/>
     <col min="5" max="5" width="10.26953125" customWidth="1"/>
-    <col min="6" max="6" width="11.453125" customWidth="1"/>
-    <col min="8" max="10" width="10" style="6" customWidth="1"/>
-    <col min="11" max="11" width="10.7265625" style="6" customWidth="1"/>
-    <col min="13" max="14" width="8.7265625" style="6"/>
-    <col min="15" max="15" width="10.1796875" style="6" customWidth="1"/>
-    <col min="16" max="16" width="10.7265625" style="58" customWidth="1"/>
+    <col min="6" max="6" width="10.26953125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="11.453125" customWidth="1"/>
+    <col min="9" max="11" width="10" style="6" customWidth="1"/>
+    <col min="12" max="12" width="10.7265625" style="6" customWidth="1"/>
+    <col min="14" max="15" width="8.7265625" style="6"/>
+    <col min="16" max="16" width="10.1796875" style="6" customWidth="1"/>
+    <col min="17" max="17" width="10.7265625" style="58" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="1" customFormat="1" ht="48.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" s="1" customFormat="1" ht="48.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="35" t="s">
         <v>3</v>
       </c>
@@ -23276,49 +23286,52 @@
         <v>7</v>
       </c>
       <c r="F1" s="37" t="s">
+        <v>654</v>
+      </c>
+      <c r="G1" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="38" t="s">
+      <c r="H1" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="42" t="s">
+      <c r="I1" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="50" t="s">
+      <c r="J1" s="50" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="84" t="s">
+      <c r="K1" s="84" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="50" t="s">
+      <c r="L1" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="L1" s="50" t="s">
+      <c r="M1" s="50" t="s">
         <v>14</v>
       </c>
-      <c r="M1" s="6" t="s">
+      <c r="N1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="N1" s="6" t="s">
+      <c r="O1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="O1" s="55" t="s">
+      <c r="P1" s="55" t="s">
         <v>17</v>
       </c>
-      <c r="P1" s="56" t="s">
+      <c r="Q1" s="56" t="s">
         <v>18</v>
       </c>
-      <c r="Q1" s="10" t="s">
+      <c r="R1" s="10" t="s">
         <v>604</v>
       </c>
-      <c r="R1" s="1" t="s">
+      <c r="S1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="S1" s="1" t="s">
+      <c r="T1" s="1" t="s">
         <v>638</v>
       </c>
     </row>
-    <row r="2" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="33" t="s">
         <v>19</v>
       </c>
@@ -23333,44 +23346,47 @@
         <v>80</v>
       </c>
       <c r="F2" s="5">
+        <v>72</v>
+      </c>
+      <c r="G2" s="5">
         <v>17</v>
       </c>
-      <c r="G2" s="34">
+      <c r="H2" s="34">
         <v>10</v>
       </c>
-      <c r="H2" s="5">
+      <c r="I2" s="5">
         <v>4600</v>
       </c>
-      <c r="I2" s="48">
+      <c r="J2" s="48">
         <v>100</v>
       </c>
-      <c r="J2" s="48"/>
-      <c r="K2" s="48">
+      <c r="K2" s="48"/>
+      <c r="L2" s="48">
         <v>0</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="N2" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="O2" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O2" s="6" t="s">
+      <c r="P2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P2" s="57" t="s">
+      <c r="Q2" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="Q2" s="6" t="s">
+      <c r="R2" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="R2" s="141" t="s">
+      <c r="S2" s="141" t="s">
         <v>566</v>
       </c>
-      <c r="S2" s="6" t="s">
+      <c r="T2" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="39" t="s">
         <v>24</v>
       </c>
@@ -23385,44 +23401,47 @@
         <v>80</v>
       </c>
       <c r="F3" s="21">
+        <v>72</v>
+      </c>
+      <c r="G3" s="21">
         <v>17</v>
       </c>
-      <c r="G3" s="40">
+      <c r="H3" s="40">
         <v>15</v>
       </c>
-      <c r="H3" s="21">
+      <c r="I3" s="21">
         <v>6200</v>
       </c>
-      <c r="I3" s="49">
+      <c r="J3" s="49">
         <v>100</v>
       </c>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49">
+      <c r="K3" s="49"/>
+      <c r="L3" s="49">
         <v>0</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="N3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="O3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O3" s="6" t="s">
+      <c r="P3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P3" s="57" t="s">
+      <c r="Q3" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="Q3" s="6" t="s">
+      <c r="R3" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="R3" s="141" t="s">
+      <c r="S3" s="141" t="s">
         <v>566</v>
       </c>
-      <c r="S3" s="6" t="s">
+      <c r="T3" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="4" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="33" t="s">
         <v>26</v>
       </c>
@@ -23437,44 +23456,47 @@
         <v>80</v>
       </c>
       <c r="F4" s="5">
+        <v>72</v>
+      </c>
+      <c r="G4" s="5">
         <v>17</v>
       </c>
-      <c r="G4" s="34">
+      <c r="H4" s="34">
         <v>10</v>
       </c>
-      <c r="H4" s="5">
+      <c r="I4" s="5">
         <v>4600</v>
       </c>
-      <c r="I4" s="48">
+      <c r="J4" s="48">
         <v>100</v>
       </c>
-      <c r="J4" s="48"/>
-      <c r="K4" s="48">
+      <c r="K4" s="48"/>
+      <c r="L4" s="48">
         <v>0</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="N4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="O4" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O4" s="6" t="s">
+      <c r="P4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P4" s="57" t="s">
+      <c r="Q4" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="Q4" s="6" t="s">
+      <c r="R4" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="R4" s="141" t="s">
+      <c r="S4" s="141" t="s">
         <v>566</v>
       </c>
-      <c r="S4" s="6" t="s">
+      <c r="T4" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="39" t="s">
         <v>27</v>
       </c>
@@ -23489,44 +23511,47 @@
         <v>80</v>
       </c>
       <c r="F5" s="21">
+        <v>72</v>
+      </c>
+      <c r="G5" s="21">
         <v>17</v>
       </c>
-      <c r="G5" s="40">
+      <c r="H5" s="40">
         <v>15</v>
       </c>
-      <c r="H5" s="21">
+      <c r="I5" s="21">
         <v>10000</v>
       </c>
-      <c r="I5" s="49">
+      <c r="J5" s="49">
         <v>100</v>
       </c>
-      <c r="J5" s="49"/>
-      <c r="K5" s="49">
+      <c r="K5" s="49"/>
+      <c r="L5" s="49">
         <v>0</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="N5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="N5" s="6" t="s">
+      <c r="O5" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O5" s="6" t="s">
+      <c r="P5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P5" s="57" t="s">
+      <c r="Q5" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="Q5" s="6" t="s">
+      <c r="R5" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="R5" s="141" t="s">
+      <c r="S5" s="141" t="s">
         <v>566</v>
       </c>
-      <c r="S5" s="6" t="s">
+      <c r="T5" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="33" t="s">
         <v>28</v>
       </c>
@@ -23540,45 +23565,48 @@
       <c r="E6" s="5">
         <v>80</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="5">
+        <v>72</v>
+      </c>
+      <c r="G6" s="4">
         <v>17</v>
       </c>
-      <c r="G6" s="34">
+      <c r="H6" s="34">
         <v>10</v>
       </c>
-      <c r="H6" s="5">
+      <c r="I6" s="5">
         <v>4600</v>
       </c>
-      <c r="I6" s="48">
+      <c r="J6" s="48">
         <v>100</v>
       </c>
-      <c r="J6" s="48"/>
-      <c r="K6" s="48">
+      <c r="K6" s="48"/>
+      <c r="L6" s="48">
         <v>0</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="N6" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="O6" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O6" s="6" t="s">
+      <c r="P6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P6" s="57" t="s">
+      <c r="Q6" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="Q6" s="6" t="s">
+      <c r="R6" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="R6" s="141" t="s">
+      <c r="S6" s="141" t="s">
         <v>566</v>
       </c>
-      <c r="S6" s="6" t="s">
+      <c r="T6" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="7" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="39" t="s">
         <v>29</v>
       </c>
@@ -23592,45 +23620,48 @@
       <c r="E7" s="21">
         <v>80</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="21">
+        <v>72</v>
+      </c>
+      <c r="G7" s="22">
         <v>17</v>
       </c>
-      <c r="G7" s="40">
+      <c r="H7" s="40">
         <v>15</v>
       </c>
-      <c r="H7" s="21">
+      <c r="I7" s="21">
         <v>10000</v>
       </c>
-      <c r="I7" s="49">
+      <c r="J7" s="49">
         <v>100</v>
       </c>
-      <c r="J7" s="49"/>
-      <c r="K7" s="49">
+      <c r="K7" s="49"/>
+      <c r="L7" s="49">
         <v>0</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="N7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="N7" s="6" t="s">
+      <c r="O7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O7" s="6" t="s">
+      <c r="P7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P7" s="57" t="s">
+      <c r="Q7" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="Q7" s="6" t="s">
+      <c r="R7" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="R7" s="141" t="s">
+      <c r="S7" s="141" t="s">
         <v>566</v>
       </c>
-      <c r="S7" s="6" t="s">
+      <c r="T7" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="33" t="s">
         <v>30</v>
       </c>
@@ -23645,44 +23676,47 @@
         <v>80</v>
       </c>
       <c r="F8" s="5">
+        <v>72</v>
+      </c>
+      <c r="G8" s="5">
         <v>17</v>
       </c>
-      <c r="G8" s="34">
+      <c r="H8" s="34">
         <v>10</v>
       </c>
-      <c r="H8" s="5">
+      <c r="I8" s="5">
         <v>4000</v>
       </c>
-      <c r="I8" s="48">
+      <c r="J8" s="48">
         <v>100</v>
       </c>
-      <c r="J8" s="48"/>
-      <c r="K8" s="48">
+      <c r="K8" s="48"/>
+      <c r="L8" s="48">
         <v>30</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="N8" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N8" s="6" t="s">
+      <c r="O8" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O8" s="6" t="s">
+      <c r="P8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P8" s="57" t="s">
+      <c r="Q8" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="Q8" s="6" t="s">
+      <c r="R8" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="R8" s="141" t="s">
+      <c r="S8" s="141" t="s">
         <v>566</v>
       </c>
-      <c r="S8" s="6" t="s">
+      <c r="T8" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="39" t="s">
         <v>31</v>
       </c>
@@ -23697,44 +23731,47 @@
         <v>80</v>
       </c>
       <c r="F9" s="21">
+        <v>72</v>
+      </c>
+      <c r="G9" s="21">
         <v>17</v>
       </c>
-      <c r="G9" s="40">
+      <c r="H9" s="40">
         <v>15</v>
       </c>
-      <c r="H9" s="21">
+      <c r="I9" s="21">
         <v>6200</v>
       </c>
-      <c r="I9" s="49">
+      <c r="J9" s="49">
         <v>100</v>
       </c>
-      <c r="J9" s="49"/>
-      <c r="K9" s="49">
+      <c r="K9" s="49"/>
+      <c r="L9" s="49">
         <v>30</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="N9" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="N9" s="6" t="s">
+      <c r="O9" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O9" s="6" t="s">
+      <c r="P9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P9" s="57" t="s">
+      <c r="Q9" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="Q9" s="6" t="s">
+      <c r="R9" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="R9" s="141" t="s">
+      <c r="S9" s="141" t="s">
         <v>566</v>
       </c>
-      <c r="S9" s="6" t="s">
+      <c r="T9" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="10" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="33" t="s">
         <v>32</v>
       </c>
@@ -23749,44 +23786,47 @@
         <v>80</v>
       </c>
       <c r="F10" s="5">
+        <v>72</v>
+      </c>
+      <c r="G10" s="5">
         <v>17</v>
       </c>
-      <c r="G10" s="34">
+      <c r="H10" s="34">
         <v>10</v>
       </c>
-      <c r="H10" s="5">
+      <c r="I10" s="5">
         <v>4000</v>
       </c>
-      <c r="I10" s="48">
+      <c r="J10" s="48">
         <v>100</v>
       </c>
-      <c r="J10" s="48"/>
-      <c r="K10" s="48">
+      <c r="K10" s="48"/>
+      <c r="L10" s="48">
         <v>30</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="N10" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N10" s="6" t="s">
+      <c r="O10" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O10" s="6" t="s">
+      <c r="P10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P10" s="57" t="s">
+      <c r="Q10" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="Q10" s="6" t="s">
+      <c r="R10" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="R10" s="141" t="s">
+      <c r="S10" s="141" t="s">
         <v>566</v>
       </c>
-      <c r="S10" s="6" t="s">
+      <c r="T10" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="11" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="39" t="s">
         <v>33</v>
       </c>
@@ -23801,44 +23841,47 @@
         <v>80</v>
       </c>
       <c r="F11" s="21">
+        <v>72</v>
+      </c>
+      <c r="G11" s="21">
         <v>17</v>
       </c>
-      <c r="G11" s="40">
+      <c r="H11" s="40">
         <v>15</v>
       </c>
-      <c r="H11" s="21">
+      <c r="I11" s="21">
         <v>8200</v>
       </c>
-      <c r="I11" s="49">
+      <c r="J11" s="49">
         <v>100</v>
       </c>
-      <c r="J11" s="49"/>
-      <c r="K11" s="49">
+      <c r="K11" s="49"/>
+      <c r="L11" s="49">
         <v>30</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="N11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="N11" s="6" t="s">
+      <c r="O11" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O11" s="6" t="s">
+      <c r="P11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P11" s="57" t="s">
+      <c r="Q11" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="Q11" s="6" t="s">
+      <c r="R11" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="R11" s="141" t="s">
+      <c r="S11" s="141" t="s">
         <v>566</v>
       </c>
-      <c r="S11" s="6" t="s">
+      <c r="T11" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="33" t="s">
         <v>34</v>
       </c>
@@ -23853,44 +23896,47 @@
         <v>80</v>
       </c>
       <c r="F12" s="5">
+        <v>72</v>
+      </c>
+      <c r="G12" s="5">
         <v>17</v>
       </c>
-      <c r="G12" s="34">
+      <c r="H12" s="34">
         <v>10</v>
       </c>
-      <c r="H12" s="5">
+      <c r="I12" s="5">
         <v>4000</v>
       </c>
-      <c r="I12" s="48">
+      <c r="J12" s="48">
         <v>100</v>
       </c>
-      <c r="J12" s="48"/>
-      <c r="K12" s="48">
+      <c r="K12" s="48"/>
+      <c r="L12" s="48">
         <v>30</v>
       </c>
-      <c r="M12" s="6" t="s">
+      <c r="N12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N12" s="6" t="s">
+      <c r="O12" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O12" s="6" t="s">
+      <c r="P12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P12" s="57" t="s">
+      <c r="Q12" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="Q12" s="6" t="s">
+      <c r="R12" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="R12" s="141" t="s">
+      <c r="S12" s="141" t="s">
         <v>566</v>
       </c>
-      <c r="S12" s="6" t="s">
+      <c r="T12" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="13" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="39" t="s">
         <v>35</v>
       </c>
@@ -23905,44 +23951,47 @@
         <v>80</v>
       </c>
       <c r="F13" s="21">
+        <v>72</v>
+      </c>
+      <c r="G13" s="21">
         <v>17</v>
       </c>
-      <c r="G13" s="40">
+      <c r="H13" s="40">
         <v>15</v>
       </c>
-      <c r="H13" s="21">
+      <c r="I13" s="21">
         <v>9000</v>
       </c>
-      <c r="I13" s="49">
+      <c r="J13" s="49">
         <v>100</v>
       </c>
-      <c r="J13" s="49"/>
-      <c r="K13" s="49">
+      <c r="K13" s="49"/>
+      <c r="L13" s="49">
         <v>30</v>
       </c>
-      <c r="M13" s="6" t="s">
+      <c r="N13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="N13" s="6" t="s">
+      <c r="O13" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O13" s="6" t="s">
+      <c r="P13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P13" s="57" t="s">
+      <c r="Q13" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="Q13" s="6" t="s">
+      <c r="R13" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="R13" s="141" t="s">
+      <c r="S13" s="141" t="s">
         <v>566</v>
       </c>
-      <c r="S13" s="6" t="s">
+      <c r="T13" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="14" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="33" t="s">
         <v>36</v>
       </c>
@@ -23957,44 +24006,47 @@
         <v>80</v>
       </c>
       <c r="F14" s="5">
+        <v>72</v>
+      </c>
+      <c r="G14" s="5">
         <v>17</v>
       </c>
-      <c r="G14" s="34">
+      <c r="H14" s="34">
         <v>10</v>
       </c>
-      <c r="H14" s="5">
+      <c r="I14" s="5">
         <v>4000</v>
       </c>
-      <c r="I14" s="48">
+      <c r="J14" s="48">
         <v>100</v>
       </c>
-      <c r="J14" s="48"/>
-      <c r="K14" s="48">
+      <c r="K14" s="48"/>
+      <c r="L14" s="48">
         <v>25</v>
       </c>
-      <c r="M14" s="6" t="s">
+      <c r="N14" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N14" s="6" t="s">
+      <c r="O14" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O14" s="6" t="s">
+      <c r="P14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P14" s="57" t="s">
+      <c r="Q14" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="Q14" s="6" t="s">
+      <c r="R14" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="R14" s="141" t="s">
+      <c r="S14" s="141" t="s">
         <v>566</v>
       </c>
-      <c r="S14" s="6" t="s">
+      <c r="T14" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="15" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="39" t="s">
         <v>37</v>
       </c>
@@ -24009,44 +24061,47 @@
         <v>80</v>
       </c>
       <c r="F15" s="21">
+        <v>72</v>
+      </c>
+      <c r="G15" s="21">
         <v>17</v>
       </c>
-      <c r="G15" s="40">
+      <c r="H15" s="40">
         <v>15</v>
       </c>
-      <c r="H15" s="21">
+      <c r="I15" s="21">
         <v>6100</v>
       </c>
-      <c r="I15" s="49">
+      <c r="J15" s="49">
         <v>100</v>
       </c>
-      <c r="J15" s="49"/>
-      <c r="K15" s="49">
+      <c r="K15" s="49"/>
+      <c r="L15" s="49">
         <v>25</v>
       </c>
-      <c r="M15" s="6" t="s">
+      <c r="N15" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="N15" s="6" t="s">
+      <c r="O15" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O15" s="6" t="s">
+      <c r="P15" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P15" s="57" t="s">
+      <c r="Q15" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="Q15" s="6" t="s">
+      <c r="R15" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="R15" s="141" t="s">
+      <c r="S15" s="141" t="s">
         <v>566</v>
       </c>
-      <c r="S15" s="6" t="s">
+      <c r="T15" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="16" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="33" t="s">
         <v>38</v>
       </c>
@@ -24061,44 +24116,47 @@
         <v>80</v>
       </c>
       <c r="F16" s="5">
+        <v>72</v>
+      </c>
+      <c r="G16" s="5">
         <v>17</v>
       </c>
-      <c r="G16" s="34">
+      <c r="H16" s="34">
         <v>10</v>
       </c>
-      <c r="H16" s="5">
+      <c r="I16" s="5">
         <v>4000</v>
       </c>
-      <c r="I16" s="48">
+      <c r="J16" s="48">
         <v>100</v>
       </c>
-      <c r="J16" s="48"/>
-      <c r="K16" s="48">
+      <c r="K16" s="48"/>
+      <c r="L16" s="48">
         <v>25</v>
       </c>
-      <c r="M16" s="6" t="s">
+      <c r="N16" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N16" s="6" t="s">
+      <c r="O16" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O16" s="6" t="s">
+      <c r="P16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P16" s="57" t="s">
+      <c r="Q16" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="Q16" s="6" t="s">
+      <c r="R16" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="R16" s="141" t="s">
+      <c r="S16" s="141" t="s">
         <v>566</v>
       </c>
-      <c r="S16" s="6" t="s">
+      <c r="T16" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="39" t="s">
         <v>39</v>
       </c>
@@ -24113,44 +24171,47 @@
         <v>80</v>
       </c>
       <c r="F17" s="21">
+        <v>72</v>
+      </c>
+      <c r="G17" s="21">
         <v>17</v>
       </c>
-      <c r="G17" s="40">
+      <c r="H17" s="40">
         <v>15</v>
       </c>
-      <c r="H17" s="21">
+      <c r="I17" s="21">
         <v>8200</v>
       </c>
-      <c r="I17" s="49">
+      <c r="J17" s="49">
         <v>100</v>
       </c>
-      <c r="J17" s="49"/>
-      <c r="K17" s="49">
+      <c r="K17" s="49"/>
+      <c r="L17" s="49">
         <v>25</v>
       </c>
-      <c r="M17" s="6" t="s">
+      <c r="N17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="N17" s="6" t="s">
+      <c r="O17" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O17" s="6" t="s">
+      <c r="P17" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="P17" s="57" t="s">
+      <c r="Q17" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="Q17" s="6" t="s">
+      <c r="R17" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="R17" s="141" t="s">
+      <c r="S17" s="141" t="s">
         <v>566</v>
       </c>
-      <c r="S17" s="6" t="s">
+      <c r="T17" s="6" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="18" spans="1:19" s="69" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:20" s="69" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="101" t="s">
         <v>40</v>
       </c>
@@ -24159,17 +24220,18 @@
       <c r="D18" s="73"/>
       <c r="E18" s="73"/>
       <c r="F18" s="73"/>
-      <c r="G18" s="72"/>
-      <c r="H18" s="67"/>
-      <c r="I18" s="68"/>
+      <c r="G18" s="73"/>
+      <c r="H18" s="72"/>
+      <c r="I18" s="67"/>
       <c r="J18" s="68"/>
       <c r="K18" s="68"/>
-      <c r="M18" s="68"/>
+      <c r="L18" s="68"/>
       <c r="N18" s="68"/>
       <c r="O18" s="68"/>
-      <c r="P18" s="70"/>
-    </row>
-    <row r="19" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P18" s="68"/>
+      <c r="Q18" s="70"/>
+    </row>
+    <row r="19" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="33" t="s">
         <v>41</v>
       </c>
@@ -24184,43 +24246,46 @@
         <v>82</v>
       </c>
       <c r="F19" s="5">
+        <v>77</v>
+      </c>
+      <c r="G19" s="5">
         <v>17</v>
       </c>
-      <c r="G19" s="34">
+      <c r="H19" s="34">
         <v>10</v>
       </c>
-      <c r="H19" s="41">
+      <c r="I19" s="41">
         <v>6000</v>
       </c>
-      <c r="I19" s="6">
+      <c r="J19" s="6">
         <v>100</v>
       </c>
-      <c r="K19" s="6">
+      <c r="L19" s="6">
         <v>0</v>
       </c>
-      <c r="M19" s="6" t="s">
+      <c r="N19" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N19" s="6" t="s">
+      <c r="O19" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O19" s="6" t="s">
+      <c r="P19" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="P19" s="57" t="s">
+      <c r="Q19" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="Q19" s="6" t="s">
+      <c r="R19" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="R19" s="26" t="s">
+      <c r="S19" s="26" t="s">
         <v>569</v>
       </c>
-      <c r="S19" s="6" t="s">
+      <c r="T19" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:19" s="69" customFormat="1" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:20" s="69" customFormat="1" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="101" t="s">
         <v>40</v>
       </c>
@@ -24228,18 +24293,19 @@
       <c r="C20" s="66"/>
       <c r="D20" s="66"/>
       <c r="E20" s="66"/>
-      <c r="F20" s="66"/>
+      <c r="F20" s="67"/>
       <c r="G20" s="66"/>
-      <c r="H20" s="67"/>
-      <c r="I20" s="68"/>
+      <c r="H20" s="66"/>
+      <c r="I20" s="67"/>
       <c r="J20" s="68"/>
       <c r="K20" s="68"/>
-      <c r="M20" s="68"/>
+      <c r="L20" s="68"/>
       <c r="N20" s="68"/>
       <c r="O20" s="68"/>
-      <c r="P20" s="70"/>
-    </row>
-    <row r="21" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P20" s="68"/>
+      <c r="Q20" s="70"/>
+    </row>
+    <row r="21" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="33" t="s">
         <v>43</v>
       </c>
@@ -24254,44 +24320,47 @@
         <v>95</v>
       </c>
       <c r="F21" s="5">
+        <v>50</v>
+      </c>
+      <c r="G21" s="5">
         <v>25</v>
       </c>
-      <c r="G21" s="34">
+      <c r="H21" s="34">
         <v>10</v>
       </c>
-      <c r="H21" s="5">
+      <c r="I21" s="5">
         <v>10000</v>
       </c>
-      <c r="I21" s="48">
+      <c r="J21" s="48">
         <v>127</v>
       </c>
-      <c r="J21" s="48"/>
-      <c r="K21" s="48">
+      <c r="K21" s="48"/>
+      <c r="L21" s="48">
         <v>0</v>
       </c>
-      <c r="M21" s="6" t="s">
+      <c r="N21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N21" s="6" t="s">
+      <c r="O21" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O21" s="6">
+      <c r="P21" s="6">
         <v>3.2</v>
       </c>
-      <c r="P21" s="57" t="s">
+      <c r="Q21" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="Q21" s="6" t="s">
+      <c r="R21" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="R21" s="26" t="s">
+      <c r="S21" s="26" t="s">
         <v>567</v>
       </c>
-      <c r="S21" s="6" t="s">
+      <c r="T21" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="33" t="s">
         <v>44</v>
       </c>
@@ -24306,42 +24375,45 @@
         <v>95</v>
       </c>
       <c r="F22" s="5">
+        <v>50</v>
+      </c>
+      <c r="G22" s="5">
         <v>25</v>
       </c>
-      <c r="G22" s="34">
+      <c r="H22" s="34">
         <v>10</v>
       </c>
-      <c r="H22" s="5">
+      <c r="I22" s="5">
         <v>9000</v>
       </c>
-      <c r="I22" s="48">
+      <c r="J22" s="48">
         <v>127</v>
       </c>
-      <c r="J22" s="48"/>
       <c r="K22" s="48"/>
-      <c r="M22" s="6" t="s">
+      <c r="L22" s="48"/>
+      <c r="N22" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N22" s="6" t="s">
+      <c r="O22" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O22" s="6" t="s">
+      <c r="P22" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="P22" s="57" t="s">
+      <c r="Q22" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="Q22" s="6" t="s">
+      <c r="R22" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="R22" s="26" t="s">
+      <c r="S22" s="26" t="s">
         <v>567</v>
       </c>
-      <c r="S22" s="6" t="s">
+      <c r="T22" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:19" s="69" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:20" s="69" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="101" t="s">
         <v>40</v>
       </c>
@@ -24350,17 +24422,18 @@
       <c r="D23" s="73"/>
       <c r="E23" s="73"/>
       <c r="F23" s="73"/>
-      <c r="G23" s="72"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="74"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="72"/>
+      <c r="I23" s="73"/>
       <c r="J23" s="74"/>
       <c r="K23" s="74"/>
-      <c r="M23" s="68"/>
+      <c r="L23" s="74"/>
       <c r="N23" s="68"/>
       <c r="O23" s="68"/>
-      <c r="P23" s="70"/>
-    </row>
-    <row r="24" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P23" s="68"/>
+      <c r="Q23" s="70"/>
+    </row>
+    <row r="24" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="33" t="s">
         <v>45</v>
       </c>
@@ -24376,45 +24449,46 @@
       <c r="E24" s="5">
         <v>121</v>
       </c>
-      <c r="F24" s="5">
+      <c r="F24" s="5"/>
+      <c r="G24" s="5">
         <v>25</v>
       </c>
-      <c r="G24" s="34">
+      <c r="H24" s="34">
         <v>10</v>
       </c>
-      <c r="H24" s="5">
+      <c r="I24" s="5">
         <v>9000</v>
       </c>
-      <c r="I24" s="48">
+      <c r="J24" s="48">
         <v>100</v>
       </c>
-      <c r="J24" s="48"/>
-      <c r="K24" s="48">
+      <c r="K24" s="48"/>
+      <c r="L24" s="48">
         <v>0</v>
       </c>
-      <c r="M24" s="6" t="s">
+      <c r="N24" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N24" s="6" t="s">
+      <c r="O24" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="O24" s="6">
+      <c r="P24" s="6">
         <v>4.3</v>
       </c>
-      <c r="P24" s="57" t="s">
+      <c r="Q24" s="57" t="s">
         <v>23</v>
       </c>
-      <c r="Q24" s="6" t="s">
+      <c r="R24" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="R24" s="26" t="s">
+      <c r="S24" s="26" t="s">
         <v>568</v>
       </c>
-      <c r="S24" s="6" t="s">
+      <c r="T24" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:19" s="69" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:20" s="69" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="101" t="s">
         <v>40</v>
       </c>
@@ -24423,17 +24497,18 @@
       <c r="D25" s="71"/>
       <c r="E25" s="71"/>
       <c r="F25" s="71"/>
-      <c r="G25" s="72"/>
-      <c r="H25" s="67"/>
-      <c r="I25" s="68"/>
+      <c r="G25" s="71"/>
+      <c r="H25" s="72"/>
+      <c r="I25" s="67"/>
       <c r="J25" s="68"/>
       <c r="K25" s="68"/>
-      <c r="M25" s="68"/>
+      <c r="L25" s="68"/>
       <c r="N25" s="68"/>
       <c r="O25" s="68"/>
-      <c r="P25" s="70"/>
-    </row>
-    <row r="26" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P25" s="68"/>
+      <c r="Q25" s="70"/>
+    </row>
+    <row r="26" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="33" t="s">
         <v>46</v>
       </c>
@@ -24448,40 +24523,43 @@
         <v>42</v>
       </c>
       <c r="F26" s="60">
+        <v>100</v>
+      </c>
+      <c r="G26" s="60">
         <v>9</v>
       </c>
-      <c r="G26" s="62">
+      <c r="H26" s="62">
         <v>10</v>
       </c>
-      <c r="H26" s="41">
+      <c r="I26" s="41">
         <v>3800</v>
       </c>
-      <c r="I26" s="6">
+      <c r="J26" s="6">
         <v>60</v>
       </c>
-      <c r="M26" s="6" t="s">
+      <c r="N26" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N26" s="6" t="s">
+      <c r="O26" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="O26" s="6" t="s">
+      <c r="P26" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="P26" s="57" t="s">
+      <c r="Q26" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="Q26" s="6" t="s">
+      <c r="R26" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="R26" s="26" t="s">
+      <c r="S26" s="26" t="s">
         <v>571</v>
       </c>
-      <c r="S26" s="6" t="s">
+      <c r="T26" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="33" t="s">
         <v>49</v>
       </c>
@@ -24496,40 +24574,43 @@
         <v>38</v>
       </c>
       <c r="F27" s="60">
+        <v>100</v>
+      </c>
+      <c r="G27" s="60">
         <v>9</v>
       </c>
-      <c r="G27" s="62">
+      <c r="H27" s="62">
         <v>10</v>
       </c>
-      <c r="H27" s="41">
+      <c r="I27" s="41">
         <v>5000</v>
       </c>
-      <c r="I27" s="6">
+      <c r="J27" s="6">
         <v>60</v>
       </c>
-      <c r="M27" s="6" t="s">
+      <c r="N27" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N27" s="6" t="s">
+      <c r="O27" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="O27" s="6" t="s">
+      <c r="P27" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="P27" s="57" t="s">
+      <c r="Q27" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="Q27" s="6" t="s">
+      <c r="R27" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="R27" s="26" t="s">
+      <c r="S27" s="26" t="s">
         <v>570</v>
       </c>
-      <c r="S27" s="6" t="s">
+      <c r="T27" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="33" t="s">
         <v>50</v>
       </c>
@@ -24544,40 +24625,43 @@
         <v>38</v>
       </c>
       <c r="F28" s="60">
+        <v>100</v>
+      </c>
+      <c r="G28" s="60">
         <v>9</v>
       </c>
-      <c r="G28" s="62">
+      <c r="H28" s="62">
         <v>10</v>
       </c>
-      <c r="H28" s="41">
+      <c r="I28" s="41">
         <v>3000</v>
       </c>
-      <c r="I28" s="6">
+      <c r="J28" s="6">
         <v>60</v>
       </c>
-      <c r="M28" s="6" t="s">
+      <c r="N28" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N28" s="6" t="s">
+      <c r="O28" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="O28" s="6" t="s">
+      <c r="P28" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="P28" s="57" t="s">
+      <c r="Q28" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="Q28" s="6" t="s">
+      <c r="R28" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="R28" s="26" t="s">
+      <c r="S28" s="26" t="s">
         <v>570</v>
       </c>
-      <c r="S28" s="6" t="s">
+      <c r="T28" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="33" t="s">
         <v>51</v>
       </c>
@@ -24592,40 +24676,43 @@
         <v>38</v>
       </c>
       <c r="F29" s="60">
+        <v>100</v>
+      </c>
+      <c r="G29" s="60">
         <v>9</v>
       </c>
-      <c r="G29" s="62">
+      <c r="H29" s="62">
         <v>10</v>
       </c>
-      <c r="H29" s="41">
+      <c r="I29" s="41">
         <v>3000</v>
       </c>
-      <c r="I29" s="6">
+      <c r="J29" s="6">
         <v>60</v>
       </c>
-      <c r="M29" s="6" t="s">
+      <c r="N29" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N29" s="6" t="s">
+      <c r="O29" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="O29" s="6" t="s">
+      <c r="P29" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="P29" s="57" t="s">
+      <c r="Q29" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="Q29" s="6" t="s">
+      <c r="R29" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="R29" s="26" t="s">
+      <c r="S29" s="26" t="s">
         <v>570</v>
       </c>
-      <c r="S29" s="6" t="s">
+      <c r="T29" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="33" t="s">
         <v>52</v>
       </c>
@@ -24640,40 +24727,43 @@
         <v>38</v>
       </c>
       <c r="F30" s="60">
+        <v>100</v>
+      </c>
+      <c r="G30" s="60">
         <v>9</v>
       </c>
-      <c r="G30" s="62">
+      <c r="H30" s="62">
         <v>10</v>
       </c>
-      <c r="H30" s="41">
+      <c r="I30" s="41">
         <v>3000</v>
       </c>
-      <c r="I30" s="6">
+      <c r="J30" s="6">
         <v>60</v>
       </c>
-      <c r="M30" s="6" t="s">
+      <c r="N30" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N30" s="6" t="s">
+      <c r="O30" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="O30" s="6" t="s">
+      <c r="P30" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="P30" s="57" t="s">
+      <c r="Q30" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="Q30" s="6" t="s">
+      <c r="R30" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="R30" s="26" t="s">
+      <c r="S30" s="26" t="s">
         <v>570</v>
       </c>
-      <c r="S30" s="6" t="s">
+      <c r="T30" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="33" t="s">
         <v>53</v>
       </c>
@@ -24688,40 +24778,43 @@
         <v>59</v>
       </c>
       <c r="F31" s="60">
+        <v>100</v>
+      </c>
+      <c r="G31" s="60">
         <v>15</v>
       </c>
-      <c r="G31" s="62">
+      <c r="H31" s="62">
         <v>10</v>
       </c>
-      <c r="H31" s="41">
+      <c r="I31" s="41">
         <v>6000</v>
       </c>
-      <c r="I31" s="6">
+      <c r="J31" s="6">
         <v>60</v>
       </c>
-      <c r="M31" s="6" t="s">
+      <c r="N31" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N31" s="6" t="s">
+      <c r="O31" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="O31" s="6" t="s">
+      <c r="P31" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="P31" s="57" t="s">
+      <c r="Q31" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="Q31" s="6" t="s">
+      <c r="R31" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="R31" s="26" t="s">
+      <c r="S31" s="26" t="s">
         <v>572</v>
       </c>
-      <c r="S31" s="6" t="s">
+      <c r="T31" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="33" t="s">
         <v>54</v>
       </c>
@@ -24735,41 +24828,44 @@
       <c r="E32" s="61">
         <v>79</v>
       </c>
-      <c r="F32" s="61">
+      <c r="F32" s="60">
+        <v>100</v>
+      </c>
+      <c r="G32" s="61">
         <v>19</v>
       </c>
-      <c r="G32" s="61">
+      <c r="H32" s="61">
         <v>10</v>
       </c>
-      <c r="H32" s="41">
+      <c r="I32" s="41">
         <v>6000</v>
       </c>
-      <c r="I32" s="6">
+      <c r="J32" s="6">
         <v>60</v>
       </c>
-      <c r="M32" s="6" t="s">
+      <c r="N32" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N32" s="6" t="s">
+      <c r="O32" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="O32" s="6" t="s">
+      <c r="P32" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="P32" s="57" t="s">
+      <c r="Q32" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="Q32" s="6" t="s">
+      <c r="R32" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="R32" s="26" t="s">
+      <c r="S32" s="26" t="s">
         <v>573</v>
       </c>
-      <c r="S32" s="6" t="s">
+      <c r="T32" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="33" t="s">
         <v>55</v>
       </c>
@@ -24783,41 +24879,44 @@
       <c r="E33" s="61">
         <v>79</v>
       </c>
-      <c r="F33" s="61">
+      <c r="F33" s="60">
+        <v>100</v>
+      </c>
+      <c r="G33" s="61">
         <v>19</v>
       </c>
-      <c r="G33" s="61">
+      <c r="H33" s="61">
         <v>10</v>
       </c>
-      <c r="H33" s="41">
+      <c r="I33" s="41">
         <v>6000</v>
       </c>
-      <c r="I33" s="6">
+      <c r="J33" s="6">
         <v>60</v>
       </c>
-      <c r="M33" s="6" t="s">
+      <c r="N33" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N33" s="6" t="s">
+      <c r="O33" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="O33" s="6" t="s">
+      <c r="P33" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="P33" s="57" t="s">
+      <c r="Q33" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="Q33" s="6" t="s">
+      <c r="R33" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="R33" s="26" t="s">
+      <c r="S33" s="26" t="s">
         <v>573</v>
       </c>
-      <c r="S33" s="6" t="s">
+      <c r="T33" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="33" t="s">
         <v>56</v>
       </c>
@@ -24831,41 +24930,44 @@
       <c r="E34" s="61">
         <v>79</v>
       </c>
-      <c r="F34" s="61">
+      <c r="F34" s="60">
+        <v>100</v>
+      </c>
+      <c r="G34" s="61">
         <v>19</v>
       </c>
-      <c r="G34" s="61">
+      <c r="H34" s="61">
         <v>10</v>
       </c>
-      <c r="H34" s="41">
+      <c r="I34" s="41">
         <v>6000</v>
       </c>
-      <c r="I34" s="6">
+      <c r="J34" s="6">
         <v>60</v>
       </c>
-      <c r="M34" s="6" t="s">
+      <c r="N34" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N34" s="6" t="s">
+      <c r="O34" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="O34" s="6" t="s">
+      <c r="P34" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="P34" s="57" t="s">
+      <c r="Q34" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="Q34" s="6" t="s">
+      <c r="R34" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="R34" s="26" t="s">
+      <c r="S34" s="26" t="s">
         <v>573</v>
       </c>
-      <c r="S34" s="6" t="s">
+      <c r="T34" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="33" t="s">
         <v>57</v>
       </c>
@@ -24879,41 +24981,44 @@
       <c r="E35" s="61">
         <v>90</v>
       </c>
-      <c r="F35" s="61">
+      <c r="F35" s="60">
+        <v>100</v>
+      </c>
+      <c r="G35" s="61">
         <v>27</v>
       </c>
-      <c r="G35" s="61">
+      <c r="H35" s="61">
         <v>10</v>
       </c>
-      <c r="H35" s="41">
+      <c r="I35" s="41">
         <v>5000</v>
       </c>
-      <c r="I35" s="6">
+      <c r="J35" s="6">
         <v>60</v>
       </c>
-      <c r="M35" s="6" t="s">
+      <c r="N35" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N35" s="6" t="s">
+      <c r="O35" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="O35" s="6" t="s">
+      <c r="P35" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="P35" s="57" t="s">
+      <c r="Q35" s="57" t="s">
         <v>48</v>
       </c>
-      <c r="Q35" s="6" t="s">
+      <c r="R35" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="R35" s="26" t="s">
+      <c r="S35" s="26" t="s">
         <v>574</v>
       </c>
-      <c r="S35" s="6" t="s">
+      <c r="T35" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:19" s="69" customFormat="1" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:20" s="69" customFormat="1" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="101" t="s">
         <v>40</v>
       </c>
@@ -24921,18 +25026,19 @@
       <c r="C36" s="66"/>
       <c r="D36" s="66"/>
       <c r="E36" s="66"/>
-      <c r="F36" s="66"/>
+      <c r="F36" s="67"/>
       <c r="G36" s="66"/>
-      <c r="H36" s="67"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="68"/>
+      <c r="H36" s="66"/>
+      <c r="I36" s="67"/>
+      <c r="J36" s="6"/>
       <c r="K36" s="68"/>
-      <c r="M36" s="68"/>
+      <c r="L36" s="68"/>
       <c r="N36" s="68"/>
       <c r="O36" s="68"/>
-      <c r="P36" s="70"/>
-    </row>
-    <row r="37" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="P36" s="68"/>
+      <c r="Q36" s="70"/>
+    </row>
+    <row r="37" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="33" t="s">
         <v>59</v>
       </c>
@@ -24946,41 +25052,44 @@
       <c r="E37" s="61">
         <v>79</v>
       </c>
-      <c r="F37" s="61">
+      <c r="F37" s="148">
+        <v>200</v>
+      </c>
+      <c r="G37" s="61">
         <v>21</v>
       </c>
-      <c r="G37" s="61">
+      <c r="H37" s="61">
         <v>10</v>
       </c>
-      <c r="H37" s="41">
+      <c r="I37" s="41">
         <v>5400</v>
       </c>
-      <c r="I37" s="6">
+      <c r="J37" s="6">
         <v>60</v>
       </c>
-      <c r="M37" s="6" t="s">
+      <c r="N37" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N37" s="6" t="s">
+      <c r="O37" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="O37" s="6" t="s">
+      <c r="P37" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="P37" s="57" t="s">
+      <c r="Q37" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="Q37" s="6" t="s">
+      <c r="R37" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="R37" s="26" t="s">
+      <c r="S37" s="26" t="s">
         <v>569</v>
       </c>
-      <c r="S37" s="6" t="s">
+      <c r="T37" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="33" t="s">
         <v>61</v>
       </c>
@@ -24993,50 +25102,53 @@
       <c r="E38" s="100">
         <v>57</v>
       </c>
-      <c r="F38" s="100">
+      <c r="F38" s="149">
+        <v>150</v>
+      </c>
+      <c r="G38" s="100">
         <v>14</v>
       </c>
-      <c r="G38" s="100">
+      <c r="H38" s="100">
         <v>10</v>
       </c>
-      <c r="H38" s="6">
+      <c r="I38" s="6">
         <v>3000</v>
       </c>
-      <c r="I38" s="6">
+      <c r="J38" s="6">
         <v>60</v>
       </c>
-      <c r="M38" s="6" t="s">
+      <c r="N38" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="N38" s="6" t="s">
+      <c r="O38" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="O38" s="6" t="s">
+      <c r="P38" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="P38" s="57" t="s">
+      <c r="Q38" s="57" t="s">
         <v>60</v>
       </c>
-      <c r="Q38" s="6" t="s">
+      <c r="R38" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="R38" s="26" t="s">
+      <c r="S38" s="26" t="s">
         <v>575</v>
       </c>
-      <c r="S38" s="6" t="s">
+      <c r="T38" s="6" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="40" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="41" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="42" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="43" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="44" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="45" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="46" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="47" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="48" spans="1:19" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="39" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="40" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="41" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="42" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="43" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="44" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="45" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="46" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="47" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="48" spans="1:20" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="49" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="50" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="51" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3645" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E547D04-74D7-43DD-8C26-B45A0FCBD33B}"/>
+  <xr:revisionPtr revIDLastSave="3647" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B67B0AD4-B4E7-4F48-823C-2CFC38DB9B90}"/>
   <bookViews>
-    <workbookView xWindow="3210" yWindow="1320" windowWidth="33520" windowHeight="18240" tabRatio="905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9240" yWindow="1150" windowWidth="28030" windowHeight="18390" tabRatio="905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="4" r:id="rId1"/>
@@ -3498,13 +3498,13 @@
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -20409,19 +20409,19 @@
       <c r="X55" s="87"/>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="H60" s="147" t="s">
+      <c r="H60" s="149" t="s">
         <v>547</v>
       </c>
-      <c r="I60" s="147"/>
-      <c r="J60" s="147"/>
-      <c r="K60" s="147"/>
-      <c r="L60" s="147"/>
-      <c r="M60" s="147"/>
-      <c r="N60" s="147"/>
-      <c r="O60" s="147"/>
-      <c r="P60" s="147"/>
-      <c r="Q60" s="147"/>
-      <c r="R60" s="147"/>
+      <c r="I60" s="149"/>
+      <c r="J60" s="149"/>
+      <c r="K60" s="149"/>
+      <c r="L60" s="149"/>
+      <c r="M60" s="149"/>
+      <c r="N60" s="149"/>
+      <c r="O60" s="149"/>
+      <c r="P60" s="149"/>
+      <c r="Q60" s="149"/>
+      <c r="R60" s="149"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -22357,14 +22357,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="147" t="s">
+      <c r="A2" s="149" t="s">
         <v>538</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
+      <c r="B2" s="149"/>
+      <c r="C2" s="149"/>
+      <c r="D2" s="149"/>
+      <c r="E2" s="149"/>
+      <c r="F2" s="149"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -24320,7 +24320,7 @@
         <v>95</v>
       </c>
       <c r="F21" s="5">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="G21" s="5">
         <v>25</v>
@@ -24375,7 +24375,7 @@
         <v>95</v>
       </c>
       <c r="F22" s="5">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="G22" s="5">
         <v>25</v>
@@ -25052,7 +25052,7 @@
       <c r="E37" s="61">
         <v>79</v>
       </c>
-      <c r="F37" s="148">
+      <c r="F37" s="147">
         <v>200</v>
       </c>
       <c r="G37" s="61">
@@ -25102,7 +25102,7 @@
       <c r="E38" s="100">
         <v>57</v>
       </c>
-      <c r="F38" s="149">
+      <c r="F38" s="148">
         <v>150</v>
       </c>
       <c r="G38" s="100">
@@ -26336,16 +26336,16 @@
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B45" s="147"/>
-      <c r="C45" s="147"/>
-      <c r="D45" s="147"/>
-      <c r="E45" s="147"/>
-      <c r="F45" s="147"/>
-      <c r="G45" s="147"/>
-      <c r="H45" s="147"/>
-      <c r="I45" s="147"/>
-      <c r="J45" s="147"/>
-      <c r="K45" s="147"/>
+      <c r="B45" s="149"/>
+      <c r="C45" s="149"/>
+      <c r="D45" s="149"/>
+      <c r="E45" s="149"/>
+      <c r="F45" s="149"/>
+      <c r="G45" s="149"/>
+      <c r="H45" s="149"/>
+      <c r="I45" s="149"/>
+      <c r="J45" s="149"/>
+      <c r="K45" s="149"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3647" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B67B0AD4-B4E7-4F48-823C-2CFC38DB9B90}"/>
+  <xr:revisionPtr revIDLastSave="3649" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{35DEF60B-4FEA-4048-84A3-55D08D3AD2EC}"/>
   <bookViews>
-    <workbookView xWindow="9240" yWindow="1150" windowWidth="28030" windowHeight="18390" tabRatio="905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9580" yWindow="1490" windowWidth="28030" windowHeight="18390" tabRatio="905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="4" r:id="rId1"/>
@@ -24320,7 +24320,7 @@
         <v>95</v>
       </c>
       <c r="F21" s="5">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="G21" s="5">
         <v>25</v>
@@ -24375,7 +24375,7 @@
         <v>95</v>
       </c>
       <c r="F22" s="5">
-        <v>95</v>
+        <v>150</v>
       </c>
       <c r="G22" s="5">
         <v>25</v>

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3669" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8736C662-090F-48E1-BDD5-D81EE4652817}"/>
+  <xr:revisionPtr revIDLastSave="3673" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6B76627-CD00-477D-A97F-48D34F575C1A}"/>
   <bookViews>
-    <workbookView xWindow="8490" yWindow="1940" windowWidth="28030" windowHeight="18390" tabRatio="905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="750" yWindow="2010" windowWidth="28030" windowHeight="18390" tabRatio="905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="4" r:id="rId1"/>
@@ -3487,13 +3487,13 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -20399,19 +20399,19 @@
       <c r="X55" s="87"/>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="H60" s="148" t="s">
+      <c r="H60" s="150" t="s">
         <v>541</v>
       </c>
-      <c r="I60" s="148"/>
-      <c r="J60" s="148"/>
-      <c r="K60" s="148"/>
-      <c r="L60" s="148"/>
-      <c r="M60" s="148"/>
-      <c r="N60" s="148"/>
-      <c r="O60" s="148"/>
-      <c r="P60" s="148"/>
-      <c r="Q60" s="148"/>
-      <c r="R60" s="148"/>
+      <c r="I60" s="150"/>
+      <c r="J60" s="150"/>
+      <c r="K60" s="150"/>
+      <c r="L60" s="150"/>
+      <c r="M60" s="150"/>
+      <c r="N60" s="150"/>
+      <c r="O60" s="150"/>
+      <c r="P60" s="150"/>
+      <c r="Q60" s="150"/>
+      <c r="R60" s="150"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -22347,14 +22347,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="148" t="s">
+      <c r="A2" s="150" t="s">
         <v>532</v>
       </c>
-      <c r="B2" s="148"/>
-      <c r="C2" s="148"/>
-      <c r="D2" s="148"/>
-      <c r="E2" s="148"/>
-      <c r="F2" s="148"/>
+      <c r="B2" s="150"/>
+      <c r="C2" s="150"/>
+      <c r="D2" s="150"/>
+      <c r="E2" s="150"/>
+      <c r="F2" s="150"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -24310,7 +24310,7 @@
         <v>95</v>
       </c>
       <c r="F21" s="5">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="G21" s="5">
         <v>25</v>
@@ -24365,7 +24365,7 @@
         <v>95</v>
       </c>
       <c r="F22" s="5">
-        <v>150</v>
+        <v>400</v>
       </c>
       <c r="G22" s="5">
         <v>25</v>
@@ -25042,7 +25042,7 @@
       <c r="E37" s="61">
         <v>79</v>
       </c>
-      <c r="F37" s="149">
+      <c r="F37" s="148">
         <v>200</v>
       </c>
       <c r="G37" s="61">
@@ -25092,7 +25092,7 @@
       <c r="E38" s="100">
         <v>57</v>
       </c>
-      <c r="F38" s="150">
+      <c r="F38" s="149">
         <v>150</v>
       </c>
       <c r="G38" s="100">
@@ -26309,16 +26309,16 @@
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B45" s="148"/>
-      <c r="C45" s="148"/>
-      <c r="D45" s="148"/>
-      <c r="E45" s="148"/>
-      <c r="F45" s="148"/>
-      <c r="G45" s="148"/>
-      <c r="H45" s="148"/>
-      <c r="I45" s="148"/>
-      <c r="J45" s="148"/>
-      <c r="K45" s="148"/>
+      <c r="B45" s="150"/>
+      <c r="C45" s="150"/>
+      <c r="D45" s="150"/>
+      <c r="E45" s="150"/>
+      <c r="F45" s="150"/>
+      <c r="G45" s="150"/>
+      <c r="H45" s="150"/>
+      <c r="I45" s="150"/>
+      <c r="J45" s="150"/>
+      <c r="K45" s="150"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3673" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C6B76627-CD00-477D-A97F-48D34F575C1A}"/>
+  <xr:revisionPtr revIDLastSave="3674" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CCCC603-5204-4439-82F1-6C0347645B22}"/>
   <bookViews>
-    <workbookView xWindow="750" yWindow="2010" windowWidth="28030" windowHeight="18390" tabRatio="905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1430" yWindow="2690" windowWidth="28030" windowHeight="18390" tabRatio="905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="4" r:id="rId1"/>
@@ -2778,7 +2778,7 @@
     <t>110mm lath</t>
   </si>
   <si>
-    <t>Attchement strap</t>
+    <t>attachment strap</t>
   </si>
 </sst>
 </file>

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3674" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9CCCC603-5204-4439-82F1-6C0347645B22}"/>
+  <xr:revisionPtr revIDLastSave="3676" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AD08707-E2B2-41A3-A5A8-2256722D3219}"/>
   <bookViews>
     <workbookView xWindow="1430" yWindow="2690" windowWidth="28030" windowHeight="18390" tabRatio="905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -24310,7 +24310,7 @@
         <v>95</v>
       </c>
       <c r="F21" s="5">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="G21" s="5">
         <v>25</v>
@@ -24365,7 +24365,7 @@
         <v>95</v>
       </c>
       <c r="F22" s="5">
-        <v>400</v>
+        <v>150</v>
       </c>
       <c r="G22" s="5">
         <v>25</v>

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3676" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0AD08707-E2B2-41A3-A5A8-2256722D3219}"/>
+  <xr:revisionPtr revIDLastSave="3682" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49768E2A-3340-47B0-9135-F8C4C9AA40A5}"/>
   <bookViews>
-    <workbookView xWindow="1430" yWindow="2690" windowWidth="28030" windowHeight="18390" tabRatio="905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1090" yWindow="2350" windowWidth="28030" windowHeight="18390" tabRatio="905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="4" r:id="rId1"/>
@@ -23330,13 +23330,13 @@
       </c>
       <c r="C2" s="5"/>
       <c r="D2" s="5">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E2" s="5">
         <v>80</v>
       </c>
       <c r="F2" s="5">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G2" s="5">
         <v>17</v>
@@ -23385,13 +23385,13 @@
       </c>
       <c r="C3" s="21"/>
       <c r="D3" s="21">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E3" s="21">
         <v>80</v>
       </c>
       <c r="F3" s="21">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G3" s="21">
         <v>17</v>
@@ -23440,13 +23440,13 @@
       </c>
       <c r="C4" s="5"/>
       <c r="D4" s="5">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E4" s="5">
         <v>80</v>
       </c>
       <c r="F4" s="5">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G4" s="5">
         <v>17</v>
@@ -23501,7 +23501,7 @@
         <v>80</v>
       </c>
       <c r="F5" s="21">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G5" s="21">
         <v>17</v>
@@ -23556,7 +23556,7 @@
         <v>80</v>
       </c>
       <c r="F6" s="5">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G6" s="4">
         <v>17</v>
@@ -23611,7 +23611,7 @@
         <v>80</v>
       </c>
       <c r="F7" s="21">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G7" s="22">
         <v>17</v>
@@ -23666,7 +23666,7 @@
         <v>80</v>
       </c>
       <c r="F8" s="5">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G8" s="5">
         <v>17</v>
@@ -23721,7 +23721,7 @@
         <v>80</v>
       </c>
       <c r="F9" s="21">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G9" s="21">
         <v>17</v>
@@ -23776,7 +23776,7 @@
         <v>80</v>
       </c>
       <c r="F10" s="5">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G10" s="5">
         <v>17</v>
@@ -23831,7 +23831,7 @@
         <v>80</v>
       </c>
       <c r="F11" s="21">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G11" s="21">
         <v>17</v>
@@ -23886,7 +23886,7 @@
         <v>80</v>
       </c>
       <c r="F12" s="5">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G12" s="5">
         <v>17</v>
@@ -23941,7 +23941,7 @@
         <v>80</v>
       </c>
       <c r="F13" s="21">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G13" s="21">
         <v>17</v>
@@ -23996,7 +23996,7 @@
         <v>80</v>
       </c>
       <c r="F14" s="5">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G14" s="5">
         <v>17</v>
@@ -24051,7 +24051,7 @@
         <v>80</v>
       </c>
       <c r="F15" s="21">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G15" s="21">
         <v>17</v>
@@ -24106,7 +24106,7 @@
         <v>80</v>
       </c>
       <c r="F16" s="5">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G16" s="5">
         <v>17</v>
@@ -24161,7 +24161,7 @@
         <v>80</v>
       </c>
       <c r="F17" s="21">
-        <v>72</v>
+        <v>0</v>
       </c>
       <c r="G17" s="21">
         <v>17</v>
@@ -24310,7 +24310,7 @@
         <v>95</v>
       </c>
       <c r="F21" s="5">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="G21" s="5">
         <v>25</v>
@@ -24365,7 +24365,7 @@
         <v>95</v>
       </c>
       <c r="F22" s="5">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="G22" s="5">
         <v>25</v>

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3682" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{49768E2A-3340-47B0-9135-F8C4C9AA40A5}"/>
+  <xr:revisionPtr revIDLastSave="3685" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D4A5351A-0C6C-49A2-B73C-3A38C046F7F7}"/>
   <bookViews>
     <workbookView xWindow="1090" yWindow="2350" windowWidth="28030" windowHeight="18390" tabRatio="905" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23336,7 +23336,7 @@
         <v>80</v>
       </c>
       <c r="F2" s="5">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G2" s="5">
         <v>17</v>
@@ -23391,7 +23391,7 @@
         <v>80</v>
       </c>
       <c r="F3" s="21">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G3" s="21">
         <v>17</v>
@@ -23446,7 +23446,7 @@
         <v>80</v>
       </c>
       <c r="F4" s="5">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G4" s="5">
         <v>17</v>
@@ -23501,7 +23501,7 @@
         <v>80</v>
       </c>
       <c r="F5" s="21">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G5" s="21">
         <v>17</v>
@@ -23556,7 +23556,7 @@
         <v>80</v>
       </c>
       <c r="F6" s="5">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G6" s="4">
         <v>17</v>
@@ -23611,7 +23611,7 @@
         <v>80</v>
       </c>
       <c r="F7" s="21">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G7" s="22">
         <v>17</v>
@@ -23666,7 +23666,7 @@
         <v>80</v>
       </c>
       <c r="F8" s="5">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G8" s="5">
         <v>17</v>
@@ -23721,7 +23721,7 @@
         <v>80</v>
       </c>
       <c r="F9" s="21">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G9" s="21">
         <v>17</v>
@@ -23776,7 +23776,7 @@
         <v>80</v>
       </c>
       <c r="F10" s="5">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G10" s="5">
         <v>17</v>
@@ -23831,7 +23831,7 @@
         <v>80</v>
       </c>
       <c r="F11" s="21">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G11" s="21">
         <v>17</v>
@@ -23886,7 +23886,7 @@
         <v>80</v>
       </c>
       <c r="F12" s="5">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G12" s="5">
         <v>17</v>
@@ -23941,7 +23941,7 @@
         <v>80</v>
       </c>
       <c r="F13" s="21">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G13" s="21">
         <v>17</v>
@@ -23996,7 +23996,7 @@
         <v>80</v>
       </c>
       <c r="F14" s="5">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G14" s="5">
         <v>17</v>
@@ -24051,7 +24051,7 @@
         <v>80</v>
       </c>
       <c r="F15" s="21">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G15" s="21">
         <v>17</v>
@@ -24106,7 +24106,7 @@
         <v>80</v>
       </c>
       <c r="F16" s="5">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G16" s="5">
         <v>17</v>
@@ -24161,7 +24161,7 @@
         <v>80</v>
       </c>
       <c r="F17" s="21">
-        <v>0</v>
+        <v>73</v>
       </c>
       <c r="G17" s="21">
         <v>17</v>

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3798" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FC94E49-C17B-413A-B779-EA2790D57A80}"/>
+  <xr:revisionPtr revIDLastSave="3799" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F3F89394-FD15-44FE-99BD-28E8DBDFD7A0}"/>
   <bookViews>
-    <workbookView xWindow="8160" yWindow="300" windowWidth="28030" windowHeight="19260" tabRatio="905" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11130" yWindow="100" windowWidth="26720" windowHeight="19260" tabRatio="905" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Overview" sheetId="4" r:id="rId1"/>
@@ -829,7 +829,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2658" uniqueCount="652">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2659" uniqueCount="653">
   <si>
     <t>This over view explaines the working of this file and how it feeds information to the online calculator.</t>
   </si>
@@ -2785,6 +2785,9 @@
   </si>
   <si>
     <t>AEG + RUBBER SEAL</t>
+  </si>
+  <si>
+    <t>guide image</t>
   </si>
 </sst>
 </file>
@@ -3492,9 +3495,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -3504,6 +3504,9 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -21210,19 +21213,19 @@
       <c r="X55" s="85"/>
     </row>
     <row r="60" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="H60" s="148" t="s">
+      <c r="H60" s="151" t="s">
         <v>541</v>
       </c>
-      <c r="I60" s="148"/>
-      <c r="J60" s="148"/>
-      <c r="K60" s="148"/>
-      <c r="L60" s="148"/>
-      <c r="M60" s="148"/>
-      <c r="N60" s="148"/>
-      <c r="O60" s="148"/>
-      <c r="P60" s="148"/>
-      <c r="Q60" s="148"/>
-      <c r="R60" s="148"/>
+      <c r="I60" s="151"/>
+      <c r="J60" s="151"/>
+      <c r="K60" s="151"/>
+      <c r="L60" s="151"/>
+      <c r="M60" s="151"/>
+      <c r="N60" s="151"/>
+      <c r="O60" s="151"/>
+      <c r="P60" s="151"/>
+      <c r="Q60" s="151"/>
+      <c r="R60" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -23158,14 +23161,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="148" t="s">
+      <c r="A2" s="151" t="s">
         <v>532</v>
       </c>
-      <c r="B2" s="148"/>
-      <c r="C2" s="148"/>
-      <c r="D2" s="148"/>
-      <c r="E2" s="148"/>
-      <c r="F2" s="148"/>
+      <c r="B2" s="151"/>
+      <c r="C2" s="151"/>
+      <c r="D2" s="151"/>
+      <c r="E2" s="151"/>
+      <c r="F2" s="151"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -26483,7 +26486,7 @@
       <c r="A9" s="102" t="s">
         <v>177</v>
       </c>
-      <c r="B9" s="150">
+      <c r="B9" s="149">
         <v>1.2</v>
       </c>
       <c r="C9" s="1">
@@ -26533,7 +26536,7 @@
       <c r="A10" s="102" t="s">
         <v>621</v>
       </c>
-      <c r="B10" s="151">
+      <c r="B10" s="150">
         <f>0.82+0.72</f>
         <v>1.54</v>
       </c>
@@ -26919,22 +26922,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="149" t="s">
+      <c r="A1" s="148" t="s">
         <v>182</v>
       </c>
-      <c r="B1" s="149" t="s">
+      <c r="B1" s="148" t="s">
         <v>3</v>
       </c>
-      <c r="C1" s="149" t="s">
+      <c r="C1" s="148" t="s">
         <v>597</v>
       </c>
-      <c r="D1" s="149" t="s">
+      <c r="D1" s="148" t="s">
         <v>138</v>
       </c>
-      <c r="E1" s="149" t="s">
+      <c r="E1" s="148" t="s">
         <v>183</v>
       </c>
-      <c r="F1" s="149" t="s">
+      <c r="F1" s="148" t="s">
         <v>16</v>
       </c>
       <c r="G1" s="24" t="s">
@@ -26966,6 +26969,9 @@
       </c>
       <c r="P1" s="24" t="s">
         <v>568</v>
+      </c>
+      <c r="Q1" s="142" t="s">
+        <v>652</v>
       </c>
       <c r="U1" s="6" t="s">
         <v>184</v>
@@ -28079,16 +28085,16 @@
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B45" s="148"/>
-      <c r="C45" s="148"/>
-      <c r="D45" s="148"/>
-      <c r="E45" s="148"/>
-      <c r="F45" s="148"/>
-      <c r="G45" s="148"/>
-      <c r="H45" s="148"/>
-      <c r="I45" s="148"/>
-      <c r="J45" s="148"/>
-      <c r="K45" s="148"/>
+      <c r="B45" s="151"/>
+      <c r="C45" s="151"/>
+      <c r="D45" s="151"/>
+      <c r="E45" s="151"/>
+      <c r="F45" s="151"/>
+      <c r="G45" s="151"/>
+      <c r="H45" s="151"/>
+      <c r="I45" s="151"/>
+      <c r="J45" s="151"/>
+      <c r="K45" s="151"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3939" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3225624D-42C4-4EC1-9330-B3F107FB96A9}"/>
+  <xr:revisionPtr revIDLastSave="4050" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7056A581-8C31-4175-9C1F-BF41EB2E2D61}"/>
   <bookViews>
-    <workbookView xWindow="2260" yWindow="710" windowWidth="23180" windowHeight="15150" tabRatio="905" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1430" yWindow="2040" windowWidth="36940" windowHeight="19260" tabRatio="905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lath" sheetId="7" r:id="rId1"/>
@@ -18,20 +18,21 @@
     <sheet name="Guides" sheetId="12" r:id="rId3"/>
     <sheet name="Endlock" sheetId="16" r:id="rId4"/>
     <sheet name="Axles" sheetId="6" r:id="rId5"/>
-    <sheet name="Disc size" sheetId="21" r:id="rId6"/>
-    <sheet name="Motors" sheetId="5" r:id="rId7"/>
-    <sheet name="Chaindrive" sheetId="11" r:id="rId8"/>
-    <sheet name="Chain" sheetId="15" r:id="rId9"/>
-    <sheet name="Bearings" sheetId="10" r:id="rId10"/>
-    <sheet name="SafetyB" sheetId="8" r:id="rId11"/>
-    <sheet name="Endplate" sheetId="13" r:id="rId12"/>
-    <sheet name="Wicket doors" sheetId="14" r:id="rId13"/>
-    <sheet name="Wind class" sheetId="20" r:id="rId14"/>
-    <sheet name="Size range" sheetId="19" r:id="rId15"/>
-    <sheet name="Online codes" sheetId="17" r:id="rId16"/>
+    <sheet name="Coiling data" sheetId="22" r:id="rId6"/>
+    <sheet name="Disc size" sheetId="21" r:id="rId7"/>
+    <sheet name="Motors" sheetId="5" r:id="rId8"/>
+    <sheet name="Chaindrive" sheetId="11" r:id="rId9"/>
+    <sheet name="Chain" sheetId="15" r:id="rId10"/>
+    <sheet name="Bearings" sheetId="10" r:id="rId11"/>
+    <sheet name="SafetyB" sheetId="8" r:id="rId12"/>
+    <sheet name="Endplate" sheetId="13" r:id="rId13"/>
+    <sheet name="Wicket doors" sheetId="14" r:id="rId14"/>
+    <sheet name="Wind class" sheetId="20" r:id="rId15"/>
+    <sheet name="Size range" sheetId="19" r:id="rId16"/>
+    <sheet name="Online codes" sheetId="17" r:id="rId17"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="6">Motors!$A$1:$S$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7">Motors!$A$1:$S$145</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -163,7 +164,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>robert hyrons:</t>
         </r>
@@ -172,7 +173,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 This is for lath that can be rever coiled, the calulation will add 10mm to the first wrap of the shutter, this will increase troque and possibly endplate size.</t>
@@ -255,7 +256,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>robert hyrons:</t>
         </r>
@@ -264,7 +265,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 This will group in to common configerations such as seceurodoor motor opp, seceurodor spring opp or shield. There the physical make up is common.  </t>
@@ -827,7 +828,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2815" uniqueCount="650">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2871" uniqueCount="675">
   <si>
     <t>Name</t>
   </si>
@@ -2777,6 +2778,417 @@
   </si>
   <si>
     <t>55 plastic</t>
+  </si>
+  <si>
+    <t>New cast endlock?</t>
+  </si>
+  <si>
+    <t>Eurodrive 500</t>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>st</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 145mm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 130mm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>rd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 120mm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 110mm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">th </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 95mm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  75mm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  65mm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  55mm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>st</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 137mm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>nd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 122mm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>rd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 110mm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 92mm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">th </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> 75mm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  61mm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>7</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  48mm</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>8</t>
+    </r>
+    <r>
+      <rPr>
+        <vertAlign val="superscript"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t>th</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">  35mm</t>
+    </r>
+  </si>
+  <si>
+    <t>Internal coil per wrap</t>
+  </si>
+  <si>
+    <t>External coil per wrap</t>
+  </si>
+  <si>
+    <t>Average lath width</t>
+  </si>
+  <si>
+    <t>Ranger 90 3ph 12-57 5/8"</t>
+  </si>
+  <si>
+    <t>Motor usage type available</t>
+  </si>
+  <si>
+    <t>Standard, Hi usage</t>
+  </si>
+  <si>
+    <t>Standard, Hi usage, Hi speed</t>
   </si>
 </sst>
 </file>
@@ -2788,7 +3200,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2917,20 +3329,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <vertAlign val="superscript"/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
@@ -3076,7 +3482,7 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="155">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3487,10 +3893,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="22" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="20" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="22" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="20" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
@@ -3502,8 +3908,18 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="2"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -10445,6 +10861,50 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>18144</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>61016</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>19</xdr:col>
+      <xdr:colOff>834571</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>447361</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="112" name="Picture 111">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C865F238-1195-0215-EF87-31FDE1C4555B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId50"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="22451787" y="4633016"/>
+          <a:ext cx="816427" cy="386345"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -11714,8 +12174,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47E91FF3-79AA-48A9-9F88-C48DFFEF60AE}">
-  <dimension ref="A1:T199"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:U199"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="35.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="8.7265625" style="6"/>
@@ -11728,9 +12188,10 @@
     <col min="14" max="15" width="8.7265625" style="6"/>
     <col min="16" max="16" width="10.1796875" style="6" customWidth="1"/>
     <col min="17" max="17" width="10.7265625" style="51" customWidth="1"/>
+    <col min="21" max="21" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" s="1" customFormat="1" ht="48.65" customHeight="1">
+    <row r="1" spans="1:21" s="1" customFormat="1" ht="48.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
@@ -11791,8 +12252,11 @@
       <c r="T1" s="1" t="s">
         <v>627</v>
       </c>
-    </row>
-    <row r="2" spans="1:20" ht="40" customHeight="1">
+      <c r="U1" s="10" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="26" t="s">
         <v>16</v>
       </c>
@@ -11846,8 +12310,11 @@
       <c r="T2" s="6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="3" spans="1:20" ht="40" customHeight="1">
+      <c r="U2" s="158" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="32" t="s">
         <v>21</v>
       </c>
@@ -11901,8 +12368,11 @@
       <c r="T3" s="6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="4" spans="1:20" ht="40" customHeight="1">
+      <c r="U3" s="158" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="26" t="s">
         <v>23</v>
       </c>
@@ -11956,8 +12426,11 @@
       <c r="T4" s="6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="5" spans="1:20" ht="40" customHeight="1">
+      <c r="U4" s="158" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="32" t="s">
         <v>24</v>
       </c>
@@ -12011,8 +12484,11 @@
       <c r="T5" s="6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="6" spans="1:20" ht="40" customHeight="1">
+      <c r="U5" s="158" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="26" t="s">
         <v>25</v>
       </c>
@@ -12066,8 +12542,11 @@
       <c r="T6" s="6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="7" spans="1:20" ht="40" customHeight="1">
+      <c r="U6" s="158" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="32" t="s">
         <v>26</v>
       </c>
@@ -12121,8 +12600,11 @@
       <c r="T7" s="6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="8" spans="1:20" ht="40" customHeight="1">
+      <c r="U7" s="158" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="26" t="s">
         <v>27</v>
       </c>
@@ -12176,8 +12658,11 @@
       <c r="T8" s="6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="9" spans="1:20" ht="40" customHeight="1">
+      <c r="U8" s="158" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="32" t="s">
         <v>28</v>
       </c>
@@ -12201,7 +12686,7 @@
         <v>15</v>
       </c>
       <c r="I9" s="16">
-        <v>6200</v>
+        <v>4000</v>
       </c>
       <c r="J9" s="42">
         <v>100</v>
@@ -12231,8 +12716,11 @@
       <c r="T9" s="6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="10" spans="1:20" ht="40" customHeight="1">
+      <c r="U9" s="158" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="26" t="s">
         <v>29</v>
       </c>
@@ -12286,8 +12774,11 @@
       <c r="T10" s="6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="11" spans="1:20" ht="40" customHeight="1">
+      <c r="U10" s="158" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="32" t="s">
         <v>30</v>
       </c>
@@ -12341,8 +12832,11 @@
       <c r="T11" s="6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="12" spans="1:20" ht="40" customHeight="1">
+      <c r="U11" s="158" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="26" t="s">
         <v>31</v>
       </c>
@@ -12396,8 +12890,11 @@
       <c r="T12" s="6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="13" spans="1:20" ht="40" customHeight="1">
+      <c r="U12" s="158" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="32" t="s">
         <v>32</v>
       </c>
@@ -12451,8 +12948,11 @@
       <c r="T13" s="6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" spans="1:20" ht="40" customHeight="1">
+      <c r="U13" s="158" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="26" t="s">
         <v>33</v>
       </c>
@@ -12506,8 +13006,11 @@
       <c r="T14" s="6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="15" spans="1:20" ht="40" customHeight="1">
+      <c r="U14" s="158" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="32" t="s">
         <v>34</v>
       </c>
@@ -12561,8 +13064,11 @@
       <c r="T15" s="6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="16" spans="1:20" ht="40" customHeight="1">
+      <c r="U15" s="158" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="26" t="s">
         <v>35</v>
       </c>
@@ -12616,8 +13122,11 @@
       <c r="T16" s="6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="17" spans="1:20" ht="40" customHeight="1">
+      <c r="U16" s="158" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="32" t="s">
         <v>36</v>
       </c>
@@ -12671,8 +13180,11 @@
       <c r="T17" s="6" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="18" spans="1:20" s="62" customFormat="1" ht="16" customHeight="1">
+      <c r="U17" s="158" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" s="62" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="94" t="s">
         <v>37</v>
       </c>
@@ -12692,7 +13204,7 @@
       <c r="P18" s="61"/>
       <c r="Q18" s="63"/>
     </row>
-    <row r="19" spans="1:20" ht="40" customHeight="1">
+    <row r="19" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="26" t="s">
         <v>38</v>
       </c>
@@ -12745,8 +13257,11 @@
       <c r="T19" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="20" spans="1:20" s="62" customFormat="1" ht="12.65" customHeight="1">
+      <c r="U19" s="158" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" s="62" customFormat="1" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="94" t="s">
         <v>37</v>
       </c>
@@ -12766,7 +13281,7 @@
       <c r="P20" s="61"/>
       <c r="Q20" s="63"/>
     </row>
-    <row r="21" spans="1:20" ht="40" customHeight="1">
+    <row r="21" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="26" t="s">
         <v>40</v>
       </c>
@@ -12820,8 +13335,11 @@
       <c r="T21" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="22" spans="1:20" ht="40" customHeight="1">
+      <c r="U21" s="158" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="26" t="s">
         <v>41</v>
       </c>
@@ -12873,8 +13391,11 @@
       <c r="T22" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="23" spans="1:20" s="62" customFormat="1" ht="10" customHeight="1">
+      <c r="U22" s="158" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" s="62" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="94" t="s">
         <v>37</v>
       </c>
@@ -12894,7 +13415,7 @@
       <c r="P23" s="61"/>
       <c r="Q23" s="63"/>
     </row>
-    <row r="24" spans="1:20" ht="40" customHeight="1">
+    <row r="24" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="26" t="s">
         <v>42</v>
       </c>
@@ -12948,8 +13469,11 @@
       <c r="T24" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="25" spans="1:20" s="62" customFormat="1" ht="16.5" customHeight="1">
+      <c r="U24" s="158" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" s="62" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="94" t="s">
         <v>37</v>
       </c>
@@ -12969,7 +13493,7 @@
       <c r="P25" s="61"/>
       <c r="Q25" s="63"/>
     </row>
-    <row r="26" spans="1:20" ht="40" customHeight="1">
+    <row r="26" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="26" t="s">
         <v>43</v>
       </c>
@@ -13019,8 +13543,11 @@
       <c r="T26" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="27" spans="1:20" ht="40" customHeight="1">
+      <c r="U26" s="158" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="26" t="s">
         <v>46</v>
       </c>
@@ -13070,8 +13597,11 @@
       <c r="T27" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="28" spans="1:20" ht="40" customHeight="1">
+      <c r="U27" s="158" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="26" t="s">
         <v>47</v>
       </c>
@@ -13121,8 +13651,11 @@
       <c r="T28" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="29" spans="1:20" ht="40" customHeight="1">
+      <c r="U28" s="158" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="26" t="s">
         <v>48</v>
       </c>
@@ -13172,8 +13705,11 @@
       <c r="T29" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="30" spans="1:20" ht="40" customHeight="1">
+      <c r="U29" s="158" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="26" t="s">
         <v>49</v>
       </c>
@@ -13223,8 +13759,11 @@
       <c r="T30" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="31" spans="1:20" ht="40" customHeight="1">
+      <c r="U30" s="158" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="26" t="s">
         <v>50</v>
       </c>
@@ -13274,8 +13813,11 @@
       <c r="T31" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="32" spans="1:20" ht="40" customHeight="1">
+      <c r="U31" s="158" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="26" t="s">
         <v>51</v>
       </c>
@@ -13325,8 +13867,11 @@
       <c r="T32" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="33" spans="1:20" ht="40" customHeight="1">
+      <c r="U32" s="158" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="26" t="s">
         <v>52</v>
       </c>
@@ -13376,8 +13921,11 @@
       <c r="T33" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="34" spans="1:20" ht="40" customHeight="1">
+      <c r="U33" s="158" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="26" t="s">
         <v>53</v>
       </c>
@@ -13427,8 +13975,11 @@
       <c r="T34" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="35" spans="1:20" ht="40" customHeight="1">
+      <c r="U34" s="158" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="26" t="s">
         <v>54</v>
       </c>
@@ -13478,8 +14029,11 @@
       <c r="T35" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="36" spans="1:20" s="62" customFormat="1" ht="14.15" customHeight="1">
+      <c r="U35" s="158" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" s="62" customFormat="1" ht="14.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="94" t="s">
         <v>37</v>
       </c>
@@ -13499,7 +14053,7 @@
       <c r="P36" s="61"/>
       <c r="Q36" s="63"/>
     </row>
-    <row r="37" spans="1:20" ht="40" customHeight="1">
+    <row r="37" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="26" t="s">
         <v>56</v>
       </c>
@@ -13549,8 +14103,11 @@
       <c r="T37" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="38" spans="1:20" ht="40" customHeight="1">
+      <c r="U37" s="158" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="26" t="s">
         <v>58</v>
       </c>
@@ -13599,168 +14156,171 @@
       <c r="T38" s="6" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="39" spans="1:20" ht="40" customHeight="1"/>
-    <row r="40" spans="1:20" ht="40" customHeight="1"/>
-    <row r="41" spans="1:20" ht="40" customHeight="1"/>
-    <row r="42" spans="1:20" ht="40" customHeight="1"/>
-    <row r="43" spans="1:20" ht="40" customHeight="1"/>
-    <row r="44" spans="1:20" ht="40" customHeight="1"/>
-    <row r="45" spans="1:20" ht="40" customHeight="1"/>
-    <row r="46" spans="1:20" ht="40" customHeight="1"/>
-    <row r="47" spans="1:20" ht="40" customHeight="1"/>
-    <row r="48" spans="1:20" ht="40" customHeight="1"/>
-    <row r="49" ht="40" customHeight="1"/>
-    <row r="50" ht="40" customHeight="1"/>
-    <row r="51" ht="40" customHeight="1"/>
-    <row r="52" ht="40" customHeight="1"/>
-    <row r="53" ht="40" customHeight="1"/>
-    <row r="54" ht="40" customHeight="1"/>
-    <row r="55" ht="40" customHeight="1"/>
-    <row r="56" ht="40" customHeight="1"/>
-    <row r="57" ht="40" customHeight="1"/>
-    <row r="58" ht="40" customHeight="1"/>
-    <row r="59" ht="40" customHeight="1"/>
-    <row r="60" ht="40" customHeight="1"/>
-    <row r="61" ht="40" customHeight="1"/>
-    <row r="62" ht="40" customHeight="1"/>
-    <row r="63" ht="40" customHeight="1"/>
-    <row r="64" ht="40" customHeight="1"/>
-    <row r="65" ht="40" customHeight="1"/>
-    <row r="66" ht="40" customHeight="1"/>
-    <row r="67" ht="40" customHeight="1"/>
-    <row r="68" ht="40" customHeight="1"/>
-    <row r="69" ht="40" customHeight="1"/>
-    <row r="70" ht="40" customHeight="1"/>
-    <row r="71" ht="40" customHeight="1"/>
-    <row r="72" ht="40" customHeight="1"/>
-    <row r="73" ht="40" customHeight="1"/>
-    <row r="74" ht="40" customHeight="1"/>
-    <row r="75" ht="40" customHeight="1"/>
-    <row r="76" ht="40" customHeight="1"/>
-    <row r="77" ht="40" customHeight="1"/>
-    <row r="78" ht="40" customHeight="1"/>
-    <row r="79" ht="40" customHeight="1"/>
-    <row r="80" ht="40" customHeight="1"/>
-    <row r="81" ht="40" customHeight="1"/>
-    <row r="82" ht="40" customHeight="1"/>
-    <row r="83" ht="40" customHeight="1"/>
-    <row r="84" ht="40" customHeight="1"/>
-    <row r="85" ht="40" customHeight="1"/>
-    <row r="86" ht="40" customHeight="1"/>
-    <row r="87" ht="40" customHeight="1"/>
-    <row r="88" ht="40" customHeight="1"/>
-    <row r="89" ht="40" customHeight="1"/>
-    <row r="90" ht="40" customHeight="1"/>
-    <row r="91" ht="40" customHeight="1"/>
-    <row r="92" ht="40" customHeight="1"/>
-    <row r="93" ht="40" customHeight="1"/>
-    <row r="94" ht="40" customHeight="1"/>
-    <row r="95" ht="40" customHeight="1"/>
-    <row r="96" ht="40" customHeight="1"/>
-    <row r="97" ht="40" customHeight="1"/>
-    <row r="98" ht="40" customHeight="1"/>
-    <row r="99" ht="40" customHeight="1"/>
-    <row r="100" ht="40" customHeight="1"/>
-    <row r="101" ht="40" customHeight="1"/>
-    <row r="102" ht="40" customHeight="1"/>
-    <row r="103" ht="40" customHeight="1"/>
-    <row r="104" ht="40" customHeight="1"/>
-    <row r="105" ht="40" customHeight="1"/>
-    <row r="106" ht="40" customHeight="1"/>
-    <row r="107" ht="40" customHeight="1"/>
-    <row r="108" ht="40" customHeight="1"/>
-    <row r="109" ht="40" customHeight="1"/>
-    <row r="110" ht="40" customHeight="1"/>
-    <row r="111" ht="40" customHeight="1"/>
-    <row r="112" ht="40" customHeight="1"/>
-    <row r="113" ht="40" customHeight="1"/>
-    <row r="114" ht="40" customHeight="1"/>
-    <row r="115" ht="40" customHeight="1"/>
-    <row r="116" ht="40" customHeight="1"/>
-    <row r="117" ht="40" customHeight="1"/>
-    <row r="118" ht="40" customHeight="1"/>
-    <row r="119" ht="40" customHeight="1"/>
-    <row r="120" ht="40" customHeight="1"/>
-    <row r="121" ht="40" customHeight="1"/>
-    <row r="122" ht="40" customHeight="1"/>
-    <row r="123" ht="40" customHeight="1"/>
-    <row r="124" ht="40" customHeight="1"/>
-    <row r="125" ht="40" customHeight="1"/>
-    <row r="126" ht="40" customHeight="1"/>
-    <row r="127" ht="40" customHeight="1"/>
-    <row r="128" ht="40" customHeight="1"/>
-    <row r="129" ht="40" customHeight="1"/>
-    <row r="130" ht="40" customHeight="1"/>
-    <row r="131" ht="40" customHeight="1"/>
-    <row r="132" ht="40" customHeight="1"/>
-    <row r="133" ht="40" customHeight="1"/>
-    <row r="134" ht="40" customHeight="1"/>
-    <row r="135" ht="40" customHeight="1"/>
-    <row r="136" ht="40" customHeight="1"/>
-    <row r="137" ht="40" customHeight="1"/>
-    <row r="138" ht="40" customHeight="1"/>
-    <row r="139" ht="40" customHeight="1"/>
-    <row r="140" ht="40" customHeight="1"/>
-    <row r="141" ht="40" customHeight="1"/>
-    <row r="142" ht="40" customHeight="1"/>
-    <row r="143" ht="40" customHeight="1"/>
-    <row r="144" ht="40" customHeight="1"/>
-    <row r="145" ht="40" customHeight="1"/>
-    <row r="146" ht="40" customHeight="1"/>
-    <row r="147" ht="40" customHeight="1"/>
-    <row r="148" ht="40" customHeight="1"/>
-    <row r="149" ht="40" customHeight="1"/>
-    <row r="150" ht="40" customHeight="1"/>
-    <row r="151" ht="40" customHeight="1"/>
-    <row r="152" ht="40" customHeight="1"/>
-    <row r="153" ht="40" customHeight="1"/>
-    <row r="154" ht="40" customHeight="1"/>
-    <row r="155" ht="40" customHeight="1"/>
-    <row r="156" ht="40" customHeight="1"/>
-    <row r="157" ht="40" customHeight="1"/>
-    <row r="158" ht="40" customHeight="1"/>
-    <row r="159" ht="40" customHeight="1"/>
-    <row r="160" ht="40" customHeight="1"/>
-    <row r="161" ht="40" customHeight="1"/>
-    <row r="162" ht="40" customHeight="1"/>
-    <row r="163" ht="40" customHeight="1"/>
-    <row r="164" ht="40" customHeight="1"/>
-    <row r="165" ht="40" customHeight="1"/>
-    <row r="166" ht="40" customHeight="1"/>
-    <row r="167" ht="40" customHeight="1"/>
-    <row r="168" ht="40" customHeight="1"/>
-    <row r="169" ht="40" customHeight="1"/>
-    <row r="170" ht="40" customHeight="1"/>
-    <row r="171" ht="40" customHeight="1"/>
-    <row r="172" ht="40" customHeight="1"/>
-    <row r="173" ht="40" customHeight="1"/>
-    <row r="174" ht="40" customHeight="1"/>
-    <row r="175" ht="40" customHeight="1"/>
-    <row r="176" ht="40" customHeight="1"/>
-    <row r="177" ht="40" customHeight="1"/>
-    <row r="178" ht="40" customHeight="1"/>
-    <row r="179" ht="40" customHeight="1"/>
-    <row r="180" ht="40" customHeight="1"/>
-    <row r="181" ht="40" customHeight="1"/>
-    <row r="182" ht="40" customHeight="1"/>
-    <row r="183" ht="40" customHeight="1"/>
-    <row r="184" ht="40" customHeight="1"/>
-    <row r="185" ht="40" customHeight="1"/>
-    <row r="186" ht="40" customHeight="1"/>
-    <row r="187" ht="40" customHeight="1"/>
-    <row r="188" ht="40" customHeight="1"/>
-    <row r="189" ht="40" customHeight="1"/>
-    <row r="190" ht="40" customHeight="1"/>
-    <row r="191" ht="40" customHeight="1"/>
-    <row r="192" ht="40" customHeight="1"/>
-    <row r="193" ht="40" customHeight="1"/>
-    <row r="194" ht="40" customHeight="1"/>
-    <row r="195" ht="40" customHeight="1"/>
-    <row r="196" ht="40" customHeight="1"/>
-    <row r="197" ht="40" customHeight="1"/>
-    <row r="198" ht="40" customHeight="1"/>
-    <row r="199" ht="40" customHeight="1"/>
+      <c r="U38" s="158" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="40" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="41" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="42" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="43" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="44" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="45" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="46" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="47" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="48" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="49" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="50" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="51" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="52" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="53" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="54" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="55" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="56" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="57" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="58" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="59" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="60" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="61" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="62" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="63" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="64" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="65" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="66" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="67" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="68" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="69" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="70" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="71" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="72" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="73" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="74" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="75" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="76" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="77" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="78" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="79" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="80" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="81" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="82" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="83" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="84" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="85" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="86" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="87" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="88" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="89" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="90" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="91" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="92" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="93" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="94" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="95" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="96" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="97" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="98" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="99" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="100" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="101" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="102" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="103" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="104" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="105" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="106" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="107" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="108" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="109" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="110" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="111" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="112" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="113" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="114" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="115" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="116" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="117" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="118" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="119" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="120" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="121" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="122" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="123" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="124" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="125" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="126" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="127" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="128" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="129" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="130" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="131" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="132" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="133" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="134" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="135" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="136" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="137" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="138" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="139" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="140" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="141" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="142" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="143" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="144" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="145" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="146" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="147" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="148" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="149" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="150" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="151" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="152" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="153" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="154" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="155" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="156" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="157" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="158" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="159" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="160" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="161" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="162" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="163" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="164" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="165" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="166" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="167" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="168" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="169" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="170" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="171" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="172" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="173" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="174" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="175" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="176" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="177" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="178" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="179" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="180" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="181" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="182" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="183" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="184" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="185" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="186" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="187" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="188" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="189" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="190" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="191" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="192" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="193" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="194" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="195" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="196" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="197" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="198" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="199" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -13770,9 +14330,406 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09BBB0E4-3072-46AD-B687-93FC8399DD89}">
+  <dimension ref="A1:J15"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="10.54296875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="24" style="6" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="24.81640625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="21.26953125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.26953125" style="6" customWidth="1"/>
+    <col min="7" max="7" width="15.54296875" style="6" customWidth="1"/>
+    <col min="8" max="8" width="18.54296875" style="6" customWidth="1"/>
+    <col min="9" max="9" width="8.7265625" style="6"/>
+    <col min="10" max="10" width="20.81640625" style="6" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A1" s="8" t="s">
+        <v>410</v>
+      </c>
+      <c r="B1" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>412</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>413</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>414</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>415</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>417</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="87" t="s">
+        <v>392</v>
+      </c>
+      <c r="B2" s="87">
+        <v>12</v>
+      </c>
+      <c r="C2" s="87">
+        <v>25.4</v>
+      </c>
+      <c r="D2" s="87">
+        <v>57</v>
+      </c>
+      <c r="E2" s="87">
+        <v>30</v>
+      </c>
+      <c r="F2" s="87">
+        <v>18000</v>
+      </c>
+      <c r="G2" s="88">
+        <f>0.5*25.4</f>
+        <v>12.7</v>
+      </c>
+      <c r="H2" s="87">
+        <v>18000</v>
+      </c>
+      <c r="I2" s="87">
+        <f>D2/B2</f>
+        <v>4.75</v>
+      </c>
+      <c r="J2" s="87">
+        <v>230.54</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A3" s="87" t="s">
+        <v>392</v>
+      </c>
+      <c r="B3" s="87">
+        <v>15</v>
+      </c>
+      <c r="C3" s="87">
+        <v>25.4</v>
+      </c>
+      <c r="D3" s="87">
+        <v>57</v>
+      </c>
+      <c r="E3" s="87">
+        <v>30</v>
+      </c>
+      <c r="F3" s="87">
+        <v>18000</v>
+      </c>
+      <c r="G3" s="88">
+        <f>0.5*25.4</f>
+        <v>12.7</v>
+      </c>
+      <c r="H3" s="87">
+        <v>18000</v>
+      </c>
+      <c r="I3" s="87">
+        <f>D3/B3</f>
+        <v>3.8</v>
+      </c>
+      <c r="J3" s="87">
+        <v>230.54</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A4" s="87" t="s">
+        <v>392</v>
+      </c>
+      <c r="B4" s="87">
+        <v>19</v>
+      </c>
+      <c r="C4" s="87">
+        <v>25.4</v>
+      </c>
+      <c r="D4" s="87">
+        <v>57</v>
+      </c>
+      <c r="E4" s="87">
+        <v>30</v>
+      </c>
+      <c r="F4" s="87">
+        <v>18000</v>
+      </c>
+      <c r="G4" s="88">
+        <f>0.5*25.4</f>
+        <v>12.7</v>
+      </c>
+      <c r="H4" s="87">
+        <v>18000</v>
+      </c>
+      <c r="I4" s="87">
+        <f t="shared" ref="I4:I7" si="0">D4/B4</f>
+        <v>3</v>
+      </c>
+      <c r="J4" s="87">
+        <v>230.54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="89" t="s">
+        <v>398</v>
+      </c>
+      <c r="B5" s="90">
+        <v>12</v>
+      </c>
+      <c r="C5" s="90">
+        <v>25.4</v>
+      </c>
+      <c r="D5" s="90">
+        <v>57</v>
+      </c>
+      <c r="E5" s="90" t="s">
+        <v>419</v>
+      </c>
+      <c r="F5" s="90">
+        <v>22400</v>
+      </c>
+      <c r="G5" s="91">
+        <f>0.625*25.4</f>
+        <v>15.875</v>
+      </c>
+      <c r="H5" s="90">
+        <v>22400</v>
+      </c>
+      <c r="I5" s="90">
+        <f t="shared" si="0"/>
+        <v>4.75</v>
+      </c>
+      <c r="J5" s="90">
+        <v>288.18</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="89" t="s">
+        <v>398</v>
+      </c>
+      <c r="B6" s="90">
+        <v>18</v>
+      </c>
+      <c r="C6" s="90">
+        <v>25.4</v>
+      </c>
+      <c r="D6" s="90">
+        <v>57</v>
+      </c>
+      <c r="E6" s="90" t="s">
+        <v>419</v>
+      </c>
+      <c r="F6" s="90">
+        <v>22400</v>
+      </c>
+      <c r="G6" s="91">
+        <f>0.625*25.4</f>
+        <v>15.875</v>
+      </c>
+      <c r="H6" s="90">
+        <v>22400</v>
+      </c>
+      <c r="I6" s="90">
+        <f t="shared" si="0"/>
+        <v>3.1666666666666665</v>
+      </c>
+      <c r="J6" s="90">
+        <v>288.18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A7" s="122" t="s">
+        <v>400</v>
+      </c>
+      <c r="B7" s="122">
+        <v>12</v>
+      </c>
+      <c r="C7" s="122">
+        <v>25.4</v>
+      </c>
+      <c r="D7" s="122">
+        <v>57</v>
+      </c>
+      <c r="E7" s="122" t="s">
+        <v>420</v>
+      </c>
+      <c r="F7" s="122">
+        <v>29000</v>
+      </c>
+      <c r="G7" s="123">
+        <f>0.75*25.4</f>
+        <v>19.049999999999997</v>
+      </c>
+      <c r="H7" s="122">
+        <v>29000</v>
+      </c>
+      <c r="I7" s="122">
+        <f t="shared" si="0"/>
+        <v>4.75</v>
+      </c>
+      <c r="J7" s="122">
+        <v>345.81</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A8" s="122" t="s">
+        <v>400</v>
+      </c>
+      <c r="B8" s="122">
+        <v>12</v>
+      </c>
+      <c r="C8" s="122">
+        <v>30</v>
+      </c>
+      <c r="D8" s="122">
+        <v>57</v>
+      </c>
+      <c r="E8" s="122" t="s">
+        <v>420</v>
+      </c>
+      <c r="F8" s="122">
+        <v>29000</v>
+      </c>
+      <c r="G8" s="123">
+        <f>0.75*25.4</f>
+        <v>19.049999999999997</v>
+      </c>
+      <c r="H8" s="122">
+        <v>29000</v>
+      </c>
+      <c r="I8" s="122">
+        <f t="shared" ref="I8" si="1">D8/B8</f>
+        <v>4.75</v>
+      </c>
+      <c r="J8" s="122">
+        <v>345.81</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A9" s="122" t="s">
+        <v>400</v>
+      </c>
+      <c r="B9" s="122">
+        <v>15</v>
+      </c>
+      <c r="C9" s="122">
+        <v>30</v>
+      </c>
+      <c r="D9" s="122">
+        <v>57</v>
+      </c>
+      <c r="E9" s="122" t="s">
+        <v>420</v>
+      </c>
+      <c r="F9" s="122">
+        <v>29000</v>
+      </c>
+      <c r="G9" s="123">
+        <f>0.75*25.4</f>
+        <v>19.049999999999997</v>
+      </c>
+      <c r="H9" s="122">
+        <v>29000</v>
+      </c>
+      <c r="I9" s="122">
+        <f>D9/B9</f>
+        <v>3.8</v>
+      </c>
+      <c r="J9" s="122">
+        <v>345.81</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A10" s="124" t="s">
+        <v>402</v>
+      </c>
+      <c r="B10" s="124">
+        <v>15</v>
+      </c>
+      <c r="C10" s="124">
+        <v>40</v>
+      </c>
+      <c r="D10" s="124">
+        <v>57</v>
+      </c>
+      <c r="E10" s="124" t="s">
+        <v>421</v>
+      </c>
+      <c r="F10" s="124">
+        <v>60000</v>
+      </c>
+      <c r="G10" s="125">
+        <v>25.4</v>
+      </c>
+      <c r="H10" s="124">
+        <v>60000</v>
+      </c>
+      <c r="I10" s="124">
+        <f>D10/B10</f>
+        <v>3.8</v>
+      </c>
+      <c r="J10" s="124">
+        <v>461.07</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A11" s="126" t="s">
+        <v>403</v>
+      </c>
+      <c r="B11" s="126">
+        <v>15</v>
+      </c>
+      <c r="C11" s="126">
+        <v>55</v>
+      </c>
+      <c r="D11" s="126">
+        <v>57</v>
+      </c>
+      <c r="E11" s="126" t="s">
+        <v>422</v>
+      </c>
+      <c r="F11" s="126">
+        <v>95000</v>
+      </c>
+      <c r="G11" s="127">
+        <f>1.25*25.4</f>
+        <v>31.75</v>
+      </c>
+      <c r="H11" s="126">
+        <v>95000</v>
+      </c>
+      <c r="I11" s="126">
+        <f>D11/B11</f>
+        <v>3.8</v>
+      </c>
+      <c r="J11" s="126">
+        <v>576.36</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A15" s="45"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{91673066-48CE-40A8-80D4-43FC435ADD39}">
   <dimension ref="A1:G12"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.453125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.81640625" style="6" customWidth="1"/>
@@ -13782,7 +14739,7 @@
     <col min="6" max="6" width="10" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="11" customFormat="1" ht="32" customHeight="1">
+    <row r="1" spans="1:7" s="11" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="43" t="s">
         <v>423</v>
       </c>
@@ -13805,7 +14762,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="40" customHeight="1">
+    <row r="2" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>427</v>
       </c>
@@ -13824,7 +14781,7 @@
       </c>
       <c r="F2" s="1"/>
     </row>
-    <row r="3" spans="1:7" ht="40" customHeight="1">
+    <row r="3" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>428</v>
       </c>
@@ -13843,7 +14800,7 @@
       </c>
       <c r="F3" s="1"/>
     </row>
-    <row r="4" spans="1:7" ht="40" customHeight="1">
+    <row r="4" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>427</v>
       </c>
@@ -13864,7 +14821,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="5" spans="1:7" ht="40" customHeight="1">
+    <row r="5" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>428</v>
       </c>
@@ -13885,7 +14842,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="40" customHeight="1">
+    <row r="6" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>429</v>
       </c>
@@ -13906,7 +14863,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="40" customHeight="1">
+    <row r="7" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>497</v>
       </c>
@@ -13927,7 +14884,7 @@
         <v>533</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="40" customHeight="1">
+    <row r="8" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B8" s="1">
         <v>80</v>
       </c>
@@ -13938,8 +14895,8 @@
       </c>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:7" ht="40" customHeight="1"/>
-    <row r="12" spans="1:7">
+    <row r="9" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E12" s="105"/>
     </row>
   </sheetData>
@@ -13950,10 +14907,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F0484E2-9992-4491-920F-B8AE57D8A0EE}">
   <dimension ref="A1:K33"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.81640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.453125" customWidth="1"/>
@@ -13966,7 +14923,7 @@
     <col min="11" max="11" width="49.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="43.5">
+    <row r="1" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
@@ -14001,7 +14958,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="40" customHeight="1">
+    <row r="2" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>436</v>
       </c>
@@ -14024,7 +14981,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="40" customHeight="1">
+    <row r="3" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>439</v>
       </c>
@@ -14047,7 +15004,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="40" customHeight="1">
+    <row r="4" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>440</v>
       </c>
@@ -14076,7 +15033,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="40" customHeight="1">
+    <row r="5" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>441</v>
       </c>
@@ -14102,7 +15059,7 @@
         <v>543</v>
       </c>
     </row>
-    <row r="6" spans="1:11" ht="40" customHeight="1">
+    <row r="6" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="95" t="s">
         <v>448</v>
       </c>
@@ -14126,7 +15083,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="40" customHeight="1">
+    <row r="7" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="95" t="s">
         <v>449</v>
       </c>
@@ -14150,7 +15107,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="40" customHeight="1">
+    <row r="8" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="95" t="s">
         <v>450</v>
       </c>
@@ -14177,7 +15134,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="9" spans="1:11" ht="40" customHeight="1">
+    <row r="9" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="104" t="s">
         <v>451</v>
       </c>
@@ -14205,7 +15162,7 @@
         <v>498</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="40" customHeight="1">
+    <row r="10" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="85" t="s">
         <v>442</v>
       </c>
@@ -14228,7 +15185,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="40" customHeight="1">
+    <row r="11" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="85" t="s">
         <v>443</v>
       </c>
@@ -14254,7 +15211,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="40" customHeight="1">
+    <row r="12" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="85" t="s">
         <v>444</v>
       </c>
@@ -14280,7 +15237,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="40" customHeight="1">
+    <row r="13" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="85" t="s">
         <v>445</v>
       </c>
@@ -14304,7 +15261,7 @@
       </c>
       <c r="I13" s="7"/>
     </row>
-    <row r="14" spans="1:11" ht="40" customHeight="1">
+    <row r="14" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="85" t="s">
         <v>446</v>
       </c>
@@ -14327,14 +15284,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="40" customHeight="1">
+    <row r="15" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="85"/>
       <c r="B15" s="84"/>
       <c r="C15" s="84"/>
       <c r="D15" s="84"/>
       <c r="E15" s="84"/>
     </row>
-    <row r="16" spans="1:11" ht="49" customHeight="1">
+    <row r="16" spans="1:11" ht="49" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>447</v>
       </c>
@@ -14360,19 +15317,19 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:11" ht="40" customHeight="1">
+    <row r="17" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="84"/>
       <c r="C17" s="84"/>
       <c r="E17" s="84"/>
       <c r="G17" s="84"/>
     </row>
-    <row r="18" spans="1:11" ht="40" customHeight="1">
+    <row r="18" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B18" s="84"/>
       <c r="C18" s="84"/>
       <c r="E18" s="84"/>
       <c r="G18" s="84"/>
     </row>
-    <row r="19" spans="1:11" ht="40" customHeight="1">
+    <row r="19" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="85"/>
       <c r="B19" s="84"/>
       <c r="C19" s="84"/>
@@ -14380,7 +15337,7 @@
       <c r="E19" s="84"/>
       <c r="G19" s="84"/>
     </row>
-    <row r="20" spans="1:11" ht="40" customHeight="1">
+    <row r="20" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="85"/>
       <c r="B20" s="84"/>
       <c r="C20" s="84"/>
@@ -14388,20 +15345,20 @@
       <c r="E20" s="84"/>
       <c r="G20" s="84"/>
     </row>
-    <row r="21" spans="1:11" ht="40" customHeight="1"/>
-    <row r="27" spans="1:11" ht="40" customHeight="1">
+    <row r="21" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="27" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="D27"/>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D28"/>
     </row>
-    <row r="29" spans="1:11" ht="40" customHeight="1"/>
-    <row r="30" spans="1:11" ht="40" customHeight="1">
+    <row r="29" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="30" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="K30" s="7"/>
     </row>
-    <row r="31" spans="1:11" ht="40" customHeight="1"/>
-    <row r="32" spans="1:11" ht="40" customHeight="1"/>
-    <row r="33" ht="40" customHeight="1"/>
+    <row r="31" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="32" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="33" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -14410,10 +15367,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63386739-1836-4135-BDCC-F0CD02A919B6}">
   <dimension ref="A1:H35"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15.90625" style="25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.54296875" customWidth="1"/>
@@ -14424,7 +15381,7 @@
     <col min="8" max="8" width="26.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="25" t="s">
         <v>0</v>
       </c>
@@ -14450,7 +15407,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
@@ -14458,7 +15415,7 @@
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="25" t="s">
         <v>476</v>
       </c>
@@ -14485,7 +15442,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="4" spans="1:8">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="25" t="s">
         <v>477</v>
       </c>
@@ -14512,7 +15469,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="5" spans="1:8">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="25" t="s">
         <v>478</v>
       </c>
@@ -14539,7 +15496,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="6" spans="1:8">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="25" t="s">
         <v>479</v>
       </c>
@@ -14566,7 +15523,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="7" spans="1:8">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="25" t="s">
         <v>475</v>
       </c>
@@ -14593,7 +15550,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="8" spans="1:8">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="25" t="s">
         <v>480</v>
       </c>
@@ -14620,7 +15577,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="9" spans="1:8">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="25" t="s">
         <v>481</v>
       </c>
@@ -14647,7 +15604,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="10" spans="1:8">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="25" t="s">
         <v>482</v>
       </c>
@@ -14674,7 +15631,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="11" spans="1:8">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="B11" s="6"/>
       <c r="C11" s="6"/>
       <c r="D11" s="6"/>
@@ -14682,7 +15639,7 @@
       <c r="F11" s="6"/>
       <c r="G11" s="6"/>
     </row>
-    <row r="13" spans="1:8">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="25" t="s">
         <v>457</v>
       </c>
@@ -14709,7 +15666,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="14" spans="1:8">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="25" t="s">
         <v>458</v>
       </c>
@@ -14736,7 +15693,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="15" spans="1:8">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="25" t="s">
         <v>459</v>
       </c>
@@ -14763,7 +15720,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="16" spans="1:8">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="25" t="s">
         <v>460</v>
       </c>
@@ -14790,7 +15747,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="17" spans="1:8">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="25" t="s">
         <v>461</v>
       </c>
@@ -14817,7 +15774,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="18" spans="1:8">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="25" t="s">
         <v>462</v>
       </c>
@@ -14844,7 +15801,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="19" spans="1:8">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="46" t="s">
         <v>463</v>
       </c>
@@ -14871,10 +15828,10 @@
         <v>619</v>
       </c>
     </row>
-    <row r="20" spans="1:8">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.35">
       <c r="F20" s="6"/>
     </row>
-    <row r="21" spans="1:8">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="25" t="s">
         <v>596</v>
       </c>
@@ -14901,7 +15858,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="22" spans="1:8">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="25" t="s">
         <v>597</v>
       </c>
@@ -14928,7 +15885,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="23" spans="1:8">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="25" t="s">
         <v>598</v>
       </c>
@@ -14955,7 +15912,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="24" spans="1:8">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="25" t="s">
         <v>599</v>
       </c>
@@ -14982,7 +15939,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="25" spans="1:8">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="25" t="s">
         <v>600</v>
       </c>
@@ -15009,7 +15966,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="26" spans="1:8">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="25" t="s">
         <v>601</v>
       </c>
@@ -15036,7 +15993,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="27" spans="1:8">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="46" t="s">
         <v>602</v>
       </c>
@@ -15063,7 +16020,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="30" spans="1:8">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="25" t="s">
         <v>464</v>
       </c>
@@ -15090,7 +16047,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="31" spans="1:8">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="25" t="s">
         <v>465</v>
       </c>
@@ -15117,7 +16074,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="32" spans="1:8">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="25" t="s">
         <v>466</v>
       </c>
@@ -15144,7 +16101,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="25" t="s">
         <v>467</v>
       </c>
@@ -15171,7 +16128,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="25" t="s">
         <v>468</v>
       </c>
@@ -15198,7 +16155,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="25" t="s">
         <v>469</v>
       </c>
@@ -15232,16 +16189,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F5897A5-8278-44A3-89B0-43E5A8B043EB}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="10.453125" customWidth="1"/>
     <col min="3" max="3" width="11.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -15252,7 +16209,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>156</v>
       </c>
@@ -15263,7 +16220,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>471</v>
       </c>
@@ -15279,17 +16236,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1ADABCF3-96BE-45E9-B437-F36F44B301C9}">
   <dimension ref="A3:K45"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="13.453125" style="6" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="14.36328125" style="6" customWidth="1"/>
     <col min="3" max="6" width="8.7265625" style="6"/>
   </cols>
   <sheetData>
-    <row r="3" spans="1:6" ht="29">
+    <row r="3" spans="1:6" ht="29" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>132</v>
       </c>
@@ -15309,7 +16266,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="1:6">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>138</v>
       </c>
@@ -15329,7 +16286,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>138</v>
       </c>
@@ -15349,7 +16306,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>142</v>
       </c>
@@ -15369,7 +16326,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:6">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>143</v>
       </c>
@@ -15389,7 +16346,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>143</v>
       </c>
@@ -15409,7 +16366,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:6">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>143</v>
       </c>
@@ -15429,7 +16386,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="13" spans="1:6">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>144</v>
       </c>
@@ -15449,7 +16406,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>144</v>
       </c>
@@ -15469,7 +16426,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>146</v>
       </c>
@@ -15489,7 +16446,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>138</v>
       </c>
@@ -15509,7 +16466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>138</v>
       </c>
@@ -15529,7 +16486,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>143</v>
       </c>
@@ -15549,17 +16506,17 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="2:11">
-      <c r="B45" s="154"/>
-      <c r="C45" s="154"/>
-      <c r="D45" s="154"/>
-      <c r="E45" s="154"/>
-      <c r="F45" s="154"/>
-      <c r="G45" s="154"/>
-      <c r="H45" s="154"/>
-      <c r="I45" s="154"/>
-      <c r="J45" s="154"/>
-      <c r="K45" s="154"/>
+    <row r="45" spans="2:11" x14ac:dyDescent="0.35">
+      <c r="B45" s="157"/>
+      <c r="C45" s="157"/>
+      <c r="D45" s="157"/>
+      <c r="E45" s="157"/>
+      <c r="F45" s="157"/>
+      <c r="G45" s="157"/>
+      <c r="H45" s="157"/>
+      <c r="I45" s="157"/>
+      <c r="J45" s="157"/>
+      <c r="K45" s="157"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -15570,10 +16527,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC4BF8E8-AD64-4A17-9082-6704FD390289}">
   <dimension ref="A2:J27"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="15.1796875" customWidth="1"/>
     <col min="3" max="3" width="13.54296875" customWidth="1"/>
@@ -15586,17 +16543,17 @@
     <col min="10" max="10" width="9" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:10">
-      <c r="A2" s="154" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A2" s="157" t="s">
         <v>527</v>
       </c>
-      <c r="B2" s="154"/>
-      <c r="C2" s="154"/>
-      <c r="D2" s="154"/>
-      <c r="E2" s="154"/>
-      <c r="F2" s="154"/>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="B2" s="157"/>
+      <c r="C2" s="157"/>
+      <c r="D2" s="157"/>
+      <c r="E2" s="157"/>
+      <c r="F2" s="157"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>523</v>
       </c>
@@ -15620,7 +16577,7 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>138</v>
       </c>
@@ -15644,7 +16601,7 @@
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
     </row>
-    <row r="6" spans="1:10">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>143</v>
       </c>
@@ -15664,7 +16621,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>144</v>
       </c>
@@ -15688,7 +16645,7 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>162</v>
       </c>
@@ -15712,7 +16669,7 @@
       <c r="I8" s="6"/>
       <c r="J8" s="6"/>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>146</v>
       </c>
@@ -15736,7 +16693,7 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>138</v>
       </c>
@@ -15756,7 +16713,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>143</v>
       </c>
@@ -15776,7 +16733,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>144</v>
       </c>
@@ -15796,7 +16753,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>162</v>
       </c>
@@ -15816,7 +16773,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>146</v>
       </c>
@@ -15836,7 +16793,7 @@
         <v>8000</v>
       </c>
     </row>
-    <row r="17" spans="1:6">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>138</v>
       </c>
@@ -15856,7 +16813,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="18" spans="1:6">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>143</v>
       </c>
@@ -15876,7 +16833,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="19" spans="1:6">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>144</v>
       </c>
@@ -15896,7 +16853,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="20" spans="1:6">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>162</v>
       </c>
@@ -15916,7 +16873,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="21" spans="1:6">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>146</v>
       </c>
@@ -15936,7 +16893,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="23" spans="1:6">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>138</v>
       </c>
@@ -15944,7 +16901,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="24" spans="1:6">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>143</v>
       </c>
@@ -15952,7 +16909,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="25" spans="1:6">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>144</v>
       </c>
@@ -15960,7 +16917,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="26" spans="1:6">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>162</v>
       </c>
@@ -15968,7 +16925,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="27" spans="1:6">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>146</v>
       </c>
@@ -15984,10 +16941,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3B9ED08-8454-4272-8896-17578EF9EBC9}">
   <dimension ref="A1:K36"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="12.26953125" customWidth="1"/>
     <col min="2" max="2" width="30" customWidth="1"/>
@@ -15998,7 +16955,7 @@
     <col min="8" max="8" width="15.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A1" s="70" t="s">
         <v>59</v>
       </c>
@@ -16022,7 +16979,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A2" s="68" t="s">
         <v>65</v>
       </c>
@@ -16039,7 +16996,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A3" s="68" t="s">
         <v>67</v>
       </c>
@@ -16056,7 +17013,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A4" s="68" t="s">
         <v>69</v>
       </c>
@@ -16073,7 +17030,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A5" s="68" t="s">
         <v>71</v>
       </c>
@@ -16090,7 +17047,7 @@
         <v>589</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A6" s="68" t="s">
         <v>65</v>
       </c>
@@ -16104,7 +17061,7 @@
         <v>590</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A7" s="68" t="s">
         <v>67</v>
       </c>
@@ -16118,7 +17075,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="16">
+    <row r="8" spans="1:11" ht="16" x14ac:dyDescent="0.35">
       <c r="A8" s="68" t="s">
         <v>69</v>
       </c>
@@ -16129,7 +17086,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A9" s="68" t="s">
         <v>76</v>
       </c>
@@ -16140,7 +17097,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:11" ht="16">
+    <row r="10" spans="1:11" ht="16" x14ac:dyDescent="0.35">
       <c r="A10" s="68" t="s">
         <v>78</v>
       </c>
@@ -16151,7 +17108,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="68" t="s">
         <v>80</v>
       </c>
@@ -16162,7 +17119,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="16">
+    <row r="12" spans="1:11" ht="16" x14ac:dyDescent="0.35">
       <c r="A12" s="68" t="s">
         <v>82</v>
       </c>
@@ -16173,7 +17130,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="16">
+    <row r="13" spans="1:11" ht="16" x14ac:dyDescent="0.35">
       <c r="A13" s="68" t="s">
         <v>84</v>
       </c>
@@ -16184,7 +17141,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="68" t="s">
         <v>86</v>
       </c>
@@ -16195,7 +17152,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="16">
+    <row r="15" spans="1:11" ht="16" x14ac:dyDescent="0.35">
       <c r="A15" s="68" t="s">
         <v>88</v>
       </c>
@@ -16206,7 +17163,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A16" s="68" t="s">
         <v>90</v>
       </c>
@@ -16217,7 +17174,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="17" spans="1:3" ht="16">
+    <row r="17" spans="1:3" ht="16" x14ac:dyDescent="0.35">
       <c r="A17" s="68" t="s">
         <v>92</v>
       </c>
@@ -16228,7 +17185,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="18" spans="1:3">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A18" s="68" t="s">
         <v>94</v>
       </c>
@@ -16239,7 +17196,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="19" spans="1:3" ht="16">
+    <row r="19" spans="1:3" ht="16" x14ac:dyDescent="0.35">
       <c r="A19" s="68" t="s">
         <v>96</v>
       </c>
@@ -16250,7 +17207,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="20" spans="1:3" ht="16">
+    <row r="20" spans="1:3" ht="16" x14ac:dyDescent="0.35">
       <c r="A20" s="68" t="s">
         <v>98</v>
       </c>
@@ -16261,7 +17218,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A21" s="68" t="s">
         <v>100</v>
       </c>
@@ -16272,7 +17229,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="16">
+    <row r="22" spans="1:3" ht="16" x14ac:dyDescent="0.35">
       <c r="A22" s="68" t="s">
         <v>102</v>
       </c>
@@ -16283,7 +17240,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="23" spans="1:3" ht="16">
+    <row r="23" spans="1:3" ht="16" x14ac:dyDescent="0.35">
       <c r="A23" s="68" t="s">
         <v>104</v>
       </c>
@@ -16294,7 +17251,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="24" spans="1:3" ht="16">
+    <row r="24" spans="1:3" ht="16" x14ac:dyDescent="0.35">
       <c r="A24" s="68" t="s">
         <v>106</v>
       </c>
@@ -16305,7 +17262,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="25" spans="1:3" ht="16">
+    <row r="25" spans="1:3" ht="16" x14ac:dyDescent="0.35">
       <c r="A25" s="68" t="s">
         <v>108</v>
       </c>
@@ -16316,7 +17273,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="26" spans="1:3" ht="16">
+    <row r="26" spans="1:3" ht="16" x14ac:dyDescent="0.35">
       <c r="A26" s="68" t="s">
         <v>110</v>
       </c>
@@ -16327,7 +17284,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="27" spans="1:3" ht="16">
+    <row r="27" spans="1:3" ht="16" x14ac:dyDescent="0.35">
       <c r="A27" s="68" t="s">
         <v>112</v>
       </c>
@@ -16338,7 +17295,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="28" spans="1:3" ht="16">
+    <row r="28" spans="1:3" ht="16" x14ac:dyDescent="0.35">
       <c r="A28" s="68" t="s">
         <v>114</v>
       </c>
@@ -16349,7 +17306,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="29" spans="1:3" ht="16">
+    <row r="29" spans="1:3" ht="16" x14ac:dyDescent="0.35">
       <c r="A29" s="68" t="s">
         <v>116</v>
       </c>
@@ -16360,7 +17317,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="30" spans="1:3" ht="16">
+    <row r="30" spans="1:3" ht="16" x14ac:dyDescent="0.35">
       <c r="A30" s="68" t="s">
         <v>118</v>
       </c>
@@ -16371,7 +17328,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A31" s="68" t="s">
         <v>120</v>
       </c>
@@ -16382,7 +17339,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A32" s="68" t="s">
         <v>122</v>
       </c>
@@ -16393,7 +17350,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="33" spans="1:3" ht="16">
+    <row r="33" spans="1:3" ht="16" x14ac:dyDescent="0.35">
       <c r="A33" s="68" t="s">
         <v>124</v>
       </c>
@@ -16404,7 +17361,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="34" spans="1:3" ht="16">
+    <row r="34" spans="1:3" ht="16" x14ac:dyDescent="0.35">
       <c r="A34" s="68" t="s">
         <v>126</v>
       </c>
@@ -16415,7 +17372,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="35" spans="1:3" ht="16">
+    <row r="35" spans="1:3" ht="16" x14ac:dyDescent="0.35">
       <c r="A35" s="68" t="s">
         <v>128</v>
       </c>
@@ -16426,7 +17383,7 @@
         <v>415</v>
       </c>
     </row>
-    <row r="36" spans="1:3" ht="16">
+    <row r="36" spans="1:3" ht="16" x14ac:dyDescent="0.35">
       <c r="A36" s="68" t="s">
         <v>130</v>
       </c>
@@ -16446,7 +17403,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB485315-044F-4FB0-A3DD-44B741CAB625}">
   <dimension ref="A1:Q20"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="37.54296875" customWidth="1"/>
     <col min="2" max="2" width="34" bestFit="1" customWidth="1"/>
@@ -16457,7 +17414,7 @@
     <col min="16" max="16" width="11.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="29">
+    <row r="1" spans="1:17" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="19" t="s">
         <v>165</v>
       </c>
@@ -16510,7 +17467,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="2" spans="1:17" ht="50" customHeight="1">
+    <row r="2" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="142" t="s">
         <v>169</v>
       </c>
@@ -16560,7 +17517,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="50" customHeight="1">
+    <row r="3" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="142" t="s">
         <v>170</v>
       </c>
@@ -16611,7 +17568,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="50" customHeight="1">
+    <row r="4" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="142" t="s">
         <v>614</v>
       </c>
@@ -16662,7 +17619,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="50" customHeight="1">
+    <row r="5" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="142" t="s">
         <v>171</v>
       </c>
@@ -16712,7 +17669,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="50" customHeight="1">
+    <row r="6" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="142" t="s">
         <v>615</v>
       </c>
@@ -16763,7 +17720,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="7" spans="1:17" ht="50" customHeight="1">
+    <row r="7" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="142" t="s">
         <v>172</v>
       </c>
@@ -16813,7 +17770,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="50" customHeight="1">
+    <row r="8" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="143" t="s">
         <v>173</v>
       </c>
@@ -16863,7 +17820,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="50" customHeight="1">
+    <row r="9" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="143" t="s">
         <v>616</v>
       </c>
@@ -16914,7 +17871,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="50" customHeight="1">
+    <row r="10" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="144" t="s">
         <v>617</v>
       </c>
@@ -16964,7 +17921,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="11" spans="1:17" ht="50" customHeight="1">
+    <row r="11" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="144" t="s">
         <v>646</v>
       </c>
@@ -17014,7 +17971,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="12" spans="1:17" ht="50" customHeight="1">
+    <row r="12" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="144" t="s">
         <v>174</v>
       </c>
@@ -17064,7 +18021,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="50" customHeight="1">
+    <row r="13" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="144" t="s">
         <v>175</v>
       </c>
@@ -17114,7 +18071,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="50" customHeight="1">
+    <row r="14" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="144" t="s">
         <v>176</v>
       </c>
@@ -17164,7 +18121,7 @@
         <v>583</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="50" customHeight="1">
+    <row r="15" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="144" t="s">
         <v>177</v>
       </c>
@@ -17214,19 +18171,19 @@
         <v>583</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="16">
+    <row r="16" spans="1:17" ht="16" x14ac:dyDescent="0.35">
       <c r="B16" s="58"/>
     </row>
-    <row r="17" spans="2:2" ht="16">
+    <row r="17" spans="2:2" ht="16" x14ac:dyDescent="0.35">
       <c r="B17" s="58"/>
     </row>
-    <row r="18" spans="2:2">
+    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B18" s="57"/>
     </row>
-    <row r="19" spans="2:2">
+    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B19" s="57"/>
     </row>
-    <row r="20" spans="2:2">
+    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
       <c r="B20" s="57"/>
     </row>
   </sheetData>
@@ -17240,7 +18197,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9B0CC1CC-64D0-4115-AE5E-AF959282EFAA}">
   <dimension ref="A1:Y15"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.6328125" style="6" customWidth="1"/>
     <col min="2" max="2" width="15.54296875" customWidth="1"/>
@@ -17253,7 +18210,7 @@
     <col min="11" max="11" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="29">
+    <row r="1" spans="1:25" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="139" t="s">
         <v>178</v>
       </c>
@@ -17321,7 +18278,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="2" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1">
+    <row r="2" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="145" t="s">
         <v>183</v>
       </c>
@@ -17385,7 +18342,7 @@
       </c>
       <c r="Y2" s="1"/>
     </row>
-    <row r="3" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1">
+    <row r="3" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="145" t="s">
         <v>185</v>
       </c>
@@ -17449,7 +18406,7 @@
       </c>
       <c r="Y3" s="1"/>
     </row>
-    <row r="4" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1">
+    <row r="4" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="145" t="s">
         <v>186</v>
       </c>
@@ -17513,7 +18470,7 @@
       </c>
       <c r="Y4" s="1"/>
     </row>
-    <row r="5" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1">
+    <row r="5" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="145" t="s">
         <v>188</v>
       </c>
@@ -17577,7 +18534,7 @@
       </c>
       <c r="Y5" s="1"/>
     </row>
-    <row r="6" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1">
+    <row r="6" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="145" t="s">
         <v>189</v>
       </c>
@@ -17643,7 +18600,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="7" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1">
+    <row r="7" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="145" t="s">
         <v>485</v>
       </c>
@@ -17709,7 +18666,7 @@
         <v>484</v>
       </c>
     </row>
-    <row r="8" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1">
+    <row r="8" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="145"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
@@ -17724,7 +18681,7 @@
       <c r="W8" s="1"/>
       <c r="X8" s="1"/>
     </row>
-    <row r="9" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1">
+    <row r="9" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="145" t="s">
         <v>190</v>
       </c>
@@ -17783,7 +18740,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="10" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1">
+    <row r="10" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="145" t="s">
         <v>191</v>
       </c>
@@ -17842,7 +18799,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="11" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1">
+    <row r="11" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="145" t="s">
         <v>192</v>
       </c>
@@ -17901,7 +18858,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="12" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1">
+    <row r="12" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="145" t="s">
         <v>193</v>
       </c>
@@ -17960,7 +18917,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="13" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1">
+    <row r="13" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="145" t="s">
         <v>194</v>
       </c>
@@ -18017,7 +18974,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="14" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1">
+    <row r="14" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="145" t="s">
         <v>195</v>
       </c>
@@ -18074,7 +19031,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="15" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1">
+    <row r="15" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="145" t="s">
         <v>196</v>
       </c>
@@ -18142,10 +19099,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A45B228-839B-4CA5-9448-9CA1774CB22C}">
-  <dimension ref="A1:Q16"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:Q21"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="15.36328125" customWidth="1"/>
+    <col min="1" max="1" width="16.1796875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.81640625" style="6" customWidth="1"/>
     <col min="3" max="3" width="10.7265625" style="6" customWidth="1"/>
     <col min="4" max="4" width="9" style="6" customWidth="1"/>
@@ -18155,7 +19112,7 @@
     <col min="8" max="17" width="8.7265625" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="29">
+    <row r="1" spans="1:17" ht="29" x14ac:dyDescent="0.35">
       <c r="A1" s="29" t="s">
         <v>60</v>
       </c>
@@ -18208,7 +19165,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="146" t="s">
         <v>153</v>
       </c>
@@ -18261,7 +19218,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="146" t="s">
         <v>157</v>
       </c>
@@ -18314,7 +19271,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="146" t="s">
         <v>159</v>
       </c>
@@ -18367,7 +19324,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="146" t="s">
         <v>160</v>
       </c>
@@ -18420,7 +19377,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="146" t="s">
         <v>162</v>
       </c>
@@ -18473,7 +19430,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="146" t="s">
         <v>146</v>
       </c>
@@ -18526,7 +19483,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="147" t="s">
         <v>612</v>
       </c>
@@ -18534,7 +19491,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="146" t="s">
         <v>608</v>
       </c>
@@ -18587,7 +19544,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="146" t="s">
         <v>609</v>
       </c>
@@ -18640,7 +19597,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="11" spans="1:17">
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="146" t="s">
         <v>625</v>
       </c>
@@ -18690,7 +19647,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:17">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="146" t="s">
         <v>610</v>
       </c>
@@ -18743,7 +19700,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="13" spans="1:17">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="146" t="s">
         <v>611</v>
       </c>
@@ -18796,7 +19753,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="14" spans="1:17">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="146" t="s">
         <v>613</v>
       </c>
@@ -18849,7 +19806,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:17">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="146" t="s">
         <v>163</v>
       </c>
@@ -18902,7 +19859,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="16" spans="1:17">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="146" t="s">
         <v>649</v>
       </c>
@@ -18953,6 +19910,14 @@
       </c>
       <c r="Q16" s="1" t="s">
         <v>55</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.35">
+      <c r="B21" s="146" t="s">
+        <v>650</v>
+      </c>
+      <c r="D21" s="6">
+        <v>92</v>
       </c>
     </row>
   </sheetData>
@@ -18965,7 +19930,7 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04DB295D-7881-4D5C-8380-F1C84A7F5934}">
   <dimension ref="A1:N13"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="11.453125" customWidth="1"/>
     <col min="3" max="3" width="13.81640625" bestFit="1" customWidth="1"/>
@@ -18979,7 +19944,7 @@
     <col min="14" max="14" width="10.7265625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -19023,7 +19988,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="2" spans="1:14">
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
         <v>207</v>
       </c>
@@ -19059,7 +20024,7 @@
       </c>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>210</v>
       </c>
@@ -19095,7 +20060,7 @@
       </c>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="14" t="s">
         <v>212</v>
       </c>
@@ -19131,7 +20096,7 @@
       </c>
       <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>213</v>
       </c>
@@ -19175,7 +20140,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
         <v>642</v>
       </c>
@@ -19219,7 +20184,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>218</v>
       </c>
@@ -19263,7 +20228,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
         <v>220</v>
       </c>
@@ -19307,7 +20272,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
         <v>222</v>
       </c>
@@ -19351,7 +20316,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="101" t="s">
         <v>224</v>
       </c>
@@ -19395,7 +20360,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="98" t="s">
         <v>226</v>
       </c>
@@ -19439,7 +20404,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="98" t="s">
         <v>228</v>
       </c>
@@ -19481,7 +20446,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="98" t="s">
         <v>494</v>
       </c>
@@ -19527,9 +20492,215 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{592FF6A4-5CAD-4DCE-81FD-0858E77FC850}">
+  <dimension ref="B3:H13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="24.36328125" customWidth="1"/>
+    <col min="3" max="3" width="19.6328125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="B3" s="154" t="s">
+        <v>668</v>
+      </c>
+      <c r="C3" s="154" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="4" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="B4" s="155" t="s">
+        <v>652</v>
+      </c>
+      <c r="C4" s="155" t="s">
+        <v>660</v>
+      </c>
+      <c r="E4">
+        <v>145</v>
+      </c>
+      <c r="G4">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="5" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="B5" s="155" t="s">
+        <v>653</v>
+      </c>
+      <c r="C5" s="155" t="s">
+        <v>661</v>
+      </c>
+      <c r="E5">
+        <v>130</v>
+      </c>
+      <c r="F5">
+        <f>E4-E5</f>
+        <v>15</v>
+      </c>
+      <c r="G5">
+        <v>122</v>
+      </c>
+      <c r="H5">
+        <f>G4-G5</f>
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="B6" s="155" t="s">
+        <v>654</v>
+      </c>
+      <c r="C6" s="155" t="s">
+        <v>662</v>
+      </c>
+      <c r="E6">
+        <v>120</v>
+      </c>
+      <c r="F6">
+        <f t="shared" ref="F6:F11" si="0">E5-E6</f>
+        <v>10</v>
+      </c>
+      <c r="G6">
+        <v>110</v>
+      </c>
+      <c r="H6">
+        <f t="shared" ref="H6:H11" si="1">G5-G6</f>
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="B7" s="155" t="s">
+        <v>655</v>
+      </c>
+      <c r="C7" s="155" t="s">
+        <v>663</v>
+      </c>
+      <c r="E7">
+        <v>110</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G7">
+        <v>92</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="8" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="B8" s="155" t="s">
+        <v>656</v>
+      </c>
+      <c r="C8" s="155" t="s">
+        <v>664</v>
+      </c>
+      <c r="E8">
+        <v>95</v>
+      </c>
+      <c r="F8">
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="G8">
+        <v>75</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="1"/>
+        <v>17</v>
+      </c>
+    </row>
+    <row r="9" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="B9" s="155" t="s">
+        <v>657</v>
+      </c>
+      <c r="C9" s="155" t="s">
+        <v>665</v>
+      </c>
+      <c r="E9">
+        <v>75</v>
+      </c>
+      <c r="F9">
+        <f t="shared" si="0"/>
+        <v>20</v>
+      </c>
+      <c r="G9">
+        <v>61</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="1"/>
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="B10" s="155" t="s">
+        <v>658</v>
+      </c>
+      <c r="C10" s="155" t="s">
+        <v>666</v>
+      </c>
+      <c r="E10">
+        <v>65</v>
+      </c>
+      <c r="F10">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G10">
+        <v>48</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="B11" s="155" t="s">
+        <v>659</v>
+      </c>
+      <c r="C11" s="155" t="s">
+        <v>667</v>
+      </c>
+      <c r="E11">
+        <v>55</v>
+      </c>
+      <c r="F11">
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="G11">
+        <v>35</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="1"/>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" spans="2:8" x14ac:dyDescent="0.35">
+      <c r="C13" s="156" t="s">
+        <v>670</v>
+      </c>
+      <c r="D13" s="117"/>
+      <c r="E13" s="117"/>
+      <c r="F13" s="117">
+        <f>AVERAGE(F5:F12)</f>
+        <v>12.857142857142858</v>
+      </c>
+      <c r="G13" s="117"/>
+      <c r="H13" s="117">
+        <f>AVERAGE(H5:H12)</f>
+        <v>14.571428571428571</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E438F573-1137-4940-BD62-685CBD871B42}">
   <dimension ref="A1:N77"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="11.81640625" customWidth="1"/>
     <col min="2" max="2" width="13.1796875" bestFit="1" customWidth="1"/>
@@ -19544,7 +20715,7 @@
     <col min="11" max="11" width="11.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>486</v>
       </c>
@@ -19582,7 +20753,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="3" spans="1:14">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>487</v>
       </c>
@@ -19620,7 +20791,7 @@
         <v>3.1415926535897931</v>
       </c>
     </row>
-    <row r="4" spans="1:14">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>487</v>
       </c>
@@ -19660,7 +20831,7 @@
         <v>3.7105425042399132</v>
       </c>
     </row>
-    <row r="5" spans="1:14">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>487</v>
       </c>
@@ -19698,7 +20869,7 @@
         <v>4.3289662549465655</v>
       </c>
     </row>
-    <row r="6" spans="1:14">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
         <v>488</v>
       </c>
@@ -19736,7 +20907,7 @@
         <v>3.1415926535897931</v>
       </c>
     </row>
-    <row r="7" spans="1:14">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
         <v>488</v>
       </c>
@@ -19776,7 +20947,7 @@
         <v>3.7105425042399132</v>
       </c>
     </row>
-    <row r="8" spans="1:14">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
         <v>488</v>
       </c>
@@ -19814,7 +20985,7 @@
         <v>4.3289662549465655</v>
       </c>
     </row>
-    <row r="9" spans="1:14">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
         <v>488</v>
       </c>
@@ -19854,7 +21025,7 @@
         <v>4.9473900056532178</v>
       </c>
     </row>
-    <row r="10" spans="1:14">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
         <v>488</v>
       </c>
@@ -19892,7 +21063,7 @@
         <v>5.5658137563598702</v>
       </c>
     </row>
-    <row r="11" spans="1:14">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A11" s="6" t="s">
         <v>219</v>
       </c>
@@ -19930,7 +21101,7 @@
         <v>3.1415926535897931</v>
       </c>
     </row>
-    <row r="12" spans="1:14">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A12" s="6" t="s">
         <v>219</v>
       </c>
@@ -19970,7 +21141,7 @@
         <v>3.7105425042399132</v>
       </c>
     </row>
-    <row r="13" spans="1:14">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A13" s="6" t="s">
         <v>219</v>
       </c>
@@ -20008,7 +21179,7 @@
         <v>4.3289662549465655</v>
       </c>
     </row>
-    <row r="14" spans="1:14">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>219</v>
       </c>
@@ -20048,7 +21219,7 @@
         <v>4.9473900056532178</v>
       </c>
     </row>
-    <row r="15" spans="1:14">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>219</v>
       </c>
@@ -20086,7 +21257,7 @@
         <v>5.5658137563598702</v>
       </c>
     </row>
-    <row r="16" spans="1:14">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A16" s="6" t="s">
         <v>221</v>
       </c>
@@ -20126,7 +21297,7 @@
         <v>3.7105425042399132</v>
       </c>
     </row>
-    <row r="17" spans="1:14">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A17" s="6" t="s">
         <v>221</v>
       </c>
@@ -20164,7 +21335,7 @@
         <v>4.3289662549465655</v>
       </c>
     </row>
-    <row r="18" spans="1:14">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A18" s="6" t="s">
         <v>221</v>
       </c>
@@ -20204,7 +21375,7 @@
         <v>4.9473900056532178</v>
       </c>
     </row>
-    <row r="19" spans="1:14">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A19" s="6" t="s">
         <v>221</v>
       </c>
@@ -20242,7 +21413,7 @@
         <v>5.5658137563598702</v>
       </c>
     </row>
-    <row r="20" spans="1:14">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A20" s="6" t="s">
         <v>221</v>
       </c>
@@ -20282,7 +21453,7 @@
         <v>6.8026612577731749</v>
       </c>
     </row>
-    <row r="21" spans="1:14">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A21" s="6" t="s">
         <v>223</v>
       </c>
@@ -20320,7 +21491,7 @@
         <v>4.9473900056532178</v>
       </c>
     </row>
-    <row r="22" spans="1:14">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A22" s="6" t="s">
         <v>223</v>
       </c>
@@ -20358,7 +21529,7 @@
         <v>5.5658137563598702</v>
       </c>
     </row>
-    <row r="23" spans="1:14">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A23" s="6" t="s">
         <v>223</v>
       </c>
@@ -20396,7 +21567,7 @@
         <v>6.8026612577731749</v>
       </c>
     </row>
-    <row r="24" spans="1:14">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A24" s="6" t="s">
         <v>223</v>
       </c>
@@ -20434,7 +21605,7 @@
         <v>3.7105425042399132</v>
       </c>
     </row>
-    <row r="25" spans="1:14">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A25" s="6" t="s">
         <v>223</v>
       </c>
@@ -20472,7 +21643,7 @@
         <v>4.3289662549465655</v>
       </c>
     </row>
-    <row r="26" spans="1:14">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A26" s="6" t="s">
         <v>223</v>
       </c>
@@ -20510,7 +21681,7 @@
         <v>4.9473900056532178</v>
       </c>
     </row>
-    <row r="27" spans="1:14">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A27" s="6" t="s">
         <v>223</v>
       </c>
@@ -20548,7 +21719,7 @@
         <v>5.5658137563598702</v>
       </c>
     </row>
-    <row r="28" spans="1:14">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A28" s="6" t="s">
         <v>223</v>
       </c>
@@ -20586,7 +21757,7 @@
         <v>6.8026612577731749</v>
       </c>
     </row>
-    <row r="29" spans="1:14">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A29" s="6" t="s">
         <v>223</v>
       </c>
@@ -20624,7 +21795,7 @@
         <v>3.7105425042399132</v>
       </c>
     </row>
-    <row r="30" spans="1:14">
+    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A30" s="6" t="s">
         <v>223</v>
       </c>
@@ -20662,7 +21833,7 @@
         <v>4.3289662549465655</v>
       </c>
     </row>
-    <row r="31" spans="1:14">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A31" s="6" t="s">
         <v>223</v>
       </c>
@@ -20700,7 +21871,7 @@
         <v>4.9473900056532178</v>
       </c>
     </row>
-    <row r="32" spans="1:14">
+    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A32" s="6" t="s">
         <v>223</v>
       </c>
@@ -20738,7 +21909,7 @@
         <v>5.5658137563598702</v>
       </c>
     </row>
-    <row r="33" spans="1:14">
+    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A33" s="6" t="s">
         <v>223</v>
       </c>
@@ -20776,7 +21947,7 @@
         <v>6.8026612577731749</v>
       </c>
     </row>
-    <row r="34" spans="1:14">
+    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A34" s="102" t="s">
         <v>225</v>
       </c>
@@ -20814,7 +21985,7 @@
         <v>4.9473900056532178</v>
       </c>
     </row>
-    <row r="35" spans="1:14">
+    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A35" s="102" t="s">
         <v>225</v>
       </c>
@@ -20852,7 +22023,7 @@
         <v>5.5658137563598702</v>
       </c>
     </row>
-    <row r="36" spans="1:14">
+    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A36" s="102" t="s">
         <v>225</v>
       </c>
@@ -20890,7 +22061,7 @@
         <v>6.1842375070665225</v>
       </c>
     </row>
-    <row r="37" spans="1:14">
+    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A37" s="102" t="s">
         <v>225</v>
       </c>
@@ -20928,7 +22099,7 @@
         <v>6.8026612577731749</v>
       </c>
     </row>
-    <row r="38" spans="1:14">
+    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A38" s="102" t="s">
         <v>225</v>
       </c>
@@ -20966,7 +22137,7 @@
         <v>7.4210850084798263</v>
       </c>
     </row>
-    <row r="39" spans="1:14">
+    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A39" s="102" t="s">
         <v>227</v>
       </c>
@@ -21004,7 +22175,7 @@
         <v>6.1842375070665225</v>
       </c>
     </row>
-    <row r="40" spans="1:14">
+    <row r="40" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A40" s="102" t="s">
         <v>227</v>
       </c>
@@ -21042,7 +22213,7 @@
         <v>6.8026612577731749</v>
       </c>
     </row>
-    <row r="41" spans="1:14">
+    <row r="41" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A41" s="102" t="s">
         <v>227</v>
       </c>
@@ -21080,7 +22251,7 @@
         <v>7.4210850084798263</v>
       </c>
     </row>
-    <row r="42" spans="1:14">
+    <row r="42" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A42" s="102" t="s">
         <v>227</v>
       </c>
@@ -21118,7 +22289,7 @@
         <v>6.8026612577731749</v>
       </c>
     </row>
-    <row r="43" spans="1:14">
+    <row r="43" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A43" s="102" t="s">
         <v>227</v>
       </c>
@@ -21156,7 +22327,7 @@
         <v>7.4210850084798263</v>
       </c>
     </row>
-    <row r="44" spans="1:14">
+    <row r="44" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A44" s="102" t="s">
         <v>227</v>
       </c>
@@ -21194,7 +22365,7 @@
         <v>3.7105425042399132</v>
       </c>
     </row>
-    <row r="45" spans="1:14">
+    <row r="45" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A45" s="102" t="s">
         <v>227</v>
       </c>
@@ -21232,7 +22403,7 @@
         <v>4.9473900056532178</v>
       </c>
     </row>
-    <row r="46" spans="1:14">
+    <row r="46" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A46" s="102" t="s">
         <v>227</v>
       </c>
@@ -21270,7 +22441,7 @@
         <v>6.1842375070665225</v>
       </c>
     </row>
-    <row r="47" spans="1:14">
+    <row r="47" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A47" s="102" t="s">
         <v>227</v>
       </c>
@@ -21308,7 +22479,7 @@
         <v>6.8026612577731749</v>
       </c>
     </row>
-    <row r="48" spans="1:14">
+    <row r="48" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A48" s="102" t="s">
         <v>227</v>
       </c>
@@ -21346,7 +22517,7 @@
         <v>7.4210850084798263</v>
       </c>
     </row>
-    <row r="49" spans="1:14">
+    <row r="49" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A49" s="1" t="s">
         <v>229</v>
       </c>
@@ -21384,7 +22555,7 @@
         <v>6.8026612577731749</v>
       </c>
     </row>
-    <row r="50" spans="1:14">
+    <row r="50" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A50" s="1" t="s">
         <v>229</v>
       </c>
@@ -21422,7 +22593,7 @@
         <v>6.1842375070665225</v>
       </c>
     </row>
-    <row r="51" spans="1:14">
+    <row r="51" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A51" s="1" t="s">
         <v>229</v>
       </c>
@@ -21460,7 +22631,7 @@
         <v>7.4210850084798263</v>
       </c>
     </row>
-    <row r="52" spans="1:14">
+    <row r="52" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A52" s="1" t="s">
         <v>538</v>
       </c>
@@ -21496,7 +22667,7 @@
         <v>7.4210850084798263</v>
       </c>
     </row>
-    <row r="53" spans="1:14">
+    <row r="53" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
         <v>538</v>
       </c>
@@ -21532,7 +22703,7 @@
         <v>9.8947800113064357</v>
       </c>
     </row>
-    <row r="58" spans="1:14">
+    <row r="58" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A58" s="61"/>
       <c r="B58" s="61"/>
       <c r="C58" s="61"/>
@@ -21544,7 +22715,7 @@
       <c r="I58" s="61"/>
       <c r="J58" s="61"/>
     </row>
-    <row r="59" spans="1:14">
+    <row r="59" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A59" s="6" t="s">
         <v>488</v>
       </c>
@@ -21565,7 +22736,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="60" spans="1:14">
+    <row r="60" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A60" s="6" t="s">
         <v>487</v>
       </c>
@@ -21586,7 +22757,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="61" spans="1:14">
+    <row r="61" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A61" s="6"/>
       <c r="B61" s="6"/>
       <c r="D61" s="6"/>
@@ -21605,7 +22776,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="62" spans="1:14">
+    <row r="62" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A62" s="6"/>
       <c r="B62" s="6"/>
       <c r="D62" s="6"/>
@@ -21624,7 +22795,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="63" spans="1:14">
+    <row r="63" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A63" s="6"/>
       <c r="B63" s="6"/>
       <c r="D63" s="6"/>
@@ -21643,7 +22814,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="64" spans="1:14">
+    <row r="64" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A64" s="6"/>
       <c r="B64" s="6"/>
       <c r="D64" s="6"/>
@@ -21662,7 +22833,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="65" spans="1:10">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A65" s="6" t="s">
         <v>488</v>
       </c>
@@ -21683,7 +22854,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="66" spans="1:10">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" s="6" t="s">
         <v>487</v>
       </c>
@@ -21704,7 +22875,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="67" spans="1:10">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" s="6"/>
       <c r="B67" s="6"/>
       <c r="D67" s="6"/>
@@ -21723,7 +22894,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="68" spans="1:10">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A68" s="6"/>
       <c r="B68" s="6"/>
       <c r="D68" s="6"/>
@@ -21742,7 +22913,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="69" spans="1:10">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A69" s="6"/>
       <c r="B69" s="6"/>
       <c r="D69" s="6"/>
@@ -21761,7 +22932,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="70" spans="1:10">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A70" s="6"/>
       <c r="B70" s="6"/>
       <c r="D70" s="6"/>
@@ -21780,7 +22951,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="71" spans="1:10">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A71" s="6"/>
       <c r="B71" s="6"/>
       <c r="D71" s="6"/>
@@ -21799,7 +22970,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="72" spans="1:10">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A72" s="6"/>
       <c r="B72" s="6"/>
       <c r="D72" s="6"/>
@@ -21818,7 +22989,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="73" spans="1:10">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A73" s="6"/>
       <c r="B73" s="6"/>
       <c r="D73" s="6"/>
@@ -21837,7 +23008,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="74" spans="1:10">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A74" s="6"/>
       <c r="B74" s="6"/>
       <c r="D74" s="6"/>
@@ -21856,7 +23027,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="75" spans="1:10">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A75" s="6"/>
       <c r="B75" s="6"/>
       <c r="D75" s="6"/>
@@ -21866,7 +23037,7 @@
       <c r="I75" s="6"/>
       <c r="J75" s="6"/>
     </row>
-    <row r="76" spans="1:10">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A76" s="6"/>
       <c r="B76" s="6"/>
       <c r="D76" s="6"/>
@@ -21876,7 +23047,7 @@
       <c r="I76" s="6"/>
       <c r="J76" s="6"/>
     </row>
-    <row r="77" spans="1:10">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A77" s="6"/>
       <c r="B77" s="6"/>
       <c r="D77" s="6"/>
@@ -21901,10 +23072,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB77DDB-B6D9-4CBA-9145-50EF6FDCE517}">
   <dimension ref="A1:AA156"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.1796875" style="3" customWidth="1"/>
     <col min="2" max="2" width="12.90625" style="3" customWidth="1"/>
@@ -21927,7 +23098,7 @@
     <col min="22" max="22" width="24.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="11" customFormat="1" ht="40" customHeight="1">
+    <row r="1" spans="1:27" s="11" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
@@ -22010,7 +23181,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="2" spans="1:27" ht="40" customHeight="1">
+    <row r="2" spans="1:27" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>258</v>
       </c>
@@ -22063,7 +23234,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="3" spans="1:27" ht="40" customHeight="1">
+    <row r="3" spans="1:27" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>261</v>
       </c>
@@ -22116,7 +23287,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="40" customHeight="1">
+    <row r="4" spans="1:27" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="3" t="s">
         <v>262</v>
       </c>
@@ -22163,7 +23334,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="5" spans="1:27" ht="40" customHeight="1">
+    <row r="5" spans="1:27" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>263</v>
       </c>
@@ -22210,7 +23381,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="6" spans="1:27" ht="40" customHeight="1">
+    <row r="6" spans="1:27" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="3" t="s">
         <v>264</v>
       </c>
@@ -22257,7 +23428,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="7" spans="1:27" ht="40" customHeight="1">
+    <row r="7" spans="1:27" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="3" t="s">
         <v>265</v>
       </c>
@@ -22304,7 +23475,7 @@
         <v>390</v>
       </c>
     </row>
-    <row r="8" spans="1:27" ht="40" customHeight="1">
+    <row r="8" spans="1:27" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="3" t="s">
         <v>266</v>
       </c>
@@ -22351,7 +23522,7 @@
         <v>570</v>
       </c>
     </row>
-    <row r="9" spans="1:27" ht="40" customHeight="1">
+    <row r="9" spans="1:27" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
         <v>267</v>
       </c>
@@ -22398,28 +23569,53 @@
         <v>670</v>
       </c>
     </row>
-    <row r="10" spans="1:27" ht="40" customHeight="1">
+    <row r="10" spans="1:27" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A10" s="3" t="s">
-        <v>268</v>
+        <v>651</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="H10" s="97" t="s">
-        <v>472</v>
-      </c>
-      <c r="N10" s="97" t="s">
-        <v>472</v>
+        <v>303</v>
+      </c>
+      <c r="C10" s="1">
+        <f>D9+0.01</f>
+        <v>350.01</v>
+      </c>
+      <c r="D10" s="1">
+        <v>500</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F10" s="1">
+        <v>7</v>
+      </c>
+      <c r="G10" s="1">
+        <v>230</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="I10" s="1">
+        <v>65</v>
+      </c>
+      <c r="K10" s="1">
+        <v>119.5</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O10" s="6">
+        <v>28</v>
       </c>
       <c r="Q10" s="52"/>
-    </row>
-    <row r="11" spans="1:27" ht="40" customHeight="1">
+      <c r="R10" s="6">
+        <v>1650</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="3" t="s">
         <v>269</v>
       </c>
@@ -22467,7 +23663,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="12" spans="1:27" ht="40" customHeight="1">
+    <row r="12" spans="1:27" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="3" t="s">
         <v>271</v>
       </c>
@@ -22515,7 +23711,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="13" spans="1:27" s="109" customFormat="1" ht="40" customHeight="1">
+    <row r="13" spans="1:27" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="106" t="s">
         <v>268</v>
       </c>
@@ -22549,7 +23745,7 @@
       <c r="S13" s="110"/>
       <c r="U13" s="111"/>
     </row>
-    <row r="14" spans="1:27" s="57" customFormat="1" ht="40" customHeight="1">
+    <row r="14" spans="1:27" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="3" t="s">
         <v>272</v>
       </c>
@@ -22605,7 +23801,7 @@
       <c r="S14" s="1"/>
       <c r="U14" s="113"/>
     </row>
-    <row r="15" spans="1:27" s="57" customFormat="1" ht="40" customHeight="1">
+    <row r="15" spans="1:27" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
         <v>274</v>
       </c>
@@ -22662,7 +23858,7 @@
       <c r="S15" s="1"/>
       <c r="U15" s="113"/>
     </row>
-    <row r="16" spans="1:27" s="57" customFormat="1" ht="40" customHeight="1">
+    <row r="16" spans="1:27" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>508</v>
       </c>
@@ -22717,7 +23913,7 @@
       <c r="S16" s="1"/>
       <c r="U16" s="113"/>
     </row>
-    <row r="17" spans="1:21" s="57" customFormat="1" ht="40" customHeight="1">
+    <row r="17" spans="1:21" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A17" s="57" t="s">
         <v>275</v>
       </c>
@@ -22767,7 +23963,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="18" spans="1:21" s="57" customFormat="1" ht="40" customHeight="1">
+    <row r="18" spans="1:21" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A18" s="57" t="s">
         <v>276</v>
       </c>
@@ -22817,7 +24013,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="19" spans="1:21" s="57" customFormat="1" ht="40" customHeight="1">
+    <row r="19" spans="1:21" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>277</v>
       </c>
@@ -22870,7 +24066,7 @@
       <c r="S19" s="1"/>
       <c r="U19" s="113"/>
     </row>
-    <row r="20" spans="1:21" s="57" customFormat="1" ht="40" customHeight="1">
+    <row r="20" spans="1:21" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>278</v>
       </c>
@@ -22923,7 +24119,7 @@
       <c r="S20" s="1"/>
       <c r="U20" s="113"/>
     </row>
-    <row r="21" spans="1:21" s="57" customFormat="1" ht="40" customHeight="1">
+    <row r="21" spans="1:21" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>279</v>
       </c>
@@ -22976,7 +24172,7 @@
       <c r="S21" s="1"/>
       <c r="U21" s="113"/>
     </row>
-    <row r="22" spans="1:21" s="57" customFormat="1" ht="40" customHeight="1">
+    <row r="22" spans="1:21" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>280</v>
       </c>
@@ -23031,7 +24227,7 @@
       <c r="S22" s="1"/>
       <c r="U22" s="113"/>
     </row>
-    <row r="23" spans="1:21" s="57" customFormat="1" ht="40" customHeight="1">
+    <row r="23" spans="1:21" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>281</v>
       </c>
@@ -23086,7 +24282,7 @@
       <c r="S23" s="1"/>
       <c r="U23" s="113"/>
     </row>
-    <row r="24" spans="1:21" s="57" customFormat="1" ht="40" customHeight="1">
+    <row r="24" spans="1:21" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>282</v>
       </c>
@@ -23139,7 +24335,7 @@
       <c r="S24" s="1"/>
       <c r="U24" s="113"/>
     </row>
-    <row r="25" spans="1:21" s="57" customFormat="1" ht="40" customHeight="1">
+    <row r="25" spans="1:21" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>283</v>
       </c>
@@ -23192,7 +24388,7 @@
       <c r="S25" s="1"/>
       <c r="U25" s="113"/>
     </row>
-    <row r="26" spans="1:21" s="57" customFormat="1" ht="40" customHeight="1">
+    <row r="26" spans="1:21" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>284</v>
       </c>
@@ -23247,7 +24443,7 @@
       <c r="S26" s="1"/>
       <c r="U26" s="113"/>
     </row>
-    <row r="27" spans="1:21" s="57" customFormat="1" ht="40" customHeight="1">
+    <row r="27" spans="1:21" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>285</v>
       </c>
@@ -23302,7 +24498,7 @@
       <c r="S27" s="1"/>
       <c r="U27" s="113"/>
     </row>
-    <row r="28" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1">
+    <row r="28" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A28" s="106" t="s">
         <v>268</v>
       </c>
@@ -23336,7 +24532,7 @@
       <c r="S28" s="110"/>
       <c r="U28" s="111"/>
     </row>
-    <row r="29" spans="1:21" s="24" customFormat="1" ht="40" customHeight="1">
+    <row r="29" spans="1:21" s="24" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A29" s="78" t="s">
         <v>286</v>
       </c>
@@ -23388,7 +24584,7 @@
       </c>
       <c r="U29" s="81"/>
     </row>
-    <row r="30" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1">
+    <row r="30" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A30" s="106" t="s">
         <v>268</v>
       </c>
@@ -23418,7 +24614,7 @@
       <c r="S30" s="110"/>
       <c r="U30" s="111"/>
     </row>
-    <row r="31" spans="1:21" ht="40" customHeight="1">
+    <row r="31" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>289</v>
       </c>
@@ -23465,7 +24661,7 @@
         <v>290</v>
       </c>
     </row>
-    <row r="32" spans="1:21" ht="40" customHeight="1">
+    <row r="32" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>291</v>
       </c>
@@ -23512,7 +24708,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="33" spans="1:21" ht="40" customHeight="1">
+    <row r="33" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>293</v>
       </c>
@@ -23559,7 +24755,7 @@
         <v>294</v>
       </c>
     </row>
-    <row r="34" spans="1:21" ht="40" customHeight="1">
+    <row r="34" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>295</v>
       </c>
@@ -23606,7 +24802,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="35" spans="1:21" ht="40" customHeight="1">
+    <row r="35" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>297</v>
       </c>
@@ -23653,7 +24849,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="36" spans="1:21" ht="40" customHeight="1">
+    <row r="36" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>299</v>
       </c>
@@ -23700,7 +24896,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="37" spans="1:21" ht="40" customHeight="1">
+    <row r="37" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>301</v>
       </c>
@@ -23747,7 +24943,7 @@
         <v>302</v>
       </c>
     </row>
-    <row r="38" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1">
+    <row r="38" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="106" t="s">
         <v>268</v>
       </c>
@@ -23781,7 +24977,7 @@
       <c r="S38" s="110"/>
       <c r="U38" s="111"/>
     </row>
-    <row r="39" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1">
+    <row r="39" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>516</v>
       </c>
@@ -23829,7 +25025,7 @@
       </c>
       <c r="U39" s="116"/>
     </row>
-    <row r="40" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1">
+    <row r="40" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>515</v>
       </c>
@@ -23878,7 +25074,7 @@
       </c>
       <c r="U40" s="116"/>
     </row>
-    <row r="41" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1">
+    <row r="41" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>517</v>
       </c>
@@ -23927,7 +25123,7 @@
       </c>
       <c r="U41" s="116"/>
     </row>
-    <row r="42" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1">
+    <row r="42" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>518</v>
       </c>
@@ -23976,7 +25172,7 @@
       </c>
       <c r="U42" s="116"/>
     </row>
-    <row r="43" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1">
+    <row r="43" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>304</v>
       </c>
@@ -24019,7 +25215,7 @@
       </c>
       <c r="U43" s="116"/>
     </row>
-    <row r="44" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1">
+    <row r="44" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>305</v>
       </c>
@@ -24062,7 +25258,7 @@
       </c>
       <c r="U44" s="116"/>
     </row>
-    <row r="45" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1">
+    <row r="45" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>306</v>
       </c>
@@ -24105,7 +25301,7 @@
       </c>
       <c r="U45" s="116"/>
     </row>
-    <row r="46" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1">
+    <row r="46" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>307</v>
       </c>
@@ -24148,7 +25344,7 @@
       </c>
       <c r="U46" s="116"/>
     </row>
-    <row r="47" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1">
+    <row r="47" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>308</v>
       </c>
@@ -24191,7 +25387,7 @@
       </c>
       <c r="U47" s="116"/>
     </row>
-    <row r="48" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1">
+    <row r="48" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A48" s="106" t="s">
         <v>268</v>
       </c>
@@ -24225,7 +25421,7 @@
       <c r="S48" s="110"/>
       <c r="U48" s="111"/>
     </row>
-    <row r="49" spans="1:21" ht="40" customHeight="1">
+    <row r="49" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>309</v>
       </c>
@@ -24266,7 +25462,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="50" spans="1:21" ht="40" customHeight="1">
+    <row r="50" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>310</v>
       </c>
@@ -24307,7 +25503,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="51" spans="1:21" s="3" customFormat="1" ht="40" customHeight="1">
+    <row r="51" spans="1:21" s="3" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>311</v>
       </c>
@@ -24353,7 +25549,7 @@
       <c r="S51" s="1"/>
       <c r="U51" s="82"/>
     </row>
-    <row r="52" spans="1:21" ht="40" customHeight="1">
+    <row r="52" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
         <v>312</v>
       </c>
@@ -24394,7 +25590,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="53" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1">
+    <row r="53" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A53" s="106" t="s">
         <v>268</v>
       </c>
@@ -24428,9 +25624,9 @@
       <c r="S53" s="110"/>
       <c r="U53" s="111"/>
     </row>
-    <row r="54" spans="1:21" ht="40" customHeight="1">
+    <row r="54" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="str">
-        <f>Chaindrive!A40</f>
+        <f>Chaindrive!A41</f>
         <v>JM200</v>
       </c>
       <c r="B54" s="3" t="s">
@@ -24440,14 +25636,14 @@
         <v>0</v>
       </c>
       <c r="D54" s="23">
-        <f>Chaindrive!J40</f>
+        <f>Chaindrive!J41</f>
         <v>110.90909090909092</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F54" s="22">
-        <f>Chaindrive!L40</f>
+        <f>Chaindrive!L41</f>
         <v>6.1311475409836058</v>
       </c>
       <c r="G54" s="1">
@@ -24478,7 +25674,7 @@
         <v>314</v>
       </c>
     </row>
-    <row r="55" spans="1:21" ht="40" customHeight="1">
+    <row r="55" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>315</v>
       </c>
@@ -24489,14 +25685,14 @@
         <v>15.01</v>
       </c>
       <c r="D55" s="23">
-        <f>Chaindrive!J41</f>
+        <f>Chaindrive!J42</f>
         <v>344.44444444444446</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F55" s="1">
-        <f>Chaindrive!L41</f>
+        <f>Chaindrive!L42</f>
         <v>6.12</v>
       </c>
       <c r="G55" s="1">
@@ -24527,7 +25723,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="56" spans="1:21" ht="40" customHeight="1">
+    <row r="56" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>317</v>
       </c>
@@ -24538,14 +25734,14 @@
         <v>62.01</v>
       </c>
       <c r="D56" s="1">
-        <f>Chaindrive!J42</f>
+        <f>Chaindrive!J43</f>
         <v>608</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F56" s="1">
-        <f>Chaindrive!L42</f>
+        <f>Chaindrive!L43</f>
         <v>3.4375</v>
       </c>
       <c r="G56" s="1">
@@ -24573,7 +25769,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="57" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1">
+    <row r="57" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A57" s="106" t="s">
         <v>268</v>
       </c>
@@ -24607,9 +25803,9 @@
       <c r="S57" s="110"/>
       <c r="U57" s="111"/>
     </row>
-    <row r="58" spans="1:21" ht="40" customHeight="1">
+    <row r="58" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="str">
-        <f>Chaindrive!A51</f>
+        <f>Chaindrive!A52</f>
         <v>F100c</v>
       </c>
       <c r="B58" s="3" t="s">
@@ -24619,14 +25815,14 @@
         <v>0</v>
       </c>
       <c r="D58" s="1">
-        <f>Chaindrive!J51</f>
+        <f>Chaindrive!J52</f>
         <v>300</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F58" s="1">
-        <f>Chaindrive!L44</f>
+        <f>Chaindrive!L45</f>
         <v>3.4375000000000004</v>
       </c>
       <c r="G58" s="1">
@@ -24651,9 +25847,9 @@
         <v>22</v>
       </c>
     </row>
-    <row r="59" spans="1:21" ht="40" customHeight="1">
+    <row r="59" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="str">
-        <f>Chaindrive!A52</f>
+        <f>Chaindrive!A53</f>
         <v>F160c</v>
       </c>
       <c r="B59" s="3" t="s">
@@ -24663,14 +25859,14 @@
         <v>1</v>
       </c>
       <c r="D59" s="1">
-        <f>Chaindrive!J52</f>
+        <f>Chaindrive!J53</f>
         <v>608</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F59" s="1">
-        <f>Chaindrive!L45</f>
+        <f>Chaindrive!L46</f>
         <v>3.208333333333333</v>
       </c>
       <c r="G59" s="1">
@@ -24695,7 +25891,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="60" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1">
+    <row r="60" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A60" s="106"/>
       <c r="B60" s="106"/>
       <c r="C60" s="106"/>
@@ -24717,7 +25913,7 @@
       <c r="S60" s="110"/>
       <c r="U60" s="111"/>
     </row>
-    <row r="61" spans="1:21" ht="40" customHeight="1">
+    <row r="61" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="str">
         <f>Chaindrive!A4</f>
         <v>Ranger 70 1ph 19-57 1/2"</v>
@@ -24775,7 +25971,7 @@
         <v>300.41000000000003</v>
       </c>
     </row>
-    <row r="62" spans="1:21" ht="40" customHeight="1">
+    <row r="62" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="str">
         <f>Chaindrive!A5</f>
         <v>Ranger 70 1ph 15-57 1/2"</v>
@@ -24833,7 +26029,7 @@
         <v>300.41000000000003</v>
       </c>
     </row>
-    <row r="63" spans="1:21" ht="40" customHeight="1">
+    <row r="63" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="str">
         <f>Chaindrive!A7</f>
         <v>Ranger 90 1ph 19-57 1/2"</v>
@@ -24894,7 +26090,7 @@
         <v>300.41000000000003</v>
       </c>
     </row>
-    <row r="64" spans="1:21" ht="40" customHeight="1">
+    <row r="64" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="str">
         <f>Chaindrive!A8</f>
         <v>Ranger 90 1ph 15-57 1/2"</v>
@@ -24952,7 +26148,7 @@
         <v>300.41000000000003</v>
       </c>
     </row>
-    <row r="65" spans="1:22" s="109" customFormat="1" ht="40" customHeight="1">
+    <row r="65" spans="1:23" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="106" t="s">
         <v>268</v>
       </c>
@@ -24986,7 +26182,7 @@
       <c r="S65" s="110"/>
       <c r="U65" s="152"/>
     </row>
-    <row r="66" spans="1:22" ht="40" customHeight="1">
+    <row r="66" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="str">
         <f>Chaindrive!A10</f>
         <v>Ranger 90 3ph 19-57 1/2"</v>
@@ -25046,7 +26242,7 @@
         <v>179.04</v>
       </c>
     </row>
-    <row r="67" spans="1:22" ht="40" customHeight="1">
+    <row r="67" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="str">
         <f>Chaindrive!A11</f>
         <v>Ranger 90 3ph 15-57 1/2"</v>
@@ -25107,10 +26303,11 @@
         <v>179.04</v>
       </c>
       <c r="V67" s="83"/>
-    </row>
-    <row r="68" spans="1:22" ht="40" customHeight="1">
+      <c r="W67" s="83"/>
+    </row>
+    <row r="68" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="str">
-        <f>Chaindrive!A13</f>
+        <f>Chaindrive!A14</f>
         <v>Ranger150 3ph 18-57 5/8"</v>
       </c>
       <c r="B68" t="s">
@@ -25121,14 +26318,14 @@
         <v>270.01</v>
       </c>
       <c r="D68" s="23">
-        <f>Chaindrive!J13</f>
+        <f>Chaindrive!J14</f>
         <v>471.83333333333331</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F68" s="2">
-        <f>Chaindrive!L13</f>
+        <f>Chaindrive!L14</f>
         <v>14.842105263157896</v>
       </c>
       <c r="G68" s="1">
@@ -25153,7 +26350,7 @@
         <v>22</v>
       </c>
       <c r="O68" s="6">
-        <f>Chaindrive!O13</f>
+        <f>Chaindrive!O14</f>
         <v>12.631578947368421</v>
       </c>
       <c r="P68" s="1">
@@ -25170,9 +26367,9 @@
       </c>
       <c r="V68" s="83"/>
     </row>
-    <row r="69" spans="1:22" ht="40" customHeight="1">
+    <row r="69" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="str">
-        <f>Chaindrive!A14</f>
+        <f>Chaindrive!A15</f>
         <v>Ranger150 3ph 12-57 5/8"</v>
       </c>
       <c r="B69" t="s">
@@ -25213,7 +26410,7 @@
         <v>22</v>
       </c>
       <c r="O69" s="6">
-        <f>Chaindrive!O14</f>
+        <f>Chaindrive!O15</f>
         <v>8.4210526315789469</v>
       </c>
       <c r="P69" s="1">
@@ -25229,9 +26426,9 @@
         <v>472.24</v>
       </c>
     </row>
-    <row r="70" spans="1:22" ht="40" customHeight="1">
+    <row r="70" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="str">
-        <f>Chaindrive!A16</f>
+        <f>Chaindrive!A17</f>
         <v>Ranger220 3ph 15-57 3/4"</v>
       </c>
       <c r="B70" t="s">
@@ -25241,14 +26438,14 @@
         <v>713.01</v>
       </c>
       <c r="D70" s="23">
-        <f>Chaindrive!J16</f>
+        <f>Chaindrive!J17</f>
         <v>836</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F70" s="2">
-        <f>Chaindrive!L16</f>
+        <f>Chaindrive!L17</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="G70" s="1">
@@ -25273,7 +26470,7 @@
         <v>22</v>
       </c>
       <c r="O70" s="6">
-        <f>Chaindrive!O16</f>
+        <f>Chaindrive!O17</f>
         <v>10.526315789473685</v>
       </c>
       <c r="P70" s="1">
@@ -25286,7 +26483,7 @@
         <v>498.07</v>
       </c>
     </row>
-    <row r="71" spans="1:22" s="109" customFormat="1" ht="40" customHeight="1">
+    <row r="71" spans="1:23" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="106" t="s">
         <v>268</v>
       </c>
@@ -25320,9 +26517,9 @@
       <c r="S71" s="110"/>
       <c r="U71" s="111"/>
     </row>
-    <row r="72" spans="1:22" ht="40" customHeight="1">
+    <row r="72" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="str">
-        <f>Chaindrive!A19</f>
+        <f>Chaindrive!A20</f>
         <v>Ranger 90 Fi 1ph 15-57 1/2"</v>
       </c>
       <c r="B72" t="s">
@@ -25332,14 +26529,14 @@
         <v>0</v>
       </c>
       <c r="D72" s="23">
-        <f>Chaindrive!J19</f>
+        <f>Chaindrive!J20</f>
         <v>342</v>
       </c>
       <c r="E72" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F72" s="22">
-        <f>Chaindrive!L19</f>
+        <f>Chaindrive!L20</f>
         <v>21.05263157894737</v>
       </c>
       <c r="G72" s="1">
@@ -25364,7 +26561,7 @@
         <v>22</v>
       </c>
       <c r="O72" s="6">
-        <f>Chaindrive!O19</f>
+        <f>Chaindrive!O20</f>
         <v>5.2631578947368425</v>
       </c>
       <c r="P72" s="1">
@@ -25374,9 +26571,9 @@
         <v>850</v>
       </c>
     </row>
-    <row r="73" spans="1:22" ht="40" customHeight="1">
+    <row r="73" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="str">
-        <f>Chaindrive!A20</f>
+        <f>Chaindrive!A21</f>
         <v>Ranger 90 Fi 3ph 15-57 1/2"</v>
       </c>
       <c r="B73" t="s">
@@ -25387,14 +26584,14 @@
         <v>342.01</v>
       </c>
       <c r="D73" s="23">
-        <f>Chaindrive!J20</f>
+        <f>Chaindrive!J21</f>
         <v>342</v>
       </c>
       <c r="E73" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F73" s="22">
-        <f>Chaindrive!L20</f>
+        <f>Chaindrive!L21</f>
         <v>21.05263157894737</v>
       </c>
       <c r="G73" s="1">
@@ -25419,7 +26616,7 @@
         <v>22</v>
       </c>
       <c r="O73" s="6">
-        <f>Chaindrive!O20</f>
+        <f>Chaindrive!O21</f>
         <v>5.2631578947368425</v>
       </c>
       <c r="P73" s="1">
@@ -25429,9 +26626,9 @@
         <v>850</v>
       </c>
     </row>
-    <row r="74" spans="1:22" ht="40" customHeight="1">
+    <row r="74" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="str">
-        <f>Chaindrive!A21</f>
+        <f>Chaindrive!A22</f>
         <v>Ranger140 Fi 1ph 18-57 5/8"</v>
       </c>
       <c r="B74" t="s">
@@ -25442,14 +26639,14 @@
         <v>342.01</v>
       </c>
       <c r="D74" s="23">
-        <f>Chaindrive!J21</f>
+        <f>Chaindrive!J22</f>
         <v>475</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F74" s="22">
-        <f>Chaindrive!L21</f>
+        <f>Chaindrive!L22</f>
         <v>25.263157894736842</v>
       </c>
       <c r="G74" s="1">
@@ -25474,7 +26671,7 @@
         <v>22</v>
       </c>
       <c r="O74" s="6">
-        <f>Chaindrive!O21</f>
+        <f>Chaindrive!O22</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="P74" s="1">
@@ -25484,9 +26681,9 @@
         <v>850</v>
       </c>
     </row>
-    <row r="75" spans="1:22" ht="40" customHeight="1">
+    <row r="75" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="str">
-        <f>Chaindrive!A22</f>
+        <f>Chaindrive!A23</f>
         <v>Ranger140 Fi 3ph 18-57 5/8"</v>
       </c>
       <c r="B75" t="s">
@@ -25497,14 +26694,14 @@
         <v>475.01</v>
       </c>
       <c r="D75" s="23">
-        <f>Chaindrive!J22</f>
+        <f>Chaindrive!J23</f>
         <v>475</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F75" s="22">
-        <f>Chaindrive!L22</f>
+        <f>Chaindrive!L23</f>
         <v>25.263157894736842</v>
       </c>
       <c r="G75" s="1">
@@ -25529,7 +26726,7 @@
         <v>22</v>
       </c>
       <c r="O75" s="6">
-        <f>Chaindrive!O22</f>
+        <f>Chaindrive!O23</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="P75" s="1">
@@ -25539,9 +26736,9 @@
         <v>850</v>
       </c>
     </row>
-    <row r="76" spans="1:22" ht="40" customHeight="1">
+    <row r="76" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="str">
-        <f>Chaindrive!A23</f>
+        <f>Chaindrive!A24</f>
         <v>Ranger140 fi 1ph 12-57 5/8"</v>
       </c>
       <c r="B76" t="s">
@@ -25552,14 +26749,14 @@
         <v>475.01</v>
       </c>
       <c r="D76" s="23">
-        <f>Chaindrive!J23</f>
+        <f>Chaindrive!J24</f>
         <v>712.5</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F76" s="22">
-        <f>Chaindrive!L23</f>
+        <f>Chaindrive!L24</f>
         <v>16.842105263157894</v>
       </c>
       <c r="G76" s="1">
@@ -25584,7 +26781,7 @@
         <v>22</v>
       </c>
       <c r="O76" s="6">
-        <f>Chaindrive!O23</f>
+        <f>Chaindrive!O24</f>
         <v>4.2105263157894735</v>
       </c>
       <c r="P76" s="1">
@@ -25594,9 +26791,9 @@
         <v>850</v>
       </c>
     </row>
-    <row r="77" spans="1:22" ht="40" customHeight="1">
+    <row r="77" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="str">
-        <f>Chaindrive!A24</f>
+        <f>Chaindrive!A25</f>
         <v>Ranger140 fi 3ph 12-57 5/8"</v>
       </c>
       <c r="B77" t="s">
@@ -25607,14 +26804,14 @@
         <v>712.51</v>
       </c>
       <c r="D77" s="23">
-        <f>Chaindrive!J24</f>
+        <f>Chaindrive!J25</f>
         <v>712.5</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F77" s="22">
-        <f>Chaindrive!L24</f>
+        <f>Chaindrive!L25</f>
         <v>16.842105263157894</v>
       </c>
       <c r="G77" s="1">
@@ -25639,7 +26836,7 @@
         <v>22</v>
       </c>
       <c r="O77" s="6">
-        <f>Chaindrive!O24</f>
+        <f>Chaindrive!O25</f>
         <v>4.2105263157894735</v>
       </c>
       <c r="P77" s="1">
@@ -25649,7 +26846,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="78" spans="1:22" s="109" customFormat="1" ht="40" customHeight="1">
+    <row r="78" spans="1:23" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="106"/>
       <c r="C78" s="107"/>
       <c r="D78" s="115"/>
@@ -25670,9 +26867,9 @@
       <c r="S78" s="110"/>
       <c r="U78" s="111"/>
     </row>
-    <row r="79" spans="1:22" ht="40" customHeight="1">
+    <row r="79" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A79" s="3" t="str">
-        <f>Chaindrive!A27</f>
+        <f>Chaindrive!A28</f>
         <v>KE 40.24  15-57 3/4"</v>
       </c>
       <c r="B79" t="s">
@@ -25682,18 +26879,18 @@
         <v>600.01</v>
       </c>
       <c r="D79" s="23">
-        <f>Chaindrive!J27</f>
+        <f>Chaindrive!J28</f>
         <v>1520</v>
       </c>
       <c r="E79" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F79" s="2">
-        <f>Chaindrive!L27</f>
+        <f>Chaindrive!L28</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="G79" s="1">
-        <f>Chaindrive!M27</f>
+        <f>Chaindrive!M28</f>
         <v>415</v>
       </c>
       <c r="H79" s="1" t="s">
@@ -25706,7 +26903,7 @@
         <v>260</v>
       </c>
       <c r="L79" s="1">
-        <f>Chaindrive!D27</f>
+        <f>Chaindrive!D28</f>
         <v>40</v>
       </c>
       <c r="M79" s="1" t="s">
@@ -25716,7 +26913,7 @@
         <v>22</v>
       </c>
       <c r="O79" s="6">
-        <f>Chaindrive!O27</f>
+        <f>Chaindrive!O28</f>
         <v>10.526315789473685</v>
       </c>
       <c r="P79" s="1">
@@ -25726,9 +26923,9 @@
         <v>850</v>
       </c>
     </row>
-    <row r="80" spans="1:22" ht="40" customHeight="1">
+    <row r="80" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="str">
-        <f>Chaindrive!A28</f>
+        <f>Chaindrive!A29</f>
         <v>KE 40.24  15-57 1"</v>
       </c>
       <c r="B80" t="s">
@@ -25738,18 +26935,18 @@
         <v>900.01</v>
       </c>
       <c r="D80" s="23">
-        <f>Chaindrive!J28</f>
+        <f>Chaindrive!J29</f>
         <v>1520</v>
       </c>
       <c r="E80" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F80" s="2">
-        <f>Chaindrive!L28</f>
+        <f>Chaindrive!L29</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="G80" s="1">
-        <f>Chaindrive!M28</f>
+        <f>Chaindrive!M29</f>
         <v>415</v>
       </c>
       <c r="H80" s="1" t="s">
@@ -25763,7 +26960,7 @@
         <v>260</v>
       </c>
       <c r="L80" s="1">
-        <f>Chaindrive!D28</f>
+        <f>Chaindrive!D29</f>
         <v>40</v>
       </c>
       <c r="M80" s="1" t="s">
@@ -25773,7 +26970,7 @@
         <v>22</v>
       </c>
       <c r="O80" s="6">
-        <f>Chaindrive!O28</f>
+        <f>Chaindrive!O29</f>
         <v>10.526315789473685</v>
       </c>
       <c r="P80" s="1">
@@ -25783,9 +26980,9 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="81" spans="1:22" ht="40" customHeight="1">
+    <row r="81" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="str">
-        <f>Chaindrive!A29</f>
+        <f>Chaindrive!A30</f>
         <v>KE 60.24   15-57 1"</v>
       </c>
       <c r="B81" t="s">
@@ -25795,18 +26992,18 @@
         <v>1200.01</v>
       </c>
       <c r="D81" s="23">
-        <f>Chaindrive!J29</f>
+        <f>Chaindrive!J30</f>
         <v>2280</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F81" s="2">
-        <f>Chaindrive!L29</f>
+        <f>Chaindrive!L30</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="G81" s="1">
-        <f>Chaindrive!M29</f>
+        <f>Chaindrive!M30</f>
         <v>415</v>
       </c>
       <c r="H81" s="1" t="s">
@@ -25819,7 +27016,7 @@
         <v>260</v>
       </c>
       <c r="L81" s="1">
-        <f>Chaindrive!D29</f>
+        <f>Chaindrive!D30</f>
         <v>55</v>
       </c>
       <c r="M81" s="1" t="s">
@@ -25829,7 +27026,7 @@
         <v>22</v>
       </c>
       <c r="O81" s="6">
-        <f>Chaindrive!O29</f>
+        <f>Chaindrive!O30</f>
         <v>15.789473684210527</v>
       </c>
       <c r="P81" s="1">
@@ -25839,9 +27036,9 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="82" spans="1:22" ht="40" customHeight="1">
+    <row r="82" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="str">
-        <f>Chaindrive!A30</f>
+        <f>Chaindrive!A31</f>
         <v>KE 80.24   15-57 1"</v>
       </c>
       <c r="B82" t="s">
@@ -25851,18 +27048,18 @@
         <v>1800.01</v>
       </c>
       <c r="D82" s="23">
-        <f>Chaindrive!J30</f>
+        <f>Chaindrive!J31</f>
         <v>3040</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F82" s="2">
-        <f>Chaindrive!L30</f>
+        <f>Chaindrive!L31</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="G82" s="1">
-        <f>Chaindrive!M30</f>
+        <f>Chaindrive!M31</f>
         <v>415</v>
       </c>
       <c r="H82" s="1" t="s">
@@ -25875,7 +27072,7 @@
         <v>260</v>
       </c>
       <c r="L82" s="1">
-        <f>Chaindrive!D30</f>
+        <f>Chaindrive!D31</f>
         <v>55</v>
       </c>
       <c r="M82" s="1" t="s">
@@ -25885,7 +27082,7 @@
         <v>22</v>
       </c>
       <c r="O82" s="6">
-        <f>Chaindrive!O30</f>
+        <f>Chaindrive!O31</f>
         <v>15.789473684210527</v>
       </c>
       <c r="P82" s="1">
@@ -25895,9 +27092,9 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="83" spans="1:22" ht="40" customHeight="1">
+    <row r="83" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="str">
-        <f>Chaindrive!A31</f>
+        <f>Chaindrive!A32</f>
         <v>KE 80.24   15-57 1 1/4"</v>
       </c>
       <c r="B83" t="s">
@@ -25907,18 +27104,18 @@
         <v>1800.01</v>
       </c>
       <c r="D83" s="23">
-        <f>Chaindrive!J31</f>
+        <f>Chaindrive!J32</f>
         <v>3040</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F83" s="2">
-        <f>Chaindrive!L31</f>
+        <f>Chaindrive!L32</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="G83" s="1">
-        <f>Chaindrive!M31</f>
+        <f>Chaindrive!M32</f>
         <v>415</v>
       </c>
       <c r="H83" s="1" t="s">
@@ -25931,7 +27128,7 @@
         <v>260</v>
       </c>
       <c r="L83" s="1">
-        <f>Chaindrive!D31</f>
+        <f>Chaindrive!D32</f>
         <v>55</v>
       </c>
       <c r="M83" s="1" t="s">
@@ -25941,7 +27138,7 @@
         <v>22</v>
       </c>
       <c r="O83" s="6">
-        <f>Chaindrive!O31</f>
+        <f>Chaindrive!O32</f>
         <v>15.789473684210527</v>
       </c>
       <c r="P83" s="1">
@@ -25951,7 +27148,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="84" spans="1:22" s="109" customFormat="1" ht="40" customHeight="1">
+    <row r="84" spans="1:22" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="106" t="s">
         <v>268</v>
       </c>
@@ -25985,9 +27182,9 @@
       <c r="S84" s="110"/>
       <c r="U84" s="111"/>
     </row>
-    <row r="85" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1">
+    <row r="85" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A85" s="3" t="str">
-        <f>Chaindrive!A34</f>
+        <f>Chaindrive!A35</f>
         <v>KE 40.40 Fi 15-57 3/4"</v>
       </c>
       <c r="B85" s="57" t="s">
@@ -25997,14 +27194,14 @@
         <v>0</v>
       </c>
       <c r="D85" s="23">
-        <f>Chaindrive!J34</f>
+        <f>Chaindrive!J35</f>
         <v>1140</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F85" s="2">
-        <f>Chaindrive!L34</f>
+        <f>Chaindrive!L35</f>
         <v>10.526315789473685</v>
       </c>
       <c r="G85" s="1">
@@ -26021,7 +27218,7 @@
         <v>260</v>
       </c>
       <c r="L85" s="1">
-        <f>Chaindrive!R34</f>
+        <f>Chaindrive!R35</f>
         <v>40</v>
       </c>
       <c r="M85" s="1" t="s">
@@ -26031,7 +27228,7 @@
         <v>22</v>
       </c>
       <c r="O85" s="1">
-        <f>Chaindrive!O34</f>
+        <f>Chaindrive!O35</f>
         <v>10.526315789473685</v>
       </c>
       <c r="P85" s="1">
@@ -26044,9 +27241,9 @@
       <c r="S85" s="1"/>
       <c r="U85" s="113"/>
     </row>
-    <row r="86" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1">
+    <row r="86" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="3" t="str">
-        <f>Chaindrive!A36</f>
+        <f>Chaindrive!A37</f>
         <v>KE 50.80 Fi 15-57 1"</v>
       </c>
       <c r="B86" s="57" t="s">
@@ -26057,14 +27254,14 @@
         <v>1140.01</v>
       </c>
       <c r="D86" s="23">
-        <f>Chaindrive!J36</f>
+        <f>Chaindrive!J37</f>
         <v>1900</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F86" s="2">
-        <f>Chaindrive!L36</f>
+        <f>Chaindrive!L37</f>
         <v>21.05263157894737</v>
       </c>
       <c r="G86" s="1">
@@ -26081,7 +27278,7 @@
         <v>260</v>
       </c>
       <c r="L86" s="1">
-        <f>Chaindrive!R36</f>
+        <f>Chaindrive!R37</f>
         <v>55</v>
       </c>
       <c r="M86" s="1" t="s">
@@ -26091,7 +27288,7 @@
         <v>22</v>
       </c>
       <c r="O86" s="1">
-        <f>Chaindrive!O36</f>
+        <f>Chaindrive!O37</f>
         <v>15.789473684210527</v>
       </c>
       <c r="P86" s="1">
@@ -26104,9 +27301,9 @@
       <c r="S86" s="1"/>
       <c r="U86" s="113"/>
     </row>
-    <row r="87" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1">
+    <row r="87" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="str">
-        <f>Chaindrive!A37</f>
+        <f>Chaindrive!A38</f>
         <v>KE 80.40 Fi 15-57 1"</v>
       </c>
       <c r="B87" s="57" t="s">
@@ -26117,14 +27314,14 @@
         <v>1900.01</v>
       </c>
       <c r="D87" s="23">
-        <f>Chaindrive!J37</f>
+        <f>Chaindrive!J38</f>
         <v>3040</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F87" s="2">
-        <f>Chaindrive!L37</f>
+        <f>Chaindrive!L38</f>
         <v>10.526315789473685</v>
       </c>
       <c r="G87" s="1">
@@ -26141,7 +27338,7 @@
         <v>260</v>
       </c>
       <c r="L87" s="1">
-        <f>Chaindrive!R37</f>
+        <f>Chaindrive!R38</f>
         <v>55</v>
       </c>
       <c r="M87" s="1" t="s">
@@ -26151,7 +27348,7 @@
         <v>22</v>
       </c>
       <c r="O87" s="1">
-        <f>Chaindrive!O37</f>
+        <f>Chaindrive!O38</f>
         <v>15.789473684210527</v>
       </c>
       <c r="P87" s="1">
@@ -26164,9 +27361,9 @@
       <c r="S87" s="1"/>
       <c r="U87" s="113"/>
     </row>
-    <row r="88" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1">
+    <row r="88" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="str">
-        <f>Chaindrive!A34</f>
+        <f>Chaindrive!A35</f>
         <v>KE 40.40 Fi 15-57 3/4"</v>
       </c>
       <c r="B88" s="57" t="s">
@@ -26176,14 +27373,14 @@
         <v>0</v>
       </c>
       <c r="D88" s="23">
-        <f>Chaindrive!J34</f>
+        <f>Chaindrive!J35</f>
         <v>1140</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F88" s="2">
-        <f>Chaindrive!L34</f>
+        <f>Chaindrive!L35</f>
         <v>10.526315789473685</v>
       </c>
       <c r="G88" s="1">
@@ -26200,7 +27397,7 @@
         <v>260</v>
       </c>
       <c r="L88" s="1">
-        <f>Chaindrive!R34</f>
+        <f>Chaindrive!R35</f>
         <v>40</v>
       </c>
       <c r="M88" s="1" t="s">
@@ -26210,7 +27407,7 @@
         <v>22</v>
       </c>
       <c r="O88" s="1">
-        <f>Chaindrive!O34</f>
+        <f>Chaindrive!O35</f>
         <v>10.526315789473685</v>
       </c>
       <c r="P88" s="1">
@@ -26223,9 +27420,9 @@
       <c r="S88" s="1"/>
       <c r="U88" s="113"/>
     </row>
-    <row r="89" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1">
+    <row r="89" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="str">
-        <f>Chaindrive!A35</f>
+        <f>Chaindrive!A36</f>
         <v>KE 40.40 Fi 15-57 1"</v>
       </c>
       <c r="B89" s="57" t="s">
@@ -26236,14 +27433,14 @@
         <v>1140.01</v>
       </c>
       <c r="D89" s="23">
-        <f>Chaindrive!J35</f>
+        <f>Chaindrive!J36</f>
         <v>1140</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F89" s="2">
-        <f>Chaindrive!L35</f>
+        <f>Chaindrive!L36</f>
         <v>10.526315789473685</v>
       </c>
       <c r="G89" s="1">
@@ -26260,7 +27457,7 @@
         <v>260</v>
       </c>
       <c r="L89" s="1">
-        <f>Chaindrive!R35</f>
+        <f>Chaindrive!R36</f>
         <v>40</v>
       </c>
       <c r="M89" s="1" t="s">
@@ -26270,7 +27467,7 @@
         <v>22</v>
       </c>
       <c r="O89" s="1">
-        <f>Chaindrive!O35</f>
+        <f>Chaindrive!O36</f>
         <v>10.526315789473685</v>
       </c>
       <c r="P89" s="1">
@@ -26283,9 +27480,9 @@
       <c r="S89" s="1"/>
       <c r="U89" s="113"/>
     </row>
-    <row r="90" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1">
+    <row r="90" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="3" t="str">
-        <f>Chaindrive!A36</f>
+        <f>Chaindrive!A37</f>
         <v>KE 50.80 Fi 15-57 1"</v>
       </c>
       <c r="B90" s="57" t="s">
@@ -26296,14 +27493,14 @@
         <v>1140.01</v>
       </c>
       <c r="D90" s="23">
-        <f>Chaindrive!J36</f>
+        <f>Chaindrive!J37</f>
         <v>1900</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F90" s="2">
-        <f>Chaindrive!L36</f>
+        <f>Chaindrive!L37</f>
         <v>21.05263157894737</v>
       </c>
       <c r="G90" s="1">
@@ -26320,7 +27517,7 @@
         <v>260</v>
       </c>
       <c r="L90" s="1">
-        <f>Chaindrive!R36</f>
+        <f>Chaindrive!R37</f>
         <v>55</v>
       </c>
       <c r="M90" s="1" t="s">
@@ -26330,7 +27527,7 @@
         <v>22</v>
       </c>
       <c r="O90" s="1">
-        <f>Chaindrive!O36</f>
+        <f>Chaindrive!O37</f>
         <v>15.789473684210527</v>
       </c>
       <c r="P90" s="1">
@@ -26343,7 +27540,7 @@
       <c r="S90" s="1"/>
       <c r="U90" s="113"/>
     </row>
-    <row r="91" spans="1:22" s="109" customFormat="1" ht="40" customHeight="1">
+    <row r="91" spans="1:22" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="106"/>
       <c r="B91" s="106"/>
       <c r="C91" s="106"/>
@@ -26365,7 +27562,7 @@
       <c r="S91" s="110"/>
       <c r="U91" s="111"/>
     </row>
-    <row r="92" spans="1:22" ht="40" customHeight="1">
+    <row r="92" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="3" t="s">
         <v>268</v>
       </c>
@@ -26391,7 +27588,7 @@
       <c r="U92" s="113"/>
       <c r="V92" s="57"/>
     </row>
-    <row r="93" spans="1:22" ht="40" customHeight="1">
+    <row r="93" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
         <v>578</v>
       </c>
@@ -26452,7 +27649,7 @@
       </c>
       <c r="V93" s="57"/>
     </row>
-    <row r="94" spans="1:22" ht="40" customHeight="1">
+    <row r="94" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A94" s="57" t="s">
         <v>324</v>
       </c>
@@ -26514,7 +27711,7 @@
       </c>
       <c r="V94" s="57"/>
     </row>
-    <row r="95" spans="1:22" ht="40" customHeight="1">
+    <row r="95" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="57" t="s">
         <v>326</v>
       </c>
@@ -26576,7 +27773,7 @@
       </c>
       <c r="V95" s="57"/>
     </row>
-    <row r="96" spans="1:22" ht="40" customHeight="1">
+    <row r="96" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="57" t="s">
         <v>328</v>
       </c>
@@ -26635,7 +27832,7 @@
       </c>
       <c r="V96" s="57"/>
     </row>
-    <row r="97" spans="1:22" ht="40" customHeight="1">
+    <row r="97" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="57" t="s">
         <v>330</v>
       </c>
@@ -26694,7 +27891,7 @@
       </c>
       <c r="V97" s="57"/>
     </row>
-    <row r="98" spans="1:22" ht="40" customHeight="1">
+    <row r="98" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="57" t="s">
         <v>332</v>
       </c>
@@ -26753,7 +27950,7 @@
       </c>
       <c r="V98" s="57"/>
     </row>
-    <row r="99" spans="1:22" ht="40" customHeight="1">
+    <row r="99" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="57" t="s">
         <v>333</v>
       </c>
@@ -26812,7 +28009,7 @@
       </c>
       <c r="V99" s="57"/>
     </row>
-    <row r="100" spans="1:22" ht="40" customHeight="1">
+    <row r="100" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="57" t="s">
         <v>335</v>
       </c>
@@ -26871,7 +28068,7 @@
       </c>
       <c r="V100" s="57"/>
     </row>
-    <row r="101" spans="1:22" ht="40" customHeight="1">
+    <row r="101" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="57" t="s">
         <v>337</v>
       </c>
@@ -26930,7 +28127,7 @@
       </c>
       <c r="V101" s="57"/>
     </row>
-    <row r="102" spans="1:22" ht="40" customHeight="1">
+    <row r="102" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="57" t="s">
         <v>339</v>
       </c>
@@ -26989,7 +28186,7 @@
       </c>
       <c r="V102" s="57"/>
     </row>
-    <row r="103" spans="1:22" ht="40" customHeight="1">
+    <row r="103" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="57" t="s">
         <v>341</v>
       </c>
@@ -27048,7 +28245,7 @@
       </c>
       <c r="V103" s="57"/>
     </row>
-    <row r="104" spans="1:22" ht="40" customHeight="1">
+    <row r="104" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="57" t="s">
         <v>343</v>
       </c>
@@ -27107,7 +28304,7 @@
       <c r="U104" s="133"/>
       <c r="V104" s="57"/>
     </row>
-    <row r="105" spans="1:22" ht="40" customHeight="1">
+    <row r="105" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="130" t="s">
         <v>344</v>
       </c>
@@ -27164,7 +28361,7 @@
       <c r="U105" s="133"/>
       <c r="V105" s="57"/>
     </row>
-    <row r="106" spans="1:22" ht="40" customHeight="1">
+    <row r="106" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="130" t="s">
         <v>345</v>
       </c>
@@ -27221,7 +28418,7 @@
       <c r="U106" s="133"/>
       <c r="V106" s="57"/>
     </row>
-    <row r="107" spans="1:22" ht="40" customHeight="1">
+    <row r="107" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="130" t="s">
         <v>346</v>
       </c>
@@ -27278,7 +28475,7 @@
       <c r="U107" s="133"/>
       <c r="V107" s="57"/>
     </row>
-    <row r="108" spans="1:22" ht="40" customHeight="1">
+    <row r="108" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="130" t="s">
         <v>347</v>
       </c>
@@ -27335,7 +28532,7 @@
       <c r="U108" s="133"/>
       <c r="V108" s="57"/>
     </row>
-    <row r="109" spans="1:22" ht="40" customHeight="1">
+    <row r="109" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="130" t="s">
         <v>503</v>
       </c>
@@ -27392,7 +28589,7 @@
       <c r="U109" s="133"/>
       <c r="V109" s="57"/>
     </row>
-    <row r="110" spans="1:22" s="109" customFormat="1" ht="40" customHeight="1">
+    <row r="110" spans="1:22" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="106" t="s">
         <v>268</v>
       </c>
@@ -27426,7 +28623,7 @@
       <c r="S110" s="110"/>
       <c r="U110" s="111"/>
     </row>
-    <row r="111" spans="1:22" ht="40" customHeight="1">
+    <row r="111" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="3" t="s">
         <v>348</v>
       </c>
@@ -27482,7 +28679,7 @@
         <v>418</v>
       </c>
     </row>
-    <row r="112" spans="1:22" ht="40" customHeight="1">
+    <row r="112" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="3" t="s">
         <v>350</v>
       </c>
@@ -27539,7 +28736,7 @@
         <v>474</v>
       </c>
     </row>
-    <row r="113" spans="1:21" ht="40" customHeight="1">
+    <row r="113" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="3" t="s">
         <v>352</v>
       </c>
@@ -27596,7 +28793,7 @@
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="114" spans="1:21" ht="40" customHeight="1">
+    <row r="114" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="3" t="s">
         <v>354</v>
       </c>
@@ -27651,7 +28848,7 @@
       </c>
       <c r="U114" s="92"/>
     </row>
-    <row r="115" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1">
+    <row r="115" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="106" t="s">
         <v>268</v>
       </c>
@@ -27685,7 +28882,7 @@
       <c r="S115" s="110"/>
       <c r="U115" s="111"/>
     </row>
-    <row r="116" spans="1:21" ht="40" customHeight="1">
+    <row r="116" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" t="s">
         <v>356</v>
       </c>
@@ -27735,7 +28932,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="117" spans="1:21" ht="40" customHeight="1">
+    <row r="117" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
         <v>358</v>
       </c>
@@ -27792,7 +28989,7 @@
         <v>1481.78</v>
       </c>
     </row>
-    <row r="118" spans="1:21" ht="40" customHeight="1">
+    <row r="118" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A118" s="3" t="s">
         <v>360</v>
       </c>
@@ -27843,7 +29040,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="119" spans="1:21" ht="40" customHeight="1">
+    <row r="119" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="3" t="s">
         <v>361</v>
       </c>
@@ -27894,7 +29091,7 @@
         <v>750</v>
       </c>
     </row>
-    <row r="120" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1">
+    <row r="120" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="106" t="s">
         <v>268</v>
       </c>
@@ -27928,7 +29125,7 @@
       <c r="S120" s="110"/>
       <c r="U120" s="111"/>
     </row>
-    <row r="121" spans="1:21" ht="40" customHeight="1">
+    <row r="121" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" t="s">
         <v>506</v>
       </c>
@@ -27978,7 +29175,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="122" spans="1:21" ht="40" customHeight="1">
+    <row r="122" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
         <v>501</v>
       </c>
@@ -28028,7 +29225,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="123" spans="1:21" ht="40" customHeight="1">
+    <row r="123" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
         <v>358</v>
       </c>
@@ -28079,7 +29276,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="124" spans="1:21" ht="40" customHeight="1">
+    <row r="124" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
         <v>362</v>
       </c>
@@ -28130,7 +29327,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="125" spans="1:21" ht="40" customHeight="1">
+    <row r="125" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" t="s">
         <v>363</v>
       </c>
@@ -28181,7 +29378,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="126" spans="1:21" ht="40" customHeight="1">
+    <row r="126" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="3" t="s">
         <v>360</v>
       </c>
@@ -28232,7 +29429,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="127" spans="1:21" ht="40" customHeight="1">
+    <row r="127" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="3" t="s">
         <v>364</v>
       </c>
@@ -28283,7 +29480,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="128" spans="1:21" ht="40" customHeight="1">
+    <row r="128" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="3" t="s">
         <v>361</v>
       </c>
@@ -28334,7 +29531,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="129" spans="1:21" ht="40" customHeight="1">
+    <row r="129" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="3" t="s">
         <v>365</v>
       </c>
@@ -28385,7 +29582,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="130" spans="1:21" ht="40" customHeight="1">
+    <row r="130" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="3" t="s">
         <v>366</v>
       </c>
@@ -28436,7 +29633,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="131" spans="1:21" ht="40" customHeight="1">
+    <row r="131" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
         <v>367</v>
       </c>
@@ -28487,7 +29684,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="132" spans="1:21" ht="40" customHeight="1">
+    <row r="132" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="3" t="s">
         <v>500</v>
       </c>
@@ -28538,7 +29735,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="133" spans="1:21" ht="40" customHeight="1">
+    <row r="133" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="3" t="s">
         <v>509</v>
       </c>
@@ -28589,7 +29786,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="134" spans="1:21" ht="40" customHeight="1">
+    <row r="134" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="3" t="s">
         <v>510</v>
       </c>
@@ -28640,7 +29837,7 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="135" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1">
+    <row r="135" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="106" t="s">
         <v>268</v>
       </c>
@@ -28674,7 +29871,7 @@
       <c r="S135" s="110"/>
       <c r="U135" s="111"/>
     </row>
-    <row r="136" spans="1:21" ht="40" customHeight="1">
+    <row r="136" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="3" t="s">
         <v>368</v>
       </c>
@@ -28730,7 +29927,7 @@
         <v>624.37</v>
       </c>
     </row>
-    <row r="137" spans="1:21" ht="40" customHeight="1">
+    <row r="137" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="3" t="s">
         <v>504</v>
       </c>
@@ -28781,7 +29978,7 @@
         <v>850</v>
       </c>
     </row>
-    <row r="138" spans="1:21" ht="40" customHeight="1">
+    <row r="138" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="3" t="s">
         <v>371</v>
       </c>
@@ -28832,7 +30029,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="139" spans="1:21" ht="40" customHeight="1">
+    <row r="139" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="3" t="s">
         <v>372</v>
       </c>
@@ -28883,7 +30080,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="140" spans="1:21" ht="40" customHeight="1">
+    <row r="140" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="3" t="s">
         <v>373</v>
       </c>
@@ -28934,7 +30131,7 @@
         <v>1100</v>
       </c>
     </row>
-    <row r="141" spans="1:21" ht="40" customHeight="1">
+    <row r="141" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="3" t="s">
         <v>374</v>
       </c>
@@ -28985,7 +30182,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="142" spans="1:21" ht="40" customHeight="1">
+    <row r="142" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="3" t="s">
         <v>375</v>
       </c>
@@ -29036,7 +30233,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="143" spans="1:21" ht="40" customHeight="1">
+    <row r="143" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="3" t="s">
         <v>376</v>
       </c>
@@ -29087,7 +30284,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="144" spans="1:21" ht="40" customHeight="1">
+    <row r="144" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="3" t="s">
         <v>505</v>
       </c>
@@ -29138,7 +30335,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="40" customHeight="1">
+    <row r="145" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="3" t="s">
         <v>268</v>
       </c>
@@ -29149,17 +30346,17 @@
         <v>268</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="40" customHeight="1"/>
-    <row r="147" spans="1:4" ht="40" customHeight="1"/>
-    <row r="148" spans="1:4" ht="40" customHeight="1"/>
-    <row r="149" spans="1:4" ht="40" customHeight="1"/>
-    <row r="150" spans="1:4" ht="40" customHeight="1"/>
-    <row r="151" spans="1:4" ht="40" customHeight="1"/>
-    <row r="152" spans="1:4" ht="40" customHeight="1"/>
-    <row r="153" spans="1:4" ht="40" customHeight="1"/>
-    <row r="154" spans="1:4" ht="40" customHeight="1"/>
-    <row r="155" spans="1:4" ht="40" customHeight="1"/>
-    <row r="156" spans="1:4" ht="40" customHeight="1"/>
+    <row r="146" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="147" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="148" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="149" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="150" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="151" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="152" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="153" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="154" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="155" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="156" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <autoFilter ref="A1:S145" xr:uid="{5FB77DDB-B6D9-4CBA-9145-50EF6FDCE517}"/>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -29170,10 +30367,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B1E18F3-2DFA-476D-A4F8-F41E93C21C92}">
-  <dimension ref="A1:X59"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:X60"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="25.7265625" customWidth="1"/>
     <col min="3" max="4" width="14.81640625" style="6" customWidth="1"/>
@@ -29197,7 +30394,7 @@
     <col min="23" max="23" width="9.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="11" customFormat="1" ht="30" customHeight="1">
+    <row r="1" spans="1:21" s="11" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="11" t="s">
         <v>377</v>
       </c>
@@ -29259,13 +30456,13 @@
         <v>257</v>
       </c>
     </row>
-    <row r="2" spans="1:21">
+    <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:21">
+    <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:21">
+    <row r="4" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A4" s="56" t="s">
         <v>391</v>
       </c>
@@ -29328,7 +30525,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="5" spans="1:21">
+    <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" s="56" t="s">
         <v>393</v>
       </c>
@@ -29389,7 +30586,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="6" spans="1:21">
+    <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" s="62"/>
       <c r="B6" s="62"/>
       <c r="C6" s="61"/>
@@ -29412,7 +30609,7 @@
       <c r="R6" s="61"/>
       <c r="S6" s="61"/>
     </row>
-    <row r="7" spans="1:21">
+    <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" s="56" t="s">
         <v>394</v>
       </c>
@@ -29459,7 +30656,7 @@
         <v>40</v>
       </c>
       <c r="O7" s="71">
-        <f t="shared" ref="O7:O16" si="0">N7/G7</f>
+        <f t="shared" ref="O7:O17" si="0">N7/G7</f>
         <v>13.333333333333334</v>
       </c>
       <c r="P7" s="6">
@@ -29475,7 +30672,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="8" spans="1:21">
+    <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" s="56" t="s">
         <v>395</v>
       </c>
@@ -29538,7 +30735,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="9" spans="1:21">
+    <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" s="62"/>
       <c r="B9" s="62"/>
       <c r="C9" s="61"/>
@@ -29561,7 +30758,7 @@
       <c r="R9" s="61"/>
       <c r="S9" s="61"/>
     </row>
-    <row r="10" spans="1:21">
+    <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" s="56" t="s">
         <v>396</v>
       </c>
@@ -29624,7 +30821,7 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="11" spans="1:21">
+    <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" s="56" t="s">
         <v>397</v>
       </c>
@@ -29687,338 +30884,338 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="12" spans="1:21">
-      <c r="A12" s="62"/>
-      <c r="B12" s="62"/>
-      <c r="C12" s="61"/>
-      <c r="D12" s="61"/>
-      <c r="E12" s="61"/>
-      <c r="F12" s="61"/>
-      <c r="G12" s="76"/>
-      <c r="H12" s="61"/>
-      <c r="I12" s="61"/>
-      <c r="J12" s="61"/>
-      <c r="K12" s="61"/>
-      <c r="L12" s="76"/>
-      <c r="M12" s="61"/>
-      <c r="N12" s="61"/>
-      <c r="O12" s="61"/>
-      <c r="P12" s="61" t="s">
+    <row r="12" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A12" s="56" t="s">
+        <v>671</v>
+      </c>
+      <c r="B12" s="56" t="s">
+        <v>319</v>
+      </c>
+      <c r="C12" s="71">
+        <v>12</v>
+      </c>
+      <c r="D12" s="71">
+        <v>25.4</v>
+      </c>
+      <c r="E12" s="71">
+        <v>57</v>
+      </c>
+      <c r="F12" s="71">
+        <v>30</v>
+      </c>
+      <c r="G12" s="75">
+        <f t="shared" ref="G12" si="7">E12/C12</f>
+        <v>4.75</v>
+      </c>
+      <c r="H12" s="71" t="s">
+        <v>398</v>
+      </c>
+      <c r="I12" s="71">
+        <v>90</v>
+      </c>
+      <c r="J12" s="73">
+        <f t="shared" ref="J12" si="8">I12*G12</f>
+        <v>427.5</v>
+      </c>
+      <c r="K12" s="71">
+        <v>32</v>
+      </c>
+      <c r="L12" s="75">
+        <f t="shared" ref="L12" si="9">K12/G12</f>
+        <v>6.7368421052631575</v>
+      </c>
+      <c r="M12" s="71">
+        <v>415</v>
+      </c>
+      <c r="N12" s="71">
+        <v>40</v>
+      </c>
+      <c r="O12" s="71">
+        <f t="shared" ref="O12" si="10">N12/G12</f>
+        <v>8.4210526315789469</v>
+      </c>
+      <c r="P12" s="6">
+        <v>73.599999999999994</v>
+      </c>
+      <c r="Q12" s="6">
+        <v>288</v>
+      </c>
+      <c r="R12" s="1">
+        <v>25.4</v>
+      </c>
+      <c r="S12" s="6">
+        <v>22400</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A13" s="62"/>
+      <c r="B13" s="62"/>
+      <c r="C13" s="61"/>
+      <c r="D13" s="61"/>
+      <c r="E13" s="61"/>
+      <c r="F13" s="61"/>
+      <c r="G13" s="76"/>
+      <c r="H13" s="61"/>
+      <c r="I13" s="61"/>
+      <c r="J13" s="61"/>
+      <c r="K13" s="61"/>
+      <c r="L13" s="76"/>
+      <c r="M13" s="61"/>
+      <c r="N13" s="61"/>
+      <c r="O13" s="61"/>
+      <c r="P13" s="61" t="s">
         <v>268</v>
       </c>
-      <c r="Q12" s="61"/>
-      <c r="R12" s="61"/>
-      <c r="S12" s="61"/>
-    </row>
-    <row r="13" spans="1:21">
-      <c r="A13" s="56" t="s">
+      <c r="Q13" s="61"/>
+      <c r="R13" s="61"/>
+      <c r="S13" s="61"/>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A14" s="56" t="s">
         <v>544</v>
       </c>
-      <c r="B13" s="56" t="s">
+      <c r="B14" s="56" t="s">
         <v>319</v>
       </c>
-      <c r="C13" s="71">
+      <c r="C14" s="71">
         <v>18</v>
       </c>
-      <c r="D13" s="71">
+      <c r="D14" s="71">
         <v>25.4</v>
       </c>
-      <c r="E13" s="71">
+      <c r="E14" s="71">
         <v>57</v>
       </c>
-      <c r="F13" s="71">
+      <c r="F14" s="71">
         <v>30</v>
       </c>
-      <c r="G13" s="75">
-        <f t="shared" ref="G13" si="7">E13/C13</f>
+      <c r="G14" s="75">
+        <f t="shared" ref="G14" si="11">E14/C14</f>
         <v>3.1666666666666665</v>
       </c>
-      <c r="H13" s="71" t="s">
+      <c r="H14" s="71" t="s">
         <v>398</v>
       </c>
-      <c r="I13" s="71">
+      <c r="I14" s="71">
         <v>149</v>
       </c>
-      <c r="J13" s="73">
-        <f>I13*G13</f>
+      <c r="J14" s="73">
+        <f>I14*G14</f>
         <v>471.83333333333331</v>
       </c>
-      <c r="K13" s="71">
+      <c r="K14" s="71">
         <v>47</v>
       </c>
-      <c r="L13" s="75">
-        <f t="shared" ref="L13" si="8">K13/G13</f>
+      <c r="L14" s="75">
+        <f t="shared" ref="L14" si="12">K14/G14</f>
         <v>14.842105263157896</v>
       </c>
-      <c r="M13" s="71">
+      <c r="M14" s="71">
         <v>415</v>
       </c>
-      <c r="N13" s="71">
+      <c r="N14" s="71">
         <v>40</v>
       </c>
-      <c r="O13" s="71">
-        <f t="shared" ref="O13" si="9">N13/G13</f>
+      <c r="O14" s="71">
+        <f t="shared" ref="O14" si="13">N14/G14</f>
         <v>12.631578947368421</v>
       </c>
-      <c r="P13" s="6">
+      <c r="P14" s="6">
         <v>91.42</v>
       </c>
-      <c r="Q13" s="6">
+      <c r="Q14" s="6">
         <v>288</v>
       </c>
-      <c r="R13" s="1">
+      <c r="R14" s="1">
         <v>25.4</v>
       </c>
-      <c r="S13" s="6">
+      <c r="S14" s="6">
         <v>22400</v>
       </c>
     </row>
-    <row r="14" spans="1:21">
-      <c r="A14" s="117" t="s">
+    <row r="15" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A15" s="117" t="s">
         <v>399</v>
       </c>
-      <c r="B14" s="117" t="s">
+      <c r="B15" s="117" t="s">
         <v>319</v>
       </c>
-      <c r="C14" s="118">
+      <c r="C15" s="118">
         <v>12</v>
       </c>
-      <c r="D14" s="118">
+      <c r="D15" s="118">
         <v>25.4</v>
       </c>
-      <c r="E14" s="118">
+      <c r="E15" s="118">
         <v>57</v>
       </c>
-      <c r="F14" s="118">
+      <c r="F15" s="118">
         <v>40</v>
       </c>
-      <c r="G14" s="119">
-        <f t="shared" ref="G14" si="10">E14/C14</f>
+      <c r="G15" s="119">
+        <f t="shared" ref="G15" si="14">E15/C15</f>
         <v>4.75</v>
       </c>
-      <c r="H14" s="118" t="s">
+      <c r="H15" s="118" t="s">
         <v>398</v>
       </c>
-      <c r="I14" s="118">
+      <c r="I15" s="118">
         <v>150</v>
       </c>
-      <c r="J14" s="120">
-        <f>I14*G14</f>
+      <c r="J15" s="120">
+        <f>I15*G15</f>
         <v>712.5</v>
       </c>
-      <c r="K14" s="118">
+      <c r="K15" s="118">
         <v>48</v>
       </c>
-      <c r="L14" s="119">
-        <f>K14/G14</f>
+      <c r="L15" s="119">
+        <f>K15/G15</f>
         <v>10.105263157894736</v>
       </c>
-      <c r="M14" s="118">
+      <c r="M15" s="118">
         <v>415</v>
       </c>
-      <c r="N14" s="118">
+      <c r="N15" s="118">
         <v>40</v>
       </c>
-      <c r="O14" s="118">
+      <c r="O15" s="118">
         <f t="shared" si="0"/>
         <v>8.4210526315789469</v>
       </c>
-      <c r="P14" s="6">
+      <c r="P15" s="6">
         <v>73.599999999999994</v>
       </c>
-      <c r="Q14" s="6">
+      <c r="Q15" s="6">
         <v>288</v>
       </c>
-      <c r="R14" s="1">
+      <c r="R15" s="1">
         <v>25.4</v>
       </c>
-      <c r="S14" s="6">
+      <c r="S15" s="6">
         <v>22400</v>
       </c>
     </row>
-    <row r="15" spans="1:21">
-      <c r="A15" s="62"/>
-      <c r="B15" s="62"/>
-      <c r="C15" s="61"/>
-      <c r="D15" s="61"/>
-      <c r="E15" s="61"/>
-      <c r="F15" s="61"/>
-      <c r="G15" s="76"/>
-      <c r="H15" s="61"/>
-      <c r="I15" s="61"/>
-      <c r="J15" s="61"/>
-      <c r="K15" s="61"/>
-      <c r="L15" s="76"/>
-      <c r="M15" s="61"/>
-      <c r="N15" s="61"/>
-      <c r="O15" s="61"/>
-      <c r="P15" s="61" t="s">
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A16" s="62"/>
+      <c r="B16" s="62"/>
+      <c r="C16" s="61"/>
+      <c r="D16" s="61"/>
+      <c r="E16" s="61"/>
+      <c r="F16" s="61"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="61"/>
+      <c r="I16" s="61"/>
+      <c r="J16" s="61"/>
+      <c r="K16" s="61"/>
+      <c r="L16" s="76"/>
+      <c r="M16" s="61"/>
+      <c r="N16" s="61"/>
+      <c r="O16" s="61"/>
+      <c r="P16" s="61" t="s">
         <v>268</v>
       </c>
-      <c r="Q15" s="61"/>
-      <c r="R15" s="61"/>
-      <c r="S15" s="61"/>
-    </row>
-    <row r="16" spans="1:21">
-      <c r="A16" s="56" t="s">
+      <c r="Q16" s="61"/>
+      <c r="R16" s="61"/>
+      <c r="S16" s="61"/>
+    </row>
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A17" s="56" t="s">
         <v>537</v>
       </c>
-      <c r="B16" s="56" t="s">
+      <c r="B17" s="56" t="s">
         <v>319</v>
       </c>
-      <c r="C16" s="71">
+      <c r="C17" s="71">
         <v>15</v>
       </c>
-      <c r="D16" s="71">
+      <c r="D17" s="71">
         <v>30</v>
       </c>
-      <c r="E16" s="71">
+      <c r="E17" s="71">
         <v>57</v>
       </c>
-      <c r="F16" s="71">
+      <c r="F17" s="71">
         <v>30</v>
       </c>
-      <c r="G16" s="75">
-        <f>E16/C16</f>
+      <c r="G17" s="75">
+        <f>E17/C17</f>
         <v>3.8</v>
       </c>
-      <c r="H16" s="71" t="s">
+      <c r="H17" s="71" t="s">
         <v>400</v>
       </c>
-      <c r="I16" s="71">
+      <c r="I17" s="71">
         <v>220</v>
       </c>
-      <c r="J16" s="73">
-        <f>I16*G16</f>
+      <c r="J17" s="73">
+        <f>I17*G17</f>
         <v>836</v>
       </c>
-      <c r="K16" s="71">
+      <c r="K17" s="71">
         <v>24</v>
       </c>
-      <c r="L16" s="75">
-        <f>K16/G16</f>
+      <c r="L17" s="75">
+        <f>K17/G17</f>
         <v>6.3157894736842106</v>
       </c>
-      <c r="M16" s="71">
+      <c r="M17" s="71">
         <v>415</v>
       </c>
-      <c r="N16" s="71">
+      <c r="N17" s="71">
         <v>40</v>
       </c>
-      <c r="O16" s="71">
+      <c r="O17" s="71">
         <f t="shared" si="0"/>
         <v>10.526315789473685</v>
       </c>
-      <c r="P16" s="6">
+      <c r="P17" s="6">
         <v>115.75</v>
       </c>
-      <c r="Q16" s="6">
+      <c r="Q17" s="6">
         <v>345.81</v>
       </c>
-      <c r="R16" s="1">
+      <c r="R17" s="1">
         <v>25.4</v>
       </c>
-      <c r="S16" s="6">
+      <c r="S17" s="6">
         <v>22400</v>
       </c>
     </row>
-    <row r="17" spans="1:19">
-      <c r="G17" s="74"/>
-      <c r="J17" s="72"/>
-      <c r="L17" s="74"/>
-      <c r="N17" s="6"/>
-      <c r="O17" s="6"/>
-      <c r="P17" s="6" t="s">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="G18" s="74"/>
+      <c r="J18" s="72"/>
+      <c r="L18" s="74"/>
+      <c r="N18" s="6"/>
+      <c r="O18" s="6"/>
+      <c r="P18" s="6" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="18" spans="1:19">
-      <c r="A18" s="62"/>
-      <c r="B18" s="62"/>
-      <c r="C18" s="61"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="61"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="61"/>
-      <c r="H18" s="61"/>
-      <c r="I18" s="61"/>
-      <c r="J18" s="61"/>
-      <c r="K18" s="61"/>
-      <c r="L18" s="61"/>
-      <c r="M18" s="61"/>
-      <c r="N18" s="62"/>
-      <c r="O18" s="62"/>
-      <c r="P18" s="61"/>
-      <c r="Q18" s="61"/>
-      <c r="R18" s="61"/>
-      <c r="S18" s="61"/>
-    </row>
-    <row r="19" spans="1:19">
-      <c r="A19" s="56" t="s">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A19" s="62"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="61"/>
+      <c r="D19" s="61"/>
+      <c r="E19" s="61"/>
+      <c r="F19" s="61"/>
+      <c r="G19" s="61"/>
+      <c r="H19" s="61"/>
+      <c r="I19" s="61"/>
+      <c r="J19" s="61"/>
+      <c r="K19" s="61"/>
+      <c r="L19" s="61"/>
+      <c r="M19" s="61"/>
+      <c r="N19" s="62"/>
+      <c r="O19" s="62"/>
+      <c r="P19" s="61"/>
+      <c r="Q19" s="61"/>
+      <c r="R19" s="61"/>
+      <c r="S19" s="61"/>
+    </row>
+    <row r="20" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A20" s="56" t="s">
         <v>513</v>
-      </c>
-      <c r="B19" s="56" t="s">
-        <v>319</v>
-      </c>
-      <c r="C19" s="71">
-        <v>15</v>
-      </c>
-      <c r="D19" s="71">
-        <v>25.4</v>
-      </c>
-      <c r="E19" s="71">
-        <v>57</v>
-      </c>
-      <c r="F19" s="71">
-        <v>30</v>
-      </c>
-      <c r="G19" s="75">
-        <f t="shared" ref="G19" si="11">E19/C19</f>
-        <v>3.8</v>
-      </c>
-      <c r="H19" s="71" t="s">
-        <v>392</v>
-      </c>
-      <c r="I19" s="71">
-        <v>90</v>
-      </c>
-      <c r="J19" s="73">
-        <f t="shared" ref="J19" si="12">I19*G19</f>
-        <v>342</v>
-      </c>
-      <c r="K19" s="71">
-        <v>80</v>
-      </c>
-      <c r="L19" s="75">
-        <f t="shared" ref="L19" si="13">K19/G19</f>
-        <v>21.05263157894737</v>
-      </c>
-      <c r="M19" s="71">
-        <v>230</v>
-      </c>
-      <c r="N19" s="71">
-        <v>20</v>
-      </c>
-      <c r="O19" s="71">
-        <f t="shared" ref="O19" si="14">N19/G19</f>
-        <v>5.2631578947368425</v>
-      </c>
-      <c r="P19" s="6">
-        <v>61.09</v>
-      </c>
-      <c r="Q19" s="6">
-        <v>230</v>
-      </c>
-      <c r="R19" s="1">
-        <v>25.4</v>
-      </c>
-      <c r="S19" s="6">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="20" spans="1:19">
-      <c r="A20" s="56" t="s">
-        <v>568</v>
       </c>
       <c r="B20" s="56" t="s">
         <v>319</v>
@@ -30057,7 +31254,7 @@
         <v>21.05263157894737</v>
       </c>
       <c r="M20" s="71">
-        <v>415</v>
+        <v>230</v>
       </c>
       <c r="N20" s="71">
         <v>20</v>
@@ -30079,15 +31276,15 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="21" spans="1:19">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" s="56" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B21" s="56" t="s">
         <v>319</v>
       </c>
       <c r="C21" s="71">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D21" s="71">
         <v>25.4</v>
@@ -30099,52 +31296,52 @@
         <v>30</v>
       </c>
       <c r="G21" s="75">
-        <f t="shared" ref="G21:G23" si="19">E21/C21</f>
-        <v>3.1666666666666665</v>
+        <f t="shared" ref="G21" si="19">E21/C21</f>
+        <v>3.8</v>
       </c>
       <c r="H21" s="71" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="I21" s="71">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="J21" s="73">
-        <f>I21*G21</f>
-        <v>475</v>
+        <f t="shared" ref="J21" si="20">I21*G21</f>
+        <v>342</v>
       </c>
       <c r="K21" s="71">
         <v>80</v>
       </c>
       <c r="L21" s="75">
-        <f t="shared" ref="L21" si="20">K21/G21</f>
-        <v>25.263157894736842</v>
+        <f t="shared" ref="L21" si="21">K21/G21</f>
+        <v>21.05263157894737</v>
       </c>
       <c r="M21" s="71">
-        <v>230</v>
+        <v>415</v>
       </c>
       <c r="N21" s="71">
         <v>20</v>
       </c>
       <c r="O21" s="71">
-        <f t="shared" ref="O21:O23" si="21">N21/G21</f>
-        <v>6.3157894736842106</v>
+        <f t="shared" ref="O21" si="22">N21/G21</f>
+        <v>5.2631578947368425</v>
       </c>
       <c r="P21" s="6">
-        <v>91.42</v>
+        <v>61.09</v>
       </c>
       <c r="Q21" s="6">
-        <v>288</v>
+        <v>230</v>
       </c>
       <c r="R21" s="1">
         <v>25.4</v>
       </c>
       <c r="S21" s="6">
-        <v>22400</v>
-      </c>
-    </row>
-    <row r="22" spans="1:19">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" s="56" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="B22" s="56" t="s">
         <v>319</v>
@@ -30162,7 +31359,7 @@
         <v>30</v>
       </c>
       <c r="G22" s="75">
-        <f>E22/C22</f>
+        <f t="shared" ref="G22:G24" si="23">E22/C22</f>
         <v>3.1666666666666665</v>
       </c>
       <c r="H22" s="71" t="s">
@@ -30179,17 +31376,17 @@
         <v>80</v>
       </c>
       <c r="L22" s="75">
-        <f t="shared" ref="L22" si="22">K22/G22</f>
+        <f t="shared" ref="L22" si="24">K22/G22</f>
         <v>25.263157894736842</v>
       </c>
       <c r="M22" s="71">
-        <v>415</v>
+        <v>230</v>
       </c>
       <c r="N22" s="71">
         <v>20</v>
       </c>
       <c r="O22" s="71">
-        <f>N22/G22</f>
+        <f t="shared" ref="O22:O24" si="25">N22/G22</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="P22" s="6">
@@ -30205,15 +31402,15 @@
         <v>22400</v>
       </c>
     </row>
-    <row r="23" spans="1:19">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="56" t="s">
-        <v>567</v>
+        <v>545</v>
       </c>
       <c r="B23" s="56" t="s">
         <v>319</v>
       </c>
       <c r="C23" s="71">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D23" s="71">
         <v>25.4</v>
@@ -30222,11 +31419,11 @@
         <v>57</v>
       </c>
       <c r="F23" s="71">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G23" s="75">
-        <f t="shared" si="19"/>
-        <v>4.75</v>
+        <f>E23/C23</f>
+        <v>3.1666666666666665</v>
       </c>
       <c r="H23" s="71" t="s">
         <v>398</v>
@@ -30236,27 +31433,27 @@
       </c>
       <c r="J23" s="73">
         <f>I23*G23</f>
-        <v>712.5</v>
+        <v>475</v>
       </c>
       <c r="K23" s="71">
         <v>80</v>
       </c>
       <c r="L23" s="75">
-        <f>K23/G23</f>
-        <v>16.842105263157894</v>
+        <f t="shared" ref="L23" si="26">K23/G23</f>
+        <v>25.263157894736842</v>
       </c>
       <c r="M23" s="71">
-        <v>230</v>
+        <v>415</v>
       </c>
       <c r="N23" s="71">
         <v>20</v>
       </c>
       <c r="O23" s="71">
-        <f t="shared" si="21"/>
-        <v>4.2105263157894735</v>
+        <f>N23/G23</f>
+        <v>6.3157894736842106</v>
       </c>
       <c r="P23" s="6">
-        <v>73.599999999999994</v>
+        <v>91.42</v>
       </c>
       <c r="Q23" s="6">
         <v>288</v>
@@ -30268,9 +31465,9 @@
         <v>22400</v>
       </c>
     </row>
-    <row r="24" spans="1:19">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" s="56" t="s">
-        <v>514</v>
+        <v>567</v>
       </c>
       <c r="B24" s="56" t="s">
         <v>319</v>
@@ -30288,7 +31485,7 @@
         <v>40</v>
       </c>
       <c r="G24" s="75">
-        <f t="shared" ref="G24" si="23">E24/C24</f>
+        <f t="shared" si="23"/>
         <v>4.75</v>
       </c>
       <c r="H24" s="71" t="s">
@@ -30309,13 +31506,13 @@
         <v>16.842105263157894</v>
       </c>
       <c r="M24" s="71">
-        <v>415</v>
+        <v>230</v>
       </c>
       <c r="N24" s="71">
         <v>20</v>
       </c>
       <c r="O24" s="71">
-        <f t="shared" ref="O24" si="24">N24/G24</f>
+        <f t="shared" si="25"/>
         <v>4.2105263157894735</v>
       </c>
       <c r="P24" s="6">
@@ -30331,90 +31528,89 @@
         <v>22400</v>
       </c>
     </row>
-    <row r="25" spans="1:19">
-      <c r="C25"/>
-      <c r="D25"/>
-      <c r="E25"/>
-      <c r="F25"/>
-      <c r="G25"/>
-      <c r="H25"/>
-      <c r="I25"/>
-      <c r="J25"/>
-      <c r="K25"/>
-      <c r="L25"/>
-      <c r="M25"/>
-      <c r="P25"/>
-      <c r="Q25"/>
-      <c r="R25"/>
-      <c r="S25"/>
-    </row>
-    <row r="27" spans="1:19">
-      <c r="A27" s="86" t="s">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A25" s="56" t="s">
+        <v>514</v>
+      </c>
+      <c r="B25" s="56" t="s">
+        <v>319</v>
+      </c>
+      <c r="C25" s="71">
+        <v>12</v>
+      </c>
+      <c r="D25" s="71">
+        <v>25.4</v>
+      </c>
+      <c r="E25" s="71">
+        <v>57</v>
+      </c>
+      <c r="F25" s="71">
+        <v>40</v>
+      </c>
+      <c r="G25" s="75">
+        <f t="shared" ref="G25" si="27">E25/C25</f>
+        <v>4.75</v>
+      </c>
+      <c r="H25" s="71" t="s">
+        <v>398</v>
+      </c>
+      <c r="I25" s="71">
+        <v>150</v>
+      </c>
+      <c r="J25" s="73">
+        <f>I25*G25</f>
+        <v>712.5</v>
+      </c>
+      <c r="K25" s="71">
+        <v>80</v>
+      </c>
+      <c r="L25" s="75">
+        <f>K25/G25</f>
+        <v>16.842105263157894</v>
+      </c>
+      <c r="M25" s="71">
+        <v>415</v>
+      </c>
+      <c r="N25" s="71">
+        <v>20</v>
+      </c>
+      <c r="O25" s="71">
+        <f t="shared" ref="O25" si="28">N25/G25</f>
+        <v>4.2105263157894735</v>
+      </c>
+      <c r="P25" s="6">
+        <v>73.599999999999994</v>
+      </c>
+      <c r="Q25" s="6">
+        <v>288</v>
+      </c>
+      <c r="R25" s="1">
+        <v>25.4</v>
+      </c>
+      <c r="S25" s="6">
+        <v>22400</v>
+      </c>
+    </row>
+    <row r="26" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="C26"/>
+      <c r="D26"/>
+      <c r="E26"/>
+      <c r="F26"/>
+      <c r="G26"/>
+      <c r="H26"/>
+      <c r="I26"/>
+      <c r="J26"/>
+      <c r="K26"/>
+      <c r="L26"/>
+      <c r="M26"/>
+      <c r="P26"/>
+      <c r="Q26"/>
+      <c r="R26"/>
+      <c r="S26"/>
+    </row>
+    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A28" s="86" t="s">
         <v>546</v>
-      </c>
-      <c r="B27" t="s">
-        <v>319</v>
-      </c>
-      <c r="C27" s="6">
-        <v>15</v>
-      </c>
-      <c r="D27" s="6">
-        <v>40</v>
-      </c>
-      <c r="E27" s="6">
-        <v>57</v>
-      </c>
-      <c r="F27" s="6">
-        <v>40</v>
-      </c>
-      <c r="G27" s="74">
-        <f t="shared" ref="G27" si="25">E27/C27</f>
-        <v>3.8</v>
-      </c>
-      <c r="H27" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="I27" s="6">
-        <v>400</v>
-      </c>
-      <c r="J27" s="72">
-        <f t="shared" ref="J27" si="26">I27*G27</f>
-        <v>1520</v>
-      </c>
-      <c r="K27" s="1">
-        <v>24</v>
-      </c>
-      <c r="L27" s="74">
-        <f t="shared" ref="L27" si="27">K27/G27</f>
-        <v>6.3157894736842106</v>
-      </c>
-      <c r="M27" s="6">
-        <v>415</v>
-      </c>
-      <c r="N27" s="71">
-        <v>40</v>
-      </c>
-      <c r="O27" s="71">
-        <f t="shared" ref="O27" si="28">N27/G27</f>
-        <v>10.526315789473685</v>
-      </c>
-      <c r="P27" s="6">
-        <v>192.91</v>
-      </c>
-      <c r="Q27" s="6">
-        <v>461</v>
-      </c>
-      <c r="R27" s="6">
-        <f t="shared" ref="R27" si="29">D27</f>
-        <v>40</v>
-      </c>
-      <c r="S27" s="6">
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="28" spans="1:19">
-      <c r="A28" s="86" t="s">
-        <v>473</v>
       </c>
       <c r="B28" t="s">
         <v>319</v>
@@ -30432,24 +31628,24 @@
         <v>40</v>
       </c>
       <c r="G28" s="74">
-        <f t="shared" ref="G28" si="30">E28/C28</f>
+        <f t="shared" ref="G28" si="29">E28/C28</f>
         <v>3.8</v>
       </c>
       <c r="H28" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I28" s="6">
         <v>400</v>
       </c>
       <c r="J28" s="72">
-        <f t="shared" ref="J28" si="31">I28*G28</f>
+        <f t="shared" ref="J28" si="30">I28*G28</f>
         <v>1520</v>
       </c>
       <c r="K28" s="1">
         <v>24</v>
       </c>
       <c r="L28" s="74">
-        <f t="shared" ref="L28" si="32">K28/G28</f>
+        <f t="shared" ref="L28" si="31">K28/G28</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="M28" s="6">
@@ -30459,7 +31655,7 @@
         <v>40</v>
       </c>
       <c r="O28" s="71">
-        <f t="shared" ref="O28:O30" si="33">N28/G28</f>
+        <f t="shared" ref="O28" si="32">N28/G28</f>
         <v>10.526315789473685</v>
       </c>
       <c r="P28" s="6">
@@ -30469,16 +31665,16 @@
         <v>461</v>
       </c>
       <c r="R28" s="6">
-        <f t="shared" ref="R28:R30" si="34">D28</f>
+        <f t="shared" ref="R28" si="33">D28</f>
         <v>40</v>
       </c>
       <c r="S28" s="6">
         <v>60000</v>
       </c>
     </row>
-    <row r="29" spans="1:19">
-      <c r="A29" t="s">
-        <v>547</v>
+    <row r="29" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A29" s="86" t="s">
+        <v>473</v>
       </c>
       <c r="B29" t="s">
         <v>319</v>
@@ -30487,44 +31683,44 @@
         <v>15</v>
       </c>
       <c r="D29" s="6">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E29" s="6">
         <v>57</v>
       </c>
       <c r="F29" s="6">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="G29" s="74">
-        <f t="shared" ref="G29:G30" si="35">E29/C29</f>
+        <f t="shared" ref="G29" si="34">E29/C29</f>
         <v>3.8</v>
       </c>
       <c r="H29" s="6" t="s">
         <v>402</v>
       </c>
       <c r="I29" s="6">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="J29" s="72">
-        <f t="shared" ref="J29:J30" si="36">I29*G29</f>
-        <v>2280</v>
+        <f t="shared" ref="J29" si="35">I29*G29</f>
+        <v>1520</v>
       </c>
       <c r="K29" s="1">
         <v>24</v>
       </c>
       <c r="L29" s="74">
-        <f t="shared" ref="L29:L30" si="37">K29/G29</f>
+        <f t="shared" ref="L29" si="36">K29/G29</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="M29" s="6">
         <v>415</v>
       </c>
       <c r="N29" s="71">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O29" s="71">
-        <f t="shared" si="33"/>
-        <v>15.789473684210527</v>
+        <f t="shared" ref="O29:O31" si="37">N29/G29</f>
+        <v>10.526315789473685</v>
       </c>
       <c r="P29" s="6">
         <v>192.91</v>
@@ -30533,16 +31729,16 @@
         <v>461</v>
       </c>
       <c r="R29" s="6">
-        <f t="shared" si="34"/>
-        <v>55</v>
+        <f t="shared" ref="R29:R31" si="38">D29</f>
+        <v>40</v>
       </c>
       <c r="S29" s="6">
         <v>60000</v>
       </c>
     </row>
-    <row r="30" spans="1:19">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B30" t="s">
         <v>319</v>
@@ -30560,24 +31756,24 @@
         <v>55</v>
       </c>
       <c r="G30" s="74">
-        <f t="shared" si="35"/>
+        <f t="shared" ref="G30:G31" si="39">E30/C30</f>
         <v>3.8</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>402</v>
       </c>
       <c r="I30" s="6">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="J30" s="72">
-        <f t="shared" si="36"/>
-        <v>3040</v>
+        <f t="shared" ref="J30:J31" si="40">I30*G30</f>
+        <v>2280</v>
       </c>
       <c r="K30" s="1">
         <v>24</v>
       </c>
       <c r="L30" s="74">
-        <f t="shared" si="37"/>
+        <f t="shared" ref="L30:L31" si="41">K30/G30</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="M30" s="6">
@@ -30587,26 +31783,26 @@
         <v>60</v>
       </c>
       <c r="O30" s="71">
-        <f t="shared" si="33"/>
+        <f t="shared" si="37"/>
         <v>15.789473684210527</v>
       </c>
       <c r="P30" s="6">
-        <v>152.72</v>
+        <v>192.91</v>
       </c>
       <c r="Q30" s="6">
-        <v>576</v>
+        <v>461</v>
       </c>
       <c r="R30" s="6">
-        <f t="shared" si="34"/>
+        <f t="shared" si="38"/>
         <v>55</v>
       </c>
       <c r="S30" s="6">
-        <v>95000</v>
-      </c>
-    </row>
-    <row r="31" spans="1:19">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B31" t="s">
         <v>319</v>
@@ -30624,24 +31820,24 @@
         <v>55</v>
       </c>
       <c r="G31" s="74">
-        <f t="shared" ref="G31" si="38">E31/C31</f>
+        <f t="shared" si="39"/>
         <v>3.8</v>
       </c>
       <c r="H31" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I31" s="6">
         <v>800</v>
       </c>
       <c r="J31" s="72">
-        <f t="shared" ref="J31" si="39">I31*G31</f>
+        <f t="shared" si="40"/>
         <v>3040</v>
       </c>
       <c r="K31" s="1">
         <v>24</v>
       </c>
       <c r="L31" s="74">
-        <f t="shared" ref="L31" si="40">K31/G31</f>
+        <f t="shared" si="41"/>
         <v>6.3157894736842106</v>
       </c>
       <c r="M31" s="6">
@@ -30651,7 +31847,7 @@
         <v>60</v>
       </c>
       <c r="O31" s="71">
-        <f t="shared" ref="O31" si="41">N31/G31</f>
+        <f t="shared" si="37"/>
         <v>15.789473684210527</v>
       </c>
       <c r="P31" s="6">
@@ -30661,79 +31857,80 @@
         <v>576</v>
       </c>
       <c r="R31" s="6">
-        <f t="shared" ref="R31" si="42">D31</f>
+        <f t="shared" si="38"/>
         <v>55</v>
       </c>
       <c r="S31" s="6">
         <v>95000</v>
       </c>
     </row>
-    <row r="34" spans="1:19">
-      <c r="A34" t="s">
+    <row r="32" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>548</v>
+      </c>
+      <c r="B32" t="s">
+        <v>319</v>
+      </c>
+      <c r="C32" s="6">
+        <v>15</v>
+      </c>
+      <c r="D32" s="6">
+        <v>55</v>
+      </c>
+      <c r="E32" s="6">
+        <v>57</v>
+      </c>
+      <c r="F32" s="6">
+        <v>55</v>
+      </c>
+      <c r="G32" s="74">
+        <f t="shared" ref="G32" si="42">E32/C32</f>
+        <v>3.8</v>
+      </c>
+      <c r="H32" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="I32" s="6">
+        <v>800</v>
+      </c>
+      <c r="J32" s="72">
+        <f t="shared" ref="J32" si="43">I32*G32</f>
+        <v>3040</v>
+      </c>
+      <c r="K32" s="1">
+        <v>24</v>
+      </c>
+      <c r="L32" s="74">
+        <f t="shared" ref="L32" si="44">K32/G32</f>
+        <v>6.3157894736842106</v>
+      </c>
+      <c r="M32" s="6">
+        <v>415</v>
+      </c>
+      <c r="N32" s="71">
+        <v>60</v>
+      </c>
+      <c r="O32" s="71">
+        <f t="shared" ref="O32" si="45">N32/G32</f>
+        <v>15.789473684210527</v>
+      </c>
+      <c r="P32" s="6">
+        <v>152.72</v>
+      </c>
+      <c r="Q32" s="6">
+        <v>576</v>
+      </c>
+      <c r="R32" s="6">
+        <f t="shared" ref="R32" si="46">D32</f>
+        <v>55</v>
+      </c>
+      <c r="S32" s="6">
+        <v>95000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
         <v>550</v>
-      </c>
-      <c r="B34" t="s">
-        <v>319</v>
-      </c>
-      <c r="C34" s="6">
-        <v>15</v>
-      </c>
-      <c r="D34" s="6">
-        <v>40</v>
-      </c>
-      <c r="E34" s="6">
-        <v>57</v>
-      </c>
-      <c r="F34" s="6">
-        <v>40</v>
-      </c>
-      <c r="G34" s="74">
-        <f t="shared" ref="G34" si="43">E34/C34</f>
-        <v>3.8</v>
-      </c>
-      <c r="H34" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="I34" s="6">
-        <v>300</v>
-      </c>
-      <c r="J34" s="72">
-        <f t="shared" ref="J34" si="44">I34*G34</f>
-        <v>1140</v>
-      </c>
-      <c r="K34" s="1">
-        <v>40</v>
-      </c>
-      <c r="L34" s="74">
-        <f t="shared" ref="L34" si="45">K34/G34</f>
-        <v>10.526315789473685</v>
-      </c>
-      <c r="M34" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="N34" s="71">
-        <v>40</v>
-      </c>
-      <c r="O34" s="71">
-        <f>N34/G34</f>
-        <v>10.526315789473685</v>
-      </c>
-      <c r="P34" s="6">
-        <v>115.75</v>
-      </c>
-      <c r="Q34" s="6">
-        <v>345.81</v>
-      </c>
-      <c r="R34" s="6">
-        <v>40</v>
-      </c>
-      <c r="S34" s="6">
-        <v>29000</v>
-      </c>
-    </row>
-    <row r="35" spans="1:19">
-      <c r="A35" t="s">
-        <v>553</v>
       </c>
       <c r="B35" t="s">
         <v>319</v>
@@ -30751,24 +31948,24 @@
         <v>40</v>
       </c>
       <c r="G35" s="74">
-        <f t="shared" ref="G35" si="46">E35/C35</f>
+        <f t="shared" ref="G35" si="47">E35/C35</f>
         <v>3.8</v>
       </c>
       <c r="H35" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I35" s="6">
         <v>300</v>
       </c>
       <c r="J35" s="72">
-        <f t="shared" ref="J35" si="47">I35*G35</f>
+        <f t="shared" ref="J35" si="48">I35*G35</f>
         <v>1140</v>
       </c>
       <c r="K35" s="1">
         <v>40</v>
       </c>
       <c r="L35" s="74">
-        <f t="shared" ref="L35" si="48">K35/G35</f>
+        <f t="shared" ref="L35" si="49">K35/G35</f>
         <v>10.526315789473685</v>
       </c>
       <c r="M35" s="6" t="s">
@@ -30794,9 +31991,9 @@
         <v>29000</v>
       </c>
     </row>
-    <row r="36" spans="1:19">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B36" t="s">
         <v>319</v>
@@ -30805,44 +32002,44 @@
         <v>15</v>
       </c>
       <c r="D36" s="6">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E36" s="6">
         <v>57</v>
       </c>
       <c r="F36" s="6">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="G36" s="74">
-        <f t="shared" ref="G36" si="49">E36/C36</f>
+        <f t="shared" ref="G36" si="50">E36/C36</f>
         <v>3.8</v>
       </c>
       <c r="H36" s="6" t="s">
         <v>402</v>
       </c>
       <c r="I36" s="6">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="J36" s="72">
-        <f t="shared" ref="J36" si="50">I36*G36</f>
-        <v>1900</v>
+        <f t="shared" ref="J36" si="51">I36*G36</f>
+        <v>1140</v>
       </c>
       <c r="K36" s="1">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="L36" s="74">
-        <f>K36/G36</f>
-        <v>21.05263157894737</v>
+        <f t="shared" ref="L36" si="52">K36/G36</f>
+        <v>10.526315789473685</v>
       </c>
       <c r="M36" s="6" t="s">
         <v>401</v>
       </c>
       <c r="N36" s="71">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O36" s="71">
         <f>N36/G36</f>
-        <v>15.789473684210527</v>
+        <v>10.526315789473685</v>
       </c>
       <c r="P36" s="6">
         <v>115.75</v>
@@ -30851,15 +32048,15 @@
         <v>345.81</v>
       </c>
       <c r="R36" s="6">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="S36" s="6">
-        <v>60000</v>
-      </c>
-    </row>
-    <row r="37" spans="1:19">
+        <v>29000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B37" t="s">
         <v>319</v>
@@ -30877,25 +32074,25 @@
         <v>55</v>
       </c>
       <c r="G37" s="74">
-        <f t="shared" ref="G37" si="51">E37/C37</f>
+        <f t="shared" ref="G37" si="53">E37/C37</f>
         <v>3.8</v>
       </c>
       <c r="H37" s="6" t="s">
         <v>402</v>
       </c>
       <c r="I37" s="6">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="J37" s="72">
-        <f t="shared" ref="J37" si="52">I37*G37</f>
-        <v>3040</v>
+        <f t="shared" ref="J37" si="54">I37*G37</f>
+        <v>1900</v>
       </c>
       <c r="K37" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L37" s="74">
         <f>K37/G37</f>
-        <v>10.526315789473685</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>401</v>
@@ -30920,9 +32117,9 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="38" spans="1:19">
+    <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B38" t="s">
         <v>319</v>
@@ -30940,17 +32137,17 @@
         <v>55</v>
       </c>
       <c r="G38" s="74">
-        <f t="shared" ref="G38" si="53">E38/C38</f>
+        <f t="shared" ref="G38" si="55">E38/C38</f>
         <v>3.8</v>
       </c>
       <c r="H38" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I38" s="6">
         <v>800</v>
       </c>
       <c r="J38" s="72">
-        <f t="shared" ref="J38" si="54">I38*G38</f>
+        <f t="shared" ref="J38" si="56">I38*G38</f>
         <v>3040</v>
       </c>
       <c r="K38" s="1">
@@ -30983,127 +32180,149 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="40" spans="1:19">
-      <c r="A40" s="3" t="s">
+    <row r="39" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>554</v>
+      </c>
+      <c r="B39" t="s">
+        <v>319</v>
+      </c>
+      <c r="C39" s="6">
+        <v>15</v>
+      </c>
+      <c r="D39" s="6">
+        <v>55</v>
+      </c>
+      <c r="E39" s="6">
+        <v>57</v>
+      </c>
+      <c r="F39" s="6">
+        <v>55</v>
+      </c>
+      <c r="G39" s="74">
+        <f t="shared" ref="G39" si="57">E39/C39</f>
+        <v>3.8</v>
+      </c>
+      <c r="H39" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="I39" s="6">
+        <v>800</v>
+      </c>
+      <c r="J39" s="72">
+        <f t="shared" ref="J39" si="58">I39*G39</f>
+        <v>3040</v>
+      </c>
+      <c r="K39" s="1">
+        <v>40</v>
+      </c>
+      <c r="L39" s="74">
+        <f>K39/G39</f>
+        <v>10.526315789473685</v>
+      </c>
+      <c r="M39" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="N39" s="71">
+        <v>60</v>
+      </c>
+      <c r="O39" s="71">
+        <f>N39/G39</f>
+        <v>15.789473684210527</v>
+      </c>
+      <c r="P39" s="6">
+        <v>115.75</v>
+      </c>
+      <c r="Q39" s="6">
+        <v>345.81</v>
+      </c>
+      <c r="R39" s="6">
+        <v>55</v>
+      </c>
+      <c r="S39" s="6">
+        <v>60000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A41" s="3" t="s">
         <v>404</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="C40" s="6">
-        <v>11</v>
-      </c>
-      <c r="D40" s="6">
-        <v>25.4</v>
-      </c>
-      <c r="E40" s="6">
-        <v>61</v>
-      </c>
-      <c r="G40" s="74">
-        <f>E40/C40</f>
-        <v>5.5454545454545459</v>
-      </c>
-      <c r="H40" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="I40" s="1">
-        <v>20</v>
-      </c>
-      <c r="J40" s="23">
-        <f>I40*G40</f>
-        <v>110.90909090909092</v>
-      </c>
-      <c r="K40" s="1">
-        <v>34</v>
-      </c>
-      <c r="L40" s="74">
-        <f t="shared" ref="L40:L45" si="55">K40/G40</f>
-        <v>6.1311475409836058</v>
-      </c>
-      <c r="M40" s="6">
-        <v>415</v>
-      </c>
-      <c r="R40" s="1">
-        <v>25.4</v>
-      </c>
-      <c r="S40" s="6">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="41" spans="1:19">
-      <c r="A41" s="3" t="s">
-        <v>315</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>238</v>
       </c>
       <c r="C41" s="6">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="D41" s="6">
+        <v>25.4</v>
       </c>
       <c r="E41" s="6">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G41" s="74">
-        <f t="shared" ref="G41:G42" si="56">E41/C41</f>
-        <v>5.5555555555555554</v>
+        <f>E41/C41</f>
+        <v>5.5454545454545459</v>
       </c>
       <c r="H41" s="6" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="I41" s="1">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="J41" s="23">
-        <f t="shared" ref="J41:J44" si="57">I41*G41</f>
-        <v>344.44444444444446</v>
+        <f>I41*G41</f>
+        <v>110.90909090909092</v>
       </c>
       <c r="K41" s="1">
         <v>34</v>
       </c>
       <c r="L41" s="74">
-        <f t="shared" si="55"/>
-        <v>6.12</v>
+        <f t="shared" ref="L41:L46" si="59">K41/G41</f>
+        <v>6.1311475409836058</v>
       </c>
       <c r="M41" s="6">
         <v>415</v>
       </c>
+      <c r="R41" s="1">
+        <v>25.4</v>
+      </c>
       <c r="S41" s="6">
-        <v>22400</v>
-      </c>
-    </row>
-    <row r="42" spans="1:19">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>238</v>
       </c>
       <c r="C42" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E42" s="6">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G42" s="74">
-        <f t="shared" si="56"/>
-        <v>6.4</v>
+        <f t="shared" ref="G42:G43" si="60">E42/C42</f>
+        <v>5.5555555555555554</v>
       </c>
       <c r="H42" s="6" t="s">
         <v>398</v>
       </c>
       <c r="I42" s="1">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="J42" s="23">
-        <f t="shared" si="57"/>
-        <v>608</v>
+        <f t="shared" ref="J42:J45" si="61">I42*G42</f>
+        <v>344.44444444444446</v>
       </c>
       <c r="K42" s="1">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="L42" s="74">
-        <f t="shared" si="55"/>
-        <v>3.4375</v>
+        <f t="shared" si="59"/>
+        <v>6.12</v>
       </c>
       <c r="M42" s="6">
         <v>415</v>
@@ -31112,176 +32331,170 @@
         <v>22400</v>
       </c>
     </row>
-    <row r="43" spans="1:19">
+    <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
-        <v>405</v>
+        <v>317</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>238</v>
       </c>
       <c r="C43" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E43" s="6">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G43" s="74">
-        <f t="shared" ref="G43:G45" si="58">E43/C43</f>
-        <v>6.333333333333333</v>
+        <f t="shared" si="60"/>
+        <v>6.4</v>
       </c>
       <c r="H43" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="I43" s="6">
-        <v>128</v>
+        <v>398</v>
+      </c>
+      <c r="I43" s="1">
+        <v>95</v>
       </c>
       <c r="J43" s="23">
-        <f>I43*G43</f>
-        <v>810.66666666666663</v>
-      </c>
-      <c r="K43" s="6">
+        <f t="shared" si="61"/>
+        <v>608</v>
+      </c>
+      <c r="K43" s="1">
         <v>22</v>
       </c>
       <c r="L43" s="74">
-        <f>K43/G43</f>
-        <v>3.4736842105263159</v>
+        <f t="shared" si="59"/>
+        <v>3.4375</v>
       </c>
       <c r="M43" s="6">
         <v>415</v>
       </c>
       <c r="S43" s="6">
-        <v>29000</v>
-      </c>
-    </row>
-    <row r="44" spans="1:19">
+        <v>22400</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>238</v>
       </c>
       <c r="C44" s="6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E44" s="6">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G44" s="74">
-        <f t="shared" si="58"/>
-        <v>4.3636363636363633</v>
+        <f t="shared" ref="G44:G46" si="62">E44/C44</f>
+        <v>6.333333333333333</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I44" s="6">
-        <v>369</v>
+        <v>128</v>
       </c>
       <c r="J44" s="23">
-        <f t="shared" si="57"/>
-        <v>1610.181818181818</v>
+        <f>I44*G44</f>
+        <v>810.66666666666663</v>
       </c>
       <c r="K44" s="6">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L44" s="74">
-        <f t="shared" si="55"/>
-        <v>3.4375000000000004</v>
+        <f>K44/G44</f>
+        <v>3.4736842105263159</v>
       </c>
       <c r="M44" s="6">
         <v>415</v>
       </c>
-    </row>
-    <row r="45" spans="1:19">
-      <c r="A45" t="s">
-        <v>407</v>
+      <c r="S44" s="6">
+        <v>29000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A45" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>238</v>
       </c>
       <c r="C45" s="6">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E45" s="6">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="G45" s="74">
-        <f t="shared" si="58"/>
-        <v>5.1428571428571432</v>
+        <f t="shared" si="62"/>
+        <v>4.3636363636363633</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
       <c r="I45" s="6">
-        <v>428</v>
+        <v>369</v>
       </c>
       <c r="J45" s="23">
-        <f>I45*G45</f>
-        <v>2201.1428571428573</v>
+        <f t="shared" si="61"/>
+        <v>1610.181818181818</v>
       </c>
       <c r="K45" s="6">
-        <v>16.5</v>
+        <v>15</v>
       </c>
       <c r="L45" s="74">
-        <f t="shared" si="55"/>
-        <v>3.208333333333333</v>
+        <f t="shared" si="59"/>
+        <v>3.4375000000000004</v>
       </c>
       <c r="M45" s="6">
         <v>415</v>
       </c>
-      <c r="R45" s="1">
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>407</v>
+      </c>
+      <c r="C46" s="6">
+        <v>14</v>
+      </c>
+      <c r="E46" s="6">
+        <v>72</v>
+      </c>
+      <c r="G46" s="74">
+        <f t="shared" si="62"/>
+        <v>5.1428571428571432</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="I46" s="6">
+        <v>428</v>
+      </c>
+      <c r="J46" s="23">
+        <f>I46*G46</f>
+        <v>2201.1428571428573</v>
+      </c>
+      <c r="K46" s="6">
+        <v>16.5</v>
+      </c>
+      <c r="L46" s="74">
+        <f t="shared" si="59"/>
+        <v>3.208333333333333</v>
+      </c>
+      <c r="M46" s="6">
+        <v>415</v>
+      </c>
+      <c r="R46" s="1">
         <v>25.4</v>
       </c>
-      <c r="S45" s="6">
+      <c r="S46" s="6">
         <v>18000</v>
       </c>
     </row>
-    <row r="47" spans="1:19">
-      <c r="A47" s="3" t="s">
+    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A48" s="3" t="s">
         <v>408</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="C47" s="6">
-        <v>19</v>
-      </c>
-      <c r="D47" s="6">
-        <v>25.4</v>
-      </c>
-      <c r="E47" s="6">
-        <v>57</v>
-      </c>
-      <c r="G47" s="6">
-        <f t="shared" ref="G47:G49" si="59">E47/C47</f>
-        <v>3</v>
-      </c>
-      <c r="H47" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="I47" s="1">
-        <v>15</v>
-      </c>
-      <c r="J47" s="1">
-        <f>I47*G47</f>
-        <v>45</v>
-      </c>
-      <c r="K47" s="1">
-        <v>34</v>
-      </c>
-      <c r="L47" s="74">
-        <f>K47/G47</f>
-        <v>11.333333333333334</v>
-      </c>
-      <c r="M47" s="6">
-        <v>230</v>
-      </c>
-      <c r="R47" s="1">
-        <v>25.4</v>
-      </c>
-      <c r="S47" s="6">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19">
-      <c r="A48" s="3" t="s">
-        <v>315</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>238</v>
@@ -31296,18 +32509,18 @@
         <v>57</v>
       </c>
       <c r="G48" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" ref="G48:G50" si="63">E48/C48</f>
         <v>3</v>
       </c>
       <c r="H48" s="6" t="s">
         <v>392</v>
       </c>
       <c r="I48" s="1">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="J48" s="1">
         <f>I48*G48</f>
-        <v>186</v>
+        <v>45</v>
       </c>
       <c r="K48" s="1">
         <v>34</v>
@@ -31326,9 +32539,9 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="49" spans="1:24">
+    <row r="49" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>238</v>
@@ -31343,25 +32556,25 @@
         <v>57</v>
       </c>
       <c r="G49" s="6">
-        <f t="shared" si="59"/>
+        <f t="shared" si="63"/>
         <v>3</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>392</v>
       </c>
       <c r="I49" s="1">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="J49" s="1">
-        <f t="shared" ref="J49" si="60">I49*G49</f>
-        <v>285</v>
+        <f>I49*G49</f>
+        <v>186</v>
       </c>
       <c r="K49" s="1">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="L49" s="74">
-        <f t="shared" ref="L49" si="61">K49/G49</f>
-        <v>7.333333333333333</v>
+        <f>K49/G49</f>
+        <v>11.333333333333334</v>
       </c>
       <c r="M49" s="6">
         <v>230</v>
@@ -31373,69 +32586,66 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="50" spans="1:24">
-      <c r="G50" s="74"/>
-      <c r="L50" s="74"/>
-    </row>
-    <row r="51" spans="1:24" s="56" customFormat="1">
-      <c r="A51" s="56" t="s">
+    <row r="50" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A50" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="C50" s="6">
+        <v>19</v>
+      </c>
+      <c r="D50" s="6">
+        <v>25.4</v>
+      </c>
+      <c r="E50" s="6">
+        <v>57</v>
+      </c>
+      <c r="G50" s="6">
+        <f t="shared" si="63"/>
+        <v>3</v>
+      </c>
+      <c r="H50" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="I50" s="1">
+        <v>95</v>
+      </c>
+      <c r="J50" s="1">
+        <f t="shared" ref="J50" si="64">I50*G50</f>
+        <v>285</v>
+      </c>
+      <c r="K50" s="1">
+        <v>22</v>
+      </c>
+      <c r="L50" s="74">
+        <f t="shared" ref="L50" si="65">K50/G50</f>
+        <v>7.333333333333333</v>
+      </c>
+      <c r="M50" s="6">
+        <v>230</v>
+      </c>
+      <c r="R50" s="1">
+        <v>25.4</v>
+      </c>
+      <c r="S50" s="6">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="G51" s="74"/>
+      <c r="L51" s="74"/>
+    </row>
+    <row r="52" spans="1:24" s="56" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="56" t="s">
         <v>511</v>
-      </c>
-      <c r="B51" s="121" t="s">
-        <v>238</v>
-      </c>
-      <c r="C51" s="71">
-        <v>19</v>
-      </c>
-      <c r="D51" s="71">
-        <v>25.4</v>
-      </c>
-      <c r="E51" s="71">
-        <v>57</v>
-      </c>
-      <c r="F51" s="71"/>
-      <c r="G51" s="71">
-        <f t="shared" ref="G51" si="62">E51/C51</f>
-        <v>3</v>
-      </c>
-      <c r="H51" s="71" t="s">
-        <v>392</v>
-      </c>
-      <c r="I51" s="114">
-        <v>100</v>
-      </c>
-      <c r="J51" s="114">
-        <f>I51*G51</f>
-        <v>300</v>
-      </c>
-      <c r="K51" s="114">
-        <v>28</v>
-      </c>
-      <c r="L51" s="75">
-        <f t="shared" ref="L51" si="63">K51/G51</f>
-        <v>9.3333333333333339</v>
-      </c>
-      <c r="M51" s="71">
-        <v>415</v>
-      </c>
-      <c r="P51" s="71"/>
-      <c r="Q51" s="71"/>
-      <c r="R51" s="114">
-        <v>25.4</v>
-      </c>
-      <c r="S51" s="71">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="52" spans="1:24" s="56" customFormat="1">
-      <c r="A52" s="56" t="s">
-        <v>512</v>
       </c>
       <c r="B52" s="121" t="s">
         <v>238</v>
       </c>
       <c r="C52" s="71">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D52" s="71">
         <v>25.4</v>
@@ -31445,25 +32655,25 @@
       </c>
       <c r="F52" s="71"/>
       <c r="G52" s="71">
-        <f t="shared" ref="G52" si="64">E52/C52</f>
-        <v>3.8</v>
+        <f t="shared" ref="G52" si="66">E52/C52</f>
+        <v>3</v>
       </c>
       <c r="H52" s="71" t="s">
         <v>392</v>
       </c>
       <c r="I52" s="114">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="J52" s="114">
         <f>I52*G52</f>
-        <v>608</v>
+        <v>300</v>
       </c>
       <c r="K52" s="114">
         <v>28</v>
       </c>
       <c r="L52" s="75">
-        <f t="shared" ref="L52" si="65">K52/G52</f>
-        <v>7.3684210526315796</v>
+        <f t="shared" ref="L52" si="67">K52/G52</f>
+        <v>9.3333333333333339</v>
       </c>
       <c r="M52" s="71">
         <v>415</v>
@@ -31477,481 +32687,134 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="53" spans="1:24">
-      <c r="G53" s="74"/>
-      <c r="L53" s="74"/>
-    </row>
-    <row r="54" spans="1:24">
-      <c r="A54" s="3" t="s">
+    <row r="53" spans="1:24" s="56" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="56" t="s">
+        <v>512</v>
+      </c>
+      <c r="B53" s="121" t="s">
+        <v>238</v>
+      </c>
+      <c r="C53" s="71">
+        <v>15</v>
+      </c>
+      <c r="D53" s="71">
+        <v>25.4</v>
+      </c>
+      <c r="E53" s="71">
+        <v>57</v>
+      </c>
+      <c r="F53" s="71"/>
+      <c r="G53" s="71">
+        <f t="shared" ref="G53" si="68">E53/C53</f>
+        <v>3.8</v>
+      </c>
+      <c r="H53" s="71" t="s">
+        <v>392</v>
+      </c>
+      <c r="I53" s="114">
+        <v>160</v>
+      </c>
+      <c r="J53" s="114">
+        <f>I53*G53</f>
+        <v>608</v>
+      </c>
+      <c r="K53" s="114">
+        <v>28</v>
+      </c>
+      <c r="L53" s="75">
+        <f t="shared" ref="L53" si="69">K53/G53</f>
+        <v>7.3684210526315796</v>
+      </c>
+      <c r="M53" s="71">
+        <v>415</v>
+      </c>
+      <c r="P53" s="71"/>
+      <c r="Q53" s="71"/>
+      <c r="R53" s="114">
+        <v>25.4</v>
+      </c>
+      <c r="S53" s="71">
+        <v>18000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="G54" s="74"/>
+      <c r="L54" s="74"/>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A55" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="B54" s="3" t="s">
+      <c r="B55" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C54" s="6">
+      <c r="C55" s="6">
         <v>19</v>
       </c>
-      <c r="D54" s="6">
+      <c r="D55" s="6">
         <v>25.4</v>
       </c>
-      <c r="E54" s="6">
+      <c r="E55" s="6">
         <v>57</v>
       </c>
-      <c r="G54" s="6">
-        <f>E54/C54</f>
+      <c r="G55" s="6">
+        <f>E55/C55</f>
         <v>3</v>
       </c>
-      <c r="H54" s="6" t="s">
+      <c r="H55" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="I54" s="1">
+      <c r="I55" s="1">
         <v>70</v>
       </c>
-      <c r="J54" s="1">
-        <f>I54*G54</f>
+      <c r="J55" s="1">
+        <f>I55*G55</f>
         <v>210</v>
       </c>
-      <c r="K54" s="1">
+      <c r="K55" s="1">
         <v>28</v>
       </c>
-      <c r="L54" s="74">
-        <f t="shared" ref="L54" si="66">K54/G54</f>
+      <c r="L55" s="74">
+        <f t="shared" ref="L55" si="70">K55/G55</f>
         <v>9.3333333333333339</v>
       </c>
-      <c r="M54" s="6">
+      <c r="M55" s="6">
         <v>230</v>
       </c>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
-      <c r="P54" s="1"/>
-      <c r="Q54" s="1"/>
-      <c r="R54" s="1">
+      <c r="N55" s="1"/>
+      <c r="O55" s="1"/>
+      <c r="P55" s="1"/>
+      <c r="Q55" s="1"/>
+      <c r="R55" s="1">
         <v>25.4</v>
       </c>
-      <c r="S54" s="6">
+      <c r="S55" s="6">
         <v>18000</v>
       </c>
-      <c r="U54" s="6"/>
-      <c r="X54" s="80"/>
-    </row>
-    <row r="59" spans="1:24">
-      <c r="H59" s="154" t="s">
+      <c r="U55" s="6"/>
+      <c r="X55" s="80"/>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="H60" s="157" t="s">
         <v>536</v>
       </c>
-      <c r="I59" s="154"/>
-      <c r="J59" s="154"/>
-      <c r="K59" s="154"/>
-      <c r="L59" s="154"/>
-      <c r="M59" s="154"/>
-      <c r="N59" s="154"/>
-      <c r="O59" s="154"/>
-      <c r="P59" s="154"/>
-      <c r="Q59" s="154"/>
-      <c r="R59" s="154"/>
+      <c r="I60" s="157"/>
+      <c r="J60" s="157"/>
+      <c r="K60" s="157"/>
+      <c r="L60" s="157"/>
+      <c r="M60" s="157"/>
+      <c r="N60" s="157"/>
+      <c r="O60" s="157"/>
+      <c r="P60" s="157"/>
+      <c r="Q60" s="157"/>
+      <c r="R60" s="157"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="H59:R59"/>
+    <mergeCell ref="H60:R60"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09BBB0E4-3072-46AD-B687-93FC8399DD89}">
-  <dimension ref="A1:J15"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" width="10.54296875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="24" style="6" customWidth="1"/>
-    <col min="3" max="3" width="21.54296875" style="6" customWidth="1"/>
-    <col min="4" max="4" width="24.81640625" style="6" customWidth="1"/>
-    <col min="5" max="5" width="21.26953125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.26953125" style="6" customWidth="1"/>
-    <col min="7" max="7" width="15.54296875" style="6" customWidth="1"/>
-    <col min="8" max="8" width="18.54296875" style="6" customWidth="1"/>
-    <col min="9" max="9" width="8.7265625" style="6"/>
-    <col min="10" max="10" width="20.81640625" style="6" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="8" t="s">
-        <v>410</v>
-      </c>
-      <c r="B1" s="8" t="s">
-        <v>411</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>412</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>413</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>414</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>415</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>416</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>417</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>418</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="87" t="s">
-        <v>392</v>
-      </c>
-      <c r="B2" s="87">
-        <v>12</v>
-      </c>
-      <c r="C2" s="87">
-        <v>25.4</v>
-      </c>
-      <c r="D2" s="87">
-        <v>57</v>
-      </c>
-      <c r="E2" s="87">
-        <v>30</v>
-      </c>
-      <c r="F2" s="87">
-        <v>18000</v>
-      </c>
-      <c r="G2" s="88">
-        <f>0.5*25.4</f>
-        <v>12.7</v>
-      </c>
-      <c r="H2" s="87">
-        <v>17999</v>
-      </c>
-      <c r="I2" s="87">
-        <f>D2/B2</f>
-        <v>4.75</v>
-      </c>
-      <c r="J2" s="87">
-        <v>230.54</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="87" t="s">
-        <v>392</v>
-      </c>
-      <c r="B3" s="87">
-        <v>15</v>
-      </c>
-      <c r="C3" s="87">
-        <v>25.4</v>
-      </c>
-      <c r="D3" s="87">
-        <v>57</v>
-      </c>
-      <c r="E3" s="87">
-        <v>30</v>
-      </c>
-      <c r="F3" s="87">
-        <v>18000</v>
-      </c>
-      <c r="G3" s="88">
-        <f>0.5*25.4</f>
-        <v>12.7</v>
-      </c>
-      <c r="H3" s="87">
-        <v>18000</v>
-      </c>
-      <c r="I3" s="87">
-        <f>D3/B3</f>
-        <v>3.8</v>
-      </c>
-      <c r="J3" s="87">
-        <v>230.54</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="87" t="s">
-        <v>392</v>
-      </c>
-      <c r="B4" s="87">
-        <v>19</v>
-      </c>
-      <c r="C4" s="87">
-        <v>25.4</v>
-      </c>
-      <c r="D4" s="87">
-        <v>57</v>
-      </c>
-      <c r="E4" s="87">
-        <v>30</v>
-      </c>
-      <c r="F4" s="87">
-        <v>18000</v>
-      </c>
-      <c r="G4" s="88">
-        <f>0.5*25.4</f>
-        <v>12.7</v>
-      </c>
-      <c r="H4" s="87">
-        <v>18000</v>
-      </c>
-      <c r="I4" s="87">
-        <f t="shared" ref="I4:I7" si="0">D4/B4</f>
-        <v>3</v>
-      </c>
-      <c r="J4" s="87">
-        <v>230.54</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="89" t="s">
-        <v>398</v>
-      </c>
-      <c r="B5" s="90">
-        <v>12</v>
-      </c>
-      <c r="C5" s="90">
-        <v>25.4</v>
-      </c>
-      <c r="D5" s="90">
-        <v>57</v>
-      </c>
-      <c r="E5" s="90" t="s">
-        <v>419</v>
-      </c>
-      <c r="F5" s="90">
-        <v>22400</v>
-      </c>
-      <c r="G5" s="91">
-        <f>0.625*25.4</f>
-        <v>15.875</v>
-      </c>
-      <c r="H5" s="90">
-        <v>22400</v>
-      </c>
-      <c r="I5" s="90">
-        <f t="shared" si="0"/>
-        <v>4.75</v>
-      </c>
-      <c r="J5" s="90">
-        <v>288.18</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="89" t="s">
-        <v>398</v>
-      </c>
-      <c r="B6" s="90">
-        <v>18</v>
-      </c>
-      <c r="C6" s="90">
-        <v>25.4</v>
-      </c>
-      <c r="D6" s="90">
-        <v>57</v>
-      </c>
-      <c r="E6" s="90" t="s">
-        <v>419</v>
-      </c>
-      <c r="F6" s="90">
-        <v>22400</v>
-      </c>
-      <c r="G6" s="91">
-        <f>0.625*25.4</f>
-        <v>15.875</v>
-      </c>
-      <c r="H6" s="90">
-        <v>22400</v>
-      </c>
-      <c r="I6" s="90">
-        <f t="shared" si="0"/>
-        <v>3.1666666666666665</v>
-      </c>
-      <c r="J6" s="90">
-        <v>288.18</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="122" t="s">
-        <v>400</v>
-      </c>
-      <c r="B7" s="122">
-        <v>12</v>
-      </c>
-      <c r="C7" s="122">
-        <v>25.4</v>
-      </c>
-      <c r="D7" s="122">
-        <v>57</v>
-      </c>
-      <c r="E7" s="122" t="s">
-        <v>420</v>
-      </c>
-      <c r="F7" s="122">
-        <v>29000</v>
-      </c>
-      <c r="G7" s="123">
-        <f>0.75*25.4</f>
-        <v>19.049999999999997</v>
-      </c>
-      <c r="H7" s="122">
-        <v>29000</v>
-      </c>
-      <c r="I7" s="122">
-        <f t="shared" si="0"/>
-        <v>4.75</v>
-      </c>
-      <c r="J7" s="122">
-        <v>345.81</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="122" t="s">
-        <v>400</v>
-      </c>
-      <c r="B8" s="122">
-        <v>12</v>
-      </c>
-      <c r="C8" s="122">
-        <v>30</v>
-      </c>
-      <c r="D8" s="122">
-        <v>57</v>
-      </c>
-      <c r="E8" s="122" t="s">
-        <v>420</v>
-      </c>
-      <c r="F8" s="122">
-        <v>29000</v>
-      </c>
-      <c r="G8" s="123">
-        <f>0.75*25.4</f>
-        <v>19.049999999999997</v>
-      </c>
-      <c r="H8" s="122">
-        <v>29000</v>
-      </c>
-      <c r="I8" s="122">
-        <f t="shared" ref="I8" si="1">D8/B8</f>
-        <v>4.75</v>
-      </c>
-      <c r="J8" s="122">
-        <v>345.81</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="122" t="s">
-        <v>400</v>
-      </c>
-      <c r="B9" s="122">
-        <v>15</v>
-      </c>
-      <c r="C9" s="122">
-        <v>30</v>
-      </c>
-      <c r="D9" s="122">
-        <v>57</v>
-      </c>
-      <c r="E9" s="122" t="s">
-        <v>420</v>
-      </c>
-      <c r="F9" s="122">
-        <v>29000</v>
-      </c>
-      <c r="G9" s="123">
-        <f>0.75*25.4</f>
-        <v>19.049999999999997</v>
-      </c>
-      <c r="H9" s="122">
-        <v>29000</v>
-      </c>
-      <c r="I9" s="122">
-        <f>D9/B9</f>
-        <v>3.8</v>
-      </c>
-      <c r="J9" s="122">
-        <v>345.81</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="124" t="s">
-        <v>402</v>
-      </c>
-      <c r="B10" s="124">
-        <v>15</v>
-      </c>
-      <c r="C10" s="124">
-        <v>40</v>
-      </c>
-      <c r="D10" s="124">
-        <v>57</v>
-      </c>
-      <c r="E10" s="124" t="s">
-        <v>421</v>
-      </c>
-      <c r="F10" s="124">
-        <v>60000</v>
-      </c>
-      <c r="G10" s="125">
-        <v>25.4</v>
-      </c>
-      <c r="H10" s="124">
-        <v>60000</v>
-      </c>
-      <c r="I10" s="124">
-        <f>D10/B10</f>
-        <v>3.8</v>
-      </c>
-      <c r="J10" s="124">
-        <v>461.07</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="126" t="s">
-        <v>403</v>
-      </c>
-      <c r="B11" s="126">
-        <v>15</v>
-      </c>
-      <c r="C11" s="126">
-        <v>55</v>
-      </c>
-      <c r="D11" s="126">
-        <v>57</v>
-      </c>
-      <c r="E11" s="126" t="s">
-        <v>422</v>
-      </c>
-      <c r="F11" s="126">
-        <v>95000</v>
-      </c>
-      <c r="G11" s="127">
-        <f>1.25*25.4</f>
-        <v>31.75</v>
-      </c>
-      <c r="H11" s="126">
-        <v>95000</v>
-      </c>
-      <c r="I11" s="126">
-        <f>D11/B11</f>
-        <v>3.8</v>
-      </c>
-      <c r="J11" s="126">
-        <v>576.36</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="45"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4050" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7056A581-8C31-4175-9C1F-BF41EB2E2D61}"/>
+  <xr:revisionPtr revIDLastSave="4066" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C82E44D2-4CBB-45BE-9B1B-7E5BC80A4BEB}"/>
   <bookViews>
-    <workbookView xWindow="1430" yWindow="2040" windowWidth="36940" windowHeight="19260" tabRatio="905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1140" yWindow="1140" windowWidth="36940" windowHeight="19260" tabRatio="905" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lath" sheetId="7" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <sheet name="Online codes" sheetId="17" r:id="rId17"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7">Motors!$A$1:$S$145</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7">Motors!$A$1:$S$146</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -828,7 +828,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2871" uniqueCount="675">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2882" uniqueCount="677">
   <si>
     <t>Name</t>
   </si>
@@ -3189,6 +3189,12 @@
   </si>
   <si>
     <t>Standard, Hi usage, Hi speed</t>
+  </si>
+  <si>
+    <t>Ranger150 3ph 15-57 5/8"</t>
+  </si>
+  <si>
+    <t>MT273M2</t>
   </si>
 </sst>
 </file>
@@ -3482,7 +3488,7 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="158">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3917,9 +3923,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="5">
@@ -6124,13 +6127,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>120</xdr:row>
+      <xdr:row>121</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>628682</xdr:colOff>
-      <xdr:row>120</xdr:row>
+      <xdr:row>121</xdr:row>
       <xdr:rowOff>450873</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6828,13 +6831,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>66260</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>650490</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>431822</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6871,15 +6874,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>66261</xdr:colOff>
+      <xdr:colOff>77807</xdr:colOff>
       <xdr:row>68</xdr:row>
-      <xdr:rowOff>27609</xdr:rowOff>
+      <xdr:rowOff>39155</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>650491</xdr:colOff>
+      <xdr:colOff>662037</xdr:colOff>
       <xdr:row>68</xdr:row>
-      <xdr:rowOff>459431</xdr:rowOff>
+      <xdr:rowOff>470977</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -6902,7 +6905,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22539739" y="35079609"/>
+          <a:off x="22522171" y="34583155"/>
           <a:ext cx="584230" cy="431822"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -6916,13 +6919,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>641383</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>450873</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -6960,13 +6963,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>641383</xdr:colOff>
-      <xdr:row>79</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>444523</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7004,13 +7007,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>79</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>641383</xdr:colOff>
-      <xdr:row>79</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>444523</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7048,13 +7051,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>641383</xdr:colOff>
-      <xdr:row>80</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>444523</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7092,13 +7095,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>641383</xdr:colOff>
-      <xdr:row>81</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>444523</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7136,13 +7139,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>622332</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>457223</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7180,13 +7183,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>628682</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>438173</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7224,13 +7227,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>679485</xdr:colOff>
-      <xdr:row>93</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>469924</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7268,13 +7271,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>698536</xdr:colOff>
-      <xdr:row>94</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>387370</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7312,13 +7315,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>704886</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>381020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7356,13 +7359,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>704886</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>387370</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7400,13 +7403,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>723937</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>469924</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7444,13 +7447,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>98</xdr:row>
+      <xdr:row>99</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>717587</xdr:colOff>
-      <xdr:row>98</xdr:row>
+      <xdr:row>99</xdr:row>
       <xdr:rowOff>463574</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7488,13 +7491,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>99</xdr:row>
+      <xdr:row>100</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>711237</xdr:colOff>
-      <xdr:row>99</xdr:row>
+      <xdr:row>100</xdr:row>
       <xdr:rowOff>450873</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7532,13 +7535,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>100</xdr:row>
+      <xdr:row>101</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>717587</xdr:colOff>
-      <xdr:row>100</xdr:row>
+      <xdr:row>101</xdr:row>
       <xdr:rowOff>450873</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7576,13 +7579,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>101</xdr:row>
+      <xdr:row>102</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>711237</xdr:colOff>
-      <xdr:row>101</xdr:row>
+      <xdr:row>102</xdr:row>
       <xdr:rowOff>444523</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7620,13 +7623,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>42334</xdr:colOff>
-      <xdr:row>101</xdr:row>
+      <xdr:row>102</xdr:row>
       <xdr:rowOff>497416</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>753571</xdr:colOff>
-      <xdr:row>102</xdr:row>
+      <xdr:row>103</xdr:row>
       <xdr:rowOff>433939</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7664,13 +7667,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>104</xdr:row>
+      <xdr:row>105</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>654084</xdr:colOff>
-      <xdr:row>105</xdr:row>
+      <xdr:row>106</xdr:row>
       <xdr:rowOff>12727</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7708,13 +7711,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>105</xdr:row>
+      <xdr:row>106</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>666784</xdr:colOff>
-      <xdr:row>106</xdr:row>
+      <xdr:row>107</xdr:row>
       <xdr:rowOff>19077</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7752,13 +7755,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>106</xdr:row>
+      <xdr:row>107</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>666784</xdr:colOff>
-      <xdr:row>107</xdr:row>
+      <xdr:row>108</xdr:row>
       <xdr:rowOff>19077</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7796,13 +7799,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>107</xdr:row>
+      <xdr:row>108</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>666784</xdr:colOff>
-      <xdr:row>108</xdr:row>
+      <xdr:row>109</xdr:row>
       <xdr:rowOff>19077</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7840,13 +7843,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>108</xdr:row>
+      <xdr:row>109</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>666784</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>110</xdr:row>
       <xdr:rowOff>19077</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7884,13 +7887,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>110</xdr:row>
+      <xdr:row>111</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>431822</xdr:colOff>
-      <xdr:row>110</xdr:row>
+      <xdr:row>111</xdr:row>
       <xdr:rowOff>463574</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7928,13 +7931,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>111</xdr:row>
+      <xdr:row>112</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>431822</xdr:colOff>
-      <xdr:row>111</xdr:row>
+      <xdr:row>112</xdr:row>
       <xdr:rowOff>457223</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7972,13 +7975,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>113</xdr:row>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>54428</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>647733</xdr:colOff>
-      <xdr:row>113</xdr:row>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>403696</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8016,13 +8019,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>135</xdr:row>
+      <xdr:row>136</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>685835</xdr:colOff>
-      <xdr:row>135</xdr:row>
+      <xdr:row>136</xdr:row>
       <xdr:rowOff>476274</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8060,13 +8063,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>136</xdr:row>
+      <xdr:row>137</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>673135</xdr:colOff>
-      <xdr:row>136</xdr:row>
+      <xdr:row>137</xdr:row>
       <xdr:rowOff>482625</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8104,13 +8107,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>137</xdr:row>
+      <xdr:row>138</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>654084</xdr:colOff>
-      <xdr:row>137</xdr:row>
+      <xdr:row>138</xdr:row>
       <xdr:rowOff>463574</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8148,13 +8151,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>138</xdr:row>
+      <xdr:row>139</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>679485</xdr:colOff>
-      <xdr:row>138</xdr:row>
+      <xdr:row>139</xdr:row>
       <xdr:rowOff>476274</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8192,13 +8195,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>139</xdr:row>
+      <xdr:row>140</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>647733</xdr:colOff>
-      <xdr:row>139</xdr:row>
+      <xdr:row>140</xdr:row>
       <xdr:rowOff>457223</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8236,13 +8239,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>140</xdr:row>
+      <xdr:row>141</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>647733</xdr:colOff>
-      <xdr:row>140</xdr:row>
+      <xdr:row>141</xdr:row>
       <xdr:rowOff>457223</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8280,13 +8283,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>141</xdr:row>
+      <xdr:row>142</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>647733</xdr:colOff>
-      <xdr:row>141</xdr:row>
+      <xdr:row>142</xdr:row>
       <xdr:rowOff>457223</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8324,13 +8327,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>143</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>723937</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>143</xdr:row>
       <xdr:rowOff>488975</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9468,13 +9471,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>136071</xdr:colOff>
-      <xdr:row>121</xdr:row>
+      <xdr:row>122</xdr:row>
       <xdr:rowOff>27216</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>666012</xdr:colOff>
-      <xdr:row>121</xdr:row>
+      <xdr:row>122</xdr:row>
       <xdr:rowOff>495054</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9512,13 +9515,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>122</xdr:row>
+      <xdr:row>123</xdr:row>
       <xdr:rowOff>36285</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>656941</xdr:colOff>
-      <xdr:row>122</xdr:row>
+      <xdr:row>123</xdr:row>
       <xdr:rowOff>504123</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9556,13 +9559,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>102333</xdr:colOff>
-      <xdr:row>124</xdr:row>
+      <xdr:row>125</xdr:row>
       <xdr:rowOff>81643</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>695956</xdr:colOff>
-      <xdr:row>124</xdr:row>
+      <xdr:row>125</xdr:row>
       <xdr:rowOff>475915</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9600,13 +9603,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>123</xdr:row>
+      <xdr:row>124</xdr:row>
       <xdr:rowOff>34470</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>682341</xdr:colOff>
-      <xdr:row>123</xdr:row>
+      <xdr:row>124</xdr:row>
       <xdr:rowOff>502308</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9644,13 +9647,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>108857</xdr:colOff>
-      <xdr:row>125</xdr:row>
+      <xdr:row>126</xdr:row>
       <xdr:rowOff>45358</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>702480</xdr:colOff>
-      <xdr:row>125</xdr:row>
+      <xdr:row>126</xdr:row>
       <xdr:rowOff>439630</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9688,13 +9691,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>127</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>720623</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>127</xdr:row>
       <xdr:rowOff>457772</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9732,13 +9735,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>154214</xdr:colOff>
-      <xdr:row>127</xdr:row>
+      <xdr:row>128</xdr:row>
       <xdr:rowOff>54428</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>747837</xdr:colOff>
-      <xdr:row>127</xdr:row>
+      <xdr:row>128</xdr:row>
       <xdr:rowOff>448700</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9776,13 +9779,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>129</xdr:row>
       <xdr:rowOff>45357</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>720623</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>129</xdr:row>
       <xdr:rowOff>439629</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9820,13 +9823,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>172358</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:row>130</xdr:row>
       <xdr:rowOff>63501</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>693709</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:row>130</xdr:row>
       <xdr:rowOff>399405</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9864,13 +9867,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>86082</xdr:colOff>
-      <xdr:row>131</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>54429</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>722315</xdr:colOff>
-      <xdr:row>131</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>435429</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9908,13 +9911,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>125186</xdr:colOff>
-      <xdr:row>130</xdr:row>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>79829</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>646537</xdr:colOff>
-      <xdr:row>130</xdr:row>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>415733</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9952,13 +9955,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>151269</xdr:colOff>
-      <xdr:row>132</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>45357</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>758090</xdr:colOff>
-      <xdr:row>132</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>480786</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -9996,7 +9999,7 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>151269</xdr:colOff>
-      <xdr:row>133</xdr:row>
+      <xdr:row>134</xdr:row>
       <xdr:rowOff>45357</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="606821" cy="435429"/>
@@ -10035,13 +10038,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>198559</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>706419</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>417286</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10123,13 +10126,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>179917</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>52916</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>687777</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>470202</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10167,13 +10170,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>21166</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>634860</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>438452</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10211,13 +10214,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>137583</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>645443</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>480786</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10255,13 +10258,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>74084</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>10583</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>677334</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>493956</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10299,13 +10302,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>137584</xdr:colOff>
-      <xdr:row>85</xdr:row>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>10583</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>740834</xdr:colOff>
-      <xdr:row>85</xdr:row>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>493956</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10343,13 +10346,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>86</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>31750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>730250</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>7123</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10431,13 +10434,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>38652</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>11044</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>635583</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>487318</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10513,9 +10516,9 @@
   <xdr:oneCellAnchor>
     <xdr:from>
       <xdr:col>19</xdr:col>
-      <xdr:colOff>66261</xdr:colOff>
+      <xdr:colOff>112443</xdr:colOff>
       <xdr:row>67</xdr:row>
-      <xdr:rowOff>33130</xdr:rowOff>
+      <xdr:rowOff>21584</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="584230" cy="431822"/>
     <xdr:pic>
@@ -10539,7 +10542,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="22539739" y="34069130"/>
+          <a:off x="22556807" y="34057584"/>
           <a:ext cx="584230" cy="431822"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -10553,7 +10556,7 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>198559</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="507860" cy="417286"/>
@@ -10592,7 +10595,7 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>179917</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>52916</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="507860" cy="417286"/>
@@ -10631,7 +10634,7 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>76</xdr:row>
       <xdr:rowOff>21166</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="507860" cy="417286"/>
@@ -10670,7 +10673,7 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>73</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>21166</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="507860" cy="417286"/>
@@ -10709,7 +10712,7 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>83</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="641383" cy="444523"/>
@@ -10748,7 +10751,7 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>74084</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>10583</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="603250" cy="483373"/>
@@ -10787,7 +10790,7 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>137584</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>10583</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="603250" cy="483373"/>
@@ -10826,7 +10829,7 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>31750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="603250" cy="483373"/>
@@ -12310,7 +12313,7 @@
       <c r="T2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="U2" s="158" t="s">
+      <c r="U2" s="48" t="s">
         <v>673</v>
       </c>
     </row>
@@ -12368,7 +12371,7 @@
       <c r="T3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="U3" s="158" t="s">
+      <c r="U3" s="48" t="s">
         <v>673</v>
       </c>
     </row>
@@ -12426,7 +12429,7 @@
       <c r="T4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="U4" s="158" t="s">
+      <c r="U4" s="48" t="s">
         <v>673</v>
       </c>
     </row>
@@ -12484,7 +12487,7 @@
       <c r="T5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="U5" s="158" t="s">
+      <c r="U5" s="48" t="s">
         <v>673</v>
       </c>
     </row>
@@ -12542,7 +12545,7 @@
       <c r="T6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="U6" s="158" t="s">
+      <c r="U6" s="48" t="s">
         <v>673</v>
       </c>
     </row>
@@ -12600,7 +12603,7 @@
       <c r="T7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="U7" s="158" t="s">
+      <c r="U7" s="48" t="s">
         <v>673</v>
       </c>
     </row>
@@ -12658,7 +12661,7 @@
       <c r="T8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="U8" s="158" t="s">
+      <c r="U8" s="48" t="s">
         <v>673</v>
       </c>
     </row>
@@ -12716,7 +12719,7 @@
       <c r="T9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="U9" s="158" t="s">
+      <c r="U9" s="48" t="s">
         <v>673</v>
       </c>
     </row>
@@ -12774,7 +12777,7 @@
       <c r="T10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="U10" s="158" t="s">
+      <c r="U10" s="48" t="s">
         <v>673</v>
       </c>
     </row>
@@ -12832,7 +12835,7 @@
       <c r="T11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="U11" s="158" t="s">
+      <c r="U11" s="48" t="s">
         <v>673</v>
       </c>
     </row>
@@ -12890,7 +12893,7 @@
       <c r="T12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="U12" s="158" t="s">
+      <c r="U12" s="48" t="s">
         <v>673</v>
       </c>
     </row>
@@ -12948,7 +12951,7 @@
       <c r="T13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="U13" s="158" t="s">
+      <c r="U13" s="48" t="s">
         <v>673</v>
       </c>
     </row>
@@ -13006,7 +13009,7 @@
       <c r="T14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="U14" s="158" t="s">
+      <c r="U14" s="48" t="s">
         <v>673</v>
       </c>
     </row>
@@ -13064,7 +13067,7 @@
       <c r="T15" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="U15" s="158" t="s">
+      <c r="U15" s="48" t="s">
         <v>673</v>
       </c>
     </row>
@@ -13122,7 +13125,7 @@
       <c r="T16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="U16" s="158" t="s">
+      <c r="U16" s="48" t="s">
         <v>673</v>
       </c>
     </row>
@@ -13180,7 +13183,7 @@
       <c r="T17" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="U17" s="158" t="s">
+      <c r="U17" s="48" t="s">
         <v>673</v>
       </c>
     </row>
@@ -13257,7 +13260,7 @@
       <c r="T19" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U19" s="158" t="s">
+      <c r="U19" s="48" t="s">
         <v>674</v>
       </c>
     </row>
@@ -13335,7 +13338,7 @@
       <c r="T21" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U21" s="158" t="s">
+      <c r="U21" s="48" t="s">
         <v>674</v>
       </c>
     </row>
@@ -13391,7 +13394,7 @@
       <c r="T22" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U22" s="158" t="s">
+      <c r="U22" s="48" t="s">
         <v>674</v>
       </c>
     </row>
@@ -13469,7 +13472,7 @@
       <c r="T24" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U24" s="158" t="s">
+      <c r="U24" s="48" t="s">
         <v>674</v>
       </c>
     </row>
@@ -13543,7 +13546,7 @@
       <c r="T26" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U26" s="158" t="s">
+      <c r="U26" s="48" t="s">
         <v>156</v>
       </c>
     </row>
@@ -13597,7 +13600,7 @@
       <c r="T27" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U27" s="158" t="s">
+      <c r="U27" s="48" t="s">
         <v>156</v>
       </c>
     </row>
@@ -13651,7 +13654,7 @@
       <c r="T28" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U28" s="158" t="s">
+      <c r="U28" s="48" t="s">
         <v>156</v>
       </c>
     </row>
@@ -13705,7 +13708,7 @@
       <c r="T29" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U29" s="158" t="s">
+      <c r="U29" s="48" t="s">
         <v>156</v>
       </c>
     </row>
@@ -13759,7 +13762,7 @@
       <c r="T30" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U30" s="158" t="s">
+      <c r="U30" s="48" t="s">
         <v>156</v>
       </c>
     </row>
@@ -13813,7 +13816,7 @@
       <c r="T31" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U31" s="158" t="s">
+      <c r="U31" s="48" t="s">
         <v>156</v>
       </c>
     </row>
@@ -13867,7 +13870,7 @@
       <c r="T32" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U32" s="158" t="s">
+      <c r="U32" s="48" t="s">
         <v>156</v>
       </c>
     </row>
@@ -13921,7 +13924,7 @@
       <c r="T33" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U33" s="158" t="s">
+      <c r="U33" s="48" t="s">
         <v>156</v>
       </c>
     </row>
@@ -13975,7 +13978,7 @@
       <c r="T34" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U34" s="158" t="s">
+      <c r="U34" s="48" t="s">
         <v>156</v>
       </c>
     </row>
@@ -14029,7 +14032,7 @@
       <c r="T35" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U35" s="158" t="s">
+      <c r="U35" s="48" t="s">
         <v>156</v>
       </c>
     </row>
@@ -14103,7 +14106,7 @@
       <c r="T37" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U37" s="158" t="s">
+      <c r="U37" s="48" t="s">
         <v>156</v>
       </c>
     </row>
@@ -14156,7 +14159,7 @@
       <c r="T38" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="U38" s="158" t="s">
+      <c r="U38" s="48" t="s">
         <v>156</v>
       </c>
     </row>
@@ -23074,7 +23077,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB77DDB-B6D9-4CBA-9145-50EF6FDCE517}">
-  <dimension ref="A1:AA156"/>
+  <dimension ref="A1:AA157"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.1796875" style="3" customWidth="1"/>
@@ -25626,7 +25629,7 @@
     </row>
     <row r="54" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="str">
-        <f>Chaindrive!A41</f>
+        <f>Chaindrive!A42</f>
         <v>JM200</v>
       </c>
       <c r="B54" s="3" t="s">
@@ -25636,14 +25639,14 @@
         <v>0</v>
       </c>
       <c r="D54" s="23">
-        <f>Chaindrive!J41</f>
+        <f>Chaindrive!J42</f>
         <v>110.90909090909092</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F54" s="22">
-        <f>Chaindrive!L41</f>
+        <f>Chaindrive!L42</f>
         <v>6.1311475409836058</v>
       </c>
       <c r="G54" s="1">
@@ -25685,14 +25688,14 @@
         <v>15.01</v>
       </c>
       <c r="D55" s="23">
-        <f>Chaindrive!J42</f>
+        <f>Chaindrive!J43</f>
         <v>344.44444444444446</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F55" s="1">
-        <f>Chaindrive!L42</f>
+        <f>Chaindrive!L43</f>
         <v>6.12</v>
       </c>
       <c r="G55" s="1">
@@ -25734,14 +25737,14 @@
         <v>62.01</v>
       </c>
       <c r="D56" s="1">
-        <f>Chaindrive!J43</f>
+        <f>Chaindrive!J44</f>
         <v>608</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F56" s="1">
-        <f>Chaindrive!L43</f>
+        <f>Chaindrive!L44</f>
         <v>3.4375</v>
       </c>
       <c r="G56" s="1">
@@ -25805,7 +25808,7 @@
     </row>
     <row r="58" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="str">
-        <f>Chaindrive!A52</f>
+        <f>Chaindrive!A53</f>
         <v>F100c</v>
       </c>
       <c r="B58" s="3" t="s">
@@ -25815,14 +25818,14 @@
         <v>0</v>
       </c>
       <c r="D58" s="1">
-        <f>Chaindrive!J52</f>
+        <f>Chaindrive!J53</f>
         <v>300</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F58" s="1">
-        <f>Chaindrive!L45</f>
+        <f>Chaindrive!L46</f>
         <v>3.4375000000000004</v>
       </c>
       <c r="G58" s="1">
@@ -25849,7 +25852,7 @@
     </row>
     <row r="59" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="str">
-        <f>Chaindrive!A53</f>
+        <f>Chaindrive!A54</f>
         <v>F160c</v>
       </c>
       <c r="B59" s="3" t="s">
@@ -25859,14 +25862,14 @@
         <v>1</v>
       </c>
       <c r="D59" s="1">
-        <f>Chaindrive!J53</f>
+        <f>Chaindrive!J54</f>
         <v>608</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F59" s="1">
-        <f>Chaindrive!L46</f>
+        <f>Chaindrive!L47</f>
         <v>3.208333333333333</v>
       </c>
       <c r="G59" s="1">
@@ -26370,7 +26373,7 @@
     <row r="69" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="str">
         <f>Chaindrive!A15</f>
-        <v>Ranger150 3ph 12-57 5/8"</v>
+        <v>Ranger150 3ph 15-57 5/8"</v>
       </c>
       <c r="B69" t="s">
         <v>319</v>
@@ -26380,13 +26383,15 @@
         <v>342.01</v>
       </c>
       <c r="D69" s="23">
-        <v>713</v>
+        <f>Chaindrive!J15</f>
+        <v>566.19999999999993</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F69" s="2">
-        <v>10</v>
+        <f>Chaindrive!L15</f>
+        <v>12.368421052631579</v>
       </c>
       <c r="G69" s="1">
         <v>415</v>
@@ -26411,7 +26416,7 @@
       </c>
       <c r="O69" s="6">
         <f>Chaindrive!O15</f>
-        <v>8.4210526315789469</v>
+        <v>10.526315789473685</v>
       </c>
       <c r="P69" s="1">
         <v>11</v>
@@ -26420,33 +26425,33 @@
         <v>400</v>
       </c>
       <c r="S69" s="6" t="s">
-        <v>322</v>
+        <v>676</v>
       </c>
       <c r="U69" s="153">
         <v>472.24</v>
       </c>
+      <c r="V69" s="83"/>
     </row>
     <row r="70" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="str">
-        <f>Chaindrive!A17</f>
-        <v>Ranger220 3ph 15-57 3/4"</v>
+        <f>Chaindrive!A16</f>
+        <v>Ranger150 3ph 12-57 5/8"</v>
       </c>
       <c r="B70" t="s">
         <v>319</v>
       </c>
       <c r="C70" s="2">
-        <v>713.01</v>
+        <f>D67+0.01</f>
+        <v>342.01</v>
       </c>
       <c r="D70" s="23">
-        <f>Chaindrive!J17</f>
-        <v>836</v>
+        <v>713</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F70" s="2">
-        <f>Chaindrive!L17</f>
-        <v>6.3157894736842106</v>
+        <v>10</v>
       </c>
       <c r="G70" s="1">
         <v>415</v>
@@ -26461,7 +26466,7 @@
         <v>260</v>
       </c>
       <c r="L70" s="1">
-        <v>30</v>
+        <v>25.4</v>
       </c>
       <c r="M70" s="1" t="s">
         <v>22</v>
@@ -26470,118 +26475,123 @@
         <v>22</v>
       </c>
       <c r="O70" s="6">
-        <f>Chaindrive!O17</f>
+        <f>Chaindrive!O16</f>
+        <v>8.4210526315789469</v>
+      </c>
+      <c r="P70" s="1">
+        <v>11</v>
+      </c>
+      <c r="R70" s="6">
+        <v>400</v>
+      </c>
+      <c r="S70" s="6" t="s">
+        <v>322</v>
+      </c>
+      <c r="U70" s="153">
+        <v>472.24</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A71" s="3" t="str">
+        <f>Chaindrive!A18</f>
+        <v>Ranger220 3ph 15-57 3/4"</v>
+      </c>
+      <c r="B71" t="s">
+        <v>319</v>
+      </c>
+      <c r="C71" s="2">
+        <v>713.01</v>
+      </c>
+      <c r="D71" s="23">
+        <f>Chaindrive!J18</f>
+        <v>836</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F71" s="2">
+        <f>Chaindrive!L18</f>
+        <v>6.3157894736842106</v>
+      </c>
+      <c r="G71" s="1">
+        <v>415</v>
+      </c>
+      <c r="H71" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I71" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K71" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="L71" s="1">
+        <v>30</v>
+      </c>
+      <c r="M71" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N71" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O71" s="6">
+        <f>Chaindrive!O18</f>
         <v>10.526315789473685</v>
       </c>
-      <c r="P70" s="1">
+      <c r="P71" s="1">
         <v>10</v>
       </c>
-      <c r="R70" s="6">
+      <c r="R71" s="6">
         <v>650</v>
       </c>
-      <c r="U70" s="153">
+      <c r="U71" s="153">
         <v>498.07</v>
       </c>
     </row>
-    <row r="71" spans="1:23" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="106" t="s">
+    <row r="72" spans="1:23" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="B71" s="106" t="s">
+      <c r="B72" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="C71" s="106" t="s">
+      <c r="C72" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="D71" s="106" t="s">
+      <c r="D72" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="E71" s="107"/>
-      <c r="F71" s="112"/>
-      <c r="G71" s="107"/>
-      <c r="H71" s="108" t="s">
+      <c r="E72" s="107"/>
+      <c r="F72" s="112"/>
+      <c r="G72" s="107"/>
+      <c r="H72" s="108" t="s">
         <v>472</v>
       </c>
-      <c r="I71" s="107"/>
-      <c r="J71" s="107"/>
-      <c r="K71" s="107"/>
-      <c r="L71" s="107"/>
-      <c r="M71" s="107"/>
-      <c r="N71" s="108" t="s">
+      <c r="I72" s="107"/>
+      <c r="J72" s="107"/>
+      <c r="K72" s="107"/>
+      <c r="L72" s="107"/>
+      <c r="M72" s="107"/>
+      <c r="N72" s="108" t="s">
         <v>472</v>
       </c>
-      <c r="O71" s="110"/>
-      <c r="P71" s="107"/>
-      <c r="Q71" s="107"/>
-      <c r="R71" s="110"/>
-      <c r="S71" s="110"/>
-      <c r="U71" s="111"/>
-    </row>
-    <row r="72" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="3" t="str">
-        <f>Chaindrive!A20</f>
-        <v>Ranger 90 Fi 1ph 15-57 1/2"</v>
-      </c>
-      <c r="B72" t="s">
-        <v>319</v>
-      </c>
-      <c r="C72" s="2">
-        <v>0</v>
-      </c>
-      <c r="D72" s="23">
-        <f>Chaindrive!J20</f>
-        <v>342</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="F72" s="22">
-        <f>Chaindrive!L20</f>
-        <v>21.05263157894737</v>
-      </c>
-      <c r="G72" s="1">
-        <v>230</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K72" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="L72" s="1">
-        <v>25.4</v>
-      </c>
-      <c r="M72" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N72" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O72" s="6">
-        <f>Chaindrive!O20</f>
-        <v>5.2631578947368425</v>
-      </c>
-      <c r="P72" s="1">
-        <v>18</v>
-      </c>
-      <c r="R72" s="6">
-        <v>850</v>
-      </c>
+      <c r="O72" s="110"/>
+      <c r="P72" s="107"/>
+      <c r="Q72" s="107"/>
+      <c r="R72" s="110"/>
+      <c r="S72" s="110"/>
+      <c r="U72" s="111"/>
     </row>
     <row r="73" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="str">
         <f>Chaindrive!A21</f>
-        <v>Ranger 90 Fi 3ph 15-57 1/2"</v>
+        <v>Ranger 90 Fi 1ph 15-57 1/2"</v>
       </c>
       <c r="B73" t="s">
         <v>319</v>
       </c>
       <c r="C73" s="2">
-        <f t="shared" ref="C73:C74" si="2">D72+0.01</f>
-        <v>342.01</v>
+        <v>0</v>
       </c>
       <c r="D73" s="23">
         <f>Chaindrive!J21</f>
@@ -26595,7 +26605,7 @@
         <v>21.05263157894737</v>
       </c>
       <c r="G73" s="1">
-        <v>415</v>
+        <v>230</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>313</v>
@@ -26629,28 +26639,28 @@
     <row r="74" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="str">
         <f>Chaindrive!A22</f>
-        <v>Ranger140 Fi 1ph 18-57 5/8"</v>
+        <v>Ranger 90 Fi 3ph 15-57 1/2"</v>
       </c>
       <c r="B74" t="s">
         <v>319</v>
       </c>
       <c r="C74" s="2">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="C74:C75" si="2">D73+0.01</f>
         <v>342.01</v>
       </c>
       <c r="D74" s="23">
         <f>Chaindrive!J22</f>
-        <v>475</v>
+        <v>342</v>
       </c>
       <c r="E74" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F74" s="22">
         <f>Chaindrive!L22</f>
-        <v>25.263157894736842</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="G74" s="1">
-        <v>230</v>
+        <v>415</v>
       </c>
       <c r="H74" s="1" t="s">
         <v>313</v>
@@ -26672,7 +26682,7 @@
       </c>
       <c r="O74" s="6">
         <f>Chaindrive!O22</f>
-        <v>6.3157894736842106</v>
+        <v>5.2631578947368425</v>
       </c>
       <c r="P74" s="1">
         <v>18</v>
@@ -26684,14 +26694,14 @@
     <row r="75" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="str">
         <f>Chaindrive!A23</f>
-        <v>Ranger140 Fi 3ph 18-57 5/8"</v>
+        <v>Ranger140 Fi 1ph 18-57 5/8"</v>
       </c>
       <c r="B75" t="s">
         <v>319</v>
       </c>
       <c r="C75" s="2">
-        <f>D74+0.01</f>
-        <v>475.01</v>
+        <f t="shared" si="2"/>
+        <v>342.01</v>
       </c>
       <c r="D75" s="23">
         <f>Chaindrive!J23</f>
@@ -26705,7 +26715,7 @@
         <v>25.263157894736842</v>
       </c>
       <c r="G75" s="1">
-        <v>415</v>
+        <v>230</v>
       </c>
       <c r="H75" s="1" t="s">
         <v>313</v>
@@ -26739,28 +26749,28 @@
     <row r="76" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="str">
         <f>Chaindrive!A24</f>
-        <v>Ranger140 fi 1ph 12-57 5/8"</v>
+        <v>Ranger140 Fi 3ph 18-57 5/8"</v>
       </c>
       <c r="B76" t="s">
         <v>319</v>
       </c>
       <c r="C76" s="2">
-        <f t="shared" ref="C76:C77" si="3">D75+0.01</f>
+        <f>D75+0.01</f>
         <v>475.01</v>
       </c>
       <c r="D76" s="23">
         <f>Chaindrive!J24</f>
-        <v>712.5</v>
+        <v>475</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F76" s="22">
         <f>Chaindrive!L24</f>
-        <v>16.842105263157894</v>
+        <v>25.263157894736842</v>
       </c>
       <c r="G76" s="1">
-        <v>230</v>
+        <v>415</v>
       </c>
       <c r="H76" s="1" t="s">
         <v>313</v>
@@ -26782,7 +26792,7 @@
       </c>
       <c r="O76" s="6">
         <f>Chaindrive!O24</f>
-        <v>4.2105263157894735</v>
+        <v>6.3157894736842106</v>
       </c>
       <c r="P76" s="1">
         <v>18</v>
@@ -26794,14 +26804,14 @@
     <row r="77" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="str">
         <f>Chaindrive!A25</f>
-        <v>Ranger140 fi 3ph 12-57 5/8"</v>
+        <v>Ranger140 fi 1ph 12-57 5/8"</v>
       </c>
       <c r="B77" t="s">
         <v>319</v>
       </c>
       <c r="C77" s="2">
-        <f t="shared" si="3"/>
-        <v>712.51</v>
+        <f t="shared" ref="C77:C78" si="3">D76+0.01</f>
+        <v>475.01</v>
       </c>
       <c r="D77" s="23">
         <f>Chaindrive!J25</f>
@@ -26815,7 +26825,7 @@
         <v>16.842105263157894</v>
       </c>
       <c r="G77" s="1">
-        <v>415</v>
+        <v>230</v>
       </c>
       <c r="H77" s="1" t="s">
         <v>313</v>
@@ -26846,93 +26856,92 @@
         <v>850</v>
       </c>
     </row>
-    <row r="78" spans="1:23" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A78" s="106"/>
-      <c r="C78" s="107"/>
-      <c r="D78" s="115"/>
-      <c r="E78" s="107"/>
-      <c r="F78" s="112"/>
-      <c r="G78" s="107"/>
-      <c r="H78" s="107"/>
-      <c r="I78" s="107"/>
-      <c r="J78" s="107"/>
-      <c r="K78" s="107"/>
-      <c r="L78" s="107"/>
-      <c r="M78" s="107"/>
-      <c r="N78" s="107"/>
-      <c r="O78" s="110"/>
-      <c r="P78" s="107"/>
-      <c r="Q78" s="107"/>
-      <c r="R78" s="110"/>
-      <c r="S78" s="110"/>
-      <c r="U78" s="111"/>
-    </row>
-    <row r="79" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="3" t="str">
-        <f>Chaindrive!A28</f>
-        <v>KE 40.24  15-57 3/4"</v>
-      </c>
-      <c r="B79" t="s">
+    <row r="78" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A78" s="3" t="str">
+        <f>Chaindrive!A26</f>
+        <v>Ranger140 fi 3ph 12-57 5/8"</v>
+      </c>
+      <c r="B78" t="s">
         <v>319</v>
       </c>
-      <c r="C79" s="1">
-        <v>600.01</v>
-      </c>
-      <c r="D79" s="23">
-        <f>Chaindrive!J28</f>
-        <v>1520</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F79" s="2">
-        <f>Chaindrive!L28</f>
-        <v>6.3157894736842106</v>
-      </c>
-      <c r="G79" s="1">
-        <f>Chaindrive!M28</f>
+      <c r="C78" s="2">
+        <f t="shared" si="3"/>
+        <v>712.51</v>
+      </c>
+      <c r="D78" s="23">
+        <f>Chaindrive!J26</f>
+        <v>712.5</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="F78" s="22">
+        <f>Chaindrive!L26</f>
+        <v>16.842105263157894</v>
+      </c>
+      <c r="G78" s="1">
         <v>415</v>
       </c>
-      <c r="H79" s="1" t="s">
+      <c r="H78" s="1" t="s">
         <v>313</v>
       </c>
-      <c r="I79" s="1" t="s">
+      <c r="I78" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="K79" s="1" t="s">
+      <c r="K78" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L79" s="1">
-        <f>Chaindrive!D28</f>
-        <v>40</v>
-      </c>
-      <c r="M79" s="1" t="s">
+      <c r="L78" s="1">
+        <v>25.4</v>
+      </c>
+      <c r="M78" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="N79" s="1" t="s">
+      <c r="N78" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O79" s="6">
-        <f>Chaindrive!O28</f>
-        <v>10.526315789473685</v>
-      </c>
-      <c r="P79" s="1">
-        <v>11</v>
-      </c>
-      <c r="R79" s="6">
+      <c r="O78" s="6">
+        <f>Chaindrive!O26</f>
+        <v>4.2105263157894735</v>
+      </c>
+      <c r="P78" s="1">
+        <v>18</v>
+      </c>
+      <c r="R78" s="6">
         <v>850</v>
       </c>
+    </row>
+    <row r="79" spans="1:23" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="106"/>
+      <c r="C79" s="107"/>
+      <c r="D79" s="115"/>
+      <c r="E79" s="107"/>
+      <c r="F79" s="112"/>
+      <c r="G79" s="107"/>
+      <c r="H79" s="107"/>
+      <c r="I79" s="107"/>
+      <c r="J79" s="107"/>
+      <c r="K79" s="107"/>
+      <c r="L79" s="107"/>
+      <c r="M79" s="107"/>
+      <c r="N79" s="107"/>
+      <c r="O79" s="110"/>
+      <c r="P79" s="107"/>
+      <c r="Q79" s="107"/>
+      <c r="R79" s="110"/>
+      <c r="S79" s="110"/>
+      <c r="U79" s="111"/>
     </row>
     <row r="80" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="str">
         <f>Chaindrive!A29</f>
-        <v>KE 40.24  15-57 1"</v>
+        <v>KE 40.24  15-57 3/4"</v>
       </c>
       <c r="B80" t="s">
         <v>319</v>
       </c>
-      <c r="C80" s="2">
-        <v>900.01</v>
+      <c r="C80" s="1">
+        <v>600.01</v>
       </c>
       <c r="D80" s="23">
         <f>Chaindrive!J29</f>
@@ -26955,7 +26964,6 @@
       <c r="I80" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="J80" s="3"/>
       <c r="K80" s="1" t="s">
         <v>260</v>
       </c>
@@ -26977,23 +26985,23 @@
         <v>11</v>
       </c>
       <c r="R80" s="6">
-        <v>1100</v>
+        <v>850</v>
       </c>
     </row>
     <row r="81" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A81" s="3" t="str">
         <f>Chaindrive!A30</f>
-        <v>KE 60.24   15-57 1"</v>
+        <v>KE 40.24  15-57 1"</v>
       </c>
       <c r="B81" t="s">
         <v>319</v>
       </c>
       <c r="C81" s="2">
-        <v>1200.01</v>
+        <v>900.01</v>
       </c>
       <c r="D81" s="23">
         <f>Chaindrive!J30</f>
-        <v>2280</v>
+        <v>1520</v>
       </c>
       <c r="E81" s="1" t="s">
         <v>156</v>
@@ -27012,12 +27020,13 @@
       <c r="I81" s="1" t="s">
         <v>260</v>
       </c>
+      <c r="J81" s="3"/>
       <c r="K81" s="1" t="s">
         <v>260</v>
       </c>
       <c r="L81" s="1">
         <f>Chaindrive!D30</f>
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="M81" s="1" t="s">
         <v>22</v>
@@ -27027,29 +27036,29 @@
       </c>
       <c r="O81" s="6">
         <f>Chaindrive!O30</f>
-        <v>15.789473684210527</v>
+        <v>10.526315789473685</v>
       </c>
       <c r="P81" s="1">
         <v>11</v>
       </c>
       <c r="R81" s="6">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="82" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="str">
         <f>Chaindrive!A31</f>
-        <v>KE 80.24   15-57 1"</v>
+        <v>KE 60.24   15-57 1"</v>
       </c>
       <c r="B82" t="s">
         <v>319</v>
       </c>
       <c r="C82" s="2">
-        <v>1800.01</v>
+        <v>1200.01</v>
       </c>
       <c r="D82" s="23">
         <f>Chaindrive!J31</f>
-        <v>3040</v>
+        <v>2280</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>156</v>
@@ -27086,16 +27095,16 @@
         <v>15.789473684210527</v>
       </c>
       <c r="P82" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R82" s="6">
-        <v>2000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="83" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="str">
         <f>Chaindrive!A32</f>
-        <v>KE 80.24   15-57 1 1/4"</v>
+        <v>KE 80.24   15-57 1"</v>
       </c>
       <c r="B83" t="s">
         <v>319</v>
@@ -27148,121 +27157,117 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="84" spans="1:22" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A84" s="106" t="s">
+    <row r="84" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A84" s="3" t="str">
+        <f>Chaindrive!A33</f>
+        <v>KE 80.24   15-57 1 1/4"</v>
+      </c>
+      <c r="B84" t="s">
+        <v>319</v>
+      </c>
+      <c r="C84" s="2">
+        <v>1800.01</v>
+      </c>
+      <c r="D84" s="23">
+        <f>Chaindrive!J33</f>
+        <v>3040</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F84" s="2">
+        <f>Chaindrive!L33</f>
+        <v>6.3157894736842106</v>
+      </c>
+      <c r="G84" s="1">
+        <f>Chaindrive!M33</f>
+        <v>415</v>
+      </c>
+      <c r="H84" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I84" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K84" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="L84" s="1">
+        <f>Chaindrive!D33</f>
+        <v>55</v>
+      </c>
+      <c r="M84" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N84" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O84" s="6">
+        <f>Chaindrive!O33</f>
+        <v>15.789473684210527</v>
+      </c>
+      <c r="P84" s="1">
+        <v>12</v>
+      </c>
+      <c r="R84" s="6">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="B84" s="106" t="s">
+      <c r="B85" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="C84" s="106" t="s">
+      <c r="C85" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="D84" s="106" t="s">
+      <c r="D85" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="E84" s="107"/>
-      <c r="F84" s="112"/>
-      <c r="G84" s="107"/>
-      <c r="H84" s="108" t="s">
+      <c r="E85" s="107"/>
+      <c r="F85" s="112"/>
+      <c r="G85" s="107"/>
+      <c r="H85" s="108" t="s">
         <v>472</v>
       </c>
-      <c r="I84" s="107"/>
-      <c r="J84" s="107"/>
-      <c r="K84" s="107"/>
-      <c r="L84" s="107"/>
-      <c r="M84" s="107"/>
-      <c r="N84" s="108" t="s">
+      <c r="I85" s="107"/>
+      <c r="J85" s="107"/>
+      <c r="K85" s="107"/>
+      <c r="L85" s="107"/>
+      <c r="M85" s="107"/>
+      <c r="N85" s="108" t="s">
         <v>472</v>
       </c>
-      <c r="O84" s="110"/>
-      <c r="P84" s="107"/>
-      <c r="Q84" s="107"/>
-      <c r="R84" s="110"/>
-      <c r="S84" s="110"/>
-      <c r="U84" s="111"/>
-    </row>
-    <row r="85" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="3" t="str">
-        <f>Chaindrive!A35</f>
-        <v>KE 40.40 Fi 15-57 3/4"</v>
-      </c>
-      <c r="B85" s="57" t="s">
-        <v>319</v>
-      </c>
-      <c r="C85" s="1">
-        <v>0</v>
-      </c>
-      <c r="D85" s="23">
-        <f>Chaindrive!J35</f>
-        <v>1140</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="F85" s="2">
-        <f>Chaindrive!L35</f>
-        <v>10.526315789473685</v>
-      </c>
-      <c r="G85" s="1">
-        <v>230</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="J85" s="1"/>
-      <c r="K85" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="L85" s="1">
-        <f>Chaindrive!R35</f>
-        <v>40</v>
-      </c>
-      <c r="M85" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N85" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O85" s="1">
-        <f>Chaindrive!O35</f>
-        <v>10.526315789473685</v>
-      </c>
-      <c r="P85" s="1">
-        <v>17</v>
-      </c>
-      <c r="Q85" s="1"/>
-      <c r="R85" s="1">
-        <v>1500</v>
-      </c>
-      <c r="S85" s="1"/>
-      <c r="U85" s="113"/>
+      <c r="O85" s="110"/>
+      <c r="P85" s="107"/>
+      <c r="Q85" s="107"/>
+      <c r="R85" s="110"/>
+      <c r="S85" s="110"/>
+      <c r="U85" s="111"/>
     </row>
     <row r="86" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="3" t="str">
-        <f>Chaindrive!A37</f>
-        <v>KE 50.80 Fi 15-57 1"</v>
+        <f>Chaindrive!A36</f>
+        <v>KE 40.40 Fi 15-57 3/4"</v>
       </c>
       <c r="B86" s="57" t="s">
         <v>319</v>
       </c>
-      <c r="C86" s="2">
-        <f>D85+0.01</f>
-        <v>1140.01</v>
+      <c r="C86" s="1">
+        <v>0</v>
       </c>
       <c r="D86" s="23">
-        <f>Chaindrive!J37</f>
-        <v>1900</v>
+        <f>Chaindrive!J36</f>
+        <v>1140</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F86" s="2">
-        <f>Chaindrive!L37</f>
-        <v>21.05263157894737</v>
+        <f>Chaindrive!L36</f>
+        <v>10.526315789473685</v>
       </c>
       <c r="G86" s="1">
         <v>230</v>
@@ -27278,8 +27283,8 @@
         <v>260</v>
       </c>
       <c r="L86" s="1">
-        <f>Chaindrive!R37</f>
-        <v>55</v>
+        <f>Chaindrive!R36</f>
+        <v>40</v>
       </c>
       <c r="M86" s="1" t="s">
         <v>22</v>
@@ -27288,15 +27293,15 @@
         <v>22</v>
       </c>
       <c r="O86" s="1">
-        <f>Chaindrive!O37</f>
-        <v>15.789473684210527</v>
+        <f>Chaindrive!O36</f>
+        <v>10.526315789473685</v>
       </c>
       <c r="P86" s="1">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q86" s="1"/>
       <c r="R86" s="1">
-        <v>4500</v>
+        <v>1500</v>
       </c>
       <c r="S86" s="1"/>
       <c r="U86" s="113"/>
@@ -27304,25 +27309,25 @@
     <row r="87" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A87" s="3" t="str">
         <f>Chaindrive!A38</f>
-        <v>KE 80.40 Fi 15-57 1"</v>
+        <v>KE 50.80 Fi 15-57 1"</v>
       </c>
       <c r="B87" s="57" t="s">
         <v>319</v>
       </c>
       <c r="C87" s="2">
         <f>D86+0.01</f>
-        <v>1900.01</v>
+        <v>1140.01</v>
       </c>
       <c r="D87" s="23">
         <f>Chaindrive!J38</f>
-        <v>3040</v>
+        <v>1900</v>
       </c>
       <c r="E87" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F87" s="2">
         <f>Chaindrive!L38</f>
-        <v>10.526315789473685</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="G87" s="1">
         <v>230</v>
@@ -27352,7 +27357,7 @@
         <v>15.789473684210527</v>
       </c>
       <c r="P87" s="1">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q87" s="1"/>
       <c r="R87" s="1">
@@ -27363,28 +27368,29 @@
     </row>
     <row r="88" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="str">
-        <f>Chaindrive!A35</f>
-        <v>KE 40.40 Fi 15-57 3/4"</v>
+        <f>Chaindrive!A39</f>
+        <v>KE 80.40 Fi 15-57 1"</v>
       </c>
       <c r="B88" s="57" t="s">
         <v>319</v>
       </c>
-      <c r="C88" s="1">
-        <v>0</v>
+      <c r="C88" s="2">
+        <f>D87+0.01</f>
+        <v>1900.01</v>
       </c>
       <c r="D88" s="23">
-        <f>Chaindrive!J35</f>
-        <v>1140</v>
+        <f>Chaindrive!J39</f>
+        <v>3040</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F88" s="2">
-        <f>Chaindrive!L35</f>
+        <f>Chaindrive!L39</f>
         <v>10.526315789473685</v>
       </c>
       <c r="G88" s="1">
-        <v>415</v>
+        <v>230</v>
       </c>
       <c r="H88" s="1" t="s">
         <v>313</v>
@@ -27397,8 +27403,8 @@
         <v>260</v>
       </c>
       <c r="L88" s="1">
-        <f>Chaindrive!R35</f>
-        <v>40</v>
+        <f>Chaindrive!R39</f>
+        <v>55</v>
       </c>
       <c r="M88" s="1" t="s">
         <v>22</v>
@@ -27407,15 +27413,15 @@
         <v>22</v>
       </c>
       <c r="O88" s="1">
-        <f>Chaindrive!O35</f>
-        <v>10.526315789473685</v>
+        <f>Chaindrive!O39</f>
+        <v>15.789473684210527</v>
       </c>
       <c r="P88" s="1">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Q88" s="1"/>
       <c r="R88" s="1">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="S88" s="1"/>
       <c r="U88" s="113"/>
@@ -27423,14 +27429,13 @@
     <row r="89" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="str">
         <f>Chaindrive!A36</f>
-        <v>KE 40.40 Fi 15-57 1"</v>
+        <v>KE 40.40 Fi 15-57 3/4"</v>
       </c>
       <c r="B89" s="57" t="s">
         <v>319</v>
       </c>
-      <c r="C89" s="2">
-        <f>D88+0.01</f>
-        <v>1140.01</v>
+      <c r="C89" s="1">
+        <v>0</v>
       </c>
       <c r="D89" s="23">
         <f>Chaindrive!J36</f>
@@ -27471,11 +27476,11 @@
         <v>10.526315789473685</v>
       </c>
       <c r="P89" s="1">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q89" s="1"/>
       <c r="R89" s="1">
-        <v>4500</v>
+        <v>1500</v>
       </c>
       <c r="S89" s="1"/>
       <c r="U89" s="113"/>
@@ -27483,7 +27488,7 @@
     <row r="90" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="3" t="str">
         <f>Chaindrive!A37</f>
-        <v>KE 50.80 Fi 15-57 1"</v>
+        <v>KE 40.40 Fi 15-57 1"</v>
       </c>
       <c r="B90" s="57" t="s">
         <v>319</v>
@@ -27494,14 +27499,14 @@
       </c>
       <c r="D90" s="23">
         <f>Chaindrive!J37</f>
-        <v>1900</v>
+        <v>1140</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F90" s="2">
         <f>Chaindrive!L37</f>
-        <v>21.05263157894737</v>
+        <v>10.526315789473685</v>
       </c>
       <c r="G90" s="1">
         <v>415</v>
@@ -27518,7 +27523,7 @@
       </c>
       <c r="L90" s="1">
         <f>Chaindrive!R37</f>
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="M90" s="1" t="s">
         <v>22</v>
@@ -27528,10 +27533,10 @@
       </c>
       <c r="O90" s="1">
         <f>Chaindrive!O37</f>
-        <v>15.789473684210527</v>
+        <v>10.526315789473685</v>
       </c>
       <c r="P90" s="1">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q90" s="1"/>
       <c r="R90" s="1">
@@ -27540,128 +27545,126 @@
       <c r="S90" s="1"/>
       <c r="U90" s="113"/>
     </row>
-    <row r="91" spans="1:22" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A91" s="106"/>
-      <c r="B91" s="106"/>
-      <c r="C91" s="106"/>
-      <c r="D91" s="106"/>
-      <c r="E91" s="107"/>
-      <c r="F91" s="112"/>
-      <c r="G91" s="107"/>
-      <c r="H91" s="108"/>
-      <c r="I91" s="107"/>
-      <c r="J91" s="107"/>
-      <c r="K91" s="107"/>
-      <c r="L91" s="107"/>
-      <c r="M91" s="107"/>
-      <c r="N91" s="108"/>
-      <c r="O91" s="110"/>
-      <c r="P91" s="107"/>
-      <c r="Q91" s="107"/>
-      <c r="R91" s="110"/>
-      <c r="S91" s="110"/>
-      <c r="U91" s="111"/>
-    </row>
-    <row r="92" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B92" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C92" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="D92" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="H92" s="97" t="s">
-        <v>472</v>
-      </c>
-      <c r="N92" s="97" t="s">
-        <v>472</v>
-      </c>
-      <c r="O92" s="1"/>
-      <c r="R92" s="1"/>
-      <c r="S92" s="1"/>
-      <c r="T92" s="57"/>
-      <c r="U92" s="113"/>
-      <c r="V92" s="57"/>
+    <row r="91" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A91" s="3" t="str">
+        <f>Chaindrive!A38</f>
+        <v>KE 50.80 Fi 15-57 1"</v>
+      </c>
+      <c r="B91" s="57" t="s">
+        <v>319</v>
+      </c>
+      <c r="C91" s="2">
+        <f>D90+0.01</f>
+        <v>1140.01</v>
+      </c>
+      <c r="D91" s="23">
+        <f>Chaindrive!J38</f>
+        <v>1900</v>
+      </c>
+      <c r="E91" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="F91" s="2">
+        <f>Chaindrive!L38</f>
+        <v>21.05263157894737</v>
+      </c>
+      <c r="G91" s="1">
+        <v>415</v>
+      </c>
+      <c r="H91" s="1" t="s">
+        <v>313</v>
+      </c>
+      <c r="I91" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="J91" s="1"/>
+      <c r="K91" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="L91" s="1">
+        <f>Chaindrive!R38</f>
+        <v>55</v>
+      </c>
+      <c r="M91" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N91" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O91" s="1">
+        <f>Chaindrive!O38</f>
+        <v>15.789473684210527</v>
+      </c>
+      <c r="P91" s="1">
+        <v>12</v>
+      </c>
+      <c r="Q91" s="1"/>
+      <c r="R91" s="1">
+        <v>4500</v>
+      </c>
+      <c r="S91" s="1"/>
+      <c r="U91" s="113"/>
+    </row>
+    <row r="92" spans="1:22" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="106"/>
+      <c r="B92" s="106"/>
+      <c r="C92" s="106"/>
+      <c r="D92" s="106"/>
+      <c r="E92" s="107"/>
+      <c r="F92" s="112"/>
+      <c r="G92" s="107"/>
+      <c r="H92" s="108"/>
+      <c r="I92" s="107"/>
+      <c r="J92" s="107"/>
+      <c r="K92" s="107"/>
+      <c r="L92" s="107"/>
+      <c r="M92" s="107"/>
+      <c r="N92" s="108"/>
+      <c r="O92" s="110"/>
+      <c r="P92" s="107"/>
+      <c r="Q92" s="107"/>
+      <c r="R92" s="110"/>
+      <c r="S92" s="110"/>
+      <c r="U92" s="111"/>
     </row>
     <row r="93" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="H93" s="97" t="s">
+        <v>472</v>
+      </c>
+      <c r="N93" s="97" t="s">
+        <v>472</v>
+      </c>
+      <c r="O93" s="1"/>
+      <c r="R93" s="1"/>
+      <c r="S93" s="1"/>
+      <c r="T93" s="57"/>
+      <c r="U93" s="113"/>
+      <c r="V93" s="57"/>
+    </row>
+    <row r="94" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="3" t="s">
         <v>578</v>
       </c>
-      <c r="B93" s="3" t="s">
+      <c r="B94" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="C93" s="1">
+      <c r="C94" s="1">
         <v>0</v>
       </c>
-      <c r="D93" s="1">
+      <c r="D94" s="1">
         <v>100</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F93" s="1">
-        <v>15</v>
-      </c>
-      <c r="G93" s="1">
-        <v>415</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K93" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="L93" s="1">
-        <v>30</v>
-      </c>
-      <c r="M93" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N93" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O93" s="1">
-        <v>20</v>
-      </c>
-      <c r="P93" s="1">
-        <v>8</v>
-      </c>
-      <c r="Q93" s="1">
-        <v>15</v>
-      </c>
-      <c r="R93" s="1">
-        <v>300</v>
-      </c>
-      <c r="S93" s="1" t="s">
-        <v>323</v>
-      </c>
-      <c r="T93" s="57"/>
-      <c r="U93" s="150">
-        <v>266.06</v>
-      </c>
-      <c r="V93" s="57"/>
-    </row>
-    <row r="94" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="57" t="s">
-        <v>324</v>
-      </c>
-      <c r="B94" s="57" t="s">
-        <v>319</v>
-      </c>
-      <c r="C94" s="1">
-        <f>D93+0.01</f>
-        <v>100.01</v>
-      </c>
-      <c r="D94" s="1">
-        <v>170</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>156</v>
@@ -27697,33 +27700,33 @@
         <v>8</v>
       </c>
       <c r="Q94" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="R94" s="1">
-        <v>450</v>
+        <v>300</v>
       </c>
       <c r="S94" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="T94" s="57"/>
       <c r="U94" s="150">
-        <v>280.37</v>
+        <v>266.06</v>
       </c>
       <c r="V94" s="57"/>
     </row>
     <row r="95" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="57" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B95" s="57" t="s">
         <v>319</v>
       </c>
       <c r="C95" s="1">
         <f>D94+0.01</f>
-        <v>170.01</v>
+        <v>100.01</v>
       </c>
       <c r="D95" s="1">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>156</v>
@@ -27756,36 +27759,36 @@
         <v>20</v>
       </c>
       <c r="P95" s="1">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="Q95" s="1">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="R95" s="1">
-        <v>750</v>
+        <v>450</v>
       </c>
       <c r="S95" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="T95" s="57"/>
       <c r="U95" s="150">
-        <v>307.35000000000002</v>
+        <v>280.37</v>
       </c>
       <c r="V95" s="57"/>
     </row>
     <row r="96" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A96" s="57" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B96" s="57" t="s">
         <v>319</v>
       </c>
       <c r="C96" s="1">
-        <f t="shared" ref="C96:C104" si="4">D95+0.01</f>
-        <v>250.01</v>
+        <f>D95+0.01</f>
+        <v>170.01</v>
       </c>
       <c r="D96" s="1">
-        <v>350</v>
+        <v>250</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>156</v>
@@ -27806,7 +27809,7 @@
         <v>260</v>
       </c>
       <c r="L96" s="1">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M96" s="1" t="s">
         <v>55</v>
@@ -27818,562 +27821,567 @@
         <v>20</v>
       </c>
       <c r="P96" s="1">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="Q96" s="1">
+        <v>19</v>
       </c>
       <c r="R96" s="1">
-        <v>850</v>
+        <v>750</v>
       </c>
       <c r="S96" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="T96" s="57"/>
-      <c r="U96" s="149">
-        <v>383.55</v>
+      <c r="U96" s="150">
+        <v>307.35000000000002</v>
       </c>
       <c r="V96" s="57"/>
     </row>
     <row r="97" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="57" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B97" s="57" t="s">
         <v>319</v>
       </c>
       <c r="C97" s="1">
+        <f t="shared" ref="C97:C105" si="4">D96+0.01</f>
+        <v>250.01</v>
+      </c>
+      <c r="D97" s="1">
+        <v>350</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F97" s="1">
+        <v>15</v>
+      </c>
+      <c r="G97" s="1">
+        <v>415</v>
+      </c>
+      <c r="H97" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I97" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K97" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="L97" s="1">
+        <v>40</v>
+      </c>
+      <c r="M97" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N97" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O97" s="1">
+        <v>20</v>
+      </c>
+      <c r="P97" s="1">
+        <v>9</v>
+      </c>
+      <c r="R97" s="1">
+        <v>850</v>
+      </c>
+      <c r="S97" s="1" t="s">
+        <v>329</v>
+      </c>
+      <c r="T97" s="57"/>
+      <c r="U97" s="149">
+        <v>383.55</v>
+      </c>
+      <c r="V97" s="57"/>
+    </row>
+    <row r="98" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A98" s="57" t="s">
+        <v>330</v>
+      </c>
+      <c r="B98" s="57" t="s">
+        <v>319</v>
+      </c>
+      <c r="C98" s="1">
         <f t="shared" si="4"/>
         <v>350.01</v>
       </c>
-      <c r="D97" s="1">
+      <c r="D98" s="1">
         <v>450</v>
       </c>
-      <c r="E97" s="1" t="s">
+      <c r="E98" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F97" s="1">
+      <c r="F98" s="1">
         <v>15</v>
       </c>
-      <c r="G97" s="1">
+      <c r="G98" s="1">
         <v>415</v>
       </c>
-      <c r="H97" s="1" t="s">
+      <c r="H98" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I97" s="1" t="s">
+      <c r="I98" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="K97" s="1" t="s">
+      <c r="K98" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L97" s="1">
+      <c r="L98" s="1">
         <v>40</v>
       </c>
-      <c r="M97" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N97" s="1" t="s">
+      <c r="M98" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N98" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O97" s="1">
+      <c r="O98" s="1">
         <v>20</v>
       </c>
-      <c r="P97" s="1">
+      <c r="P98" s="1">
         <v>9</v>
       </c>
-      <c r="R97" s="1">
+      <c r="R98" s="1">
         <v>1100</v>
       </c>
-      <c r="S97" s="1" t="s">
+      <c r="S98" s="1" t="s">
         <v>331</v>
       </c>
-      <c r="T97" s="57"/>
-      <c r="U97" s="149">
+      <c r="T98" s="57"/>
+      <c r="U98" s="149">
         <v>475.98</v>
       </c>
-      <c r="V97" s="57"/>
-    </row>
-    <row r="98" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A98" s="57" t="s">
+      <c r="V98" s="57"/>
+    </row>
+    <row r="99" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A99" s="57" t="s">
         <v>332</v>
       </c>
-      <c r="B98" s="57" t="s">
+      <c r="B99" s="57" t="s">
         <v>319</v>
       </c>
-      <c r="C98" s="1">
+      <c r="C99" s="1">
         <f t="shared" si="4"/>
         <v>450.01</v>
       </c>
-      <c r="D98" s="1">
+      <c r="D99" s="1">
         <v>550</v>
       </c>
-      <c r="E98" s="1" t="s">
+      <c r="E99" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F98" s="1">
+      <c r="F99" s="1">
         <v>15</v>
       </c>
-      <c r="G98" s="1">
+      <c r="G99" s="1">
         <v>415</v>
       </c>
-      <c r="H98" s="1" t="s">
+      <c r="H99" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I98" s="1" t="s">
+      <c r="I99" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="K98" s="1" t="s">
+      <c r="K99" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L98" s="1">
+      <c r="L99" s="1">
         <v>40</v>
       </c>
-      <c r="M98" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N98" s="1" t="s">
+      <c r="M99" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N99" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O98" s="1">
+      <c r="O99" s="1">
         <v>20</v>
       </c>
-      <c r="P98" s="1">
+      <c r="P99" s="1">
         <v>9</v>
       </c>
-      <c r="R98" s="1">
+      <c r="R99" s="1">
         <v>1100</v>
       </c>
-      <c r="S98" s="1" t="s">
+      <c r="S99" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="T98" s="57"/>
-      <c r="U98" s="149">
+      <c r="T99" s="57"/>
+      <c r="U99" s="149">
         <v>574.51</v>
       </c>
-      <c r="V98" s="57"/>
-    </row>
-    <row r="99" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A99" s="57" t="s">
+      <c r="V99" s="57"/>
+    </row>
+    <row r="100" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A100" s="57" t="s">
         <v>333</v>
       </c>
-      <c r="B99" s="57" t="s">
+      <c r="B100" s="57" t="s">
         <v>319</v>
       </c>
-      <c r="C99" s="1">
+      <c r="C100" s="1">
         <f t="shared" si="4"/>
         <v>550.01</v>
       </c>
-      <c r="D99" s="1">
+      <c r="D100" s="1">
         <v>650</v>
       </c>
-      <c r="E99" s="1" t="s">
+      <c r="E100" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F99" s="1">
+      <c r="F100" s="1">
         <v>15</v>
       </c>
-      <c r="G99" s="1">
+      <c r="G100" s="1">
         <v>415</v>
       </c>
-      <c r="H99" s="1" t="s">
+      <c r="H100" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I99" s="1" t="s">
+      <c r="I100" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="K99" s="1" t="s">
+      <c r="K100" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L99" s="1">
+      <c r="L100" s="1">
         <v>40</v>
       </c>
-      <c r="M99" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N99" s="1" t="s">
+      <c r="M100" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N100" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O99" s="1">
+      <c r="O100" s="1">
         <v>20</v>
       </c>
-      <c r="P99" s="1">
+      <c r="P100" s="1">
         <v>9</v>
       </c>
-      <c r="R99" s="1">
+      <c r="R100" s="1">
         <v>1100</v>
       </c>
-      <c r="S99" s="1" t="s">
+      <c r="S100" s="1" t="s">
         <v>334</v>
       </c>
-      <c r="T99" s="57"/>
-      <c r="U99" s="149">
+      <c r="T100" s="57"/>
+      <c r="U100" s="149">
         <v>617.67999999999995</v>
       </c>
-      <c r="V99" s="57"/>
-    </row>
-    <row r="100" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A100" s="57" t="s">
+      <c r="V100" s="57"/>
+    </row>
+    <row r="101" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A101" s="57" t="s">
         <v>335</v>
       </c>
-      <c r="B100" s="57" t="s">
+      <c r="B101" s="57" t="s">
         <v>319</v>
       </c>
-      <c r="C100" s="1">
+      <c r="C101" s="1">
         <f t="shared" si="4"/>
         <v>650.01</v>
       </c>
-      <c r="D100" s="1">
+      <c r="D101" s="1">
         <v>750</v>
       </c>
-      <c r="E100" s="1" t="s">
+      <c r="E101" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F100" s="1">
+      <c r="F101" s="1">
         <v>15</v>
       </c>
-      <c r="G100" s="1">
+      <c r="G101" s="1">
         <v>415</v>
       </c>
-      <c r="H100" s="1" t="s">
+      <c r="H101" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I100" s="1" t="s">
+      <c r="I101" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="K100" s="1" t="s">
+      <c r="K101" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L100" s="1">
-        <v>55</v>
-      </c>
-      <c r="M100" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N100" s="1" t="s">
+      <c r="L101" s="1">
+        <v>55</v>
+      </c>
+      <c r="M101" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N101" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O100" s="1">
+      <c r="O101" s="1">
         <v>20</v>
       </c>
-      <c r="P100" s="1">
+      <c r="P101" s="1">
         <v>9</v>
       </c>
-      <c r="R100" s="1">
+      <c r="R101" s="1">
         <v>2800</v>
       </c>
-      <c r="S100" s="1" t="s">
+      <c r="S101" s="1" t="s">
         <v>336</v>
       </c>
-      <c r="T100" s="57"/>
-      <c r="U100" s="149">
+      <c r="T101" s="57"/>
+      <c r="U101" s="149">
         <v>965.9</v>
       </c>
-      <c r="V100" s="57"/>
-    </row>
-    <row r="101" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A101" s="57" t="s">
+      <c r="V101" s="57"/>
+    </row>
+    <row r="102" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A102" s="57" t="s">
         <v>337</v>
       </c>
-      <c r="B101" s="57" t="s">
+      <c r="B102" s="57" t="s">
         <v>319</v>
       </c>
-      <c r="C101" s="1">
+      <c r="C102" s="1">
         <f t="shared" si="4"/>
         <v>750.01</v>
       </c>
-      <c r="D101" s="1">
+      <c r="D102" s="1">
         <v>850</v>
       </c>
-      <c r="E101" s="1" t="s">
+      <c r="E102" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F101" s="1">
+      <c r="F102" s="1">
         <v>10</v>
       </c>
-      <c r="G101" s="1">
+      <c r="G102" s="1">
         <v>415</v>
       </c>
-      <c r="H101" s="1" t="s">
+      <c r="H102" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I101" s="1" t="s">
+      <c r="I102" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="K101" s="1" t="s">
+      <c r="K102" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L101" s="1">
-        <v>55</v>
-      </c>
-      <c r="M101" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N101" s="1" t="s">
+      <c r="L102" s="1">
+        <v>55</v>
+      </c>
+      <c r="M102" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N102" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O101" s="1">
+      <c r="O102" s="1">
         <v>20</v>
       </c>
-      <c r="P101" s="1">
+      <c r="P102" s="1">
         <v>7</v>
       </c>
-      <c r="R101" s="1">
+      <c r="R102" s="1">
         <v>1100</v>
       </c>
-      <c r="S101" s="1" t="s">
+      <c r="S102" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="T101" s="57"/>
-      <c r="U101" s="149">
+      <c r="T102" s="57"/>
+      <c r="U102" s="149">
         <v>1031.17</v>
       </c>
-      <c r="V101" s="57"/>
-    </row>
-    <row r="102" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A102" s="57" t="s">
+      <c r="V102" s="57"/>
+    </row>
+    <row r="103" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="57" t="s">
         <v>339</v>
       </c>
-      <c r="B102" s="57" t="s">
+      <c r="B103" s="57" t="s">
         <v>319</v>
       </c>
-      <c r="C102" s="1">
+      <c r="C103" s="1">
         <f t="shared" si="4"/>
         <v>850.01</v>
       </c>
-      <c r="D102" s="1">
+      <c r="D103" s="1">
         <v>1000</v>
       </c>
-      <c r="E102" s="1" t="s">
+      <c r="E103" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F102" s="1">
+      <c r="F103" s="1">
         <v>10</v>
       </c>
-      <c r="G102" s="1">
+      <c r="G103" s="1">
         <v>415</v>
       </c>
-      <c r="H102" s="1" t="s">
+      <c r="H103" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I102" s="1" t="s">
+      <c r="I103" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="K102" s="1" t="s">
+      <c r="K103" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L102" s="1">
-        <v>55</v>
-      </c>
-      <c r="M102" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N102" s="1" t="s">
+      <c r="L103" s="1">
+        <v>55</v>
+      </c>
+      <c r="M103" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N103" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O102" s="1">
+      <c r="O103" s="1">
         <v>20</v>
       </c>
-      <c r="P102" s="1">
+      <c r="P103" s="1">
         <v>7</v>
       </c>
-      <c r="R102" s="1">
+      <c r="R103" s="1">
         <v>2800</v>
       </c>
-      <c r="S102" s="1" t="s">
+      <c r="S103" s="1" t="s">
         <v>340</v>
       </c>
-      <c r="T102" s="57"/>
-      <c r="U102" s="149">
+      <c r="T103" s="57"/>
+      <c r="U103" s="149">
         <v>1351.89</v>
       </c>
-      <c r="V102" s="57"/>
-    </row>
-    <row r="103" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="57" t="s">
+      <c r="V103" s="57"/>
+    </row>
+    <row r="104" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A104" s="57" t="s">
         <v>341</v>
       </c>
-      <c r="B103" s="57" t="s">
+      <c r="B104" s="57" t="s">
         <v>319</v>
       </c>
-      <c r="C103" s="1">
+      <c r="C104" s="1">
         <f t="shared" si="4"/>
         <v>1000.01</v>
       </c>
-      <c r="D103" s="1">
+      <c r="D104" s="1">
         <v>1400</v>
       </c>
-      <c r="E103" s="1" t="s">
+      <c r="E104" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F103" s="1">
+      <c r="F104" s="1">
         <v>7</v>
       </c>
-      <c r="G103" s="1">
+      <c r="G104" s="1">
         <v>415</v>
       </c>
-      <c r="H103" s="1" t="s">
+      <c r="H104" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I103" s="1" t="s">
+      <c r="I104" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="K103" s="1" t="s">
+      <c r="K104" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L103" s="1">
-        <v>55</v>
-      </c>
-      <c r="M103" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N103" s="1" t="s">
+      <c r="L104" s="1">
+        <v>55</v>
+      </c>
+      <c r="M104" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N104" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O103" s="1">
+      <c r="O104" s="1">
         <v>20</v>
       </c>
-      <c r="P103" s="1">
+      <c r="P104" s="1">
         <v>7</v>
       </c>
-      <c r="R103" s="1">
+      <c r="R104" s="1">
         <v>2800</v>
       </c>
-      <c r="S103" s="1" t="s">
+      <c r="S104" s="1" t="s">
         <v>342</v>
       </c>
-      <c r="T103" s="57"/>
-      <c r="U103" s="149">
+      <c r="T104" s="57"/>
+      <c r="U104" s="149">
         <v>1685.96</v>
       </c>
-      <c r="V103" s="57"/>
-    </row>
-    <row r="104" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A104" s="57" t="s">
+      <c r="V104" s="57"/>
+    </row>
+    <row r="105" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A105" s="57" t="s">
         <v>343</v>
       </c>
-      <c r="B104" s="57" t="s">
+      <c r="B105" s="57" t="s">
         <v>319</v>
       </c>
-      <c r="C104" s="1">
+      <c r="C105" s="1">
         <f t="shared" si="4"/>
         <v>1400.01</v>
       </c>
-      <c r="D104" s="1">
+      <c r="D105" s="1">
         <v>1800</v>
       </c>
-      <c r="E104" s="1" t="s">
+      <c r="E105" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F104" s="1">
+      <c r="F105" s="1">
         <v>6</v>
       </c>
-      <c r="G104" s="1">
+      <c r="G105" s="1">
         <v>415</v>
       </c>
-      <c r="H104" s="1" t="s">
+      <c r="H105" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I104" s="1" t="s">
+      <c r="I105" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="K104" s="1" t="s">
+      <c r="K105" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L104" s="1">
+      <c r="L105" s="1">
         <v>60</v>
       </c>
-      <c r="M104" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N104" s="1" t="s">
+      <c r="M105" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N105" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O104" s="1">
+      <c r="O105" s="1">
         <v>10</v>
       </c>
-      <c r="P104" s="1">
+      <c r="P105" s="1">
         <v>7</v>
       </c>
-      <c r="R104" s="1">
+      <c r="R105" s="1">
         <v>3125</v>
       </c>
-      <c r="S104" s="1" t="s">
+      <c r="S105" s="1" t="s">
         <v>579</v>
       </c>
-      <c r="T104" s="57" t="e" vm="1">
+      <c r="T105" s="57" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="U104" s="133"/>
-      <c r="V104" s="57"/>
-    </row>
-    <row r="105" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="130" t="s">
-        <v>344</v>
-      </c>
-      <c r="B105" s="130" t="s">
-        <v>319</v>
-      </c>
-      <c r="C105" s="52">
-        <f t="shared" ref="C105:C108" si="5">D104+0.01</f>
-        <v>1800.01</v>
-      </c>
-      <c r="D105" s="52">
-        <v>2600</v>
-      </c>
-      <c r="E105" s="52" t="s">
-        <v>156</v>
-      </c>
-      <c r="F105" s="52">
-        <v>5</v>
-      </c>
-      <c r="G105" s="52">
-        <v>415</v>
-      </c>
-      <c r="H105" s="52" t="s">
-        <v>287</v>
-      </c>
-      <c r="I105" s="52" t="s">
-        <v>260</v>
-      </c>
-      <c r="J105" s="52"/>
-      <c r="K105" s="52" t="s">
-        <v>260</v>
-      </c>
-      <c r="L105" s="52">
-        <v>80</v>
-      </c>
-      <c r="M105" s="52" t="s">
-        <v>55</v>
-      </c>
-      <c r="N105" s="52" t="s">
-        <v>22</v>
-      </c>
-      <c r="O105" s="52">
-        <v>10</v>
-      </c>
-      <c r="P105" s="52">
-        <v>9</v>
-      </c>
-      <c r="Q105" s="52"/>
-      <c r="R105" s="52">
-        <v>1500</v>
-      </c>
-      <c r="S105" s="52"/>
-      <c r="T105" s="57"/>
       <c r="U105" s="133"/>
       <c r="V105" s="57"/>
     </row>
     <row r="106" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="130" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="B106" s="130" t="s">
         <v>319</v>
       </c>
       <c r="C106" s="52">
-        <f t="shared" si="5"/>
-        <v>2600.0100000000002</v>
+        <f t="shared" ref="C106:C109" si="5">D105+0.01</f>
+        <v>1800.01</v>
       </c>
       <c r="D106" s="52">
-        <v>3600</v>
+        <v>2600</v>
       </c>
       <c r="E106" s="52" t="s">
         <v>156</v>
@@ -28411,7 +28419,7 @@
       </c>
       <c r="Q106" s="52"/>
       <c r="R106" s="52">
-        <v>2000</v>
+        <v>1500</v>
       </c>
       <c r="S106" s="52"/>
       <c r="T106" s="57"/>
@@ -28420,14 +28428,14 @@
     </row>
     <row r="107" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A107" s="130" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="B107" s="130" t="s">
         <v>319</v>
       </c>
       <c r="C107" s="52">
         <f t="shared" si="5"/>
-        <v>3600.01</v>
+        <v>2600.0100000000002</v>
       </c>
       <c r="D107" s="52">
         <v>3600</v>
@@ -28436,7 +28444,7 @@
         <v>156</v>
       </c>
       <c r="F107" s="52">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G107" s="52">
         <v>415</v>
@@ -28464,11 +28472,11 @@
         <v>10</v>
       </c>
       <c r="P107" s="52">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q107" s="52"/>
       <c r="R107" s="52">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="S107" s="52"/>
       <c r="T107" s="57"/>
@@ -28477,7 +28485,7 @@
     </row>
     <row r="108" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="130" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="B108" s="130" t="s">
         <v>319</v>
@@ -28487,7 +28495,7 @@
         <v>3600.01</v>
       </c>
       <c r="D108" s="52">
-        <v>4800</v>
+        <v>3600</v>
       </c>
       <c r="E108" s="52" t="s">
         <v>156</v>
@@ -28509,7 +28517,7 @@
         <v>260</v>
       </c>
       <c r="L108" s="52">
-        <v>100</v>
+        <v>80</v>
       </c>
       <c r="M108" s="52" t="s">
         <v>55</v>
@@ -28534,23 +28542,23 @@
     </row>
     <row r="109" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="130" t="s">
-        <v>503</v>
+        <v>347</v>
       </c>
       <c r="B109" s="130" t="s">
         <v>319</v>
       </c>
       <c r="C109" s="52">
-        <f t="shared" ref="C109" si="6">D108+0.01</f>
-        <v>4800.01</v>
+        <f t="shared" si="5"/>
+        <v>3600.01</v>
       </c>
       <c r="D109" s="52">
-        <v>5000</v>
+        <v>4800</v>
       </c>
       <c r="E109" s="52" t="s">
         <v>156</v>
       </c>
       <c r="F109" s="52">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G109" s="52">
         <v>415</v>
@@ -28578,120 +28586,120 @@
         <v>10</v>
       </c>
       <c r="P109" s="52">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q109" s="52"/>
       <c r="R109" s="52">
-        <v>2500</v>
+        <v>3000</v>
       </c>
       <c r="S109" s="52"/>
       <c r="T109" s="57"/>
       <c r="U109" s="133"/>
       <c r="V109" s="57"/>
     </row>
-    <row r="110" spans="1:22" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="106" t="s">
+    <row r="110" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A110" s="130" t="s">
+        <v>503</v>
+      </c>
+      <c r="B110" s="130" t="s">
+        <v>319</v>
+      </c>
+      <c r="C110" s="52">
+        <f t="shared" ref="C110" si="6">D109+0.01</f>
+        <v>4800.01</v>
+      </c>
+      <c r="D110" s="52">
+        <v>5000</v>
+      </c>
+      <c r="E110" s="52" t="s">
+        <v>156</v>
+      </c>
+      <c r="F110" s="52">
+        <v>5</v>
+      </c>
+      <c r="G110" s="52">
+        <v>415</v>
+      </c>
+      <c r="H110" s="52" t="s">
+        <v>287</v>
+      </c>
+      <c r="I110" s="52" t="s">
+        <v>260</v>
+      </c>
+      <c r="J110" s="52"/>
+      <c r="K110" s="52" t="s">
+        <v>260</v>
+      </c>
+      <c r="L110" s="52">
+        <v>100</v>
+      </c>
+      <c r="M110" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="N110" s="52" t="s">
+        <v>22</v>
+      </c>
+      <c r="O110" s="52">
+        <v>10</v>
+      </c>
+      <c r="P110" s="52">
+        <v>9</v>
+      </c>
+      <c r="Q110" s="52"/>
+      <c r="R110" s="52">
+        <v>2500</v>
+      </c>
+      <c r="S110" s="52"/>
+      <c r="T110" s="57"/>
+      <c r="U110" s="133"/>
+      <c r="V110" s="57"/>
+    </row>
+    <row r="111" spans="1:22" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="B110" s="106" t="s">
+      <c r="B111" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="C110" s="106" t="s">
+      <c r="C111" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="D110" s="106" t="s">
+      <c r="D111" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="E110" s="107"/>
-      <c r="F110" s="107"/>
-      <c r="G110" s="107"/>
-      <c r="H110" s="108" t="s">
+      <c r="E111" s="107"/>
+      <c r="F111" s="107"/>
+      <c r="G111" s="107"/>
+      <c r="H111" s="108" t="s">
         <v>472</v>
       </c>
-      <c r="I110" s="107"/>
-      <c r="J110" s="107"/>
-      <c r="K110" s="107"/>
-      <c r="L110" s="107"/>
-      <c r="M110" s="107"/>
-      <c r="N110" s="108" t="s">
+      <c r="I111" s="107"/>
+      <c r="J111" s="107"/>
+      <c r="K111" s="107"/>
+      <c r="L111" s="107"/>
+      <c r="M111" s="107"/>
+      <c r="N111" s="108" t="s">
         <v>472</v>
       </c>
-      <c r="O110" s="110"/>
-      <c r="P110" s="107"/>
-      <c r="Q110" s="107"/>
-      <c r="R110" s="110"/>
-      <c r="S110" s="110"/>
-      <c r="U110" s="111"/>
-    </row>
-    <row r="111" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="B111" s="3" t="s">
-        <v>319</v>
-      </c>
-      <c r="C111" s="1">
-        <v>0</v>
-      </c>
-      <c r="D111" s="1">
-        <v>170</v>
-      </c>
-      <c r="E111" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F111" s="1">
-        <v>10</v>
-      </c>
-      <c r="G111" s="1">
-        <v>230</v>
-      </c>
-      <c r="H111" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="I111" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K111" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="L111" s="1">
-        <v>30</v>
-      </c>
-      <c r="M111" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N111" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O111" s="1">
-        <v>10</v>
-      </c>
-      <c r="P111" s="1">
-        <v>8</v>
-      </c>
-      <c r="R111" s="1">
-        <v>400</v>
-      </c>
-      <c r="S111" s="6" t="s">
-        <v>349</v>
-      </c>
-      <c r="U111" s="80">
-        <v>418</v>
-      </c>
+      <c r="O111" s="110"/>
+      <c r="P111" s="107"/>
+      <c r="Q111" s="107"/>
+      <c r="R111" s="110"/>
+      <c r="S111" s="110"/>
+      <c r="U111" s="111"/>
     </row>
     <row r="112" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A112" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B112" s="3" t="s">
         <v>319</v>
       </c>
       <c r="C112" s="1">
-        <f>D111+0.01</f>
-        <v>170.01</v>
+        <v>0</v>
       </c>
       <c r="D112" s="1">
-        <v>250</v>
+        <v>170</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>156</v>
@@ -28724,28 +28732,28 @@
         <v>10</v>
       </c>
       <c r="P112" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="R112" s="1">
         <v>400</v>
       </c>
       <c r="S112" s="6" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="U112" s="80">
-        <v>474</v>
+        <v>418</v>
       </c>
     </row>
     <row r="113" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A113" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B113" s="3" t="s">
         <v>319</v>
       </c>
       <c r="C113" s="1">
         <f>D112+0.01</f>
-        <v>250.01</v>
+        <v>170.01</v>
       </c>
       <c r="D113" s="1">
         <v>250</v>
@@ -28754,7 +28762,7 @@
         <v>156</v>
       </c>
       <c r="F113" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G113" s="1">
         <v>230</v>
@@ -28778,24 +28786,24 @@
         <v>22</v>
       </c>
       <c r="O113" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="P113" s="1">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="R113" s="1">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="S113" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="T113" t="e" vm="2">
-        <v>#VALUE!</v>
+        <v>351</v>
+      </c>
+      <c r="U113" s="80">
+        <v>474</v>
       </c>
     </row>
     <row r="114" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>319</v>
@@ -28805,13 +28813,13 @@
         <v>250.01</v>
       </c>
       <c r="D114" s="1">
-        <v>450</v>
+        <v>250</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F114" s="1">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="G114" s="1">
         <v>230</v>
@@ -28826,7 +28834,7 @@
         <v>260</v>
       </c>
       <c r="L114" s="1">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M114" s="1" t="s">
         <v>55</v>
@@ -28838,119 +28846,125 @@
         <v>20</v>
       </c>
       <c r="P114" s="1">
+        <v>7</v>
+      </c>
+      <c r="R114" s="1">
+        <v>550</v>
+      </c>
+      <c r="S114" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="T114" t="e" vm="2">
+        <v>#VALUE!</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="B115" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="C115" s="1">
+        <f>D114+0.01</f>
+        <v>250.01</v>
+      </c>
+      <c r="D115" s="1">
+        <v>450</v>
+      </c>
+      <c r="E115" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F115" s="1">
+        <v>7</v>
+      </c>
+      <c r="G115" s="1">
+        <v>230</v>
+      </c>
+      <c r="H115" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I115" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K115" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="L115" s="1">
+        <v>40</v>
+      </c>
+      <c r="M115" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N115" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O115" s="1">
+        <v>20</v>
+      </c>
+      <c r="P115" s="1">
         <v>5</v>
       </c>
-      <c r="R114" s="1">
+      <c r="R115" s="1">
         <v>750</v>
       </c>
-      <c r="S114" s="6" t="s">
+      <c r="S115" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="U114" s="92"/>
-    </row>
-    <row r="115" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A115" s="106" t="s">
+      <c r="U115" s="92"/>
+    </row>
+    <row r="116" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="B115" s="106" t="s">
+      <c r="B116" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="C115" s="106" t="s">
+      <c r="C116" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="D115" s="106" t="s">
+      <c r="D116" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="E115" s="107"/>
-      <c r="F115" s="107"/>
-      <c r="G115" s="107"/>
-      <c r="H115" s="108" t="s">
+      <c r="E116" s="107"/>
+      <c r="F116" s="107"/>
+      <c r="G116" s="107"/>
+      <c r="H116" s="108" t="s">
         <v>472</v>
       </c>
-      <c r="I115" s="107"/>
-      <c r="J115" s="107"/>
-      <c r="K115" s="107"/>
-      <c r="L115" s="107"/>
-      <c r="M115" s="107"/>
-      <c r="N115" s="108" t="s">
+      <c r="I116" s="107"/>
+      <c r="J116" s="107"/>
+      <c r="K116" s="107"/>
+      <c r="L116" s="107"/>
+      <c r="M116" s="107"/>
+      <c r="N116" s="108" t="s">
         <v>472</v>
       </c>
-      <c r="O115" s="110"/>
-      <c r="P115" s="107"/>
-      <c r="Q115" s="107"/>
-      <c r="R115" s="110"/>
-      <c r="S115" s="110"/>
-      <c r="U115" s="111"/>
-    </row>
-    <row r="116" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A116" t="s">
-        <v>356</v>
-      </c>
-      <c r="B116" t="s">
-        <v>319</v>
-      </c>
-      <c r="C116" s="1">
-        <v>0</v>
-      </c>
-      <c r="D116" s="6">
-        <v>250</v>
-      </c>
-      <c r="E116" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="F116" s="6">
-        <v>80</v>
-      </c>
-      <c r="G116" s="1">
-        <v>230</v>
-      </c>
-      <c r="H116" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="I116" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K116" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="L116" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="M116" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N116" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O116" s="6">
-        <v>20</v>
-      </c>
-      <c r="P116" s="1">
-        <v>8</v>
-      </c>
-      <c r="R116" s="6">
-        <v>750</v>
-      </c>
+      <c r="O116" s="110"/>
+      <c r="P116" s="107"/>
+      <c r="Q116" s="107"/>
+      <c r="R116" s="110"/>
+      <c r="S116" s="110"/>
+      <c r="U116" s="111"/>
     </row>
     <row r="117" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B117" t="s">
         <v>319</v>
       </c>
       <c r="C117" s="1">
-        <f>D116+0.01</f>
-        <v>250.01</v>
+        <v>0</v>
       </c>
       <c r="D117" s="6">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F117" s="6">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G117" s="1">
         <v>230</v>
@@ -28964,8 +28978,8 @@
       <c r="K117" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L117" s="1">
-        <v>40</v>
+      <c r="L117" s="1" t="s">
+        <v>419</v>
       </c>
       <c r="M117" s="1" t="s">
         <v>55</v>
@@ -28982,32 +28996,26 @@
       <c r="R117" s="6">
         <v>750</v>
       </c>
-      <c r="S117" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="U117" s="80">
-        <v>1481.78</v>
-      </c>
     </row>
     <row r="118" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A118" s="3" t="s">
-        <v>360</v>
+      <c r="A118" t="s">
+        <v>358</v>
       </c>
       <c r="B118" t="s">
         <v>319</v>
       </c>
       <c r="C118" s="1">
         <f>D117+0.01</f>
-        <v>400.01</v>
+        <v>250.01</v>
       </c>
       <c r="D118" s="6">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F118" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G118" s="1">
         <v>230</v>
@@ -29039,20 +29047,26 @@
       <c r="R118" s="6">
         <v>750</v>
       </c>
+      <c r="S118" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="U118" s="80">
+        <v>1481.78</v>
+      </c>
     </row>
     <row r="119" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A119" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B119" t="s">
         <v>319</v>
       </c>
       <c r="C119" s="1">
         <f>D118+0.01</f>
-        <v>550.01</v>
+        <v>400.01</v>
       </c>
       <c r="D119" s="6">
-        <v>750</v>
+        <v>550</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>357</v>
@@ -29073,7 +29087,7 @@
         <v>260</v>
       </c>
       <c r="L119" s="1">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="M119" s="1" t="s">
         <v>55</v>
@@ -29091,93 +29105,94 @@
         <v>750</v>
       </c>
     </row>
-    <row r="120" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="106" t="s">
+    <row r="120" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A120" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="B120" t="s">
+        <v>319</v>
+      </c>
+      <c r="C120" s="1">
+        <f>D119+0.01</f>
+        <v>550.01</v>
+      </c>
+      <c r="D120" s="6">
+        <v>750</v>
+      </c>
+      <c r="E120" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="F120" s="6">
+        <v>20</v>
+      </c>
+      <c r="G120" s="1">
+        <v>230</v>
+      </c>
+      <c r="H120" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I120" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K120" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="L120" s="1">
+        <v>55</v>
+      </c>
+      <c r="M120" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N120" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O120" s="6">
+        <v>20</v>
+      </c>
+      <c r="P120" s="1">
+        <v>8</v>
+      </c>
+      <c r="R120" s="6">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="121" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="B120" s="106" t="s">
+      <c r="B121" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="C120" s="106" t="s">
+      <c r="C121" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="D120" s="106" t="s">
+      <c r="D121" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="E120" s="107"/>
-      <c r="F120" s="107"/>
-      <c r="G120" s="107"/>
-      <c r="H120" s="108" t="s">
+      <c r="E121" s="107"/>
+      <c r="F121" s="107"/>
+      <c r="G121" s="107"/>
+      <c r="H121" s="108" t="s">
         <v>472</v>
       </c>
-      <c r="I120" s="107"/>
-      <c r="J120" s="107"/>
-      <c r="K120" s="107"/>
-      <c r="L120" s="107"/>
-      <c r="M120" s="107"/>
-      <c r="N120" s="108" t="s">
+      <c r="I121" s="107"/>
+      <c r="J121" s="107"/>
+      <c r="K121" s="107"/>
+      <c r="L121" s="107"/>
+      <c r="M121" s="107"/>
+      <c r="N121" s="108" t="s">
         <v>472</v>
       </c>
-      <c r="O120" s="110"/>
-      <c r="P120" s="107"/>
-      <c r="Q120" s="107"/>
-      <c r="R120" s="110"/>
-      <c r="S120" s="110"/>
-      <c r="U120" s="111"/>
-    </row>
-    <row r="121" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A121" t="s">
-        <v>506</v>
-      </c>
-      <c r="B121" t="s">
-        <v>319</v>
-      </c>
-      <c r="C121" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="D121" s="6">
-        <v>250</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="F121" s="6">
-        <v>80</v>
-      </c>
-      <c r="G121" s="1">
-        <v>415</v>
-      </c>
-      <c r="H121" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="I121" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K121" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="L121" s="1" t="s">
-        <v>507</v>
-      </c>
-      <c r="M121" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N121" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O121" s="6">
-        <v>20</v>
-      </c>
-      <c r="P121" s="1">
-        <v>26</v>
-      </c>
-      <c r="R121" s="6">
-        <v>1500</v>
-      </c>
+      <c r="O121" s="110"/>
+      <c r="P121" s="107"/>
+      <c r="Q121" s="107"/>
+      <c r="R121" s="110"/>
+      <c r="S121" s="110"/>
+      <c r="U121" s="111"/>
     </row>
     <row r="122" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
       <c r="B122" t="s">
         <v>319</v>
@@ -29207,7 +29222,7 @@
         <v>260</v>
       </c>
       <c r="L122" s="1" t="s">
-        <v>419</v>
+        <v>507</v>
       </c>
       <c r="M122" s="1" t="s">
         <v>55</v>
@@ -29227,23 +29242,22 @@
     </row>
     <row r="123" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A123" t="s">
-        <v>358</v>
+        <v>501</v>
       </c>
       <c r="B123" t="s">
         <v>319</v>
       </c>
       <c r="C123" s="1">
-        <f t="shared" ref="C123:C131" si="7">D122+0.01</f>
-        <v>250.01</v>
+        <v>0.01</v>
       </c>
       <c r="D123" s="6">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F123" s="6">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G123" s="1">
         <v>415</v>
@@ -29257,8 +29271,8 @@
       <c r="K123" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L123" s="1">
-        <v>40</v>
+      <c r="L123" s="1" t="s">
+        <v>419</v>
       </c>
       <c r="M123" s="1" t="s">
         <v>55</v>
@@ -29270,7 +29284,7 @@
         <v>20</v>
       </c>
       <c r="P123" s="1">
-        <v>17</v>
+        <v>26</v>
       </c>
       <c r="R123" s="6">
         <v>1500</v>
@@ -29278,168 +29292,168 @@
     </row>
     <row r="124" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B124" t="s">
         <v>319</v>
       </c>
       <c r="C124" s="1">
+        <f t="shared" ref="C124:C132" si="7">D123+0.01</f>
+        <v>250.01</v>
+      </c>
+      <c r="D124" s="6">
+        <v>400</v>
+      </c>
+      <c r="E124" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="F124" s="6">
+        <v>40</v>
+      </c>
+      <c r="G124" s="1">
+        <v>415</v>
+      </c>
+      <c r="H124" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I124" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K124" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="L124" s="1">
+        <v>40</v>
+      </c>
+      <c r="M124" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N124" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O124" s="6">
+        <v>20</v>
+      </c>
+      <c r="P124" s="1">
+        <v>17</v>
+      </c>
+      <c r="R124" s="6">
+        <v>1500</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A125" t="s">
+        <v>362</v>
+      </c>
+      <c r="B125" t="s">
+        <v>319</v>
+      </c>
+      <c r="C125" s="1">
         <f t="shared" si="7"/>
         <v>400.01</v>
       </c>
-      <c r="D124" s="6">
+      <c r="D125" s="6">
         <v>450</v>
       </c>
-      <c r="E124" s="1" t="s">
+      <c r="E125" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F124" s="6">
+      <c r="F125" s="6">
         <v>60</v>
       </c>
-      <c r="G124" s="1">
+      <c r="G125" s="1">
         <v>415</v>
       </c>
-      <c r="H124" s="1" t="s">
+      <c r="H125" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I124" s="1" t="s">
+      <c r="I125" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="K124" s="1" t="s">
+      <c r="K125" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L124" s="1">
+      <c r="L125" s="1">
         <v>40</v>
       </c>
-      <c r="M124" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N124" s="1" t="s">
+      <c r="M125" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N125" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O124" s="6">
+      <c r="O125" s="6">
         <v>20</v>
       </c>
-      <c r="P124" s="1">
+      <c r="P125" s="1">
         <v>11</v>
       </c>
-      <c r="R124" s="6">
+      <c r="R125" s="6">
         <v>1500</v>
       </c>
     </row>
-    <row r="125" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
+    <row r="126" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A126" t="s">
         <v>363</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B126" t="s">
         <v>319</v>
       </c>
-      <c r="C125" s="1">
+      <c r="C126" s="1">
         <f t="shared" si="7"/>
         <v>450.01</v>
       </c>
-      <c r="D125" s="6">
+      <c r="D126" s="6">
         <v>500</v>
       </c>
-      <c r="E125" s="1" t="s">
+      <c r="E126" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F125" s="6">
+      <c r="F126" s="6">
         <v>80</v>
       </c>
-      <c r="G125" s="1">
+      <c r="G126" s="1">
         <v>415</v>
       </c>
-      <c r="H125" s="1" t="s">
+      <c r="H126" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I125" s="1" t="s">
+      <c r="I126" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="K125" s="1" t="s">
+      <c r="K126" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L125" s="1">
-        <v>55</v>
-      </c>
-      <c r="M125" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N125" s="1" t="s">
+      <c r="L126" s="1">
+        <v>55</v>
+      </c>
+      <c r="M126" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N126" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O125" s="6">
+      <c r="O126" s="6">
         <v>20</v>
       </c>
-      <c r="P125" s="1">
+      <c r="P126" s="1">
         <v>19</v>
       </c>
-      <c r="R125" s="6">
+      <c r="R126" s="6">
         <v>4500</v>
       </c>
     </row>
-    <row r="126" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A126" s="3" t="s">
+    <row r="127" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A127" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B127" t="s">
         <v>319</v>
       </c>
-      <c r="C126" s="1">
+      <c r="C127" s="1">
         <f t="shared" si="7"/>
         <v>500.01</v>
       </c>
-      <c r="D126" s="6">
-        <v>550</v>
-      </c>
-      <c r="E126" s="1" t="s">
-        <v>357</v>
-      </c>
-      <c r="F126" s="6">
-        <v>20</v>
-      </c>
-      <c r="G126" s="1">
-        <v>415</v>
-      </c>
-      <c r="H126" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="I126" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K126" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="L126" s="1">
-        <v>40</v>
-      </c>
-      <c r="M126" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N126" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O126" s="6">
-        <v>20</v>
-      </c>
-      <c r="P126" s="1">
-        <v>12</v>
-      </c>
-      <c r="R126" s="6">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="127" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="B127" t="s">
-        <v>319</v>
-      </c>
-      <c r="C127" s="1">
-        <f t="shared" si="7"/>
-        <v>550.01</v>
-      </c>
       <c r="D127" s="6">
         <v>550</v>
       </c>
@@ -29447,7 +29461,7 @@
         <v>357</v>
       </c>
       <c r="F127" s="6">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G127" s="1">
         <v>415</v>
@@ -29477,12 +29491,12 @@
         <v>12</v>
       </c>
       <c r="R127" s="6">
-        <v>4500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="128" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="3" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="B128" t="s">
         <v>319</v>
@@ -29492,13 +29506,13 @@
         <v>550.01</v>
       </c>
       <c r="D128" s="6">
-        <v>750</v>
+        <v>550</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F128" s="6">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="G128" s="1">
         <v>415</v>
@@ -29513,7 +29527,7 @@
         <v>260</v>
       </c>
       <c r="L128" s="1">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="M128" s="1" t="s">
         <v>55</v>
@@ -29522,25 +29536,25 @@
         <v>22</v>
       </c>
       <c r="O128" s="6">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="P128" s="1">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="R128" s="6">
-        <v>1500</v>
+        <v>4500</v>
       </c>
     </row>
     <row r="129" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="3" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B129" t="s">
         <v>319</v>
       </c>
       <c r="C129" s="1">
         <f t="shared" si="7"/>
-        <v>750.01</v>
+        <v>550.01</v>
       </c>
       <c r="D129" s="6">
         <v>750</v>
@@ -29549,7 +29563,7 @@
         <v>357</v>
       </c>
       <c r="F129" s="6">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G129" s="1">
         <v>415</v>
@@ -29573,18 +29587,18 @@
         <v>22</v>
       </c>
       <c r="O129" s="6">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="P129" s="1">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="R129" s="6">
-        <v>4500</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="130" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B130" t="s">
         <v>319</v>
@@ -29594,13 +29608,13 @@
         <v>750.01</v>
       </c>
       <c r="D130" s="6">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F130" s="6">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="G130" s="1">
         <v>415</v>
@@ -29627,7 +29641,7 @@
         <v>20</v>
       </c>
       <c r="P130" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R130" s="6">
         <v>4500</v>
@@ -29635,23 +29649,23 @@
     </row>
     <row r="131" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="B131" t="s">
         <v>319</v>
       </c>
       <c r="C131" s="1">
         <f t="shared" si="7"/>
-        <v>1000.01</v>
+        <v>750.01</v>
       </c>
       <c r="D131" s="6">
-        <v>1400</v>
+        <v>1000</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>357</v>
       </c>
       <c r="F131" s="6">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G131" s="1">
         <v>415</v>
@@ -29678,7 +29692,7 @@
         <v>20</v>
       </c>
       <c r="P131" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R131" s="6">
         <v>4500</v>
@@ -29686,23 +29700,23 @@
     </row>
     <row r="132" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="3" t="s">
-        <v>500</v>
+        <v>367</v>
       </c>
       <c r="B132" t="s">
         <v>319</v>
       </c>
       <c r="C132" s="1">
-        <f t="shared" ref="C132" si="8">D131+0.01</f>
-        <v>1400.01</v>
+        <f t="shared" si="7"/>
+        <v>1000.01</v>
       </c>
       <c r="D132" s="6">
-        <v>1800</v>
+        <v>1400</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F132" s="1">
-        <v>12</v>
+      <c r="F132" s="6">
+        <v>20</v>
       </c>
       <c r="G132" s="1">
         <v>415</v>
@@ -29717,7 +29731,7 @@
         <v>260</v>
       </c>
       <c r="L132" s="1">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="M132" s="1" t="s">
         <v>55</v>
@@ -29726,7 +29740,7 @@
         <v>22</v>
       </c>
       <c r="O132" s="6">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="P132" s="1">
         <v>10</v>
@@ -29737,17 +29751,17 @@
     </row>
     <row r="133" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="3" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="B133" t="s">
         <v>319</v>
       </c>
       <c r="C133" s="1">
-        <f t="shared" ref="C133" si="9">D132+0.01</f>
-        <v>1800.01</v>
+        <f t="shared" ref="C133" si="8">D132+0.01</f>
+        <v>1400.01</v>
       </c>
       <c r="D133" s="6">
-        <v>2600</v>
+        <v>1800</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>357</v>
@@ -29768,7 +29782,7 @@
         <v>260</v>
       </c>
       <c r="L133" s="1">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="M133" s="1" t="s">
         <v>55</v>
@@ -29780,7 +29794,7 @@
         <v>10</v>
       </c>
       <c r="P133" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R133" s="6">
         <v>4500</v>
@@ -29788,17 +29802,17 @@
     </row>
     <row r="134" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B134" t="s">
         <v>319</v>
       </c>
       <c r="C134" s="1">
-        <f t="shared" ref="C134" si="10">D133+0.01</f>
-        <v>2600.0100000000002</v>
+        <f t="shared" ref="C134" si="9">D133+0.01</f>
+        <v>1800.01</v>
       </c>
       <c r="D134" s="6">
-        <v>3600</v>
+        <v>2600</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>357</v>
@@ -29837,106 +29851,100 @@
         <v>4500</v>
       </c>
     </row>
-    <row r="135" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A135" s="106" t="s">
+    <row r="135" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A135" s="3" t="s">
+        <v>510</v>
+      </c>
+      <c r="B135" t="s">
+        <v>319</v>
+      </c>
+      <c r="C135" s="1">
+        <f t="shared" ref="C135" si="10">D134+0.01</f>
+        <v>2600.0100000000002</v>
+      </c>
+      <c r="D135" s="6">
+        <v>3600</v>
+      </c>
+      <c r="E135" s="1" t="s">
+        <v>357</v>
+      </c>
+      <c r="F135" s="1">
+        <v>12</v>
+      </c>
+      <c r="G135" s="1">
+        <v>415</v>
+      </c>
+      <c r="H135" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I135" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K135" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="L135" s="1">
+        <v>80</v>
+      </c>
+      <c r="M135" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N135" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O135" s="6">
+        <v>10</v>
+      </c>
+      <c r="P135" s="1">
+        <v>11</v>
+      </c>
+      <c r="R135" s="6">
+        <v>4500</v>
+      </c>
+    </row>
+    <row r="136" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A136" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="B135" s="106" t="s">
+      <c r="B136" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="C135" s="106" t="s">
+      <c r="C136" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="D135" s="106" t="s">
+      <c r="D136" s="106" t="s">
         <v>268</v>
       </c>
-      <c r="E135" s="107"/>
-      <c r="F135" s="107"/>
-      <c r="G135" s="107"/>
-      <c r="H135" s="108" t="s">
+      <c r="E136" s="107"/>
+      <c r="F136" s="107"/>
+      <c r="G136" s="107"/>
+      <c r="H136" s="108" t="s">
         <v>472</v>
       </c>
-      <c r="I135" s="107"/>
-      <c r="J135" s="107"/>
-      <c r="K135" s="107"/>
-      <c r="L135" s="107"/>
-      <c r="M135" s="107"/>
-      <c r="N135" s="108" t="s">
+      <c r="I136" s="107"/>
+      <c r="J136" s="107"/>
+      <c r="K136" s="107"/>
+      <c r="L136" s="107"/>
+      <c r="M136" s="107"/>
+      <c r="N136" s="108" t="s">
         <v>472</v>
       </c>
-      <c r="O135" s="110"/>
-      <c r="P135" s="107"/>
-      <c r="Q135" s="107"/>
-      <c r="R135" s="110"/>
-      <c r="S135" s="110"/>
-      <c r="U135" s="111"/>
-    </row>
-    <row r="136" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A136" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="B136" t="s">
-        <v>319</v>
-      </c>
-      <c r="C136" s="1">
-        <v>0.01</v>
-      </c>
-      <c r="D136" s="6">
-        <v>250</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>369</v>
-      </c>
-      <c r="F136" s="6">
-        <v>15</v>
-      </c>
-      <c r="G136" s="1">
-        <v>415</v>
-      </c>
-      <c r="H136" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="I136" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K136" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="L136" s="1">
-        <v>30</v>
-      </c>
-      <c r="M136" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N136" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O136" s="6">
-        <v>20</v>
-      </c>
-      <c r="P136" s="1">
-        <v>11</v>
-      </c>
-      <c r="R136" s="6">
-        <v>510</v>
-      </c>
-      <c r="S136" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="U136" s="80">
-        <v>624.37</v>
-      </c>
+      <c r="O136" s="110"/>
+      <c r="P136" s="107"/>
+      <c r="Q136" s="107"/>
+      <c r="R136" s="110"/>
+      <c r="S136" s="110"/>
+      <c r="U136" s="111"/>
     </row>
     <row r="137" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="3" t="s">
-        <v>504</v>
+        <v>368</v>
       </c>
       <c r="B137" t="s">
         <v>319</v>
       </c>
       <c r="C137" s="1">
-        <f>D136+0.01</f>
-        <v>250.01</v>
+        <v>0.01</v>
       </c>
       <c r="D137" s="6">
         <v>250</v>
@@ -29945,7 +29953,7 @@
         <v>369</v>
       </c>
       <c r="F137" s="6">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G137" s="1">
         <v>415</v>
@@ -29975,28 +29983,34 @@
         <v>11</v>
       </c>
       <c r="R137" s="6">
-        <v>850</v>
+        <v>510</v>
+      </c>
+      <c r="S137" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="U137" s="80">
+        <v>624.37</v>
       </c>
     </row>
     <row r="138" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A138" s="3" t="s">
-        <v>371</v>
+        <v>504</v>
       </c>
       <c r="B138" t="s">
         <v>319</v>
       </c>
       <c r="C138" s="1">
-        <f t="shared" ref="C138:C144" si="11">D137+0.01</f>
+        <f>D137+0.01</f>
         <v>250.01</v>
       </c>
       <c r="D138" s="6">
-        <v>400</v>
+        <v>250</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>369</v>
       </c>
       <c r="F138" s="6">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G138" s="1">
         <v>415</v>
@@ -30011,7 +30025,7 @@
         <v>260</v>
       </c>
       <c r="L138" s="1">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="M138" s="1" t="s">
         <v>55</v>
@@ -30026,19 +30040,19 @@
         <v>11</v>
       </c>
       <c r="R138" s="6">
-        <v>1100</v>
+        <v>850</v>
       </c>
     </row>
     <row r="139" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="B139" t="s">
         <v>319</v>
       </c>
       <c r="C139" s="1">
-        <f t="shared" si="11"/>
-        <v>400.01</v>
+        <f t="shared" ref="C139:C145" si="11">D138+0.01</f>
+        <v>250.01</v>
       </c>
       <c r="D139" s="6">
         <v>400</v>
@@ -30047,7 +30061,7 @@
         <v>369</v>
       </c>
       <c r="F139" s="6">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G139" s="1">
         <v>415</v>
@@ -30082,7 +30096,7 @@
     </row>
     <row r="140" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="B140" t="s">
         <v>319</v>
@@ -30092,13 +30106,13 @@
         <v>400.01</v>
       </c>
       <c r="D140" s="6">
-        <v>550</v>
+        <v>400</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>369</v>
       </c>
       <c r="F140" s="6">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G140" s="1">
         <v>415</v>
@@ -30125,7 +30139,7 @@
         <v>20</v>
       </c>
       <c r="P140" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="R140" s="6">
         <v>1100</v>
@@ -30133,14 +30147,14 @@
     </row>
     <row r="141" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="B141" t="s">
         <v>319</v>
       </c>
       <c r="C141" s="1">
         <f t="shared" si="11"/>
-        <v>550.01</v>
+        <v>400.01</v>
       </c>
       <c r="D141" s="6">
         <v>550</v>
@@ -30149,7 +30163,7 @@
         <v>369</v>
       </c>
       <c r="F141" s="6">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G141" s="1">
         <v>415</v>
@@ -30164,7 +30178,7 @@
         <v>260</v>
       </c>
       <c r="L141" s="1">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="M141" s="1" t="s">
         <v>55</v>
@@ -30176,15 +30190,15 @@
         <v>20</v>
       </c>
       <c r="P141" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="R141" s="6">
-        <v>1500</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="142" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="B142" t="s">
         <v>319</v>
@@ -30194,7 +30208,7 @@
         <v>550.01</v>
       </c>
       <c r="D142" s="6">
-        <v>750</v>
+        <v>550</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>369</v>
@@ -30227,25 +30241,25 @@
         <v>20</v>
       </c>
       <c r="P142" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="R142" s="6">
-        <v>2000</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="143" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="B143" t="s">
         <v>319</v>
       </c>
       <c r="C143" s="1">
         <f t="shared" si="11"/>
-        <v>750.01</v>
+        <v>550.01</v>
       </c>
       <c r="D143" s="6">
-        <v>1000</v>
+        <v>750</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>369</v>
@@ -30278,31 +30292,31 @@
         <v>20</v>
       </c>
       <c r="P143" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R143" s="6">
-        <v>3000</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="144" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="3" t="s">
-        <v>505</v>
+        <v>376</v>
       </c>
       <c r="B144" t="s">
         <v>319</v>
       </c>
       <c r="C144" s="1">
         <f t="shared" si="11"/>
-        <v>1000.01</v>
+        <v>750.01</v>
       </c>
       <c r="D144" s="6">
-        <v>1200</v>
+        <v>1000</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>369</v>
       </c>
       <c r="F144" s="6">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="G144" s="1">
         <v>415</v>
@@ -30329,36 +30343,87 @@
         <v>20</v>
       </c>
       <c r="P144" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R144" s="6">
         <v>3000</v>
       </c>
     </row>
-    <row r="145" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="3" t="s">
+        <v>505</v>
+      </c>
+      <c r="B145" t="s">
+        <v>319</v>
+      </c>
+      <c r="C145" s="1">
+        <f t="shared" si="11"/>
+        <v>1000.01</v>
+      </c>
+      <c r="D145" s="6">
+        <v>1200</v>
+      </c>
+      <c r="E145" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="F145" s="6">
+        <v>12</v>
+      </c>
+      <c r="G145" s="1">
+        <v>415</v>
+      </c>
+      <c r="H145" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I145" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K145" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="L145" s="1">
+        <v>55</v>
+      </c>
+      <c r="M145" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N145" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O145" s="6">
+        <v>20</v>
+      </c>
+      <c r="P145" s="1">
+        <v>10</v>
+      </c>
+      <c r="R145" s="6">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="146" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A146" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="C145" s="3" t="s">
+      <c r="C146" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="D145" s="3" t="s">
+      <c r="D146" s="3" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="146" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="147" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="148" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="149" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="150" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="151" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="152" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="153" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="154" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="155" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="156" spans="1:4" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="147" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="148" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="149" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="150" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="151" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="152" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="153" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="154" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="155" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="156" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="157" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <autoFilter ref="A1:S145" xr:uid="{5FB77DDB-B6D9-4CBA-9145-50EF6FDCE517}"/>
+  <autoFilter ref="A1:S146" xr:uid="{5FB77DDB-B6D9-4CBA-9145-50EF6FDCE517}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -30369,7 +30434,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B1E18F3-2DFA-476D-A4F8-F41E93C21C92}">
-  <dimension ref="A1:X60"/>
+  <dimension ref="A1:X61"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="25.7265625" customWidth="1"/>
@@ -30656,7 +30721,7 @@
         <v>40</v>
       </c>
       <c r="O7" s="71">
-        <f t="shared" ref="O7:O17" si="0">N7/G7</f>
+        <f t="shared" ref="O7:O18" si="0">N7/G7</f>
         <v>13.333333333333334</v>
       </c>
       <c r="P7" s="6">
@@ -31034,251 +31099,251 @@
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A15" s="117" t="s">
+      <c r="A15" s="56" t="s">
+        <v>675</v>
+      </c>
+      <c r="B15" s="56" t="s">
+        <v>319</v>
+      </c>
+      <c r="C15" s="71">
+        <v>15</v>
+      </c>
+      <c r="D15" s="71">
+        <v>25.4</v>
+      </c>
+      <c r="E15" s="71">
+        <v>57</v>
+      </c>
+      <c r="F15" s="71">
+        <v>30</v>
+      </c>
+      <c r="G15" s="75">
+        <f t="shared" ref="G15" si="14">E15/C15</f>
+        <v>3.8</v>
+      </c>
+      <c r="H15" s="71" t="s">
+        <v>398</v>
+      </c>
+      <c r="I15" s="71">
+        <v>149</v>
+      </c>
+      <c r="J15" s="73">
+        <f>I15*G15</f>
+        <v>566.19999999999993</v>
+      </c>
+      <c r="K15" s="71">
+        <v>47</v>
+      </c>
+      <c r="L15" s="75">
+        <f t="shared" ref="L15" si="15">K15/G15</f>
+        <v>12.368421052631579</v>
+      </c>
+      <c r="M15" s="71">
+        <v>415</v>
+      </c>
+      <c r="N15" s="71">
+        <v>40</v>
+      </c>
+      <c r="O15" s="71">
+        <f t="shared" ref="O15" si="16">N15/G15</f>
+        <v>10.526315789473685</v>
+      </c>
+      <c r="P15" s="6">
+        <v>91.42</v>
+      </c>
+      <c r="Q15" s="6">
+        <v>288</v>
+      </c>
+      <c r="R15" s="1">
+        <v>25.4</v>
+      </c>
+      <c r="S15" s="6">
+        <v>22400</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
+      <c r="A16" s="117" t="s">
         <v>399</v>
       </c>
-      <c r="B15" s="117" t="s">
+      <c r="B16" s="117" t="s">
         <v>319</v>
       </c>
-      <c r="C15" s="118">
+      <c r="C16" s="118">
         <v>12</v>
       </c>
-      <c r="D15" s="118">
+      <c r="D16" s="118">
         <v>25.4</v>
       </c>
-      <c r="E15" s="118">
+      <c r="E16" s="118">
         <v>57</v>
       </c>
-      <c r="F15" s="118">
+      <c r="F16" s="118">
         <v>40</v>
       </c>
-      <c r="G15" s="119">
-        <f t="shared" ref="G15" si="14">E15/C15</f>
+      <c r="G16" s="119">
+        <f t="shared" ref="G16" si="17">E16/C16</f>
         <v>4.75</v>
       </c>
-      <c r="H15" s="118" t="s">
+      <c r="H16" s="118" t="s">
         <v>398</v>
       </c>
-      <c r="I15" s="118">
+      <c r="I16" s="118">
         <v>150</v>
       </c>
-      <c r="J15" s="120">
-        <f>I15*G15</f>
+      <c r="J16" s="120">
+        <f>I16*G16</f>
         <v>712.5</v>
       </c>
-      <c r="K15" s="118">
+      <c r="K16" s="118">
         <v>48</v>
       </c>
-      <c r="L15" s="119">
-        <f>K15/G15</f>
+      <c r="L16" s="119">
+        <f>K16/G16</f>
         <v>10.105263157894736</v>
       </c>
-      <c r="M15" s="118">
+      <c r="M16" s="118">
         <v>415</v>
       </c>
-      <c r="N15" s="118">
+      <c r="N16" s="118">
         <v>40</v>
       </c>
-      <c r="O15" s="118">
+      <c r="O16" s="118">
         <f t="shared" si="0"/>
         <v>8.4210526315789469</v>
       </c>
-      <c r="P15" s="6">
+      <c r="P16" s="6">
         <v>73.599999999999994</v>
       </c>
-      <c r="Q15" s="6">
+      <c r="Q16" s="6">
         <v>288</v>
       </c>
-      <c r="R15" s="1">
+      <c r="R16" s="1">
         <v>25.4</v>
       </c>
-      <c r="S15" s="6">
+      <c r="S16" s="6">
         <v>22400</v>
       </c>
     </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A16" s="62"/>
-      <c r="B16" s="62"/>
-      <c r="C16" s="61"/>
-      <c r="D16" s="61"/>
-      <c r="E16" s="61"/>
-      <c r="F16" s="61"/>
-      <c r="G16" s="76"/>
-      <c r="H16" s="61"/>
-      <c r="I16" s="61"/>
-      <c r="J16" s="61"/>
-      <c r="K16" s="61"/>
-      <c r="L16" s="76"/>
-      <c r="M16" s="61"/>
-      <c r="N16" s="61"/>
-      <c r="O16" s="61"/>
-      <c r="P16" s="61" t="s">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A17" s="62"/>
+      <c r="B17" s="62"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
+      <c r="F17" s="61"/>
+      <c r="G17" s="76"/>
+      <c r="H17" s="61"/>
+      <c r="I17" s="61"/>
+      <c r="J17" s="61"/>
+      <c r="K17" s="61"/>
+      <c r="L17" s="76"/>
+      <c r="M17" s="61"/>
+      <c r="N17" s="61"/>
+      <c r="O17" s="61"/>
+      <c r="P17" s="61" t="s">
         <v>268</v>
       </c>
-      <c r="Q16" s="61"/>
-      <c r="R16" s="61"/>
-      <c r="S16" s="61"/>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A17" s="56" t="s">
+      <c r="Q17" s="61"/>
+      <c r="R17" s="61"/>
+      <c r="S17" s="61"/>
+    </row>
+    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A18" s="56" t="s">
         <v>537</v>
       </c>
-      <c r="B17" s="56" t="s">
+      <c r="B18" s="56" t="s">
         <v>319</v>
       </c>
-      <c r="C17" s="71">
+      <c r="C18" s="71">
         <v>15</v>
       </c>
-      <c r="D17" s="71">
+      <c r="D18" s="71">
         <v>30</v>
       </c>
-      <c r="E17" s="71">
+      <c r="E18" s="71">
         <v>57</v>
       </c>
-      <c r="F17" s="71">
+      <c r="F18" s="71">
         <v>30</v>
       </c>
-      <c r="G17" s="75">
-        <f>E17/C17</f>
+      <c r="G18" s="75">
+        <f>E18/C18</f>
         <v>3.8</v>
       </c>
-      <c r="H17" s="71" t="s">
+      <c r="H18" s="71" t="s">
         <v>400</v>
       </c>
-      <c r="I17" s="71">
+      <c r="I18" s="71">
         <v>220</v>
       </c>
-      <c r="J17" s="73">
-        <f>I17*G17</f>
+      <c r="J18" s="73">
+        <f>I18*G18</f>
         <v>836</v>
       </c>
-      <c r="K17" s="71">
+      <c r="K18" s="71">
         <v>24</v>
       </c>
-      <c r="L17" s="75">
-        <f>K17/G17</f>
+      <c r="L18" s="75">
+        <f>K18/G18</f>
         <v>6.3157894736842106</v>
       </c>
-      <c r="M17" s="71">
+      <c r="M18" s="71">
         <v>415</v>
       </c>
-      <c r="N17" s="71">
+      <c r="N18" s="71">
         <v>40</v>
       </c>
-      <c r="O17" s="71">
+      <c r="O18" s="71">
         <f t="shared" si="0"/>
         <v>10.526315789473685</v>
       </c>
-      <c r="P17" s="6">
+      <c r="P18" s="6">
         <v>115.75</v>
       </c>
-      <c r="Q17" s="6">
+      <c r="Q18" s="6">
         <v>345.81</v>
       </c>
-      <c r="R17" s="1">
+      <c r="R18" s="1">
         <v>25.4</v>
       </c>
-      <c r="S17" s="6">
+      <c r="S18" s="6">
         <v>22400</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="G18" s="74"/>
-      <c r="J18" s="72"/>
-      <c r="L18" s="74"/>
-      <c r="N18" s="6"/>
-      <c r="O18" s="6"/>
-      <c r="P18" s="6" t="s">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="G19" s="74"/>
+      <c r="J19" s="72"/>
+      <c r="L19" s="74"/>
+      <c r="N19" s="6"/>
+      <c r="O19" s="6"/>
+      <c r="P19" s="6" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A19" s="62"/>
-      <c r="B19" s="62"/>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="61"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="61"/>
-      <c r="J19" s="61"/>
-      <c r="K19" s="61"/>
-      <c r="L19" s="61"/>
-      <c r="M19" s="61"/>
-      <c r="N19" s="62"/>
-      <c r="O19" s="62"/>
-      <c r="P19" s="61"/>
-      <c r="Q19" s="61"/>
-      <c r="R19" s="61"/>
-      <c r="S19" s="61"/>
-    </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A20" s="56" t="s">
-        <v>513</v>
-      </c>
-      <c r="B20" s="56" t="s">
-        <v>319</v>
-      </c>
-      <c r="C20" s="71">
-        <v>15</v>
-      </c>
-      <c r="D20" s="71">
-        <v>25.4</v>
-      </c>
-      <c r="E20" s="71">
-        <v>57</v>
-      </c>
-      <c r="F20" s="71">
-        <v>30</v>
-      </c>
-      <c r="G20" s="75">
-        <f t="shared" ref="G20" si="15">E20/C20</f>
-        <v>3.8</v>
-      </c>
-      <c r="H20" s="71" t="s">
-        <v>392</v>
-      </c>
-      <c r="I20" s="71">
-        <v>90</v>
-      </c>
-      <c r="J20" s="73">
-        <f t="shared" ref="J20" si="16">I20*G20</f>
-        <v>342</v>
-      </c>
-      <c r="K20" s="71">
-        <v>80</v>
-      </c>
-      <c r="L20" s="75">
-        <f t="shared" ref="L20" si="17">K20/G20</f>
-        <v>21.05263157894737</v>
-      </c>
-      <c r="M20" s="71">
-        <v>230</v>
-      </c>
-      <c r="N20" s="71">
-        <v>20</v>
-      </c>
-      <c r="O20" s="71">
-        <f t="shared" ref="O20" si="18">N20/G20</f>
-        <v>5.2631578947368425</v>
-      </c>
-      <c r="P20" s="6">
-        <v>61.09</v>
-      </c>
-      <c r="Q20" s="6">
-        <v>230</v>
-      </c>
-      <c r="R20" s="1">
-        <v>25.4</v>
-      </c>
-      <c r="S20" s="6">
-        <v>18000</v>
-      </c>
+      <c r="A20" s="62"/>
+      <c r="B20" s="62"/>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61"/>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="61"/>
+      <c r="L20" s="61"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="62"/>
+      <c r="O20" s="62"/>
+      <c r="P20" s="61"/>
+      <c r="Q20" s="61"/>
+      <c r="R20" s="61"/>
+      <c r="S20" s="61"/>
     </row>
     <row r="21" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A21" s="56" t="s">
-        <v>568</v>
+        <v>513</v>
       </c>
       <c r="B21" s="56" t="s">
         <v>319</v>
@@ -31296,7 +31361,7 @@
         <v>30</v>
       </c>
       <c r="G21" s="75">
-        <f t="shared" ref="G21" si="19">E21/C21</f>
+        <f t="shared" ref="G21" si="18">E21/C21</f>
         <v>3.8</v>
       </c>
       <c r="H21" s="71" t="s">
@@ -31306,24 +31371,24 @@
         <v>90</v>
       </c>
       <c r="J21" s="73">
-        <f t="shared" ref="J21" si="20">I21*G21</f>
+        <f t="shared" ref="J21" si="19">I21*G21</f>
         <v>342</v>
       </c>
       <c r="K21" s="71">
         <v>80</v>
       </c>
       <c r="L21" s="75">
-        <f t="shared" ref="L21" si="21">K21/G21</f>
+        <f t="shared" ref="L21" si="20">K21/G21</f>
         <v>21.05263157894737</v>
       </c>
       <c r="M21" s="71">
-        <v>415</v>
+        <v>230</v>
       </c>
       <c r="N21" s="71">
         <v>20</v>
       </c>
       <c r="O21" s="71">
-        <f t="shared" ref="O21" si="22">N21/G21</f>
+        <f t="shared" ref="O21" si="21">N21/G21</f>
         <v>5.2631578947368425</v>
       </c>
       <c r="P21" s="6">
@@ -31341,13 +31406,13 @@
     </row>
     <row r="22" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A22" s="56" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B22" s="56" t="s">
         <v>319</v>
       </c>
       <c r="C22" s="71">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D22" s="71">
         <v>25.4</v>
@@ -31359,52 +31424,52 @@
         <v>30</v>
       </c>
       <c r="G22" s="75">
-        <f t="shared" ref="G22:G24" si="23">E22/C22</f>
-        <v>3.1666666666666665</v>
+        <f t="shared" ref="G22" si="22">E22/C22</f>
+        <v>3.8</v>
       </c>
       <c r="H22" s="71" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="I22" s="71">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="J22" s="73">
-        <f>I22*G22</f>
-        <v>475</v>
+        <f t="shared" ref="J22" si="23">I22*G22</f>
+        <v>342</v>
       </c>
       <c r="K22" s="71">
         <v>80</v>
       </c>
       <c r="L22" s="75">
         <f t="shared" ref="L22" si="24">K22/G22</f>
-        <v>25.263157894736842</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="M22" s="71">
-        <v>230</v>
+        <v>415</v>
       </c>
       <c r="N22" s="71">
         <v>20</v>
       </c>
       <c r="O22" s="71">
-        <f t="shared" ref="O22:O24" si="25">N22/G22</f>
-        <v>6.3157894736842106</v>
+        <f t="shared" ref="O22" si="25">N22/G22</f>
+        <v>5.2631578947368425</v>
       </c>
       <c r="P22" s="6">
-        <v>91.42</v>
+        <v>61.09</v>
       </c>
       <c r="Q22" s="6">
-        <v>288</v>
+        <v>230</v>
       </c>
       <c r="R22" s="1">
         <v>25.4</v>
       </c>
       <c r="S22" s="6">
-        <v>22400</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="56" t="s">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="B23" s="56" t="s">
         <v>319</v>
@@ -31422,7 +31487,7 @@
         <v>30</v>
       </c>
       <c r="G23" s="75">
-        <f>E23/C23</f>
+        <f t="shared" ref="G23:G25" si="26">E23/C23</f>
         <v>3.1666666666666665</v>
       </c>
       <c r="H23" s="71" t="s">
@@ -31439,17 +31504,17 @@
         <v>80</v>
       </c>
       <c r="L23" s="75">
-        <f t="shared" ref="L23" si="26">K23/G23</f>
+        <f t="shared" ref="L23" si="27">K23/G23</f>
         <v>25.263157894736842</v>
       </c>
       <c r="M23" s="71">
-        <v>415</v>
+        <v>230</v>
       </c>
       <c r="N23" s="71">
         <v>20</v>
       </c>
       <c r="O23" s="71">
-        <f>N23/G23</f>
+        <f t="shared" ref="O23:O25" si="28">N23/G23</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="P23" s="6">
@@ -31467,13 +31532,13 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" s="56" t="s">
-        <v>567</v>
+        <v>545</v>
       </c>
       <c r="B24" s="56" t="s">
         <v>319</v>
       </c>
       <c r="C24" s="71">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="D24" s="71">
         <v>25.4</v>
@@ -31482,11 +31547,11 @@
         <v>57</v>
       </c>
       <c r="F24" s="71">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="G24" s="75">
-        <f t="shared" si="23"/>
-        <v>4.75</v>
+        <f>E24/C24</f>
+        <v>3.1666666666666665</v>
       </c>
       <c r="H24" s="71" t="s">
         <v>398</v>
@@ -31496,27 +31561,27 @@
       </c>
       <c r="J24" s="73">
         <f>I24*G24</f>
-        <v>712.5</v>
+        <v>475</v>
       </c>
       <c r="K24" s="71">
         <v>80</v>
       </c>
       <c r="L24" s="75">
-        <f>K24/G24</f>
-        <v>16.842105263157894</v>
+        <f t="shared" ref="L24" si="29">K24/G24</f>
+        <v>25.263157894736842</v>
       </c>
       <c r="M24" s="71">
-        <v>230</v>
+        <v>415</v>
       </c>
       <c r="N24" s="71">
         <v>20</v>
       </c>
       <c r="O24" s="71">
-        <f t="shared" si="25"/>
-        <v>4.2105263157894735</v>
+        <f>N24/G24</f>
+        <v>6.3157894736842106</v>
       </c>
       <c r="P24" s="6">
-        <v>73.599999999999994</v>
+        <v>91.42</v>
       </c>
       <c r="Q24" s="6">
         <v>288</v>
@@ -31530,7 +31595,7 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" s="56" t="s">
-        <v>514</v>
+        <v>567</v>
       </c>
       <c r="B25" s="56" t="s">
         <v>319</v>
@@ -31548,7 +31613,7 @@
         <v>40</v>
       </c>
       <c r="G25" s="75">
-        <f t="shared" ref="G25" si="27">E25/C25</f>
+        <f t="shared" si="26"/>
         <v>4.75</v>
       </c>
       <c r="H25" s="71" t="s">
@@ -31569,13 +31634,13 @@
         <v>16.842105263157894</v>
       </c>
       <c r="M25" s="71">
-        <v>415</v>
+        <v>230</v>
       </c>
       <c r="N25" s="71">
         <v>20</v>
       </c>
       <c r="O25" s="71">
-        <f t="shared" ref="O25" si="28">N25/G25</f>
+        <f t="shared" si="28"/>
         <v>4.2105263157894735</v>
       </c>
       <c r="P25" s="6">
@@ -31592,89 +31657,88 @@
       </c>
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="C26"/>
-      <c r="D26"/>
-      <c r="E26"/>
-      <c r="F26"/>
-      <c r="G26"/>
-      <c r="H26"/>
-      <c r="I26"/>
-      <c r="J26"/>
-      <c r="K26"/>
-      <c r="L26"/>
-      <c r="M26"/>
-      <c r="P26"/>
-      <c r="Q26"/>
-      <c r="R26"/>
-      <c r="S26"/>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A28" s="86" t="s">
-        <v>546</v>
-      </c>
-      <c r="B28" t="s">
+      <c r="A26" s="56" t="s">
+        <v>514</v>
+      </c>
+      <c r="B26" s="56" t="s">
         <v>319</v>
       </c>
-      <c r="C28" s="6">
-        <v>15</v>
-      </c>
-      <c r="D28" s="6">
+      <c r="C26" s="71">
+        <v>12</v>
+      </c>
+      <c r="D26" s="71">
+        <v>25.4</v>
+      </c>
+      <c r="E26" s="71">
+        <v>57</v>
+      </c>
+      <c r="F26" s="71">
         <v>40</v>
       </c>
-      <c r="E28" s="6">
-        <v>57</v>
-      </c>
-      <c r="F28" s="6">
-        <v>40</v>
-      </c>
-      <c r="G28" s="74">
-        <f t="shared" ref="G28" si="29">E28/C28</f>
-        <v>3.8</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="I28" s="6">
-        <v>400</v>
-      </c>
-      <c r="J28" s="72">
-        <f t="shared" ref="J28" si="30">I28*G28</f>
-        <v>1520</v>
-      </c>
-      <c r="K28" s="1">
-        <v>24</v>
-      </c>
-      <c r="L28" s="74">
-        <f t="shared" ref="L28" si="31">K28/G28</f>
-        <v>6.3157894736842106</v>
-      </c>
-      <c r="M28" s="6">
+      <c r="G26" s="75">
+        <f t="shared" ref="G26" si="30">E26/C26</f>
+        <v>4.75</v>
+      </c>
+      <c r="H26" s="71" t="s">
+        <v>398</v>
+      </c>
+      <c r="I26" s="71">
+        <v>150</v>
+      </c>
+      <c r="J26" s="73">
+        <f>I26*G26</f>
+        <v>712.5</v>
+      </c>
+      <c r="K26" s="71">
+        <v>80</v>
+      </c>
+      <c r="L26" s="75">
+        <f>K26/G26</f>
+        <v>16.842105263157894</v>
+      </c>
+      <c r="M26" s="71">
         <v>415</v>
       </c>
-      <c r="N28" s="71">
-        <v>40</v>
-      </c>
-      <c r="O28" s="71">
-        <f t="shared" ref="O28" si="32">N28/G28</f>
-        <v>10.526315789473685</v>
-      </c>
-      <c r="P28" s="6">
-        <v>192.91</v>
-      </c>
-      <c r="Q28" s="6">
-        <v>461</v>
-      </c>
-      <c r="R28" s="6">
-        <f t="shared" ref="R28" si="33">D28</f>
-        <v>40</v>
-      </c>
-      <c r="S28" s="6">
-        <v>60000</v>
-      </c>
+      <c r="N26" s="71">
+        <v>20</v>
+      </c>
+      <c r="O26" s="71">
+        <f t="shared" ref="O26" si="31">N26/G26</f>
+        <v>4.2105263157894735</v>
+      </c>
+      <c r="P26" s="6">
+        <v>73.599999999999994</v>
+      </c>
+      <c r="Q26" s="6">
+        <v>288</v>
+      </c>
+      <c r="R26" s="1">
+        <v>25.4</v>
+      </c>
+      <c r="S26" s="6">
+        <v>22400</v>
+      </c>
+    </row>
+    <row r="27" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="C27"/>
+      <c r="D27"/>
+      <c r="E27"/>
+      <c r="F27"/>
+      <c r="G27"/>
+      <c r="H27"/>
+      <c r="I27"/>
+      <c r="J27"/>
+      <c r="K27"/>
+      <c r="L27"/>
+      <c r="M27"/>
+      <c r="P27"/>
+      <c r="Q27"/>
+      <c r="R27"/>
+      <c r="S27"/>
     </row>
     <row r="29" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A29" s="86" t="s">
-        <v>473</v>
+        <v>546</v>
       </c>
       <c r="B29" t="s">
         <v>319</v>
@@ -31692,24 +31756,24 @@
         <v>40</v>
       </c>
       <c r="G29" s="74">
-        <f t="shared" ref="G29" si="34">E29/C29</f>
+        <f t="shared" ref="G29" si="32">E29/C29</f>
         <v>3.8</v>
       </c>
       <c r="H29" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I29" s="6">
         <v>400</v>
       </c>
       <c r="J29" s="72">
-        <f t="shared" ref="J29" si="35">I29*G29</f>
+        <f t="shared" ref="J29" si="33">I29*G29</f>
         <v>1520</v>
       </c>
       <c r="K29" s="1">
         <v>24</v>
       </c>
       <c r="L29" s="74">
-        <f t="shared" ref="L29" si="36">K29/G29</f>
+        <f t="shared" ref="L29" si="34">K29/G29</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="M29" s="6">
@@ -31719,7 +31783,7 @@
         <v>40</v>
       </c>
       <c r="O29" s="71">
-        <f t="shared" ref="O29:O31" si="37">N29/G29</f>
+        <f t="shared" ref="O29" si="35">N29/G29</f>
         <v>10.526315789473685</v>
       </c>
       <c r="P29" s="6">
@@ -31729,7 +31793,7 @@
         <v>461</v>
       </c>
       <c r="R29" s="6">
-        <f t="shared" ref="R29:R31" si="38">D29</f>
+        <f t="shared" ref="R29" si="36">D29</f>
         <v>40</v>
       </c>
       <c r="S29" s="6">
@@ -31737,8 +31801,8 @@
       </c>
     </row>
     <row r="30" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A30" t="s">
-        <v>547</v>
+      <c r="A30" s="86" t="s">
+        <v>473</v>
       </c>
       <c r="B30" t="s">
         <v>319</v>
@@ -31747,44 +31811,44 @@
         <v>15</v>
       </c>
       <c r="D30" s="6">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E30" s="6">
         <v>57</v>
       </c>
       <c r="F30" s="6">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="G30" s="74">
-        <f t="shared" ref="G30:G31" si="39">E30/C30</f>
+        <f t="shared" ref="G30" si="37">E30/C30</f>
         <v>3.8</v>
       </c>
       <c r="H30" s="6" t="s">
         <v>402</v>
       </c>
       <c r="I30" s="6">
-        <v>600</v>
+        <v>400</v>
       </c>
       <c r="J30" s="72">
-        <f t="shared" ref="J30:J31" si="40">I30*G30</f>
-        <v>2280</v>
+        <f t="shared" ref="J30" si="38">I30*G30</f>
+        <v>1520</v>
       </c>
       <c r="K30" s="1">
         <v>24</v>
       </c>
       <c r="L30" s="74">
-        <f t="shared" ref="L30:L31" si="41">K30/G30</f>
+        <f t="shared" ref="L30" si="39">K30/G30</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="M30" s="6">
         <v>415</v>
       </c>
       <c r="N30" s="71">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O30" s="71">
-        <f t="shared" si="37"/>
-        <v>15.789473684210527</v>
+        <f t="shared" ref="O30:O32" si="40">N30/G30</f>
+        <v>10.526315789473685</v>
       </c>
       <c r="P30" s="6">
         <v>192.91</v>
@@ -31793,8 +31857,8 @@
         <v>461</v>
       </c>
       <c r="R30" s="6">
-        <f t="shared" si="38"/>
-        <v>55</v>
+        <f t="shared" ref="R30:R32" si="41">D30</f>
+        <v>40</v>
       </c>
       <c r="S30" s="6">
         <v>60000</v>
@@ -31802,7 +31866,7 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="B31" t="s">
         <v>319</v>
@@ -31820,24 +31884,24 @@
         <v>55</v>
       </c>
       <c r="G31" s="74">
-        <f t="shared" si="39"/>
+        <f t="shared" ref="G31:G32" si="42">E31/C31</f>
         <v>3.8</v>
       </c>
       <c r="H31" s="6" t="s">
         <v>402</v>
       </c>
       <c r="I31" s="6">
-        <v>800</v>
+        <v>600</v>
       </c>
       <c r="J31" s="72">
-        <f t="shared" si="40"/>
-        <v>3040</v>
+        <f t="shared" ref="J31:J32" si="43">I31*G31</f>
+        <v>2280</v>
       </c>
       <c r="K31" s="1">
         <v>24</v>
       </c>
       <c r="L31" s="74">
-        <f t="shared" si="41"/>
+        <f t="shared" ref="L31:L32" si="44">K31/G31</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="M31" s="6">
@@ -31847,26 +31911,26 @@
         <v>60</v>
       </c>
       <c r="O31" s="71">
-        <f t="shared" si="37"/>
+        <f t="shared" si="40"/>
         <v>15.789473684210527</v>
       </c>
       <c r="P31" s="6">
-        <v>152.72</v>
+        <v>192.91</v>
       </c>
       <c r="Q31" s="6">
-        <v>576</v>
+        <v>461</v>
       </c>
       <c r="R31" s="6">
-        <f t="shared" si="38"/>
+        <f t="shared" si="41"/>
         <v>55</v>
       </c>
       <c r="S31" s="6">
-        <v>95000</v>
+        <v>60000</v>
       </c>
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="B32" t="s">
         <v>319</v>
@@ -31884,24 +31948,24 @@
         <v>55</v>
       </c>
       <c r="G32" s="74">
-        <f t="shared" ref="G32" si="42">E32/C32</f>
+        <f t="shared" si="42"/>
         <v>3.8</v>
       </c>
       <c r="H32" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I32" s="6">
         <v>800</v>
       </c>
       <c r="J32" s="72">
-        <f t="shared" ref="J32" si="43">I32*G32</f>
+        <f t="shared" si="43"/>
         <v>3040</v>
       </c>
       <c r="K32" s="1">
         <v>24</v>
       </c>
       <c r="L32" s="74">
-        <f t="shared" ref="L32" si="44">K32/G32</f>
+        <f t="shared" si="44"/>
         <v>6.3157894736842106</v>
       </c>
       <c r="M32" s="6">
@@ -31911,7 +31975,7 @@
         <v>60</v>
       </c>
       <c r="O32" s="71">
-        <f t="shared" ref="O32" si="45">N32/G32</f>
+        <f t="shared" si="40"/>
         <v>15.789473684210527</v>
       </c>
       <c r="P32" s="6">
@@ -31921,79 +31985,80 @@
         <v>576</v>
       </c>
       <c r="R32" s="6">
-        <f t="shared" ref="R32" si="46">D32</f>
+        <f t="shared" si="41"/>
         <v>55</v>
       </c>
       <c r="S32" s="6">
         <v>95000</v>
       </c>
     </row>
-    <row r="35" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>550</v>
-      </c>
-      <c r="B35" t="s">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>548</v>
+      </c>
+      <c r="B33" t="s">
         <v>319</v>
       </c>
-      <c r="C35" s="6">
+      <c r="C33" s="6">
         <v>15</v>
       </c>
-      <c r="D35" s="6">
-        <v>40</v>
-      </c>
-      <c r="E35" s="6">
+      <c r="D33" s="6">
+        <v>55</v>
+      </c>
+      <c r="E33" s="6">
         <v>57</v>
       </c>
-      <c r="F35" s="6">
-        <v>40</v>
-      </c>
-      <c r="G35" s="74">
-        <f t="shared" ref="G35" si="47">E35/C35</f>
+      <c r="F33" s="6">
+        <v>55</v>
+      </c>
+      <c r="G33" s="74">
+        <f t="shared" ref="G33" si="45">E33/C33</f>
         <v>3.8</v>
       </c>
-      <c r="H35" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="I35" s="6">
-        <v>300</v>
-      </c>
-      <c r="J35" s="72">
-        <f t="shared" ref="J35" si="48">I35*G35</f>
-        <v>1140</v>
-      </c>
-      <c r="K35" s="1">
-        <v>40</v>
-      </c>
-      <c r="L35" s="74">
-        <f t="shared" ref="L35" si="49">K35/G35</f>
-        <v>10.526315789473685</v>
-      </c>
-      <c r="M35" s="6" t="s">
-        <v>401</v>
-      </c>
-      <c r="N35" s="71">
-        <v>40</v>
-      </c>
-      <c r="O35" s="71">
-        <f>N35/G35</f>
-        <v>10.526315789473685</v>
-      </c>
-      <c r="P35" s="6">
-        <v>115.75</v>
-      </c>
-      <c r="Q35" s="6">
-        <v>345.81</v>
-      </c>
-      <c r="R35" s="6">
-        <v>40</v>
-      </c>
-      <c r="S35" s="6">
-        <v>29000</v>
+      <c r="H33" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="I33" s="6">
+        <v>800</v>
+      </c>
+      <c r="J33" s="72">
+        <f t="shared" ref="J33" si="46">I33*G33</f>
+        <v>3040</v>
+      </c>
+      <c r="K33" s="1">
+        <v>24</v>
+      </c>
+      <c r="L33" s="74">
+        <f t="shared" ref="L33" si="47">K33/G33</f>
+        <v>6.3157894736842106</v>
+      </c>
+      <c r="M33" s="6">
+        <v>415</v>
+      </c>
+      <c r="N33" s="71">
+        <v>60</v>
+      </c>
+      <c r="O33" s="71">
+        <f t="shared" ref="O33" si="48">N33/G33</f>
+        <v>15.789473684210527</v>
+      </c>
+      <c r="P33" s="6">
+        <v>152.72</v>
+      </c>
+      <c r="Q33" s="6">
+        <v>576</v>
+      </c>
+      <c r="R33" s="6">
+        <f t="shared" ref="R33" si="49">D33</f>
+        <v>55</v>
+      </c>
+      <c r="S33" s="6">
+        <v>95000</v>
       </c>
     </row>
     <row r="36" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="B36" t="s">
         <v>319</v>
@@ -32015,7 +32080,7 @@
         <v>3.8</v>
       </c>
       <c r="H36" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I36" s="6">
         <v>300</v>
@@ -32056,7 +32121,7 @@
     </row>
     <row r="37" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B37" t="s">
         <v>319</v>
@@ -32065,13 +32130,13 @@
         <v>15</v>
       </c>
       <c r="D37" s="6">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="E37" s="6">
         <v>57</v>
       </c>
       <c r="F37" s="6">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="G37" s="74">
         <f t="shared" ref="G37" si="53">E37/C37</f>
@@ -32081,28 +32146,28 @@
         <v>402</v>
       </c>
       <c r="I37" s="6">
-        <v>500</v>
+        <v>300</v>
       </c>
       <c r="J37" s="72">
         <f t="shared" ref="J37" si="54">I37*G37</f>
-        <v>1900</v>
+        <v>1140</v>
       </c>
       <c r="K37" s="1">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="L37" s="74">
-        <f>K37/G37</f>
-        <v>21.05263157894737</v>
+        <f t="shared" ref="L37" si="55">K37/G37</f>
+        <v>10.526315789473685</v>
       </c>
       <c r="M37" s="6" t="s">
         <v>401</v>
       </c>
       <c r="N37" s="71">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O37" s="71">
         <f>N37/G37</f>
-        <v>15.789473684210527</v>
+        <v>10.526315789473685</v>
       </c>
       <c r="P37" s="6">
         <v>115.75</v>
@@ -32111,15 +32176,15 @@
         <v>345.81</v>
       </c>
       <c r="R37" s="6">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="S37" s="6">
-        <v>60000</v>
+        <v>29000</v>
       </c>
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B38" t="s">
         <v>319</v>
@@ -32137,25 +32202,25 @@
         <v>55</v>
       </c>
       <c r="G38" s="74">
-        <f t="shared" ref="G38" si="55">E38/C38</f>
+        <f t="shared" ref="G38" si="56">E38/C38</f>
         <v>3.8</v>
       </c>
       <c r="H38" s="6" t="s">
         <v>402</v>
       </c>
       <c r="I38" s="6">
-        <v>800</v>
+        <v>500</v>
       </c>
       <c r="J38" s="72">
-        <f t="shared" ref="J38" si="56">I38*G38</f>
-        <v>3040</v>
+        <f t="shared" ref="J38" si="57">I38*G38</f>
+        <v>1900</v>
       </c>
       <c r="K38" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L38" s="74">
         <f>K38/G38</f>
-        <v>10.526315789473685</v>
+        <v>21.05263157894737</v>
       </c>
       <c r="M38" s="6" t="s">
         <v>401</v>
@@ -32182,7 +32247,7 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>554</v>
+        <v>552</v>
       </c>
       <c r="B39" t="s">
         <v>319</v>
@@ -32200,17 +32265,17 @@
         <v>55</v>
       </c>
       <c r="G39" s="74">
-        <f t="shared" ref="G39" si="57">E39/C39</f>
+        <f t="shared" ref="G39" si="58">E39/C39</f>
         <v>3.8</v>
       </c>
       <c r="H39" s="6" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I39" s="6">
         <v>800</v>
       </c>
       <c r="J39" s="72">
-        <f t="shared" ref="J39" si="58">I39*G39</f>
+        <f t="shared" ref="J39" si="59">I39*G39</f>
         <v>3040</v>
       </c>
       <c r="K39" s="1">
@@ -32243,127 +32308,149 @@
         <v>60000</v>
       </c>
     </row>
-    <row r="41" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A41" s="3" t="s">
-        <v>404</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="C41" s="6">
-        <v>11</v>
-      </c>
-      <c r="D41" s="6">
-        <v>25.4</v>
-      </c>
-      <c r="E41" s="6">
-        <v>61</v>
-      </c>
-      <c r="G41" s="74">
-        <f>E41/C41</f>
-        <v>5.5454545454545459</v>
-      </c>
-      <c r="H41" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="I41" s="1">
-        <v>20</v>
-      </c>
-      <c r="J41" s="23">
-        <f>I41*G41</f>
-        <v>110.90909090909092</v>
-      </c>
-      <c r="K41" s="1">
-        <v>34</v>
-      </c>
-      <c r="L41" s="74">
-        <f t="shared" ref="L41:L46" si="59">K41/G41</f>
-        <v>6.1311475409836058</v>
-      </c>
-      <c r="M41" s="6">
-        <v>415</v>
-      </c>
-      <c r="R41" s="1">
-        <v>25.4</v>
-      </c>
-      <c r="S41" s="6">
-        <v>18000</v>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>554</v>
+      </c>
+      <c r="B40" t="s">
+        <v>319</v>
+      </c>
+      <c r="C40" s="6">
+        <v>15</v>
+      </c>
+      <c r="D40" s="6">
+        <v>55</v>
+      </c>
+      <c r="E40" s="6">
+        <v>57</v>
+      </c>
+      <c r="F40" s="6">
+        <v>55</v>
+      </c>
+      <c r="G40" s="74">
+        <f t="shared" ref="G40" si="60">E40/C40</f>
+        <v>3.8</v>
+      </c>
+      <c r="H40" s="6" t="s">
+        <v>403</v>
+      </c>
+      <c r="I40" s="6">
+        <v>800</v>
+      </c>
+      <c r="J40" s="72">
+        <f t="shared" ref="J40" si="61">I40*G40</f>
+        <v>3040</v>
+      </c>
+      <c r="K40" s="1">
+        <v>40</v>
+      </c>
+      <c r="L40" s="74">
+        <f>K40/G40</f>
+        <v>10.526315789473685</v>
+      </c>
+      <c r="M40" s="6" t="s">
+        <v>401</v>
+      </c>
+      <c r="N40" s="71">
+        <v>60</v>
+      </c>
+      <c r="O40" s="71">
+        <f>N40/G40</f>
+        <v>15.789473684210527</v>
+      </c>
+      <c r="P40" s="6">
+        <v>115.75</v>
+      </c>
+      <c r="Q40" s="6">
+        <v>345.81</v>
+      </c>
+      <c r="R40" s="6">
+        <v>55</v>
+      </c>
+      <c r="S40" s="6">
+        <v>60000</v>
       </c>
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>315</v>
+        <v>404</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>238</v>
       </c>
       <c r="C42" s="6">
-        <v>9</v>
+        <v>11</v>
+      </c>
+      <c r="D42" s="6">
+        <v>25.4</v>
       </c>
       <c r="E42" s="6">
-        <v>50</v>
+        <v>61</v>
       </c>
       <c r="G42" s="74">
-        <f t="shared" ref="G42:G43" si="60">E42/C42</f>
-        <v>5.5555555555555554</v>
+        <f>E42/C42</f>
+        <v>5.5454545454545459</v>
       </c>
       <c r="H42" s="6" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="I42" s="1">
-        <v>62</v>
+        <v>20</v>
       </c>
       <c r="J42" s="23">
-        <f t="shared" ref="J42:J45" si="61">I42*G42</f>
-        <v>344.44444444444446</v>
+        <f>I42*G42</f>
+        <v>110.90909090909092</v>
       </c>
       <c r="K42" s="1">
         <v>34</v>
       </c>
       <c r="L42" s="74">
-        <f t="shared" si="59"/>
-        <v>6.12</v>
+        <f t="shared" ref="L42:L47" si="62">K42/G42</f>
+        <v>6.1311475409836058</v>
       </c>
       <c r="M42" s="6">
         <v>415</v>
       </c>
+      <c r="R42" s="1">
+        <v>25.4</v>
+      </c>
       <c r="S42" s="6">
-        <v>22400</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="43" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>238</v>
       </c>
       <c r="C43" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E43" s="6">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="G43" s="74">
-        <f t="shared" si="60"/>
-        <v>6.4</v>
+        <f t="shared" ref="G43:G44" si="63">E43/C43</f>
+        <v>5.5555555555555554</v>
       </c>
       <c r="H43" s="6" t="s">
         <v>398</v>
       </c>
       <c r="I43" s="1">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="J43" s="23">
-        <f t="shared" si="61"/>
-        <v>608</v>
+        <f t="shared" ref="J43:J46" si="64">I43*G43</f>
+        <v>344.44444444444446</v>
       </c>
       <c r="K43" s="1">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="L43" s="74">
-        <f t="shared" si="59"/>
-        <v>3.4375</v>
+        <f t="shared" si="62"/>
+        <v>6.12</v>
       </c>
       <c r="M43" s="6">
         <v>415</v>
@@ -32374,174 +32461,168 @@
     </row>
     <row r="44" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>405</v>
+        <v>317</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>238</v>
       </c>
       <c r="C44" s="6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E44" s="6">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="G44" s="74">
-        <f t="shared" ref="G44:G46" si="62">E44/C44</f>
-        <v>6.333333333333333</v>
+        <f t="shared" si="63"/>
+        <v>6.4</v>
       </c>
       <c r="H44" s="6" t="s">
-        <v>400</v>
-      </c>
-      <c r="I44" s="6">
-        <v>128</v>
+        <v>398</v>
+      </c>
+      <c r="I44" s="1">
+        <v>95</v>
       </c>
       <c r="J44" s="23">
-        <f>I44*G44</f>
-        <v>810.66666666666663</v>
-      </c>
-      <c r="K44" s="6">
+        <f t="shared" si="64"/>
+        <v>608</v>
+      </c>
+      <c r="K44" s="1">
         <v>22</v>
       </c>
       <c r="L44" s="74">
-        <f>K44/G44</f>
-        <v>3.4736842105263159</v>
+        <f t="shared" si="62"/>
+        <v>3.4375</v>
       </c>
       <c r="M44" s="6">
         <v>415</v>
       </c>
       <c r="S44" s="6">
-        <v>29000</v>
+        <v>22400</v>
       </c>
     </row>
     <row r="45" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>238</v>
       </c>
       <c r="C45" s="6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E45" s="6">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="G45" s="74">
-        <f t="shared" si="62"/>
-        <v>4.3636363636363633</v>
+        <f t="shared" ref="G45:G47" si="65">E45/C45</f>
+        <v>6.333333333333333</v>
       </c>
       <c r="H45" s="6" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="I45" s="6">
-        <v>369</v>
+        <v>128</v>
       </c>
       <c r="J45" s="23">
-        <f t="shared" si="61"/>
-        <v>1610.181818181818</v>
+        <f>I45*G45</f>
+        <v>810.66666666666663</v>
       </c>
       <c r="K45" s="6">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="L45" s="74">
-        <f t="shared" si="59"/>
-        <v>3.4375000000000004</v>
+        <f>K45/G45</f>
+        <v>3.4736842105263159</v>
       </c>
       <c r="M45" s="6">
         <v>415</v>
       </c>
+      <c r="S45" s="6">
+        <v>29000</v>
+      </c>
     </row>
     <row r="46" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>407</v>
+      <c r="A46" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>238</v>
       </c>
       <c r="C46" s="6">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E46" s="6">
-        <v>72</v>
+        <v>48</v>
       </c>
       <c r="G46" s="74">
+        <f t="shared" si="65"/>
+        <v>4.3636363636363633</v>
+      </c>
+      <c r="H46" s="6" t="s">
+        <v>402</v>
+      </c>
+      <c r="I46" s="6">
+        <v>369</v>
+      </c>
+      <c r="J46" s="23">
+        <f t="shared" si="64"/>
+        <v>1610.181818181818</v>
+      </c>
+      <c r="K46" s="6">
+        <v>15</v>
+      </c>
+      <c r="L46" s="74">
         <f t="shared" si="62"/>
-        <v>5.1428571428571432</v>
-      </c>
-      <c r="H46" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="I46" s="6">
-        <v>428</v>
-      </c>
-      <c r="J46" s="23">
-        <f>I46*G46</f>
-        <v>2201.1428571428573</v>
-      </c>
-      <c r="K46" s="6">
-        <v>16.5</v>
-      </c>
-      <c r="L46" s="74">
-        <f t="shared" si="59"/>
-        <v>3.208333333333333</v>
+        <v>3.4375000000000004</v>
       </c>
       <c r="M46" s="6">
         <v>415</v>
       </c>
-      <c r="R46" s="1">
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>407</v>
+      </c>
+      <c r="C47" s="6">
+        <v>14</v>
+      </c>
+      <c r="E47" s="6">
+        <v>72</v>
+      </c>
+      <c r="G47" s="74">
+        <f t="shared" si="65"/>
+        <v>5.1428571428571432</v>
+      </c>
+      <c r="H47" s="6" t="s">
+        <v>392</v>
+      </c>
+      <c r="I47" s="6">
+        <v>428</v>
+      </c>
+      <c r="J47" s="23">
+        <f>I47*G47</f>
+        <v>2201.1428571428573</v>
+      </c>
+      <c r="K47" s="6">
+        <v>16.5</v>
+      </c>
+      <c r="L47" s="74">
+        <f t="shared" si="62"/>
+        <v>3.208333333333333</v>
+      </c>
+      <c r="M47" s="6">
+        <v>415</v>
+      </c>
+      <c r="R47" s="1">
         <v>25.4</v>
       </c>
-      <c r="S46" s="6">
-        <v>18000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A48" s="3" t="s">
-        <v>408</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="C48" s="6">
-        <v>19</v>
-      </c>
-      <c r="D48" s="6">
-        <v>25.4</v>
-      </c>
-      <c r="E48" s="6">
-        <v>57</v>
-      </c>
-      <c r="G48" s="6">
-        <f t="shared" ref="G48:G50" si="63">E48/C48</f>
-        <v>3</v>
-      </c>
-      <c r="H48" s="6" t="s">
-        <v>392</v>
-      </c>
-      <c r="I48" s="1">
-        <v>15</v>
-      </c>
-      <c r="J48" s="1">
-        <f>I48*G48</f>
-        <v>45</v>
-      </c>
-      <c r="K48" s="1">
-        <v>34</v>
-      </c>
-      <c r="L48" s="74">
-        <f>K48/G48</f>
-        <v>11.333333333333334</v>
-      </c>
-      <c r="M48" s="6">
-        <v>230</v>
-      </c>
-      <c r="R48" s="1">
-        <v>25.4</v>
-      </c>
-      <c r="S48" s="6">
+      <c r="S47" s="6">
         <v>18000</v>
       </c>
     </row>
     <row r="49" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
-        <v>315</v>
+        <v>408</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>238</v>
@@ -32556,18 +32637,18 @@
         <v>57</v>
       </c>
       <c r="G49" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" ref="G49:G51" si="66">E49/C49</f>
         <v>3</v>
       </c>
       <c r="H49" s="6" t="s">
         <v>392</v>
       </c>
       <c r="I49" s="1">
-        <v>62</v>
+        <v>15</v>
       </c>
       <c r="J49" s="1">
         <f>I49*G49</f>
-        <v>186</v>
+        <v>45</v>
       </c>
       <c r="K49" s="1">
         <v>34</v>
@@ -32588,7 +32669,7 @@
     </row>
     <row r="50" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>238</v>
@@ -32603,25 +32684,25 @@
         <v>57</v>
       </c>
       <c r="G50" s="6">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>3</v>
       </c>
       <c r="H50" s="6" t="s">
         <v>392</v>
       </c>
       <c r="I50" s="1">
-        <v>95</v>
+        <v>62</v>
       </c>
       <c r="J50" s="1">
-        <f t="shared" ref="J50" si="64">I50*G50</f>
-        <v>285</v>
+        <f>I50*G50</f>
+        <v>186</v>
       </c>
       <c r="K50" s="1">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="L50" s="74">
-        <f t="shared" ref="L50" si="65">K50/G50</f>
-        <v>7.333333333333333</v>
+        <f>K50/G50</f>
+        <v>11.333333333333334</v>
       </c>
       <c r="M50" s="6">
         <v>230</v>
@@ -32634,68 +32715,65 @@
       </c>
     </row>
     <row r="51" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="G51" s="74"/>
-      <c r="L51" s="74"/>
-    </row>
-    <row r="52" spans="1:24" s="56" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="56" t="s">
-        <v>511</v>
-      </c>
-      <c r="B52" s="121" t="s">
+      <c r="A51" s="3" t="s">
+        <v>317</v>
+      </c>
+      <c r="B51" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C52" s="71">
+      <c r="C51" s="6">
         <v>19</v>
       </c>
-      <c r="D52" s="71">
+      <c r="D51" s="6">
         <v>25.4</v>
       </c>
-      <c r="E52" s="71">
+      <c r="E51" s="6">
         <v>57</v>
       </c>
-      <c r="F52" s="71"/>
-      <c r="G52" s="71">
-        <f t="shared" ref="G52" si="66">E52/C52</f>
+      <c r="G51" s="6">
+        <f t="shared" si="66"/>
         <v>3</v>
       </c>
-      <c r="H52" s="71" t="s">
+      <c r="H51" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="I52" s="114">
-        <v>100</v>
-      </c>
-      <c r="J52" s="114">
-        <f>I52*G52</f>
-        <v>300</v>
-      </c>
-      <c r="K52" s="114">
-        <v>28</v>
-      </c>
-      <c r="L52" s="75">
-        <f t="shared" ref="L52" si="67">K52/G52</f>
-        <v>9.3333333333333339</v>
-      </c>
-      <c r="M52" s="71">
-        <v>415</v>
-      </c>
-      <c r="P52" s="71"/>
-      <c r="Q52" s="71"/>
-      <c r="R52" s="114">
+      <c r="I51" s="1">
+        <v>95</v>
+      </c>
+      <c r="J51" s="1">
+        <f t="shared" ref="J51" si="67">I51*G51</f>
+        <v>285</v>
+      </c>
+      <c r="K51" s="1">
+        <v>22</v>
+      </c>
+      <c r="L51" s="74">
+        <f t="shared" ref="L51" si="68">K51/G51</f>
+        <v>7.333333333333333</v>
+      </c>
+      <c r="M51" s="6">
+        <v>230</v>
+      </c>
+      <c r="R51" s="1">
         <v>25.4</v>
       </c>
-      <c r="S52" s="71">
+      <c r="S51" s="6">
         <v>18000</v>
       </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="G52" s="74"/>
+      <c r="L52" s="74"/>
     </row>
     <row r="53" spans="1:24" s="56" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A53" s="56" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B53" s="121" t="s">
         <v>238</v>
       </c>
       <c r="C53" s="71">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D53" s="71">
         <v>25.4</v>
@@ -32705,25 +32783,25 @@
       </c>
       <c r="F53" s="71"/>
       <c r="G53" s="71">
-        <f t="shared" ref="G53" si="68">E53/C53</f>
-        <v>3.8</v>
+        <f t="shared" ref="G53" si="69">E53/C53</f>
+        <v>3</v>
       </c>
       <c r="H53" s="71" t="s">
         <v>392</v>
       </c>
       <c r="I53" s="114">
-        <v>160</v>
+        <v>100</v>
       </c>
       <c r="J53" s="114">
         <f>I53*G53</f>
-        <v>608</v>
+        <v>300</v>
       </c>
       <c r="K53" s="114">
         <v>28</v>
       </c>
       <c r="L53" s="75">
-        <f t="shared" ref="L53" si="69">K53/G53</f>
-        <v>7.3684210526315796</v>
+        <f t="shared" ref="L53" si="70">K53/G53</f>
+        <v>9.3333333333333339</v>
       </c>
       <c r="M53" s="71">
         <v>415</v>
@@ -32737,81 +32815,131 @@
         <v>18000</v>
       </c>
     </row>
-    <row r="54" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="G54" s="74"/>
-      <c r="L54" s="74"/>
+    <row r="54" spans="1:24" s="56" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A54" s="56" t="s">
+        <v>512</v>
+      </c>
+      <c r="B54" s="121" t="s">
+        <v>238</v>
+      </c>
+      <c r="C54" s="71">
+        <v>15</v>
+      </c>
+      <c r="D54" s="71">
+        <v>25.4</v>
+      </c>
+      <c r="E54" s="71">
+        <v>57</v>
+      </c>
+      <c r="F54" s="71"/>
+      <c r="G54" s="71">
+        <f t="shared" ref="G54" si="71">E54/C54</f>
+        <v>3.8</v>
+      </c>
+      <c r="H54" s="71" t="s">
+        <v>392</v>
+      </c>
+      <c r="I54" s="114">
+        <v>160</v>
+      </c>
+      <c r="J54" s="114">
+        <f>I54*G54</f>
+        <v>608</v>
+      </c>
+      <c r="K54" s="114">
+        <v>28</v>
+      </c>
+      <c r="L54" s="75">
+        <f t="shared" ref="L54" si="72">K54/G54</f>
+        <v>7.3684210526315796</v>
+      </c>
+      <c r="M54" s="71">
+        <v>415</v>
+      </c>
+      <c r="P54" s="71"/>
+      <c r="Q54" s="71"/>
+      <c r="R54" s="114">
+        <v>25.4</v>
+      </c>
+      <c r="S54" s="71">
+        <v>18000</v>
+      </c>
     </row>
     <row r="55" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="A55" s="3" t="s">
+      <c r="G55" s="74"/>
+      <c r="L55" s="74"/>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="A56" s="3" t="s">
         <v>409</v>
       </c>
-      <c r="B55" s="3" t="s">
+      <c r="B56" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="C55" s="6">
+      <c r="C56" s="6">
         <v>19</v>
       </c>
-      <c r="D55" s="6">
+      <c r="D56" s="6">
         <v>25.4</v>
       </c>
-      <c r="E55" s="6">
+      <c r="E56" s="6">
         <v>57</v>
       </c>
-      <c r="G55" s="6">
-        <f>E55/C55</f>
+      <c r="G56" s="6">
+        <f>E56/C56</f>
         <v>3</v>
       </c>
-      <c r="H55" s="6" t="s">
+      <c r="H56" s="6" t="s">
         <v>392</v>
       </c>
-      <c r="I55" s="1">
+      <c r="I56" s="1">
         <v>70</v>
       </c>
-      <c r="J55" s="1">
-        <f>I55*G55</f>
+      <c r="J56" s="1">
+        <f>I56*G56</f>
         <v>210</v>
       </c>
-      <c r="K55" s="1">
+      <c r="K56" s="1">
         <v>28</v>
       </c>
-      <c r="L55" s="74">
-        <f t="shared" ref="L55" si="70">K55/G55</f>
+      <c r="L56" s="74">
+        <f t="shared" ref="L56" si="73">K56/G56</f>
         <v>9.3333333333333339</v>
       </c>
-      <c r="M55" s="6">
+      <c r="M56" s="6">
         <v>230</v>
       </c>
-      <c r="N55" s="1"/>
-      <c r="O55" s="1"/>
-      <c r="P55" s="1"/>
-      <c r="Q55" s="1"/>
-      <c r="R55" s="1">
+      <c r="N56" s="1"/>
+      <c r="O56" s="1"/>
+      <c r="P56" s="1"/>
+      <c r="Q56" s="1"/>
+      <c r="R56" s="1">
         <v>25.4</v>
       </c>
-      <c r="S55" s="6">
+      <c r="S56" s="6">
         <v>18000</v>
       </c>
-      <c r="U55" s="6"/>
-      <c r="X55" s="80"/>
-    </row>
-    <row r="60" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="H60" s="157" t="s">
+      <c r="U56" s="6"/>
+      <c r="X56" s="80"/>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.35">
+      <c r="H61" s="157" t="s">
         <v>536</v>
       </c>
-      <c r="I60" s="157"/>
-      <c r="J60" s="157"/>
-      <c r="K60" s="157"/>
-      <c r="L60" s="157"/>
-      <c r="M60" s="157"/>
-      <c r="N60" s="157"/>
-      <c r="O60" s="157"/>
-      <c r="P60" s="157"/>
-      <c r="Q60" s="157"/>
-      <c r="R60" s="157"/>
+      <c r="I61" s="157"/>
+      <c r="J61" s="157"/>
+      <c r="K61" s="157"/>
+      <c r="L61" s="157"/>
+      <c r="M61" s="157"/>
+      <c r="N61" s="157"/>
+      <c r="O61" s="157"/>
+      <c r="P61" s="157"/>
+      <c r="Q61" s="157"/>
+      <c r="R61" s="157"/>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="H60:R60"/>
+    <mergeCell ref="H61:R61"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4066" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C82E44D2-4CBB-45BE-9B1B-7E5BC80A4BEB}"/>
+  <xr:revisionPtr revIDLastSave="4078" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A639EE8-EE0D-4229-8F67-136FF11FA90B}"/>
   <bookViews>
-    <workbookView xWindow="1140" yWindow="1140" windowWidth="36940" windowHeight="19260" tabRatio="905" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1090" yWindow="1700" windowWidth="27440" windowHeight="14800" tabRatio="905" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lath" sheetId="7" r:id="rId1"/>
@@ -5533,6 +5533,402 @@
         <a:xfrm>
           <a:off x="13970000" y="8184690"/>
           <a:ext cx="228600" cy="600808"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>57150</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>101601</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>543584</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>546101</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7C012EEA-D38A-AEA6-277A-57DDCA44BF91}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13855700" y="469901"/>
+          <a:ext cx="486434" cy="444500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>553585</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>615950</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{393B96B4-B583-2BD4-6F73-232246868705}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13874750" y="1060450"/>
+          <a:ext cx="477385" cy="558800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>171451</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>22614</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>501651</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>613056</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Picture 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BB090BFD-63CB-B6A3-6212-6859A2E40454}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13970001" y="1660914"/>
+          <a:ext cx="330200" cy="590442"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>158750</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>69850</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>482600</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>557972</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Picture 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7D43752-AEB0-E9FA-494B-9289A1E1348D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13957300" y="2343150"/>
+          <a:ext cx="323850" cy="488122"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>31989</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>406400</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>603489</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Picture 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9A161DE-9612-86FF-27B4-0E07DE011735}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13970000" y="4210289"/>
+          <a:ext cx="234950" cy="571500"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>234950</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>438173</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>603511</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Picture 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16106B56-54CA-6868-2310-935112FFA874}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14033500" y="2908300"/>
+          <a:ext cx="203223" cy="603511"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>215901</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>25656</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>355601</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>3432</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="Picture 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{68A14468-03E4-DDE9-12A3-E9743ACAF69D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14014451" y="4838956"/>
+          <a:ext cx="139700" cy="612776"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>222250</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>74276</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>609842</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Picture 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31DD0808-E5C4-0EDB-295A-86CBAE475A89}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14020800" y="5522576"/>
+          <a:ext cx="120650" cy="535566"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>247650</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>368769</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>571907</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Picture 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{394AA241-A0D8-9CE3-C648-8DB53F0835D0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14046200" y="3600450"/>
+          <a:ext cx="121119" cy="514757"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4078" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3A639EE8-EE0D-4229-8F67-136FF11FA90B}"/>
+  <xr:revisionPtr revIDLastSave="4085" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8A552DB-6E23-4584-9243-73C7268C7866}"/>
   <bookViews>
-    <workbookView xWindow="1090" yWindow="1700" windowWidth="27440" windowHeight="14800" tabRatio="905" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1770" yWindow="2380" windowWidth="34490" windowHeight="16610" tabRatio="905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lath" sheetId="7" r:id="rId1"/>
@@ -177,6 +177,30 @@
           </rPr>
           <t xml:space="preserve">
 This is for lath that can be rever coiled, the calulation will add 10mm to the first wrap of the shutter, this will increase troque and possibly endplate size.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="U1" authorId="0" shapeId="0" xr:uid="{38D03422-E7DC-4F8F-805D-489017F7899C}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t>robert hyrons:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+Hi speed is added to single skin with a warning that the max RPM must be set to 15, this is to allow for 1 phase motors to lift high capacity. </t>
         </r>
       </text>
     </comment>
@@ -828,7 +852,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2882" uniqueCount="677">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2882" uniqueCount="678">
   <si>
     <t>Name</t>
   </si>
@@ -3185,9 +3209,6 @@
     <t>Motor usage type available</t>
   </si>
   <si>
-    <t>Standard, Hi usage</t>
-  </si>
-  <si>
     <t>Standard, Hi usage, Hi speed</t>
   </si>
   <si>
@@ -3195,6 +3216,12 @@
   </si>
   <si>
     <t>MT273M2</t>
+  </si>
+  <si>
+    <t>Standard, Hi usage, Hi speed(warning)</t>
+  </si>
+  <si>
+    <t>Standard, Hi usage, Hi speed(Max 15 RPM)</t>
   </si>
 </sst>
 </file>
@@ -3206,7 +3233,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3346,6 +3373,19 @@
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="17">
@@ -12587,7 +12627,7 @@
     <col min="14" max="15" width="8.7265625" style="6"/>
     <col min="16" max="16" width="10.1796875" style="6" customWidth="1"/>
     <col min="17" max="17" width="10.7265625" style="51" customWidth="1"/>
-    <col min="21" max="21" width="11" customWidth="1"/>
+    <col min="21" max="21" width="12.26953125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:21" s="1" customFormat="1" ht="48.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -12710,7 +12750,7 @@
         <v>22</v>
       </c>
       <c r="U2" s="48" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -12768,7 +12808,7 @@
         <v>22</v>
       </c>
       <c r="U3" s="48" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -12826,7 +12866,7 @@
         <v>22</v>
       </c>
       <c r="U4" s="48" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -12884,7 +12924,7 @@
         <v>22</v>
       </c>
       <c r="U5" s="48" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -12942,7 +12982,7 @@
         <v>22</v>
       </c>
       <c r="U6" s="48" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13000,7 +13040,7 @@
         <v>22</v>
       </c>
       <c r="U7" s="48" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13058,7 +13098,7 @@
         <v>22</v>
       </c>
       <c r="U8" s="48" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13116,7 +13156,7 @@
         <v>22</v>
       </c>
       <c r="U9" s="48" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13174,7 +13214,7 @@
         <v>22</v>
       </c>
       <c r="U10" s="48" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13232,7 +13272,7 @@
         <v>22</v>
       </c>
       <c r="U11" s="48" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13290,7 +13330,7 @@
         <v>22</v>
       </c>
       <c r="U12" s="48" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13348,7 +13388,7 @@
         <v>22</v>
       </c>
       <c r="U13" s="48" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13406,7 +13446,7 @@
         <v>22</v>
       </c>
       <c r="U14" s="48" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13464,7 +13504,7 @@
         <v>22</v>
       </c>
       <c r="U15" s="48" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13522,7 +13562,7 @@
         <v>22</v>
       </c>
       <c r="U16" s="48" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13580,7 +13620,7 @@
         <v>22</v>
       </c>
       <c r="U17" s="48" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
     </row>
     <row r="18" spans="1:21" s="62" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -13657,7 +13697,7 @@
         <v>17</v>
       </c>
       <c r="U19" s="48" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="20" spans="1:21" s="62" customFormat="1" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -13735,7 +13775,7 @@
         <v>17</v>
       </c>
       <c r="U21" s="48" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="22" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13791,7 +13831,7 @@
         <v>17</v>
       </c>
       <c r="U22" s="48" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="23" spans="1:21" s="62" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.35">
@@ -13869,7 +13909,7 @@
         <v>17</v>
       </c>
       <c r="U24" s="48" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
     </row>
     <row r="25" spans="1:21" s="62" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -26821,7 +26861,7 @@
         <v>400</v>
       </c>
       <c r="S69" s="6" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="U69" s="153">
         <v>472.24</v>
@@ -31496,7 +31536,7 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" s="56" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B15" s="56" t="s">
         <v>319</v>

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4085" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C8A552DB-6E23-4584-9243-73C7268C7866}"/>
+  <xr:revisionPtr revIDLastSave="4100" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17AF83D6-9CDD-44AE-828B-7303B40376B2}"/>
   <bookViews>
-    <workbookView xWindow="1770" yWindow="2380" windowWidth="34490" windowHeight="16610" tabRatio="905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1770" yWindow="2380" windowWidth="34490" windowHeight="16610" tabRatio="905" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lath" sheetId="7" r:id="rId1"/>
@@ -852,7 +852,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2882" uniqueCount="678">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2908" uniqueCount="680">
   <si>
     <t>Name</t>
   </si>
@@ -3222,6 +3222,12 @@
   </si>
   <si>
     <t>Standard, Hi usage, Hi speed(Max 15 RPM)</t>
+  </si>
+  <si>
+    <t>T-Rail  with 22mm wireless-rubber 4.2kg/m</t>
+  </si>
+  <si>
+    <t>L-Rail with 22mm wireless-rubber 3.32kg/m</t>
   </si>
 </sst>
 </file>
@@ -5365,13 +5371,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>203201</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>14711</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>450851</xdr:colOff>
-      <xdr:row>14</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>613199</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5409,13 +5415,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>107951</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>23945</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>457201</xdr:colOff>
-      <xdr:row>12</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>625665</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5453,13 +5459,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>203200</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>44450</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>413391</xdr:colOff>
-      <xdr:row>11</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>622475</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5497,13 +5503,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>203200</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>19050</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>413391</xdr:colOff>
-      <xdr:row>10</xdr:row>
+      <xdr:row>12</xdr:row>
       <xdr:rowOff>597075</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5541,13 +5547,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>12240</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>13</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>613048</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5717,13 +5723,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>158750</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>69850</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>482600</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>5</xdr:row>
       <xdr:rowOff>557972</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5761,13 +5767,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>171450</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>31989</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>406400</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>9</xdr:row>
       <xdr:rowOff>603489</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5805,13 +5811,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>234950</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>438173</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>6</xdr:row>
       <xdr:rowOff>603511</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5849,13 +5855,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>215901</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>10</xdr:row>
       <xdr:rowOff>25656</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>355601</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>3432</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5893,13 +5899,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>222250</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>74276</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>9</xdr:row>
+      <xdr:row>11</xdr:row>
       <xdr:rowOff>609842</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5937,13 +5943,13 @@
     <xdr:from>
       <xdr:col>16</xdr:col>
       <xdr:colOff>247650</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
       <xdr:colOff>368769</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>571907</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -5977,6 +5983,84 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>171451</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>22614</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="330200" cy="590442"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Picture 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{501AFE80-3263-4FDE-BA97-57DF2670ADB4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13970001" y="1660914"/>
+          <a:ext cx="330200" cy="590442"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>234950</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="203223" cy="603511"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Picture 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A70C0A9-BD54-4941-BB60-89A80E627878}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14033500" y="3543300"/>
+          <a:ext cx="203223" cy="603511"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -17841,7 +17925,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB485315-044F-4FB0-A3DD-44B741CAB625}">
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:Q22"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="37.54296875" customWidth="1"/>
@@ -18060,16 +18144,17 @@
     </row>
     <row r="5" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="142" t="s">
-        <v>171</v>
+        <v>678</v>
       </c>
       <c r="B5" s="18">
-        <v>2.1</v>
+        <f>B2+0.85+0.5</f>
+        <v>4.55</v>
       </c>
       <c r="C5" s="1">
-        <v>65</v>
+        <v>120</v>
       </c>
       <c r="D5" s="1">
-        <v>50</v>
+        <v>95</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>22</v>
@@ -18105,22 +18190,21 @@
         <v>55</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="142" t="s">
-        <v>615</v>
+        <v>171</v>
       </c>
       <c r="B6" s="18">
-        <f>B5+0.72+0.5</f>
-        <v>3.3200000000000003</v>
+        <v>2.1</v>
       </c>
       <c r="C6" s="1">
-        <v>110</v>
+        <v>65</v>
       </c>
       <c r="D6" s="1">
-        <v>85</v>
+        <v>50</v>
       </c>
       <c r="E6" s="1" t="s">
         <v>22</v>
@@ -18161,224 +18245,226 @@
     </row>
     <row r="7" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="142" t="s">
+        <v>615</v>
+      </c>
+      <c r="B7" s="18">
+        <f>B6+0.72+0.5</f>
+        <v>3.3200000000000003</v>
+      </c>
+      <c r="C7" s="1">
+        <v>110</v>
+      </c>
+      <c r="D7" s="1">
+        <v>85</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P7" s="1" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="142" t="s">
+        <v>679</v>
+      </c>
+      <c r="B8" s="18">
+        <f>B6+0.85+0.5</f>
+        <v>3.45</v>
+      </c>
+      <c r="C8" s="1">
+        <v>120</v>
+      </c>
+      <c r="D8" s="1">
+        <v>95</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O8" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P8" s="1" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="142" t="s">
         <v>172</v>
       </c>
-      <c r="B7" s="18">
+      <c r="B9" s="18">
         <v>2</v>
       </c>
-      <c r="C7" s="1">
+      <c r="C9" s="1">
         <v>112</v>
       </c>
-      <c r="D7" s="1">
+      <c r="D9" s="1">
         <v>80</v>
       </c>
-      <c r="E7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I7" s="1" t="s">
+      <c r="E9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="K7" s="1" t="s">
+      <c r="J9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="O7" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="P7" s="1" t="s">
+      <c r="L9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P9" s="1" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="143" t="s">
+    <row r="10" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="143" t="s">
         <v>173</v>
       </c>
-      <c r="B8" s="140">
+      <c r="B10" s="140">
         <v>1.2</v>
       </c>
-      <c r="C8" s="1">
+      <c r="C10" s="1">
         <v>80</v>
       </c>
-      <c r="D8" s="1">
+      <c r="D10" s="1">
         <v>100</v>
       </c>
-      <c r="E8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F8" s="1" t="s">
+      <c r="E10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="O8" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="P8" s="1" t="s">
+      <c r="G10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O10" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P10" s="1" t="s">
         <v>583</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="143" t="s">
+    <row r="11" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="143" t="s">
         <v>616</v>
       </c>
-      <c r="B9" s="141">
+      <c r="B11" s="141">
         <f>0.82+0.72</f>
         <v>1.54</v>
       </c>
-      <c r="C9" s="1">
+      <c r="C11" s="1">
         <v>120</v>
       </c>
-      <c r="D9" s="1">
+      <c r="D11" s="1">
         <v>100</v>
       </c>
-      <c r="E9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F9" s="1" t="s">
+      <c r="E11" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="G9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="O9" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="P9" s="1" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="10" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="144" t="s">
-        <v>617</v>
-      </c>
-      <c r="B10" s="18">
-        <v>0.95</v>
-      </c>
-      <c r="C10" s="1">
-        <v>20</v>
-      </c>
-      <c r="D10" s="1">
-        <v>100</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="I10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="M10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="O10" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="P10" s="1" t="s">
-        <v>583</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="144" t="s">
-        <v>646</v>
-      </c>
-      <c r="B11" s="52">
-        <v>1.2</v>
-      </c>
-      <c r="C11" s="1">
-        <v>58</v>
-      </c>
-      <c r="D11" s="1">
-        <v>50</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="G11" s="1" t="s">
         <v>55</v>
       </c>
@@ -18392,10 +18478,10 @@
         <v>55</v>
       </c>
       <c r="K11" s="1" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="L11" s="1" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>55</v>
@@ -18412,16 +18498,16 @@
     </row>
     <row r="12" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="144" t="s">
-        <v>174</v>
-      </c>
-      <c r="B12" s="52">
-        <v>1.2</v>
+        <v>617</v>
+      </c>
+      <c r="B12" s="18">
+        <v>0.95</v>
       </c>
       <c r="C12" s="1">
-        <v>58</v>
+        <v>20</v>
       </c>
       <c r="D12" s="1">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="E12" s="1" t="s">
         <v>55</v>
@@ -18430,7 +18516,7 @@
         <v>55</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="H12" s="1" t="s">
         <v>55</v>
@@ -18442,10 +18528,10 @@
         <v>55</v>
       </c>
       <c r="K12" s="1" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>55</v>
@@ -18462,16 +18548,16 @@
     </row>
     <row r="13" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="144" t="s">
-        <v>175</v>
-      </c>
-      <c r="B13" s="47">
-        <v>1.5</v>
+        <v>646</v>
+      </c>
+      <c r="B13" s="52">
+        <v>1.2</v>
       </c>
       <c r="C13" s="1">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="D13" s="1">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>55</v>
@@ -18512,16 +18598,16 @@
     </row>
     <row r="14" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A14" s="144" t="s">
-        <v>176</v>
-      </c>
-      <c r="B14" s="47">
-        <v>2.5</v>
+        <v>174</v>
+      </c>
+      <c r="B14" s="52">
+        <v>1.2</v>
       </c>
       <c r="C14" s="1">
-        <v>96</v>
+        <v>58</v>
       </c>
       <c r="D14" s="1">
-        <v>96</v>
+        <v>50</v>
       </c>
       <c r="E14" s="1" t="s">
         <v>55</v>
@@ -18539,22 +18625,22 @@
         <v>55</v>
       </c>
       <c r="J14" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="K14" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="L14" s="1" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="M14" s="1" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="N14" s="1" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="O14" s="1" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
       <c r="P14" s="1" t="s">
         <v>583</v>
@@ -18562,16 +18648,16 @@
     </row>
     <row r="15" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="144" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="B15" s="47">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="C15" s="1">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="D15" s="1">
-        <v>114</v>
+        <v>65</v>
       </c>
       <c r="E15" s="1" t="s">
         <v>55</v>
@@ -18586,16 +18672,16 @@
         <v>55</v>
       </c>
       <c r="I15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K15" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="J15" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="L15" s="1" t="s">
-        <v>55</v>
+        <v>22</v>
       </c>
       <c r="M15" s="1" t="s">
         <v>55</v>
@@ -18610,20 +18696,120 @@
         <v>583</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="16" x14ac:dyDescent="0.35">
-      <c r="B16" s="58"/>
-    </row>
-    <row r="17" spans="2:2" ht="16" x14ac:dyDescent="0.35">
-      <c r="B17" s="58"/>
-    </row>
-    <row r="18" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B18" s="57"/>
-    </row>
-    <row r="19" spans="2:2" x14ac:dyDescent="0.35">
-      <c r="B19" s="57"/>
-    </row>
-    <row r="20" spans="2:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="144" t="s">
+        <v>176</v>
+      </c>
+      <c r="B16" s="47">
+        <v>2.5</v>
+      </c>
+      <c r="C16" s="1">
+        <v>96</v>
+      </c>
+      <c r="D16" s="1">
+        <v>96</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F16" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H16" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I16" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="J16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="17" spans="1:16" ht="50" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="144" t="s">
+        <v>177</v>
+      </c>
+      <c r="B17" s="47">
+        <v>2</v>
+      </c>
+      <c r="C17" s="1">
+        <v>114</v>
+      </c>
+      <c r="D17" s="1">
+        <v>114</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="H17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="I17" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="J17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="K17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="M17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="O17" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="P17" s="1" t="s">
+        <v>583</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" ht="16" x14ac:dyDescent="0.35">
+      <c r="B18" s="58"/>
+    </row>
+    <row r="19" spans="1:16" ht="16" x14ac:dyDescent="0.35">
+      <c r="B19" s="58"/>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.35">
       <c r="B20" s="57"/>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B21" s="57"/>
+    </row>
+    <row r="22" spans="1:16" x14ac:dyDescent="0.35">
+      <c r="B22" s="57"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4100" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17AF83D6-9CDD-44AE-828B-7303B40376B2}"/>
+  <xr:revisionPtr revIDLastSave="4126" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70F50962-26D1-45FF-A7FE-91193536CB9F}"/>
   <bookViews>
-    <workbookView xWindow="1770" yWindow="2380" windowWidth="34490" windowHeight="16610" tabRatio="905" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="16170" yWindow="1610" windowWidth="21140" windowHeight="19510" tabRatio="905" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lath" sheetId="7" r:id="rId1"/>
@@ -188,7 +188,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>robert hyrons:</t>
         </r>
@@ -197,7 +197,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Hi speed is added to single skin with a warning that the max RPM must be set to 15, this is to allow for 1 phase motors to lift high capacity. </t>
@@ -852,7 +852,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2908" uniqueCount="680">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2921" uniqueCount="686">
   <si>
     <t>Name</t>
   </si>
@@ -3229,6 +3229,24 @@
   <si>
     <t>L-Rail with 22mm wireless-rubber 3.32kg/m</t>
   </si>
+  <si>
+    <t>Price per m</t>
+  </si>
+  <si>
+    <t>MT233M1</t>
+  </si>
+  <si>
+    <t>MT245M9</t>
+  </si>
+  <si>
+    <t>???</t>
+  </si>
+  <si>
+    <t>??</t>
+  </si>
+  <si>
+    <t>square</t>
+  </si>
 </sst>
 </file>
 
@@ -3239,7 +3257,7 @@
     <numFmt numFmtId="164" formatCode="0.0"/>
     <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3381,17 +3399,10 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="Tahoma"/>
-      <charset val="1"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="17">
@@ -3534,7 +3545,7 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3970,6 +3981,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="20% - Accent1 2" xfId="1" xr:uid="{4B6C72F7-C4CA-450E-9C13-94CEF72F8B8D}"/>
@@ -20554,7 +20569,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04DB295D-7881-4D5C-8380-F1C84A7F5934}">
-  <dimension ref="A1:N13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="11.453125" customWidth="1"/>
@@ -20567,9 +20582,10 @@
     <col min="12" max="12" width="0" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="11.6328125" style="1" customWidth="1"/>
     <col min="14" max="14" width="10.7265625" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="10.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -20612,8 +20628,11 @@
       <c r="N1" s="44" t="s">
         <v>631</v>
       </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O1" s="158" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
         <v>207</v>
       </c>
@@ -20649,7 +20668,7 @@
       </c>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>210</v>
       </c>
@@ -20685,7 +20704,7 @@
       </c>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A4" s="14" t="s">
         <v>212</v>
       </c>
@@ -20721,7 +20740,7 @@
       </c>
       <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
         <v>213</v>
       </c>
@@ -20765,7 +20784,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
         <v>642</v>
       </c>
@@ -20809,7 +20828,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
         <v>218</v>
       </c>
@@ -20853,7 +20872,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
         <v>220</v>
       </c>
@@ -20897,7 +20916,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
         <v>222</v>
       </c>
@@ -20941,7 +20960,7 @@
         <v>7.5</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="101" t="s">
         <v>224</v>
       </c>
@@ -20985,7 +21004,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A11" s="98" t="s">
         <v>226</v>
       </c>
@@ -21029,7 +21048,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A12" s="98" t="s">
         <v>228</v>
       </c>
@@ -21071,7 +21090,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A13" s="98" t="s">
         <v>494</v>
       </c>
@@ -21378,6 +21397,46 @@
         <v>569</v>
       </c>
     </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="A2" s="6" t="s">
+        <v>487</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>213</v>
+      </c>
+      <c r="C2" s="6">
+        <f>Axles!F4</f>
+        <v>67</v>
+      </c>
+      <c r="D2" s="102">
+        <f t="shared" ref="D2" si="0">(E2-C2)/2</f>
+        <v>15.25</v>
+      </c>
+      <c r="E2" s="6">
+        <v>97.5</v>
+      </c>
+      <c r="F2" s="6">
+        <v>5</v>
+      </c>
+      <c r="G2" s="6">
+        <v>18</v>
+      </c>
+      <c r="H2" s="6"/>
+      <c r="I2" s="6" t="s">
+        <v>685</v>
+      </c>
+      <c r="J2" s="6" t="s">
+        <v>319</v>
+      </c>
+      <c r="L2">
+        <f>PI() * G2</f>
+        <v>56.548667764616276</v>
+      </c>
+      <c r="N2">
+        <f>L2/25.4</f>
+        <v>2.2263255025439479</v>
+      </c>
+    </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
         <v>487</v>
@@ -21390,7 +21449,7 @@
         <v>98.8</v>
       </c>
       <c r="D3" s="102">
-        <f t="shared" ref="D3:D20" si="0">(E3-C3)/2</f>
+        <f t="shared" ref="D3:D20" si="1">(E3-C3)/2</f>
         <v>-0.64999999999999858</v>
       </c>
       <c r="E3" s="6">
@@ -21428,7 +21487,7 @@
         <v>98.8</v>
       </c>
       <c r="D4" s="102">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-0.64999999999999858</v>
       </c>
       <c r="E4" s="6">
@@ -21448,11 +21507,11 @@
         <v>319</v>
       </c>
       <c r="L4">
-        <f t="shared" ref="L4:L53" si="1">PI() * G4</f>
+        <f t="shared" ref="L4:L53" si="2">PI() * G4</f>
         <v>94.247779607693786</v>
       </c>
       <c r="N4">
-        <f t="shared" ref="N4:N53" si="2">L4/25.4</f>
+        <f t="shared" ref="N4:N53" si="3">L4/25.4</f>
         <v>3.7105425042399132</v>
       </c>
     </row>
@@ -21468,7 +21527,7 @@
         <v>98.8</v>
       </c>
       <c r="D5" s="102">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-0.64999999999999858</v>
       </c>
       <c r="E5" s="6">
@@ -21486,11 +21545,11 @@
         <v>319</v>
       </c>
       <c r="L5">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>109.95574287564276</v>
       </c>
       <c r="N5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.3289662549465655</v>
       </c>
     </row>
@@ -21506,7 +21565,7 @@
         <v>96</v>
       </c>
       <c r="D6" s="102">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-1.5</v>
       </c>
       <c r="E6" s="6">
@@ -21524,11 +21583,11 @@
         <v>319</v>
       </c>
       <c r="L6">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>79.796453401180742</v>
       </c>
       <c r="N6">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.1415926535897931</v>
       </c>
     </row>
@@ -21544,7 +21603,7 @@
         <v>96</v>
       </c>
       <c r="D7" s="102">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-1.5</v>
       </c>
       <c r="E7" s="6">
@@ -21564,11 +21623,11 @@
         <v>319</v>
       </c>
       <c r="L7">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>94.247779607693786</v>
       </c>
       <c r="N7">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.7105425042399132</v>
       </c>
     </row>
@@ -21584,7 +21643,7 @@
         <v>96</v>
       </c>
       <c r="D8" s="102">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-1.5</v>
       </c>
       <c r="E8" s="6">
@@ -21602,11 +21661,11 @@
         <v>319</v>
       </c>
       <c r="L8">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>109.95574287564276</v>
       </c>
       <c r="N8">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.3289662549465655</v>
       </c>
     </row>
@@ -21622,7 +21681,7 @@
         <v>96</v>
       </c>
       <c r="D9" s="102">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-1.5</v>
       </c>
       <c r="E9" s="6">
@@ -21642,11 +21701,11 @@
         <v>319</v>
       </c>
       <c r="L9">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>125.66370614359172</v>
       </c>
       <c r="N9">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.9473900056532178</v>
       </c>
     </row>
@@ -21662,7 +21721,7 @@
         <v>96</v>
       </c>
       <c r="D10" s="102">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-1.5</v>
       </c>
       <c r="E10" s="6">
@@ -21680,11 +21739,11 @@
         <v>319</v>
       </c>
       <c r="L10">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>141.37166941154069</v>
       </c>
       <c r="N10">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.5658137563598702</v>
       </c>
     </row>
@@ -21700,7 +21759,7 @@
         <v>120.5</v>
       </c>
       <c r="D11" s="102">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-0.25</v>
       </c>
       <c r="E11" s="6">
@@ -21718,11 +21777,11 @@
         <v>319</v>
       </c>
       <c r="L11">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>79.796453401180742</v>
       </c>
       <c r="N11">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.1415926535897931</v>
       </c>
     </row>
@@ -21738,7 +21797,7 @@
         <v>120.5</v>
       </c>
       <c r="D12" s="102">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-0.25</v>
       </c>
       <c r="E12" s="6">
@@ -21758,11 +21817,11 @@
         <v>319</v>
       </c>
       <c r="L12">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>94.247779607693786</v>
       </c>
       <c r="N12">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.7105425042399132</v>
       </c>
     </row>
@@ -21778,7 +21837,7 @@
         <v>120.5</v>
       </c>
       <c r="D13" s="102">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-0.25</v>
       </c>
       <c r="E13" s="6">
@@ -21796,11 +21855,11 @@
         <v>319</v>
       </c>
       <c r="L13">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>109.95574287564276</v>
       </c>
       <c r="N13">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.3289662549465655</v>
       </c>
     </row>
@@ -21816,7 +21875,7 @@
         <v>120.5</v>
       </c>
       <c r="D14" s="102">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-0.25</v>
       </c>
       <c r="E14" s="6">
@@ -21836,11 +21895,11 @@
         <v>319</v>
       </c>
       <c r="L14">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>125.66370614359172</v>
       </c>
       <c r="N14">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.9473900056532178</v>
       </c>
     </row>
@@ -21856,7 +21915,7 @@
         <v>120.5</v>
       </c>
       <c r="D15" s="102">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-0.25</v>
       </c>
       <c r="E15" s="6">
@@ -21874,11 +21933,11 @@
         <v>319</v>
       </c>
       <c r="L15">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>141.37166941154069</v>
       </c>
       <c r="N15">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.5658137563598702</v>
       </c>
     </row>
@@ -21894,7 +21953,7 @@
         <v>129.4</v>
       </c>
       <c r="D16" s="102">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-0.45000000000000284</v>
       </c>
       <c r="E16" s="6">
@@ -21914,11 +21973,11 @@
         <v>319</v>
       </c>
       <c r="L16">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>94.247779607693786</v>
       </c>
       <c r="N16">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.7105425042399132</v>
       </c>
     </row>
@@ -21934,7 +21993,7 @@
         <v>129.4</v>
       </c>
       <c r="D17" s="102">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-0.45000000000000284</v>
       </c>
       <c r="E17" s="6">
@@ -21952,11 +22011,11 @@
         <v>319</v>
       </c>
       <c r="L17">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>109.95574287564276</v>
       </c>
       <c r="N17">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.3289662549465655</v>
       </c>
     </row>
@@ -21972,7 +22031,7 @@
         <v>129.4</v>
       </c>
       <c r="D18" s="102">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-0.45000000000000284</v>
       </c>
       <c r="E18" s="6">
@@ -21992,11 +22051,11 @@
         <v>319</v>
       </c>
       <c r="L18">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>125.66370614359172</v>
       </c>
       <c r="N18">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.9473900056532178</v>
       </c>
     </row>
@@ -22012,7 +22071,7 @@
         <v>129.4</v>
       </c>
       <c r="D19" s="102">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-0.45000000000000284</v>
       </c>
       <c r="E19" s="6">
@@ -22030,11 +22089,11 @@
         <v>319</v>
       </c>
       <c r="L19">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>141.37166941154069</v>
       </c>
       <c r="N19">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.5658137563598702</v>
       </c>
     </row>
@@ -22050,7 +22109,7 @@
         <v>129.4</v>
       </c>
       <c r="D20" s="102">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>-0.45000000000000284</v>
       </c>
       <c r="E20" s="6">
@@ -22070,11 +22129,11 @@
         <v>319</v>
       </c>
       <c r="L20">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>172.78759594743863</v>
       </c>
       <c r="N20">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.8026612577731749</v>
       </c>
     </row>
@@ -22090,7 +22149,7 @@
         <v>158.4</v>
       </c>
       <c r="D21" s="102">
-        <f t="shared" ref="D21:D33" si="3">(E21-C21)/2</f>
+        <f t="shared" ref="D21:D33" si="4">(E21-C21)/2</f>
         <v>-1.7000000000000028</v>
       </c>
       <c r="E21" s="6">
@@ -22099,20 +22158,22 @@
       <c r="F21" s="6">
         <v>8</v>
       </c>
-      <c r="G21" s="6">
+      <c r="G21" s="118">
         <v>40</v>
       </c>
-      <c r="H21" s="6"/>
-      <c r="I21" s="6"/>
+      <c r="H21" s="118"/>
+      <c r="I21" s="118" t="s">
+        <v>684</v>
+      </c>
       <c r="J21" s="6" t="s">
         <v>319</v>
       </c>
       <c r="L21">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>125.66370614359172</v>
       </c>
       <c r="N21">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.9473900056532178</v>
       </c>
     </row>
@@ -22128,7 +22189,7 @@
         <v>158.4</v>
       </c>
       <c r="D22" s="102">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-1.7000000000000028</v>
       </c>
       <c r="E22" s="6">
@@ -22146,11 +22207,11 @@
         <v>319</v>
       </c>
       <c r="L22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>141.37166941154069</v>
       </c>
       <c r="N22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.5658137563598702</v>
       </c>
     </row>
@@ -22166,7 +22227,7 @@
         <v>158.4</v>
       </c>
       <c r="D23" s="102">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-1.7000000000000028</v>
       </c>
       <c r="E23" s="6">
@@ -22175,20 +22236,22 @@
       <c r="F23" s="6">
         <v>8</v>
       </c>
-      <c r="G23" s="6">
-        <v>55</v>
-      </c>
-      <c r="H23" s="6"/>
-      <c r="I23" s="6"/>
+      <c r="G23" s="118">
+        <v>55</v>
+      </c>
+      <c r="H23" s="118"/>
+      <c r="I23" s="118" t="s">
+        <v>684</v>
+      </c>
       <c r="J23" s="6" t="s">
         <v>319</v>
       </c>
       <c r="L23">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>172.78759594743863</v>
       </c>
       <c r="N23">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.8026612577731749</v>
       </c>
     </row>
@@ -22204,7 +22267,7 @@
         <v>158.4</v>
       </c>
       <c r="D24" s="102">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E24" s="6">
@@ -22222,11 +22285,11 @@
         <v>319</v>
       </c>
       <c r="L24">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>94.247779607693786</v>
       </c>
       <c r="N24">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.7105425042399132</v>
       </c>
     </row>
@@ -22242,7 +22305,7 @@
         <v>158.4</v>
       </c>
       <c r="D25" s="102">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E25" s="6">
@@ -22260,11 +22323,11 @@
         <v>319</v>
       </c>
       <c r="L25">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>109.95574287564276</v>
       </c>
       <c r="N25">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.3289662549465655</v>
       </c>
     </row>
@@ -22280,7 +22343,7 @@
         <v>158.4</v>
       </c>
       <c r="D26" s="102">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E26" s="6">
@@ -22293,16 +22356,18 @@
         <v>40</v>
       </c>
       <c r="H26" s="6"/>
-      <c r="I26" s="6"/>
+      <c r="I26" s="159" t="s">
+        <v>681</v>
+      </c>
       <c r="J26" s="6" t="s">
         <v>319</v>
       </c>
       <c r="L26">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>125.66370614359172</v>
       </c>
       <c r="N26">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.9473900056532178</v>
       </c>
     </row>
@@ -22318,7 +22383,7 @@
         <v>158.4</v>
       </c>
       <c r="D27" s="102">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E27" s="6">
@@ -22336,11 +22401,11 @@
         <v>319</v>
       </c>
       <c r="L27">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>141.37166941154069</v>
       </c>
       <c r="N27">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.5658137563598702</v>
       </c>
     </row>
@@ -22356,7 +22421,7 @@
         <v>158.4</v>
       </c>
       <c r="D28" s="102">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E28" s="6">
@@ -22365,20 +22430,22 @@
       <c r="F28" s="6">
         <v>8</v>
       </c>
-      <c r="G28" s="6">
-        <v>55</v>
-      </c>
-      <c r="H28" s="6"/>
-      <c r="I28" s="6"/>
+      <c r="G28" s="118">
+        <v>55</v>
+      </c>
+      <c r="H28" s="118"/>
+      <c r="I28" s="118" t="s">
+        <v>683</v>
+      </c>
       <c r="J28" s="6" t="s">
         <v>319</v>
       </c>
       <c r="L28">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>172.78759594743863</v>
       </c>
       <c r="N28">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.8026612577731749</v>
       </c>
     </row>
@@ -22394,7 +22461,7 @@
         <v>158.4</v>
       </c>
       <c r="D29" s="102">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.2999999999999972</v>
       </c>
       <c r="E29" s="6">
@@ -22412,11 +22479,11 @@
         <v>319</v>
       </c>
       <c r="L29">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>94.247779607693786</v>
       </c>
       <c r="N29">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.7105425042399132</v>
       </c>
     </row>
@@ -22432,7 +22499,7 @@
         <v>158.4</v>
       </c>
       <c r="D30" s="102">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.2999999999999972</v>
       </c>
       <c r="E30" s="6">
@@ -22450,11 +22517,11 @@
         <v>319</v>
       </c>
       <c r="L30">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>109.95574287564276</v>
       </c>
       <c r="N30">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.3289662549465655</v>
       </c>
     </row>
@@ -22470,7 +22537,7 @@
         <v>158.4</v>
       </c>
       <c r="D31" s="102">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.2999999999999972</v>
       </c>
       <c r="E31" s="6">
@@ -22479,20 +22546,22 @@
       <c r="F31" s="6">
         <v>8</v>
       </c>
-      <c r="G31" s="6">
+      <c r="G31" s="118">
         <v>40</v>
       </c>
-      <c r="H31" s="6"/>
-      <c r="I31" s="6"/>
+      <c r="H31" s="118"/>
+      <c r="I31" s="118" t="s">
+        <v>683</v>
+      </c>
       <c r="J31" s="6" t="s">
         <v>319</v>
       </c>
       <c r="L31">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>125.66370614359172</v>
       </c>
       <c r="N31">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.9473900056532178</v>
       </c>
     </row>
@@ -22508,7 +22577,7 @@
         <v>158.4</v>
       </c>
       <c r="D32" s="102">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.2999999999999972</v>
       </c>
       <c r="E32" s="6">
@@ -22526,11 +22595,11 @@
         <v>319</v>
       </c>
       <c r="L32">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>141.37166941154069</v>
       </c>
       <c r="N32">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.5658137563598702</v>
       </c>
     </row>
@@ -22546,7 +22615,7 @@
         <v>158.4</v>
       </c>
       <c r="D33" s="102">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.2999999999999972</v>
       </c>
       <c r="E33" s="6">
@@ -22555,20 +22624,22 @@
       <c r="F33" s="6">
         <v>8</v>
       </c>
-      <c r="G33" s="6">
-        <v>55</v>
-      </c>
-      <c r="H33" s="6"/>
-      <c r="I33" s="6"/>
+      <c r="G33" s="118">
+        <v>55</v>
+      </c>
+      <c r="H33" s="118"/>
+      <c r="I33" s="118" t="s">
+        <v>683</v>
+      </c>
       <c r="J33" s="6" t="s">
         <v>319</v>
       </c>
       <c r="L33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>172.78759594743863</v>
       </c>
       <c r="N33">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.8026612577731749</v>
       </c>
     </row>
@@ -22597,16 +22668,18 @@
         <v>40</v>
       </c>
       <c r="H34" s="6"/>
-      <c r="I34" s="6"/>
+      <c r="I34" s="6" t="s">
+        <v>682</v>
+      </c>
       <c r="J34" s="6" t="s">
         <v>319</v>
       </c>
       <c r="L34">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>125.66370614359172</v>
       </c>
       <c r="N34">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.9473900056532178</v>
       </c>
     </row>
@@ -22622,7 +22695,7 @@
         <v>180.4</v>
       </c>
       <c r="D35" s="102">
-        <f t="shared" ref="D35:D51" si="4">(E35-C35)/2</f>
+        <f t="shared" ref="D35:D51" si="5">(E35-C35)/2</f>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E35" s="6">
@@ -22640,11 +22713,11 @@
         <v>319</v>
       </c>
       <c r="L35">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>141.37166941154069</v>
       </c>
       <c r="N35">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>5.5658137563598702</v>
       </c>
     </row>
@@ -22660,7 +22733,7 @@
         <v>180.4</v>
       </c>
       <c r="D36" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E36" s="6">
@@ -22678,11 +22751,11 @@
         <v>319</v>
       </c>
       <c r="L36">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>157.07963267948966</v>
       </c>
       <c r="N36">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.1842375070665225</v>
       </c>
     </row>
@@ -22698,7 +22771,7 @@
         <v>180.4</v>
       </c>
       <c r="D37" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E37" s="6">
@@ -22707,20 +22780,22 @@
       <c r="F37" s="6">
         <v>8</v>
       </c>
-      <c r="G37" s="6">
-        <v>55</v>
-      </c>
-      <c r="H37" s="6"/>
-      <c r="I37" s="6"/>
+      <c r="G37" s="118">
+        <v>55</v>
+      </c>
+      <c r="H37" s="118"/>
+      <c r="I37" s="118" t="s">
+        <v>684</v>
+      </c>
       <c r="J37" s="6" t="s">
         <v>319</v>
       </c>
       <c r="L37">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>172.78759594743863</v>
       </c>
       <c r="N37">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.8026612577731749</v>
       </c>
     </row>
@@ -22736,7 +22811,7 @@
         <v>180.4</v>
       </c>
       <c r="D38" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E38" s="6">
@@ -22754,11 +22829,11 @@
         <v>319</v>
       </c>
       <c r="L38">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>188.49555921538757</v>
       </c>
       <c r="N38">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.4210850084798263</v>
       </c>
     </row>
@@ -22774,7 +22849,7 @@
         <v>206.4</v>
       </c>
       <c r="D39" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-3.7000000000000028</v>
       </c>
       <c r="E39" s="6">
@@ -22792,11 +22867,11 @@
         <v>319</v>
       </c>
       <c r="L39">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>157.07963267948966</v>
       </c>
       <c r="N39">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.1842375070665225</v>
       </c>
     </row>
@@ -22812,7 +22887,7 @@
         <v>206.4</v>
       </c>
       <c r="D40" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-3.7000000000000028</v>
       </c>
       <c r="E40" s="6">
@@ -22830,11 +22905,11 @@
         <v>319</v>
       </c>
       <c r="L40">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>172.78759594743863</v>
       </c>
       <c r="N40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.8026612577731749</v>
       </c>
     </row>
@@ -22850,7 +22925,7 @@
         <v>206.4</v>
       </c>
       <c r="D41" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-3.7000000000000028</v>
       </c>
       <c r="E41" s="6">
@@ -22868,11 +22943,11 @@
         <v>319</v>
       </c>
       <c r="L41">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>188.49555921538757</v>
       </c>
       <c r="N41">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.4210850084798263</v>
       </c>
     </row>
@@ -22888,7 +22963,7 @@
         <v>206.4</v>
       </c>
       <c r="D42" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-1.7000000000000028</v>
       </c>
       <c r="E42" s="6">
@@ -22906,11 +22981,11 @@
         <v>319</v>
       </c>
       <c r="L42">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>172.78759594743863</v>
       </c>
       <c r="N42">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.8026612577731749</v>
       </c>
     </row>
@@ -22926,7 +23001,7 @@
         <v>206.4</v>
       </c>
       <c r="D43" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-1.7000000000000028</v>
       </c>
       <c r="E43" s="6">
@@ -22944,11 +23019,11 @@
         <v>319</v>
       </c>
       <c r="L43">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>188.49555921538757</v>
       </c>
       <c r="N43">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.4210850084798263</v>
       </c>
     </row>
@@ -22964,7 +23039,7 @@
         <v>206.4</v>
       </c>
       <c r="D44" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E44" s="6">
@@ -22982,11 +23057,11 @@
         <v>319</v>
       </c>
       <c r="L44">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>94.247779607693786</v>
       </c>
       <c r="N44">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.7105425042399132</v>
       </c>
     </row>
@@ -23002,7 +23077,7 @@
         <v>206.4</v>
       </c>
       <c r="D45" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E45" s="6">
@@ -23020,11 +23095,11 @@
         <v>319</v>
       </c>
       <c r="L45">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>125.66370614359172</v>
       </c>
       <c r="N45">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>4.9473900056532178</v>
       </c>
     </row>
@@ -23040,7 +23115,7 @@
         <v>206.4</v>
       </c>
       <c r="D46" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E46" s="6">
@@ -23058,11 +23133,11 @@
         <v>319</v>
       </c>
       <c r="L46">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>157.07963267948966</v>
       </c>
       <c r="N46">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.1842375070665225</v>
       </c>
     </row>
@@ -23078,7 +23153,7 @@
         <v>206.4</v>
       </c>
       <c r="D47" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E47" s="6">
@@ -23096,11 +23171,11 @@
         <v>319</v>
       </c>
       <c r="L47">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>172.78759594743863</v>
       </c>
       <c r="N47">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.8026612577731749</v>
       </c>
     </row>
@@ -23116,7 +23191,7 @@
         <v>206.4</v>
       </c>
       <c r="D48" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-0.20000000000000284</v>
       </c>
       <c r="E48" s="6">
@@ -23134,11 +23209,11 @@
         <v>319</v>
       </c>
       <c r="L48">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>188.49555921538757</v>
       </c>
       <c r="N48">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.4210850084798263</v>
       </c>
     </row>
@@ -23154,7 +23229,7 @@
         <v>261.27000000000004</v>
       </c>
       <c r="D49" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-2.1350000000000193</v>
       </c>
       <c r="E49" s="6">
@@ -23172,11 +23247,11 @@
         <v>319</v>
       </c>
       <c r="L49">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>172.78759594743863</v>
       </c>
       <c r="N49">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.8026612577731749</v>
       </c>
     </row>
@@ -23192,7 +23267,7 @@
         <v>261.27000000000004</v>
       </c>
       <c r="D50" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-1.1350000000000193</v>
       </c>
       <c r="E50" s="6">
@@ -23210,11 +23285,11 @@
         <v>319</v>
       </c>
       <c r="L50">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>157.07963267948966</v>
       </c>
       <c r="N50">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>6.1842375070665225</v>
       </c>
     </row>
@@ -23230,7 +23305,7 @@
         <v>261.27000000000004</v>
       </c>
       <c r="D51" s="102">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-1.1350000000000193</v>
       </c>
       <c r="E51" s="6">
@@ -23248,11 +23323,11 @@
         <v>319</v>
       </c>
       <c r="L51">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>188.49555921538757</v>
       </c>
       <c r="N51">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.4210850084798263</v>
       </c>
     </row>
@@ -23268,7 +23343,7 @@
         <v>257.05</v>
       </c>
       <c r="D52" s="102">
-        <f t="shared" ref="D52" si="5">(E52-C52)/2</f>
+        <f t="shared" ref="D52" si="6">(E52-C52)/2</f>
         <v>1.4749999999999943</v>
       </c>
       <c r="E52" s="6">
@@ -23284,11 +23359,11 @@
         <v>319</v>
       </c>
       <c r="L52">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>188.49555921538757</v>
       </c>
       <c r="N52">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>7.4210850084798263</v>
       </c>
     </row>
@@ -23304,7 +23379,7 @@
         <v>257.05</v>
       </c>
       <c r="D53" s="102">
-        <f t="shared" ref="D53" si="6">(E53-C53)/2</f>
+        <f t="shared" ref="D53" si="7">(E53-C53)/2</f>
         <v>1.4749999999999943</v>
       </c>
       <c r="E53" s="6">
@@ -23320,11 +23395,11 @@
         <v>319</v>
       </c>
       <c r="L53">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>251.32741228718345</v>
       </c>
       <c r="N53">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9.8947800113064357</v>
       </c>
     </row>
@@ -26951,7 +27026,7 @@
       </c>
       <c r="F68" s="2">
         <f>Chaindrive!L14</f>
-        <v>14.842105263157896</v>
+        <v>15.157894736842106</v>
       </c>
       <c r="G68" s="1">
         <v>415</v>
@@ -27013,7 +27088,7 @@
       </c>
       <c r="F69" s="2">
         <f>Chaindrive!L15</f>
-        <v>12.368421052631579</v>
+        <v>12.631578947368421</v>
       </c>
       <c r="G69" s="1">
         <v>415</v>
@@ -31691,11 +31766,11 @@
         <v>471.83333333333331</v>
       </c>
       <c r="K14" s="71">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L14" s="75">
         <f t="shared" ref="L14" si="12">K14/G14</f>
-        <v>14.842105263157896</v>
+        <v>15.157894736842106</v>
       </c>
       <c r="M14" s="71">
         <v>415</v>
@@ -31754,11 +31829,11 @@
         <v>566.19999999999993</v>
       </c>
       <c r="K15" s="71">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L15" s="75">
         <f t="shared" ref="L15" si="15">K15/G15</f>
-        <v>12.368421052631579</v>
+        <v>12.631578947368421</v>
       </c>
       <c r="M15" s="71">
         <v>415</v>

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4126" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{70F50962-26D1-45FF-A7FE-91193536CB9F}"/>
+  <xr:revisionPtr revIDLastSave="4157" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DCDF4D2-3E6A-4347-BE61-3BDC158C1055}"/>
   <bookViews>
-    <workbookView xWindow="16170" yWindow="1610" windowWidth="21140" windowHeight="19510" tabRatio="905" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4620" yWindow="180" windowWidth="26210" windowHeight="19510" tabRatio="905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lath" sheetId="7" r:id="rId1"/>
@@ -852,7 +852,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2921" uniqueCount="686">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2921" uniqueCount="693">
   <si>
     <t>Name</t>
   </si>
@@ -3246,6 +3246,27 @@
   </si>
   <si>
     <t>square</t>
+  </si>
+  <si>
+    <t>139.7 x 5</t>
+  </si>
+  <si>
+    <t>193.7 x 6.3</t>
+  </si>
+  <si>
+    <t>219.1 x 6.3</t>
+  </si>
+  <si>
+    <t>273 x 6.3</t>
+  </si>
+  <si>
+    <t>127 x 3.25</t>
+  </si>
+  <si>
+    <t>102 x 1.5</t>
+  </si>
+  <si>
+    <t>168.3 x 5</t>
   </si>
 </sst>
 </file>
@@ -3545,7 +3566,7 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3917,9 +3938,6 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -3978,13 +3996,13 @@
     <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="20% - Accent1 2" xfId="1" xr:uid="{4B6C72F7-C4CA-450E-9C13-94CEF72F8B8D}"/>
@@ -14605,7 +14623,7 @@
       <c r="E37" s="54">
         <v>79</v>
       </c>
-      <c r="F37" s="137">
+      <c r="F37" s="136">
         <v>200</v>
       </c>
       <c r="G37" s="54">
@@ -14658,7 +14676,7 @@
       <c r="E38" s="93">
         <v>57</v>
       </c>
-      <c r="F38" s="138">
+      <c r="F38" s="137">
         <v>150</v>
       </c>
       <c r="G38" s="93">
@@ -17974,7 +17992,7 @@
       <c r="G1" s="19" t="s">
         <v>557</v>
       </c>
-      <c r="H1" s="136" t="s">
+      <c r="H1" s="135" t="s">
         <v>643</v>
       </c>
       <c r="I1" s="19" t="s">
@@ -18006,7 +18024,7 @@
       </c>
     </row>
     <row r="2" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="142" t="s">
+      <c r="A2" s="141" t="s">
         <v>169</v>
       </c>
       <c r="B2" s="18">
@@ -18056,7 +18074,7 @@
       </c>
     </row>
     <row r="3" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="142" t="s">
+      <c r="A3" s="141" t="s">
         <v>170</v>
       </c>
       <c r="B3" s="18">
@@ -18107,7 +18125,7 @@
       </c>
     </row>
     <row r="4" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="142" t="s">
+      <c r="A4" s="141" t="s">
         <v>614</v>
       </c>
       <c r="B4" s="18">
@@ -18158,7 +18176,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="142" t="s">
+      <c r="A5" s="141" t="s">
         <v>678</v>
       </c>
       <c r="B5" s="18">
@@ -18209,7 +18227,7 @@
       </c>
     </row>
     <row r="6" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="142" t="s">
+      <c r="A6" s="141" t="s">
         <v>171</v>
       </c>
       <c r="B6" s="18">
@@ -18259,7 +18277,7 @@
       </c>
     </row>
     <row r="7" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="142" t="s">
+      <c r="A7" s="141" t="s">
         <v>615</v>
       </c>
       <c r="B7" s="18">
@@ -18310,7 +18328,7 @@
       </c>
     </row>
     <row r="8" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="142" t="s">
+      <c r="A8" s="141" t="s">
         <v>679</v>
       </c>
       <c r="B8" s="18">
@@ -18361,7 +18379,7 @@
       </c>
     </row>
     <row r="9" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="142" t="s">
+      <c r="A9" s="141" t="s">
         <v>172</v>
       </c>
       <c r="B9" s="18">
@@ -18411,10 +18429,10 @@
       </c>
     </row>
     <row r="10" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="143" t="s">
+      <c r="A10" s="142" t="s">
         <v>173</v>
       </c>
-      <c r="B10" s="140">
+      <c r="B10" s="139">
         <v>1.2</v>
       </c>
       <c r="C10" s="1">
@@ -18461,10 +18479,10 @@
       </c>
     </row>
     <row r="11" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="143" t="s">
+      <c r="A11" s="142" t="s">
         <v>616</v>
       </c>
-      <c r="B11" s="141">
+      <c r="B11" s="140">
         <f>0.82+0.72</f>
         <v>1.54</v>
       </c>
@@ -18512,7 +18530,7 @@
       </c>
     </row>
     <row r="12" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="144" t="s">
+      <c r="A12" s="143" t="s">
         <v>617</v>
       </c>
       <c r="B12" s="18">
@@ -18562,7 +18580,7 @@
       </c>
     </row>
     <row r="13" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="144" t="s">
+      <c r="A13" s="143" t="s">
         <v>646</v>
       </c>
       <c r="B13" s="52">
@@ -18612,7 +18630,7 @@
       </c>
     </row>
     <row r="14" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="144" t="s">
+      <c r="A14" s="143" t="s">
         <v>174</v>
       </c>
       <c r="B14" s="52">
@@ -18662,7 +18680,7 @@
       </c>
     </row>
     <row r="15" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="144" t="s">
+      <c r="A15" s="143" t="s">
         <v>175</v>
       </c>
       <c r="B15" s="47">
@@ -18712,7 +18730,7 @@
       </c>
     </row>
     <row r="16" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="144" t="s">
+      <c r="A16" s="143" t="s">
         <v>176</v>
       </c>
       <c r="B16" s="47">
@@ -18762,7 +18780,7 @@
       </c>
     </row>
     <row r="17" spans="1:16" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="144" t="s">
+      <c r="A17" s="143" t="s">
         <v>177</v>
       </c>
       <c r="B17" s="47">
@@ -18851,22 +18869,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="139" t="s">
+      <c r="A1" s="138" t="s">
         <v>178</v>
       </c>
-      <c r="B1" s="139" t="s">
+      <c r="B1" s="138" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="139" t="s">
+      <c r="C1" s="138" t="s">
         <v>592</v>
       </c>
-      <c r="D1" s="139" t="s">
+      <c r="D1" s="138" t="s">
         <v>135</v>
       </c>
-      <c r="E1" s="139" t="s">
+      <c r="E1" s="138" t="s">
         <v>179</v>
       </c>
-      <c r="F1" s="139" t="s">
+      <c r="F1" s="138" t="s">
         <v>13</v>
       </c>
       <c r="G1" s="19" t="s">
@@ -18919,7 +18937,7 @@
       </c>
     </row>
     <row r="2" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="145" t="s">
+      <c r="A2" s="144" t="s">
         <v>183</v>
       </c>
       <c r="B2" s="57" t="s">
@@ -18983,7 +19001,7 @@
       <c r="Y2" s="1"/>
     </row>
     <row r="3" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="145" t="s">
+      <c r="A3" s="144" t="s">
         <v>185</v>
       </c>
       <c r="B3" s="57" t="s">
@@ -19047,7 +19065,7 @@
       <c r="Y3" s="1"/>
     </row>
     <row r="4" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="145" t="s">
+      <c r="A4" s="144" t="s">
         <v>186</v>
       </c>
       <c r="B4" s="57" t="s">
@@ -19111,7 +19129,7 @@
       <c r="Y4" s="1"/>
     </row>
     <row r="5" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="145" t="s">
+      <c r="A5" s="144" t="s">
         <v>188</v>
       </c>
       <c r="B5" s="57" t="s">
@@ -19175,7 +19193,7 @@
       <c r="Y5" s="1"/>
     </row>
     <row r="6" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="145" t="s">
+      <c r="A6" s="144" t="s">
         <v>189</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -19241,7 +19259,7 @@
       </c>
     </row>
     <row r="7" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="145" t="s">
+      <c r="A7" s="144" t="s">
         <v>485</v>
       </c>
       <c r="B7" s="57" t="s">
@@ -19307,7 +19325,7 @@
       </c>
     </row>
     <row r="8" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="145"/>
+      <c r="A8" s="144"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -19322,7 +19340,7 @@
       <c r="X8" s="1"/>
     </row>
     <row r="9" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="145" t="s">
+      <c r="A9" s="144" t="s">
         <v>190</v>
       </c>
       <c r="B9" s="57" t="s">
@@ -19381,7 +19399,7 @@
       </c>
     </row>
     <row r="10" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="145" t="s">
+      <c r="A10" s="144" t="s">
         <v>191</v>
       </c>
       <c r="B10" s="57" t="s">
@@ -19440,7 +19458,7 @@
       </c>
     </row>
     <row r="11" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="145" t="s">
+      <c r="A11" s="144" t="s">
         <v>192</v>
       </c>
       <c r="B11" s="57" t="s">
@@ -19499,7 +19517,7 @@
       </c>
     </row>
     <row r="12" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="145" t="s">
+      <c r="A12" s="144" t="s">
         <v>193</v>
       </c>
       <c r="B12" s="57" t="s">
@@ -19558,7 +19576,7 @@
       </c>
     </row>
     <row r="13" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="145" t="s">
+      <c r="A13" s="144" t="s">
         <v>194</v>
       </c>
       <c r="B13" s="57" t="s">
@@ -19615,7 +19633,7 @@
       </c>
     </row>
     <row r="14" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="145" t="s">
+      <c r="A14" s="144" t="s">
         <v>195</v>
       </c>
       <c r="B14" s="57" t="s">
@@ -19672,7 +19690,7 @@
       </c>
     </row>
     <row r="15" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="145" t="s">
+      <c r="A15" s="144" t="s">
         <v>196</v>
       </c>
       <c r="B15" s="57" t="s">
@@ -19806,7 +19824,7 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A2" s="146" t="s">
+      <c r="A2" s="145" t="s">
         <v>153</v>
       </c>
       <c r="B2" s="6" t="s">
@@ -19859,7 +19877,7 @@
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A3" s="146" t="s">
+      <c r="A3" s="145" t="s">
         <v>157</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -19912,7 +19930,7 @@
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A4" s="146" t="s">
+      <c r="A4" s="145" t="s">
         <v>159</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -19965,7 +19983,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A5" s="146" t="s">
+      <c r="A5" s="145" t="s">
         <v>160</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -20018,7 +20036,7 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A6" s="146" t="s">
+      <c r="A6" s="145" t="s">
         <v>162</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -20071,7 +20089,7 @@
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A7" s="146" t="s">
+      <c r="A7" s="145" t="s">
         <v>146</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -20124,15 +20142,15 @@
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A8" s="147" t="s">
+      <c r="A8" s="146" t="s">
         <v>612</v>
       </c>
-      <c r="B8" s="148" t="s">
+      <c r="B8" s="147" t="s">
         <v>612</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A9" s="146" t="s">
+      <c r="A9" s="145" t="s">
         <v>608</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -20185,7 +20203,7 @@
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A10" s="146" t="s">
+      <c r="A10" s="145" t="s">
         <v>609</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -20238,7 +20256,7 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A11" s="146" t="s">
+      <c r="A11" s="145" t="s">
         <v>625</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -20288,7 +20306,7 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A12" s="146" t="s">
+      <c r="A12" s="145" t="s">
         <v>610</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -20341,7 +20359,7 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A13" s="146" t="s">
+      <c r="A13" s="145" t="s">
         <v>611</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -20394,7 +20412,7 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A14" s="146" t="s">
+      <c r="A14" s="145" t="s">
         <v>613</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -20447,7 +20465,7 @@
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A15" s="146" t="s">
+      <c r="A15" s="145" t="s">
         <v>163</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -20500,7 +20518,7 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A16" s="146" t="s">
+      <c r="A16" s="145" t="s">
         <v>649</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -20553,7 +20571,7 @@
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B21" s="146" t="s">
+      <c r="B21" s="145" t="s">
         <v>650</v>
       </c>
       <c r="D21" s="6">
@@ -20628,7 +20646,7 @@
       <c r="N1" s="44" t="s">
         <v>631</v>
       </c>
-      <c r="O1" s="158" t="s">
+      <c r="O1" s="44" t="s">
         <v>680</v>
       </c>
     </row>
@@ -20742,7 +20760,7 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
-        <v>213</v>
+        <v>691</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>214</v>
@@ -20751,14 +20769,14 @@
         <v>215</v>
       </c>
       <c r="D5" s="21">
-        <v>102</v>
+        <v>101.6</v>
       </c>
       <c r="E5" s="21">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="F5" s="14">
         <f>D5-(E5*2)</f>
-        <v>98.8</v>
+        <v>98.6</v>
       </c>
       <c r="G5" s="14">
         <v>190000</v>
@@ -20775,7 +20793,7 @@
       </c>
       <c r="L5">
         <f>D5/25.4</f>
-        <v>4.015748031496063</v>
+        <v>4</v>
       </c>
       <c r="M5" s="1" t="s">
         <v>22</v>
@@ -20795,14 +20813,14 @@
         <v>217</v>
       </c>
       <c r="D6" s="21">
-        <v>102</v>
+        <v>101.6</v>
       </c>
       <c r="E6" s="21">
         <v>3</v>
       </c>
       <c r="F6" s="14">
         <f t="shared" ref="F6:F7" si="3">D6-(E6*2)</f>
-        <v>96</v>
+        <v>95.6</v>
       </c>
       <c r="G6" s="14">
         <v>190000</v>
@@ -20819,7 +20837,7 @@
       </c>
       <c r="L6">
         <f t="shared" ref="L6:L12" si="4">D6/25.4</f>
-        <v>4.015748031496063</v>
+        <v>4</v>
       </c>
       <c r="M6" s="1" t="s">
         <v>22</v>
@@ -20830,7 +20848,7 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
-        <v>218</v>
+        <v>690</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>214</v>
@@ -20874,7 +20892,7 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
-        <v>220</v>
+        <v>686</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>214</v>
@@ -20883,14 +20901,14 @@
         <v>221</v>
       </c>
       <c r="D8" s="21">
-        <v>139</v>
+        <v>139.69999999999999</v>
       </c>
       <c r="E8" s="21">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="F8" s="14">
         <f>D8-(E8*2)</f>
-        <v>129.4</v>
+        <v>129.69999999999999</v>
       </c>
       <c r="G8" s="14">
         <v>210000</v>
@@ -20907,7 +20925,7 @@
       </c>
       <c r="L8">
         <f t="shared" si="4"/>
-        <v>5.4724409448818898</v>
+        <v>5.5</v>
       </c>
       <c r="M8" s="1" t="s">
         <v>55</v>
@@ -20918,7 +20936,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
-        <v>222</v>
+        <v>692</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>214</v>
@@ -20927,17 +20945,17 @@
         <v>223</v>
       </c>
       <c r="D9" s="21">
-        <v>168</v>
+        <v>168.3</v>
       </c>
       <c r="E9" s="21">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="F9" s="14">
         <f>D9-(E9*2)</f>
-        <v>158.4</v>
+        <v>158.30000000000001</v>
       </c>
       <c r="G9" s="14">
-        <v>210000</v>
+        <v>190000</v>
       </c>
       <c r="H9" s="14">
         <v>7850</v>
@@ -20951,7 +20969,7 @@
       </c>
       <c r="L9">
         <f t="shared" si="4"/>
-        <v>6.6141732283464574</v>
+        <v>6.6259842519685046</v>
       </c>
       <c r="M9" s="1" t="s">
         <v>55</v>
@@ -20962,7 +20980,7 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A10" s="101" t="s">
-        <v>224</v>
+        <v>687</v>
       </c>
       <c r="B10" s="101" t="s">
         <v>214</v>
@@ -20971,14 +20989,14 @@
         <v>225</v>
       </c>
       <c r="D10" s="101">
-        <v>193</v>
+        <v>193.7</v>
       </c>
       <c r="E10" s="101">
         <v>6.3</v>
       </c>
       <c r="F10" s="100">
         <f t="shared" ref="F10" si="6">D10-(E10*2)</f>
-        <v>180.4</v>
+        <v>181.1</v>
       </c>
       <c r="G10" s="100">
         <v>190000</v>
@@ -20995,7 +21013,7 @@
       </c>
       <c r="L10">
         <f t="shared" si="4"/>
-        <v>7.5984251968503944</v>
+        <v>7.6259842519685037</v>
       </c>
       <c r="M10" s="1" t="s">
         <v>55</v>
@@ -21005,41 +21023,41 @@
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A11" s="98" t="s">
-        <v>226</v>
-      </c>
-      <c r="B11" s="98" t="s">
+      <c r="A11" s="100" t="s">
+        <v>688</v>
+      </c>
+      <c r="B11" s="100" t="s">
         <v>214</v>
       </c>
-      <c r="C11" s="135" t="s">
+      <c r="C11" s="101" t="s">
         <v>227</v>
       </c>
-      <c r="D11" s="99">
-        <v>219</v>
-      </c>
-      <c r="E11" s="99">
+      <c r="D11" s="158">
+        <v>219.1</v>
+      </c>
+      <c r="E11" s="158">
         <v>6.3</v>
       </c>
-      <c r="F11" s="98">
+      <c r="F11" s="100">
         <f t="shared" ref="F11:F12" si="7">D11-(E11*2)</f>
-        <v>206.4</v>
-      </c>
-      <c r="G11" s="98">
+        <v>206.5</v>
+      </c>
+      <c r="G11" s="100">
         <v>190000</v>
       </c>
-      <c r="H11" s="98">
+      <c r="H11" s="100">
         <v>7850</v>
       </c>
-      <c r="I11" s="98"/>
-      <c r="J11" s="98" t="s">
+      <c r="I11" s="100"/>
+      <c r="J11" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="K11" s="98" t="s">
+      <c r="K11" s="100" t="s">
         <v>630</v>
       </c>
       <c r="L11">
         <f t="shared" si="4"/>
-        <v>8.6220472440944889</v>
+        <v>8.6259842519685037</v>
       </c>
       <c r="M11" s="1" t="s">
         <v>55</v>
@@ -21049,39 +21067,39 @@
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.35">
-      <c r="A12" s="98" t="s">
-        <v>228</v>
-      </c>
-      <c r="B12" s="98" t="s">
+      <c r="A12" s="100" t="s">
+        <v>689</v>
+      </c>
+      <c r="B12" s="100" t="s">
         <v>214</v>
       </c>
-      <c r="C12" s="98" t="s">
+      <c r="C12" s="100" t="s">
         <v>229</v>
       </c>
-      <c r="D12" s="99">
-        <v>273.05</v>
-      </c>
-      <c r="E12" s="99">
-        <v>5.89</v>
-      </c>
-      <c r="F12" s="98">
+      <c r="D12" s="158">
+        <v>273</v>
+      </c>
+      <c r="E12" s="158">
+        <v>6.3</v>
+      </c>
+      <c r="F12" s="100">
         <f t="shared" si="7"/>
-        <v>261.27000000000004</v>
-      </c>
-      <c r="G12" s="98">
+        <v>260.39999999999998</v>
+      </c>
+      <c r="G12" s="100">
         <v>199000</v>
       </c>
-      <c r="H12" s="98">
+      <c r="H12" s="100">
         <v>7850</v>
       </c>
-      <c r="I12" s="98"/>
-      <c r="J12" s="98" t="s">
+      <c r="I12" s="100"/>
+      <c r="J12" s="100" t="s">
         <v>22</v>
       </c>
-      <c r="K12" s="98"/>
+      <c r="K12" s="100"/>
       <c r="L12">
         <f t="shared" si="4"/>
-        <v>10.750000000000002</v>
+        <v>10.748031496062993</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>55</v>
@@ -21101,14 +21119,14 @@
         <v>495</v>
       </c>
       <c r="D13" s="99">
-        <v>273.05</v>
+        <v>273</v>
       </c>
       <c r="E13" s="99">
         <v>8</v>
       </c>
       <c r="F13" s="98">
         <f t="shared" ref="F13" si="8">D13-(E13*2)</f>
-        <v>257.05</v>
+        <v>257</v>
       </c>
       <c r="G13" s="98">
         <v>199000</v>
@@ -21145,18 +21163,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B3" s="154" t="s">
+      <c r="B3" s="153" t="s">
         <v>668</v>
       </c>
-      <c r="C3" s="154" t="s">
+      <c r="C3" s="153" t="s">
         <v>669</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B4" s="155" t="s">
+      <c r="B4" s="154" t="s">
         <v>652</v>
       </c>
-      <c r="C4" s="155" t="s">
+      <c r="C4" s="154" t="s">
         <v>660</v>
       </c>
       <c r="E4">
@@ -21167,10 +21185,10 @@
       </c>
     </row>
     <row r="5" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B5" s="155" t="s">
+      <c r="B5" s="154" t="s">
         <v>653</v>
       </c>
-      <c r="C5" s="155" t="s">
+      <c r="C5" s="154" t="s">
         <v>661</v>
       </c>
       <c r="E5">
@@ -21189,10 +21207,10 @@
       </c>
     </row>
     <row r="6" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B6" s="155" t="s">
+      <c r="B6" s="154" t="s">
         <v>654</v>
       </c>
-      <c r="C6" s="155" t="s">
+      <c r="C6" s="154" t="s">
         <v>662</v>
       </c>
       <c r="E6">
@@ -21211,10 +21229,10 @@
       </c>
     </row>
     <row r="7" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B7" s="155" t="s">
+      <c r="B7" s="154" t="s">
         <v>655</v>
       </c>
-      <c r="C7" s="155" t="s">
+      <c r="C7" s="154" t="s">
         <v>663</v>
       </c>
       <c r="E7">
@@ -21233,10 +21251,10 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B8" s="155" t="s">
+      <c r="B8" s="154" t="s">
         <v>656</v>
       </c>
-      <c r="C8" s="155" t="s">
+      <c r="C8" s="154" t="s">
         <v>664</v>
       </c>
       <c r="E8">
@@ -21255,10 +21273,10 @@
       </c>
     </row>
     <row r="9" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B9" s="155" t="s">
+      <c r="B9" s="154" t="s">
         <v>657</v>
       </c>
-      <c r="C9" s="155" t="s">
+      <c r="C9" s="154" t="s">
         <v>665</v>
       </c>
       <c r="E9">
@@ -21277,10 +21295,10 @@
       </c>
     </row>
     <row r="10" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B10" s="155" t="s">
+      <c r="B10" s="154" t="s">
         <v>658</v>
       </c>
-      <c r="C10" s="155" t="s">
+      <c r="C10" s="154" t="s">
         <v>666</v>
       </c>
       <c r="E10">
@@ -21299,10 +21317,10 @@
       </c>
     </row>
     <row r="11" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B11" s="155" t="s">
+      <c r="B11" s="154" t="s">
         <v>659</v>
       </c>
-      <c r="C11" s="155" t="s">
+      <c r="C11" s="154" t="s">
         <v>667</v>
       </c>
       <c r="E11">
@@ -21321,7 +21339,7 @@
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="C13" s="156" t="s">
+      <c r="C13" s="155" t="s">
         <v>670</v>
       </c>
       <c r="D13" s="117"/>
@@ -21446,11 +21464,11 @@
       </c>
       <c r="C3" s="6">
         <f>Axles!F5</f>
-        <v>98.8</v>
+        <v>98.6</v>
       </c>
       <c r="D3" s="102">
         <f t="shared" ref="D3:D20" si="1">(E3-C3)/2</f>
-        <v>-0.64999999999999858</v>
+        <v>-0.54999999999999716</v>
       </c>
       <c r="E3" s="6">
         <v>97.5</v>
@@ -21484,11 +21502,11 @@
       </c>
       <c r="C4" s="6">
         <f>Axles!F5</f>
-        <v>98.8</v>
+        <v>98.6</v>
       </c>
       <c r="D4" s="102">
         <f t="shared" si="1"/>
-        <v>-0.64999999999999858</v>
+        <v>-0.54999999999999716</v>
       </c>
       <c r="E4" s="6">
         <v>97.5</v>
@@ -21524,11 +21542,11 @@
       </c>
       <c r="C5" s="6">
         <f>Axles!F5</f>
-        <v>98.8</v>
+        <v>98.6</v>
       </c>
       <c r="D5" s="102">
         <f t="shared" si="1"/>
-        <v>-0.64999999999999858</v>
+        <v>-0.54999999999999716</v>
       </c>
       <c r="E5" s="6">
         <v>97.5</v>
@@ -21562,11 +21580,11 @@
       </c>
       <c r="C6" s="6">
         <f>Axles!F6</f>
-        <v>96</v>
+        <v>95.6</v>
       </c>
       <c r="D6" s="102">
         <f t="shared" si="1"/>
-        <v>-1.5</v>
+        <v>-1.2999999999999972</v>
       </c>
       <c r="E6" s="6">
         <v>93</v>
@@ -21600,11 +21618,11 @@
       </c>
       <c r="C7" s="6">
         <f>Axles!F6</f>
-        <v>96</v>
+        <v>95.6</v>
       </c>
       <c r="D7" s="102">
         <f t="shared" si="1"/>
-        <v>-1.5</v>
+        <v>-1.2999999999999972</v>
       </c>
       <c r="E7" s="6">
         <v>93</v>
@@ -21640,11 +21658,11 @@
       </c>
       <c r="C8" s="6">
         <f>Axles!F6</f>
-        <v>96</v>
+        <v>95.6</v>
       </c>
       <c r="D8" s="102">
         <f t="shared" si="1"/>
-        <v>-1.5</v>
+        <v>-1.2999999999999972</v>
       </c>
       <c r="E8" s="6">
         <v>93</v>
@@ -21678,11 +21696,11 @@
       </c>
       <c r="C9" s="6">
         <f>Axles!F6</f>
-        <v>96</v>
+        <v>95.6</v>
       </c>
       <c r="D9" s="102">
         <f t="shared" si="1"/>
-        <v>-1.5</v>
+        <v>-1.2999999999999972</v>
       </c>
       <c r="E9" s="6">
         <v>93</v>
@@ -21718,11 +21736,11 @@
       </c>
       <c r="C10" s="6">
         <f>Axles!F6</f>
-        <v>96</v>
+        <v>95.6</v>
       </c>
       <c r="D10" s="102">
         <f t="shared" si="1"/>
-        <v>-1.5</v>
+        <v>-1.2999999999999972</v>
       </c>
       <c r="E10" s="6">
         <v>93</v>
@@ -21950,11 +21968,11 @@
       </c>
       <c r="C16" s="6">
         <f>Axles!F8</f>
-        <v>129.4</v>
+        <v>129.69999999999999</v>
       </c>
       <c r="D16" s="102">
         <f t="shared" si="1"/>
-        <v>-0.45000000000000284</v>
+        <v>-0.59999999999999432</v>
       </c>
       <c r="E16" s="6">
         <v>128.5</v>
@@ -21990,11 +22008,11 @@
       </c>
       <c r="C17" s="6">
         <f>Axles!F8</f>
-        <v>129.4</v>
+        <v>129.69999999999999</v>
       </c>
       <c r="D17" s="102">
         <f t="shared" si="1"/>
-        <v>-0.45000000000000284</v>
+        <v>-0.59999999999999432</v>
       </c>
       <c r="E17" s="6">
         <v>128.5</v>
@@ -22028,11 +22046,11 @@
       </c>
       <c r="C18" s="6">
         <f>Axles!F8</f>
-        <v>129.4</v>
+        <v>129.69999999999999</v>
       </c>
       <c r="D18" s="102">
         <f t="shared" si="1"/>
-        <v>-0.45000000000000284</v>
+        <v>-0.59999999999999432</v>
       </c>
       <c r="E18" s="6">
         <v>128.5</v>
@@ -22068,11 +22086,11 @@
       </c>
       <c r="C19" s="6">
         <f>Axles!F8</f>
-        <v>129.4</v>
+        <v>129.69999999999999</v>
       </c>
       <c r="D19" s="102">
         <f t="shared" si="1"/>
-        <v>-0.45000000000000284</v>
+        <v>-0.59999999999999432</v>
       </c>
       <c r="E19" s="6">
         <v>128.5</v>
@@ -22106,11 +22124,11 @@
       </c>
       <c r="C20" s="6">
         <f>Axles!F8</f>
-        <v>129.4</v>
+        <v>129.69999999999999</v>
       </c>
       <c r="D20" s="102">
         <f t="shared" si="1"/>
-        <v>-0.45000000000000284</v>
+        <v>-0.59999999999999432</v>
       </c>
       <c r="E20" s="6">
         <v>128.5</v>
@@ -22146,11 +22164,11 @@
       </c>
       <c r="C21" s="6">
         <f>Axles!F9</f>
-        <v>158.4</v>
+        <v>158.30000000000001</v>
       </c>
       <c r="D21" s="102">
         <f t="shared" ref="D21:D33" si="4">(E21-C21)/2</f>
-        <v>-1.7000000000000028</v>
+        <v>-1.6500000000000057</v>
       </c>
       <c r="E21" s="6">
         <v>155</v>
@@ -22186,11 +22204,11 @@
       </c>
       <c r="C22" s="6">
         <f>Axles!F9</f>
-        <v>158.4</v>
+        <v>158.30000000000001</v>
       </c>
       <c r="D22" s="102">
         <f t="shared" si="4"/>
-        <v>-1.7000000000000028</v>
+        <v>-1.6500000000000057</v>
       </c>
       <c r="E22" s="6">
         <v>155</v>
@@ -22224,11 +22242,11 @@
       </c>
       <c r="C23" s="6">
         <f>Axles!F9</f>
-        <v>158.4</v>
+        <v>158.30000000000001</v>
       </c>
       <c r="D23" s="102">
         <f t="shared" si="4"/>
-        <v>-1.7000000000000028</v>
+        <v>-1.6500000000000057</v>
       </c>
       <c r="E23" s="6">
         <v>155</v>
@@ -22264,11 +22282,11 @@
       </c>
       <c r="C24" s="6">
         <f>Axles!F9</f>
-        <v>158.4</v>
+        <v>158.30000000000001</v>
       </c>
       <c r="D24" s="102">
         <f t="shared" si="4"/>
-        <v>-0.20000000000000284</v>
+        <v>-0.15000000000000568</v>
       </c>
       <c r="E24" s="6">
         <v>158</v>
@@ -22302,11 +22320,11 @@
       </c>
       <c r="C25" s="6">
         <f>Axles!F9</f>
-        <v>158.4</v>
+        <v>158.30000000000001</v>
       </c>
       <c r="D25" s="102">
         <f t="shared" si="4"/>
-        <v>-0.20000000000000284</v>
+        <v>-0.15000000000000568</v>
       </c>
       <c r="E25" s="6">
         <v>158</v>
@@ -22340,11 +22358,11 @@
       </c>
       <c r="C26" s="6">
         <f>Axles!F9</f>
-        <v>158.4</v>
+        <v>158.30000000000001</v>
       </c>
       <c r="D26" s="102">
         <f t="shared" si="4"/>
-        <v>-0.20000000000000284</v>
+        <v>-0.15000000000000568</v>
       </c>
       <c r="E26" s="6">
         <v>158</v>
@@ -22356,7 +22374,7 @@
         <v>40</v>
       </c>
       <c r="H26" s="6"/>
-      <c r="I26" s="159" t="s">
+      <c r="I26" s="156" t="s">
         <v>681</v>
       </c>
       <c r="J26" s="6" t="s">
@@ -22380,11 +22398,11 @@
       </c>
       <c r="C27" s="6">
         <f>Axles!F9</f>
-        <v>158.4</v>
+        <v>158.30000000000001</v>
       </c>
       <c r="D27" s="102">
         <f t="shared" si="4"/>
-        <v>-0.20000000000000284</v>
+        <v>-0.15000000000000568</v>
       </c>
       <c r="E27" s="6">
         <v>158</v>
@@ -22418,11 +22436,11 @@
       </c>
       <c r="C28" s="6">
         <f>Axles!F9</f>
-        <v>158.4</v>
+        <v>158.30000000000001</v>
       </c>
       <c r="D28" s="102">
         <f t="shared" si="4"/>
-        <v>-0.20000000000000284</v>
+        <v>-0.15000000000000568</v>
       </c>
       <c r="E28" s="6">
         <v>158</v>
@@ -22458,11 +22476,11 @@
       </c>
       <c r="C29" s="6">
         <f>Axles!F9</f>
-        <v>158.4</v>
+        <v>158.30000000000001</v>
       </c>
       <c r="D29" s="102">
         <f t="shared" si="4"/>
-        <v>1.2999999999999972</v>
+        <v>1.3499999999999943</v>
       </c>
       <c r="E29" s="6">
         <v>161</v>
@@ -22496,11 +22514,11 @@
       </c>
       <c r="C30" s="6">
         <f>Axles!F9</f>
-        <v>158.4</v>
+        <v>158.30000000000001</v>
       </c>
       <c r="D30" s="102">
         <f t="shared" si="4"/>
-        <v>1.2999999999999972</v>
+        <v>1.3499999999999943</v>
       </c>
       <c r="E30" s="6">
         <v>161</v>
@@ -22534,11 +22552,11 @@
       </c>
       <c r="C31" s="6">
         <f>Axles!F9</f>
-        <v>158.4</v>
+        <v>158.30000000000001</v>
       </c>
       <c r="D31" s="102">
         <f t="shared" si="4"/>
-        <v>1.2999999999999972</v>
+        <v>1.3499999999999943</v>
       </c>
       <c r="E31" s="6">
         <v>161</v>
@@ -22574,11 +22592,11 @@
       </c>
       <c r="C32" s="6">
         <f>Axles!F9</f>
-        <v>158.4</v>
+        <v>158.30000000000001</v>
       </c>
       <c r="D32" s="102">
         <f t="shared" si="4"/>
-        <v>1.2999999999999972</v>
+        <v>1.3499999999999943</v>
       </c>
       <c r="E32" s="6">
         <v>161</v>
@@ -22612,11 +22630,11 @@
       </c>
       <c r="C33" s="6">
         <f>Axles!F9</f>
-        <v>158.4</v>
+        <v>158.30000000000001</v>
       </c>
       <c r="D33" s="102">
         <f t="shared" si="4"/>
-        <v>1.2999999999999972</v>
+        <v>1.3499999999999943</v>
       </c>
       <c r="E33" s="6">
         <v>161</v>
@@ -22652,11 +22670,11 @@
       </c>
       <c r="C34" s="102">
         <f>Axles!F10</f>
-        <v>180.4</v>
+        <v>181.1</v>
       </c>
       <c r="D34" s="102">
         <f>(E34-C34)/2</f>
-        <v>-0.20000000000000284</v>
+        <v>-0.54999999999999716</v>
       </c>
       <c r="E34" s="6">
         <v>180</v>
@@ -22692,11 +22710,11 @@
       </c>
       <c r="C35" s="102">
         <f>Axles!F10</f>
-        <v>180.4</v>
+        <v>181.1</v>
       </c>
       <c r="D35" s="102">
         <f t="shared" ref="D35:D51" si="5">(E35-C35)/2</f>
-        <v>-0.20000000000000284</v>
+        <v>-0.54999999999999716</v>
       </c>
       <c r="E35" s="6">
         <v>180</v>
@@ -22730,11 +22748,11 @@
       </c>
       <c r="C36" s="102">
         <f>Axles!F10</f>
-        <v>180.4</v>
+        <v>181.1</v>
       </c>
       <c r="D36" s="102">
         <f t="shared" si="5"/>
-        <v>-0.20000000000000284</v>
+        <v>-0.54999999999999716</v>
       </c>
       <c r="E36" s="6">
         <v>180</v>
@@ -22768,11 +22786,11 @@
       </c>
       <c r="C37" s="102">
         <f>Axles!F10</f>
-        <v>180.4</v>
+        <v>181.1</v>
       </c>
       <c r="D37" s="102">
         <f t="shared" si="5"/>
-        <v>-0.20000000000000284</v>
+        <v>-0.54999999999999716</v>
       </c>
       <c r="E37" s="6">
         <v>180</v>
@@ -22808,11 +22826,11 @@
       </c>
       <c r="C38" s="102">
         <f>Axles!F10</f>
-        <v>180.4</v>
+        <v>181.1</v>
       </c>
       <c r="D38" s="102">
         <f t="shared" si="5"/>
-        <v>-0.20000000000000284</v>
+        <v>-0.54999999999999716</v>
       </c>
       <c r="E38" s="6">
         <v>180</v>
@@ -22846,11 +22864,11 @@
       </c>
       <c r="C39" s="102">
         <f>Axles!F11</f>
-        <v>206.4</v>
+        <v>206.5</v>
       </c>
       <c r="D39" s="102">
         <f t="shared" si="5"/>
-        <v>-3.7000000000000028</v>
+        <v>-3.75</v>
       </c>
       <c r="E39" s="6">
         <v>199</v>
@@ -22884,11 +22902,11 @@
       </c>
       <c r="C40" s="102">
         <f>Axles!F11</f>
-        <v>206.4</v>
+        <v>206.5</v>
       </c>
       <c r="D40" s="102">
         <f t="shared" si="5"/>
-        <v>-3.7000000000000028</v>
+        <v>-3.75</v>
       </c>
       <c r="E40" s="6">
         <v>199</v>
@@ -22922,11 +22940,11 @@
       </c>
       <c r="C41" s="102">
         <f>Axles!F11</f>
-        <v>206.4</v>
+        <v>206.5</v>
       </c>
       <c r="D41" s="102">
         <f t="shared" si="5"/>
-        <v>-3.7000000000000028</v>
+        <v>-3.75</v>
       </c>
       <c r="E41" s="6">
         <v>199</v>
@@ -22960,11 +22978,11 @@
       </c>
       <c r="C42" s="102">
         <f>Axles!F11</f>
-        <v>206.4</v>
+        <v>206.5</v>
       </c>
       <c r="D42" s="102">
         <f t="shared" si="5"/>
-        <v>-1.7000000000000028</v>
+        <v>-1.75</v>
       </c>
       <c r="E42" s="6">
         <v>203</v>
@@ -22998,11 +23016,11 @@
       </c>
       <c r="C43" s="102">
         <f>Axles!F11</f>
-        <v>206.4</v>
+        <v>206.5</v>
       </c>
       <c r="D43" s="102">
         <f t="shared" si="5"/>
-        <v>-1.7000000000000028</v>
+        <v>-1.75</v>
       </c>
       <c r="E43" s="6">
         <v>203</v>
@@ -23036,11 +23054,11 @@
       </c>
       <c r="C44" s="102">
         <f>Axles!F11</f>
-        <v>206.4</v>
+        <v>206.5</v>
       </c>
       <c r="D44" s="102">
         <f t="shared" si="5"/>
-        <v>-0.20000000000000284</v>
+        <v>-0.25</v>
       </c>
       <c r="E44" s="6">
         <v>206</v>
@@ -23074,11 +23092,11 @@
       </c>
       <c r="C45" s="102">
         <f>Axles!F11</f>
-        <v>206.4</v>
+        <v>206.5</v>
       </c>
       <c r="D45" s="102">
         <f t="shared" si="5"/>
-        <v>-0.20000000000000284</v>
+        <v>-0.25</v>
       </c>
       <c r="E45" s="6">
         <v>206</v>
@@ -23112,11 +23130,11 @@
       </c>
       <c r="C46" s="102">
         <f>Axles!F11</f>
-        <v>206.4</v>
+        <v>206.5</v>
       </c>
       <c r="D46" s="102">
         <f t="shared" si="5"/>
-        <v>-0.20000000000000284</v>
+        <v>-0.25</v>
       </c>
       <c r="E46" s="6">
         <v>206</v>
@@ -23150,11 +23168,11 @@
       </c>
       <c r="C47" s="102">
         <f>Axles!F11</f>
-        <v>206.4</v>
+        <v>206.5</v>
       </c>
       <c r="D47" s="102">
         <f t="shared" si="5"/>
-        <v>-0.20000000000000284</v>
+        <v>-0.25</v>
       </c>
       <c r="E47" s="6">
         <v>206</v>
@@ -23188,11 +23206,11 @@
       </c>
       <c r="C48" s="102">
         <f>Axles!F11</f>
-        <v>206.4</v>
+        <v>206.5</v>
       </c>
       <c r="D48" s="102">
         <f t="shared" si="5"/>
-        <v>-0.20000000000000284</v>
+        <v>-0.25</v>
       </c>
       <c r="E48" s="6">
         <v>206</v>
@@ -23226,11 +23244,11 @@
       </c>
       <c r="C49" s="1">
         <f>Axles!F12</f>
-        <v>261.27000000000004</v>
+        <v>260.39999999999998</v>
       </c>
       <c r="D49" s="102">
         <f t="shared" si="5"/>
-        <v>-2.1350000000000193</v>
+        <v>-1.6999999999999886</v>
       </c>
       <c r="E49" s="6">
         <v>257</v>
@@ -23264,11 +23282,11 @@
       </c>
       <c r="C50" s="1">
         <f>Axles!F12</f>
-        <v>261.27000000000004</v>
+        <v>260.39999999999998</v>
       </c>
       <c r="D50" s="102">
         <f t="shared" si="5"/>
-        <v>-1.1350000000000193</v>
+        <v>-0.69999999999998863</v>
       </c>
       <c r="E50" s="6">
         <v>259</v>
@@ -23302,11 +23320,11 @@
       </c>
       <c r="C51" s="1">
         <f>Axles!F12</f>
-        <v>261.27000000000004</v>
+        <v>260.39999999999998</v>
       </c>
       <c r="D51" s="102">
         <f t="shared" si="5"/>
-        <v>-1.1350000000000193</v>
+        <v>-0.69999999999998863</v>
       </c>
       <c r="E51" s="6">
         <v>259</v>
@@ -23340,11 +23358,11 @@
       </c>
       <c r="C52" s="6">
         <f>Axles!F13</f>
-        <v>257.05</v>
+        <v>257</v>
       </c>
       <c r="D52" s="102">
         <f t="shared" ref="D52" si="6">(E52-C52)/2</f>
-        <v>1.4749999999999943</v>
+        <v>1.5</v>
       </c>
       <c r="E52" s="6">
         <v>260</v>
@@ -23376,11 +23394,11 @@
       </c>
       <c r="C53" s="6">
         <f>Axles!F13</f>
-        <v>257.05</v>
+        <v>257</v>
       </c>
       <c r="D53" s="102">
         <f t="shared" ref="D53" si="7">(E53-C53)/2</f>
-        <v>1.4749999999999943</v>
+        <v>1.5</v>
       </c>
       <c r="E53" s="6">
         <v>260</v>
@@ -23794,7 +23812,7 @@
     <col min="18" max="18" width="10.54296875" style="6" customWidth="1"/>
     <col min="19" max="19" width="25" style="6" customWidth="1"/>
     <col min="20" max="20" width="12.26953125" customWidth="1"/>
-    <col min="21" max="21" width="10.54296875" style="80" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12" style="80" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="24.36328125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -26667,7 +26685,7 @@
       <c r="S61" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="U61" s="153">
+      <c r="U61" s="152">
         <v>300.41000000000003</v>
       </c>
     </row>
@@ -26725,7 +26743,7 @@
       <c r="S62" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="U62" s="153">
+      <c r="U62" s="152">
         <v>300.41000000000003</v>
       </c>
     </row>
@@ -26786,7 +26804,7 @@
       <c r="S63" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="U63" s="153">
+      <c r="U63" s="152">
         <v>300.41000000000003</v>
       </c>
     </row>
@@ -26844,7 +26862,7 @@
       <c r="R64" s="6">
         <v>450</v>
       </c>
-      <c r="U64" s="153">
+      <c r="U64" s="152">
         <v>300.41000000000003</v>
       </c>
     </row>
@@ -26880,7 +26898,7 @@
       <c r="Q65" s="107"/>
       <c r="R65" s="110"/>
       <c r="S65" s="110"/>
-      <c r="U65" s="152"/>
+      <c r="U65" s="151"/>
     </row>
     <row r="66" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="str">
@@ -26938,7 +26956,7 @@
       <c r="S66" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="U66" s="151">
+      <c r="U66" s="150">
         <v>179.04</v>
       </c>
     </row>
@@ -26999,7 +27017,7 @@
       <c r="S67" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="U67" s="153">
+      <c r="U67" s="152">
         <v>179.04</v>
       </c>
       <c r="V67" s="83"/>
@@ -27062,7 +27080,7 @@
       <c r="S68" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="U68" s="153">
+      <c r="U68" s="152">
         <v>472.24</v>
       </c>
       <c r="V68" s="83"/>
@@ -27124,7 +27142,7 @@
       <c r="S69" s="6" t="s">
         <v>675</v>
       </c>
-      <c r="U69" s="153">
+      <c r="U69" s="152">
         <v>472.24</v>
       </c>
       <c r="V69" s="83"/>
@@ -27184,7 +27202,7 @@
       <c r="S70" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="U70" s="153">
+      <c r="U70" s="152">
         <v>472.24</v>
       </c>
     </row>
@@ -27241,7 +27259,7 @@
       <c r="R71" s="6">
         <v>650</v>
       </c>
-      <c r="U71" s="153">
+      <c r="U71" s="152">
         <v>498.07</v>
       </c>
     </row>
@@ -28406,7 +28424,7 @@
         <v>323</v>
       </c>
       <c r="T94" s="57"/>
-      <c r="U94" s="150">
+      <c r="U94" s="149">
         <v>266.06</v>
       </c>
       <c r="V94" s="57"/>
@@ -28468,7 +28486,7 @@
         <v>325</v>
       </c>
       <c r="T95" s="57"/>
-      <c r="U95" s="150">
+      <c r="U95" s="149">
         <v>280.37</v>
       </c>
       <c r="V95" s="57"/>
@@ -28530,7 +28548,7 @@
         <v>327</v>
       </c>
       <c r="T96" s="57"/>
-      <c r="U96" s="150">
+      <c r="U96" s="149">
         <v>307.35000000000002</v>
       </c>
       <c r="V96" s="57"/>
@@ -28589,7 +28607,7 @@
         <v>329</v>
       </c>
       <c r="T97" s="57"/>
-      <c r="U97" s="149">
+      <c r="U97" s="148">
         <v>383.55</v>
       </c>
       <c r="V97" s="57"/>
@@ -28648,7 +28666,7 @@
         <v>331</v>
       </c>
       <c r="T98" s="57"/>
-      <c r="U98" s="149">
+      <c r="U98" s="148">
         <v>475.98</v>
       </c>
       <c r="V98" s="57"/>
@@ -28707,7 +28725,7 @@
         <v>355</v>
       </c>
       <c r="T99" s="57"/>
-      <c r="U99" s="149">
+      <c r="U99" s="148">
         <v>574.51</v>
       </c>
       <c r="V99" s="57"/>
@@ -28766,7 +28784,7 @@
         <v>334</v>
       </c>
       <c r="T100" s="57"/>
-      <c r="U100" s="149">
+      <c r="U100" s="148">
         <v>617.67999999999995</v>
       </c>
       <c r="V100" s="57"/>
@@ -28825,7 +28843,7 @@
         <v>336</v>
       </c>
       <c r="T101" s="57"/>
-      <c r="U101" s="149">
+      <c r="U101" s="148">
         <v>965.9</v>
       </c>
       <c r="V101" s="57"/>
@@ -28884,7 +28902,7 @@
         <v>338</v>
       </c>
       <c r="T102" s="57"/>
-      <c r="U102" s="149">
+      <c r="U102" s="148">
         <v>1031.17</v>
       </c>
       <c r="V102" s="57"/>
@@ -28943,7 +28961,7 @@
         <v>340</v>
       </c>
       <c r="T103" s="57"/>
-      <c r="U103" s="149">
+      <c r="U103" s="148">
         <v>1351.89</v>
       </c>
       <c r="V103" s="57"/>
@@ -29002,7 +29020,7 @@
         <v>342</v>
       </c>
       <c r="T104" s="57"/>
-      <c r="U104" s="149">
+      <c r="U104" s="148">
         <v>1685.96</v>
       </c>
       <c r="V104" s="57"/>
@@ -29434,7 +29452,7 @@
       <c r="R112" s="1">
         <v>400</v>
       </c>
-      <c r="S112" s="6" t="s">
+      <c r="S112" s="1" t="s">
         <v>349</v>
       </c>
       <c r="U112" s="80">
@@ -29491,7 +29509,7 @@
       <c r="R113" s="1">
         <v>400</v>
       </c>
-      <c r="S113" s="6" t="s">
+      <c r="S113" s="1" t="s">
         <v>351</v>
       </c>
       <c r="U113" s="80">
@@ -29548,7 +29566,7 @@
       <c r="R114" s="1">
         <v>550</v>
       </c>
-      <c r="S114" s="6" t="s">
+      <c r="S114" s="1" t="s">
         <v>353</v>
       </c>
       <c r="T114" t="e" vm="2">
@@ -29605,7 +29623,7 @@
       <c r="R115" s="1">
         <v>750</v>
       </c>
-      <c r="S115" s="6" t="s">
+      <c r="S115" s="1" t="s">
         <v>355</v>
       </c>
       <c r="U115" s="92"/>
@@ -29645,22 +29663,22 @@
       <c r="U116" s="111"/>
     </row>
     <row r="117" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A117" t="s">
+      <c r="A117" s="57" t="s">
         <v>356</v>
       </c>
-      <c r="B117" t="s">
+      <c r="B117" s="57" t="s">
         <v>319</v>
       </c>
       <c r="C117" s="1">
         <v>0</v>
       </c>
-      <c r="D117" s="6">
+      <c r="D117" s="1">
         <v>250</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F117" s="6">
+      <c r="F117" s="1">
         <v>80</v>
       </c>
       <c r="G117" s="1">
@@ -29684,34 +29702,35 @@
       <c r="N117" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O117" s="6">
+      <c r="O117" s="1">
         <v>20</v>
       </c>
       <c r="P117" s="1">
         <v>8</v>
       </c>
-      <c r="R117" s="6">
+      <c r="R117" s="1">
         <v>750</v>
       </c>
+      <c r="S117" s="1"/>
     </row>
     <row r="118" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A118" t="s">
+      <c r="A118" s="57" t="s">
         <v>358</v>
       </c>
-      <c r="B118" t="s">
+      <c r="B118" s="57" t="s">
         <v>319</v>
       </c>
       <c r="C118" s="1">
         <f>D117+0.01</f>
         <v>250.01</v>
       </c>
-      <c r="D118" s="6">
+      <c r="D118" s="1">
         <v>400</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F118" s="6">
+      <c r="F118" s="1">
         <v>40</v>
       </c>
       <c r="G118" s="1">
@@ -29735,16 +29754,16 @@
       <c r="N118" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O118" s="6">
+      <c r="O118" s="1">
         <v>20</v>
       </c>
       <c r="P118" s="1">
         <v>8</v>
       </c>
-      <c r="R118" s="6">
+      <c r="R118" s="1">
         <v>750</v>
       </c>
-      <c r="S118" s="6" t="s">
+      <c r="S118" s="1" t="s">
         <v>359</v>
       </c>
       <c r="U118" s="80">
@@ -29755,20 +29774,20 @@
       <c r="A119" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="B119" t="s">
+      <c r="B119" s="57" t="s">
         <v>319</v>
       </c>
       <c r="C119" s="1">
         <f>D118+0.01</f>
         <v>400.01</v>
       </c>
-      <c r="D119" s="6">
+      <c r="D119" s="1">
         <v>550</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F119" s="6">
+      <c r="F119" s="1">
         <v>20</v>
       </c>
       <c r="G119" s="1">
@@ -29792,34 +29811,35 @@
       <c r="N119" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O119" s="6">
+      <c r="O119" s="1">
         <v>20</v>
       </c>
       <c r="P119" s="1">
         <v>8</v>
       </c>
-      <c r="R119" s="6">
+      <c r="R119" s="1">
         <v>750</v>
       </c>
+      <c r="S119" s="1"/>
     </row>
     <row r="120" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="B120" t="s">
+      <c r="B120" s="57" t="s">
         <v>319</v>
       </c>
       <c r="C120" s="1">
         <f>D119+0.01</f>
         <v>550.01</v>
       </c>
-      <c r="D120" s="6">
+      <c r="D120" s="1">
         <v>750</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F120" s="6">
+      <c r="F120" s="1">
         <v>20</v>
       </c>
       <c r="G120" s="1">
@@ -29843,14 +29863,18 @@
       <c r="N120" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O120" s="6">
+      <c r="O120" s="1">
         <v>20</v>
       </c>
       <c r="P120" s="1">
         <v>8</v>
       </c>
-      <c r="R120" s="6">
+      <c r="R120" s="1">
         <v>750</v>
+      </c>
+      <c r="S120" s="1"/>
+      <c r="U120" s="148">
+        <v>2614.38</v>
       </c>
     </row>
     <row r="121" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -29888,22 +29912,22 @@
       <c r="U121" s="111"/>
     </row>
     <row r="122" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A122" t="s">
+      <c r="A122" s="57" t="s">
         <v>506</v>
       </c>
-      <c r="B122" t="s">
+      <c r="B122" s="57" t="s">
         <v>319</v>
       </c>
       <c r="C122" s="1">
         <v>0.01</v>
       </c>
-      <c r="D122" s="6">
+      <c r="D122" s="1">
         <v>250</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F122" s="6">
+      <c r="F122" s="1">
         <v>80</v>
       </c>
       <c r="G122" s="1">
@@ -29927,33 +29951,34 @@
       <c r="N122" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O122" s="6">
+      <c r="O122" s="1">
         <v>20</v>
       </c>
       <c r="P122" s="1">
         <v>26</v>
       </c>
-      <c r="R122" s="6">
+      <c r="R122" s="1">
         <v>1500</v>
       </c>
+      <c r="S122" s="1"/>
     </row>
     <row r="123" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A123" t="s">
+      <c r="A123" s="57" t="s">
         <v>501</v>
       </c>
-      <c r="B123" t="s">
+      <c r="B123" s="57" t="s">
         <v>319</v>
       </c>
       <c r="C123" s="1">
         <v>0.01</v>
       </c>
-      <c r="D123" s="6">
+      <c r="D123" s="1">
         <v>250</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F123" s="6">
+      <c r="F123" s="1">
         <v>80</v>
       </c>
       <c r="G123" s="1">
@@ -29977,34 +30002,35 @@
       <c r="N123" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O123" s="6">
+      <c r="O123" s="1">
         <v>20</v>
       </c>
       <c r="P123" s="1">
         <v>26</v>
       </c>
-      <c r="R123" s="6">
+      <c r="R123" s="1">
         <v>1500</v>
       </c>
+      <c r="S123" s="1"/>
     </row>
     <row r="124" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A124" t="s">
+      <c r="A124" s="57" t="s">
         <v>358</v>
       </c>
-      <c r="B124" t="s">
+      <c r="B124" s="57" t="s">
         <v>319</v>
       </c>
       <c r="C124" s="1">
         <f t="shared" ref="C124:C132" si="7">D123+0.01</f>
         <v>250.01</v>
       </c>
-      <c r="D124" s="6">
+      <c r="D124" s="1">
         <v>400</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F124" s="6">
+      <c r="F124" s="1">
         <v>40</v>
       </c>
       <c r="G124" s="1">
@@ -30028,34 +30054,35 @@
       <c r="N124" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O124" s="6">
+      <c r="O124" s="1">
         <v>20</v>
       </c>
       <c r="P124" s="1">
         <v>17</v>
       </c>
-      <c r="R124" s="6">
+      <c r="R124" s="1">
         <v>1500</v>
       </c>
+      <c r="S124" s="1"/>
     </row>
     <row r="125" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A125" t="s">
+      <c r="A125" s="57" t="s">
         <v>362</v>
       </c>
-      <c r="B125" t="s">
+      <c r="B125" s="57" t="s">
         <v>319</v>
       </c>
       <c r="C125" s="1">
         <f t="shared" si="7"/>
         <v>400.01</v>
       </c>
-      <c r="D125" s="6">
+      <c r="D125" s="1">
         <v>450</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F125" s="6">
+      <c r="F125" s="1">
         <v>60</v>
       </c>
       <c r="G125" s="1">
@@ -30079,34 +30106,35 @@
       <c r="N125" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O125" s="6">
+      <c r="O125" s="1">
         <v>20</v>
       </c>
       <c r="P125" s="1">
         <v>11</v>
       </c>
-      <c r="R125" s="6">
+      <c r="R125" s="1">
         <v>1500</v>
       </c>
+      <c r="S125" s="1"/>
     </row>
     <row r="126" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A126" t="s">
+      <c r="A126" s="57" t="s">
         <v>363</v>
       </c>
-      <c r="B126" t="s">
+      <c r="B126" s="57" t="s">
         <v>319</v>
       </c>
       <c r="C126" s="1">
         <f t="shared" si="7"/>
         <v>450.01</v>
       </c>
-      <c r="D126" s="6">
+      <c r="D126" s="1">
         <v>500</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F126" s="6">
+      <c r="F126" s="1">
         <v>80</v>
       </c>
       <c r="G126" s="1">
@@ -30130,34 +30158,35 @@
       <c r="N126" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O126" s="6">
+      <c r="O126" s="1">
         <v>20</v>
       </c>
       <c r="P126" s="1">
         <v>19</v>
       </c>
-      <c r="R126" s="6">
+      <c r="R126" s="1">
         <v>4500</v>
       </c>
+      <c r="S126" s="1"/>
     </row>
     <row r="127" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A127" s="3" t="s">
         <v>360</v>
       </c>
-      <c r="B127" t="s">
+      <c r="B127" s="57" t="s">
         <v>319</v>
       </c>
       <c r="C127" s="1">
         <f t="shared" si="7"/>
         <v>500.01</v>
       </c>
-      <c r="D127" s="6">
+      <c r="D127" s="1">
         <v>550</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F127" s="6">
+      <c r="F127" s="1">
         <v>20</v>
       </c>
       <c r="G127" s="1">
@@ -30181,34 +30210,38 @@
       <c r="N127" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O127" s="6">
+      <c r="O127" s="1">
         <v>20</v>
       </c>
       <c r="P127" s="1">
         <v>12</v>
       </c>
-      <c r="R127" s="6">
+      <c r="R127" s="1">
         <v>1500</v>
+      </c>
+      <c r="S127" s="1"/>
+      <c r="U127" s="149">
+        <v>2021.94</v>
       </c>
     </row>
     <row r="128" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A128" s="3" t="s">
         <v>364</v>
       </c>
-      <c r="B128" t="s">
+      <c r="B128" s="57" t="s">
         <v>319</v>
       </c>
       <c r="C128" s="1">
         <f t="shared" si="7"/>
         <v>550.01</v>
       </c>
-      <c r="D128" s="6">
+      <c r="D128" s="1">
         <v>550</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F128" s="6">
+      <c r="F128" s="1">
         <v>40</v>
       </c>
       <c r="G128" s="1">
@@ -30232,34 +30265,35 @@
       <c r="N128" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O128" s="6">
+      <c r="O128" s="1">
         <v>20</v>
       </c>
       <c r="P128" s="1">
         <v>12</v>
       </c>
-      <c r="R128" s="6">
+      <c r="R128" s="1">
         <v>4500</v>
       </c>
+      <c r="S128" s="1"/>
     </row>
     <row r="129" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="3" t="s">
         <v>361</v>
       </c>
-      <c r="B129" t="s">
+      <c r="B129" s="57" t="s">
         <v>319</v>
       </c>
       <c r="C129" s="1">
         <f t="shared" si="7"/>
         <v>550.01</v>
       </c>
-      <c r="D129" s="6">
+      <c r="D129" s="1">
         <v>750</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F129" s="6">
+      <c r="F129" s="1">
         <v>20</v>
       </c>
       <c r="G129" s="1">
@@ -30283,34 +30317,35 @@
       <c r="N129" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O129" s="6">
+      <c r="O129" s="1">
         <v>10</v>
       </c>
       <c r="P129" s="1">
         <v>17</v>
       </c>
-      <c r="R129" s="6">
+      <c r="R129" s="1">
         <v>1500</v>
       </c>
+      <c r="S129" s="1"/>
     </row>
     <row r="130" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="3" t="s">
         <v>365</v>
       </c>
-      <c r="B130" t="s">
+      <c r="B130" s="57" t="s">
         <v>319</v>
       </c>
       <c r="C130" s="1">
         <f t="shared" si="7"/>
         <v>750.01</v>
       </c>
-      <c r="D130" s="6">
+      <c r="D130" s="1">
         <v>750</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F130" s="6">
+      <c r="F130" s="1">
         <v>45</v>
       </c>
       <c r="G130" s="1">
@@ -30334,34 +30369,38 @@
       <c r="N130" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O130" s="6">
+      <c r="O130" s="1">
         <v>20</v>
       </c>
       <c r="P130" s="1">
         <v>12</v>
       </c>
-      <c r="R130" s="6">
+      <c r="R130" s="1">
         <v>4500</v>
+      </c>
+      <c r="S130" s="1"/>
+      <c r="U130" s="148">
+        <v>2676</v>
       </c>
     </row>
     <row r="131" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
         <v>366</v>
       </c>
-      <c r="B131" t="s">
+      <c r="B131" s="57" t="s">
         <v>319</v>
       </c>
       <c r="C131" s="1">
         <f t="shared" si="7"/>
         <v>750.01</v>
       </c>
-      <c r="D131" s="6">
+      <c r="D131" s="1">
         <v>1000</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F131" s="6">
+      <c r="F131" s="1">
         <v>30</v>
       </c>
       <c r="G131" s="1">
@@ -30385,34 +30424,35 @@
       <c r="N131" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O131" s="6">
+      <c r="O131" s="1">
         <v>20</v>
       </c>
       <c r="P131" s="1">
         <v>11</v>
       </c>
-      <c r="R131" s="6">
+      <c r="R131" s="1">
         <v>4500</v>
       </c>
+      <c r="S131" s="1"/>
     </row>
     <row r="132" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="3" t="s">
         <v>367</v>
       </c>
-      <c r="B132" t="s">
+      <c r="B132" s="57" t="s">
         <v>319</v>
       </c>
       <c r="C132" s="1">
         <f t="shared" si="7"/>
         <v>1000.01</v>
       </c>
-      <c r="D132" s="6">
+      <c r="D132" s="1">
         <v>1400</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>357</v>
       </c>
-      <c r="F132" s="6">
+      <c r="F132" s="1">
         <v>20</v>
       </c>
       <c r="G132" s="1">
@@ -30436,28 +30476,29 @@
       <c r="N132" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O132" s="6">
+      <c r="O132" s="1">
         <v>20</v>
       </c>
       <c r="P132" s="1">
         <v>10</v>
       </c>
-      <c r="R132" s="6">
+      <c r="R132" s="1">
         <v>4500</v>
       </c>
+      <c r="S132" s="1"/>
     </row>
     <row r="133" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="B133" t="s">
+      <c r="B133" s="57" t="s">
         <v>319</v>
       </c>
       <c r="C133" s="1">
         <f t="shared" ref="C133" si="8">D132+0.01</f>
         <v>1400.01</v>
       </c>
-      <c r="D133" s="6">
+      <c r="D133" s="1">
         <v>1800</v>
       </c>
       <c r="E133" s="1" t="s">
@@ -30487,28 +30528,29 @@
       <c r="N133" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O133" s="6">
+      <c r="O133" s="1">
         <v>10</v>
       </c>
       <c r="P133" s="1">
         <v>10</v>
       </c>
-      <c r="R133" s="6">
+      <c r="R133" s="1">
         <v>4500</v>
       </c>
+      <c r="S133" s="1"/>
     </row>
     <row r="134" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="B134" t="s">
+      <c r="B134" s="57" t="s">
         <v>319</v>
       </c>
       <c r="C134" s="1">
         <f t="shared" ref="C134" si="9">D133+0.01</f>
         <v>1800.01</v>
       </c>
-      <c r="D134" s="6">
+      <c r="D134" s="1">
         <v>2600</v>
       </c>
       <c r="E134" s="1" t="s">
@@ -30538,28 +30580,29 @@
       <c r="N134" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O134" s="6">
+      <c r="O134" s="1">
         <v>10</v>
       </c>
       <c r="P134" s="1">
         <v>11</v>
       </c>
-      <c r="R134" s="6">
+      <c r="R134" s="1">
         <v>4500</v>
       </c>
+      <c r="S134" s="1"/>
     </row>
     <row r="135" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="3" t="s">
         <v>510</v>
       </c>
-      <c r="B135" t="s">
+      <c r="B135" s="57" t="s">
         <v>319</v>
       </c>
       <c r="C135" s="1">
         <f t="shared" ref="C135" si="10">D134+0.01</f>
         <v>2600.0100000000002</v>
       </c>
-      <c r="D135" s="6">
+      <c r="D135" s="1">
         <v>3600</v>
       </c>
       <c r="E135" s="1" t="s">
@@ -30589,15 +30632,16 @@
       <c r="N135" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O135" s="6">
+      <c r="O135" s="1">
         <v>10</v>
       </c>
       <c r="P135" s="1">
         <v>11</v>
       </c>
-      <c r="R135" s="6">
+      <c r="R135" s="1">
         <v>4500</v>
       </c>
+      <c r="S135" s="1"/>
     </row>
     <row r="136" spans="1:21" s="109" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="106" t="s">

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4157" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5DCDF4D2-3E6A-4347-BE61-3BDC158C1055}"/>
+  <xr:revisionPtr revIDLastSave="4170" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{64FAE49A-5EE5-4142-AADF-F77FBAE1C26E}"/>
   <bookViews>
-    <workbookView xWindow="4620" yWindow="180" windowWidth="26210" windowHeight="19510" tabRatio="905" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2890" yWindow="550" windowWidth="29440" windowHeight="19510" tabRatio="905" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lath" sheetId="7" r:id="rId1"/>
@@ -442,7 +442,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-Check what grame material is being bought in and match for axle calculation.
+Check what grade material is being bought in and match for axle calculation.
 Young's Modulus (MPa)</t>
         </r>
       </text>
@@ -852,7 +852,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2921" uniqueCount="693">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2930" uniqueCount="697">
   <si>
     <t>Name</t>
   </si>
@@ -3267,6 +3267,18 @@
   </si>
   <si>
     <t>168.3 x 5</t>
+  </si>
+  <si>
+    <t>Grade</t>
+  </si>
+  <si>
+    <t>S235JR EN10219</t>
+  </si>
+  <si>
+    <t>S355J2H EN10210</t>
+  </si>
+  <si>
+    <t>ERW</t>
   </si>
 </sst>
 </file>
@@ -3426,7 +3438,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -3523,8 +3535,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="7">
     <border>
       <left/>
       <right/>
@@ -3558,6 +3576,60 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -3566,7 +3638,7 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="163">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3997,12 +4069,18 @@
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="6" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="20% - Accent1 2" xfId="1" xr:uid="{4B6C72F7-C4CA-450E-9C13-94CEF72F8B8D}"/>
@@ -17063,16 +17141,16 @@
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B45" s="157"/>
-      <c r="C45" s="157"/>
-      <c r="D45" s="157"/>
-      <c r="E45" s="157"/>
-      <c r="F45" s="157"/>
-      <c r="G45" s="157"/>
-      <c r="H45" s="157"/>
-      <c r="I45" s="157"/>
-      <c r="J45" s="157"/>
-      <c r="K45" s="157"/>
+      <c r="B45" s="158"/>
+      <c r="C45" s="158"/>
+      <c r="D45" s="158"/>
+      <c r="E45" s="158"/>
+      <c r="F45" s="158"/>
+      <c r="G45" s="158"/>
+      <c r="H45" s="158"/>
+      <c r="I45" s="158"/>
+      <c r="J45" s="158"/>
+      <c r="K45" s="158"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -17100,14 +17178,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="157" t="s">
+      <c r="A2" s="158" t="s">
         <v>527</v>
       </c>
-      <c r="B2" s="157"/>
-      <c r="C2" s="157"/>
-      <c r="D2" s="157"/>
-      <c r="E2" s="157"/>
-      <c r="F2" s="157"/>
+      <c r="B2" s="158"/>
+      <c r="C2" s="158"/>
+      <c r="D2" s="158"/>
+      <c r="E2" s="158"/>
+      <c r="F2" s="158"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -20587,7 +20665,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04DB295D-7881-4D5C-8380-F1C84A7F5934}">
-  <dimension ref="A1:O13"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="11.453125" customWidth="1"/>
@@ -20601,9 +20679,10 @@
     <col min="13" max="13" width="11.6328125" style="1" customWidth="1"/>
     <col min="14" max="14" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="10.90625" customWidth="1"/>
+    <col min="16" max="16" width="15.453125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
@@ -20649,8 +20728,11 @@
       <c r="O1" s="44" t="s">
         <v>680</v>
       </c>
-    </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P1" s="159" t="s">
+        <v>693</v>
+      </c>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="14" t="s">
         <v>207</v>
       </c>
@@ -20671,7 +20753,7 @@
         <v>57.6</v>
       </c>
       <c r="G2" s="14">
-        <v>190000</v>
+        <v>210000</v>
       </c>
       <c r="H2" s="14">
         <v>7850</v>
@@ -20686,7 +20768,7 @@
       </c>
       <c r="N2" s="6"/>
     </row>
-    <row r="3" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="14" t="s">
         <v>210</v>
       </c>
@@ -20707,7 +20789,7 @@
         <v>67.599999999999994</v>
       </c>
       <c r="G3" s="14">
-        <v>190000</v>
+        <v>210000</v>
       </c>
       <c r="H3" s="14">
         <v>7850</v>
@@ -20722,7 +20804,7 @@
       </c>
       <c r="N3" s="6"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="14" t="s">
         <v>212</v>
       </c>
@@ -20743,7 +20825,7 @@
         <v>67</v>
       </c>
       <c r="G4" s="14">
-        <v>190000</v>
+        <v>210000</v>
       </c>
       <c r="H4" s="14">
         <v>7850</v>
@@ -20758,7 +20840,7 @@
       </c>
       <c r="N4" s="6"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
         <v>691</v>
       </c>
@@ -20779,7 +20861,7 @@
         <v>98.6</v>
       </c>
       <c r="G5" s="14">
-        <v>190000</v>
+        <v>210000</v>
       </c>
       <c r="H5" s="14">
         <v>7850</v>
@@ -20801,8 +20883,11 @@
       <c r="N5" s="6">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P5" s="162" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="15" t="s">
         <v>642</v>
       </c>
@@ -20823,7 +20908,7 @@
         <v>95.6</v>
       </c>
       <c r="G6" s="14">
-        <v>190000</v>
+        <v>210000</v>
       </c>
       <c r="H6" s="14">
         <v>7850</v>
@@ -20845,8 +20930,11 @@
       <c r="N6" s="6">
         <v>8</v>
       </c>
-    </row>
-    <row r="7" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P6" s="162" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
         <v>690</v>
       </c>
@@ -20889,8 +20977,11 @@
       <c r="N7" s="6">
         <v>8</v>
       </c>
-    </row>
-    <row r="8" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P7" s="160" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
         <v>686</v>
       </c>
@@ -20933,8 +21024,11 @@
       <c r="N8" s="6">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P8" s="160" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
         <v>692</v>
       </c>
@@ -20955,7 +21049,7 @@
         <v>158.30000000000001</v>
       </c>
       <c r="G9" s="14">
-        <v>190000</v>
+        <v>210000</v>
       </c>
       <c r="H9" s="14">
         <v>7850</v>
@@ -20977,8 +21071,11 @@
       <c r="N9" s="6">
         <v>7.5</v>
       </c>
-    </row>
-    <row r="10" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P9" s="161" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="101" t="s">
         <v>687</v>
       </c>
@@ -20999,7 +21096,7 @@
         <v>181.1</v>
       </c>
       <c r="G10" s="100">
-        <v>190000</v>
+        <v>210000</v>
       </c>
       <c r="H10" s="100">
         <v>7850</v>
@@ -21021,8 +21118,11 @@
       <c r="N10" s="6" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="11" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P10" s="161" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="100" t="s">
         <v>688</v>
       </c>
@@ -21032,10 +21132,10 @@
       <c r="C11" s="101" t="s">
         <v>227</v>
       </c>
-      <c r="D11" s="158">
+      <c r="D11" s="157">
         <v>219.1</v>
       </c>
-      <c r="E11" s="158">
+      <c r="E11" s="157">
         <v>6.3</v>
       </c>
       <c r="F11" s="100">
@@ -21043,7 +21143,7 @@
         <v>206.5</v>
       </c>
       <c r="G11" s="100">
-        <v>190000</v>
+        <v>210000</v>
       </c>
       <c r="H11" s="100">
         <v>7850</v>
@@ -21065,8 +21165,11 @@
       <c r="N11" s="6" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="12" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P11" s="161" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="100" t="s">
         <v>689</v>
       </c>
@@ -21076,10 +21179,10 @@
       <c r="C12" s="100" t="s">
         <v>229</v>
       </c>
-      <c r="D12" s="158">
+      <c r="D12" s="157">
         <v>273</v>
       </c>
-      <c r="E12" s="158">
+      <c r="E12" s="157">
         <v>6.3</v>
       </c>
       <c r="F12" s="100">
@@ -21087,7 +21190,7 @@
         <v>260.39999999999998</v>
       </c>
       <c r="G12" s="100">
-        <v>199000</v>
+        <v>210000</v>
       </c>
       <c r="H12" s="100">
         <v>7850</v>
@@ -21107,8 +21210,11 @@
       <c r="N12" s="6" t="s">
         <v>636</v>
       </c>
-    </row>
-    <row r="13" spans="1:15" x14ac:dyDescent="0.35">
+      <c r="P12" s="161" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A13" s="98" t="s">
         <v>494</v>
       </c>
@@ -21129,7 +21235,7 @@
         <v>257</v>
       </c>
       <c r="G13" s="98">
-        <v>199000</v>
+        <v>210000</v>
       </c>
       <c r="H13" s="98">
         <v>7850</v>
@@ -33664,19 +33770,19 @@
       <c r="X56" s="80"/>
     </row>
     <row r="61" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="H61" s="157" t="s">
+      <c r="H61" s="158" t="s">
         <v>536</v>
       </c>
-      <c r="I61" s="157"/>
-      <c r="J61" s="157"/>
-      <c r="K61" s="157"/>
-      <c r="L61" s="157"/>
-      <c r="M61" s="157"/>
-      <c r="N61" s="157"/>
-      <c r="O61" s="157"/>
-      <c r="P61" s="157"/>
-      <c r="Q61" s="157"/>
-      <c r="R61" s="157"/>
+      <c r="I61" s="158"/>
+      <c r="J61" s="158"/>
+      <c r="K61" s="158"/>
+      <c r="L61" s="158"/>
+      <c r="M61" s="158"/>
+      <c r="N61" s="158"/>
+      <c r="O61" s="158"/>
+      <c r="P61" s="158"/>
+      <c r="Q61" s="158"/>
+      <c r="R61" s="158"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4253" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D58633F9-C631-4672-AB15-DCF5FD194335}"/>
+  <xr:revisionPtr revIDLastSave="4318" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D413FEA-A95F-43E3-8DB7-2FAA58F3B84B}"/>
   <bookViews>
-    <workbookView xWindow="900" yWindow="880" windowWidth="25640" windowHeight="20590" tabRatio="905" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3040" yWindow="1010" windowWidth="31280" windowHeight="20590" tabRatio="905" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lath" sheetId="7" r:id="rId1"/>
@@ -32,7 +32,7 @@
     <sheet name="Online codes" sheetId="17" r:id="rId17"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7">Motors!$A$1:$S$148</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7">Motors!$A$1:$S$146</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -852,7 +852,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2960" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2944" uniqueCount="706">
   <si>
     <t>Name</t>
   </si>
@@ -3665,7 +3665,7 @@
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="166">
+  <cellXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4111,10 +4111,14 @@
     <xf numFmtId="0" fontId="2" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -6794,13 +6798,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>123</xdr:row>
+      <xdr:row>121</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>643922</xdr:colOff>
-      <xdr:row>123</xdr:row>
+      <xdr:row>121</xdr:row>
       <xdr:rowOff>453413</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7323,13 +7327,13 @@
       <xdr:col>19</xdr:col>
       <xdr:colOff>81643</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>36285</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>650633</xdr:colOff>
       <xdr:row>63</xdr:row>
-      <xdr:rowOff>460487</xdr:rowOff>
+      <xdr:rowOff>424202</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7366,14 +7370,14 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>99786</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>45357</xdr:rowOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>684016</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>492419</xdr:rowOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>447062</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7410,13 +7414,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>72572</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>45358</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>650452</xdr:colOff>
-      <xdr:row>67</xdr:row>
+      <xdr:row>65</xdr:row>
       <xdr:rowOff>492420</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7454,13 +7458,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>88348</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>682738</xdr:colOff>
-      <xdr:row>68</xdr:row>
+      <xdr:row>66</xdr:row>
       <xdr:rowOff>421662</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7498,13 +7502,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>66260</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>650490</xdr:colOff>
-      <xdr:row>71</xdr:row>
+      <xdr:row>69</xdr:row>
       <xdr:rowOff>421662</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7542,13 +7546,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>77807</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>39155</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>650607</xdr:colOff>
-      <xdr:row>70</xdr:row>
+      <xdr:row>68</xdr:row>
       <xdr:rowOff>460817</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7586,13 +7590,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>81</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>643923</xdr:colOff>
-      <xdr:row>81</xdr:row>
+      <xdr:row>79</xdr:row>
       <xdr:rowOff>453413</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7630,13 +7634,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>643923</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>453413</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7674,13 +7678,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>643923</xdr:colOff>
-      <xdr:row>82</xdr:row>
+      <xdr:row>80</xdr:row>
       <xdr:rowOff>453413</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7718,13 +7722,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>643923</xdr:colOff>
-      <xdr:row>83</xdr:row>
+      <xdr:row>81</xdr:row>
       <xdr:rowOff>453413</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7762,13 +7766,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>643923</xdr:colOff>
-      <xdr:row>84</xdr:row>
+      <xdr:row>82</xdr:row>
       <xdr:rowOff>453413</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7806,13 +7810,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>612172</xdr:colOff>
-      <xdr:row>95</xdr:row>
+      <xdr:row>93</xdr:row>
       <xdr:rowOff>457223</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7850,13 +7854,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>643922</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>453413</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7894,13 +7898,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>682025</xdr:colOff>
-      <xdr:row>96</xdr:row>
+      <xdr:row>94</xdr:row>
       <xdr:rowOff>459764</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7938,13 +7942,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>688376</xdr:colOff>
-      <xdr:row>97</xdr:row>
+      <xdr:row>95</xdr:row>
       <xdr:rowOff>383560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -7982,13 +7986,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>98</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>720126</xdr:colOff>
-      <xdr:row>98</xdr:row>
+      <xdr:row>96</xdr:row>
       <xdr:rowOff>381020</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8026,13 +8030,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>99</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>720126</xdr:colOff>
-      <xdr:row>99</xdr:row>
+      <xdr:row>97</xdr:row>
       <xdr:rowOff>383560</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8070,13 +8074,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>100</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>723937</xdr:colOff>
-      <xdr:row>100</xdr:row>
+      <xdr:row>98</xdr:row>
       <xdr:rowOff>459764</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8114,13 +8118,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>101</xdr:row>
+      <xdr:row>99</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>720127</xdr:colOff>
-      <xdr:row>101</xdr:row>
+      <xdr:row>99</xdr:row>
       <xdr:rowOff>459764</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8158,13 +8162,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>102</xdr:row>
+      <xdr:row>100</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>720127</xdr:colOff>
-      <xdr:row>102</xdr:row>
+      <xdr:row>100</xdr:row>
       <xdr:rowOff>453413</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8202,13 +8206,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>103</xdr:row>
+      <xdr:row>101</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>720127</xdr:colOff>
-      <xdr:row>103</xdr:row>
+      <xdr:row>101</xdr:row>
       <xdr:rowOff>453413</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8246,13 +8250,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>104</xdr:row>
+      <xdr:row>102</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>720127</xdr:colOff>
-      <xdr:row>104</xdr:row>
+      <xdr:row>102</xdr:row>
       <xdr:rowOff>453413</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8290,13 +8294,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>42334</xdr:colOff>
-      <xdr:row>104</xdr:row>
+      <xdr:row>102</xdr:row>
       <xdr:rowOff>497416</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>758651</xdr:colOff>
-      <xdr:row>105</xdr:row>
+      <xdr:row>103</xdr:row>
       <xdr:rowOff>422509</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8334,13 +8338,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>107</xdr:row>
+      <xdr:row>105</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>650274</xdr:colOff>
-      <xdr:row>108</xdr:row>
+      <xdr:row>106</xdr:row>
       <xdr:rowOff>2567</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8378,13 +8382,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>108</xdr:row>
+      <xdr:row>106</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>682024</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>107</xdr:row>
       <xdr:rowOff>34317</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8422,13 +8426,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>109</xdr:row>
+      <xdr:row>107</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>682024</xdr:colOff>
-      <xdr:row>110</xdr:row>
+      <xdr:row>108</xdr:row>
       <xdr:rowOff>34317</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8466,13 +8470,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>110</xdr:row>
+      <xdr:row>108</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>682024</xdr:colOff>
-      <xdr:row>111</xdr:row>
+      <xdr:row>109</xdr:row>
       <xdr:rowOff>34317</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8510,13 +8514,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>111</xdr:row>
+      <xdr:row>109</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>682024</xdr:colOff>
-      <xdr:row>112</xdr:row>
+      <xdr:row>110</xdr:row>
       <xdr:rowOff>34317</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8554,13 +8558,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>113</xdr:row>
+      <xdr:row>111</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>421662</xdr:colOff>
-      <xdr:row>113</xdr:row>
+      <xdr:row>111</xdr:row>
       <xdr:rowOff>459764</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8598,13 +8602,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>114</xdr:row>
+      <xdr:row>112</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>421662</xdr:colOff>
-      <xdr:row>114</xdr:row>
+      <xdr:row>112</xdr:row>
       <xdr:rowOff>457223</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8642,13 +8646,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>116</xdr:row>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>54428</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>647733</xdr:colOff>
-      <xdr:row>116</xdr:row>
+      <xdr:row>114</xdr:row>
       <xdr:rowOff>416396</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8686,13 +8690,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>138</xdr:row>
+      <xdr:row>136</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>685835</xdr:colOff>
-      <xdr:row>138</xdr:row>
+      <xdr:row>136</xdr:row>
       <xdr:rowOff>491514</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8730,13 +8734,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>139</xdr:row>
+      <xdr:row>137</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>682025</xdr:colOff>
-      <xdr:row>139</xdr:row>
+      <xdr:row>137</xdr:row>
       <xdr:rowOff>491515</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8774,13 +8778,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>140</xdr:row>
+      <xdr:row>138</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>650274</xdr:colOff>
-      <xdr:row>140</xdr:row>
+      <xdr:row>138</xdr:row>
       <xdr:rowOff>459764</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8818,13 +8822,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>141</xdr:row>
+      <xdr:row>139</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>682025</xdr:colOff>
-      <xdr:row>141</xdr:row>
+      <xdr:row>139</xdr:row>
       <xdr:rowOff>491514</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8862,13 +8866,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>140</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>647733</xdr:colOff>
-      <xdr:row>142</xdr:row>
+      <xdr:row>140</xdr:row>
       <xdr:rowOff>457223</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8906,13 +8910,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>143</xdr:row>
+      <xdr:row>141</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>647733</xdr:colOff>
-      <xdr:row>143</xdr:row>
+      <xdr:row>141</xdr:row>
       <xdr:rowOff>457223</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8950,13 +8954,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>142</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>647733</xdr:colOff>
-      <xdr:row>144</xdr:row>
+      <xdr:row>142</xdr:row>
       <xdr:rowOff>457223</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -8994,13 +8998,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>145</xdr:row>
+      <xdr:row>143</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>723937</xdr:colOff>
-      <xdr:row>145</xdr:row>
+      <xdr:row>143</xdr:row>
       <xdr:rowOff>491515</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10138,13 +10142,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>136071</xdr:colOff>
-      <xdr:row>124</xdr:row>
+      <xdr:row>122</xdr:row>
       <xdr:rowOff>27216</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>650772</xdr:colOff>
-      <xdr:row>124</xdr:row>
+      <xdr:row>122</xdr:row>
       <xdr:rowOff>495054</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10182,13 +10186,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>125</xdr:row>
+      <xdr:row>123</xdr:row>
       <xdr:rowOff>36285</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>650591</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>124</xdr:row>
       <xdr:rowOff>2588</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10226,13 +10230,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>102333</xdr:colOff>
-      <xdr:row>127</xdr:row>
+      <xdr:row>125</xdr:row>
       <xdr:rowOff>81643</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>689606</xdr:colOff>
-      <xdr:row>127</xdr:row>
+      <xdr:row>125</xdr:row>
       <xdr:rowOff>460675</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10270,13 +10274,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>152400</xdr:colOff>
-      <xdr:row>126</xdr:row>
+      <xdr:row>124</xdr:row>
       <xdr:rowOff>34470</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>682341</xdr:colOff>
-      <xdr:row>127</xdr:row>
+      <xdr:row>125</xdr:row>
       <xdr:rowOff>3314</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10314,13 +10318,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>108857</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>126</xdr:row>
       <xdr:rowOff>45358</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>688510</xdr:colOff>
-      <xdr:row>128</xdr:row>
+      <xdr:row>126</xdr:row>
       <xdr:rowOff>453600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10358,13 +10362,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:row>127</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>720623</xdr:colOff>
-      <xdr:row>129</xdr:row>
+      <xdr:row>127</xdr:row>
       <xdr:rowOff>457772</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10402,13 +10406,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>154214</xdr:colOff>
-      <xdr:row>130</xdr:row>
+      <xdr:row>128</xdr:row>
       <xdr:rowOff>54428</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>759267</xdr:colOff>
-      <xdr:row>130</xdr:row>
+      <xdr:row>128</xdr:row>
       <xdr:rowOff>453780</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10446,13 +10450,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>131</xdr:row>
+      <xdr:row>129</xdr:row>
       <xdr:rowOff>45357</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>720623</xdr:colOff>
-      <xdr:row>131</xdr:row>
+      <xdr:row>129</xdr:row>
       <xdr:rowOff>453599</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10490,13 +10494,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>172358</xdr:colOff>
-      <xdr:row>132</xdr:row>
+      <xdr:row>130</xdr:row>
       <xdr:rowOff>63501</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>688629</xdr:colOff>
-      <xdr:row>132</xdr:row>
+      <xdr:row>130</xdr:row>
       <xdr:rowOff>384165</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10534,13 +10538,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>86082</xdr:colOff>
-      <xdr:row>134</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>54429</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>722315</xdr:colOff>
-      <xdr:row>134</xdr:row>
+      <xdr:row>132</xdr:row>
       <xdr:rowOff>422729</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10578,13 +10582,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>125186</xdr:colOff>
-      <xdr:row>133</xdr:row>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>79829</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>646537</xdr:colOff>
-      <xdr:row>133</xdr:row>
+      <xdr:row>131</xdr:row>
       <xdr:rowOff>415733</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10622,13 +10626,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>151269</xdr:colOff>
-      <xdr:row>135</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>45357</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>759360</xdr:colOff>
-      <xdr:row>135</xdr:row>
+      <xdr:row>133</xdr:row>
       <xdr:rowOff>492216</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10666,7 +10670,7 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>151269</xdr:colOff>
-      <xdr:row>136</xdr:row>
+      <xdr:row>134</xdr:row>
       <xdr:rowOff>45357</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="606821" cy="435429"/>
@@ -10705,13 +10709,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>198559</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>720389</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>417286</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10793,13 +10797,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>179917</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>52916</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>687777</xdr:colOff>
-      <xdr:row>74</xdr:row>
+      <xdr:row>72</xdr:row>
       <xdr:rowOff>460042</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10837,13 +10841,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>21166</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>645020</xdr:colOff>
-      <xdr:row>77</xdr:row>
+      <xdr:row>75</xdr:row>
       <xdr:rowOff>453692</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10881,13 +10885,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>137583</xdr:colOff>
-      <xdr:row>79</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>63500</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>645443</xdr:colOff>
-      <xdr:row>79</xdr:row>
+      <xdr:row>77</xdr:row>
       <xdr:rowOff>492216</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10925,13 +10929,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>74084</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>10583</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>682414</xdr:colOff>
-      <xdr:row>87</xdr:row>
+      <xdr:row>85</xdr:row>
       <xdr:rowOff>493956</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -10969,13 +10973,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>137584</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>10583</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>726864</xdr:colOff>
-      <xdr:row>88</xdr:row>
+      <xdr:row>86</xdr:row>
       <xdr:rowOff>493956</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -11013,13 +11017,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>89</xdr:row>
+      <xdr:row>87</xdr:row>
       <xdr:rowOff>31750</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>726440</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>3313</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -11101,13 +11105,13 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>38652</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>11044</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>644473</xdr:colOff>
-      <xdr:row>72</xdr:row>
+      <xdr:row>70</xdr:row>
       <xdr:rowOff>492398</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -11184,7 +11188,7 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>112443</xdr:colOff>
-      <xdr:row>69</xdr:row>
+      <xdr:row>67</xdr:row>
       <xdr:rowOff>21584</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="584230" cy="431822"/>
@@ -11223,7 +11227,7 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>198559</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="507860" cy="417286"/>
@@ -11262,7 +11266,7 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>179917</xdr:colOff>
-      <xdr:row>75</xdr:row>
+      <xdr:row>73</xdr:row>
       <xdr:rowOff>52916</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="507860" cy="417286"/>
@@ -11301,7 +11305,7 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>78</xdr:row>
+      <xdr:row>76</xdr:row>
       <xdr:rowOff>21166</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="507860" cy="417286"/>
@@ -11340,7 +11344,7 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>76</xdr:row>
+      <xdr:row>74</xdr:row>
       <xdr:rowOff>21166</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="507860" cy="417286"/>
@@ -11379,7 +11383,7 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>85</xdr:row>
+      <xdr:row>83</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="641383" cy="444523"/>
@@ -11418,7 +11422,7 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>74084</xdr:colOff>
-      <xdr:row>90</xdr:row>
+      <xdr:row>88</xdr:row>
       <xdr:rowOff>10583</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="603250" cy="483373"/>
@@ -11457,7 +11461,7 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>137584</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>89</xdr:row>
       <xdr:rowOff>10583</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="603250" cy="483373"/>
@@ -11496,7 +11500,7 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>92</xdr:row>
+      <xdr:row>90</xdr:row>
       <xdr:rowOff>31750</xdr:rowOff>
     </xdr:from>
     <xdr:ext cx="603250" cy="483373"/>
@@ -11579,14 +11583,14 @@
     <xdr:from>
       <xdr:col>19</xdr:col>
       <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>64</xdr:row>
-      <xdr:rowOff>496454</xdr:rowOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>19</xdr:col>
       <xdr:colOff>711230</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>435516</xdr:rowOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>447062</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -17260,16 +17264,16 @@
       </c>
     </row>
     <row r="45" spans="2:11" x14ac:dyDescent="0.35">
-      <c r="B45" s="164"/>
-      <c r="C45" s="164"/>
-      <c r="D45" s="164"/>
-      <c r="E45" s="164"/>
-      <c r="F45" s="164"/>
-      <c r="G45" s="164"/>
-      <c r="H45" s="164"/>
-      <c r="I45" s="164"/>
-      <c r="J45" s="164"/>
-      <c r="K45" s="164"/>
+      <c r="B45" s="165"/>
+      <c r="C45" s="165"/>
+      <c r="D45" s="165"/>
+      <c r="E45" s="165"/>
+      <c r="F45" s="165"/>
+      <c r="G45" s="165"/>
+      <c r="H45" s="165"/>
+      <c r="I45" s="165"/>
+      <c r="J45" s="165"/>
+      <c r="K45" s="165"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -17297,14 +17301,14 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="164" t="s">
+      <c r="A2" s="165" t="s">
         <v>522</v>
       </c>
-      <c r="B2" s="164"/>
-      <c r="C2" s="164"/>
-      <c r="D2" s="164"/>
-      <c r="E2" s="164"/>
-      <c r="F2" s="164"/>
+      <c r="B2" s="165"/>
+      <c r="C2" s="165"/>
+      <c r="D2" s="165"/>
+      <c r="E2" s="165"/>
+      <c r="F2" s="165"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
@@ -24020,7 +24024,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5FB77DDB-B6D9-4CBA-9145-50EF6FDCE517}">
-  <dimension ref="A1:AA159"/>
+  <dimension ref="A1:AA157"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="28.1796875" style="3" customWidth="1"/>
@@ -26710,7 +26714,7 @@
       <c r="E56" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F56" s="1">
+      <c r="F56" s="22">
         <f>Chaindrive!L46</f>
         <v>3.4375</v>
       </c>
@@ -26791,7 +26795,7 @@
       <c r="E58" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F58" s="1">
+      <c r="F58" s="22">
         <f>Chaindrive!L48</f>
         <v>3.4375000000000004</v>
       </c>
@@ -26835,7 +26839,7 @@
       <c r="E59" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F59" s="1">
+      <c r="F59" s="22">
         <f>Chaindrive!L49</f>
         <v>3.208333333333333</v>
       </c>
@@ -26900,8 +26904,9 @@
       <c r="E61" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F61" s="1">
-        <v>10.7</v>
+      <c r="F61" s="22">
+        <f>Chaindrive!L4</f>
+        <v>10.666666666666666</v>
       </c>
       <c r="G61" s="1">
         <v>230</v>
@@ -26924,7 +26929,7 @@
       <c r="N61" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O61" s="6">
+      <c r="O61" s="74">
         <f>Chaindrive!O4</f>
         <v>13.333333333333334</v>
       </c>
@@ -26959,8 +26964,9 @@
       <c r="E62" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F62" s="1">
-        <v>10.7</v>
+      <c r="F62" s="22">
+        <f>Chaindrive!L5</f>
+        <v>8.4210526315789469</v>
       </c>
       <c r="G62" s="1">
         <v>230</v>
@@ -26983,7 +26989,7 @@
       <c r="N62" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O62" s="6">
+      <c r="O62" s="74">
         <f>Chaindrive!O5</f>
         <v>10.526315789473685</v>
       </c>
@@ -27019,8 +27025,9 @@
       <c r="E63" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F63" s="1">
-        <v>10.7</v>
+      <c r="F63" s="22">
+        <f>Chaindrive!L6</f>
+        <v>6.7368421052631575</v>
       </c>
       <c r="G63" s="1">
         <v>230</v>
@@ -27043,7 +27050,7 @@
       <c r="N63" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O63" s="6">
+      <c r="O63" s="74">
         <f>Chaindrive!O6</f>
         <v>8.4210526315789469</v>
       </c>
@@ -27062,25 +27069,26 @@
     </row>
     <row r="64" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="str">
-        <f>Chaindrive!A8</f>
-        <v>Ranger 90 1ph 19-57 1/2"</v>
+        <f>Chaindrive!A10</f>
+        <v>Ranger 90 1ph 12-57 1/2"</v>
       </c>
       <c r="B64" t="s">
         <v>314</v>
       </c>
       <c r="C64" s="2">
-        <v>0</v>
+        <f>D63+0.01</f>
+        <v>332.51</v>
       </c>
       <c r="D64" s="23">
-        <f>Chaindrive!J8</f>
-        <v>270</v>
+        <f>Chaindrive!J10</f>
+        <v>427.5</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F64" s="1">
-        <f>24/3</f>
-        <v>8</v>
+      <c r="F64" s="22">
+        <f>Chaindrive!L10</f>
+        <v>5.0526315789473681</v>
       </c>
       <c r="G64" s="1">
         <v>230</v>
@@ -27103,9 +27111,9 @@
       <c r="N64" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O64" s="6">
-        <f>Chaindrive!O8</f>
-        <v>13.333333333333334</v>
+      <c r="O64" s="74">
+        <f>Chaindrive!O10</f>
+        <v>8.4210526315789469</v>
       </c>
       <c r="P64" s="1">
         <v>12</v>
@@ -27113,95 +27121,71 @@
       <c r="R64" s="6">
         <v>450</v>
       </c>
-      <c r="S64" s="165" t="s">
+      <c r="S64" s="164" t="s">
         <v>705</v>
       </c>
-      <c r="U64" s="150"/>
-    </row>
-    <row r="65" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A65" s="3" t="str">
-        <f>Chaindrive!A9</f>
-        <v>Ranger 90 1ph 15-57 1/2"</v>
-      </c>
-      <c r="B65" t="s">
-        <v>314</v>
-      </c>
-      <c r="C65" s="2">
-        <f>D64+0.01</f>
-        <v>270.01</v>
-      </c>
-      <c r="D65" s="23">
-        <f>Chaindrive!J9</f>
-        <v>342</v>
-      </c>
-      <c r="E65" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F65" s="22">
-        <f>Chaindrive!L9</f>
-        <v>6.3157894736842106</v>
-      </c>
-      <c r="G65" s="1">
-        <v>230</v>
-      </c>
-      <c r="H65" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I65" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K65" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="L65" s="1">
-        <v>25.4</v>
-      </c>
-      <c r="M65" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N65" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O65" s="6">
-        <f>Chaindrive!O9</f>
-        <v>10.526315789473685</v>
-      </c>
-      <c r="P65" s="1">
-        <v>12</v>
-      </c>
-      <c r="R65" s="6">
-        <v>450</v>
-      </c>
-      <c r="S65" s="165" t="s">
-        <v>705</v>
-      </c>
-      <c r="U65" s="150"/>
+      <c r="U64" s="166">
+        <v>345.34</v>
+      </c>
+    </row>
+    <row r="65" spans="1:23" s="107" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A65" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="B65" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="C65" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="D65" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="E65" s="105"/>
+      <c r="F65" s="105"/>
+      <c r="G65" s="105"/>
+      <c r="H65" s="106" t="s">
+        <v>467</v>
+      </c>
+      <c r="I65" s="105"/>
+      <c r="J65" s="105"/>
+      <c r="K65" s="105"/>
+      <c r="L65" s="105"/>
+      <c r="M65" s="105"/>
+      <c r="N65" s="106" t="s">
+        <v>467</v>
+      </c>
+      <c r="O65" s="108"/>
+      <c r="P65" s="105"/>
+      <c r="Q65" s="105"/>
+      <c r="R65" s="108"/>
+      <c r="S65" s="108"/>
+      <c r="U65" s="149"/>
     </row>
     <row r="66" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="str">
-        <f>Chaindrive!A10</f>
-        <v>Ranger 90 1ph 12-57 1/2"</v>
+        <f>Chaindrive!A12</f>
+        <v>Ranger 90 3ph 19-57 1/2"</v>
       </c>
       <c r="B66" t="s">
         <v>314</v>
       </c>
       <c r="C66" s="2">
-        <f>D65+0.01</f>
-        <v>342.01</v>
+        <v>0</v>
       </c>
       <c r="D66" s="23">
-        <f>Chaindrive!J10</f>
-        <v>427.5</v>
+        <f>Chaindrive!J12</f>
+        <v>270</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F66" s="22">
-        <f>Chaindrive!L10</f>
-        <v>5.0526315789473681</v>
+        <f>Chaindrive!L12</f>
+        <v>10.666666666666666</v>
       </c>
       <c r="G66" s="1">
-        <v>230</v>
+        <v>415</v>
       </c>
       <c r="H66" s="1" t="s">
         <v>308</v>
@@ -27221,76 +27205,108 @@
       <c r="N66" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O66" s="6">
-        <f>Chaindrive!O10</f>
+      <c r="O66" s="74">
+        <f>Chaindrive!O12</f>
+        <v>13.333333333333334</v>
+      </c>
+      <c r="P66" s="1">
+        <v>11</v>
+      </c>
+      <c r="R66" s="6">
+        <v>400</v>
+      </c>
+      <c r="S66" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="U66" s="148">
+        <v>179.04</v>
+      </c>
+    </row>
+    <row r="67" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="3" t="str">
+        <f>Chaindrive!A13</f>
+        <v>Ranger 90 3ph 15-57 1/2"</v>
+      </c>
+      <c r="B67" t="s">
+        <v>314</v>
+      </c>
+      <c r="C67" s="2">
+        <f>D66+0.01</f>
+        <v>270.01</v>
+      </c>
+      <c r="D67" s="23">
+        <f>Chaindrive!J13</f>
+        <v>342</v>
+      </c>
+      <c r="E67" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F67" s="22">
+        <f>Chaindrive!L13</f>
         <v>8.4210526315789469</v>
       </c>
-      <c r="P66" s="1">
-        <v>12</v>
-      </c>
-      <c r="R66" s="6">
-        <v>450</v>
-      </c>
-      <c r="S66" s="165" t="s">
-        <v>705</v>
-      </c>
-      <c r="U66" s="150"/>
-    </row>
-    <row r="67" spans="1:23" s="107" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="B67" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="C67" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="D67" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="E67" s="105"/>
-      <c r="F67" s="105"/>
-      <c r="G67" s="105"/>
-      <c r="H67" s="106" t="s">
-        <v>467</v>
-      </c>
-      <c r="I67" s="105"/>
-      <c r="J67" s="105"/>
-      <c r="K67" s="105"/>
-      <c r="L67" s="105"/>
-      <c r="M67" s="105"/>
-      <c r="N67" s="106" t="s">
-        <v>467</v>
-      </c>
-      <c r="O67" s="108"/>
-      <c r="P67" s="105"/>
-      <c r="Q67" s="105"/>
-      <c r="R67" s="108"/>
-      <c r="S67" s="108"/>
-      <c r="U67" s="149"/>
+      <c r="G67" s="1">
+        <v>415</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="I67" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K67" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="L67" s="1">
+        <v>25.4</v>
+      </c>
+      <c r="M67" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N67" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O67" s="74">
+        <f>Chaindrive!O13</f>
+        <v>10.526315789473685</v>
+      </c>
+      <c r="P67" s="1">
+        <v>11</v>
+      </c>
+      <c r="R67" s="6">
+        <v>400</v>
+      </c>
+      <c r="S67" s="6" t="s">
+        <v>316</v>
+      </c>
+      <c r="U67" s="150">
+        <v>179.04</v>
+      </c>
+      <c r="V67" s="83"/>
+      <c r="W67" s="83"/>
     </row>
     <row r="68" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="str">
-        <f>Chaindrive!A12</f>
-        <v>Ranger 90 3ph 19-57 1/2"</v>
+        <f>Chaindrive!A16</f>
+        <v>Ranger150 3ph 18-57 5/8"</v>
       </c>
       <c r="B68" t="s">
         <v>314</v>
       </c>
       <c r="C68" s="2">
-        <v>0</v>
+        <f>D66+0.01</f>
+        <v>270.01</v>
       </c>
       <c r="D68" s="23">
-        <f>Chaindrive!J12</f>
-        <v>270</v>
+        <f>Chaindrive!J16</f>
+        <v>471.83333333333331</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F68" s="22">
-        <f>Chaindrive!L12</f>
-        <v>10.666666666666666</v>
+        <f>Chaindrive!L16</f>
+        <v>15.157894736842106</v>
       </c>
       <c r="G68" s="1">
         <v>415</v>
@@ -27313,9 +27329,9 @@
       <c r="N68" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O68" s="6">
-        <f>Chaindrive!O12</f>
-        <v>13.333333333333334</v>
+      <c r="O68" s="74">
+        <f>Chaindrive!O16</f>
+        <v>12.631578947368421</v>
       </c>
       <c r="P68" s="1">
         <v>11</v>
@@ -27324,34 +27340,35 @@
         <v>400</v>
       </c>
       <c r="S68" s="6" t="s">
-        <v>316</v>
-      </c>
-      <c r="U68" s="148">
-        <v>179.04</v>
-      </c>
+        <v>317</v>
+      </c>
+      <c r="U68" s="150">
+        <v>472.24</v>
+      </c>
+      <c r="V68" s="83"/>
     </row>
     <row r="69" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="str">
-        <f>Chaindrive!A13</f>
-        <v>Ranger 90 3ph 15-57 1/2"</v>
+        <f>Chaindrive!A17</f>
+        <v>Ranger150 3ph 15-57 5/8"</v>
       </c>
       <c r="B69" t="s">
         <v>314</v>
       </c>
       <c r="C69" s="2">
-        <f>D68+0.01</f>
-        <v>270.01</v>
+        <f>D67+0.01</f>
+        <v>342.01</v>
       </c>
       <c r="D69" s="23">
-        <f>Chaindrive!J13</f>
-        <v>342</v>
+        <f>Chaindrive!J17</f>
+        <v>566.19999999999993</v>
       </c>
       <c r="E69" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F69" s="22">
-        <f>Chaindrive!L13</f>
-        <v>8.4210526315789469</v>
+        <f>Chaindrive!L17</f>
+        <v>12.631578947368421</v>
       </c>
       <c r="G69" s="1">
         <v>415</v>
@@ -27374,8 +27391,8 @@
       <c r="N69" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O69" s="6">
-        <f>Chaindrive!O13</f>
+      <c r="O69" s="74">
+        <f>Chaindrive!O17</f>
         <v>10.526315789473685</v>
       </c>
       <c r="P69" s="1">
@@ -27385,36 +27402,34 @@
         <v>400</v>
       </c>
       <c r="S69" s="6" t="s">
-        <v>316</v>
+        <v>670</v>
       </c>
       <c r="U69" s="150">
-        <v>179.04</v>
+        <v>472.24</v>
       </c>
       <c r="V69" s="83"/>
-      <c r="W69" s="83"/>
     </row>
     <row r="70" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="str">
-        <f>Chaindrive!A16</f>
-        <v>Ranger150 3ph 18-57 5/8"</v>
+        <f>Chaindrive!A18</f>
+        <v>Ranger150 3ph 12-57 5/8"</v>
       </c>
       <c r="B70" t="s">
         <v>314</v>
       </c>
       <c r="C70" s="2">
-        <f>D68+0.01</f>
-        <v>270.01</v>
+        <f>D67+0.01</f>
+        <v>342.01</v>
       </c>
       <c r="D70" s="23">
-        <f>Chaindrive!J16</f>
-        <v>471.83333333333331</v>
+        <v>713</v>
       </c>
       <c r="E70" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F70" s="2">
-        <f>Chaindrive!L16</f>
-        <v>15.157894736842106</v>
+      <c r="F70" s="22">
+        <f>Chaindrive!L18</f>
+        <v>10.105263157894736</v>
       </c>
       <c r="G70" s="1">
         <v>415</v>
@@ -27437,9 +27452,9 @@
       <c r="N70" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O70" s="6">
-        <f>Chaindrive!O16</f>
-        <v>12.631578947368421</v>
+      <c r="O70" s="74">
+        <f>Chaindrive!O18</f>
+        <v>8.4210526315789469</v>
       </c>
       <c r="P70" s="1">
         <v>11</v>
@@ -27453,30 +27468,28 @@
       <c r="U70" s="150">
         <v>472.24</v>
       </c>
-      <c r="V70" s="83"/>
     </row>
     <row r="71" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="str">
-        <f>Chaindrive!A17</f>
-        <v>Ranger150 3ph 15-57 5/8"</v>
+        <f>Chaindrive!A20</f>
+        <v>Ranger220 3ph 15-57 3/4"</v>
       </c>
       <c r="B71" t="s">
         <v>314</v>
       </c>
       <c r="C71" s="2">
-        <f>D69+0.01</f>
-        <v>342.01</v>
+        <v>713.01</v>
       </c>
       <c r="D71" s="23">
-        <f>Chaindrive!J17</f>
-        <v>566.19999999999993</v>
+        <f>Chaindrive!J20</f>
+        <v>836</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F71" s="2">
-        <f>Chaindrive!L17</f>
-        <v>12.631578947368421</v>
+      <c r="F71" s="22">
+        <f>Chaindrive!L20</f>
+        <v>6.3157894736842106</v>
       </c>
       <c r="G71" s="1">
         <v>415</v>
@@ -27491,7 +27504,7 @@
         <v>260</v>
       </c>
       <c r="L71" s="1">
-        <v>25.4</v>
+        <v>30</v>
       </c>
       <c r="M71" s="1" t="s">
         <v>22</v>
@@ -27499,107 +27512,78 @@
       <c r="N71" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O71" s="6">
-        <f>Chaindrive!O17</f>
+      <c r="O71" s="74">
+        <f>Chaindrive!O20</f>
         <v>10.526315789473685</v>
       </c>
       <c r="P71" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R71" s="6">
-        <v>400</v>
-      </c>
-      <c r="S71" s="6" t="s">
-        <v>670</v>
+        <v>650</v>
       </c>
       <c r="U71" s="150">
-        <v>472.24</v>
-      </c>
-      <c r="V71" s="83"/>
-    </row>
-    <row r="72" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A72" s="3" t="str">
-        <f>Chaindrive!A18</f>
-        <v>Ranger150 3ph 12-57 5/8"</v>
-      </c>
-      <c r="B72" t="s">
-        <v>314</v>
-      </c>
-      <c r="C72" s="2">
-        <f>D69+0.01</f>
-        <v>342.01</v>
-      </c>
-      <c r="D72" s="23">
-        <v>713</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F72" s="2">
-        <v>10</v>
-      </c>
-      <c r="G72" s="1">
-        <v>415</v>
-      </c>
-      <c r="H72" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I72" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K72" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="L72" s="1">
-        <v>25.4</v>
-      </c>
-      <c r="M72" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N72" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O72" s="6">
-        <f>Chaindrive!O18</f>
-        <v>8.4210526315789469</v>
-      </c>
-      <c r="P72" s="1">
-        <v>11</v>
-      </c>
-      <c r="R72" s="6">
-        <v>400</v>
-      </c>
-      <c r="S72" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="U72" s="150">
-        <v>472.24</v>
-      </c>
+        <v>498.07</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" s="107" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A72" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="B72" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="C72" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="D72" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="E72" s="105"/>
+      <c r="F72" s="110"/>
+      <c r="G72" s="105"/>
+      <c r="H72" s="106" t="s">
+        <v>467</v>
+      </c>
+      <c r="I72" s="105"/>
+      <c r="J72" s="105"/>
+      <c r="K72" s="105"/>
+      <c r="L72" s="105"/>
+      <c r="M72" s="105"/>
+      <c r="N72" s="106" t="s">
+        <v>467</v>
+      </c>
+      <c r="O72" s="167"/>
+      <c r="P72" s="105"/>
+      <c r="Q72" s="105"/>
+      <c r="R72" s="108"/>
+      <c r="S72" s="108"/>
+      <c r="U72" s="109"/>
     </row>
     <row r="73" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="str">
-        <f>Chaindrive!A20</f>
-        <v>Ranger220 3ph 15-57 3/4"</v>
+        <f>Chaindrive!A23</f>
+        <v>Ranger 90 Fi 1ph 15-57 1/2"</v>
       </c>
       <c r="B73" t="s">
         <v>314</v>
       </c>
       <c r="C73" s="2">
-        <v>713.01</v>
+        <v>0</v>
       </c>
       <c r="D73" s="23">
-        <f>Chaindrive!J20</f>
-        <v>836</v>
+        <f>Chaindrive!J23</f>
+        <v>342</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F73" s="2">
-        <f>Chaindrive!L20</f>
-        <v>6.3157894736842106</v>
+        <v>352</v>
+      </c>
+      <c r="F73" s="22">
+        <f>Chaindrive!L23</f>
+        <v>21.05263157894737</v>
       </c>
       <c r="G73" s="1">
-        <v>415</v>
+        <v>230</v>
       </c>
       <c r="H73" s="1" t="s">
         <v>308</v>
@@ -27611,7 +27595,7 @@
         <v>260</v>
       </c>
       <c r="L73" s="1">
-        <v>30</v>
+        <v>25.4</v>
       </c>
       <c r="M73" s="1" t="s">
         <v>22</v>
@@ -27619,75 +27603,94 @@
       <c r="N73" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O73" s="6">
-        <f>Chaindrive!O20</f>
-        <v>10.526315789473685</v>
+      <c r="O73" s="74">
+        <f>Chaindrive!O23</f>
+        <v>5.2631578947368425</v>
       </c>
       <c r="P73" s="1">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="R73" s="6">
-        <v>650</v>
-      </c>
-      <c r="U73" s="150">
-        <v>498.07</v>
-      </c>
-    </row>
-    <row r="74" spans="1:23" s="107" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A74" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="B74" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="C74" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="D74" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="E74" s="105"/>
-      <c r="F74" s="110"/>
-      <c r="G74" s="105"/>
-      <c r="H74" s="106" t="s">
-        <v>467</v>
-      </c>
-      <c r="I74" s="105"/>
-      <c r="J74" s="105"/>
-      <c r="K74" s="105"/>
-      <c r="L74" s="105"/>
-      <c r="M74" s="105"/>
-      <c r="N74" s="106" t="s">
-        <v>467</v>
-      </c>
-      <c r="O74" s="108"/>
-      <c r="P74" s="105"/>
-      <c r="Q74" s="105"/>
-      <c r="R74" s="108"/>
-      <c r="S74" s="108"/>
-      <c r="U74" s="109"/>
+        <v>850</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A74" s="3" t="str">
+        <f>Chaindrive!A24</f>
+        <v>Ranger 90 Fi 3ph 15-57 1/2"</v>
+      </c>
+      <c r="B74" t="s">
+        <v>314</v>
+      </c>
+      <c r="C74" s="2">
+        <f t="shared" ref="C74:C75" si="2">D73+0.01</f>
+        <v>342.01</v>
+      </c>
+      <c r="D74" s="23">
+        <f>Chaindrive!J24</f>
+        <v>342</v>
+      </c>
+      <c r="E74" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="F74" s="22">
+        <f>Chaindrive!L24</f>
+        <v>21.05263157894737</v>
+      </c>
+      <c r="G74" s="1">
+        <v>415</v>
+      </c>
+      <c r="H74" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="I74" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K74" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="L74" s="1">
+        <v>25.4</v>
+      </c>
+      <c r="M74" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N74" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O74" s="74">
+        <f>Chaindrive!O24</f>
+        <v>5.2631578947368425</v>
+      </c>
+      <c r="P74" s="1">
+        <v>18</v>
+      </c>
+      <c r="R74" s="6">
+        <v>850</v>
+      </c>
     </row>
     <row r="75" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="str">
-        <f>Chaindrive!A23</f>
-        <v>Ranger 90 Fi 1ph 15-57 1/2"</v>
+        <f>Chaindrive!A25</f>
+        <v>Ranger140 Fi 1ph 18-57 5/8"</v>
       </c>
       <c r="B75" t="s">
         <v>314</v>
       </c>
       <c r="C75" s="2">
-        <v>0</v>
+        <f t="shared" si="2"/>
+        <v>342.01</v>
       </c>
       <c r="D75" s="23">
-        <f>Chaindrive!J23</f>
-        <v>342</v>
+        <f>Chaindrive!J25</f>
+        <v>475</v>
       </c>
       <c r="E75" s="1" t="s">
         <v>352</v>
       </c>
       <c r="F75" s="22">
-        <f>Chaindrive!L23</f>
-        <v>21.05263157894737</v>
+        <f>Chaindrive!L25</f>
+        <v>25.263157894736842</v>
       </c>
       <c r="G75" s="1">
         <v>230</v>
@@ -27710,9 +27713,9 @@
       <c r="N75" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O75" s="6">
-        <f>Chaindrive!O23</f>
-        <v>5.2631578947368425</v>
+      <c r="O75" s="74">
+        <f>Chaindrive!O25</f>
+        <v>6.3157894736842106</v>
       </c>
       <c r="P75" s="1">
         <v>18</v>
@@ -27723,26 +27726,26 @@
     </row>
     <row r="76" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A76" s="3" t="str">
-        <f>Chaindrive!A24</f>
-        <v>Ranger 90 Fi 3ph 15-57 1/2"</v>
+        <f>Chaindrive!A26</f>
+        <v>Ranger140 Fi 3ph 18-57 5/8"</v>
       </c>
       <c r="B76" t="s">
         <v>314</v>
       </c>
       <c r="C76" s="2">
-        <f t="shared" ref="C76:C77" si="2">D75+0.01</f>
-        <v>342.01</v>
+        <f>D75+0.01</f>
+        <v>475.01</v>
       </c>
       <c r="D76" s="23">
-        <f>Chaindrive!J24</f>
-        <v>342</v>
+        <f>Chaindrive!J26</f>
+        <v>475</v>
       </c>
       <c r="E76" s="1" t="s">
         <v>352</v>
       </c>
       <c r="F76" s="22">
-        <f>Chaindrive!L24</f>
-        <v>21.05263157894737</v>
+        <f>Chaindrive!L26</f>
+        <v>25.263157894736842</v>
       </c>
       <c r="G76" s="1">
         <v>415</v>
@@ -27765,9 +27768,9 @@
       <c r="N76" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O76" s="6">
-        <f>Chaindrive!O24</f>
-        <v>5.2631578947368425</v>
+      <c r="O76" s="74">
+        <f>Chaindrive!O26</f>
+        <v>6.3157894736842106</v>
       </c>
       <c r="P76" s="1">
         <v>18</v>
@@ -27778,26 +27781,26 @@
     </row>
     <row r="77" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A77" s="3" t="str">
-        <f>Chaindrive!A25</f>
-        <v>Ranger140 Fi 1ph 18-57 5/8"</v>
+        <f>Chaindrive!A27</f>
+        <v>Ranger140 fi 1ph 12-57 5/8"</v>
       </c>
       <c r="B77" t="s">
         <v>314</v>
       </c>
       <c r="C77" s="2">
-        <f t="shared" si="2"/>
-        <v>342.01</v>
+        <f t="shared" ref="C77:C78" si="3">D76+0.01</f>
+        <v>475.01</v>
       </c>
       <c r="D77" s="23">
-        <f>Chaindrive!J25</f>
-        <v>475</v>
+        <f>Chaindrive!J27</f>
+        <v>712.5</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>352</v>
       </c>
       <c r="F77" s="22">
-        <f>Chaindrive!L25</f>
-        <v>25.263157894736842</v>
+        <f>Chaindrive!L27</f>
+        <v>16.842105263157894</v>
       </c>
       <c r="G77" s="1">
         <v>230</v>
@@ -27820,9 +27823,9 @@
       <c r="N77" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O77" s="6">
-        <f>Chaindrive!O25</f>
-        <v>6.3157894736842106</v>
+      <c r="O77" s="74">
+        <f>Chaindrive!O27</f>
+        <v>4.2105263157894735</v>
       </c>
       <c r="P77" s="1">
         <v>18</v>
@@ -27833,26 +27836,26 @@
     </row>
     <row r="78" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A78" s="3" t="str">
-        <f>Chaindrive!A26</f>
-        <v>Ranger140 Fi 3ph 18-57 5/8"</v>
+        <f>Chaindrive!A28</f>
+        <v>Ranger140 fi 3ph 12-57 5/8"</v>
       </c>
       <c r="B78" t="s">
         <v>314</v>
       </c>
       <c r="C78" s="2">
-        <f>D77+0.01</f>
-        <v>475.01</v>
+        <f t="shared" si="3"/>
+        <v>712.51</v>
       </c>
       <c r="D78" s="23">
-        <f>Chaindrive!J26</f>
-        <v>475</v>
+        <f>Chaindrive!J28</f>
+        <v>712.5</v>
       </c>
       <c r="E78" s="1" t="s">
         <v>352</v>
       </c>
       <c r="F78" s="22">
-        <f>Chaindrive!L26</f>
-        <v>25.263157894736842</v>
+        <f>Chaindrive!L28</f>
+        <v>16.842105263157894</v>
       </c>
       <c r="G78" s="1">
         <v>415</v>
@@ -27875,9 +27878,9 @@
       <c r="N78" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O78" s="6">
-        <f>Chaindrive!O26</f>
-        <v>6.3157894736842106</v>
+      <c r="O78" s="74">
+        <f>Chaindrive!O28</f>
+        <v>4.2105263157894735</v>
       </c>
       <c r="P78" s="1">
         <v>18</v>
@@ -27886,85 +27889,51 @@
         <v>850</v>
       </c>
     </row>
-    <row r="79" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A79" s="3" t="str">
-        <f>Chaindrive!A27</f>
-        <v>Ranger140 fi 1ph 12-57 5/8"</v>
-      </c>
-      <c r="B79" t="s">
-        <v>314</v>
-      </c>
-      <c r="C79" s="2">
-        <f t="shared" ref="C79:C80" si="3">D78+0.01</f>
-        <v>475.01</v>
-      </c>
-      <c r="D79" s="23">
-        <f>Chaindrive!J27</f>
-        <v>712.5</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F79" s="22">
-        <f>Chaindrive!L27</f>
-        <v>16.842105263157894</v>
-      </c>
-      <c r="G79" s="1">
-        <v>230</v>
-      </c>
-      <c r="H79" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I79" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K79" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="L79" s="1">
-        <v>25.4</v>
-      </c>
-      <c r="M79" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N79" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O79" s="6">
-        <f>Chaindrive!O27</f>
-        <v>4.2105263157894735</v>
-      </c>
-      <c r="P79" s="1">
-        <v>18</v>
-      </c>
-      <c r="R79" s="6">
-        <v>850</v>
-      </c>
+    <row r="79" spans="1:23" s="107" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A79" s="104"/>
+      <c r="C79" s="105"/>
+      <c r="D79" s="113"/>
+      <c r="E79" s="105"/>
+      <c r="F79" s="110"/>
+      <c r="G79" s="105"/>
+      <c r="H79" s="105"/>
+      <c r="I79" s="105"/>
+      <c r="J79" s="105"/>
+      <c r="K79" s="105"/>
+      <c r="L79" s="105"/>
+      <c r="M79" s="105"/>
+      <c r="N79" s="105"/>
+      <c r="O79" s="167"/>
+      <c r="P79" s="105"/>
+      <c r="Q79" s="105"/>
+      <c r="R79" s="108"/>
+      <c r="S79" s="108"/>
+      <c r="U79" s="109"/>
     </row>
     <row r="80" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A80" s="3" t="str">
-        <f>Chaindrive!A28</f>
-        <v>Ranger140 fi 3ph 12-57 5/8"</v>
+        <f>Chaindrive!A31</f>
+        <v>KE 40.24  15-57 3/4"</v>
       </c>
       <c r="B80" t="s">
         <v>314</v>
       </c>
-      <c r="C80" s="2">
-        <f t="shared" si="3"/>
-        <v>712.51</v>
+      <c r="C80" s="1">
+        <v>600.01</v>
       </c>
       <c r="D80" s="23">
-        <f>Chaindrive!J28</f>
-        <v>712.5</v>
+        <f>Chaindrive!J31</f>
+        <v>1520</v>
       </c>
       <c r="E80" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F80" s="22">
-        <f>Chaindrive!L28</f>
-        <v>16.842105263157894</v>
+        <v>156</v>
+      </c>
+      <c r="F80" s="2">
+        <f>Chaindrive!L31</f>
+        <v>6.3157894736842106</v>
       </c>
       <c r="G80" s="1">
+        <f>Chaindrive!M31</f>
         <v>415</v>
       </c>
       <c r="H80" s="1" t="s">
@@ -27977,7 +27946,8 @@
         <v>260</v>
       </c>
       <c r="L80" s="1">
-        <v>25.4</v>
+        <f>Chaindrive!D31</f>
+        <v>40</v>
       </c>
       <c r="M80" s="1" t="s">
         <v>22</v>
@@ -27985,62 +27955,98 @@
       <c r="N80" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O80" s="6">
-        <f>Chaindrive!O28</f>
-        <v>4.2105263157894735</v>
+      <c r="O80" s="74">
+        <f>Chaindrive!O31</f>
+        <v>10.526315789473685</v>
       </c>
       <c r="P80" s="1">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="R80" s="6">
         <v>850</v>
       </c>
     </row>
-    <row r="81" spans="1:22" s="107" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A81" s="104"/>
-      <c r="C81" s="105"/>
-      <c r="D81" s="113"/>
-      <c r="E81" s="105"/>
-      <c r="F81" s="110"/>
-      <c r="G81" s="105"/>
-      <c r="H81" s="105"/>
-      <c r="I81" s="105"/>
-      <c r="J81" s="105"/>
-      <c r="K81" s="105"/>
-      <c r="L81" s="105"/>
-      <c r="M81" s="105"/>
-      <c r="N81" s="105"/>
-      <c r="O81" s="108"/>
-      <c r="P81" s="105"/>
-      <c r="Q81" s="105"/>
-      <c r="R81" s="108"/>
-      <c r="S81" s="108"/>
-      <c r="U81" s="109"/>
+    <row r="81" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A81" s="3" t="str">
+        <f>Chaindrive!A32</f>
+        <v>KE 40.24  15-57 1"</v>
+      </c>
+      <c r="B81" t="s">
+        <v>314</v>
+      </c>
+      <c r="C81" s="2">
+        <v>900.01</v>
+      </c>
+      <c r="D81" s="23">
+        <f>Chaindrive!J32</f>
+        <v>1520</v>
+      </c>
+      <c r="E81" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F81" s="2">
+        <f>Chaindrive!L32</f>
+        <v>6.3157894736842106</v>
+      </c>
+      <c r="G81" s="1">
+        <f>Chaindrive!M32</f>
+        <v>415</v>
+      </c>
+      <c r="H81" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="I81" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="J81" s="3"/>
+      <c r="K81" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="L81" s="1">
+        <f>Chaindrive!D32</f>
+        <v>40</v>
+      </c>
+      <c r="M81" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N81" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O81" s="74">
+        <f>Chaindrive!O32</f>
+        <v>10.526315789473685</v>
+      </c>
+      <c r="P81" s="1">
+        <v>11</v>
+      </c>
+      <c r="R81" s="6">
+        <v>1100</v>
+      </c>
     </row>
     <row r="82" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A82" s="3" t="str">
-        <f>Chaindrive!A31</f>
-        <v>KE 40.24  15-57 3/4"</v>
+        <f>Chaindrive!A33</f>
+        <v>KE 60.24   15-57 1"</v>
       </c>
       <c r="B82" t="s">
         <v>314</v>
       </c>
-      <c r="C82" s="1">
-        <v>600.01</v>
+      <c r="C82" s="2">
+        <v>1200.01</v>
       </c>
       <c r="D82" s="23">
-        <f>Chaindrive!J31</f>
-        <v>1520</v>
+        <f>Chaindrive!J33</f>
+        <v>2280</v>
       </c>
       <c r="E82" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F82" s="2">
-        <f>Chaindrive!L31</f>
+        <f>Chaindrive!L33</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="G82" s="1">
-        <f>Chaindrive!M31</f>
+        <f>Chaindrive!M33</f>
         <v>415</v>
       </c>
       <c r="H82" s="1" t="s">
@@ -28053,8 +28059,8 @@
         <v>260</v>
       </c>
       <c r="L82" s="1">
-        <f>Chaindrive!D31</f>
-        <v>40</v>
+        <f>Chaindrive!D33</f>
+        <v>55</v>
       </c>
       <c r="M82" s="1" t="s">
         <v>22</v>
@@ -28062,41 +28068,41 @@
       <c r="N82" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O82" s="6">
-        <f>Chaindrive!O31</f>
-        <v>10.526315789473685</v>
+      <c r="O82" s="74">
+        <f>Chaindrive!O33</f>
+        <v>15.789473684210527</v>
       </c>
       <c r="P82" s="1">
         <v>11</v>
       </c>
       <c r="R82" s="6">
-        <v>850</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="83" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="3" t="str">
-        <f>Chaindrive!A32</f>
-        <v>KE 40.24  15-57 1"</v>
+        <f>Chaindrive!A34</f>
+        <v>KE 80.24   15-57 1"</v>
       </c>
       <c r="B83" t="s">
         <v>314</v>
       </c>
       <c r="C83" s="2">
-        <v>900.01</v>
+        <v>1800.01</v>
       </c>
       <c r="D83" s="23">
-        <f>Chaindrive!J32</f>
-        <v>1520</v>
+        <f>Chaindrive!J34</f>
+        <v>3040</v>
       </c>
       <c r="E83" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F83" s="2">
-        <f>Chaindrive!L32</f>
+        <f>Chaindrive!L34</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="G83" s="1">
-        <f>Chaindrive!M32</f>
+        <f>Chaindrive!M34</f>
         <v>415</v>
       </c>
       <c r="H83" s="1" t="s">
@@ -28105,13 +28111,12 @@
       <c r="I83" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="J83" s="3"/>
       <c r="K83" s="1" t="s">
         <v>260</v>
       </c>
       <c r="L83" s="1">
-        <f>Chaindrive!D32</f>
-        <v>40</v>
+        <f>Chaindrive!D34</f>
+        <v>55</v>
       </c>
       <c r="M83" s="1" t="s">
         <v>22</v>
@@ -28119,41 +28124,41 @@
       <c r="N83" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O83" s="6">
-        <f>Chaindrive!O32</f>
-        <v>10.526315789473685</v>
+      <c r="O83" s="74">
+        <f>Chaindrive!O34</f>
+        <v>15.789473684210527</v>
       </c>
       <c r="P83" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R83" s="6">
-        <v>1100</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="84" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="3" t="str">
-        <f>Chaindrive!A33</f>
-        <v>KE 60.24   15-57 1"</v>
+        <f>Chaindrive!A35</f>
+        <v>KE 80.24   15-57 1 1/4"</v>
       </c>
       <c r="B84" t="s">
         <v>314</v>
       </c>
       <c r="C84" s="2">
-        <v>1200.01</v>
+        <v>1800.01</v>
       </c>
       <c r="D84" s="23">
-        <f>Chaindrive!J33</f>
-        <v>2280</v>
+        <f>Chaindrive!J35</f>
+        <v>3040</v>
       </c>
       <c r="E84" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F84" s="2">
-        <f>Chaindrive!L33</f>
+        <f>Chaindrive!L35</f>
         <v>6.3157894736842106</v>
       </c>
       <c r="G84" s="1">
-        <f>Chaindrive!M33</f>
+        <f>Chaindrive!M35</f>
         <v>415</v>
       </c>
       <c r="H84" s="1" t="s">
@@ -28166,7 +28171,7 @@
         <v>260</v>
       </c>
       <c r="L84" s="1">
-        <f>Chaindrive!D33</f>
+        <f>Chaindrive!D35</f>
         <v>55</v>
       </c>
       <c r="M84" s="1" t="s">
@@ -28175,98 +28180,75 @@
       <c r="N84" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O84" s="6">
-        <f>Chaindrive!O33</f>
+      <c r="O84" s="74">
+        <f>Chaindrive!O35</f>
         <v>15.789473684210527</v>
       </c>
       <c r="P84" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R84" s="6">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="85" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A85" s="3" t="str">
-        <f>Chaindrive!A34</f>
-        <v>KE 80.24   15-57 1"</v>
-      </c>
-      <c r="B85" t="s">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:22" s="107" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A85" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="B85" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="C85" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="D85" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="E85" s="105"/>
+      <c r="F85" s="110"/>
+      <c r="G85" s="105"/>
+      <c r="H85" s="106" t="s">
+        <v>467</v>
+      </c>
+      <c r="I85" s="105"/>
+      <c r="J85" s="105"/>
+      <c r="K85" s="105"/>
+      <c r="L85" s="105"/>
+      <c r="M85" s="105"/>
+      <c r="N85" s="106" t="s">
+        <v>467</v>
+      </c>
+      <c r="O85" s="167"/>
+      <c r="P85" s="105"/>
+      <c r="Q85" s="105"/>
+      <c r="R85" s="108"/>
+      <c r="S85" s="108"/>
+      <c r="U85" s="109"/>
+    </row>
+    <row r="86" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A86" s="3" t="str">
+        <f>Chaindrive!A38</f>
+        <v>KE 40.40 Fi 15-57 3/4"</v>
+      </c>
+      <c r="B86" s="57" t="s">
         <v>314</v>
       </c>
-      <c r="C85" s="2">
-        <v>1800.01</v>
-      </c>
-      <c r="D85" s="23">
-        <f>Chaindrive!J34</f>
-        <v>3040</v>
-      </c>
-      <c r="E85" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F85" s="2">
-        <f>Chaindrive!L34</f>
-        <v>6.3157894736842106</v>
-      </c>
-      <c r="G85" s="1">
-        <f>Chaindrive!M34</f>
-        <v>415</v>
-      </c>
-      <c r="H85" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I85" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K85" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="L85" s="1">
-        <f>Chaindrive!D34</f>
-        <v>55</v>
-      </c>
-      <c r="M85" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N85" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O85" s="6">
-        <f>Chaindrive!O34</f>
-        <v>15.789473684210527</v>
-      </c>
-      <c r="P85" s="1">
-        <v>12</v>
-      </c>
-      <c r="R85" s="6">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="86" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A86" s="3" t="str">
-        <f>Chaindrive!A35</f>
-        <v>KE 80.24   15-57 1 1/4"</v>
-      </c>
-      <c r="B86" t="s">
-        <v>314</v>
-      </c>
-      <c r="C86" s="2">
-        <v>1800.01</v>
+      <c r="C86" s="1">
+        <v>0</v>
       </c>
       <c r="D86" s="23">
-        <f>Chaindrive!J35</f>
-        <v>3040</v>
+        <f>Chaindrive!J38</f>
+        <v>1140</v>
       </c>
       <c r="E86" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F86" s="2">
-        <f>Chaindrive!L35</f>
-        <v>6.3157894736842106</v>
+        <v>352</v>
+      </c>
+      <c r="F86" s="22">
+        <f>Chaindrive!L38</f>
+        <v>10.526315789473685</v>
       </c>
       <c r="G86" s="1">
-        <f>Chaindrive!M35</f>
-        <v>415</v>
+        <v>230</v>
       </c>
       <c r="H86" s="1" t="s">
         <v>308</v>
@@ -28274,12 +28256,13 @@
       <c r="I86" s="1" t="s">
         <v>260</v>
       </c>
+      <c r="J86" s="1"/>
       <c r="K86" s="1" t="s">
         <v>260</v>
       </c>
       <c r="L86" s="1">
-        <f>Chaindrive!D35</f>
-        <v>55</v>
+        <f>Chaindrive!R38</f>
+        <v>40</v>
       </c>
       <c r="M86" s="1" t="s">
         <v>22</v>
@@ -28287,71 +28270,101 @@
       <c r="N86" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O86" s="6">
-        <f>Chaindrive!O35</f>
+      <c r="O86" s="22">
+        <f>Chaindrive!O38</f>
+        <v>10.526315789473685</v>
+      </c>
+      <c r="P86" s="1">
+        <v>17</v>
+      </c>
+      <c r="Q86" s="1"/>
+      <c r="R86" s="1">
+        <v>1500</v>
+      </c>
+      <c r="S86" s="1"/>
+      <c r="U86" s="111"/>
+    </row>
+    <row r="87" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A87" s="3" t="str">
+        <f>Chaindrive!A40</f>
+        <v>KE 50.80 Fi 15-57 1"</v>
+      </c>
+      <c r="B87" s="57" t="s">
+        <v>314</v>
+      </c>
+      <c r="C87" s="2">
+        <f>D86+0.01</f>
+        <v>1140.01</v>
+      </c>
+      <c r="D87" s="23">
+        <f>Chaindrive!J40</f>
+        <v>1900</v>
+      </c>
+      <c r="E87" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="F87" s="22">
+        <f>Chaindrive!L40</f>
+        <v>21.05263157894737</v>
+      </c>
+      <c r="G87" s="1">
+        <v>230</v>
+      </c>
+      <c r="H87" s="1" t="s">
+        <v>308</v>
+      </c>
+      <c r="I87" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="J87" s="1"/>
+      <c r="K87" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="L87" s="1">
+        <f>Chaindrive!R40</f>
+        <v>55</v>
+      </c>
+      <c r="M87" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="N87" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O87" s="22">
+        <f>Chaindrive!O40</f>
         <v>15.789473684210527</v>
       </c>
-      <c r="P86" s="1">
-        <v>12</v>
-      </c>
-      <c r="R86" s="6">
-        <v>2000</v>
-      </c>
-    </row>
-    <row r="87" spans="1:22" s="107" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A87" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="B87" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="C87" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="D87" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="E87" s="105"/>
-      <c r="F87" s="110"/>
-      <c r="G87" s="105"/>
-      <c r="H87" s="106" t="s">
-        <v>467</v>
-      </c>
-      <c r="I87" s="105"/>
-      <c r="J87" s="105"/>
-      <c r="K87" s="105"/>
-      <c r="L87" s="105"/>
-      <c r="M87" s="105"/>
-      <c r="N87" s="106" t="s">
-        <v>467</v>
-      </c>
-      <c r="O87" s="108"/>
-      <c r="P87" s="105"/>
-      <c r="Q87" s="105"/>
-      <c r="R87" s="108"/>
-      <c r="S87" s="108"/>
-      <c r="U87" s="109"/>
+      <c r="P87" s="1">
+        <v>19</v>
+      </c>
+      <c r="Q87" s="1"/>
+      <c r="R87" s="1">
+        <v>4500</v>
+      </c>
+      <c r="S87" s="1"/>
+      <c r="U87" s="111"/>
     </row>
     <row r="88" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="3" t="str">
-        <f>Chaindrive!A38</f>
-        <v>KE 40.40 Fi 15-57 3/4"</v>
+        <f>Chaindrive!A41</f>
+        <v>KE 80.40 Fi 15-57 1"</v>
       </c>
       <c r="B88" s="57" t="s">
         <v>314</v>
       </c>
-      <c r="C88" s="1">
-        <v>0</v>
+      <c r="C88" s="2">
+        <f>D87+0.01</f>
+        <v>1900.01</v>
       </c>
       <c r="D88" s="23">
-        <f>Chaindrive!J38</f>
-        <v>1140</v>
+        <f>Chaindrive!J41</f>
+        <v>3040</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="F88" s="2">
-        <f>Chaindrive!L38</f>
+      <c r="F88" s="22">
+        <f>Chaindrive!L41</f>
         <v>10.526315789473685</v>
       </c>
       <c r="G88" s="1">
@@ -28368,8 +28381,8 @@
         <v>260</v>
       </c>
       <c r="L88" s="1">
-        <f>Chaindrive!R38</f>
-        <v>40</v>
+        <f>Chaindrive!R41</f>
+        <v>55</v>
       </c>
       <c r="M88" s="1" t="s">
         <v>22</v>
@@ -28377,45 +28390,44 @@
       <c r="N88" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O88" s="1">
-        <f>Chaindrive!O38</f>
-        <v>10.526315789473685</v>
+      <c r="O88" s="22">
+        <f>Chaindrive!O41</f>
+        <v>15.789473684210527</v>
       </c>
       <c r="P88" s="1">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Q88" s="1"/>
       <c r="R88" s="1">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="S88" s="1"/>
       <c r="U88" s="111"/>
     </row>
     <row r="89" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A89" s="3" t="str">
-        <f>Chaindrive!A40</f>
-        <v>KE 50.80 Fi 15-57 1"</v>
+        <f>Chaindrive!A38</f>
+        <v>KE 40.40 Fi 15-57 3/4"</v>
       </c>
       <c r="B89" s="57" t="s">
         <v>314</v>
       </c>
-      <c r="C89" s="2">
-        <f>D88+0.01</f>
-        <v>1140.01</v>
+      <c r="C89" s="1">
+        <v>0</v>
       </c>
       <c r="D89" s="23">
-        <f>Chaindrive!J40</f>
-        <v>1900</v>
+        <f>Chaindrive!J38</f>
+        <v>1140</v>
       </c>
       <c r="E89" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="F89" s="2">
-        <f>Chaindrive!L40</f>
-        <v>21.05263157894737</v>
+      <c r="F89" s="22">
+        <f>Chaindrive!L38</f>
+        <v>10.526315789473685</v>
       </c>
       <c r="G89" s="1">
-        <v>230</v>
+        <v>415</v>
       </c>
       <c r="H89" s="1" t="s">
         <v>308</v>
@@ -28428,8 +28440,8 @@
         <v>260</v>
       </c>
       <c r="L89" s="1">
-        <f>Chaindrive!R40</f>
-        <v>55</v>
+        <f>Chaindrive!R38</f>
+        <v>40</v>
       </c>
       <c r="M89" s="1" t="s">
         <v>22</v>
@@ -28437,45 +28449,45 @@
       <c r="N89" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O89" s="1">
-        <f>Chaindrive!O40</f>
-        <v>15.789473684210527</v>
+      <c r="O89" s="22">
+        <f>Chaindrive!O38</f>
+        <v>10.526315789473685</v>
       </c>
       <c r="P89" s="1">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="Q89" s="1"/>
       <c r="R89" s="1">
-        <v>4500</v>
+        <v>1500</v>
       </c>
       <c r="S89" s="1"/>
       <c r="U89" s="111"/>
     </row>
     <row r="90" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A90" s="3" t="str">
-        <f>Chaindrive!A41</f>
-        <v>KE 80.40 Fi 15-57 1"</v>
+        <f>Chaindrive!A39</f>
+        <v>KE 40.40 Fi 15-57 1"</v>
       </c>
       <c r="B90" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C90" s="2">
         <f>D89+0.01</f>
-        <v>1900.01</v>
+        <v>1140.01</v>
       </c>
       <c r="D90" s="23">
-        <f>Chaindrive!J41</f>
-        <v>3040</v>
+        <f>Chaindrive!J39</f>
+        <v>1140</v>
       </c>
       <c r="E90" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="F90" s="2">
-        <f>Chaindrive!L41</f>
+      <c r="F90" s="22">
+        <f>Chaindrive!L39</f>
         <v>10.526315789473685</v>
       </c>
       <c r="G90" s="1">
-        <v>230</v>
+        <v>415</v>
       </c>
       <c r="H90" s="1" t="s">
         <v>308</v>
@@ -28488,8 +28500,8 @@
         <v>260</v>
       </c>
       <c r="L90" s="1">
-        <f>Chaindrive!R41</f>
-        <v>55</v>
+        <f>Chaindrive!R39</f>
+        <v>40</v>
       </c>
       <c r="M90" s="1" t="s">
         <v>22</v>
@@ -28497,12 +28509,12 @@
       <c r="N90" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O90" s="1">
-        <f>Chaindrive!O41</f>
-        <v>15.789473684210527</v>
+      <c r="O90" s="22">
+        <f>Chaindrive!O39</f>
+        <v>10.526315789473685</v>
       </c>
       <c r="P90" s="1">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="Q90" s="1"/>
       <c r="R90" s="1">
@@ -28513,25 +28525,26 @@
     </row>
     <row r="91" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="3" t="str">
-        <f>Chaindrive!A38</f>
-        <v>KE 40.40 Fi 15-57 3/4"</v>
+        <f>Chaindrive!A40</f>
+        <v>KE 50.80 Fi 15-57 1"</v>
       </c>
       <c r="B91" s="57" t="s">
         <v>314</v>
       </c>
-      <c r="C91" s="1">
-        <v>0</v>
+      <c r="C91" s="2">
+        <f>D90+0.01</f>
+        <v>1140.01</v>
       </c>
       <c r="D91" s="23">
-        <f>Chaindrive!J38</f>
-        <v>1140</v>
+        <f>Chaindrive!J40</f>
+        <v>1900</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>352</v>
       </c>
-      <c r="F91" s="2">
-        <f>Chaindrive!L38</f>
-        <v>10.526315789473685</v>
+      <c r="F91" s="22">
+        <f>Chaindrive!L40</f>
+        <v>21.05263157894737</v>
       </c>
       <c r="G91" s="1">
         <v>415</v>
@@ -28547,8 +28560,8 @@
         <v>260</v>
       </c>
       <c r="L91" s="1">
-        <f>Chaindrive!R38</f>
-        <v>40</v>
+        <f>Chaindrive!R40</f>
+        <v>55</v>
       </c>
       <c r="M91" s="1" t="s">
         <v>22</v>
@@ -28556,200 +28569,204 @@
       <c r="N91" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O91" s="1">
-        <f>Chaindrive!O38</f>
-        <v>10.526315789473685</v>
+      <c r="O91" s="22">
+        <f>Chaindrive!O40</f>
+        <v>15.789473684210527</v>
       </c>
       <c r="P91" s="1">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="Q91" s="1"/>
       <c r="R91" s="1">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="S91" s="1"/>
       <c r="U91" s="111"/>
     </row>
-    <row r="92" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="3" t="str">
-        <f>Chaindrive!A39</f>
-        <v>KE 40.40 Fi 15-57 1"</v>
-      </c>
-      <c r="B92" s="57" t="s">
+    <row r="92" spans="1:22" s="107" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A92" s="104"/>
+      <c r="B92" s="104"/>
+      <c r="C92" s="104"/>
+      <c r="D92" s="104"/>
+      <c r="E92" s="105"/>
+      <c r="F92" s="110"/>
+      <c r="G92" s="105"/>
+      <c r="H92" s="106"/>
+      <c r="I92" s="105"/>
+      <c r="J92" s="105"/>
+      <c r="K92" s="105"/>
+      <c r="L92" s="105"/>
+      <c r="M92" s="105"/>
+      <c r="N92" s="106"/>
+      <c r="O92" s="108"/>
+      <c r="P92" s="105"/>
+      <c r="Q92" s="105"/>
+      <c r="R92" s="108"/>
+      <c r="S92" s="108"/>
+      <c r="U92" s="109"/>
+    </row>
+    <row r="93" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A93" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B93" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="C93" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D93" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="H93" s="95" t="s">
+        <v>467</v>
+      </c>
+      <c r="N93" s="95" t="s">
+        <v>467</v>
+      </c>
+      <c r="O93" s="1"/>
+      <c r="R93" s="1"/>
+      <c r="S93" s="1"/>
+      <c r="T93" s="57"/>
+      <c r="U93" s="111"/>
+      <c r="V93" s="57"/>
+    </row>
+    <row r="94" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A94" s="3" t="s">
+        <v>573</v>
+      </c>
+      <c r="B94" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="C92" s="2">
-        <f>D91+0.01</f>
-        <v>1140.01</v>
-      </c>
-      <c r="D92" s="23">
-        <f>Chaindrive!J39</f>
-        <v>1140</v>
-      </c>
-      <c r="E92" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F92" s="2">
-        <f>Chaindrive!L39</f>
-        <v>10.526315789473685</v>
-      </c>
-      <c r="G92" s="1">
+      <c r="C94" s="1">
+        <v>0</v>
+      </c>
+      <c r="D94" s="1">
+        <v>100</v>
+      </c>
+      <c r="E94" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F94" s="1">
+        <v>15</v>
+      </c>
+      <c r="G94" s="1">
         <v>415</v>
       </c>
-      <c r="H92" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I92" s="1" t="s">
+      <c r="H94" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I94" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="J92" s="1"/>
-      <c r="K92" s="1" t="s">
+      <c r="K94" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L92" s="1">
-        <f>Chaindrive!R39</f>
-        <v>40</v>
-      </c>
-      <c r="M92" s="1" t="s">
+      <c r="L94" s="1">
+        <v>30</v>
+      </c>
+      <c r="M94" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N94" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="N92" s="1" t="s">
+      <c r="O94" s="1">
+        <v>20</v>
+      </c>
+      <c r="P94" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q94" s="1">
+        <v>15</v>
+      </c>
+      <c r="R94" s="1">
+        <v>300</v>
+      </c>
+      <c r="S94" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="T94" s="57"/>
+      <c r="U94" s="147">
+        <v>266.06</v>
+      </c>
+      <c r="V94" s="57"/>
+    </row>
+    <row r="95" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A95" s="57" t="s">
+        <v>319</v>
+      </c>
+      <c r="B95" s="57" t="s">
+        <v>314</v>
+      </c>
+      <c r="C95" s="1">
+        <f>D94+0.01</f>
+        <v>100.01</v>
+      </c>
+      <c r="D95" s="1">
+        <v>170</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F95" s="1">
+        <v>15</v>
+      </c>
+      <c r="G95" s="1">
+        <v>415</v>
+      </c>
+      <c r="H95" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I95" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K95" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="L95" s="1">
+        <v>30</v>
+      </c>
+      <c r="M95" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N95" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O92" s="1">
-        <f>Chaindrive!O39</f>
-        <v>10.526315789473685</v>
-      </c>
-      <c r="P92" s="1">
-        <v>19</v>
-      </c>
-      <c r="Q92" s="1"/>
-      <c r="R92" s="1">
-        <v>4500</v>
-      </c>
-      <c r="S92" s="1"/>
-      <c r="U92" s="111"/>
-    </row>
-    <row r="93" spans="1:22" s="57" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="3" t="str">
-        <f>Chaindrive!A40</f>
-        <v>KE 50.80 Fi 15-57 1"</v>
-      </c>
-      <c r="B93" s="57" t="s">
+      <c r="O95" s="1">
+        <v>20</v>
+      </c>
+      <c r="P95" s="1">
+        <v>8</v>
+      </c>
+      <c r="Q95" s="1">
+        <v>16</v>
+      </c>
+      <c r="R95" s="1">
+        <v>450</v>
+      </c>
+      <c r="S95" s="1" t="s">
+        <v>320</v>
+      </c>
+      <c r="T95" s="57"/>
+      <c r="U95" s="147">
+        <v>280.37</v>
+      </c>
+      <c r="V95" s="57"/>
+    </row>
+    <row r="96" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A96" s="57" t="s">
+        <v>321</v>
+      </c>
+      <c r="B96" s="57" t="s">
         <v>314</v>
       </c>
-      <c r="C93" s="2">
-        <f>D92+0.01</f>
-        <v>1140.01</v>
-      </c>
-      <c r="D93" s="23">
-        <f>Chaindrive!J40</f>
-        <v>1900</v>
-      </c>
-      <c r="E93" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F93" s="2">
-        <f>Chaindrive!L40</f>
-        <v>21.05263157894737</v>
-      </c>
-      <c r="G93" s="1">
-        <v>415</v>
-      </c>
-      <c r="H93" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I93" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="J93" s="1"/>
-      <c r="K93" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="L93" s="1">
-        <f>Chaindrive!R40</f>
-        <v>55</v>
-      </c>
-      <c r="M93" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N93" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O93" s="1">
-        <f>Chaindrive!O40</f>
-        <v>15.789473684210527</v>
-      </c>
-      <c r="P93" s="1">
-        <v>12</v>
-      </c>
-      <c r="Q93" s="1"/>
-      <c r="R93" s="1">
-        <v>4500</v>
-      </c>
-      <c r="S93" s="1"/>
-      <c r="U93" s="111"/>
-    </row>
-    <row r="94" spans="1:22" s="107" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="104"/>
-      <c r="B94" s="104"/>
-      <c r="C94" s="104"/>
-      <c r="D94" s="104"/>
-      <c r="E94" s="105"/>
-      <c r="F94" s="110"/>
-      <c r="G94" s="105"/>
-      <c r="H94" s="106"/>
-      <c r="I94" s="105"/>
-      <c r="J94" s="105"/>
-      <c r="K94" s="105"/>
-      <c r="L94" s="105"/>
-      <c r="M94" s="105"/>
-      <c r="N94" s="106"/>
-      <c r="O94" s="108"/>
-      <c r="P94" s="105"/>
-      <c r="Q94" s="105"/>
-      <c r="R94" s="108"/>
-      <c r="S94" s="108"/>
-      <c r="U94" s="109"/>
-    </row>
-    <row r="95" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="B95" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="H95" s="95" t="s">
-        <v>467</v>
-      </c>
-      <c r="N95" s="95" t="s">
-        <v>467</v>
-      </c>
-      <c r="O95" s="1"/>
-      <c r="R95" s="1"/>
-      <c r="S95" s="1"/>
-      <c r="T95" s="57"/>
-      <c r="U95" s="111"/>
-      <c r="V95" s="57"/>
-    </row>
-    <row r="96" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A96" s="3" t="s">
-        <v>573</v>
-      </c>
-      <c r="B96" s="3" t="s">
-        <v>314</v>
-      </c>
       <c r="C96" s="1">
-        <v>0</v>
+        <f>D95+0.01</f>
+        <v>170.01</v>
       </c>
       <c r="D96" s="1">
-        <v>100</v>
+        <v>250</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>156</v>
@@ -28782,36 +28799,36 @@
         <v>20</v>
       </c>
       <c r="P96" s="1">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="Q96" s="1">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="R96" s="1">
-        <v>300</v>
+        <v>750</v>
       </c>
       <c r="S96" s="1" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="T96" s="57"/>
       <c r="U96" s="147">
-        <v>266.06</v>
+        <v>307.35000000000002</v>
       </c>
       <c r="V96" s="57"/>
     </row>
     <row r="97" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A97" s="57" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B97" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C97" s="1">
-        <f>D96+0.01</f>
-        <v>100.01</v>
+        <f t="shared" ref="C97:C105" si="4">D96+0.01</f>
+        <v>250.01</v>
       </c>
       <c r="D97" s="1">
-        <v>170</v>
+        <v>350</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>156</v>
@@ -28832,7 +28849,7 @@
         <v>260</v>
       </c>
       <c r="L97" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M97" s="1" t="s">
         <v>55</v>
@@ -28844,36 +28861,33 @@
         <v>20</v>
       </c>
       <c r="P97" s="1">
-        <v>8</v>
-      </c>
-      <c r="Q97" s="1">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="R97" s="1">
-        <v>450</v>
+        <v>850</v>
       </c>
       <c r="S97" s="1" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="T97" s="57"/>
-      <c r="U97" s="147">
-        <v>280.37</v>
+      <c r="U97" s="146">
+        <v>383.55</v>
       </c>
       <c r="V97" s="57"/>
     </row>
     <row r="98" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="57" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B98" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C98" s="1">
-        <f>D97+0.01</f>
-        <v>170.01</v>
+        <f t="shared" si="4"/>
+        <v>350.01</v>
       </c>
       <c r="D98" s="1">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>156</v>
@@ -28894,7 +28908,7 @@
         <v>260</v>
       </c>
       <c r="L98" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M98" s="1" t="s">
         <v>55</v>
@@ -28906,36 +28920,33 @@
         <v>20</v>
       </c>
       <c r="P98" s="1">
-        <v>11</v>
-      </c>
-      <c r="Q98" s="1">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="R98" s="1">
-        <v>750</v>
+        <v>1100</v>
       </c>
       <c r="S98" s="1" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="T98" s="57"/>
-      <c r="U98" s="147">
-        <v>307.35000000000002</v>
+      <c r="U98" s="146">
+        <v>475.98</v>
       </c>
       <c r="V98" s="57"/>
     </row>
     <row r="99" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A99" s="57" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B99" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C99" s="1">
-        <f t="shared" ref="C99:C107" si="4">D98+0.01</f>
-        <v>250.01</v>
+        <f t="shared" si="4"/>
+        <v>450.01</v>
       </c>
       <c r="D99" s="1">
-        <v>350</v>
+        <v>550</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>156</v>
@@ -28971,30 +28982,30 @@
         <v>9</v>
       </c>
       <c r="R99" s="1">
-        <v>850</v>
+        <v>1100</v>
       </c>
       <c r="S99" s="1" t="s">
-        <v>324</v>
+        <v>350</v>
       </c>
       <c r="T99" s="57"/>
       <c r="U99" s="146">
-        <v>383.55</v>
+        <v>574.51</v>
       </c>
       <c r="V99" s="57"/>
     </row>
     <row r="100" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A100" s="57" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="B100" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C100" s="1">
         <f t="shared" si="4"/>
-        <v>350.01</v>
+        <v>550.01</v>
       </c>
       <c r="D100" s="1">
-        <v>450</v>
+        <v>650</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>156</v>
@@ -29033,27 +29044,27 @@
         <v>1100</v>
       </c>
       <c r="S100" s="1" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="T100" s="57"/>
       <c r="U100" s="146">
-        <v>475.98</v>
+        <v>617.67999999999995</v>
       </c>
       <c r="V100" s="57"/>
     </row>
     <row r="101" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="57" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="B101" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C101" s="1">
         <f t="shared" si="4"/>
-        <v>450.01</v>
+        <v>650.01</v>
       </c>
       <c r="D101" s="1">
-        <v>550</v>
+        <v>750</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>156</v>
@@ -29074,7 +29085,7 @@
         <v>260</v>
       </c>
       <c r="L101" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="M101" s="1" t="s">
         <v>55</v>
@@ -29089,36 +29100,36 @@
         <v>9</v>
       </c>
       <c r="R101" s="1">
-        <v>1100</v>
+        <v>2800</v>
       </c>
       <c r="S101" s="1" t="s">
-        <v>350</v>
+        <v>331</v>
       </c>
       <c r="T101" s="57"/>
       <c r="U101" s="146">
-        <v>574.51</v>
+        <v>965.9</v>
       </c>
       <c r="V101" s="57"/>
     </row>
     <row r="102" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="57" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="B102" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C102" s="1">
         <f t="shared" si="4"/>
-        <v>550.01</v>
+        <v>750.01</v>
       </c>
       <c r="D102" s="1">
-        <v>650</v>
+        <v>850</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F102" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G102" s="1">
         <v>415</v>
@@ -29133,7 +29144,7 @@
         <v>260</v>
       </c>
       <c r="L102" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="M102" s="1" t="s">
         <v>55</v>
@@ -29145,39 +29156,39 @@
         <v>20</v>
       </c>
       <c r="P102" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R102" s="1">
         <v>1100</v>
       </c>
       <c r="S102" s="1" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="T102" s="57"/>
       <c r="U102" s="146">
-        <v>617.67999999999995</v>
+        <v>1031.17</v>
       </c>
       <c r="V102" s="57"/>
     </row>
     <row r="103" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="57" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="B103" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C103" s="1">
         <f t="shared" si="4"/>
-        <v>650.01</v>
+        <v>850.01</v>
       </c>
       <c r="D103" s="1">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F103" s="1">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G103" s="1">
         <v>415</v>
@@ -29204,39 +29215,39 @@
         <v>20</v>
       </c>
       <c r="P103" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="R103" s="1">
         <v>2800</v>
       </c>
       <c r="S103" s="1" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="T103" s="57"/>
       <c r="U103" s="146">
-        <v>965.9</v>
+        <v>1351.89</v>
       </c>
       <c r="V103" s="57"/>
     </row>
     <row r="104" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A104" s="57" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="B104" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C104" s="1">
         <f t="shared" si="4"/>
-        <v>750.01</v>
+        <v>1000.01</v>
       </c>
       <c r="D104" s="1">
-        <v>850</v>
+        <v>1400</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F104" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G104" s="1">
         <v>415</v>
@@ -29266,36 +29277,36 @@
         <v>7</v>
       </c>
       <c r="R104" s="1">
-        <v>1100</v>
+        <v>2800</v>
       </c>
       <c r="S104" s="1" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="T104" s="57"/>
       <c r="U104" s="146">
-        <v>1031.17</v>
+        <v>1685.96</v>
       </c>
       <c r="V104" s="57"/>
     </row>
     <row r="105" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="57" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="B105" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C105" s="1">
         <f t="shared" si="4"/>
-        <v>850.01</v>
+        <v>1400.01</v>
       </c>
       <c r="D105" s="1">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F105" s="1">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="G105" s="1">
         <v>415</v>
@@ -29310,7 +29321,7 @@
         <v>260</v>
       </c>
       <c r="L105" s="1">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M105" s="1" t="s">
         <v>55</v>
@@ -29319,160 +29330,156 @@
         <v>22</v>
       </c>
       <c r="O105" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="P105" s="1">
         <v>7</v>
       </c>
       <c r="R105" s="1">
-        <v>2800</v>
+        <v>3125</v>
       </c>
       <c r="S105" s="1" t="s">
-        <v>335</v>
-      </c>
-      <c r="T105" s="57"/>
-      <c r="U105" s="146">
-        <v>1351.89</v>
-      </c>
+        <v>574</v>
+      </c>
+      <c r="T105" s="57" t="e" vm="1">
+        <v>#VALUE!</v>
+      </c>
+      <c r="U105" s="131"/>
       <c r="V105" s="57"/>
     </row>
     <row r="106" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="57" t="s">
-        <v>336</v>
-      </c>
-      <c r="B106" s="57" t="s">
+      <c r="A106" s="128" t="s">
+        <v>339</v>
+      </c>
+      <c r="B106" s="128" t="s">
         <v>314</v>
       </c>
-      <c r="C106" s="1">
-        <f t="shared" si="4"/>
-        <v>1000.01</v>
-      </c>
-      <c r="D106" s="1">
-        <v>1400</v>
-      </c>
-      <c r="E106" s="1" t="s">
+      <c r="C106" s="52">
+        <f t="shared" ref="C106:C109" si="5">D105+0.01</f>
+        <v>1800.01</v>
+      </c>
+      <c r="D106" s="52">
+        <v>2600</v>
+      </c>
+      <c r="E106" s="52" t="s">
         <v>156</v>
       </c>
-      <c r="F106" s="1">
-        <v>7</v>
-      </c>
-      <c r="G106" s="1">
+      <c r="F106" s="52">
+        <v>5</v>
+      </c>
+      <c r="G106" s="52">
         <v>415</v>
       </c>
-      <c r="H106" s="1" t="s">
+      <c r="H106" s="52" t="s">
         <v>287</v>
       </c>
-      <c r="I106" s="1" t="s">
+      <c r="I106" s="52" t="s">
         <v>260</v>
       </c>
-      <c r="K106" s="1" t="s">
+      <c r="J106" s="52"/>
+      <c r="K106" s="52" t="s">
         <v>260</v>
       </c>
-      <c r="L106" s="1">
-        <v>55</v>
-      </c>
-      <c r="M106" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N106" s="1" t="s">
+      <c r="L106" s="52">
+        <v>80</v>
+      </c>
+      <c r="M106" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="N106" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="O106" s="1">
-        <v>20</v>
-      </c>
-      <c r="P106" s="1">
-        <v>7</v>
-      </c>
-      <c r="R106" s="1">
-        <v>2800</v>
-      </c>
-      <c r="S106" s="1" t="s">
-        <v>337</v>
-      </c>
+      <c r="O106" s="52">
+        <v>10</v>
+      </c>
+      <c r="P106" s="52">
+        <v>9</v>
+      </c>
+      <c r="Q106" s="52"/>
+      <c r="R106" s="52">
+        <v>1500</v>
+      </c>
+      <c r="S106" s="52"/>
       <c r="T106" s="57"/>
-      <c r="U106" s="146">
-        <v>1685.96</v>
-      </c>
+      <c r="U106" s="131"/>
       <c r="V106" s="57"/>
     </row>
     <row r="107" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="57" t="s">
-        <v>338</v>
-      </c>
-      <c r="B107" s="57" t="s">
+      <c r="A107" s="128" t="s">
+        <v>340</v>
+      </c>
+      <c r="B107" s="128" t="s">
         <v>314</v>
       </c>
-      <c r="C107" s="1">
-        <f t="shared" si="4"/>
-        <v>1400.01</v>
-      </c>
-      <c r="D107" s="1">
-        <v>1800</v>
-      </c>
-      <c r="E107" s="1" t="s">
+      <c r="C107" s="52">
+        <f t="shared" si="5"/>
+        <v>2600.0100000000002</v>
+      </c>
+      <c r="D107" s="52">
+        <v>3600</v>
+      </c>
+      <c r="E107" s="52" t="s">
         <v>156</v>
       </c>
-      <c r="F107" s="1">
-        <v>6</v>
-      </c>
-      <c r="G107" s="1">
+      <c r="F107" s="52">
+        <v>5</v>
+      </c>
+      <c r="G107" s="52">
         <v>415</v>
       </c>
-      <c r="H107" s="1" t="s">
+      <c r="H107" s="52" t="s">
         <v>287</v>
       </c>
-      <c r="I107" s="1" t="s">
+      <c r="I107" s="52" t="s">
         <v>260</v>
       </c>
-      <c r="K107" s="1" t="s">
+      <c r="J107" s="52"/>
+      <c r="K107" s="52" t="s">
         <v>260</v>
       </c>
-      <c r="L107" s="1">
-        <v>60</v>
-      </c>
-      <c r="M107" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N107" s="1" t="s">
+      <c r="L107" s="52">
+        <v>80</v>
+      </c>
+      <c r="M107" s="52" t="s">
+        <v>55</v>
+      </c>
+      <c r="N107" s="52" t="s">
         <v>22</v>
       </c>
-      <c r="O107" s="1">
+      <c r="O107" s="52">
         <v>10</v>
       </c>
-      <c r="P107" s="1">
-        <v>7</v>
-      </c>
-      <c r="R107" s="1">
-        <v>3125</v>
-      </c>
-      <c r="S107" s="1" t="s">
-        <v>574</v>
-      </c>
-      <c r="T107" s="57" t="e" vm="1">
-        <v>#VALUE!</v>
-      </c>
+      <c r="P107" s="52">
+        <v>9</v>
+      </c>
+      <c r="Q107" s="52"/>
+      <c r="R107" s="52">
+        <v>2000</v>
+      </c>
+      <c r="S107" s="52"/>
+      <c r="T107" s="57"/>
       <c r="U107" s="131"/>
       <c r="V107" s="57"/>
     </row>
     <row r="108" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A108" s="128" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="B108" s="128" t="s">
         <v>314</v>
       </c>
       <c r="C108" s="52">
-        <f t="shared" ref="C108:C111" si="5">D107+0.01</f>
-        <v>1800.01</v>
+        <f t="shared" si="5"/>
+        <v>3600.01</v>
       </c>
       <c r="D108" s="52">
-        <v>2600</v>
+        <v>3600</v>
       </c>
       <c r="E108" s="52" t="s">
         <v>156</v>
       </c>
       <c r="F108" s="52">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G108" s="52">
         <v>415</v>
@@ -29500,11 +29507,11 @@
         <v>10</v>
       </c>
       <c r="P108" s="52">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q108" s="52"/>
       <c r="R108" s="52">
-        <v>1500</v>
+        <v>3000</v>
       </c>
       <c r="S108" s="52"/>
       <c r="T108" s="57"/>
@@ -29513,23 +29520,23 @@
     </row>
     <row r="109" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="128" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="B109" s="128" t="s">
         <v>314</v>
       </c>
       <c r="C109" s="52">
         <f t="shared" si="5"/>
-        <v>2600.0100000000002</v>
+        <v>3600.01</v>
       </c>
       <c r="D109" s="52">
-        <v>3600</v>
+        <v>4800</v>
       </c>
       <c r="E109" s="52" t="s">
         <v>156</v>
       </c>
       <c r="F109" s="52">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G109" s="52">
         <v>415</v>
@@ -29545,7 +29552,7 @@
         <v>260</v>
       </c>
       <c r="L109" s="52">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M109" s="52" t="s">
         <v>55</v>
@@ -29557,11 +29564,11 @@
         <v>10</v>
       </c>
       <c r="P109" s="52">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Q109" s="52"/>
       <c r="R109" s="52">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="S109" s="52"/>
       <c r="T109" s="57"/>
@@ -29570,23 +29577,23 @@
     </row>
     <row r="110" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A110" s="128" t="s">
-        <v>341</v>
+        <v>498</v>
       </c>
       <c r="B110" s="128" t="s">
         <v>314</v>
       </c>
       <c r="C110" s="52">
-        <f t="shared" si="5"/>
-        <v>3600.01</v>
+        <f t="shared" ref="C110" si="6">D109+0.01</f>
+        <v>4800.01</v>
       </c>
       <c r="D110" s="52">
-        <v>3600</v>
+        <v>5000</v>
       </c>
       <c r="E110" s="52" t="s">
         <v>156</v>
       </c>
       <c r="F110" s="52">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="G110" s="52">
         <v>415</v>
@@ -29602,7 +29609,7 @@
         <v>260</v>
       </c>
       <c r="L110" s="52">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="M110" s="52" t="s">
         <v>55</v>
@@ -29614,183 +29621,183 @@
         <v>10</v>
       </c>
       <c r="P110" s="52">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="Q110" s="52"/>
       <c r="R110" s="52">
-        <v>3000</v>
+        <v>2500</v>
       </c>
       <c r="S110" s="52"/>
       <c r="T110" s="57"/>
       <c r="U110" s="131"/>
       <c r="V110" s="57"/>
     </row>
-    <row r="111" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A111" s="128" t="s">
-        <v>342</v>
-      </c>
-      <c r="B111" s="128" t="s">
+    <row r="111" spans="1:22" s="107" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A111" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="B111" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="C111" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="D111" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="E111" s="105"/>
+      <c r="F111" s="105"/>
+      <c r="G111" s="105"/>
+      <c r="H111" s="106" t="s">
+        <v>467</v>
+      </c>
+      <c r="I111" s="105"/>
+      <c r="J111" s="105"/>
+      <c r="K111" s="105"/>
+      <c r="L111" s="105"/>
+      <c r="M111" s="105"/>
+      <c r="N111" s="106" t="s">
+        <v>467</v>
+      </c>
+      <c r="O111" s="108"/>
+      <c r="P111" s="105"/>
+      <c r="Q111" s="105"/>
+      <c r="R111" s="108"/>
+      <c r="S111" s="108"/>
+      <c r="U111" s="109"/>
+    </row>
+    <row r="112" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A112" s="3" t="s">
+        <v>343</v>
+      </c>
+      <c r="B112" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="C111" s="52">
-        <f t="shared" si="5"/>
-        <v>3600.01</v>
-      </c>
-      <c r="D111" s="52">
-        <v>4800</v>
-      </c>
-      <c r="E111" s="52" t="s">
+      <c r="C112" s="1">
+        <v>0</v>
+      </c>
+      <c r="D112" s="1">
+        <v>170</v>
+      </c>
+      <c r="E112" s="1" t="s">
         <v>156</v>
       </c>
-      <c r="F111" s="52">
-        <v>9</v>
-      </c>
-      <c r="G111" s="52">
-        <v>415</v>
-      </c>
-      <c r="H111" s="52" t="s">
+      <c r="F112" s="1">
+        <v>10</v>
+      </c>
+      <c r="G112" s="1">
+        <v>230</v>
+      </c>
+      <c r="H112" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I111" s="52" t="s">
+      <c r="I112" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="J111" s="52"/>
-      <c r="K111" s="52" t="s">
+      <c r="K112" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L111" s="52">
-        <v>100</v>
-      </c>
-      <c r="M111" s="52" t="s">
-        <v>55</v>
-      </c>
-      <c r="N111" s="52" t="s">
+      <c r="L112" s="1">
+        <v>30</v>
+      </c>
+      <c r="M112" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N112" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O111" s="52">
+      <c r="O112" s="1">
         <v>10</v>
       </c>
-      <c r="P111" s="52">
+      <c r="P112" s="1">
+        <v>8</v>
+      </c>
+      <c r="R112" s="1">
+        <v>400</v>
+      </c>
+      <c r="S112" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="U112" s="80">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A113" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>314</v>
+      </c>
+      <c r="C113" s="1">
+        <f>D112+0.01</f>
+        <v>170.01</v>
+      </c>
+      <c r="D113" s="1">
+        <v>250</v>
+      </c>
+      <c r="E113" s="1" t="s">
+        <v>156</v>
+      </c>
+      <c r="F113" s="1">
         <v>10</v>
       </c>
-      <c r="Q111" s="52"/>
-      <c r="R111" s="52">
-        <v>3000</v>
-      </c>
-      <c r="S111" s="52"/>
-      <c r="T111" s="57"/>
-      <c r="U111" s="131"/>
-      <c r="V111" s="57"/>
-    </row>
-    <row r="112" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="128" t="s">
-        <v>498</v>
-      </c>
-      <c r="B112" s="128" t="s">
-        <v>314</v>
-      </c>
-      <c r="C112" s="52">
-        <f t="shared" ref="C112" si="6">D111+0.01</f>
-        <v>4800.01</v>
-      </c>
-      <c r="D112" s="52">
-        <v>5000</v>
-      </c>
-      <c r="E112" s="52" t="s">
-        <v>156</v>
-      </c>
-      <c r="F112" s="52">
-        <v>5</v>
-      </c>
-      <c r="G112" s="52">
-        <v>415</v>
-      </c>
-      <c r="H112" s="52" t="s">
+      <c r="G113" s="1">
+        <v>230</v>
+      </c>
+      <c r="H113" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="I112" s="52" t="s">
+      <c r="I113" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="J112" s="52"/>
-      <c r="K112" s="52" t="s">
+      <c r="K113" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L112" s="52">
-        <v>100</v>
-      </c>
-      <c r="M112" s="52" t="s">
-        <v>55</v>
-      </c>
-      <c r="N112" s="52" t="s">
+      <c r="L113" s="1">
+        <v>30</v>
+      </c>
+      <c r="M113" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N113" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O112" s="52">
+      <c r="O113" s="1">
         <v>10</v>
       </c>
-      <c r="P112" s="52">
-        <v>9</v>
-      </c>
-      <c r="Q112" s="52"/>
-      <c r="R112" s="52">
-        <v>2500</v>
-      </c>
-      <c r="S112" s="52"/>
-      <c r="T112" s="57"/>
-      <c r="U112" s="131"/>
-      <c r="V112" s="57"/>
-    </row>
-    <row r="113" spans="1:21" s="107" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A113" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="B113" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="C113" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="D113" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="E113" s="105"/>
-      <c r="F113" s="105"/>
-      <c r="G113" s="105"/>
-      <c r="H113" s="106" t="s">
-        <v>467</v>
-      </c>
-      <c r="I113" s="105"/>
-      <c r="J113" s="105"/>
-      <c r="K113" s="105"/>
-      <c r="L113" s="105"/>
-      <c r="M113" s="105"/>
-      <c r="N113" s="106" t="s">
-        <v>467</v>
-      </c>
-      <c r="O113" s="108"/>
-      <c r="P113" s="105"/>
-      <c r="Q113" s="105"/>
-      <c r="R113" s="108"/>
-      <c r="S113" s="108"/>
-      <c r="U113" s="109"/>
+      <c r="P113" s="1">
+        <v>12</v>
+      </c>
+      <c r="R113" s="1">
+        <v>400</v>
+      </c>
+      <c r="S113" s="1" t="s">
+        <v>346</v>
+      </c>
+      <c r="U113" s="80">
+        <v>474</v>
+      </c>
     </row>
     <row r="114" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A114" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B114" s="3" t="s">
         <v>314</v>
       </c>
       <c r="C114" s="1">
-        <v>0</v>
+        <f>D113+0.01</f>
+        <v>250.01</v>
       </c>
       <c r="D114" s="1">
-        <v>170</v>
+        <v>250</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F114" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G114" s="1">
         <v>230</v>
@@ -29814,40 +29821,40 @@
         <v>22</v>
       </c>
       <c r="O114" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="P114" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R114" s="1">
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="S114" s="1" t="s">
-        <v>344</v>
-      </c>
-      <c r="U114" s="80">
-        <v>418</v>
+        <v>348</v>
+      </c>
+      <c r="T114" t="e" vm="2">
+        <v>#VALUE!</v>
       </c>
     </row>
     <row r="115" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A115" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="B115" s="3" t="s">
         <v>314</v>
       </c>
       <c r="C115" s="1">
         <f>D114+0.01</f>
-        <v>170.01</v>
+        <v>250.01</v>
       </c>
       <c r="D115" s="1">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F115" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G115" s="1">
         <v>230</v>
@@ -29862,7 +29869,7 @@
         <v>260</v>
       </c>
       <c r="L115" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M115" s="1" t="s">
         <v>55</v>
@@ -29871,97 +29878,71 @@
         <v>22</v>
       </c>
       <c r="O115" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="P115" s="1">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="R115" s="1">
-        <v>400</v>
+        <v>750</v>
       </c>
       <c r="S115" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="U115" s="80">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="116" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A116" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="B116" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="U115" s="92"/>
+    </row>
+    <row r="116" spans="1:21" s="107" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A116" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="B116" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="C116" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="D116" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="E116" s="105"/>
+      <c r="F116" s="105"/>
+      <c r="G116" s="105"/>
+      <c r="H116" s="106" t="s">
+        <v>467</v>
+      </c>
+      <c r="I116" s="105"/>
+      <c r="J116" s="105"/>
+      <c r="K116" s="105"/>
+      <c r="L116" s="105"/>
+      <c r="M116" s="105"/>
+      <c r="N116" s="106" t="s">
+        <v>467</v>
+      </c>
+      <c r="O116" s="108"/>
+      <c r="P116" s="105"/>
+      <c r="Q116" s="105"/>
+      <c r="R116" s="108"/>
+      <c r="S116" s="108"/>
+      <c r="U116" s="109"/>
+    </row>
+    <row r="117" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A117" s="57" t="s">
+        <v>351</v>
+      </c>
+      <c r="B117" s="57" t="s">
         <v>314</v>
       </c>
-      <c r="C116" s="1">
-        <f>D115+0.01</f>
-        <v>250.01</v>
-      </c>
-      <c r="D116" s="1">
+      <c r="C117" s="1">
+        <v>0</v>
+      </c>
+      <c r="D117" s="1">
         <v>250</v>
       </c>
-      <c r="E116" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F116" s="1">
-        <v>15</v>
-      </c>
-      <c r="G116" s="1">
-        <v>230</v>
-      </c>
-      <c r="H116" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="I116" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K116" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="L116" s="1">
-        <v>30</v>
-      </c>
-      <c r="M116" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N116" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O116" s="1">
-        <v>20</v>
-      </c>
-      <c r="P116" s="1">
-        <v>7</v>
-      </c>
-      <c r="R116" s="1">
-        <v>550</v>
-      </c>
-      <c r="S116" s="1" t="s">
-        <v>348</v>
-      </c>
-      <c r="T116" t="e" vm="2">
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="117" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="B117" s="3" t="s">
-        <v>314</v>
-      </c>
-      <c r="C117" s="1">
-        <f>D116+0.01</f>
-        <v>250.01</v>
-      </c>
-      <c r="D117" s="1">
-        <v>450</v>
-      </c>
       <c r="E117" s="1" t="s">
-        <v>156</v>
+        <v>352</v>
       </c>
       <c r="F117" s="1">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="G117" s="1">
         <v>230</v>
@@ -29975,8 +29956,8 @@
       <c r="K117" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L117" s="1">
-        <v>40</v>
+      <c r="L117" s="1" t="s">
+        <v>414</v>
       </c>
       <c r="M117" s="1" t="s">
         <v>55</v>
@@ -29988,68 +29969,89 @@
         <v>20</v>
       </c>
       <c r="P117" s="1">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="R117" s="1">
         <v>750</v>
       </c>
-      <c r="S117" s="1" t="s">
-        <v>350</v>
-      </c>
-      <c r="U117" s="92"/>
-    </row>
-    <row r="118" spans="1:21" s="107" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A118" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="B118" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="C118" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="D118" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="E118" s="105"/>
-      <c r="F118" s="105"/>
-      <c r="G118" s="105"/>
-      <c r="H118" s="106" t="s">
-        <v>467</v>
-      </c>
-      <c r="I118" s="105"/>
-      <c r="J118" s="105"/>
-      <c r="K118" s="105"/>
-      <c r="L118" s="105"/>
-      <c r="M118" s="105"/>
-      <c r="N118" s="106" t="s">
-        <v>467</v>
-      </c>
-      <c r="O118" s="108"/>
-      <c r="P118" s="105"/>
-      <c r="Q118" s="105"/>
-      <c r="R118" s="108"/>
-      <c r="S118" s="108"/>
-      <c r="U118" s="109"/>
+      <c r="S117" s="1"/>
+    </row>
+    <row r="118" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A118" s="57" t="s">
+        <v>353</v>
+      </c>
+      <c r="B118" s="57" t="s">
+        <v>314</v>
+      </c>
+      <c r="C118" s="1">
+        <f>D117+0.01</f>
+        <v>250.01</v>
+      </c>
+      <c r="D118" s="1">
+        <v>400</v>
+      </c>
+      <c r="E118" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="F118" s="1">
+        <v>40</v>
+      </c>
+      <c r="G118" s="1">
+        <v>230</v>
+      </c>
+      <c r="H118" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I118" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K118" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="L118" s="1">
+        <v>40</v>
+      </c>
+      <c r="M118" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N118" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O118" s="1">
+        <v>20</v>
+      </c>
+      <c r="P118" s="1">
+        <v>8</v>
+      </c>
+      <c r="R118" s="1">
+        <v>750</v>
+      </c>
+      <c r="S118" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="U118" s="80">
+        <v>1481.78</v>
+      </c>
     </row>
     <row r="119" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A119" s="57" t="s">
-        <v>351</v>
+      <c r="A119" s="3" t="s">
+        <v>355</v>
       </c>
       <c r="B119" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C119" s="1">
-        <v>0</v>
+        <f>D118+0.01</f>
+        <v>400.01</v>
       </c>
       <c r="D119" s="1">
-        <v>250</v>
+        <v>550</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>352</v>
       </c>
       <c r="F119" s="1">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="G119" s="1">
         <v>230</v>
@@ -30063,8 +30065,8 @@
       <c r="K119" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L119" s="1" t="s">
-        <v>414</v>
+      <c r="L119" s="1">
+        <v>40</v>
       </c>
       <c r="M119" s="1" t="s">
         <v>55</v>
@@ -30084,24 +30086,24 @@
       <c r="S119" s="1"/>
     </row>
     <row r="120" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A120" s="57" t="s">
-        <v>353</v>
+      <c r="A120" s="3" t="s">
+        <v>356</v>
       </c>
       <c r="B120" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C120" s="1">
         <f>D119+0.01</f>
-        <v>250.01</v>
+        <v>550.01</v>
       </c>
       <c r="D120" s="1">
-        <v>400</v>
+        <v>750</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>352</v>
       </c>
       <c r="F120" s="1">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="G120" s="1">
         <v>230</v>
@@ -30116,7 +30118,7 @@
         <v>260</v>
       </c>
       <c r="L120" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="M120" s="1" t="s">
         <v>55</v>
@@ -30133,87 +30135,66 @@
       <c r="R120" s="1">
         <v>750</v>
       </c>
-      <c r="S120" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="U120" s="80">
-        <v>1481.78</v>
-      </c>
-    </row>
-    <row r="121" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A121" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="B121" s="57" t="s">
-        <v>314</v>
-      </c>
-      <c r="C121" s="1">
-        <f>D120+0.01</f>
-        <v>400.01</v>
-      </c>
-      <c r="D121" s="1">
-        <v>550</v>
-      </c>
-      <c r="E121" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F121" s="1">
-        <v>20</v>
-      </c>
-      <c r="G121" s="1">
-        <v>230</v>
-      </c>
-      <c r="H121" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="I121" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K121" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="L121" s="1">
-        <v>40</v>
-      </c>
-      <c r="M121" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N121" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O121" s="1">
-        <v>20</v>
-      </c>
-      <c r="P121" s="1">
-        <v>8</v>
-      </c>
-      <c r="R121" s="1">
-        <v>750</v>
-      </c>
-      <c r="S121" s="1"/>
+      <c r="S120" s="1"/>
+      <c r="U120" s="146">
+        <v>2614.38</v>
+      </c>
+    </row>
+    <row r="121" spans="1:21" s="107" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A121" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="B121" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="C121" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="D121" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="E121" s="105"/>
+      <c r="F121" s="105"/>
+      <c r="G121" s="105"/>
+      <c r="H121" s="106" t="s">
+        <v>467</v>
+      </c>
+      <c r="I121" s="105"/>
+      <c r="J121" s="105"/>
+      <c r="K121" s="105"/>
+      <c r="L121" s="105"/>
+      <c r="M121" s="105"/>
+      <c r="N121" s="106" t="s">
+        <v>467</v>
+      </c>
+      <c r="O121" s="108"/>
+      <c r="P121" s="105"/>
+      <c r="Q121" s="105"/>
+      <c r="R121" s="108"/>
+      <c r="S121" s="108"/>
+      <c r="U121" s="109"/>
     </row>
     <row r="122" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A122" s="3" t="s">
-        <v>356</v>
+      <c r="A122" s="57" t="s">
+        <v>501</v>
       </c>
       <c r="B122" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C122" s="1">
-        <f>D121+0.01</f>
-        <v>550.01</v>
+        <v>0.01</v>
       </c>
       <c r="D122" s="1">
-        <v>750</v>
+        <v>250</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>352</v>
       </c>
       <c r="F122" s="1">
-        <v>20</v>
+        <v>80</v>
       </c>
       <c r="G122" s="1">
-        <v>230</v>
+        <v>415</v>
       </c>
       <c r="H122" s="1" t="s">
         <v>287</v>
@@ -30224,8 +30205,8 @@
       <c r="K122" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L122" s="1">
-        <v>55</v>
+      <c r="L122" s="1" t="s">
+        <v>502</v>
       </c>
       <c r="M122" s="1" t="s">
         <v>55</v>
@@ -30237,68 +30218,83 @@
         <v>20</v>
       </c>
       <c r="P122" s="1">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="R122" s="1">
-        <v>750</v>
+        <v>1500</v>
       </c>
       <c r="S122" s="1"/>
-      <c r="U122" s="146">
-        <v>2614.38</v>
-      </c>
-    </row>
-    <row r="123" spans="1:21" s="107" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A123" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="B123" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="C123" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="D123" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="E123" s="105"/>
-      <c r="F123" s="105"/>
-      <c r="G123" s="105"/>
-      <c r="H123" s="106" t="s">
-        <v>467</v>
-      </c>
-      <c r="I123" s="105"/>
-      <c r="J123" s="105"/>
-      <c r="K123" s="105"/>
-      <c r="L123" s="105"/>
-      <c r="M123" s="105"/>
-      <c r="N123" s="106" t="s">
-        <v>467</v>
-      </c>
-      <c r="O123" s="108"/>
-      <c r="P123" s="105"/>
-      <c r="Q123" s="105"/>
-      <c r="R123" s="108"/>
-      <c r="S123" s="108"/>
-      <c r="U123" s="109"/>
+    </row>
+    <row r="123" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A123" s="57" t="s">
+        <v>496</v>
+      </c>
+      <c r="B123" s="57" t="s">
+        <v>314</v>
+      </c>
+      <c r="C123" s="1">
+        <v>0.01</v>
+      </c>
+      <c r="D123" s="1">
+        <v>250</v>
+      </c>
+      <c r="E123" s="1" t="s">
+        <v>352</v>
+      </c>
+      <c r="F123" s="1">
+        <v>80</v>
+      </c>
+      <c r="G123" s="1">
+        <v>415</v>
+      </c>
+      <c r="H123" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I123" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K123" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="L123" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="M123" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N123" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O123" s="1">
+        <v>20</v>
+      </c>
+      <c r="P123" s="1">
+        <v>26</v>
+      </c>
+      <c r="R123" s="1">
+        <v>1500</v>
+      </c>
+      <c r="S123" s="1"/>
     </row>
     <row r="124" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A124" s="57" t="s">
-        <v>501</v>
+        <v>353</v>
       </c>
       <c r="B124" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C124" s="1">
-        <v>0.01</v>
+        <f t="shared" ref="C124:C132" si="7">D123+0.01</f>
+        <v>250.01</v>
       </c>
       <c r="D124" s="1">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>352</v>
       </c>
       <c r="F124" s="1">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G124" s="1">
         <v>415</v>
@@ -30312,8 +30308,8 @@
       <c r="K124" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L124" s="1" t="s">
-        <v>502</v>
+      <c r="L124" s="1">
+        <v>40</v>
       </c>
       <c r="M124" s="1" t="s">
         <v>55</v>
@@ -30325,7 +30321,7 @@
         <v>20</v>
       </c>
       <c r="P124" s="1">
-        <v>26</v>
+        <v>17</v>
       </c>
       <c r="R124" s="1">
         <v>1500</v>
@@ -30334,22 +30330,23 @@
     </row>
     <row r="125" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A125" s="57" t="s">
-        <v>496</v>
+        <v>357</v>
       </c>
       <c r="B125" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C125" s="1">
-        <v>0.01</v>
+        <f t="shared" si="7"/>
+        <v>400.01</v>
       </c>
       <c r="D125" s="1">
-        <v>250</v>
+        <v>450</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>352</v>
       </c>
       <c r="F125" s="1">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="G125" s="1">
         <v>415</v>
@@ -30363,8 +30360,8 @@
       <c r="K125" s="1" t="s">
         <v>260</v>
       </c>
-      <c r="L125" s="1" t="s">
-        <v>414</v>
+      <c r="L125" s="1">
+        <v>40</v>
       </c>
       <c r="M125" s="1" t="s">
         <v>55</v>
@@ -30376,7 +30373,7 @@
         <v>20</v>
       </c>
       <c r="P125" s="1">
-        <v>26</v>
+        <v>11</v>
       </c>
       <c r="R125" s="1">
         <v>1500</v>
@@ -30385,23 +30382,23 @@
     </row>
     <row r="126" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A126" s="57" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="B126" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C126" s="1">
-        <f t="shared" ref="C126:C134" si="7">D125+0.01</f>
-        <v>250.01</v>
+        <f t="shared" si="7"/>
+        <v>450.01</v>
       </c>
       <c r="D126" s="1">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>352</v>
       </c>
       <c r="F126" s="1">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="G126" s="1">
         <v>415</v>
@@ -30416,7 +30413,7 @@
         <v>260</v>
       </c>
       <c r="L126" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="M126" s="1" t="s">
         <v>55</v>
@@ -30428,32 +30425,32 @@
         <v>20</v>
       </c>
       <c r="P126" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="R126" s="1">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="S126" s="1"/>
     </row>
     <row r="127" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A127" s="57" t="s">
-        <v>357</v>
+      <c r="A127" s="3" t="s">
+        <v>355</v>
       </c>
       <c r="B127" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C127" s="1">
         <f t="shared" si="7"/>
-        <v>400.01</v>
+        <v>500.01</v>
       </c>
       <c r="D127" s="1">
-        <v>450</v>
+        <v>550</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>352</v>
       </c>
       <c r="F127" s="1">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="G127" s="1">
         <v>415</v>
@@ -30480,32 +30477,35 @@
         <v>20</v>
       </c>
       <c r="P127" s="1">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R127" s="1">
         <v>1500</v>
       </c>
       <c r="S127" s="1"/>
+      <c r="U127" s="147">
+        <v>2021.94</v>
+      </c>
     </row>
     <row r="128" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A128" s="57" t="s">
-        <v>358</v>
+      <c r="A128" s="3" t="s">
+        <v>359</v>
       </c>
       <c r="B128" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C128" s="1">
         <f t="shared" si="7"/>
-        <v>450.01</v>
+        <v>550.01</v>
       </c>
       <c r="D128" s="1">
-        <v>500</v>
+        <v>550</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>352</v>
       </c>
       <c r="F128" s="1">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="G128" s="1">
         <v>415</v>
@@ -30520,7 +30520,7 @@
         <v>260</v>
       </c>
       <c r="L128" s="1">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="M128" s="1" t="s">
         <v>55</v>
@@ -30532,7 +30532,7 @@
         <v>20</v>
       </c>
       <c r="P128" s="1">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="R128" s="1">
         <v>4500</v>
@@ -30541,17 +30541,17 @@
     </row>
     <row r="129" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A129" s="3" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="B129" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C129" s="1">
         <f t="shared" si="7"/>
-        <v>500.01</v>
+        <v>550.01</v>
       </c>
       <c r="D129" s="1">
-        <v>550</v>
+        <v>750</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>352</v>
@@ -30572,7 +30572,7 @@
         <v>260</v>
       </c>
       <c r="L129" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="M129" s="1" t="s">
         <v>55</v>
@@ -30581,38 +30581,35 @@
         <v>22</v>
       </c>
       <c r="O129" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="P129" s="1">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="R129" s="1">
         <v>1500</v>
       </c>
       <c r="S129" s="1"/>
-      <c r="U129" s="147">
-        <v>2021.94</v>
-      </c>
     </row>
     <row r="130" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="3" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B130" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C130" s="1">
         <f t="shared" si="7"/>
-        <v>550.01</v>
+        <v>750.01</v>
       </c>
       <c r="D130" s="1">
-        <v>550</v>
+        <v>750</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>352</v>
       </c>
       <c r="F130" s="1">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G130" s="1">
         <v>415</v>
@@ -30627,7 +30624,7 @@
         <v>260</v>
       </c>
       <c r="L130" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="M130" s="1" t="s">
         <v>55</v>
@@ -30645,26 +30642,29 @@
         <v>4500</v>
       </c>
       <c r="S130" s="1"/>
+      <c r="U130" s="146">
+        <v>2676</v>
+      </c>
     </row>
     <row r="131" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="3" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="B131" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C131" s="1">
         <f t="shared" si="7"/>
-        <v>550.01</v>
+        <v>750.01</v>
       </c>
       <c r="D131" s="1">
-        <v>750</v>
+        <v>1000</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>352</v>
       </c>
       <c r="F131" s="1">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="G131" s="1">
         <v>415</v>
@@ -30688,35 +30688,35 @@
         <v>22</v>
       </c>
       <c r="O131" s="1">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="P131" s="1">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="R131" s="1">
-        <v>1500</v>
+        <v>4500</v>
       </c>
       <c r="S131" s="1"/>
     </row>
     <row r="132" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="3" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B132" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C132" s="1">
         <f t="shared" si="7"/>
-        <v>750.01</v>
+        <v>1000.01</v>
       </c>
       <c r="D132" s="1">
-        <v>750</v>
+        <v>1400</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>352</v>
       </c>
       <c r="F132" s="1">
-        <v>45</v>
+        <v>20</v>
       </c>
       <c r="G132" s="1">
         <v>415</v>
@@ -30743,35 +30743,32 @@
         <v>20</v>
       </c>
       <c r="P132" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R132" s="1">
         <v>4500</v>
       </c>
       <c r="S132" s="1"/>
-      <c r="U132" s="146">
-        <v>2676</v>
-      </c>
     </row>
     <row r="133" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="3" t="s">
-        <v>361</v>
+        <v>495</v>
       </c>
       <c r="B133" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C133" s="1">
-        <f t="shared" si="7"/>
-        <v>750.01</v>
+        <f t="shared" ref="C133" si="8">D132+0.01</f>
+        <v>1400.01</v>
       </c>
       <c r="D133" s="1">
-        <v>1000</v>
+        <v>1800</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>352</v>
       </c>
       <c r="F133" s="1">
-        <v>30</v>
+        <v>12</v>
       </c>
       <c r="G133" s="1">
         <v>415</v>
@@ -30786,7 +30783,7 @@
         <v>260</v>
       </c>
       <c r="L133" s="1">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="M133" s="1" t="s">
         <v>55</v>
@@ -30795,10 +30792,10 @@
         <v>22</v>
       </c>
       <c r="O133" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="P133" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="R133" s="1">
         <v>4500</v>
@@ -30807,23 +30804,23 @@
     </row>
     <row r="134" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="3" t="s">
-        <v>362</v>
+        <v>504</v>
       </c>
       <c r="B134" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C134" s="1">
-        <f t="shared" si="7"/>
-        <v>1000.01</v>
+        <f t="shared" ref="C134" si="9">D133+0.01</f>
+        <v>1800.01</v>
       </c>
       <c r="D134" s="1">
-        <v>1400</v>
+        <v>2600</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>352</v>
       </c>
       <c r="F134" s="1">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G134" s="1">
         <v>415</v>
@@ -30838,7 +30835,7 @@
         <v>260</v>
       </c>
       <c r="L134" s="1">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="M134" s="1" t="s">
         <v>55</v>
@@ -30847,10 +30844,10 @@
         <v>22</v>
       </c>
       <c r="O134" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="P134" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R134" s="1">
         <v>4500</v>
@@ -30859,17 +30856,17 @@
     </row>
     <row r="135" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A135" s="3" t="s">
-        <v>495</v>
+        <v>505</v>
       </c>
       <c r="B135" s="57" t="s">
         <v>314</v>
       </c>
       <c r="C135" s="1">
-        <f t="shared" ref="C135" si="8">D134+0.01</f>
-        <v>1400.01</v>
+        <f t="shared" ref="C135" si="10">D134+0.01</f>
+        <v>2600.0100000000002</v>
       </c>
       <c r="D135" s="1">
-        <v>1800</v>
+        <v>3600</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>352</v>
@@ -30890,7 +30887,7 @@
         <v>260</v>
       </c>
       <c r="L135" s="1">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="M135" s="1" t="s">
         <v>55</v>
@@ -30902,84 +30899,65 @@
         <v>10</v>
       </c>
       <c r="P135" s="1">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="R135" s="1">
         <v>4500</v>
       </c>
       <c r="S135" s="1"/>
     </row>
-    <row r="136" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A136" s="3" t="s">
-        <v>504</v>
-      </c>
-      <c r="B136" s="57" t="s">
-        <v>314</v>
-      </c>
-      <c r="C136" s="1">
-        <f t="shared" ref="C136" si="9">D135+0.01</f>
-        <v>1800.01</v>
-      </c>
-      <c r="D136" s="1">
-        <v>2600</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F136" s="1">
-        <v>12</v>
-      </c>
-      <c r="G136" s="1">
-        <v>415</v>
-      </c>
-      <c r="H136" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="I136" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K136" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="L136" s="1">
-        <v>80</v>
-      </c>
-      <c r="M136" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N136" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O136" s="1">
-        <v>10</v>
-      </c>
-      <c r="P136" s="1">
-        <v>11</v>
-      </c>
-      <c r="R136" s="1">
-        <v>4500</v>
-      </c>
-      <c r="S136" s="1"/>
+    <row r="136" spans="1:21" s="107" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A136" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="B136" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="C136" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="D136" s="104" t="s">
+        <v>268</v>
+      </c>
+      <c r="E136" s="105"/>
+      <c r="F136" s="105"/>
+      <c r="G136" s="105"/>
+      <c r="H136" s="106" t="s">
+        <v>467</v>
+      </c>
+      <c r="I136" s="105"/>
+      <c r="J136" s="105"/>
+      <c r="K136" s="105"/>
+      <c r="L136" s="105"/>
+      <c r="M136" s="105"/>
+      <c r="N136" s="106" t="s">
+        <v>467</v>
+      </c>
+      <c r="O136" s="108"/>
+      <c r="P136" s="105"/>
+      <c r="Q136" s="105"/>
+      <c r="R136" s="108"/>
+      <c r="S136" s="108"/>
+      <c r="U136" s="109"/>
     </row>
     <row r="137" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="3" t="s">
-        <v>505</v>
-      </c>
-      <c r="B137" s="57" t="s">
+        <v>363</v>
+      </c>
+      <c r="B137" t="s">
         <v>314</v>
       </c>
       <c r="C137" s="1">
-        <f t="shared" ref="C137" si="10">D136+0.01</f>
-        <v>2600.0100000000002</v>
-      </c>
-      <c r="D137" s="1">
-        <v>3600</v>
+        <v>0.01</v>
+      </c>
+      <c r="D137" s="6">
+        <v>250</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>352</v>
-      </c>
-      <c r="F137" s="1">
-        <v>12</v>
+        <v>364</v>
+      </c>
+      <c r="F137" s="6">
+        <v>15</v>
       </c>
       <c r="G137" s="1">
         <v>415</v>
@@ -30994,7 +30972,7 @@
         <v>260</v>
       </c>
       <c r="L137" s="1">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="M137" s="1" t="s">
         <v>55</v>
@@ -31002,63 +30980,86 @@
       <c r="N137" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="O137" s="1">
-        <v>10</v>
+      <c r="O137" s="6">
+        <v>20</v>
       </c>
       <c r="P137" s="1">
         <v>11</v>
       </c>
-      <c r="R137" s="1">
-        <v>4500</v>
-      </c>
-      <c r="S137" s="1"/>
-    </row>
-    <row r="138" spans="1:21" s="107" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A138" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="B138" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="C138" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="D138" s="104" t="s">
-        <v>268</v>
-      </c>
-      <c r="E138" s="105"/>
-      <c r="F138" s="105"/>
-      <c r="G138" s="105"/>
-      <c r="H138" s="106" t="s">
-        <v>467</v>
-      </c>
-      <c r="I138" s="105"/>
-      <c r="J138" s="105"/>
-      <c r="K138" s="105"/>
-      <c r="L138" s="105"/>
-      <c r="M138" s="105"/>
-      <c r="N138" s="106" t="s">
-        <v>467</v>
-      </c>
-      <c r="O138" s="108"/>
-      <c r="P138" s="105"/>
-      <c r="Q138" s="105"/>
-      <c r="R138" s="108"/>
-      <c r="S138" s="108"/>
-      <c r="U138" s="109"/>
+      <c r="R137" s="6">
+        <v>510</v>
+      </c>
+      <c r="S137" s="6" t="s">
+        <v>365</v>
+      </c>
+      <c r="U137" s="80">
+        <v>624.37</v>
+      </c>
+    </row>
+    <row r="138" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A138" s="3" t="s">
+        <v>499</v>
+      </c>
+      <c r="B138" t="s">
+        <v>314</v>
+      </c>
+      <c r="C138" s="1">
+        <f>D137+0.01</f>
+        <v>250.01</v>
+      </c>
+      <c r="D138" s="6">
+        <v>250</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>364</v>
+      </c>
+      <c r="F138" s="6">
+        <v>24</v>
+      </c>
+      <c r="G138" s="1">
+        <v>415</v>
+      </c>
+      <c r="H138" s="1" t="s">
+        <v>287</v>
+      </c>
+      <c r="I138" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="K138" s="1" t="s">
+        <v>260</v>
+      </c>
+      <c r="L138" s="1">
+        <v>30</v>
+      </c>
+      <c r="M138" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="N138" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="O138" s="6">
+        <v>20</v>
+      </c>
+      <c r="P138" s="1">
+        <v>11</v>
+      </c>
+      <c r="R138" s="6">
+        <v>850</v>
+      </c>
     </row>
     <row r="139" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="3" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="B139" t="s">
         <v>314</v>
       </c>
       <c r="C139" s="1">
-        <v>0.01</v>
+        <f t="shared" ref="C139:C145" si="11">D138+0.01</f>
+        <v>250.01</v>
       </c>
       <c r="D139" s="6">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>364</v>
@@ -31079,7 +31080,7 @@
         <v>260</v>
       </c>
       <c r="L139" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M139" s="1" t="s">
         <v>55</v>
@@ -31094,28 +31095,22 @@
         <v>11</v>
       </c>
       <c r="R139" s="6">
-        <v>510</v>
-      </c>
-      <c r="S139" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="U139" s="80">
-        <v>624.37</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="140" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="3" t="s">
-        <v>499</v>
+        <v>367</v>
       </c>
       <c r="B140" t="s">
         <v>314</v>
       </c>
       <c r="C140" s="1">
-        <f>D139+0.01</f>
-        <v>250.01</v>
+        <f t="shared" si="11"/>
+        <v>400.01</v>
       </c>
       <c r="D140" s="6">
-        <v>250</v>
+        <v>400</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>364</v>
@@ -31136,7 +31131,7 @@
         <v>260</v>
       </c>
       <c r="L140" s="1">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="M140" s="1" t="s">
         <v>55</v>
@@ -31151,22 +31146,22 @@
         <v>11</v>
       </c>
       <c r="R140" s="6">
-        <v>850</v>
+        <v>1100</v>
       </c>
     </row>
     <row r="141" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A141" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="B141" t="s">
         <v>314</v>
       </c>
       <c r="C141" s="1">
-        <f t="shared" ref="C141:C147" si="11">D140+0.01</f>
-        <v>250.01</v>
+        <f t="shared" si="11"/>
+        <v>400.01</v>
       </c>
       <c r="D141" s="6">
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>364</v>
@@ -31199,7 +31194,7 @@
         <v>20</v>
       </c>
       <c r="P141" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="R141" s="6">
         <v>1100</v>
@@ -31207,17 +31202,17 @@
     </row>
     <row r="142" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A142" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="B142" t="s">
         <v>314</v>
       </c>
       <c r="C142" s="1">
         <f t="shared" si="11"/>
-        <v>400.01</v>
+        <v>550.01</v>
       </c>
       <c r="D142" s="6">
-        <v>400</v>
+        <v>550</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>364</v>
@@ -31238,7 +31233,7 @@
         <v>260</v>
       </c>
       <c r="L142" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="M142" s="1" t="s">
         <v>55</v>
@@ -31253,28 +31248,28 @@
         <v>11</v>
       </c>
       <c r="R142" s="6">
-        <v>1100</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="143" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A143" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B143" t="s">
         <v>314</v>
       </c>
       <c r="C143" s="1">
         <f t="shared" si="11"/>
-        <v>400.01</v>
+        <v>550.01</v>
       </c>
       <c r="D143" s="6">
-        <v>550</v>
+        <v>750</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F143" s="6">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="G143" s="1">
         <v>415</v>
@@ -31289,7 +31284,7 @@
         <v>260</v>
       </c>
       <c r="L143" s="1">
-        <v>40</v>
+        <v>55</v>
       </c>
       <c r="M143" s="1" t="s">
         <v>55</v>
@@ -31301,25 +31296,25 @@
         <v>20</v>
       </c>
       <c r="P143" s="1">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="R143" s="6">
-        <v>1100</v>
+        <v>2000</v>
       </c>
     </row>
     <row r="144" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="B144" t="s">
         <v>314</v>
       </c>
       <c r="C144" s="1">
         <f t="shared" si="11"/>
-        <v>550.01</v>
+        <v>750.01</v>
       </c>
       <c r="D144" s="6">
-        <v>550</v>
+        <v>1000</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>364</v>
@@ -31355,28 +31350,28 @@
         <v>11</v>
       </c>
       <c r="R144" s="6">
-        <v>1500</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="145" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A145" s="3" t="s">
-        <v>370</v>
+        <v>500</v>
       </c>
       <c r="B145" t="s">
         <v>314</v>
       </c>
       <c r="C145" s="1">
         <f t="shared" si="11"/>
-        <v>550.01</v>
+        <v>1000.01</v>
       </c>
       <c r="D145" s="6">
-        <v>750</v>
+        <v>1200</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>364</v>
       </c>
       <c r="F145" s="6">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="G145" s="1">
         <v>415</v>
@@ -31403,125 +31398,25 @@
         <v>20</v>
       </c>
       <c r="P145" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="R145" s="6">
-        <v>2000</v>
+        <v>3000</v>
       </c>
     </row>
     <row r="146" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A146" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="B146" t="s">
-        <v>314</v>
-      </c>
-      <c r="C146" s="1">
-        <f t="shared" si="11"/>
-        <v>750.01</v>
-      </c>
-      <c r="D146" s="6">
-        <v>1000</v>
-      </c>
-      <c r="E146" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="F146" s="6">
-        <v>24</v>
-      </c>
-      <c r="G146" s="1">
-        <v>415</v>
-      </c>
-      <c r="H146" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="I146" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K146" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="L146" s="1">
-        <v>55</v>
-      </c>
-      <c r="M146" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N146" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O146" s="6">
-        <v>20</v>
-      </c>
-      <c r="P146" s="1">
-        <v>11</v>
-      </c>
-      <c r="R146" s="6">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="147" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A147" s="3" t="s">
-        <v>500</v>
-      </c>
-      <c r="B147" t="s">
-        <v>314</v>
-      </c>
-      <c r="C147" s="1">
-        <f t="shared" si="11"/>
-        <v>1000.01</v>
-      </c>
-      <c r="D147" s="6">
-        <v>1200</v>
-      </c>
-      <c r="E147" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="F147" s="6">
-        <v>12</v>
-      </c>
-      <c r="G147" s="1">
-        <v>415</v>
-      </c>
-      <c r="H147" s="1" t="s">
-        <v>287</v>
-      </c>
-      <c r="I147" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K147" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="L147" s="1">
-        <v>55</v>
-      </c>
-      <c r="M147" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="N147" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O147" s="6">
-        <v>20</v>
-      </c>
-      <c r="P147" s="1">
-        <v>10</v>
-      </c>
-      <c r="R147" s="6">
-        <v>3000</v>
-      </c>
-    </row>
-    <row r="148" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A148" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="C148" s="3" t="s">
+      <c r="C146" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="D148" s="3" t="s">
+      <c r="D146" s="3" t="s">
         <v>268</v>
       </c>
     </row>
+    <row r="147" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="148" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="149" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="150" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="151" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
@@ -31531,10 +31426,8 @@
     <row r="155" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="156" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="157" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="158" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="159" spans="1:18" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
-  <autoFilter ref="A1:S148" xr:uid="{5FB77DDB-B6D9-4CBA-9145-50EF6FDCE517}"/>
+  <autoFilter ref="A1:S146" xr:uid="{5FB77DDB-B6D9-4CBA-9145-50EF6FDCE517}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
@@ -34162,19 +34055,19 @@
       <c r="X58" s="80"/>
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.35">
-      <c r="H63" s="164" t="s">
+      <c r="H63" s="165" t="s">
         <v>531</v>
       </c>
-      <c r="I63" s="164"/>
-      <c r="J63" s="164"/>
-      <c r="K63" s="164"/>
-      <c r="L63" s="164"/>
-      <c r="M63" s="164"/>
-      <c r="N63" s="164"/>
-      <c r="O63" s="164"/>
-      <c r="P63" s="164"/>
-      <c r="Q63" s="164"/>
-      <c r="R63" s="164"/>
+      <c r="I63" s="165"/>
+      <c r="J63" s="165"/>
+      <c r="K63" s="165"/>
+      <c r="L63" s="165"/>
+      <c r="M63" s="165"/>
+      <c r="N63" s="165"/>
+      <c r="O63" s="165"/>
+      <c r="P63" s="165"/>
+      <c r="Q63" s="165"/>
+      <c r="R63" s="165"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4318" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7D413FEA-A95F-43E3-8DB7-2FAA58F3B84B}"/>
+  <xr:revisionPtr revIDLastSave="4321" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CE8FD62B-9FF9-4927-8172-7B6DBC4625B4}"/>
   <bookViews>
-    <workbookView xWindow="3040" yWindow="1010" windowWidth="31280" windowHeight="20590" tabRatio="905" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3620" yWindow="940" windowWidth="33980" windowHeight="20590" tabRatio="905" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lath" sheetId="7" r:id="rId1"/>
@@ -852,7 +852,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2944" uniqueCount="706">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2928" uniqueCount="705">
   <si>
     <t>Name</t>
   </si>
@@ -3198,9 +3198,6 @@
   </si>
   <si>
     <t>Ranger150 3ph 15-57 5/8"</t>
-  </si>
-  <si>
-    <t>MT273M2</t>
   </si>
   <si>
     <t>Standard, Hi usage, Hi speed(warning)</t>
@@ -3989,12 +3986,6 @@
     <xf numFmtId="0" fontId="0" fillId="13" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="0" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -4114,11 +4105,17 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1"/>
+    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" xfId="3" applyFont="1"/>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -13061,14 +13058,14 @@
       <c r="R2" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="S2" s="129" t="s">
+      <c r="S2" s="127" t="s">
         <v>550</v>
       </c>
       <c r="T2" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U2" s="48" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13119,14 +13116,14 @@
       <c r="R3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="S3" s="129" t="s">
+      <c r="S3" s="127" t="s">
         <v>550</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U3" s="48" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13177,14 +13174,14 @@
       <c r="R4" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="S4" s="129" t="s">
+      <c r="S4" s="127" t="s">
         <v>550</v>
       </c>
       <c r="T4" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U4" s="48" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13235,14 +13232,14 @@
       <c r="R5" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="S5" s="129" t="s">
+      <c r="S5" s="127" t="s">
         <v>550</v>
       </c>
       <c r="T5" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U5" s="48" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13293,14 +13290,14 @@
       <c r="R6" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="S6" s="129" t="s">
+      <c r="S6" s="127" t="s">
         <v>550</v>
       </c>
       <c r="T6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U6" s="48" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13351,14 +13348,14 @@
       <c r="R7" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="S7" s="129" t="s">
+      <c r="S7" s="127" t="s">
         <v>550</v>
       </c>
       <c r="T7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U7" s="48" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13409,14 +13406,14 @@
       <c r="R8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="S8" s="129" t="s">
+      <c r="S8" s="127" t="s">
         <v>550</v>
       </c>
       <c r="T8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U8" s="48" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13467,14 +13464,14 @@
       <c r="R9" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="S9" s="129" t="s">
+      <c r="S9" s="127" t="s">
         <v>550</v>
       </c>
       <c r="T9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U9" s="48" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13525,14 +13522,14 @@
       <c r="R10" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="S10" s="129" t="s">
+      <c r="S10" s="127" t="s">
         <v>550</v>
       </c>
       <c r="T10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U10" s="48" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13583,14 +13580,14 @@
       <c r="R11" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="S11" s="129" t="s">
+      <c r="S11" s="127" t="s">
         <v>550</v>
       </c>
       <c r="T11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U11" s="48" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13641,14 +13638,14 @@
       <c r="R12" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="S12" s="129" t="s">
+      <c r="S12" s="127" t="s">
         <v>550</v>
       </c>
       <c r="T12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U12" s="48" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13699,14 +13696,14 @@
       <c r="R13" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="S13" s="129" t="s">
+      <c r="S13" s="127" t="s">
         <v>550</v>
       </c>
       <c r="T13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U13" s="48" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13757,14 +13754,14 @@
       <c r="R14" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="S14" s="129" t="s">
+      <c r="S14" s="127" t="s">
         <v>550</v>
       </c>
       <c r="T14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U14" s="48" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13815,14 +13812,14 @@
       <c r="R15" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="S15" s="129" t="s">
+      <c r="S15" s="127" t="s">
         <v>550</v>
       </c>
       <c r="T15" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U15" s="48" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13873,14 +13870,14 @@
       <c r="R16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="S16" s="129" t="s">
+      <c r="S16" s="127" t="s">
         <v>550</v>
       </c>
       <c r="T16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U16" s="48" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13931,14 +13928,14 @@
       <c r="R17" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="S17" s="129" t="s">
+      <c r="S17" s="127" t="s">
         <v>550</v>
       </c>
       <c r="T17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U17" s="48" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
     </row>
     <row r="18" spans="1:21" s="62" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -14824,7 +14821,7 @@
       <c r="E37" s="54">
         <v>79</v>
       </c>
-      <c r="F37" s="134">
+      <c r="F37" s="132">
         <v>200</v>
       </c>
       <c r="G37" s="54">
@@ -14877,7 +14874,7 @@
       <c r="E38" s="93">
         <v>57</v>
       </c>
-      <c r="F38" s="135">
+      <c r="F38" s="133">
         <v>150</v>
       </c>
       <c r="G38" s="93">
@@ -15306,171 +15303,171 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" s="120" t="s">
+      <c r="A7" s="118" t="s">
         <v>395</v>
       </c>
-      <c r="B7" s="120">
+      <c r="B7" s="118">
         <v>12</v>
       </c>
-      <c r="C7" s="120">
+      <c r="C7" s="118">
         <v>25.4</v>
       </c>
-      <c r="D7" s="120">
+      <c r="D7" s="118">
         <v>57</v>
       </c>
-      <c r="E7" s="120" t="s">
+      <c r="E7" s="118" t="s">
         <v>415</v>
       </c>
-      <c r="F7" s="120">
+      <c r="F7" s="118">
         <v>29000</v>
       </c>
-      <c r="G7" s="121">
+      <c r="G7" s="119">
         <f>0.75*25.4</f>
         <v>19.049999999999997</v>
       </c>
-      <c r="H7" s="120">
+      <c r="H7" s="118">
         <v>29000</v>
       </c>
-      <c r="I7" s="120">
+      <c r="I7" s="118">
         <f t="shared" si="0"/>
         <v>4.75</v>
       </c>
-      <c r="J7" s="120">
+      <c r="J7" s="118">
         <v>345.81</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" s="120" t="s">
+      <c r="A8" s="118" t="s">
         <v>395</v>
       </c>
-      <c r="B8" s="120">
+      <c r="B8" s="118">
         <v>12</v>
       </c>
-      <c r="C8" s="120">
+      <c r="C8" s="118">
         <v>30</v>
       </c>
-      <c r="D8" s="120">
+      <c r="D8" s="118">
         <v>57</v>
       </c>
-      <c r="E8" s="120" t="s">
+      <c r="E8" s="118" t="s">
         <v>415</v>
       </c>
-      <c r="F8" s="120">
+      <c r="F8" s="118">
         <v>29000</v>
       </c>
-      <c r="G8" s="121">
+      <c r="G8" s="119">
         <f>0.75*25.4</f>
         <v>19.049999999999997</v>
       </c>
-      <c r="H8" s="120">
+      <c r="H8" s="118">
         <v>29000</v>
       </c>
-      <c r="I8" s="120">
+      <c r="I8" s="118">
         <f t="shared" ref="I8" si="1">D8/B8</f>
         <v>4.75</v>
       </c>
-      <c r="J8" s="120">
+      <c r="J8" s="118">
         <v>345.81</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9" s="120" t="s">
+      <c r="A9" s="118" t="s">
         <v>395</v>
       </c>
-      <c r="B9" s="120">
+      <c r="B9" s="118">
         <v>15</v>
       </c>
-      <c r="C9" s="120">
+      <c r="C9" s="118">
         <v>30</v>
       </c>
-      <c r="D9" s="120">
+      <c r="D9" s="118">
         <v>57</v>
       </c>
-      <c r="E9" s="120" t="s">
+      <c r="E9" s="118" t="s">
         <v>415</v>
       </c>
-      <c r="F9" s="120">
+      <c r="F9" s="118">
         <v>29000</v>
       </c>
-      <c r="G9" s="121">
+      <c r="G9" s="119">
         <f>0.75*25.4</f>
         <v>19.049999999999997</v>
       </c>
-      <c r="H9" s="120">
+      <c r="H9" s="118">
         <v>29000</v>
       </c>
-      <c r="I9" s="120">
+      <c r="I9" s="118">
         <f>D9/B9</f>
         <v>3.8</v>
       </c>
-      <c r="J9" s="120">
+      <c r="J9" s="118">
         <v>345.81</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" s="122" t="s">
+      <c r="A10" s="120" t="s">
         <v>397</v>
       </c>
-      <c r="B10" s="122">
+      <c r="B10" s="120">
         <v>15</v>
       </c>
-      <c r="C10" s="122">
+      <c r="C10" s="120">
         <v>40</v>
       </c>
-      <c r="D10" s="122">
+      <c r="D10" s="120">
         <v>57</v>
       </c>
-      <c r="E10" s="122" t="s">
+      <c r="E10" s="120" t="s">
         <v>416</v>
       </c>
-      <c r="F10" s="122">
+      <c r="F10" s="120">
         <v>60000</v>
       </c>
-      <c r="G10" s="123">
+      <c r="G10" s="121">
         <v>25.4</v>
       </c>
-      <c r="H10" s="122">
+      <c r="H10" s="120">
         <v>60000</v>
       </c>
-      <c r="I10" s="122">
+      <c r="I10" s="120">
         <f>D10/B10</f>
         <v>3.8</v>
       </c>
-      <c r="J10" s="122">
+      <c r="J10" s="120">
         <v>461.07</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="124" t="s">
+      <c r="A11" s="122" t="s">
         <v>398</v>
       </c>
-      <c r="B11" s="124">
+      <c r="B11" s="122">
         <v>15</v>
       </c>
-      <c r="C11" s="124">
-        <v>55</v>
-      </c>
-      <c r="D11" s="124">
+      <c r="C11" s="122">
+        <v>55</v>
+      </c>
+      <c r="D11" s="122">
         <v>57</v>
       </c>
-      <c r="E11" s="124" t="s">
+      <c r="E11" s="122" t="s">
         <v>417</v>
       </c>
-      <c r="F11" s="124">
+      <c r="F11" s="122">
         <v>95000</v>
       </c>
-      <c r="G11" s="125">
+      <c r="G11" s="123">
         <f>1.25*25.4</f>
         <v>31.75</v>
       </c>
-      <c r="H11" s="124">
+      <c r="H11" s="122">
         <v>95000</v>
       </c>
-      <c r="I11" s="124">
+      <c r="I11" s="122">
         <f>D11/B11</f>
         <v>3.8</v>
       </c>
-      <c r="J11" s="124">
+      <c r="J11" s="122">
         <v>576.36</v>
       </c>
     </row>
@@ -15624,20 +15621,20 @@
       <c r="A7" s="115" t="s">
         <v>492</v>
       </c>
-      <c r="B7" s="160">
+      <c r="B7" s="158">
         <v>60</v>
       </c>
-      <c r="C7" s="160">
+      <c r="C7" s="158">
         <v>32800</v>
       </c>
-      <c r="D7" s="161">
+      <c r="D7" s="159">
         <f t="shared" si="1"/>
         <v>3344.6691786399997</v>
       </c>
-      <c r="E7" s="160" t="s">
+      <c r="E7" s="158" t="s">
         <v>314</v>
       </c>
-      <c r="F7" s="160" t="s">
+      <c r="F7" s="158" t="s">
         <v>528</v>
       </c>
     </row>
@@ -15711,7 +15708,7 @@
       <c r="J1" s="38" t="s">
         <v>537</v>
       </c>
-      <c r="K1" s="126" t="s">
+      <c r="K1" s="124" t="s">
         <v>182</v>
       </c>
     </row>
@@ -15817,16 +15814,16 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="162" t="s">
+      <c r="A6" s="160" t="s">
         <v>443</v>
       </c>
-      <c r="B6" s="163">
+      <c r="B6" s="161">
         <v>800</v>
       </c>
       <c r="C6" s="116">
         <v>2330</v>
       </c>
-      <c r="D6" s="163">
+      <c r="D6" s="161">
         <v>24</v>
       </c>
       <c r="E6" s="116" t="s">
@@ -15841,16 +15838,16 @@
       </c>
     </row>
     <row r="7" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="162" t="s">
+      <c r="A7" s="160" t="s">
         <v>444</v>
       </c>
-      <c r="B7" s="163">
+      <c r="B7" s="161">
         <v>1200</v>
       </c>
       <c r="C7" s="116">
         <v>3530</v>
       </c>
-      <c r="D7" s="163">
+      <c r="D7" s="161">
         <v>24</v>
       </c>
       <c r="E7" s="116" t="s">
@@ -15865,16 +15862,16 @@
       </c>
     </row>
     <row r="8" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="162" t="s">
+      <c r="A8" s="160" t="s">
         <v>445</v>
       </c>
-      <c r="B8" s="163">
+      <c r="B8" s="161">
         <v>2200</v>
       </c>
       <c r="C8" s="116">
         <v>6691</v>
       </c>
-      <c r="D8" s="163">
+      <c r="D8" s="161">
         <v>15</v>
       </c>
       <c r="E8" s="116" t="s">
@@ -15895,7 +15892,7 @@
       <c r="A9" s="102" t="s">
         <v>446</v>
       </c>
-      <c r="B9" s="127">
+      <c r="B9" s="125">
         <v>3600</v>
       </c>
       <c r="C9" s="52">
@@ -15907,14 +15904,14 @@
       <c r="E9" s="52" t="s">
         <v>314</v>
       </c>
-      <c r="F9" s="128"/>
+      <c r="F9" s="126"/>
       <c r="G9" s="52">
         <v>80</v>
       </c>
       <c r="H9" s="52">
         <v>10</v>
       </c>
-      <c r="I9" s="128"/>
+      <c r="I9" s="126"/>
       <c r="K9" t="s">
         <v>493</v>
       </c>
@@ -18183,7 +18180,7 @@
       <c r="D1" s="19" t="s">
         <v>168</v>
       </c>
-      <c r="E1" s="129" t="s">
+      <c r="E1" s="127" t="s">
         <v>550</v>
       </c>
       <c r="F1" s="19" t="s">
@@ -18192,7 +18189,7 @@
       <c r="G1" s="19" t="s">
         <v>552</v>
       </c>
-      <c r="H1" s="133" t="s">
+      <c r="H1" s="131" t="s">
         <v>638</v>
       </c>
       <c r="I1" s="19" t="s">
@@ -18216,15 +18213,15 @@
       <c r="O1" s="19" t="s">
         <v>558</v>
       </c>
-      <c r="P1" s="132" t="s">
+      <c r="P1" s="130" t="s">
         <v>575</v>
       </c>
-      <c r="Q1" s="132" t="s">
+      <c r="Q1" s="130" t="s">
         <v>640</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="139" t="s">
+      <c r="A2" s="137" t="s">
         <v>169</v>
       </c>
       <c r="B2" s="18">
@@ -18274,7 +18271,7 @@
       </c>
     </row>
     <row r="3" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="139" t="s">
+      <c r="A3" s="137" t="s">
         <v>170</v>
       </c>
       <c r="B3" s="18">
@@ -18325,7 +18322,7 @@
       </c>
     </row>
     <row r="4" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="139" t="s">
+      <c r="A4" s="137" t="s">
         <v>609</v>
       </c>
       <c r="B4" s="18">
@@ -18376,8 +18373,8 @@
       </c>
     </row>
     <row r="5" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="139" t="s">
-        <v>673</v>
+      <c r="A5" s="137" t="s">
+        <v>672</v>
       </c>
       <c r="B5" s="18">
         <f>B2+0.85+0.5</f>
@@ -18427,7 +18424,7 @@
       </c>
     </row>
     <row r="6" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="139" t="s">
+      <c r="A6" s="137" t="s">
         <v>171</v>
       </c>
       <c r="B6" s="18">
@@ -18477,7 +18474,7 @@
       </c>
     </row>
     <row r="7" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="139" t="s">
+      <c r="A7" s="137" t="s">
         <v>610</v>
       </c>
       <c r="B7" s="18">
@@ -18528,8 +18525,8 @@
       </c>
     </row>
     <row r="8" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="139" t="s">
-        <v>674</v>
+      <c r="A8" s="137" t="s">
+        <v>673</v>
       </c>
       <c r="B8" s="18">
         <f>B6+0.85+0.5</f>
@@ -18579,7 +18576,7 @@
       </c>
     </row>
     <row r="9" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="139" t="s">
+      <c r="A9" s="137" t="s">
         <v>172</v>
       </c>
       <c r="B9" s="18">
@@ -18629,10 +18626,10 @@
       </c>
     </row>
     <row r="10" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="140" t="s">
+      <c r="A10" s="138" t="s">
         <v>173</v>
       </c>
-      <c r="B10" s="137">
+      <c r="B10" s="135">
         <v>1.2</v>
       </c>
       <c r="C10" s="1">
@@ -18679,10 +18676,10 @@
       </c>
     </row>
     <row r="11" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="140" t="s">
+      <c r="A11" s="138" t="s">
         <v>611</v>
       </c>
-      <c r="B11" s="138">
+      <c r="B11" s="136">
         <f>0.82+0.72</f>
         <v>1.54</v>
       </c>
@@ -18730,7 +18727,7 @@
       </c>
     </row>
     <row r="12" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="141" t="s">
+      <c r="A12" s="139" t="s">
         <v>612</v>
       </c>
       <c r="B12" s="18">
@@ -18780,7 +18777,7 @@
       </c>
     </row>
     <row r="13" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="141" t="s">
+      <c r="A13" s="139" t="s">
         <v>641</v>
       </c>
       <c r="B13" s="52">
@@ -18830,7 +18827,7 @@
       </c>
     </row>
     <row r="14" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="141" t="s">
+      <c r="A14" s="139" t="s">
         <v>174</v>
       </c>
       <c r="B14" s="52">
@@ -18880,7 +18877,7 @@
       </c>
     </row>
     <row r="15" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="141" t="s">
+      <c r="A15" s="139" t="s">
         <v>175</v>
       </c>
       <c r="B15" s="47">
@@ -18930,7 +18927,7 @@
       </c>
     </row>
     <row r="16" spans="1:17" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="141" t="s">
+      <c r="A16" s="139" t="s">
         <v>176</v>
       </c>
       <c r="B16" s="47">
@@ -18980,7 +18977,7 @@
       </c>
     </row>
     <row r="17" spans="1:16" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="141" t="s">
+      <c r="A17" s="139" t="s">
         <v>177</v>
       </c>
       <c r="B17" s="47">
@@ -19069,22 +19066,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="29" x14ac:dyDescent="0.35">
-      <c r="A1" s="136" t="s">
+      <c r="A1" s="134" t="s">
         <v>178</v>
       </c>
-      <c r="B1" s="136" t="s">
+      <c r="B1" s="134" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="136" t="s">
+      <c r="C1" s="134" t="s">
         <v>587</v>
       </c>
-      <c r="D1" s="136" t="s">
+      <c r="D1" s="134" t="s">
         <v>135</v>
       </c>
-      <c r="E1" s="136" t="s">
+      <c r="E1" s="134" t="s">
         <v>179</v>
       </c>
-      <c r="F1" s="136" t="s">
+      <c r="F1" s="134" t="s">
         <v>13</v>
       </c>
       <c r="G1" s="19" t="s">
@@ -19117,7 +19114,7 @@
       <c r="P1" s="19" t="s">
         <v>558</v>
       </c>
-      <c r="Q1" s="132" t="s">
+      <c r="Q1" s="130" t="s">
         <v>642</v>
       </c>
       <c r="U1" s="6" t="s">
@@ -19137,7 +19134,7 @@
       </c>
     </row>
     <row r="2" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="142" t="s">
+      <c r="A2" s="140" t="s">
         <v>183</v>
       </c>
       <c r="B2" s="57" t="s">
@@ -19201,7 +19198,7 @@
       <c r="Y2" s="1"/>
     </row>
     <row r="3" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="142" t="s">
+      <c r="A3" s="140" t="s">
         <v>185</v>
       </c>
       <c r="B3" s="57" t="s">
@@ -19265,7 +19262,7 @@
       <c r="Y3" s="1"/>
     </row>
     <row r="4" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="142" t="s">
+      <c r="A4" s="140" t="s">
         <v>186</v>
       </c>
       <c r="B4" s="57" t="s">
@@ -19329,7 +19326,7 @@
       <c r="Y4" s="1"/>
     </row>
     <row r="5" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A5" s="142" t="s">
+      <c r="A5" s="140" t="s">
         <v>188</v>
       </c>
       <c r="B5" s="57" t="s">
@@ -19393,7 +19390,7 @@
       <c r="Y5" s="1"/>
     </row>
     <row r="6" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A6" s="142" t="s">
+      <c r="A6" s="140" t="s">
         <v>189</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -19459,7 +19456,7 @@
       </c>
     </row>
     <row r="7" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A7" s="142" t="s">
+      <c r="A7" s="140" t="s">
         <v>480</v>
       </c>
       <c r="B7" s="57" t="s">
@@ -19525,7 +19522,7 @@
       </c>
     </row>
     <row r="8" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="142"/>
+      <c r="A8" s="140"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -19540,7 +19537,7 @@
       <c r="X8" s="1"/>
     </row>
     <row r="9" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="142" t="s">
+      <c r="A9" s="140" t="s">
         <v>190</v>
       </c>
       <c r="B9" s="57" t="s">
@@ -19599,7 +19596,7 @@
       </c>
     </row>
     <row r="10" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="142" t="s">
+      <c r="A10" s="140" t="s">
         <v>191</v>
       </c>
       <c r="B10" s="57" t="s">
@@ -19658,7 +19655,7 @@
       </c>
     </row>
     <row r="11" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="142" t="s">
+      <c r="A11" s="140" t="s">
         <v>192</v>
       </c>
       <c r="B11" s="57" t="s">
@@ -19717,7 +19714,7 @@
       </c>
     </row>
     <row r="12" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="142" t="s">
+      <c r="A12" s="140" t="s">
         <v>193</v>
       </c>
       <c r="B12" s="57" t="s">
@@ -19776,7 +19773,7 @@
       </c>
     </row>
     <row r="13" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="142" t="s">
+      <c r="A13" s="140" t="s">
         <v>194</v>
       </c>
       <c r="B13" s="57" t="s">
@@ -19833,7 +19830,7 @@
       </c>
     </row>
     <row r="14" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="142" t="s">
+      <c r="A14" s="140" t="s">
         <v>195</v>
       </c>
       <c r="B14" s="57" t="s">
@@ -19890,7 +19887,7 @@
       </c>
     </row>
     <row r="15" spans="1:25" s="57" customFormat="1" ht="50" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="142" t="s">
+      <c r="A15" s="140" t="s">
         <v>196</v>
       </c>
       <c r="B15" s="57" t="s">
@@ -20024,7 +20021,7 @@
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A2" s="143" t="s">
+      <c r="A2" s="141" t="s">
         <v>153</v>
       </c>
       <c r="B2" s="6" t="s">
@@ -20077,7 +20074,7 @@
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A3" s="143" t="s">
+      <c r="A3" s="141" t="s">
         <v>157</v>
       </c>
       <c r="B3" s="6" t="s">
@@ -20130,7 +20127,7 @@
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A4" s="143" t="s">
+      <c r="A4" s="141" t="s">
         <v>159</v>
       </c>
       <c r="B4" s="6" t="s">
@@ -20183,7 +20180,7 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A5" s="143" t="s">
+      <c r="A5" s="141" t="s">
         <v>160</v>
       </c>
       <c r="B5" s="6" t="s">
@@ -20236,7 +20233,7 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A6" s="143" t="s">
+      <c r="A6" s="141" t="s">
         <v>162</v>
       </c>
       <c r="B6" s="6" t="s">
@@ -20289,7 +20286,7 @@
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A7" s="143" t="s">
+      <c r="A7" s="141" t="s">
         <v>146</v>
       </c>
       <c r="B7" s="6" t="s">
@@ -20342,15 +20339,15 @@
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A8" s="144" t="s">
+      <c r="A8" s="142" t="s">
         <v>607</v>
       </c>
-      <c r="B8" s="145" t="s">
+      <c r="B8" s="143" t="s">
         <v>607</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A9" s="143" t="s">
+      <c r="A9" s="141" t="s">
         <v>603</v>
       </c>
       <c r="B9" s="6" t="s">
@@ -20403,7 +20400,7 @@
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A10" s="143" t="s">
+      <c r="A10" s="141" t="s">
         <v>604</v>
       </c>
       <c r="B10" s="6" t="s">
@@ -20456,7 +20453,7 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A11" s="143" t="s">
+      <c r="A11" s="141" t="s">
         <v>620</v>
       </c>
       <c r="B11" s="6" t="s">
@@ -20506,7 +20503,7 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A12" s="143" t="s">
+      <c r="A12" s="141" t="s">
         <v>605</v>
       </c>
       <c r="B12" s="6" t="s">
@@ -20559,7 +20556,7 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A13" s="143" t="s">
+      <c r="A13" s="141" t="s">
         <v>606</v>
       </c>
       <c r="B13" s="6" t="s">
@@ -20612,7 +20609,7 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A14" s="143" t="s">
+      <c r="A14" s="141" t="s">
         <v>608</v>
       </c>
       <c r="B14" s="6" t="s">
@@ -20665,7 +20662,7 @@
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A15" s="143" t="s">
+      <c r="A15" s="141" t="s">
         <v>163</v>
       </c>
       <c r="B15" s="6" t="s">
@@ -20718,7 +20715,7 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A16" s="143" t="s">
+      <c r="A16" s="141" t="s">
         <v>644</v>
       </c>
       <c r="B16" s="6" t="s">
@@ -20771,7 +20768,7 @@
       </c>
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.35">
-      <c r="B21" s="143" t="s">
+      <c r="B21" s="141" t="s">
         <v>645</v>
       </c>
       <c r="D21" s="6">
@@ -20848,10 +20845,10 @@
         <v>626</v>
       </c>
       <c r="O1" s="44" t="s">
-        <v>675</v>
-      </c>
-      <c r="P1" s="156" t="s">
-        <v>688</v>
+        <v>674</v>
+      </c>
+      <c r="P1" s="154" t="s">
+        <v>687</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
@@ -20964,7 +20961,7 @@
     </row>
     <row r="5" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A5" s="15" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>214</v>
@@ -21005,8 +21002,8 @@
       <c r="N5" s="6">
         <v>8</v>
       </c>
-      <c r="P5" s="159" t="s">
-        <v>691</v>
+      <c r="P5" s="157" t="s">
+        <v>690</v>
       </c>
     </row>
     <row r="6" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
@@ -21052,13 +21049,13 @@
       <c r="N6" s="6">
         <v>8</v>
       </c>
-      <c r="P6" s="159" t="s">
-        <v>689</v>
+      <c r="P6" s="157" t="s">
+        <v>688</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A7" s="14" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>214</v>
@@ -21099,13 +21096,13 @@
       <c r="N7" s="6">
         <v>8</v>
       </c>
-      <c r="P7" s="157" t="s">
-        <v>691</v>
+      <c r="P7" s="155" t="s">
+        <v>690</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A8" s="15" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>214</v>
@@ -21146,13 +21143,13 @@
       <c r="N8" s="6">
         <v>7.5</v>
       </c>
-      <c r="P8" s="157" t="s">
-        <v>689</v>
+      <c r="P8" s="155" t="s">
+        <v>688</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>214</v>
@@ -21193,13 +21190,13 @@
       <c r="N9" s="6">
         <v>7.5</v>
       </c>
-      <c r="P9" s="158" t="s">
-        <v>689</v>
+      <c r="P9" s="156" t="s">
+        <v>688</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="99" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B10" s="99" t="s">
         <v>214</v>
@@ -21240,13 +21237,13 @@
       <c r="N10" s="6" t="s">
         <v>631</v>
       </c>
-      <c r="P10" s="158" t="s">
-        <v>690</v>
+      <c r="P10" s="156" t="s">
+        <v>689</v>
       </c>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A11" s="98" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B11" s="98" t="s">
         <v>214</v>
@@ -21254,10 +21251,10 @@
       <c r="C11" s="99" t="s">
         <v>227</v>
       </c>
-      <c r="D11" s="155">
+      <c r="D11" s="153">
         <v>219.1</v>
       </c>
-      <c r="E11" s="155">
+      <c r="E11" s="153">
         <v>6.3</v>
       </c>
       <c r="F11" s="98">
@@ -21287,13 +21284,13 @@
       <c r="N11" s="6" t="s">
         <v>631</v>
       </c>
-      <c r="P11" s="158" t="s">
-        <v>690</v>
+      <c r="P11" s="156" t="s">
+        <v>689</v>
       </c>
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A12" s="98" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B12" s="98" t="s">
         <v>214</v>
@@ -21301,10 +21298,10 @@
       <c r="C12" s="98" t="s">
         <v>229</v>
       </c>
-      <c r="D12" s="155">
+      <c r="D12" s="153">
         <v>273</v>
       </c>
-      <c r="E12" s="155">
+      <c r="E12" s="153">
         <v>6.3</v>
       </c>
       <c r="F12" s="98">
@@ -21332,8 +21329,8 @@
       <c r="N12" s="6" t="s">
         <v>631</v>
       </c>
-      <c r="P12" s="158" t="s">
-        <v>690</v>
+      <c r="P12" s="156" t="s">
+        <v>689</v>
       </c>
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.35">
@@ -21391,18 +21388,18 @@
   </cols>
   <sheetData>
     <row r="3" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="B3" s="151" t="s">
+      <c r="B3" s="149" t="s">
         <v>663</v>
       </c>
-      <c r="C3" s="151" t="s">
+      <c r="C3" s="149" t="s">
         <v>664</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B4" s="152" t="s">
+      <c r="B4" s="150" t="s">
         <v>647</v>
       </c>
-      <c r="C4" s="152" t="s">
+      <c r="C4" s="150" t="s">
         <v>655</v>
       </c>
       <c r="E4">
@@ -21413,10 +21410,10 @@
       </c>
     </row>
     <row r="5" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B5" s="152" t="s">
+      <c r="B5" s="150" t="s">
         <v>648</v>
       </c>
-      <c r="C5" s="152" t="s">
+      <c r="C5" s="150" t="s">
         <v>656</v>
       </c>
       <c r="E5">
@@ -21435,10 +21432,10 @@
       </c>
     </row>
     <row r="6" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B6" s="152" t="s">
+      <c r="B6" s="150" t="s">
         <v>649</v>
       </c>
-      <c r="C6" s="152" t="s">
+      <c r="C6" s="150" t="s">
         <v>657</v>
       </c>
       <c r="E6">
@@ -21457,10 +21454,10 @@
       </c>
     </row>
     <row r="7" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B7" s="152" t="s">
+      <c r="B7" s="150" t="s">
         <v>650</v>
       </c>
-      <c r="C7" s="152" t="s">
+      <c r="C7" s="150" t="s">
         <v>658</v>
       </c>
       <c r="E7">
@@ -21479,10 +21476,10 @@
       </c>
     </row>
     <row r="8" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B8" s="152" t="s">
+      <c r="B8" s="150" t="s">
         <v>651</v>
       </c>
-      <c r="C8" s="152" t="s">
+      <c r="C8" s="150" t="s">
         <v>659</v>
       </c>
       <c r="E8">
@@ -21501,10 +21498,10 @@
       </c>
     </row>
     <row r="9" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B9" s="152" t="s">
+      <c r="B9" s="150" t="s">
         <v>652</v>
       </c>
-      <c r="C9" s="152" t="s">
+      <c r="C9" s="150" t="s">
         <v>660</v>
       </c>
       <c r="E9">
@@ -21523,10 +21520,10 @@
       </c>
     </row>
     <row r="10" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B10" s="152" t="s">
+      <c r="B10" s="150" t="s">
         <v>653</v>
       </c>
-      <c r="C10" s="152" t="s">
+      <c r="C10" s="150" t="s">
         <v>661</v>
       </c>
       <c r="E10">
@@ -21545,10 +21542,10 @@
       </c>
     </row>
     <row r="11" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
-      <c r="B11" s="152" t="s">
+      <c r="B11" s="150" t="s">
         <v>654</v>
       </c>
-      <c r="C11" s="152" t="s">
+      <c r="C11" s="150" t="s">
         <v>662</v>
       </c>
       <c r="E11">
@@ -21567,7 +21564,7 @@
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.35">
-      <c r="C13" s="153" t="s">
+      <c r="C13" s="151" t="s">
         <v>665</v>
       </c>
       <c r="D13" s="115"/>
@@ -21673,7 +21670,7 @@
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="J2" s="6" t="s">
         <v>314</v>
@@ -22413,7 +22410,7 @@
       </c>
       <c r="H21" s="116"/>
       <c r="I21" s="116" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>314</v>
@@ -22491,7 +22488,7 @@
       </c>
       <c r="H23" s="116"/>
       <c r="I23" s="116" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>314</v>
@@ -22606,8 +22603,8 @@
         <v>40</v>
       </c>
       <c r="H26" s="6"/>
-      <c r="I26" s="154" t="s">
-        <v>676</v>
+      <c r="I26" s="152" t="s">
+        <v>675</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>314</v>
@@ -22685,7 +22682,7 @@
       </c>
       <c r="H28" s="116"/>
       <c r="I28" s="116" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="J28" s="6" t="s">
         <v>314</v>
@@ -22801,7 +22798,7 @@
       </c>
       <c r="H31" s="116"/>
       <c r="I31" s="116" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>314</v>
@@ -22879,7 +22876,7 @@
       </c>
       <c r="H33" s="116"/>
       <c r="I33" s="116" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="J33" s="6" t="s">
         <v>314</v>
@@ -22919,7 +22916,7 @@
       </c>
       <c r="H34" s="6"/>
       <c r="I34" s="6" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="J34" s="6" t="s">
         <v>314</v>
@@ -23035,7 +23032,7 @@
       </c>
       <c r="H37" s="116"/>
       <c r="I37" s="116" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="J37" s="6" t="s">
         <v>314</v>
@@ -24109,7 +24106,7 @@
       <c r="T1" s="11" t="s">
         <v>497</v>
       </c>
-      <c r="U1" s="130" t="s">
+      <c r="U1" s="128" t="s">
         <v>256</v>
       </c>
       <c r="V1" s="11" t="s">
@@ -26024,7 +26021,7 @@
         <v>750</v>
       </c>
       <c r="S40" s="112" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="U40" s="114"/>
     </row>
@@ -26076,7 +26073,7 @@
         <v>1100</v>
       </c>
       <c r="S41" s="112" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="U41" s="114"/>
     </row>
@@ -26128,13 +26125,13 @@
         <v>1100</v>
       </c>
       <c r="S42" s="112" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="U42" s="114"/>
     </row>
     <row r="43" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>303</v>
@@ -26174,13 +26171,13 @@
         <v>22</v>
       </c>
       <c r="S43" s="112" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="U43" s="114"/>
     </row>
     <row r="44" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>303</v>
@@ -26224,7 +26221,7 @@
     </row>
     <row r="45" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>303</v>
@@ -26268,7 +26265,7 @@
     </row>
     <row r="46" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>303</v>
@@ -26312,7 +26309,7 @@
     </row>
     <row r="47" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>303</v>
@@ -26471,7 +26468,7 @@
         <v>22</v>
       </c>
       <c r="S50" s="71" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
     </row>
     <row r="51" spans="1:21" s="3" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -26561,7 +26558,7 @@
         <v>22</v>
       </c>
       <c r="S52" s="71" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
     </row>
     <row r="53" spans="1:21" s="107" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -26942,7 +26939,7 @@
       <c r="S61" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="U61" s="150">
+      <c r="U61" s="148">
         <v>300.41000000000003</v>
       </c>
     </row>
@@ -27002,7 +26999,7 @@
       <c r="S62" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="U62" s="150">
+      <c r="U62" s="148">
         <v>300.41000000000003</v>
       </c>
     </row>
@@ -27063,7 +27060,7 @@
       <c r="S63" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="U63" s="150">
+      <c r="U63" s="148">
         <v>300.41000000000003</v>
       </c>
     </row>
@@ -27121,10 +27118,10 @@
       <c r="R64" s="6">
         <v>450</v>
       </c>
-      <c r="S64" s="164" t="s">
-        <v>705</v>
-      </c>
-      <c r="U64" s="166">
+      <c r="S64" s="162" t="s">
+        <v>704</v>
+      </c>
+      <c r="U64" s="163">
         <v>345.34</v>
       </c>
     </row>
@@ -27160,7 +27157,7 @@
       <c r="Q65" s="105"/>
       <c r="R65" s="108"/>
       <c r="S65" s="108"/>
-      <c r="U65" s="149"/>
+      <c r="U65" s="147"/>
     </row>
     <row r="66" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="str">
@@ -27218,7 +27215,7 @@
       <c r="S66" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="U66" s="148">
+      <c r="U66" s="146">
         <v>179.04</v>
       </c>
     </row>
@@ -27279,134 +27276,28 @@
       <c r="S67" s="6" t="s">
         <v>316</v>
       </c>
-      <c r="U67" s="150">
+      <c r="U67" s="148">
         <v>179.04</v>
       </c>
       <c r="V67" s="83"/>
       <c r="W67" s="83"/>
     </row>
     <row r="68" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="3" t="str">
-        <f>Chaindrive!A16</f>
-        <v>Ranger150 3ph 18-57 5/8"</v>
-      </c>
-      <c r="B68" t="s">
-        <v>314</v>
-      </c>
-      <c r="C68" s="2">
-        <f>D66+0.01</f>
-        <v>270.01</v>
-      </c>
-      <c r="D68" s="23">
-        <f>Chaindrive!J16</f>
-        <v>471.83333333333331</v>
-      </c>
-      <c r="E68" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F68" s="22">
-        <f>Chaindrive!L16</f>
-        <v>15.157894736842106</v>
-      </c>
-      <c r="G68" s="1">
-        <v>415</v>
-      </c>
-      <c r="H68" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I68" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K68" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="L68" s="1">
-        <v>25.4</v>
-      </c>
-      <c r="M68" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N68" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O68" s="74">
-        <f>Chaindrive!O16</f>
-        <v>12.631578947368421</v>
-      </c>
-      <c r="P68" s="1">
-        <v>11</v>
-      </c>
-      <c r="R68" s="6">
-        <v>400</v>
-      </c>
-      <c r="S68" s="6" t="s">
-        <v>317</v>
-      </c>
-      <c r="U68" s="150">
-        <v>472.24</v>
-      </c>
+      <c r="B68"/>
+      <c r="C68" s="2"/>
+      <c r="D68" s="23"/>
+      <c r="F68" s="22"/>
+      <c r="O68" s="74"/>
+      <c r="U68" s="148"/>
       <c r="V68" s="83"/>
     </row>
     <row r="69" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="3" t="str">
-        <f>Chaindrive!A17</f>
-        <v>Ranger150 3ph 15-57 5/8"</v>
-      </c>
-      <c r="B69" t="s">
-        <v>314</v>
-      </c>
-      <c r="C69" s="2">
-        <f>D67+0.01</f>
-        <v>342.01</v>
-      </c>
-      <c r="D69" s="23">
-        <f>Chaindrive!J17</f>
-        <v>566.19999999999993</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="F69" s="22">
-        <f>Chaindrive!L17</f>
-        <v>12.631578947368421</v>
-      </c>
-      <c r="G69" s="1">
-        <v>415</v>
-      </c>
-      <c r="H69" s="1" t="s">
-        <v>308</v>
-      </c>
-      <c r="I69" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K69" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="L69" s="1">
-        <v>25.4</v>
-      </c>
-      <c r="M69" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="N69" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="O69" s="74">
-        <f>Chaindrive!O17</f>
-        <v>10.526315789473685</v>
-      </c>
-      <c r="P69" s="1">
-        <v>11</v>
-      </c>
-      <c r="R69" s="6">
-        <v>400</v>
-      </c>
-      <c r="S69" s="6" t="s">
-        <v>670</v>
-      </c>
-      <c r="U69" s="150">
-        <v>472.24</v>
-      </c>
+      <c r="B69"/>
+      <c r="C69" s="2"/>
+      <c r="D69" s="23"/>
+      <c r="F69" s="22"/>
+      <c r="O69" s="74"/>
+      <c r="U69" s="148"/>
       <c r="V69" s="83"/>
     </row>
     <row r="70" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -27465,7 +27356,7 @@
       <c r="S70" s="6" t="s">
         <v>317</v>
       </c>
-      <c r="U70" s="150">
+      <c r="U70" s="148">
         <v>472.24</v>
       </c>
     </row>
@@ -27522,7 +27413,7 @@
       <c r="R71" s="6">
         <v>650</v>
       </c>
-      <c r="U71" s="150">
+      <c r="U71" s="148">
         <v>498.07</v>
       </c>
     </row>
@@ -27553,7 +27444,7 @@
       <c r="N72" s="106" t="s">
         <v>467</v>
       </c>
-      <c r="O72" s="167"/>
+      <c r="O72" s="164"/>
       <c r="P72" s="105"/>
       <c r="Q72" s="105"/>
       <c r="R72" s="108"/>
@@ -27903,7 +27794,7 @@
       <c r="L79" s="105"/>
       <c r="M79" s="105"/>
       <c r="N79" s="105"/>
-      <c r="O79" s="167"/>
+      <c r="O79" s="164"/>
       <c r="P79" s="105"/>
       <c r="Q79" s="105"/>
       <c r="R79" s="108"/>
@@ -28218,7 +28109,7 @@
       <c r="N85" s="106" t="s">
         <v>467</v>
       </c>
-      <c r="O85" s="167"/>
+      <c r="O85" s="164"/>
       <c r="P85" s="105"/>
       <c r="Q85" s="105"/>
       <c r="R85" s="108"/>
@@ -28687,7 +28578,7 @@
         <v>318</v>
       </c>
       <c r="T94" s="57"/>
-      <c r="U94" s="147">
+      <c r="U94" s="145">
         <v>266.06</v>
       </c>
       <c r="V94" s="57"/>
@@ -28749,7 +28640,7 @@
         <v>320</v>
       </c>
       <c r="T95" s="57"/>
-      <c r="U95" s="147">
+      <c r="U95" s="145">
         <v>280.37</v>
       </c>
       <c r="V95" s="57"/>
@@ -28811,7 +28702,7 @@
         <v>322</v>
       </c>
       <c r="T96" s="57"/>
-      <c r="U96" s="147">
+      <c r="U96" s="145">
         <v>307.35000000000002</v>
       </c>
       <c r="V96" s="57"/>
@@ -28870,7 +28761,7 @@
         <v>324</v>
       </c>
       <c r="T97" s="57"/>
-      <c r="U97" s="146">
+      <c r="U97" s="144">
         <v>383.55</v>
       </c>
       <c r="V97" s="57"/>
@@ -28929,7 +28820,7 @@
         <v>326</v>
       </c>
       <c r="T98" s="57"/>
-      <c r="U98" s="146">
+      <c r="U98" s="144">
         <v>475.98</v>
       </c>
       <c r="V98" s="57"/>
@@ -28988,7 +28879,7 @@
         <v>350</v>
       </c>
       <c r="T99" s="57"/>
-      <c r="U99" s="146">
+      <c r="U99" s="144">
         <v>574.51</v>
       </c>
       <c r="V99" s="57"/>
@@ -29047,7 +28938,7 @@
         <v>329</v>
       </c>
       <c r="T100" s="57"/>
-      <c r="U100" s="146">
+      <c r="U100" s="144">
         <v>617.67999999999995</v>
       </c>
       <c r="V100" s="57"/>
@@ -29106,7 +28997,7 @@
         <v>331</v>
       </c>
       <c r="T101" s="57"/>
-      <c r="U101" s="146">
+      <c r="U101" s="144">
         <v>965.9</v>
       </c>
       <c r="V101" s="57"/>
@@ -29165,7 +29056,7 @@
         <v>333</v>
       </c>
       <c r="T102" s="57"/>
-      <c r="U102" s="146">
+      <c r="U102" s="144">
         <v>1031.17</v>
       </c>
       <c r="V102" s="57"/>
@@ -29224,7 +29115,7 @@
         <v>335</v>
       </c>
       <c r="T103" s="57"/>
-      <c r="U103" s="146">
+      <c r="U103" s="144">
         <v>1351.89</v>
       </c>
       <c r="V103" s="57"/>
@@ -29283,7 +29174,7 @@
         <v>337</v>
       </c>
       <c r="T104" s="57"/>
-      <c r="U104" s="146">
+      <c r="U104" s="144">
         <v>1685.96</v>
       </c>
       <c r="V104" s="57"/>
@@ -29344,14 +29235,14 @@
       <c r="T105" s="57" t="e" vm="1">
         <v>#VALUE!</v>
       </c>
-      <c r="U105" s="131"/>
+      <c r="U105" s="129"/>
       <c r="V105" s="57"/>
     </row>
     <row r="106" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A106" s="128" t="s">
+      <c r="A106" s="126" t="s">
         <v>339</v>
       </c>
-      <c r="B106" s="128" t="s">
+      <c r="B106" s="126" t="s">
         <v>314</v>
       </c>
       <c r="C106" s="52">
@@ -29401,14 +29292,14 @@
       </c>
       <c r="S106" s="52"/>
       <c r="T106" s="57"/>
-      <c r="U106" s="131"/>
+      <c r="U106" s="129"/>
       <c r="V106" s="57"/>
     </row>
     <row r="107" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A107" s="128" t="s">
+      <c r="A107" s="126" t="s">
         <v>340</v>
       </c>
-      <c r="B107" s="128" t="s">
+      <c r="B107" s="126" t="s">
         <v>314</v>
       </c>
       <c r="C107" s="52">
@@ -29458,14 +29349,14 @@
       </c>
       <c r="S107" s="52"/>
       <c r="T107" s="57"/>
-      <c r="U107" s="131"/>
+      <c r="U107" s="129"/>
       <c r="V107" s="57"/>
     </row>
     <row r="108" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A108" s="128" t="s">
+      <c r="A108" s="126" t="s">
         <v>341</v>
       </c>
-      <c r="B108" s="128" t="s">
+      <c r="B108" s="126" t="s">
         <v>314</v>
       </c>
       <c r="C108" s="52">
@@ -29515,14 +29406,14 @@
       </c>
       <c r="S108" s="52"/>
       <c r="T108" s="57"/>
-      <c r="U108" s="131"/>
+      <c r="U108" s="129"/>
       <c r="V108" s="57"/>
     </row>
     <row r="109" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A109" s="128" t="s">
+      <c r="A109" s="126" t="s">
         <v>342</v>
       </c>
-      <c r="B109" s="128" t="s">
+      <c r="B109" s="126" t="s">
         <v>314</v>
       </c>
       <c r="C109" s="52">
@@ -29572,14 +29463,14 @@
       </c>
       <c r="S109" s="52"/>
       <c r="T109" s="57"/>
-      <c r="U109" s="131"/>
+      <c r="U109" s="129"/>
       <c r="V109" s="57"/>
     </row>
     <row r="110" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A110" s="128" t="s">
+      <c r="A110" s="126" t="s">
         <v>498</v>
       </c>
-      <c r="B110" s="128" t="s">
+      <c r="B110" s="126" t="s">
         <v>314</v>
       </c>
       <c r="C110" s="52">
@@ -29629,7 +29520,7 @@
       </c>
       <c r="S110" s="52"/>
       <c r="T110" s="57"/>
-      <c r="U110" s="131"/>
+      <c r="U110" s="129"/>
       <c r="V110" s="57"/>
     </row>
     <row r="111" spans="1:22" s="107" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -30136,7 +30027,7 @@
         <v>750</v>
       </c>
       <c r="S120" s="1"/>
-      <c r="U120" s="146">
+      <c r="U120" s="144">
         <v>2614.38</v>
       </c>
     </row>
@@ -30483,7 +30374,7 @@
         <v>1500</v>
       </c>
       <c r="S127" s="1"/>
-      <c r="U127" s="147">
+      <c r="U127" s="145">
         <v>2021.94</v>
       </c>
     </row>
@@ -30642,7 +30533,7 @@
         <v>4500</v>
       </c>
       <c r="S130" s="1"/>
-      <c r="U130" s="146">
+      <c r="U130" s="144">
         <v>2676</v>
       </c>
     </row>
@@ -31659,7 +31550,7 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" s="56" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B6" s="56" t="s">
         <v>314</v>
@@ -31871,7 +31762,7 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" s="56" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B10" s="56" t="s">
         <v>314</v>
@@ -32168,191 +32059,191 @@
       <c r="S15" s="61"/>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.35">
-      <c r="A16" s="56" t="s">
+      <c r="A16" s="24" t="s">
         <v>539</v>
       </c>
-      <c r="B16" s="56" t="s">
+      <c r="B16" s="24" t="s">
         <v>314</v>
       </c>
-      <c r="C16" s="71">
+      <c r="C16" s="47">
         <v>18</v>
       </c>
-      <c r="D16" s="71">
+      <c r="D16" s="47">
         <v>25.4</v>
       </c>
-      <c r="E16" s="71">
+      <c r="E16" s="47">
         <v>57</v>
       </c>
-      <c r="F16" s="71">
+      <c r="F16" s="47">
         <v>30</v>
       </c>
-      <c r="G16" s="75">
+      <c r="G16" s="166">
         <f t="shared" ref="G16" si="15">E16/C16</f>
         <v>3.1666666666666665</v>
       </c>
-      <c r="H16" s="71" t="s">
+      <c r="H16" s="47" t="s">
         <v>393</v>
       </c>
-      <c r="I16" s="71">
+      <c r="I16" s="47">
         <v>149</v>
       </c>
-      <c r="J16" s="73">
+      <c r="J16" s="167">
         <f>I16*G16</f>
         <v>471.83333333333331</v>
       </c>
-      <c r="K16" s="71">
+      <c r="K16" s="47">
         <v>48</v>
       </c>
-      <c r="L16" s="75">
+      <c r="L16" s="166">
         <f t="shared" ref="L16" si="16">K16/G16</f>
         <v>15.157894736842106</v>
       </c>
-      <c r="M16" s="71">
+      <c r="M16" s="47">
         <v>415</v>
       </c>
-      <c r="N16" s="71">
+      <c r="N16" s="47">
         <v>40</v>
       </c>
-      <c r="O16" s="71">
+      <c r="O16" s="47">
         <f t="shared" ref="O16" si="17">N16/G16</f>
         <v>12.631578947368421</v>
       </c>
-      <c r="P16" s="6">
+      <c r="P16" s="47">
         <v>91.42</v>
       </c>
-      <c r="Q16" s="6">
+      <c r="Q16" s="47">
         <v>288</v>
       </c>
-      <c r="R16" s="1">
+      <c r="R16" s="52">
         <v>25.4</v>
       </c>
-      <c r="S16" s="6">
+      <c r="S16" s="47">
         <v>22400</v>
       </c>
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A17" s="56" t="s">
+      <c r="A17" s="24" t="s">
         <v>669</v>
       </c>
-      <c r="B17" s="56" t="s">
+      <c r="B17" s="24" t="s">
         <v>314</v>
       </c>
-      <c r="C17" s="71">
+      <c r="C17" s="47">
         <v>15</v>
       </c>
-      <c r="D17" s="71">
+      <c r="D17" s="47">
         <v>25.4</v>
       </c>
-      <c r="E17" s="71">
+      <c r="E17" s="47">
         <v>57</v>
       </c>
-      <c r="F17" s="71">
+      <c r="F17" s="47">
         <v>30</v>
       </c>
-      <c r="G17" s="75">
+      <c r="G17" s="166">
         <f t="shared" ref="G17" si="18">E17/C17</f>
         <v>3.8</v>
       </c>
-      <c r="H17" s="71" t="s">
+      <c r="H17" s="47" t="s">
         <v>393</v>
       </c>
-      <c r="I17" s="71">
+      <c r="I17" s="47">
         <v>149</v>
       </c>
-      <c r="J17" s="73">
+      <c r="J17" s="167">
         <f>I17*G17</f>
         <v>566.19999999999993</v>
       </c>
-      <c r="K17" s="71">
+      <c r="K17" s="47">
         <v>48</v>
       </c>
-      <c r="L17" s="75">
+      <c r="L17" s="166">
         <f t="shared" ref="L17" si="19">K17/G17</f>
         <v>12.631578947368421</v>
       </c>
-      <c r="M17" s="71">
+      <c r="M17" s="47">
         <v>415</v>
       </c>
-      <c r="N17" s="71">
+      <c r="N17" s="47">
         <v>40</v>
       </c>
-      <c r="O17" s="71">
+      <c r="O17" s="47">
         <f t="shared" ref="O17" si="20">N17/G17</f>
         <v>10.526315789473685</v>
       </c>
-      <c r="P17" s="6">
+      <c r="P17" s="47">
         <v>91.42</v>
       </c>
-      <c r="Q17" s="6">
+      <c r="Q17" s="47">
         <v>288</v>
       </c>
-      <c r="R17" s="1">
+      <c r="R17" s="52">
         <v>25.4</v>
       </c>
-      <c r="S17" s="6">
+      <c r="S17" s="47">
         <v>22400</v>
       </c>
     </row>
     <row r="18" spans="1:19" x14ac:dyDescent="0.35">
-      <c r="A18" s="115" t="s">
+      <c r="A18" s="56" t="s">
         <v>394</v>
       </c>
-      <c r="B18" s="115" t="s">
+      <c r="B18" s="56" t="s">
         <v>314</v>
       </c>
-      <c r="C18" s="116">
+      <c r="C18" s="71">
         <v>12</v>
       </c>
-      <c r="D18" s="116">
+      <c r="D18" s="71">
         <v>25.4</v>
       </c>
-      <c r="E18" s="116">
+      <c r="E18" s="71">
         <v>57</v>
       </c>
-      <c r="F18" s="116">
+      <c r="F18" s="71">
         <v>40</v>
       </c>
-      <c r="G18" s="117">
+      <c r="G18" s="75">
         <f t="shared" ref="G18" si="21">E18/C18</f>
         <v>4.75</v>
       </c>
-      <c r="H18" s="116" t="s">
+      <c r="H18" s="71" t="s">
         <v>393</v>
       </c>
-      <c r="I18" s="116">
+      <c r="I18" s="71">
         <v>150</v>
       </c>
-      <c r="J18" s="118">
+      <c r="J18" s="73">
         <f>I18*G18</f>
         <v>712.5</v>
       </c>
-      <c r="K18" s="116">
+      <c r="K18" s="71">
         <v>48</v>
       </c>
-      <c r="L18" s="117">
+      <c r="L18" s="75">
         <f>K18/G18</f>
         <v>10.105263157894736</v>
       </c>
-      <c r="M18" s="116">
+      <c r="M18" s="71">
         <v>415</v>
       </c>
-      <c r="N18" s="116">
+      <c r="N18" s="71">
         <v>40</v>
       </c>
-      <c r="O18" s="116">
+      <c r="O18" s="71">
         <f t="shared" si="0"/>
         <v>8.4210526315789469</v>
       </c>
-      <c r="P18" s="6">
+      <c r="P18" s="71">
         <v>73.599999999999994</v>
       </c>
-      <c r="Q18" s="6">
+      <c r="Q18" s="71">
         <v>288</v>
       </c>
-      <c r="R18" s="1">
+      <c r="R18" s="112">
         <v>25.4</v>
       </c>
-      <c r="S18" s="6">
+      <c r="S18" s="71">
         <v>22400</v>
       </c>
     </row>
@@ -33901,7 +33792,7 @@
       <c r="A55" s="56" t="s">
         <v>506</v>
       </c>
-      <c r="B55" s="119" t="s">
+      <c r="B55" s="117" t="s">
         <v>238</v>
       </c>
       <c r="C55" s="71">
@@ -33951,7 +33842,7 @@
       <c r="A56" s="56" t="s">
         <v>507</v>
       </c>
-      <c r="B56" s="119" t="s">
+      <c r="B56" s="117" t="s">
         <v>238</v>
       </c>
       <c r="C56" s="71">

--- a/Calculation Data.xlsx
+++ b/Calculation Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://securitywindowshutt-my.sharepoint.com/personal/rob_hyrons_swsuk_co_uk/Documents/SWS product dev/Projects/P190 - Industrial EVO/Calculators/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4392" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8434602A-BC5F-476E-8D14-D12E68B41EDB}"/>
+  <xr:revisionPtr revIDLastSave="4395" documentId="13_ncr:1_{DBA201A5-D078-4ADB-A563-7B8EA9522FCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0DD363C4-6981-4C62-9138-59A567BDE636}"/>
   <bookViews>
-    <workbookView xWindow="340" yWindow="440" windowWidth="25010" windowHeight="15470" tabRatio="905" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3580" windowWidth="38400" windowHeight="16580" tabRatio="905" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Lath" sheetId="7" r:id="rId1"/>
@@ -852,7 +852,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2946" uniqueCount="713">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2943" uniqueCount="712">
   <si>
     <t>Name</t>
   </si>
@@ -2172,9 +2172,6 @@
   </si>
   <si>
     <t>RSB 4 (PCM10A)</t>
-  </si>
-  <si>
-    <t>RSB-1-18a</t>
   </si>
   <si>
     <t>FG 80 -40</t>
@@ -12009,50 +12006,6 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>141775</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>37394</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>555599</xdr:colOff>
-      <xdr:row>15</xdr:row>
-      <xdr:rowOff>464595</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="Picture 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DB29705-D579-A5DF-33F7-34F5854A21BD}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="10259442" y="12299950"/>
-          <a:ext cx="413824" cy="428964"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
       <xdr:colOff>88900</xdr:colOff>
       <xdr:row>3</xdr:row>
       <xdr:rowOff>23003</xdr:rowOff>
@@ -12077,7 +12030,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12121,7 +12074,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12165,7 +12118,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12209,7 +12162,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12253,7 +12206,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12297,7 +12250,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12341,7 +12294,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12385,7 +12338,7 @@
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -12859,7 +12812,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="G1" s="30" t="s">
         <v>5</v>
@@ -12895,16 +12848,16 @@
         <v>15</v>
       </c>
       <c r="R1" s="10" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="S1" s="1" t="s">
         <v>61</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="U1" s="10" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
     </row>
     <row r="2" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -12956,13 +12909,13 @@
         <v>22</v>
       </c>
       <c r="S2" s="126" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="T2" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U2" s="47" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="3" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13014,13 +12967,13 @@
         <v>22</v>
       </c>
       <c r="S3" s="126" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="T3" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U3" s="47" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="4" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13072,13 +13025,13 @@
         <v>22</v>
       </c>
       <c r="S4" s="126" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="T4" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U4" s="47" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="5" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13130,13 +13083,13 @@
         <v>22</v>
       </c>
       <c r="S5" s="126" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="T5" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U5" s="47" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="6" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13188,13 +13141,13 @@
         <v>22</v>
       </c>
       <c r="S6" s="126" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="T6" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U6" s="47" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
     </row>
     <row r="7" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13246,13 +13199,13 @@
         <v>22</v>
       </c>
       <c r="S7" s="126" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="T7" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U7" s="47" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="8" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13304,13 +13257,13 @@
         <v>22</v>
       </c>
       <c r="S8" s="126" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="T8" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U8" s="47" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="9" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13362,13 +13315,13 @@
         <v>22</v>
       </c>
       <c r="S9" s="126" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="T9" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U9" s="47" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="10" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13420,13 +13373,13 @@
         <v>22</v>
       </c>
       <c r="S10" s="126" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="T10" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U10" s="47" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="11" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13478,13 +13431,13 @@
         <v>22</v>
       </c>
       <c r="S11" s="126" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="T11" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U11" s="47" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="12" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13536,13 +13489,13 @@
         <v>22</v>
       </c>
       <c r="S12" s="126" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="T12" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U12" s="47" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="13" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13594,13 +13547,13 @@
         <v>22</v>
       </c>
       <c r="S13" s="126" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="T13" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U13" s="47" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="14" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13652,13 +13605,13 @@
         <v>22</v>
       </c>
       <c r="S14" s="126" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="T14" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U14" s="47" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="15" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13710,13 +13663,13 @@
         <v>22</v>
       </c>
       <c r="S15" s="126" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="T15" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U15" s="47" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="16" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13768,13 +13721,13 @@
         <v>22</v>
       </c>
       <c r="S16" s="126" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="T16" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U16" s="47" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="17" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -13826,13 +13779,13 @@
         <v>22</v>
       </c>
       <c r="S17" s="126" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="T17" s="6" t="s">
         <v>22</v>
       </c>
       <c r="U17" s="47" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
     </row>
     <row r="18" spans="1:21" s="61" customFormat="1" ht="16" customHeight="1" x14ac:dyDescent="0.35">
@@ -13903,13 +13856,13 @@
         <v>17</v>
       </c>
       <c r="S19" s="19" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="T19" s="6" t="s">
         <v>17</v>
       </c>
       <c r="U19" s="47" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="20" spans="1:21" s="61" customFormat="1" ht="12.65" customHeight="1" x14ac:dyDescent="0.35">
@@ -13981,13 +13934,13 @@
         <v>17</v>
       </c>
       <c r="S21" s="19" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="T21" s="6" t="s">
         <v>17</v>
       </c>
       <c r="U21" s="47" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="22" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -14037,13 +13990,13 @@
         <v>17</v>
       </c>
       <c r="S22" s="19" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="T22" s="6" t="s">
         <v>17</v>
       </c>
       <c r="U22" s="47" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="23" spans="1:21" s="61" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.35">
@@ -14115,13 +14068,13 @@
         <v>17</v>
       </c>
       <c r="S24" s="19" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="T24" s="6" t="s">
         <v>17</v>
       </c>
       <c r="U24" s="47" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
     </row>
     <row r="25" spans="1:21" s="61" customFormat="1" ht="16.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -14189,7 +14142,7 @@
         <v>17</v>
       </c>
       <c r="S26" s="19" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="T26" s="6" t="s">
         <v>17</v>
@@ -14243,7 +14196,7 @@
         <v>17</v>
       </c>
       <c r="S27" s="19" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="T27" s="6" t="s">
         <v>17</v>
@@ -14297,7 +14250,7 @@
         <v>17</v>
       </c>
       <c r="S28" s="19" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="T28" s="6" t="s">
         <v>17</v>
@@ -14351,7 +14304,7 @@
         <v>17</v>
       </c>
       <c r="S29" s="19" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="T29" s="6" t="s">
         <v>17</v>
@@ -14405,7 +14358,7 @@
         <v>17</v>
       </c>
       <c r="S30" s="19" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="T30" s="6" t="s">
         <v>17</v>
@@ -14459,7 +14412,7 @@
         <v>17</v>
       </c>
       <c r="S31" s="19" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="T31" s="6" t="s">
         <v>17</v>
@@ -14513,7 +14466,7 @@
         <v>17</v>
       </c>
       <c r="S32" s="19" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="T32" s="6" t="s">
         <v>17</v>
@@ -14567,7 +14520,7 @@
         <v>17</v>
       </c>
       <c r="S33" s="19" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="T33" s="6" t="s">
         <v>17</v>
@@ -14621,7 +14574,7 @@
         <v>17</v>
       </c>
       <c r="S34" s="19" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="T34" s="6" t="s">
         <v>17</v>
@@ -14675,7 +14628,7 @@
         <v>17</v>
       </c>
       <c r="S35" s="19" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="T35" s="6" t="s">
         <v>17</v>
@@ -14749,7 +14702,7 @@
         <v>17</v>
       </c>
       <c r="S37" s="19" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="T37" s="6" t="s">
         <v>17</v>
@@ -14802,7 +14755,7 @@
         <v>17</v>
       </c>
       <c r="S38" s="19" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="T38" s="6" t="s">
         <v>17</v>
@@ -15026,7 +14979,7 @@
         <v>411</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -15395,7 +15348,7 @@
         <v>416</v>
       </c>
       <c r="B1" s="43" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C1" s="43" t="s">
         <v>417</v>
@@ -15407,10 +15360,10 @@
         <v>419</v>
       </c>
       <c r="F1" s="43" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="G1" s="43" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
     </row>
     <row r="2" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -15469,7 +15422,7 @@
         <v>312</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="5" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -15490,7 +15443,7 @@
         <v>312</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="6" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -15511,12 +15464,12 @@
         <v>312</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="7" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="114" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B7" s="153">
         <v>60</v>
@@ -15532,7 +15485,7 @@
         <v>312</v>
       </c>
       <c r="F7" s="153" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="8" spans="1:7" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -15542,7 +15495,7 @@
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="F8" s="1"/>
     </row>
@@ -15560,7 +15513,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F0484E2-9992-4491-920F-B8AE57D8A0EE}">
-  <dimension ref="A1:K33"/>
+  <dimension ref="A1:V32"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.81640625" bestFit="1" customWidth="1"/>
@@ -15574,7 +15527,7 @@
     <col min="11" max="11" width="49.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:22" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
@@ -15603,13 +15556,13 @@
         <v>428</v>
       </c>
       <c r="J1" s="38" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="K1" s="123" t="s">
         <v>182</v>
       </c>
     </row>
-    <row r="2" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>429</v>
       </c>
@@ -15632,7 +15585,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>432</v>
       </c>
@@ -15655,7 +15608,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>433</v>
       </c>
@@ -15681,10 +15634,10 @@
         <v>10</v>
       </c>
       <c r="K4" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>434</v>
       </c>
@@ -15707,12 +15660,12 @@
         <v>10</v>
       </c>
       <c r="K5" t="s">
-        <v>536</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="6" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A6" s="155" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B6" s="156">
         <v>800</v>
@@ -15734,9 +15687,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="155" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B7" s="156">
         <v>1200</v>
@@ -15758,9 +15711,9 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="155" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="B8" s="156">
         <v>2200</v>
@@ -15782,12 +15735,12 @@
         <v>10</v>
       </c>
       <c r="K8" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="9" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="101" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="B9" s="124">
         <v>3600</v>
@@ -15810,163 +15763,143 @@
       </c>
       <c r="I9" s="125"/>
       <c r="K9" t="s">
-        <v>491</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="84" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="10" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O10" s="84" t="s">
         <v>435</v>
       </c>
-      <c r="B10" s="83">
+      <c r="P10" s="83">
         <v>130</v>
       </c>
-      <c r="C10" s="83">
+      <c r="Q10" s="83">
         <v>276</v>
       </c>
-      <c r="D10" s="83">
+      <c r="R10" s="83">
         <v>22</v>
       </c>
-      <c r="E10" s="83" t="s">
+      <c r="S10" s="83" t="s">
         <v>237</v>
       </c>
-      <c r="G10" s="83" t="s">
+      <c r="U10" s="83" t="s">
         <v>431</v>
       </c>
-      <c r="H10">
+      <c r="V10">
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A11" s="84" t="s">
+    <row r="11" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O11" s="84" t="s">
         <v>436</v>
       </c>
-      <c r="B11" s="83">
+      <c r="P11" s="83">
         <v>145</v>
       </c>
-      <c r="C11" s="83">
+      <c r="Q11" s="83">
         <v>365</v>
       </c>
-      <c r="D11" s="83">
+      <c r="R11" s="83">
         <v>22</v>
       </c>
-      <c r="E11" s="83" t="s">
+      <c r="S11" s="83" t="s">
         <v>237</v>
       </c>
-      <c r="F11" s="83">
+      <c r="T11" s="83">
         <v>200</v>
       </c>
-      <c r="G11" s="83" t="s">
+      <c r="U11" s="83" t="s">
         <v>431</v>
       </c>
-      <c r="H11">
+      <c r="V11">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A12" s="84" t="s">
+    <row r="12" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O12" s="84" t="s">
         <v>437</v>
       </c>
-      <c r="B12" s="83">
+      <c r="P12" s="83">
         <v>332</v>
       </c>
-      <c r="C12" s="83">
+      <c r="Q12" s="83">
         <v>1444</v>
       </c>
-      <c r="D12" s="83">
+      <c r="R12" s="83">
         <v>22</v>
       </c>
-      <c r="E12" s="83" t="s">
+      <c r="S12" s="83" t="s">
         <v>237</v>
       </c>
-      <c r="F12" s="83">
+      <c r="T12" s="83">
         <v>460</v>
       </c>
-      <c r="G12" s="83">
+      <c r="U12" s="83">
         <v>30</v>
       </c>
-      <c r="H12">
+      <c r="V12">
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A13" s="84" t="s">
+    <row r="13" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="I13" s="7"/>
+      <c r="O13" s="84" t="s">
         <v>438</v>
       </c>
-      <c r="B13" s="83">
+      <c r="P13" s="83">
         <v>542</v>
       </c>
-      <c r="C13" s="83">
+      <c r="Q13" s="83">
         <v>1863</v>
       </c>
-      <c r="D13" s="83">
+      <c r="R13" s="83">
         <v>22</v>
       </c>
-      <c r="E13" s="83" t="s">
+      <c r="S13" s="83" t="s">
         <v>237</v>
       </c>
-      <c r="G13" s="83">
+      <c r="U13" s="83">
         <v>40</v>
       </c>
-      <c r="H13">
+      <c r="V13">
         <v>10</v>
       </c>
-      <c r="I13" s="7"/>
-    </row>
-    <row r="14" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="84" t="s">
+    </row>
+    <row r="14" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="O14" s="84" t="s">
         <v>439</v>
       </c>
-      <c r="B14" s="83">
+      <c r="P14" s="83">
         <v>1000</v>
       </c>
-      <c r="C14" s="83">
+      <c r="Q14" s="83">
         <v>3560</v>
       </c>
-      <c r="D14" s="83">
+      <c r="R14" s="83">
         <v>12</v>
       </c>
-      <c r="E14" s="83" t="s">
+      <c r="S14" s="83" t="s">
         <v>237</v>
       </c>
-      <c r="G14" s="83">
+      <c r="U14" s="83">
         <v>50</v>
       </c>
-      <c r="H14">
+      <c r="V14">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="84"/>
       <c r="B15" s="83"/>
       <c r="C15" s="83"/>
       <c r="D15" s="83"/>
       <c r="E15" s="83"/>
     </row>
-    <row r="16" spans="1:11" ht="49" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>440</v>
-      </c>
-      <c r="B16" s="83">
-        <v>145</v>
-      </c>
-      <c r="C16" s="83">
-        <v>365</v>
-      </c>
-      <c r="D16" s="6">
-        <v>22</v>
-      </c>
-      <c r="E16" s="83" t="s">
-        <v>301</v>
-      </c>
-      <c r="F16" s="83">
-        <v>200</v>
-      </c>
-      <c r="G16" s="83" t="s">
-        <v>431</v>
-      </c>
-      <c r="H16">
-        <v>10</v>
-      </c>
+    <row r="16" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B16" s="83"/>
+      <c r="C16" s="83"/>
+      <c r="E16" s="83"/>
+      <c r="G16" s="83"/>
     </row>
     <row r="17" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B17" s="83"/>
@@ -15975,8 +15908,10 @@
       <c r="G17" s="83"/>
     </row>
     <row r="18" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="84"/>
       <c r="B18" s="83"/>
       <c r="C18" s="83"/>
+      <c r="D18" s="83"/>
       <c r="E18" s="83"/>
       <c r="G18" s="83"/>
     </row>
@@ -15988,28 +15923,20 @@
       <c r="E19" s="83"/>
       <c r="G19" s="83"/>
     </row>
-    <row r="20" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="84"/>
-      <c r="B20" s="83"/>
-      <c r="C20" s="83"/>
-      <c r="D20" s="83"/>
-      <c r="E20" s="83"/>
-      <c r="G20" s="83"/>
-    </row>
-    <row r="21" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="27" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="26" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D26"/>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="D27"/>
     </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="D28"/>
-    </row>
-    <row r="29" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="K30" s="7"/>
-    </row>
+    <row r="28" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
+    <row r="29" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="K29" s="7"/>
+    </row>
+    <row r="30" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="31" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
     <row r="32" spans="1:11" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="33" ht="40" customHeight="1" x14ac:dyDescent="0.35"/>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16037,25 +15964,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>444</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>445</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>446</v>
       </c>
       <c r="D1" s="6" t="s">
         <v>13</v>
       </c>
       <c r="E1" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="F1" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="G1" s="6" t="s">
         <v>448</v>
       </c>
-      <c r="G1" s="6" t="s">
-        <v>449</v>
-      </c>
       <c r="H1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
@@ -16068,7 +15995,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="25" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="B3" s="6">
         <v>300</v>
@@ -16090,12 +16017,12 @@
         <v>40</v>
       </c>
       <c r="H3" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="25" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="B4" s="6">
         <v>350</v>
@@ -16117,12 +16044,12 @@
         <v>40</v>
       </c>
       <c r="H4" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="25" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="B5" s="6">
         <v>400</v>
@@ -16144,12 +16071,12 @@
         <v>40</v>
       </c>
       <c r="H5" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="25" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="B6" s="6">
         <v>450</v>
@@ -16171,12 +16098,12 @@
         <v>40</v>
       </c>
       <c r="H6" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="25" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="B7" s="6">
         <v>300</v>
@@ -16198,12 +16125,12 @@
         <v>60</v>
       </c>
       <c r="H7" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="25" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="B8" s="6">
         <v>350</v>
@@ -16225,12 +16152,12 @@
         <v>60</v>
       </c>
       <c r="H8" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="25" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B9" s="6">
         <v>400</v>
@@ -16252,12 +16179,12 @@
         <v>60</v>
       </c>
       <c r="H9" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="25" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B10" s="6">
         <v>450</v>
@@ -16279,7 +16206,7 @@
         <v>60</v>
       </c>
       <c r="H10" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
@@ -16292,7 +16219,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="25" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="B13" s="6">
         <v>300</v>
@@ -16314,12 +16241,12 @@
         <v>92</v>
       </c>
       <c r="H13" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="25" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="B14" s="6">
         <v>350</v>
@@ -16341,12 +16268,12 @@
         <v>92</v>
       </c>
       <c r="H14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="25" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="B15" s="6">
         <v>400</v>
@@ -16368,12 +16295,12 @@
         <v>92</v>
       </c>
       <c r="H15" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="25" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="B16" s="6">
         <v>450</v>
@@ -16395,12 +16322,12 @@
         <v>92</v>
       </c>
       <c r="H16" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A17" s="25" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="B17" s="6">
         <v>500</v>
@@ -16422,12 +16349,12 @@
         <v>92</v>
       </c>
       <c r="H17" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A18" s="25" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="B18" s="6">
         <v>550</v>
@@ -16449,12 +16376,12 @@
         <v>92</v>
       </c>
       <c r="H18" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A19" s="45" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="B19" s="46">
         <v>600</v>
@@ -16476,7 +16403,7 @@
         <v>92</v>
       </c>
       <c r="H19" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.35">
@@ -16484,7 +16411,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A21" s="25" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="B21" s="6">
         <v>300</v>
@@ -16506,12 +16433,12 @@
         <v>6</v>
       </c>
       <c r="H21" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A22" s="25" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="B22" s="6">
         <v>350</v>
@@ -16533,12 +16460,12 @@
         <v>6</v>
       </c>
       <c r="H22" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A23" s="25" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="B23" s="6">
         <v>400</v>
@@ -16560,12 +16487,12 @@
         <v>8</v>
       </c>
       <c r="H23" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A24" s="25" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="B24" s="6">
         <v>450</v>
@@ -16587,12 +16514,12 @@
         <v>8</v>
       </c>
       <c r="H24" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A25" s="25" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="B25" s="6">
         <v>500</v>
@@ -16614,12 +16541,12 @@
         <v>10</v>
       </c>
       <c r="H25" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A26" s="25" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="B26" s="6">
         <v>550</v>
@@ -16641,12 +16568,12 @@
         <v>10</v>
       </c>
       <c r="H26" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A27" s="45" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="B27" s="46">
         <v>600</v>
@@ -16668,12 +16595,12 @@
         <v>10</v>
       </c>
       <c r="H27" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A30" s="25" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="B30" s="6">
         <v>135</v>
@@ -16695,12 +16622,12 @@
         <v>1E-3</v>
       </c>
       <c r="H30" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A31" s="25" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="B31" s="6">
         <v>180</v>
@@ -16722,12 +16649,12 @@
         <v>1E-3</v>
       </c>
       <c r="H31" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A32" s="25" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B32" s="6">
         <v>205</v>
@@ -16749,12 +16676,12 @@
         <v>1E-3</v>
       </c>
       <c r="H32" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A33" s="25" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="B33" s="6">
         <v>250</v>
@@ -16776,12 +16703,12 @@
         <v>1E-3</v>
       </c>
       <c r="H33" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A34" s="25" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="B34" s="6">
         <v>300</v>
@@ -16803,12 +16730,12 @@
         <v>1E-3</v>
       </c>
       <c r="H34" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A35" s="25" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="B35" s="6">
         <v>350</v>
@@ -16830,7 +16757,7 @@
         <v>1E-3</v>
       </c>
       <c r="H35" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
   </sheetData>
@@ -16854,7 +16781,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="C1" t="s">
         <v>135</v>
@@ -16873,7 +16800,7 @@
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="B3">
         <v>1875</v>
@@ -17196,7 +17123,7 @@
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="166" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="B2" s="166"/>
       <c r="C2" s="166"/>
@@ -17206,22 +17133,22 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
+        <v>515</v>
+      </c>
+      <c r="B4" t="s">
         <v>516</v>
       </c>
-      <c r="B4" t="s">
-        <v>517</v>
-      </c>
       <c r="C4" s="6" t="s">
+        <v>511</v>
+      </c>
+      <c r="D4" s="6" t="s">
         <v>512</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="E4" s="6" t="s">
         <v>513</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="F4" s="6" t="s">
         <v>514</v>
-      </c>
-      <c r="F4" s="6" t="s">
-        <v>515</v>
       </c>
       <c r="G4" s="6"/>
       <c r="H4" s="6"/>
@@ -17233,7 +17160,7 @@
         <v>138</v>
       </c>
       <c r="B5" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C5" s="6">
         <v>1000</v>
@@ -17257,7 +17184,7 @@
         <v>143</v>
       </c>
       <c r="B6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C6" s="6">
         <v>1000</v>
@@ -17277,7 +17204,7 @@
         <v>144</v>
       </c>
       <c r="B7" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C7" s="6">
         <v>1000</v>
@@ -17301,7 +17228,7 @@
         <v>162</v>
       </c>
       <c r="B8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C8" s="6">
         <v>1000</v>
@@ -17325,7 +17252,7 @@
         <v>146</v>
       </c>
       <c r="B9" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C9" s="6">
         <v>1000</v>
@@ -17349,7 +17276,7 @@
         <v>138</v>
       </c>
       <c r="B11" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C11" s="6">
         <v>1000</v>
@@ -17369,7 +17296,7 @@
         <v>143</v>
       </c>
       <c r="B12" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C12" s="6">
         <v>1000</v>
@@ -17389,7 +17316,7 @@
         <v>144</v>
       </c>
       <c r="B13" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C13" s="6">
         <v>1000</v>
@@ -17409,7 +17336,7 @@
         <v>162</v>
       </c>
       <c r="B14" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C14" s="6">
         <v>1000</v>
@@ -17429,7 +17356,7 @@
         <v>146</v>
       </c>
       <c r="B15" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C15" s="6">
         <v>1000</v>
@@ -17449,7 +17376,7 @@
         <v>138</v>
       </c>
       <c r="B17" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C17" s="6">
         <v>1000</v>
@@ -17469,7 +17396,7 @@
         <v>143</v>
       </c>
       <c r="B18" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C18" s="6">
         <v>1000</v>
@@ -17489,7 +17416,7 @@
         <v>144</v>
       </c>
       <c r="B19" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C19" s="6">
         <v>1000</v>
@@ -17509,7 +17436,7 @@
         <v>162</v>
       </c>
       <c r="B20" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C20" s="6">
         <v>1000</v>
@@ -17529,7 +17456,7 @@
         <v>146</v>
       </c>
       <c r="B21" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C21" s="6">
         <v>1000</v>
@@ -17549,7 +17476,7 @@
         <v>138</v>
       </c>
       <c r="B23" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.35">
@@ -17557,7 +17484,7 @@
         <v>143</v>
       </c>
       <c r="B24" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.35">
@@ -17565,7 +17492,7 @@
         <v>144</v>
       </c>
       <c r="B25" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.35">
@@ -17573,7 +17500,7 @@
         <v>162</v>
       </c>
       <c r="B26" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.35">
@@ -17581,7 +17508,7 @@
         <v>146</v>
       </c>
       <c r="B27" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
     </row>
   </sheetData>
@@ -17626,7 +17553,7 @@
         <v>64</v>
       </c>
       <c r="H1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.35">
@@ -17640,10 +17567,10 @@
         <v>1</v>
       </c>
       <c r="H2" t="s">
+        <v>577</v>
+      </c>
+      <c r="K2" t="s">
         <v>578</v>
-      </c>
-      <c r="K2" t="s">
-        <v>579</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.35">
@@ -17657,10 +17584,10 @@
         <v>2</v>
       </c>
       <c r="H3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
@@ -17674,10 +17601,10 @@
         <v>3</v>
       </c>
       <c r="H4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
@@ -17691,10 +17618,10 @@
         <v>5</v>
       </c>
       <c r="H5" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="K5" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.35">
@@ -17708,7 +17635,7 @@
         <v>6</v>
       </c>
       <c r="K6" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.35">
@@ -17722,7 +17649,7 @@
         <v>7</v>
       </c>
       <c r="K7" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="16" x14ac:dyDescent="0.35">
@@ -18078,43 +18005,43 @@
         <v>168</v>
       </c>
       <c r="E1" s="126" t="s">
+        <v>547</v>
+      </c>
+      <c r="F1" s="19" t="s">
         <v>548</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="G1" s="19" t="s">
         <v>549</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="H1" s="130" t="s">
+        <v>635</v>
+      </c>
+      <c r="I1" s="19" t="s">
         <v>550</v>
       </c>
-      <c r="H1" s="130" t="s">
-        <v>636</v>
-      </c>
-      <c r="I1" s="19" t="s">
+      <c r="J1" s="19" t="s">
+        <v>556</v>
+      </c>
+      <c r="K1" s="19" t="s">
+        <v>552</v>
+      </c>
+      <c r="L1" s="19" t="s">
         <v>551</v>
       </c>
-      <c r="J1" s="19" t="s">
-        <v>557</v>
-      </c>
-      <c r="K1" s="19" t="s">
+      <c r="M1" s="19" t="s">
         <v>553</v>
       </c>
-      <c r="L1" s="19" t="s">
-        <v>552</v>
-      </c>
-      <c r="M1" s="19" t="s">
+      <c r="N1" s="19" t="s">
         <v>554</v>
       </c>
-      <c r="N1" s="19" t="s">
+      <c r="O1" s="19" t="s">
         <v>555</v>
       </c>
-      <c r="O1" s="19" t="s">
-        <v>556</v>
-      </c>
       <c r="P1" s="129" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="Q1" s="129" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
     </row>
     <row r="2" spans="1:17" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -18164,7 +18091,7 @@
         <v>55</v>
       </c>
       <c r="P2" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="3" spans="1:17" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -18215,12 +18142,12 @@
         <v>55</v>
       </c>
       <c r="P3" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="4" spans="1:17" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="136" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B4" s="18">
         <f>B2+0.72+0.5</f>
@@ -18266,12 +18193,12 @@
         <v>55</v>
       </c>
       <c r="P4" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="5" spans="1:17" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="136" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="B5" s="18">
         <f>B2+0.85+0.5</f>
@@ -18317,7 +18244,7 @@
         <v>55</v>
       </c>
       <c r="P5" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="6" spans="1:17" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -18367,12 +18294,12 @@
         <v>55</v>
       </c>
       <c r="P6" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="7" spans="1:17" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="136" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B7" s="18">
         <f>B6+0.72+0.5</f>
@@ -18418,12 +18345,12 @@
         <v>55</v>
       </c>
       <c r="P7" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="8" spans="1:17" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A8" s="136" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="B8" s="18">
         <f>B6+0.85+0.5</f>
@@ -18469,7 +18396,7 @@
         <v>55</v>
       </c>
       <c r="P8" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="9" spans="1:17" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -18519,7 +18446,7 @@
         <v>55</v>
       </c>
       <c r="P9" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -18569,12 +18496,12 @@
         <v>55</v>
       </c>
       <c r="P10" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A11" s="137" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B11" s="135">
         <f>0.82+0.72</f>
@@ -18620,12 +18547,12 @@
         <v>55</v>
       </c>
       <c r="P11" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="12" spans="1:17" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A12" s="138" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B12" s="18">
         <v>0.95</v>
@@ -18670,12 +18597,12 @@
         <v>55</v>
       </c>
       <c r="P12" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A13" s="138" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="B13" s="51">
         <v>1.2</v>
@@ -18720,7 +18647,7 @@
         <v>55</v>
       </c>
       <c r="P13" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -18770,7 +18697,7 @@
         <v>55</v>
       </c>
       <c r="P14" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -18820,7 +18747,7 @@
         <v>55</v>
       </c>
       <c r="P15" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="16" spans="1:17" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -18870,7 +18797,7 @@
         <v>22</v>
       </c>
       <c r="P16" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -18920,7 +18847,7 @@
         <v>55</v>
       </c>
       <c r="P17" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="16" x14ac:dyDescent="0.35">
@@ -18970,7 +18897,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="133" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D1" s="133" t="s">
         <v>135</v>
@@ -18982,37 +18909,37 @@
         <v>13</v>
       </c>
       <c r="G1" s="19" t="s">
+        <v>547</v>
+      </c>
+      <c r="H1" s="19" t="s">
         <v>548</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="I1" s="19" t="s">
         <v>549</v>
       </c>
-      <c r="I1" s="19" t="s">
+      <c r="J1" s="19" t="s">
         <v>550</v>
       </c>
-      <c r="J1" s="19" t="s">
+      <c r="K1" s="19" t="s">
+        <v>556</v>
+      </c>
+      <c r="L1" s="19" t="s">
+        <v>552</v>
+      </c>
+      <c r="M1" s="19" t="s">
         <v>551</v>
       </c>
-      <c r="K1" s="19" t="s">
-        <v>557</v>
-      </c>
-      <c r="L1" s="19" t="s">
+      <c r="N1" s="19" t="s">
         <v>553</v>
       </c>
-      <c r="M1" s="19" t="s">
-        <v>552</v>
-      </c>
-      <c r="N1" s="19" t="s">
+      <c r="O1" s="19" t="s">
         <v>554</v>
       </c>
-      <c r="O1" s="19" t="s">
+      <c r="P1" s="19" t="s">
         <v>555</v>
       </c>
-      <c r="P1" s="19" t="s">
-        <v>556</v>
-      </c>
       <c r="Q1" s="129" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="U1" s="6" t="s">
         <v>180</v>
@@ -19024,7 +18951,7 @@
         <v>149</v>
       </c>
       <c r="X1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="Y1" s="6" t="s">
         <v>182</v>
@@ -19087,10 +19014,10 @@
         <v>0</v>
       </c>
       <c r="W2" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X2" s="56" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="Y2" s="1"/>
     </row>
@@ -19151,10 +19078,10 @@
         <v>0</v>
       </c>
       <c r="W3" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X3" s="56" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="Y3" s="1"/>
     </row>
@@ -19215,10 +19142,10 @@
         <v>0</v>
       </c>
       <c r="W4" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X4" s="56" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="Y4" s="1"/>
     </row>
@@ -19279,10 +19206,10 @@
         <v>0</v>
       </c>
       <c r="W5" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="X5" s="56" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="Y5" s="1"/>
     </row>
@@ -19291,7 +19218,7 @@
         <v>189</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>22</v>
@@ -19343,21 +19270,21 @@
         <v>4</v>
       </c>
       <c r="W6" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="X6" s="56" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="Y6" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="7" spans="1:25" s="56" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A7" s="139" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B7" s="56" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>22</v>
@@ -19409,13 +19336,13 @@
         <v>4</v>
       </c>
       <c r="W7" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="X7" s="56" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="Y7" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="8" spans="1:25" s="56" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -19486,10 +19413,10 @@
       <c r="U9" s="1"/>
       <c r="V9" s="1"/>
       <c r="W9" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="X9" s="56" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="10" spans="1:25" s="56" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -19545,10 +19472,10 @@
       <c r="U10" s="1"/>
       <c r="V10" s="1"/>
       <c r="W10" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="X10" s="56" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="11" spans="1:25" s="56" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -19604,10 +19531,10 @@
       <c r="U11" s="1"/>
       <c r="V11" s="1"/>
       <c r="W11" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="X11" s="56" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="12" spans="1:25" s="56" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -19615,7 +19542,7 @@
         <v>193</v>
       </c>
       <c r="B12" s="56" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>22</v>
@@ -19663,10 +19590,10 @@
       <c r="U12" s="1"/>
       <c r="V12" s="1"/>
       <c r="W12" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="X12" s="56" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="13" spans="1:25" s="56" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -19723,7 +19650,7 @@
       <c r="V13" s="1"/>
       <c r="W13" s="1"/>
       <c r="X13" s="56" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="14" spans="1:25" s="56" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -19780,7 +19707,7 @@
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
       <c r="X14" s="56" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="15" spans="1:25" s="56" customFormat="1" ht="50.15" customHeight="1" x14ac:dyDescent="0.35">
@@ -19837,7 +19764,7 @@
       <c r="V15" s="1"/>
       <c r="W15" s="1"/>
       <c r="X15" s="56" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
   </sheetData>
@@ -19881,40 +19808,40 @@
         <v>152</v>
       </c>
       <c r="F1" s="29" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="G1" s="29" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H1" s="29" t="s">
+        <v>547</v>
+      </c>
+      <c r="I1" s="29" t="s">
         <v>548</v>
       </c>
-      <c r="I1" s="29" t="s">
+      <c r="J1" s="29" t="s">
         <v>549</v>
       </c>
-      <c r="J1" s="29" t="s">
+      <c r="K1" s="29" t="s">
         <v>550</v>
       </c>
-      <c r="K1" s="29" t="s">
+      <c r="L1" s="29" t="s">
+        <v>556</v>
+      </c>
+      <c r="M1" s="29" t="s">
+        <v>552</v>
+      </c>
+      <c r="N1" s="29" t="s">
         <v>551</v>
       </c>
-      <c r="L1" s="29" t="s">
-        <v>557</v>
-      </c>
-      <c r="M1" s="29" t="s">
+      <c r="O1" s="29" t="s">
         <v>553</v>
       </c>
-      <c r="N1" s="29" t="s">
-        <v>552</v>
-      </c>
-      <c r="O1" s="29" t="s">
+      <c r="P1" s="29" t="s">
         <v>554</v>
       </c>
-      <c r="P1" s="29" t="s">
+      <c r="Q1" s="29" t="s">
         <v>555</v>
-      </c>
-      <c r="Q1" s="29" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
@@ -20237,18 +20164,18 @@
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="141" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B8" s="142" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="140" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>155</v>
@@ -20298,10 +20225,10 @@
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="140" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="C10" s="6" t="s">
         <v>155</v>
@@ -20351,10 +20278,10 @@
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="140" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D11" s="6">
         <v>5</v>
@@ -20401,10 +20328,10 @@
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="140" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="C12" s="6" t="s">
         <v>155</v>
@@ -20454,10 +20381,10 @@
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="140" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="C13" s="6" t="s">
         <v>155</v>
@@ -20507,10 +20434,10 @@
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="140" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C14" s="6" t="s">
         <v>155</v>
@@ -20613,10 +20540,10 @@
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="140" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C16" s="6" t="s">
         <v>155</v>
@@ -20666,7 +20593,7 @@
     </row>
     <row r="21" spans="2:4" x14ac:dyDescent="0.35">
       <c r="B21" s="140" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D21" s="6">
         <v>92</v>
@@ -20738,19 +20665,19 @@
         <v>206</v>
       </c>
       <c r="M1" s="14" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="N1" s="14" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="O1" s="14" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="P1" s="165" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="Q1" s="14" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.35">
@@ -20875,7 +20802,7 @@
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="15" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B5" s="15" t="s">
         <v>214</v>
@@ -20904,7 +20831,7 @@
         <v>22</v>
       </c>
       <c r="K5" s="14" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="L5" s="14">
         <f>D5/25.4</f>
@@ -20918,13 +20845,13 @@
       </c>
       <c r="O5" s="14"/>
       <c r="P5" s="14" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="Q5" s="14"/>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="15" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="B6" s="15" t="s">
         <v>214</v>
@@ -20953,7 +20880,7 @@
         <v>22</v>
       </c>
       <c r="K6" s="14" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="L6" s="14">
         <f t="shared" ref="L6:L12" si="4">D6/25.4</f>
@@ -20967,13 +20894,13 @@
       </c>
       <c r="O6" s="14"/>
       <c r="P6" s="14" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="Q6" s="14"/>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="14" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="B7" s="14" t="s">
         <v>214</v>
@@ -21002,7 +20929,7 @@
         <v>22</v>
       </c>
       <c r="K7" s="14" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="L7" s="14">
         <f t="shared" ref="L7" si="5">D7/25.4</f>
@@ -21016,13 +20943,13 @@
       </c>
       <c r="O7" s="14"/>
       <c r="P7" s="14" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="Q7" s="14"/>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="15" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B8" s="15" t="s">
         <v>214</v>
@@ -21051,7 +20978,7 @@
         <v>22</v>
       </c>
       <c r="K8" s="14" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="L8" s="14">
         <f t="shared" si="4"/>
@@ -21065,13 +20992,13 @@
       </c>
       <c r="O8" s="14"/>
       <c r="P8" s="14" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="Q8" s="14"/>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="15" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B9" s="15" t="s">
         <v>214</v>
@@ -21100,7 +21027,7 @@
         <v>22</v>
       </c>
       <c r="K9" s="14" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="L9" s="14">
         <f t="shared" si="4"/>
@@ -21114,13 +21041,13 @@
       </c>
       <c r="O9" s="14"/>
       <c r="P9" s="14" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="Q9" s="14"/>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="98" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B10" s="98" t="s">
         <v>214</v>
@@ -21149,7 +21076,7 @@
         <v>22</v>
       </c>
       <c r="K10" s="97" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="L10" s="14">
         <f t="shared" si="4"/>
@@ -21159,17 +21086,17 @@
         <v>55</v>
       </c>
       <c r="N10" s="14" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="O10" s="14"/>
       <c r="P10" s="14" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="Q10" s="14"/>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="97" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="B11" s="97" t="s">
         <v>214</v>
@@ -21198,7 +21125,7 @@
         <v>22</v>
       </c>
       <c r="K11" s="97" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="L11" s="14">
         <f t="shared" si="4"/>
@@ -21208,17 +21135,17 @@
         <v>55</v>
       </c>
       <c r="N11" s="14" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="O11" s="14"/>
       <c r="P11" s="14" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="Q11" s="14"/>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="97" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="B12" s="97" t="s">
         <v>214</v>
@@ -21255,23 +21182,23 @@
         <v>55</v>
       </c>
       <c r="N12" s="14" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="O12" s="14"/>
       <c r="P12" s="14" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="Q12" s="14"/>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="95" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B13" s="95" t="s">
         <v>214</v>
       </c>
       <c r="C13" s="95" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="D13" s="96">
         <v>273</v>
@@ -21299,7 +21226,7 @@
         <v>55</v>
       </c>
       <c r="N13" s="14" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="O13" s="14"/>
       <c r="P13" s="14"/>
@@ -21323,18 +21250,18 @@
   <sheetData>
     <row r="3" spans="2:8" x14ac:dyDescent="0.35">
       <c r="B3" s="148" t="s">
+        <v>660</v>
+      </c>
+      <c r="C3" s="148" t="s">
         <v>661</v>
-      </c>
-      <c r="C3" s="148" t="s">
-        <v>662</v>
       </c>
     </row>
     <row r="4" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="B4" s="149" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C4" s="149" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E4">
         <v>145</v>
@@ -21345,10 +21272,10 @@
     </row>
     <row r="5" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="B5" s="149" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C5" s="149" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="E5">
         <v>130</v>
@@ -21367,10 +21294,10 @@
     </row>
     <row r="6" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="B6" s="149" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C6" s="149" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="E6">
         <v>120</v>
@@ -21389,10 +21316,10 @@
     </row>
     <row r="7" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="B7" s="149" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C7" s="149" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E7">
         <v>110</v>
@@ -21411,10 +21338,10 @@
     </row>
     <row r="8" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="B8" s="149" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C8" s="149" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="E8">
         <v>95</v>
@@ -21433,10 +21360,10 @@
     </row>
     <row r="9" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="B9" s="149" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C9" s="149" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="E9">
         <v>75</v>
@@ -21455,10 +21382,10 @@
     </row>
     <row r="10" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="B10" s="149" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C10" s="149" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="E10">
         <v>65</v>
@@ -21477,10 +21404,10 @@
     </row>
     <row r="11" spans="2:8" ht="16.5" x14ac:dyDescent="0.35">
       <c r="B11" s="149" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C11" s="149" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="E11">
         <v>55</v>
@@ -21499,7 +21426,7 @@
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.35">
       <c r="C13" s="150" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D13" s="114"/>
       <c r="E13" s="114"/>
@@ -21540,16 +21467,16 @@
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="C1" s="6" t="s">
+        <v>481</v>
+      </c>
+      <c r="D1" t="s">
         <v>482</v>
-      </c>
-      <c r="D1" t="s">
-        <v>483</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>229</v>
@@ -21570,13 +21497,13 @@
         <v>234</v>
       </c>
       <c r="K1" s="6" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="L1" s="6" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="P1" t="s">
         <v>256</v>
@@ -21584,7 +21511,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A2" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>213</v>
@@ -21608,7 +21535,7 @@
       </c>
       <c r="H2" s="6"/>
       <c r="I2" s="6" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="J2" s="6" t="s">
         <v>312</v>
@@ -21628,7 +21555,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A3" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>213</v>
@@ -21670,7 +21597,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>213</v>
@@ -21694,7 +21621,7 @@
       </c>
       <c r="H4" s="6"/>
       <c r="I4" s="6" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="J4" s="6" t="s">
         <v>312</v>
@@ -21714,7 +21641,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>213</v>
@@ -21756,7 +21683,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A6" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B6" s="99" t="s">
         <v>216</v>
@@ -21798,7 +21725,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A7" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B7" s="99" t="s">
         <v>216</v>
@@ -21822,7 +21749,7 @@
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="J7" s="6" t="s">
         <v>312</v>
@@ -21842,7 +21769,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A8" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B8" s="99" t="s">
         <v>216</v>
@@ -21884,7 +21811,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A9" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B9" s="99" t="s">
         <v>216</v>
@@ -21908,7 +21835,7 @@
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="J9" s="6" t="s">
         <v>312</v>
@@ -21928,7 +21855,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A10" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B10" s="99" t="s">
         <v>216</v>
@@ -22036,7 +21963,7 @@
       </c>
       <c r="H12" s="6"/>
       <c r="I12" s="6" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="J12" s="6" t="s">
         <v>312</v>
@@ -22122,7 +22049,7 @@
       </c>
       <c r="H14" s="6"/>
       <c r="I14" s="6" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="J14" s="6" t="s">
         <v>312</v>
@@ -22208,7 +22135,7 @@
       </c>
       <c r="H16" s="6"/>
       <c r="I16" s="6" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="J16" s="6" t="s">
         <v>312</v>
@@ -22294,7 +22221,7 @@
       </c>
       <c r="H18" s="6"/>
       <c r="I18" s="6" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="J18" s="6" t="s">
         <v>312</v>
@@ -22380,7 +22307,7 @@
       </c>
       <c r="H20" s="6"/>
       <c r="I20" s="6" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="J20" s="6" t="s">
         <v>312</v>
@@ -22424,7 +22351,7 @@
       </c>
       <c r="H21" s="115"/>
       <c r="I21" s="115" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="J21" s="6" t="s">
         <v>312</v>
@@ -22510,7 +22437,7 @@
       </c>
       <c r="H23" s="115"/>
       <c r="I23" s="115" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="J23" s="6" t="s">
         <v>312</v>
@@ -22638,7 +22565,7 @@
       </c>
       <c r="H26" s="6"/>
       <c r="I26" s="151" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="J26" s="6" t="s">
         <v>312</v>
@@ -22724,7 +22651,7 @@
       </c>
       <c r="H28" s="115"/>
       <c r="I28" s="115" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="J28" s="6" t="s">
         <v>312</v>
@@ -22852,7 +22779,7 @@
       </c>
       <c r="H31" s="115"/>
       <c r="I31" s="115" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="J31" s="6" t="s">
         <v>312</v>
@@ -22938,7 +22865,7 @@
       </c>
       <c r="H33" s="115"/>
       <c r="I33" s="115" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="J33" s="6" t="s">
         <v>312</v>
@@ -22982,7 +22909,7 @@
       </c>
       <c r="H34" s="6"/>
       <c r="I34" s="6" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="J34" s="6" t="s">
         <v>312</v>
@@ -23110,7 +23037,7 @@
       </c>
       <c r="H37" s="115"/>
       <c r="I37" s="115" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="J37" s="6" t="s">
         <v>312</v>
@@ -23595,7 +23522,7 @@
         <v>228</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C49" s="1">
         <f>Axles!F12</f>
@@ -23637,7 +23564,7 @@
         <v>228</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C50" s="1">
         <f>Axles!F12</f>
@@ -23679,7 +23606,7 @@
         <v>228</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C51" s="1">
         <f>Axles!F12</f>
@@ -23721,7 +23648,7 @@
         <v>228</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="C52" s="1">
         <f>Axles!F12</f>
@@ -23760,10 +23687,10 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A53" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C53" s="6">
         <f>Axles!F13</f>
@@ -23800,10 +23727,10 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A54" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C54" s="6">
         <f>Axles!F13</f>
@@ -23852,7 +23779,7 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A60" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B60" s="6"/>
       <c r="D60" s="6"/>
@@ -23873,7 +23800,7 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.35">
       <c r="A61" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B61" s="6"/>
       <c r="D61" s="6"/>
@@ -23970,7 +23897,7 @@
     </row>
     <row r="66" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A66" s="6" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B66" s="6"/>
       <c r="D66" s="6"/>
@@ -23991,7 +23918,7 @@
     </row>
     <row r="67" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A67" s="6" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B67" s="6"/>
       <c r="D67" s="6"/>
@@ -24293,7 +24220,7 @@
         <v>253</v>
       </c>
       <c r="T1" s="11" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="U1" s="127" t="s">
         <v>255</v>
@@ -24302,19 +24229,19 @@
         <v>256</v>
       </c>
       <c r="W1" s="11" t="s">
+        <v>629</v>
+      </c>
+      <c r="X1" s="11" t="s">
         <v>630</v>
       </c>
-      <c r="X1" s="11" t="s">
+      <c r="Y1" s="11" t="s">
         <v>631</v>
       </c>
-      <c r="Y1" s="11" t="s">
+      <c r="Z1" s="11" t="s">
         <v>632</v>
       </c>
-      <c r="Z1" s="11" t="s">
+      <c r="AA1" s="11" t="s">
         <v>633</v>
-      </c>
-      <c r="AA1" s="11" t="s">
-        <v>634</v>
       </c>
     </row>
     <row r="2" spans="1:27" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -24675,7 +24602,7 @@
     </row>
     <row r="9" spans="1:27" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A9" s="3" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>301</v>
@@ -24832,7 +24759,7 @@
       <c r="F12" s="104"/>
       <c r="G12" s="104"/>
       <c r="H12" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I12" s="104"/>
       <c r="J12" s="104"/>
@@ -24840,7 +24767,7 @@
       <c r="L12" s="104"/>
       <c r="M12" s="104"/>
       <c r="N12" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O12" s="107"/>
       <c r="P12" s="104"/>
@@ -24964,7 +24891,7 @@
     </row>
     <row r="15" spans="1:27" s="56" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A15" s="3" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>271</v>
@@ -25619,7 +25546,7 @@
       <c r="F27" s="104"/>
       <c r="G27" s="104"/>
       <c r="H27" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I27" s="104"/>
       <c r="J27" s="104"/>
@@ -25627,7 +25554,7 @@
       <c r="L27" s="104"/>
       <c r="M27" s="104"/>
       <c r="N27" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O27" s="107"/>
       <c r="P27" s="104"/>
@@ -25675,7 +25602,7 @@
         <v>55</v>
       </c>
       <c r="N28" s="94" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O28" s="46"/>
       <c r="P28" s="51"/>
@@ -25701,7 +25628,7 @@
       <c r="F29" s="104"/>
       <c r="G29" s="104"/>
       <c r="H29" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I29" s="104"/>
       <c r="J29" s="104"/>
@@ -25709,7 +25636,7 @@
       <c r="L29" s="104"/>
       <c r="M29" s="104"/>
       <c r="N29" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O29" s="107"/>
       <c r="P29" s="104"/>
@@ -26064,7 +25991,7 @@
       <c r="F37" s="104"/>
       <c r="G37" s="104"/>
       <c r="H37" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I37" s="104"/>
       <c r="J37" s="104"/>
@@ -26072,7 +25999,7 @@
       <c r="L37" s="104"/>
       <c r="M37" s="104"/>
       <c r="N37" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O37" s="107"/>
       <c r="P37" s="104"/>
@@ -26083,7 +26010,7 @@
     </row>
     <row r="38" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>301</v>
@@ -26132,7 +26059,7 @@
     </row>
     <row r="39" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>301</v>
@@ -26178,13 +26105,13 @@
         <v>750</v>
       </c>
       <c r="S39" s="111" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="U39" s="113"/>
     </row>
     <row r="40" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B40" s="1" t="s">
         <v>301</v>
@@ -26230,13 +26157,13 @@
         <v>1100</v>
       </c>
       <c r="S40" s="111" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="U40" s="113"/>
     </row>
     <row r="41" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>301</v>
@@ -26282,13 +26209,13 @@
         <v>1100</v>
       </c>
       <c r="S41" s="111" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="U41" s="113"/>
     </row>
     <row r="42" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>301</v>
@@ -26328,13 +26255,13 @@
         <v>22</v>
       </c>
       <c r="S42" s="111" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="U42" s="113"/>
     </row>
     <row r="43" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>301</v>
@@ -26378,7 +26305,7 @@
     </row>
     <row r="44" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B44" s="1" t="s">
         <v>301</v>
@@ -26422,7 +26349,7 @@
     </row>
     <row r="45" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>301</v>
@@ -26466,7 +26393,7 @@
     </row>
     <row r="46" spans="1:21" s="1" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B46" s="1" t="s">
         <v>301</v>
@@ -26525,7 +26452,7 @@
       <c r="F47" s="104"/>
       <c r="G47" s="104"/>
       <c r="H47" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I47" s="104"/>
       <c r="J47" s="104"/>
@@ -26533,7 +26460,7 @@
       <c r="L47" s="104"/>
       <c r="M47" s="104"/>
       <c r="N47" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O47" s="107"/>
       <c r="P47" s="104"/>
@@ -26625,7 +26552,7 @@
         <v>22</v>
       </c>
       <c r="S49" s="70" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
     </row>
     <row r="50" spans="1:21" s="3" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -26715,7 +26642,7 @@
         <v>22</v>
       </c>
       <c r="S51" s="70" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
     </row>
     <row r="52" spans="1:21" s="106" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -26735,7 +26662,7 @@
       <c r="F52" s="104"/>
       <c r="G52" s="104"/>
       <c r="H52" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I52" s="104"/>
       <c r="J52" s="104"/>
@@ -26743,7 +26670,7 @@
       <c r="L52" s="104"/>
       <c r="M52" s="104"/>
       <c r="N52" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O52" s="107"/>
       <c r="P52" s="104"/>
@@ -26914,7 +26841,7 @@
       <c r="F56" s="104"/>
       <c r="G56" s="104"/>
       <c r="H56" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I56" s="104"/>
       <c r="J56" s="104"/>
@@ -26922,7 +26849,7 @@
       <c r="L56" s="104"/>
       <c r="M56" s="104"/>
       <c r="N56" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O56" s="107"/>
       <c r="P56" s="104"/>
@@ -27276,7 +27203,7 @@
         <v>450</v>
       </c>
       <c r="S63" s="161" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="U63" s="157">
         <v>345.34</v>
@@ -27299,7 +27226,7 @@
       <c r="F64" s="104"/>
       <c r="G64" s="104"/>
       <c r="H64" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I64" s="104"/>
       <c r="J64" s="104"/>
@@ -27307,7 +27234,7 @@
       <c r="L64" s="104"/>
       <c r="M64" s="104"/>
       <c r="N64" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O64" s="107"/>
       <c r="P64" s="104"/>
@@ -27494,7 +27421,7 @@
         <v>400</v>
       </c>
       <c r="S67" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="U67" s="147"/>
       <c r="V67" s="82"/>
@@ -27623,7 +27550,7 @@
         <v>650</v>
       </c>
       <c r="S70" s="1" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="U70" s="147">
         <v>498.07</v>
@@ -27646,7 +27573,7 @@
       <c r="F71" s="109"/>
       <c r="G71" s="104"/>
       <c r="H71" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I71" s="104"/>
       <c r="J71" s="104"/>
@@ -27654,7 +27581,7 @@
       <c r="L71" s="104"/>
       <c r="M71" s="104"/>
       <c r="N71" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O71" s="158"/>
       <c r="P71" s="104"/>
@@ -27717,7 +27644,7 @@
         <v>850</v>
       </c>
       <c r="S72" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="73" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -27775,7 +27702,7 @@
         <v>850</v>
       </c>
       <c r="S73" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
     </row>
     <row r="74" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -27833,7 +27760,7 @@
         <v>850</v>
       </c>
       <c r="S74" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="75" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -27891,7 +27818,7 @@
         <v>850</v>
       </c>
       <c r="S75" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="76" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -27949,7 +27876,7 @@
         <v>850</v>
       </c>
       <c r="S76" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="77" spans="1:23" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -28007,7 +27934,7 @@
         <v>850</v>
       </c>
       <c r="S77" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
     </row>
     <row r="78" spans="1:23" s="106" customFormat="1" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -28329,7 +28256,7 @@
       <c r="F84" s="109"/>
       <c r="G84" s="104"/>
       <c r="H84" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I84" s="104"/>
       <c r="J84" s="104"/>
@@ -28337,7 +28264,7 @@
       <c r="L84" s="104"/>
       <c r="M84" s="104"/>
       <c r="N84" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O84" s="158"/>
       <c r="P84" s="104"/>
@@ -28403,7 +28330,7 @@
         <v>1500</v>
       </c>
       <c r="S85" s="1" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="U85" s="110"/>
     </row>
@@ -28742,10 +28669,10 @@
         <v>266</v>
       </c>
       <c r="H92" s="94" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="N92" s="94" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O92" s="1"/>
       <c r="R92" s="1"/>
@@ -28756,7 +28683,7 @@
     </row>
     <row r="93" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A93" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B93" s="3" t="s">
         <v>312</v>
@@ -29462,7 +29389,7 @@
         <v>3125</v>
       </c>
       <c r="S104" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="T104" s="56" t="e" vm="1">
         <v>#VALUE!</v>
@@ -29700,7 +29627,7 @@
     </row>
     <row r="109" spans="1:22" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A109" s="125" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B109" s="125" t="s">
         <v>312</v>
@@ -29772,7 +29699,7 @@
       <c r="F110" s="104"/>
       <c r="G110" s="104"/>
       <c r="H110" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I110" s="104"/>
       <c r="J110" s="104"/>
@@ -29780,7 +29707,7 @@
       <c r="L110" s="104"/>
       <c r="M110" s="104"/>
       <c r="N110" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O110" s="107"/>
       <c r="P110" s="104"/>
@@ -30031,7 +29958,7 @@
       <c r="F115" s="104"/>
       <c r="G115" s="104"/>
       <c r="H115" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I115" s="104"/>
       <c r="J115" s="104"/>
@@ -30039,7 +29966,7 @@
       <c r="L115" s="104"/>
       <c r="M115" s="104"/>
       <c r="N115" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O115" s="107"/>
       <c r="P115" s="104"/>
@@ -30280,7 +30207,7 @@
       <c r="F120" s="104"/>
       <c r="G120" s="104"/>
       <c r="H120" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I120" s="104"/>
       <c r="J120" s="104"/>
@@ -30288,7 +30215,7 @@
       <c r="L120" s="104"/>
       <c r="M120" s="104"/>
       <c r="N120" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O120" s="107"/>
       <c r="P120" s="104"/>
@@ -30299,7 +30226,7 @@
     </row>
     <row r="121" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A121" s="56" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B121" s="56" t="s">
         <v>312</v>
@@ -30329,7 +30256,7 @@
         <v>259</v>
       </c>
       <c r="L121" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="M121" s="1" t="s">
         <v>55</v>
@@ -30350,7 +30277,7 @@
     </row>
     <row r="122" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="56" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B122" s="56" t="s">
         <v>312</v>
@@ -30661,7 +30588,7 @@
         <v>4500</v>
       </c>
       <c r="S127" s="6" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
     </row>
     <row r="128" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -30767,7 +30694,7 @@
         <v>4500</v>
       </c>
       <c r="S129" s="6" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="U129" s="143">
         <v>2676</v>
@@ -30879,7 +30806,7 @@
     </row>
     <row r="132" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B132" s="56" t="s">
         <v>312</v>
@@ -30931,7 +30858,7 @@
     </row>
     <row r="133" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B133" s="56" t="s">
         <v>312</v>
@@ -30983,7 +30910,7 @@
     </row>
     <row r="134" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A134" s="3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B134" s="56" t="s">
         <v>312</v>
@@ -31050,7 +30977,7 @@
       <c r="F135" s="104"/>
       <c r="G135" s="104"/>
       <c r="H135" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="I135" s="104"/>
       <c r="J135" s="104"/>
@@ -31058,7 +30985,7 @@
       <c r="L135" s="104"/>
       <c r="M135" s="104"/>
       <c r="N135" s="105" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="O135" s="107"/>
       <c r="P135" s="104"/>
@@ -31125,7 +31052,7 @@
     </row>
     <row r="137" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B137" t="s">
         <v>312</v>
@@ -31225,7 +31152,7 @@
         <v>1100</v>
       </c>
       <c r="S138" s="162" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
     </row>
     <row r="139" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -31330,7 +31257,7 @@
         <v>1100</v>
       </c>
       <c r="S140" s="162" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
     </row>
     <row r="141" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
@@ -31488,7 +31415,7 @@
     </row>
     <row r="144" spans="1:21" ht="40" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B144" t="s">
         <v>312</v>
@@ -31640,7 +31567,7 @@
         <v>380</v>
       </c>
       <c r="O1" s="11" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="P1" s="47" t="s">
         <v>381</v>
@@ -31792,7 +31719,7 @@
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A6" s="55" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B6" s="55" t="s">
         <v>312</v>
@@ -32004,7 +31931,7 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" s="55" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B10" s="55" t="s">
         <v>312</v>
@@ -32216,7 +32143,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" s="55" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="B14" s="55" t="s">
         <v>312</v>
@@ -32302,7 +32229,7 @@
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" s="24" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="B16" s="24" t="s">
         <v>312</v>
@@ -32365,7 +32292,7 @@
     </row>
     <row r="17" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A17" s="24" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="B17" s="24" t="s">
         <v>312</v>
@@ -32514,7 +32441,7 @@
     </row>
     <row r="20" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A20" s="55" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B20" s="55" t="s">
         <v>312</v>
@@ -32608,7 +32535,7 @@
     </row>
     <row r="23" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A23" s="55" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B23" s="55" t="s">
         <v>312</v>
@@ -32671,7 +32598,7 @@
     </row>
     <row r="24" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A24" s="55" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="B24" s="55" t="s">
         <v>312</v>
@@ -32734,7 +32661,7 @@
     </row>
     <row r="25" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A25" s="55" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B25" s="55" t="s">
         <v>312</v>
@@ -32797,7 +32724,7 @@
     </row>
     <row r="26" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A26" s="55" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="B26" s="55" t="s">
         <v>312</v>
@@ -32860,7 +32787,7 @@
     </row>
     <row r="27" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A27" s="55" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B27" s="55" t="s">
         <v>312</v>
@@ -32923,7 +32850,7 @@
     </row>
     <row r="28" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A28" s="55" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B28" s="55" t="s">
         <v>312</v>
@@ -33003,7 +32930,7 @@
     </row>
     <row r="31" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A31" s="85" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="B31" t="s">
         <v>312</v>
@@ -33067,7 +32994,7 @@
     </row>
     <row r="32" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A32" s="85" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B32" t="s">
         <v>312</v>
@@ -33131,7 +33058,7 @@
     </row>
     <row r="33" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="B33" t="s">
         <v>312</v>
@@ -33195,7 +33122,7 @@
     </row>
     <row r="34" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B34" t="s">
         <v>312</v>
@@ -33259,7 +33186,7 @@
     </row>
     <row r="35" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="B35" t="s">
         <v>312</v>
@@ -33323,7 +33250,7 @@
     </row>
     <row r="38" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B38" t="s">
         <v>312</v>
@@ -33386,7 +33313,7 @@
     </row>
     <row r="39" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="B39" t="s">
         <v>312</v>
@@ -33449,7 +33376,7 @@
     </row>
     <row r="40" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="B40" t="s">
         <v>312</v>
@@ -33512,7 +33439,7 @@
     </row>
     <row r="41" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="B41" t="s">
         <v>312</v>
@@ -33575,7 +33502,7 @@
     </row>
     <row r="42" spans="1:19" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="B42" t="s">
         <v>312</v>
@@ -34032,7 +33959,7 @@
     </row>
     <row r="55" spans="1:24" s="55" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A55" s="55" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="B55" s="116" t="s">
         <v>237</v>
@@ -34082,7 +34009,7 @@
     </row>
     <row r="56" spans="1:24" s="55" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A56" s="55" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B56" s="116" t="s">
         <v>237</v>
@@ -34189,7 +34116,7 @@
     </row>
     <row r="63" spans="1:24" x14ac:dyDescent="0.35">
       <c r="H63" s="166" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="I63" s="166"/>
       <c r="J63" s="166"/>
